--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1311,7 +1311,7 @@
     <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-02T12:47:46+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-02T17:00:07+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1311,7 +1311,7 @@
     <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-02T17:00:07+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-03T11:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1338,7 +1338,7 @@
     <t>模型B 命中率（简单平均口径）</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-02 ~ 2026-10-02）</t>
+    <t>近 30 天窗口（2026-09-03 ~ 2026-10-03）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1311,7 +1311,7 @@
     <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-03T11:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-03T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1311,7 +1311,7 @@
     <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-03T17:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-04T11:00:06+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1338,7 +1338,7 @@
     <t>模型B 命中率（简单平均口径）</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-03 ~ 2026-10-03）</t>
+    <t>近 30 天窗口（2026-09-04 ~ 2026-10-04）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1311,7 +1311,7 @@
     <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-04T11:00:06+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-04T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1311,7 +1311,7 @@
     <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-04T17:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-05T11:00:06+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1338,7 +1338,7 @@
     <t>模型B 命中率（简单平均口径）</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-04 ~ 2026-10-04）</t>
+    <t>近 30 天窗口（2026-09-05 ~ 2026-10-05）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="2026-09" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="差值明细" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="模型统计" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="编号统计" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="编号追踪" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="说明" state="visible" r:id="rId9"/>
+    <sheet sheetId="2" name="2026-10" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="差值明细" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="模型统计" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="编号统计" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="编号追踪" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="说明" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="566">
   <si>
     <t>日期</t>
   </si>
@@ -1284,6 +1285,21 @@
     <t>09-30 18:30</t>
   </si>
   <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>10-06 00:00</t>
+  </si>
+  <si>
+    <t>7+球</t>
+  </si>
+  <si>
+    <t>10-05 17:00</t>
+  </si>
+  <si>
+    <t>10-06 02:45</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1308,10 +1324,196 @@
     <t>比分(赔率)</t>
   </si>
   <si>
-    <t>（暂无差值明细：需在售期抓取到含比分矩阵的快照后自动出现）</t>
-  </si>
-  <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-05T11:00:06+08:00）</t>
+    <t>0球</t>
+  </si>
+  <si>
+    <t>0:0=10.5</t>
+  </si>
+  <si>
+    <t>1球</t>
+  </si>
+  <si>
+    <t>0:1=14 1:0=6</t>
+  </si>
+  <si>
+    <t>2球</t>
+  </si>
+  <si>
+    <t>0:2=35 1:1=7 2:0=6.5</t>
+  </si>
+  <si>
+    <t>3球</t>
+  </si>
+  <si>
+    <t>0:3=90 1:2=17 2:1=7 3:0=11</t>
+  </si>
+  <si>
+    <t>4球</t>
+  </si>
+  <si>
+    <t>0:4=350 1:3=55 2:2=19 3:1=13.5 4:0=23</t>
+  </si>
+  <si>
+    <t>5球</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=250 2:3=55 3:2=29 4:1=29 5:0=55</t>
+  </si>
+  <si>
+    <t>6球</t>
+  </si>
+  <si>
+    <t>1:5=800 2:4=300 3:3=90 4:2=70 5:1=70</t>
+  </si>
+  <si>
+    <t>2:5=800 5:2=175</t>
+  </si>
+  <si>
+    <t>0:0=25</t>
+  </si>
+  <si>
+    <t>0:1=23 1:0=10.5</t>
+  </si>
+  <si>
+    <t>0:2=38 1:1=9.5 2:0=8.5</t>
+  </si>
+  <si>
+    <t>0:3=90 1:2=16 2:1=7.2 3:0=11</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=40 2:2=15 3:1=10.5 4:0=17</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=175 2:3=38 3:2=19 4:1=17 5:0=33</t>
+  </si>
+  <si>
+    <t>1:5=450 2:4=150 3:3=45 4:2=32 5:1=33</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=55</t>
+  </si>
+  <si>
+    <t>0:0=20</t>
+  </si>
+  <si>
+    <t>0:1=9.5 1:0=17</t>
+  </si>
+  <si>
+    <t>0:2=9.5 1:1=8 2:0=28</t>
+  </si>
+  <si>
+    <t>0:3=15 1:2=7 2:1=13 3:0=50</t>
+  </si>
+  <si>
+    <t>0:4=33 1:3=11 2:2=13 3:1=28 4:0=150</t>
+  </si>
+  <si>
+    <t>0:5=80 1:4=24 2:3=19 3:2=28 4:1=70 5:0=350</t>
+  </si>
+  <si>
+    <t>1:5=55 2:4=35 3:3=45 4:2=80 5:1=250</t>
+  </si>
+  <si>
+    <t>2:5=80 5:2=300</t>
+  </si>
+  <si>
+    <t>0:0=23</t>
+  </si>
+  <si>
+    <t>0:1=26 1:0=10</t>
+  </si>
+  <si>
+    <t>0:2=50 1:1=10 2:0=8.25</t>
+  </si>
+  <si>
+    <t>0:3=100 1:2=20 2:1=6.5 3:0=9.25</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=60 2:2=17 3:1=9 4:0=18</t>
+  </si>
+  <si>
+    <t>0:5=700 1:4=150 2:3=52 3:2=19 4:1=17 5:0=36</t>
+  </si>
+  <si>
+    <t>1:5=450 2:4=150 3:3=50 4:2=31 5:1=32</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=50</t>
+  </si>
+  <si>
+    <t>0:0=7.5</t>
+  </si>
+  <si>
+    <t>0:1=7.5 1:0=6.25</t>
+  </si>
+  <si>
+    <t>0:2=14 1:1=5.75 2:0=11</t>
+  </si>
+  <si>
+    <t>0:3=38 1:2=9.75 2:1=8.5 3:0=24</t>
+  </si>
+  <si>
+    <t>0:4=150 1:3=30 2:2=18 3:1=21 4:0=70</t>
+  </si>
+  <si>
+    <t>0:5=350 1:4=100 2:3=50 3:2=38 4:1=70 5:0=250</t>
+  </si>
+  <si>
+    <t>1:5=350 2:4=150 3:3=90 4:2=100 5:1=250</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=350</t>
+  </si>
+  <si>
+    <t>0:0=16</t>
+  </si>
+  <si>
+    <t>0:1=18 1:0=7.5</t>
+  </si>
+  <si>
+    <t>0:2=37 1:1=9 2:0=7.25</t>
+  </si>
+  <si>
+    <t>0:3=100 1:2=16.5 2:1=6.75 3:0=11</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=44 2:2=16 3:1=11 4:0=21</t>
+  </si>
+  <si>
+    <t>0:5=750 1:4=175 2:3=45 3:2=20 4:1=20 5:0=45</t>
+  </si>
+  <si>
+    <t>1:5=550 2:4=175 3:3=65 4:2=42 5:1=45</t>
+  </si>
+  <si>
+    <t>2:5=550 5:2=90</t>
+  </si>
+  <si>
+    <t>0:0=14</t>
+  </si>
+  <si>
+    <t>0:1=9 1:0=11</t>
+  </si>
+  <si>
+    <t>0:2=12 1:1=6 2:0=17</t>
+  </si>
+  <si>
+    <t>0:3=23 1:2=7.5 2:1=9.5 3:0=33</t>
+  </si>
+  <si>
+    <t>0:4=50 1:3=17.5 2:2=13 3:1=21 4:0=90</t>
+  </si>
+  <si>
+    <t>0:5=150 1:4=42 2:3=25 3:2=27 4:1=70 5:0=300</t>
+  </si>
+  <si>
+    <t>1:5=100 2:4=60 3:3=45 4:2=80 5:1=250</t>
+  </si>
+  <si>
+    <t>2:5=200 5:2=300</t>
+  </si>
+  <si>
+    <t>进球数预测 · 模型统计（截至 2026-10-05T17:00:06+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1387,30 +1589,6 @@
   </si>
   <si>
     <t>第8</t>
-  </si>
-  <si>
-    <t>0球</t>
-  </si>
-  <si>
-    <t>1球</t>
-  </si>
-  <si>
-    <t>2球</t>
-  </si>
-  <si>
-    <t>3球</t>
-  </si>
-  <si>
-    <t>4球</t>
-  </si>
-  <si>
-    <t>5球</t>
-  </si>
-  <si>
-    <t>6球</t>
-  </si>
-  <si>
-    <t>7+球</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -1543,7 +1721,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="+0.000;-0.000;0.000"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1561,6 +1743,12 @@
     <font>
       <b/>
       <color rgb="FFB85C00"/>
+    </font>
+    <font>
+      <color rgb="FF107C41"/>
+    </font>
+    <font>
+      <color rgb="FFC00000"/>
     </font>
     <font>
       <b/>
@@ -1617,7 +1805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1628,15 +1816,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7950,7 +8146,429 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="9" max="14" width="10" customWidth="1"/>
+    <col min="15" max="16" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>425</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" t="s">
+        <v>426</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>425</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F4" t="s">
+        <v>426</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>425</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>425</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>425</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" t="s">
+        <v>426</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F8" t="s">
+        <v>426</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s">
+        <v>425</v>
+      </c>
+      <c r="P8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -7969,7 +8587,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -7978,30 +8596,1957 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F2" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8">
+        <v>-46.39</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="8">
+        <v>-33.45</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F3" s="9">
+        <v>4.4</v>
+      </c>
+      <c r="G3" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="9">
+        <v>10</v>
+      </c>
+      <c r="J3" s="12">
+        <v>-5.6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="G4" s="10">
+        <v>3.074</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.126</v>
+      </c>
+      <c r="I4" s="9">
+        <v>16.167</v>
+      </c>
+      <c r="J4" s="12">
+        <v>-12.967</v>
+      </c>
+      <c r="K4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" t="s">
+        <v>441</v>
+      </c>
+      <c r="F5" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="G5" s="10">
+        <v>3.293</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.507</v>
+      </c>
+      <c r="I5" s="9">
+        <v>31.25</v>
+      </c>
+      <c r="J5" s="12">
+        <v>-27.45</v>
+      </c>
+      <c r="K5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" t="s">
+        <v>443</v>
+      </c>
+      <c r="F6" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="G6" s="10">
+        <v>5.229</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.971</v>
+      </c>
+      <c r="I6" s="9">
+        <v>92.1</v>
+      </c>
+      <c r="J6" s="12">
+        <v>-85.9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F7" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="G7" s="10">
+        <v>9.064</v>
+      </c>
+      <c r="H7" s="11">
+        <v>3.436</v>
+      </c>
+      <c r="I7" s="9">
+        <v>236.333</v>
+      </c>
+      <c r="J7" s="12">
+        <v>-223.833</v>
+      </c>
+      <c r="K7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" t="s">
+        <v>447</v>
+      </c>
+      <c r="F8" s="9">
+        <v>25</v>
+      </c>
+      <c r="G8" s="10">
+        <v>22.591</v>
+      </c>
+      <c r="H8" s="11">
+        <v>2.409</v>
+      </c>
+      <c r="I8" s="9">
+        <v>266</v>
+      </c>
+      <c r="J8" s="12">
+        <v>-241</v>
+      </c>
+      <c r="K8" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" t="s">
         <v>424</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>430</v>
+      <c r="F9" s="9">
+        <v>40</v>
+      </c>
+      <c r="G9" s="10">
+        <v>143.59</v>
+      </c>
+      <c r="H9" s="13">
+        <v>-103.59</v>
+      </c>
+      <c r="I9" s="9">
+        <v>487.5</v>
+      </c>
+      <c r="J9" s="12">
+        <v>-447.5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="6">
+        <v>25</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8">
+        <v>-14.875</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="8">
+        <v>7.978</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" t="s">
+        <v>437</v>
+      </c>
+      <c r="F11" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="G11" s="10">
+        <v>7.209</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0.291</v>
+      </c>
+      <c r="I11" s="9">
+        <v>16.75</v>
+      </c>
+      <c r="J11" s="12">
+        <v>-9.25</v>
+      </c>
+      <c r="K11" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B12" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" t="s">
+        <v>439</v>
+      </c>
+      <c r="F12" s="9">
+        <v>4.35</v>
+      </c>
+      <c r="G12" s="10">
+        <v>4.012</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0.338</v>
+      </c>
+      <c r="I12" s="9">
+        <v>18.667</v>
+      </c>
+      <c r="J12" s="12">
+        <v>-14.317</v>
+      </c>
+      <c r="K12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" t="s">
+        <v>441</v>
+      </c>
+      <c r="F13" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="G13" s="10">
+        <v>3.296</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.304</v>
+      </c>
+      <c r="I13" s="9">
+        <v>31.05</v>
+      </c>
+      <c r="J13" s="12">
+        <v>-27.45</v>
+      </c>
+      <c r="K13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B14" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E14" t="s">
+        <v>443</v>
+      </c>
+      <c r="F14" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="G14" s="10">
+        <v>4.015</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.485</v>
+      </c>
+      <c r="I14" s="9">
+        <v>76.5</v>
+      </c>
+      <c r="J14" s="12">
+        <v>-72</v>
+      </c>
+      <c r="K14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C15" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E15" t="s">
+        <v>445</v>
+      </c>
+      <c r="F15" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="G15" s="10">
+        <v>5.713</v>
+      </c>
+      <c r="H15" s="11">
+        <v>1.087</v>
+      </c>
+      <c r="I15" s="9">
+        <v>180.333</v>
+      </c>
+      <c r="J15" s="12">
+        <v>-173.533</v>
+      </c>
+      <c r="K15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>422</v>
+      </c>
+      <c r="B16" t="s">
+        <v>377</v>
+      </c>
+      <c r="C16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" t="s">
+        <v>447</v>
+      </c>
+      <c r="F16" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="G16" s="10">
+        <v>10.792</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0.708</v>
+      </c>
+      <c r="I16" s="9">
+        <v>142</v>
+      </c>
+      <c r="J16" s="12">
+        <v>-130.5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>422</v>
+      </c>
+      <c r="B17" t="s">
+        <v>377</v>
+      </c>
+      <c r="C17" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17" t="s">
+        <v>424</v>
+      </c>
+      <c r="F17" s="9">
+        <v>15</v>
+      </c>
+      <c r="G17" s="10">
+        <v>49.01</v>
+      </c>
+      <c r="H17" s="13">
+        <v>-34.01</v>
+      </c>
+      <c r="I17" s="9">
+        <v>252.5</v>
+      </c>
+      <c r="J17" s="12">
+        <v>-237.5</v>
+      </c>
+      <c r="K17" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F18" s="6">
+        <v>20</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="8">
+        <v>-18.246</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="8">
+        <v>-16.05</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" t="s">
+        <v>261</v>
+      </c>
+      <c r="E19" t="s">
+        <v>437</v>
+      </c>
+      <c r="F19" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="G19" s="10">
+        <v>6.094</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0.706</v>
+      </c>
+      <c r="I19" s="9">
+        <v>13.25</v>
+      </c>
+      <c r="J19" s="12">
+        <v>-6.45</v>
+      </c>
+      <c r="K19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>422</v>
+      </c>
+      <c r="B20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" t="s">
+        <v>262</v>
+      </c>
+      <c r="D20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" t="s">
+        <v>439</v>
+      </c>
+      <c r="F20" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="G20" s="10">
+        <v>3.76</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0.44</v>
+      </c>
+      <c r="I20" s="9">
+        <v>15.167</v>
+      </c>
+      <c r="J20" s="12">
+        <v>-10.967</v>
+      </c>
+      <c r="K20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>422</v>
+      </c>
+      <c r="B21" t="s">
+        <v>379</v>
+      </c>
+      <c r="C21" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" t="s">
+        <v>441</v>
+      </c>
+      <c r="F21" s="9">
+        <v>3.4</v>
+      </c>
+      <c r="G21" s="10">
+        <v>3.263</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.137</v>
+      </c>
+      <c r="I21" s="9">
+        <v>21.25</v>
+      </c>
+      <c r="J21" s="12">
+        <v>-17.85</v>
+      </c>
+      <c r="K21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>422</v>
+      </c>
+      <c r="B22" t="s">
+        <v>379</v>
+      </c>
+      <c r="C22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" s="9">
+        <v>4.25</v>
+      </c>
+      <c r="G22" s="10">
+        <v>4.158</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.092</v>
+      </c>
+      <c r="I22" s="9">
+        <v>47</v>
+      </c>
+      <c r="J22" s="12">
+        <v>-42.75</v>
+      </c>
+      <c r="K22" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>422</v>
+      </c>
+      <c r="B23" t="s">
+        <v>379</v>
+      </c>
+      <c r="C23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" t="s">
+        <v>445</v>
+      </c>
+      <c r="F23" s="9">
+        <v>8</v>
+      </c>
+      <c r="G23" s="10">
+        <v>6.263</v>
+      </c>
+      <c r="H23" s="11">
+        <v>1.737</v>
+      </c>
+      <c r="I23" s="9">
+        <v>95.167</v>
+      </c>
+      <c r="J23" s="12">
+        <v>-87.167</v>
+      </c>
+      <c r="K23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>422</v>
+      </c>
+      <c r="B24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C24" t="s">
+        <v>262</v>
+      </c>
+      <c r="D24" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" t="s">
+        <v>447</v>
+      </c>
+      <c r="F24" s="9">
+        <v>15</v>
+      </c>
+      <c r="G24" s="10">
+        <v>11.699</v>
+      </c>
+      <c r="H24" s="11">
+        <v>3.301</v>
+      </c>
+      <c r="I24" s="9">
+        <v>93</v>
+      </c>
+      <c r="J24" s="12">
+        <v>-78</v>
+      </c>
+      <c r="K24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>422</v>
+      </c>
+      <c r="B25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>424</v>
+      </c>
+      <c r="F25" s="9">
+        <v>21</v>
+      </c>
+      <c r="G25" s="10">
+        <v>63.158</v>
+      </c>
+      <c r="H25" s="13">
+        <v>-42.158</v>
+      </c>
+      <c r="I25" s="9">
+        <v>190</v>
+      </c>
+      <c r="J25" s="12">
+        <v>-169</v>
+      </c>
+      <c r="K25" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F26" s="6">
+        <v>23</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="8">
+        <v>-12.554</v>
+      </c>
+      <c r="I26" s="6"/>
+      <c r="J26" s="8">
+        <v>0.87</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>422</v>
+      </c>
+      <c r="B27" t="s">
+        <v>381</v>
+      </c>
+      <c r="C27" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E27" t="s">
+        <v>437</v>
+      </c>
+      <c r="F27" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="G27" s="10">
+        <v>7.222</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.278</v>
+      </c>
+      <c r="I27" s="9">
+        <v>18</v>
+      </c>
+      <c r="J27" s="12">
+        <v>-10.5</v>
+      </c>
+      <c r="K27" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>422</v>
+      </c>
+      <c r="B28" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" t="s">
+        <v>258</v>
+      </c>
+      <c r="E28" t="s">
+        <v>439</v>
+      </c>
+      <c r="F28" s="9">
+        <v>4.4</v>
+      </c>
+      <c r="G28" s="10">
+        <v>4.146</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0.254</v>
+      </c>
+      <c r="I28" s="9">
+        <v>22.75</v>
+      </c>
+      <c r="J28" s="12">
+        <v>-18.35</v>
+      </c>
+      <c r="K28" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>422</v>
+      </c>
+      <c r="B29" t="s">
+        <v>381</v>
+      </c>
+      <c r="C29" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" t="s">
+        <v>258</v>
+      </c>
+      <c r="E29" t="s">
+        <v>441</v>
+      </c>
+      <c r="F29" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="G29" s="10">
+        <v>3.106</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.194</v>
+      </c>
+      <c r="I29" s="9">
+        <v>33.938</v>
+      </c>
+      <c r="J29" s="12">
+        <v>-30.638</v>
+      </c>
+      <c r="K29" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>422</v>
+      </c>
+      <c r="B30" t="s">
+        <v>381</v>
+      </c>
+      <c r="C30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" t="s">
+        <v>258</v>
+      </c>
+      <c r="E30" t="s">
+        <v>443</v>
+      </c>
+      <c r="F30" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="G30" s="10">
+        <v>4.073</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0.127</v>
+      </c>
+      <c r="I30" s="9">
+        <v>80.8</v>
+      </c>
+      <c r="J30" s="12">
+        <v>-76.6</v>
+      </c>
+      <c r="K30" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>422</v>
+      </c>
+      <c r="B31" t="s">
+        <v>381</v>
+      </c>
+      <c r="C31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" t="s">
+        <v>258</v>
+      </c>
+      <c r="E31" t="s">
+        <v>445</v>
+      </c>
+      <c r="F31" s="9">
+        <v>7.8</v>
+      </c>
+      <c r="G31" s="10">
+        <v>6.004</v>
+      </c>
+      <c r="H31" s="11">
+        <v>1.796</v>
+      </c>
+      <c r="I31" s="9">
+        <v>162.333</v>
+      </c>
+      <c r="J31" s="12">
+        <v>-154.533</v>
+      </c>
+      <c r="K31" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>422</v>
+      </c>
+      <c r="B32" t="s">
+        <v>381</v>
+      </c>
+      <c r="C32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E32" t="s">
+        <v>447</v>
+      </c>
+      <c r="F32" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="G32" s="10">
+        <v>10.823</v>
+      </c>
+      <c r="H32" s="11">
+        <v>2.677</v>
+      </c>
+      <c r="I32" s="9">
+        <v>142.6</v>
+      </c>
+      <c r="J32" s="12">
+        <v>-129.1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>422</v>
+      </c>
+      <c r="B33" t="s">
+        <v>381</v>
+      </c>
+      <c r="C33" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" t="s">
+        <v>258</v>
+      </c>
+      <c r="E33" t="s">
+        <v>424</v>
+      </c>
+      <c r="F33" s="9">
+        <v>17.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>45</v>
+      </c>
+      <c r="H33" s="13">
+        <v>-27.5</v>
+      </c>
+      <c r="I33" s="9">
+        <v>250</v>
+      </c>
+      <c r="J33" s="12">
+        <v>-232.5</v>
+      </c>
+      <c r="K33" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F34" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="8">
+        <v>-62.586</v>
+      </c>
+      <c r="I34" s="6"/>
+      <c r="J34" s="8">
+        <v>-54.309</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>422</v>
+      </c>
+      <c r="B35" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" t="s">
+        <v>437</v>
+      </c>
+      <c r="F35" s="9">
+        <v>3.45</v>
+      </c>
+      <c r="G35" s="10">
+        <v>3.409</v>
+      </c>
+      <c r="H35" s="11">
+        <v>0.041</v>
+      </c>
+      <c r="I35" s="9">
+        <v>6.875</v>
+      </c>
+      <c r="J35" s="12">
+        <v>-3.425</v>
+      </c>
+      <c r="K35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>422</v>
+      </c>
+      <c r="B36" t="s">
+        <v>383</v>
+      </c>
+      <c r="C36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" t="s">
+        <v>439</v>
+      </c>
+      <c r="F36" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="G36" s="10">
+        <v>2.974</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.226</v>
+      </c>
+      <c r="I36" s="9">
+        <v>10.25</v>
+      </c>
+      <c r="J36" s="12">
+        <v>-7.05</v>
+      </c>
+      <c r="K36" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>422</v>
+      </c>
+      <c r="B37" t="s">
+        <v>383</v>
+      </c>
+      <c r="C37" t="s">
+        <v>242</v>
+      </c>
+      <c r="D37" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37" t="s">
+        <v>441</v>
+      </c>
+      <c r="F37" s="9">
+        <v>4.05</v>
+      </c>
+      <c r="G37" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.58</v>
+      </c>
+      <c r="I37" s="9">
+        <v>20.063</v>
+      </c>
+      <c r="J37" s="12">
+        <v>-16.013</v>
+      </c>
+      <c r="K37" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>422</v>
+      </c>
+      <c r="B38" t="s">
+        <v>383</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" t="s">
+        <v>443</v>
+      </c>
+      <c r="F38" s="9">
+        <v>8.2</v>
+      </c>
+      <c r="G38" s="10">
+        <v>6.351</v>
+      </c>
+      <c r="H38" s="11">
+        <v>1.849</v>
+      </c>
+      <c r="I38" s="9">
+        <v>57.8</v>
+      </c>
+      <c r="J38" s="12">
+        <v>-49.6</v>
+      </c>
+      <c r="K38" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>422</v>
+      </c>
+      <c r="B39" t="s">
+        <v>383</v>
+      </c>
+      <c r="C39" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
+        <v>445</v>
+      </c>
+      <c r="F39" s="9">
+        <v>18</v>
+      </c>
+      <c r="G39" s="10">
+        <v>12.91</v>
+      </c>
+      <c r="H39" s="11">
+        <v>5.09</v>
+      </c>
+      <c r="I39" s="9">
+        <v>143</v>
+      </c>
+      <c r="J39" s="12">
+        <v>-125</v>
+      </c>
+      <c r="K39" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>422</v>
+      </c>
+      <c r="B40" t="s">
+        <v>383</v>
+      </c>
+      <c r="C40" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" t="s">
+        <v>447</v>
+      </c>
+      <c r="F40" s="9">
+        <v>36</v>
+      </c>
+      <c r="G40" s="10">
+        <v>28.873</v>
+      </c>
+      <c r="H40" s="11">
+        <v>7.127</v>
+      </c>
+      <c r="I40" s="9">
+        <v>188</v>
+      </c>
+      <c r="J40" s="12">
+        <v>-152</v>
+      </c>
+      <c r="K40" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>422</v>
+      </c>
+      <c r="B41" t="s">
+        <v>383</v>
+      </c>
+      <c r="C41" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" t="s">
+        <v>424</v>
+      </c>
+      <c r="F41" s="9">
+        <v>60</v>
+      </c>
+      <c r="G41" s="10">
+        <v>196.875</v>
+      </c>
+      <c r="H41" s="13">
+        <v>-136.875</v>
+      </c>
+      <c r="I41" s="9">
+        <v>400</v>
+      </c>
+      <c r="J41" s="12">
+        <v>-340</v>
+      </c>
+      <c r="K41" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F42" s="6">
+        <v>16</v>
+      </c>
+      <c r="G42" s="7"/>
+      <c r="H42" s="8">
+        <v>-22.878</v>
+      </c>
+      <c r="I42" s="6"/>
+      <c r="J42" s="8">
+        <v>-10.955</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>422</v>
+      </c>
+      <c r="B43" t="s">
+        <v>384</v>
+      </c>
+      <c r="C43" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" t="s">
+        <v>437</v>
+      </c>
+      <c r="F43" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="G43" s="10">
+        <v>5.294</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.506</v>
+      </c>
+      <c r="I43" s="9">
+        <v>12.75</v>
+      </c>
+      <c r="J43" s="12">
+        <v>-6.95</v>
+      </c>
+      <c r="K43" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>422</v>
+      </c>
+      <c r="B44" t="s">
+        <v>384</v>
+      </c>
+      <c r="C44" t="s">
+        <v>252</v>
+      </c>
+      <c r="D44" t="s">
+        <v>245</v>
+      </c>
+      <c r="E44" t="s">
+        <v>439</v>
+      </c>
+      <c r="F44" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="G44" s="10">
+        <v>3.622</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0.178</v>
+      </c>
+      <c r="I44" s="9">
+        <v>17.75</v>
+      </c>
+      <c r="J44" s="12">
+        <v>-13.95</v>
+      </c>
+      <c r="K44" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>422</v>
+      </c>
+      <c r="B45" t="s">
+        <v>384</v>
+      </c>
+      <c r="C45" t="s">
+        <v>252</v>
+      </c>
+      <c r="D45" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45" t="s">
+        <v>441</v>
+      </c>
+      <c r="F45" s="9">
+        <v>3.55</v>
+      </c>
+      <c r="G45" s="10">
+        <v>3.229</v>
+      </c>
+      <c r="H45" s="11">
+        <v>0.321</v>
+      </c>
+      <c r="I45" s="9">
+        <v>33.563</v>
+      </c>
+      <c r="J45" s="12">
+        <v>-30.013</v>
+      </c>
+      <c r="K45" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>422</v>
+      </c>
+      <c r="B46" t="s">
+        <v>384</v>
+      </c>
+      <c r="C46" t="s">
+        <v>252</v>
+      </c>
+      <c r="D46" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" t="s">
+        <v>443</v>
+      </c>
+      <c r="F46" s="9">
+        <v>5</v>
+      </c>
+      <c r="G46" s="10">
+        <v>4.404</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.596</v>
+      </c>
+      <c r="I46" s="9">
+        <v>78.4</v>
+      </c>
+      <c r="J46" s="12">
+        <v>-73.4</v>
+      </c>
+      <c r="K46" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>422</v>
+      </c>
+      <c r="B47" t="s">
+        <v>384</v>
+      </c>
+      <c r="C47" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" t="s">
+        <v>245</v>
+      </c>
+      <c r="E47" t="s">
+        <v>445</v>
+      </c>
+      <c r="F47" s="9">
+        <v>8.3</v>
+      </c>
+      <c r="G47" s="10">
+        <v>6.601</v>
+      </c>
+      <c r="H47" s="11">
+        <v>1.699</v>
+      </c>
+      <c r="I47" s="9">
+        <v>175.833</v>
+      </c>
+      <c r="J47" s="12">
+        <v>-167.533</v>
+      </c>
+      <c r="K47" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>422</v>
+      </c>
+      <c r="B48" t="s">
+        <v>384</v>
+      </c>
+      <c r="C48" t="s">
+        <v>252</v>
+      </c>
+      <c r="D48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48" t="s">
+        <v>447</v>
+      </c>
+      <c r="F48" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="G48" s="10">
+        <v>14.504</v>
+      </c>
+      <c r="H48" s="11">
+        <v>0.996</v>
+      </c>
+      <c r="I48" s="9">
+        <v>175.4</v>
+      </c>
+      <c r="J48" s="12">
+        <v>-159.9</v>
+      </c>
+      <c r="K48" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>422</v>
+      </c>
+      <c r="B49" t="s">
+        <v>384</v>
+      </c>
+      <c r="C49" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" t="s">
+        <v>424</v>
+      </c>
+      <c r="F49" s="9">
+        <v>25</v>
+      </c>
+      <c r="G49" s="10">
+        <v>77.344</v>
+      </c>
+      <c r="H49" s="13">
+        <v>-52.344</v>
+      </c>
+      <c r="I49" s="9">
+        <v>320</v>
+      </c>
+      <c r="J49" s="12">
+        <v>-295</v>
+      </c>
+      <c r="K49" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F50" s="6">
+        <v>14</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="8">
+        <v>-38.314</v>
+      </c>
+      <c r="I50" s="6"/>
+      <c r="J50" s="8">
+        <v>-34.05</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>422</v>
+      </c>
+      <c r="B51" t="s">
+        <v>385</v>
+      </c>
+      <c r="C51" t="s">
+        <v>256</v>
+      </c>
+      <c r="D51" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" t="s">
+        <v>437</v>
+      </c>
+      <c r="F51" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="G51" s="10">
+        <v>4.95</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="I51" s="9">
+        <v>10</v>
+      </c>
+      <c r="J51" s="12">
+        <v>-4.6</v>
+      </c>
+      <c r="K51" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>422</v>
+      </c>
+      <c r="B52" t="s">
+        <v>385</v>
+      </c>
+      <c r="C52" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" t="s">
+        <v>439</v>
+      </c>
+      <c r="F52" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="G52" s="10">
+        <v>3.238</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0.062</v>
+      </c>
+      <c r="I52" s="9">
+        <v>11.667</v>
+      </c>
+      <c r="J52" s="12">
+        <v>-8.367</v>
+      </c>
+      <c r="K52" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>422</v>
+      </c>
+      <c r="B53" t="s">
+        <v>385</v>
+      </c>
+      <c r="C53" t="s">
+        <v>256</v>
+      </c>
+      <c r="D53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" t="s">
+        <v>441</v>
+      </c>
+      <c r="F53" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="G53" s="10">
+        <v>3.201</v>
+      </c>
+      <c r="H53" s="11">
+        <v>0.299</v>
+      </c>
+      <c r="I53" s="9">
+        <v>18.25</v>
+      </c>
+      <c r="J53" s="12">
+        <v>-14.75</v>
+      </c>
+      <c r="K53" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>422</v>
+      </c>
+      <c r="B54" t="s">
+        <v>385</v>
+      </c>
+      <c r="C54" t="s">
+        <v>256</v>
+      </c>
+      <c r="D54" t="s">
+        <v>255</v>
+      </c>
+      <c r="E54" t="s">
+        <v>443</v>
+      </c>
+      <c r="F54" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="G54" s="10">
+        <v>4.699</v>
+      </c>
+      <c r="H54" s="11">
+        <v>0.801</v>
+      </c>
+      <c r="I54" s="9">
+        <v>38.3</v>
+      </c>
+      <c r="J54" s="12">
+        <v>-32.8</v>
+      </c>
+      <c r="K54" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>422</v>
+      </c>
+      <c r="B55" t="s">
+        <v>385</v>
+      </c>
+      <c r="C55" t="s">
+        <v>256</v>
+      </c>
+      <c r="D55" t="s">
+        <v>255</v>
+      </c>
+      <c r="E55" t="s">
+        <v>445</v>
+      </c>
+      <c r="F55" s="9">
+        <v>10</v>
+      </c>
+      <c r="G55" s="10">
+        <v>7.992</v>
+      </c>
+      <c r="H55" s="11">
+        <v>2.008</v>
+      </c>
+      <c r="I55" s="9">
+        <v>102.333</v>
+      </c>
+      <c r="J55" s="12">
+        <v>-92.333</v>
+      </c>
+      <c r="K55" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>422</v>
+      </c>
+      <c r="B56" t="s">
+        <v>385</v>
+      </c>
+      <c r="C56" t="s">
+        <v>256</v>
+      </c>
+      <c r="D56" t="s">
+        <v>255</v>
+      </c>
+      <c r="E56" t="s">
+        <v>447</v>
+      </c>
+      <c r="F56" s="9">
+        <v>21</v>
+      </c>
+      <c r="G56" s="10">
+        <v>15.293</v>
+      </c>
+      <c r="H56" s="11">
+        <v>5.707</v>
+      </c>
+      <c r="I56" s="9">
+        <v>107</v>
+      </c>
+      <c r="J56" s="12">
+        <v>-86</v>
+      </c>
+      <c r="K56" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>422</v>
+      </c>
+      <c r="B57" t="s">
+        <v>385</v>
+      </c>
+      <c r="C57" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57" t="s">
+        <v>255</v>
+      </c>
+      <c r="E57" t="s">
+        <v>424</v>
+      </c>
+      <c r="F57" s="9">
+        <v>34</v>
+      </c>
+      <c r="G57" s="10">
+        <v>120</v>
+      </c>
+      <c r="H57" s="13">
+        <v>-86</v>
+      </c>
+      <c r="I57" s="9">
+        <v>250</v>
+      </c>
+      <c r="J57" s="12">
+        <v>-216</v>
+      </c>
+      <c r="K57" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -8010,7 +10555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -8020,19 +10565,19 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>432</v>
+    <row r="1" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>433</v>
+        <v>500</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8040,7 +10585,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>434</v>
+        <v>501</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8048,44 +10593,44 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>435</v>
+        <v>502</v>
       </c>
       <c r="B6" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>437</v>
+        <v>504</v>
       </c>
       <c r="B7" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>438</v>
+        <v>505</v>
       </c>
       <c r="B8" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>439</v>
+        <v>506</v>
       </c>
       <c r="B9" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>440</v>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>441</v>
+        <v>508</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -8093,73 +10638,73 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>442</v>
+        <v>509</v>
       </c>
       <c r="B13" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>443</v>
+        <v>510</v>
       </c>
       <c r="B14" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>444</v>
+        <v>511</v>
       </c>
       <c r="B15" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>445</v>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>446</v>
+        <v>513</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>447</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>448</v>
+        <v>515</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>449</v>
+        <v>516</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>450</v>
+        <v>517</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>451</v>
+        <v>518</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>452</v>
+        <v>519</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>453</v>
+        <v>520</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>454</v>
+        <v>521</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>455</v>
+        <v>522</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>456</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>457</v>
+      <c r="A20" s="16" t="s">
+        <v>435</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>22</v>
@@ -8187,8 +10732,8 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>458</v>
+      <c r="A21" s="16" t="s">
+        <v>437</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>22</v>
@@ -8216,8 +10761,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>459</v>
+      <c r="A22" s="16" t="s">
+        <v>439</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>22</v>
@@ -8245,8 +10790,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>460</v>
+      <c r="A23" s="16" t="s">
+        <v>441</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>22</v>
@@ -8274,8 +10819,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>461</v>
+      <c r="A24" s="16" t="s">
+        <v>443</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>22</v>
@@ -8303,8 +10848,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>462</v>
+      <c r="A25" s="16" t="s">
+        <v>445</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>22</v>
@@ -8332,8 +10877,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>463</v>
+      <c r="A26" s="16" t="s">
+        <v>447</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>22</v>
@@ -8361,8 +10906,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>464</v>
+      <c r="A27" s="16" t="s">
+        <v>424</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>22</v>
@@ -8391,7 +10936,7 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>465</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -8400,7 +10945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -8411,33 +10956,33 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>466</v>
+        <v>525</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>467</v>
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>468</v>
+        <v>527</v>
       </c>
       <c r="B2">
         <v>330</v>
@@ -8463,7 +11008,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>469</v>
+        <v>528</v>
       </c>
       <c r="B3">
         <v>329</v>
@@ -8489,7 +11034,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>470</v>
+        <v>529</v>
       </c>
       <c r="B4">
         <v>320</v>
@@ -8515,7 +11060,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="B5">
         <v>312</v>
@@ -8541,7 +11086,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>472</v>
+        <v>531</v>
       </c>
       <c r="B6">
         <v>304</v>
@@ -8567,7 +11112,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>473</v>
+        <v>532</v>
       </c>
       <c r="B7">
         <v>286</v>
@@ -8593,7 +11138,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>474</v>
+        <v>533</v>
       </c>
       <c r="B8">
         <v>277</v>
@@ -8619,7 +11164,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>475</v>
+        <v>534</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -8645,7 +11190,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>476</v>
+        <v>535</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -8671,7 +11216,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>477</v>
+        <v>536</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -8693,322 +11238,6 @@
       </c>
       <c r="H11">
         <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="C5" s="9">
-        <v>34</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="E5" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B9" s="3">
-        <v>3</v>
-      </c>
-      <c r="C9" s="11">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>6</v>
-      </c>
-      <c r="G9" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="B10" s="3">
-        <v>5</v>
-      </c>
-      <c r="C10" s="3">
-        <v>14</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3</v>
-      </c>
-      <c r="F10" s="11">
-        <v>18</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B11" s="11">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <v>28</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="B12" s="12">
-        <v>34</v>
-      </c>
-      <c r="C12" s="3">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B13" s="3">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>8</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>9</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="B14" s="3">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3">
-        <v>4</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="B15" s="11">
-        <v>19</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>14</v>
-      </c>
-      <c r="G16" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B17" s="11">
-        <v>26</v>
-      </c>
-      <c r="C17" s="3">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11">
-        <v>27</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2</v>
-      </c>
-      <c r="C18" s="11">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
-        <v>6</v>
-      </c>
-      <c r="G18" s="3">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9019,15 +11248,331 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" s="17">
+        <v>34</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="E5" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3</v>
+      </c>
+      <c r="C9" s="19">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B10" s="3">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3</v>
+      </c>
+      <c r="F10" s="19">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B11" s="19">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="19">
+        <v>28</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B12" s="20">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B13" s="3">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>9</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B14" s="3">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B15" s="19">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B17" s="19">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="19">
+        <v>27</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+      <c r="C18" s="19">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>6</v>
+      </c>
+      <c r="G18" s="3">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>485</v>
+    <row r="1" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -9035,49 +11580,49 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>486</v>
+    <row r="3" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>487</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>489</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>491</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>492</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>493</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>494</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -9085,34 +11630,34 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>495</v>
+    <row r="13" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>496</v>
+        <v>555</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>497</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>498</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>499</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>500</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -9120,24 +11665,24 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>501</v>
+    <row r="20" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>502</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>503</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>504</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -9145,14 +11690,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>505</v>
+    <row r="25" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>506</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -8,16 +8,17 @@
     <sheet sheetId="2" name="2026-10" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="差值明细" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="模型统计" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="编号统计" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="编号追踪" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="说明" state="visible" r:id="rId10"/>
+    <sheet sheetId="5" name="模拟投注" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="编号统计" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="编号追踪" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="说明" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="601">
   <si>
     <t>日期</t>
   </si>
@@ -1516,7 +1517,7 @@
     <t>2:5=200 5:2=300 负其他=60 平其他=300 胜其他=80</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-05T21:22:58+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-05T21:31:59+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1597,6 +1598,87 @@
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
   </si>
   <si>
+    <t>模拟投注：每场固定 100 元押"预测的进球数"；猜中按该场最后一次记录的该进球数赔率返还（口径与网页一致，可在 config.json 的 bet.stake 调整金额）</t>
+  </si>
+  <si>
+    <t>汇总</t>
+  </si>
+  <si>
+    <t>轨道</t>
+  </si>
+  <si>
+    <t>投注场次</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>总投入</t>
+  </si>
+  <si>
+    <t>总回报</t>
+  </si>
+  <si>
+    <t>净盈亏</t>
+  </si>
+  <si>
+    <t>回报率</t>
+  </si>
+  <si>
+    <t>模型A（自修正）</t>
+  </si>
+  <si>
+    <t>基线A（差值最小项）</t>
+  </si>
+  <si>
+    <t>模型B（对照）</t>
+  </si>
+  <si>
+    <t>逐场明细（模型A 为主，另列其他轨道盈亏；累计为模型A）</t>
+  </si>
+  <si>
+    <t>预测A</t>
+  </si>
+  <si>
+    <t>赔率A</t>
+  </si>
+  <si>
+    <t>模型A盈亏</t>
+  </si>
+  <si>
+    <t>模型A累计</t>
+  </si>
+  <si>
+    <t>基线A盈亏</t>
+  </si>
+  <si>
+    <t>模型B盈亏</t>
+  </si>
+  <si>
+    <t>（暂无：需完整比分池快照 + 已冻结预测 + 已出赛果）</t>
+  </si>
+  <si>
+    <t>逐日汇总</t>
+  </si>
+  <si>
+    <t>场次</t>
+  </si>
+  <si>
+    <t>当日(模型A)</t>
+  </si>
+  <si>
+    <t>累计(模型A)</t>
+  </si>
+  <si>
+    <t>累计(基线A)</t>
+  </si>
+  <si>
+    <t>累计(模型B)</t>
+  </si>
+  <si>
+    <t>（暂无）</t>
+  </si>
+  <si>
     <t>出现天数</t>
   </si>
   <si>
@@ -1709,6 +1791,18 @@
   </si>
   <si>
     <t xml:space="preserve">  每场比赛的预测在其赛果落定时冻结（只使用该场之前的数据，杜绝未来数据泄漏），两轨同场对比。</t>
+  </si>
+  <si>
+    <t>【模拟投注】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 每场固定投入（config.json 的 bet.stake，默认 100 元）押"预测的进球数"（三条轨道分别统计：模型A/基线A/模型B）；</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 猜中按该场【最后一次记录】的该进球数赔率返还，未中损失本金；</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 「模拟投注」表含：汇总、逐场明细（含累计盈亏）、逐日汇总；网页统计页有对应的每日盈亏图。</t>
   </si>
   <si>
     <t>【数据口径】</t>
@@ -1733,12 +1827,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="+0.000;-0.000;0.000"/>
     <numFmt numFmtId="166" formatCode="+0.0;-0.0;0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1770,6 +1865,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF107C41"/>
     </font>
     <font>
       <b/>
@@ -1815,7 +1914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1839,11 +1938,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -10890,6 +10991,203 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>535</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18">
+        <v>0</v>
+      </c>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="9" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -10902,7 +11200,7 @@
         <v>429</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>428</v>
@@ -10920,12 +11218,12 @@
         <v>427</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>527</v>
+        <v>554</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="B2">
         <v>330</v>
@@ -10951,7 +11249,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="B3">
         <v>329</v>
@@ -10977,7 +11275,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="B4">
         <v>320</v>
@@ -11003,7 +11301,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="B5">
         <v>312</v>
@@ -11029,7 +11327,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="B6">
         <v>304</v>
@@ -11055,7 +11353,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="B7">
         <v>286</v>
@@ -11081,7 +11379,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="B8">
         <v>277</v>
@@ -11107,7 +11405,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -11133,7 +11431,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -11159,7 +11457,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -11189,7 +11487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -11199,12 +11497,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>538</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11215,35 +11513,35 @@
         <v>430</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>540</v>
+        <v>567</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>541</v>
+        <v>568</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>531</v>
-      </c>
-      <c r="B5" s="18" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="20">
         <v>34</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>543</v>
-      </c>
-      <c r="E5" s="18">
+      <c r="D5" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="E5" s="20">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>544</v>
+    <row r="7" spans="1:1" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11266,17 +11564,17 @@
         <v>427</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>527</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="22">
         <v>21</v>
       </c>
       <c r="D9" s="3">
@@ -11294,7 +11592,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
@@ -11308,7 +11606,7 @@
       <c r="E10" s="3">
         <v>3</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <v>18</v>
       </c>
       <c r="G10" s="3">
@@ -11317,9 +11615,9 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B11" s="20">
+        <v>557</v>
+      </c>
+      <c r="B11" s="22">
         <v>21</v>
       </c>
       <c r="C11" s="3">
@@ -11331,7 +11629,7 @@
       <c r="E11" s="3">
         <v>0</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="22">
         <v>28</v>
       </c>
       <c r="G11" s="3">
@@ -11340,9 +11638,9 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="B12" s="21">
+        <v>558</v>
+      </c>
+      <c r="B12" s="23">
         <v>34</v>
       </c>
       <c r="C12" s="3">
@@ -11351,7 +11649,7 @@
       <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <v>25</v>
       </c>
       <c r="F12" s="3">
@@ -11363,7 +11661,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="B13" s="3">
         <v>13</v>
@@ -11386,7 +11684,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="B14" s="3">
         <v>13</v>
@@ -11409,9 +11707,9 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="B15" s="20">
+        <v>561</v>
+      </c>
+      <c r="B15" s="22">
         <v>19</v>
       </c>
       <c r="C15" s="3">
@@ -11432,7 +11730,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -11455,9 +11753,9 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="B17" s="20">
+        <v>563</v>
+      </c>
+      <c r="B17" s="22">
         <v>26</v>
       </c>
       <c r="C17" s="3">
@@ -11469,7 +11767,7 @@
       <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="22">
         <v>27</v>
       </c>
       <c r="G17" s="3">
@@ -11478,12 +11776,12 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="22">
         <v>19</v>
       </c>
       <c r="D18" s="3">
@@ -11505,9 +11803,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
@@ -11515,7 +11813,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -11525,62 +11823,62 @@
     </row>
     <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>546</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>547</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>549</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>550</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>551</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>552</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>554</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -11590,32 +11888,32 @@
     </row>
     <row r="16" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>559</v>
+        <v>586</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -11625,22 +11923,22 @@
     </row>
     <row r="23" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>564</v>
+        <v>591</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>565</v>
+        <v>592</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -11650,12 +11948,37 @@
     </row>
     <row r="28" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>569</v>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="608">
   <si>
     <t>日期</t>
   </si>
@@ -1289,22 +1289,37 @@
     <t>10-06 00:00</t>
   </si>
   <si>
+    <t>3球</t>
+  </si>
+  <si>
     <t>2球</t>
   </si>
   <si>
+    <t>0球</t>
+  </si>
+  <si>
+    <t>1球</t>
+  </si>
+  <si>
+    <t>✗</t>
+  </si>
+  <si>
     <t>10-05 17:00</t>
   </si>
   <si>
+    <t>10-06 11:00</t>
+  </si>
+  <si>
     <t>10-06 02:45</t>
   </si>
   <si>
-    <t>1球</t>
+    <t>5球</t>
   </si>
   <si>
     <t>4球</t>
   </si>
   <si>
-    <t>0球</t>
+    <t>✓</t>
   </si>
   <si>
     <t>编号</t>
@@ -1346,18 +1361,12 @@
     <t>0:2=35 1:1=7 2:0=6.5</t>
   </si>
   <si>
-    <t>3球</t>
-  </si>
-  <si>
     <t>0:3=90 1:2=17 2:1=7 3:0=11</t>
   </si>
   <si>
     <t>0:4=350 1:3=55 2:2=19 3:1=13.5 4:0=23</t>
   </si>
   <si>
-    <t>5球</t>
-  </si>
-  <si>
     <t>0:5=1000 1:4=250 2:3=55 3:2=29 4:1=29 5:0=55</t>
   </si>
   <si>
@@ -1517,7 +1526,7 @@
     <t>2:5=200 5:2=300 负其他=60 平其他=300 胜其他=80</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-05T21:31:59+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-06T11:00:08+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1532,7 +1541,7 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>—</t>
+    <t>2/7 = 28.6%</t>
   </si>
   <si>
     <t>模型A 命中率（自修正）</t>
@@ -1544,7 +1553,7 @@
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-05 ~ 2026-10-05）</t>
+    <t>近 30 天窗口（2026-09-06 ~ 2026-10-06）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>
@@ -1565,7 +1574,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>0 场（另剔除爆冷 0 场）</t>
+    <t>5 场（另剔除爆冷 2 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -1595,6 +1604,24 @@
     <t>第8</t>
   </si>
   <si>
+    <t>100% (1/1)</t>
+  </si>
+  <si>
+    <t>0% (0/1)</t>
+  </si>
+  <si>
+    <t>0% (0/3)</t>
+  </si>
+  <si>
+    <t>0% (0/2)</t>
+  </si>
+  <si>
+    <t>50% (1/2)</t>
+  </si>
+  <si>
+    <t>0% (0/4)</t>
+  </si>
+  <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
   </si>
   <si>
@@ -1655,9 +1682,6 @@
     <t>模型B盈亏</t>
   </si>
   <si>
-    <t>（暂无：需完整比分池快照 + 已冻结预测 + 已出赛果）</t>
-  </si>
-  <si>
     <t>逐日汇总</t>
   </si>
   <si>
@@ -1676,9 +1700,6 @@
     <t>累计(模型B)</t>
   </si>
   <si>
-    <t>（暂无）</t>
-  </si>
-  <si>
     <t>出现天数</t>
   </si>
   <si>
@@ -1715,7 +1736,7 @@
     <t>010</t>
   </si>
   <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-30，警戒线 30 次）</t>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-05，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -1827,13 +1848,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="+0.000;-0.000;0.000"/>
     <numFmt numFmtId="166" formatCode="+0.0;-0.0;0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1853,6 +1875,13 @@
       <color rgb="FFB85C00"/>
     </font>
     <font>
+      <color rgb="FFC00000"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF107C41"/>
+    </font>
+    <font>
       <color rgb="FF107C41"/>
     </font>
     <font>
@@ -1865,10 +1894,6 @@
     </font>
     <font>
       <b/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF107C41"/>
     </font>
     <font>
       <b/>
@@ -1914,7 +1939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1925,26 +1950,35 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7984,28 +8018,28 @@
         <v>55</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
+        <v>426</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -8025,34 +8059,34 @@
         <v>248</v>
       </c>
       <c r="F3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>426</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>21</v>
+        <v>426</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -8072,34 +8106,34 @@
         <v>260</v>
       </c>
       <c r="F4" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
-        <v>21</v>
+      <c r="M4" s="7" t="s">
+        <v>433</v>
       </c>
       <c r="N4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -8119,34 +8153,34 @@
         <v>257</v>
       </c>
       <c r="F5" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>21</v>
+      <c r="M5" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -8166,34 +8200,34 @@
         <v>240</v>
       </c>
       <c r="F6" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="N6" t="s">
         <v>428</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" t="s">
-        <v>424</v>
-      </c>
       <c r="O6" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -8213,34 +8247,34 @@
         <v>244</v>
       </c>
       <c r="F7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>21</v>
+        <v>426</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N7" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -8260,34 +8294,34 @@
         <v>254</v>
       </c>
       <c r="F8" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
+        <v>426</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>433</v>
       </c>
       <c r="N8" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -8320,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -8329,31 +8363,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -8370,23 +8404,23 @@
         <v>245</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F2" s="6">
+        <v>425</v>
+      </c>
+      <c r="F2" s="8">
         <v>10.5</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8">
+      <c r="G2" s="9"/>
+      <c r="H2" s="10">
         <v>1.003</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="8">
+      <c r="I2" s="11"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="10">
         <v>-5</v>
       </c>
-      <c r="L2" s="9"/>
+      <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -8405,29 +8439,29 @@
       <c r="E3" t="s">
         <v>426</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="12">
         <v>4.4</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="13">
         <v>4.2</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="14">
         <v>0.2</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="15">
         <v>4.8</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="12">
         <v>10</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="16">
         <v>-5.6</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="15">
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -8444,31 +8478,31 @@
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>423</v>
-      </c>
-      <c r="F4" s="10">
+        <v>424</v>
+      </c>
+      <c r="F4" s="12">
         <v>3.2</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="13">
         <v>3.074</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="14">
         <v>0.126</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="15">
         <v>4.1</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="12">
         <v>16.167</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="16">
         <v>-12.967</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="15">
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -8485,31 +8519,31 @@
         <v>245</v>
       </c>
       <c r="E5" t="s">
-        <v>442</v>
-      </c>
-      <c r="F5" s="10">
+        <v>423</v>
+      </c>
+      <c r="F5" s="12">
         <v>3.8</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="13">
         <v>3.293</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="14">
         <v>0.507</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="15">
         <v>15.4</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="12">
         <v>31.25</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="16">
         <v>-27.45</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="15">
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -8526,31 +8560,31 @@
         <v>245</v>
       </c>
       <c r="E6" t="s">
-        <v>427</v>
-      </c>
-      <c r="F6" s="10">
+        <v>432</v>
+      </c>
+      <c r="F6" s="12">
         <v>6.2</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="13">
         <v>5.229</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="14">
         <v>0.971</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="15">
         <v>18.6</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="12">
         <v>92.1</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="16">
         <v>-85.9</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="15">
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -8567,31 +8601,31 @@
         <v>245</v>
       </c>
       <c r="E7" t="s">
-        <v>445</v>
-      </c>
-      <c r="F7" s="10">
+        <v>431</v>
+      </c>
+      <c r="F7" s="12">
         <v>12.5</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="13">
         <v>9.064</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="14">
         <v>3.436</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="15">
         <v>37.9</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="12">
         <v>236.333</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="16">
         <v>-223.833</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="15">
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -8608,31 +8642,31 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>447</v>
-      </c>
-      <c r="F8" s="10">
+        <v>450</v>
+      </c>
+      <c r="F8" s="12">
         <v>25</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="13">
         <v>22.591</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="14">
         <v>2.409</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="15">
         <v>10.7</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="12">
         <v>266</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="16">
         <v>-241</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="15">
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8649,31 +8683,31 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>449</v>
-      </c>
-      <c r="F9" s="10">
+        <v>452</v>
+      </c>
+      <c r="F9" s="12">
         <v>40</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="13">
         <v>33.006</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="14">
         <v>6.994</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="15">
         <v>21.2</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="12">
         <v>376</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="16">
         <v>-336</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="15">
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -8690,23 +8724,23 @@
         <v>248</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F10" s="6">
+        <v>425</v>
+      </c>
+      <c r="F10" s="8">
         <v>25</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8">
+      <c r="G10" s="9"/>
+      <c r="H10" s="10">
         <v>1.448</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="8">
+      <c r="I10" s="11"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="10">
         <v>-5</v>
       </c>
-      <c r="L10" s="9"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8725,29 +8759,29 @@
       <c r="E11" t="s">
         <v>426</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="12">
         <v>7.5</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="13">
         <v>7.209</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="14">
         <v>0.291</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="15">
         <v>4</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="12">
         <v>16.75</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="16">
         <v>-9.25</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="15">
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8764,31 +8798,31 @@
         <v>248</v>
       </c>
       <c r="E12" t="s">
-        <v>423</v>
-      </c>
-      <c r="F12" s="10">
+        <v>424</v>
+      </c>
+      <c r="F12" s="12">
         <v>4.35</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="13">
         <v>4.012</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="14">
         <v>0.338</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="15">
         <v>8.4</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="12">
         <v>18.667</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="16">
         <v>-14.317</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="15">
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8805,31 +8839,31 @@
         <v>248</v>
       </c>
       <c r="E13" t="s">
-        <v>442</v>
-      </c>
-      <c r="F13" s="10">
+        <v>423</v>
+      </c>
+      <c r="F13" s="12">
         <v>3.6</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="13">
         <v>3.296</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="14">
         <v>0.304</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="15">
         <v>9.2</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="12">
         <v>31.05</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="16">
         <v>-27.45</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="15">
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8846,31 +8880,31 @@
         <v>248</v>
       </c>
       <c r="E14" t="s">
-        <v>427</v>
-      </c>
-      <c r="F14" s="10">
+        <v>432</v>
+      </c>
+      <c r="F14" s="12">
         <v>4.5</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="13">
         <v>4.015</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="14">
         <v>0.485</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="15">
         <v>12.1</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="12">
         <v>76.5</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="16">
         <v>-72</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="15">
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8887,31 +8921,31 @@
         <v>248</v>
       </c>
       <c r="E15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F15" s="10">
+        <v>431</v>
+      </c>
+      <c r="F15" s="12">
         <v>6.8</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="13">
         <v>5.713</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="14">
         <v>1.087</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="15">
         <v>19</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="12">
         <v>180.333</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="16">
         <v>-173.533</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="15">
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8928,31 +8962,31 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>447</v>
-      </c>
-      <c r="F16" s="10">
+        <v>450</v>
+      </c>
+      <c r="F16" s="12">
         <v>11.5</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="13">
         <v>10.792</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="14">
         <v>0.708</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="15">
         <v>6.6</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="12">
         <v>142</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="16">
         <v>-130.5</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="15">
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8969,31 +9003,31 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>449</v>
-      </c>
-      <c r="F17" s="10">
+        <v>452</v>
+      </c>
+      <c r="F17" s="12">
         <v>15</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="13">
         <v>10.922</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="14">
         <v>4.078</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="15">
         <v>37.3</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="12">
         <v>178.4</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="16">
         <v>-163.4</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="15">
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9010,23 +9044,23 @@
         <v>260</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F18" s="6">
+        <v>425</v>
+      </c>
+      <c r="F18" s="8">
         <v>20</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8">
+      <c r="G18" s="9"/>
+      <c r="H18" s="10">
         <v>2.341</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="8">
+      <c r="I18" s="11"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="10">
         <v>-5</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -9045,29 +9079,29 @@
       <c r="E19" t="s">
         <v>426</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="12">
         <v>6.8</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="13">
         <v>6.094</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="14">
         <v>0.706</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="15">
         <v>11.6</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="12">
         <v>13.25</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="16">
         <v>-6.45</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="15">
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -9084,31 +9118,31 @@
         <v>260</v>
       </c>
       <c r="E20" t="s">
-        <v>423</v>
-      </c>
-      <c r="F20" s="10">
+        <v>424</v>
+      </c>
+      <c r="F20" s="12">
         <v>4.2</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="13">
         <v>3.76</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="14">
         <v>0.44</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="15">
         <v>11.7</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="12">
         <v>15.167</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="16">
         <v>-10.967</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="15">
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -9125,31 +9159,31 @@
         <v>260</v>
       </c>
       <c r="E21" t="s">
-        <v>442</v>
-      </c>
-      <c r="F21" s="10">
+        <v>423</v>
+      </c>
+      <c r="F21" s="12">
         <v>3.4</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="13">
         <v>3.263</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="14">
         <v>0.137</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="15">
         <v>4.2</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="12">
         <v>21.25</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="16">
         <v>-17.85</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="15">
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -9166,31 +9200,31 @@
         <v>260</v>
       </c>
       <c r="E22" t="s">
-        <v>427</v>
-      </c>
-      <c r="F22" s="10">
+        <v>432</v>
+      </c>
+      <c r="F22" s="12">
         <v>4.25</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="13">
         <v>4.158</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="14">
         <v>0.092</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="15">
         <v>2.2</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="12">
         <v>47</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="16">
         <v>-42.75</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="15">
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -9207,31 +9241,31 @@
         <v>260</v>
       </c>
       <c r="E23" t="s">
-        <v>445</v>
-      </c>
-      <c r="F23" s="10">
+        <v>431</v>
+      </c>
+      <c r="F23" s="12">
         <v>8</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="13">
         <v>6.263</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="14">
         <v>1.737</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="15">
         <v>27.7</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="12">
         <v>95.167</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="16">
         <v>-87.167</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="15">
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -9248,31 +9282,31 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>447</v>
-      </c>
-      <c r="F24" s="10">
+        <v>450</v>
+      </c>
+      <c r="F24" s="12">
         <v>15</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="13">
         <v>11.699</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="14">
         <v>3.301</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="15">
         <v>28.2</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="12">
         <v>93</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="16">
         <v>-78</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="15">
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -9289,31 +9323,31 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>449</v>
-      </c>
-      <c r="F25" s="10">
-        <v>21</v>
-      </c>
-      <c r="G25" s="11">
+        <v>452</v>
+      </c>
+      <c r="F25" s="12">
+        <v>21</v>
+      </c>
+      <c r="G25" s="13">
         <v>15.12</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="14">
         <v>5.88</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="15">
         <v>38.9</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="12">
         <v>131.6</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="16">
         <v>-110.6</v>
       </c>
-      <c r="L25" s="13">
+      <c r="L25" s="15">
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9330,23 +9364,23 @@
         <v>257</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F26" s="6">
+        <v>425</v>
+      </c>
+      <c r="F26" s="8">
         <v>23</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8">
+      <c r="G26" s="9"/>
+      <c r="H26" s="10">
         <v>1.976</v>
       </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="8">
+      <c r="I26" s="11"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="10">
         <v>-5</v>
       </c>
-      <c r="L26" s="9"/>
+      <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -9365,29 +9399,29 @@
       <c r="E27" t="s">
         <v>426</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="12">
         <v>7.5</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="13">
         <v>7.222</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="14">
         <v>0.278</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="15">
         <v>3.9</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="12">
         <v>18</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="16">
         <v>-10.5</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="15">
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -9404,31 +9438,31 @@
         <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>423</v>
-      </c>
-      <c r="F28" s="10">
+        <v>424</v>
+      </c>
+      <c r="F28" s="12">
         <v>4.4</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="13">
         <v>4.146</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="14">
         <v>0.254</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="15">
         <v>6.1</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="12">
         <v>22.75</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="16">
         <v>-18.35</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="15">
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -9445,31 +9479,31 @@
         <v>257</v>
       </c>
       <c r="E29" t="s">
-        <v>442</v>
-      </c>
-      <c r="F29" s="10">
+        <v>423</v>
+      </c>
+      <c r="F29" s="12">
         <v>3.3</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="13">
         <v>3.106</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="14">
         <v>0.194</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="15">
         <v>6.3</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="12">
         <v>33.938</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="16">
         <v>-30.638</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="15">
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -9486,31 +9520,31 @@
         <v>257</v>
       </c>
       <c r="E30" t="s">
-        <v>427</v>
-      </c>
-      <c r="F30" s="10">
+        <v>432</v>
+      </c>
+      <c r="F30" s="12">
         <v>4.2</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="13">
         <v>4.073</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="14">
         <v>0.127</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="15">
         <v>3.1</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="12">
         <v>80.8</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="16">
         <v>-76.6</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="15">
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -9527,31 +9561,31 @@
         <v>257</v>
       </c>
       <c r="E31" t="s">
-        <v>445</v>
-      </c>
-      <c r="F31" s="10">
+        <v>431</v>
+      </c>
+      <c r="F31" s="12">
         <v>7.8</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="13">
         <v>6.004</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="14">
         <v>1.796</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="15">
         <v>29.9</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="12">
         <v>162.333</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="16">
         <v>-154.533</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="15">
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -9568,31 +9602,31 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>447</v>
-      </c>
-      <c r="F32" s="10">
+        <v>450</v>
+      </c>
+      <c r="F32" s="12">
         <v>13.5</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="13">
         <v>10.823</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="14">
         <v>2.677</v>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="15">
         <v>24.7</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="12">
         <v>142.6</v>
       </c>
-      <c r="K32" s="14">
+      <c r="K32" s="16">
         <v>-129.1</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="15">
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -9609,31 +9643,31 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>449</v>
-      </c>
-      <c r="F33" s="10">
+        <v>452</v>
+      </c>
+      <c r="F33" s="12">
         <v>17.5</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="13">
         <v>11.097</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="14">
         <v>6.403</v>
       </c>
-      <c r="I33" s="13">
+      <c r="I33" s="15">
         <v>57.7</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="12">
         <v>177.6</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="16">
         <v>-160.1</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="15">
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9650,23 +9684,23 @@
         <v>240</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F34" s="6">
+        <v>425</v>
+      </c>
+      <c r="F34" s="8">
         <v>7.5</v>
       </c>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8">
+      <c r="G34" s="9"/>
+      <c r="H34" s="10">
         <v>-0.957</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="8">
+      <c r="I34" s="11"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="10">
         <v>-2.975</v>
       </c>
-      <c r="L34" s="9"/>
+      <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -9685,29 +9719,29 @@
       <c r="E35" t="s">
         <v>426</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="12">
         <v>3.45</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="13">
         <v>3.409</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="14">
         <v>0.041</v>
       </c>
-      <c r="I35" s="13">
+      <c r="I35" s="15">
         <v>1.2</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="12">
         <v>6.875</v>
       </c>
-      <c r="K35" s="14">
+      <c r="K35" s="16">
         <v>-3.425</v>
       </c>
-      <c r="L35" s="13">
+      <c r="L35" s="15">
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -9724,31 +9758,31 @@
         <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>423</v>
-      </c>
-      <c r="F36" s="10">
+        <v>424</v>
+      </c>
+      <c r="F36" s="12">
         <v>3.2</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="13">
         <v>2.974</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="14">
         <v>0.226</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="15">
         <v>7.6</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J36" s="12">
         <v>10.25</v>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="16">
         <v>-7.05</v>
       </c>
-      <c r="L36" s="13">
+      <c r="L36" s="15">
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -9765,31 +9799,31 @@
         <v>240</v>
       </c>
       <c r="E37" t="s">
-        <v>442</v>
-      </c>
-      <c r="F37" s="10">
+        <v>423</v>
+      </c>
+      <c r="F37" s="12">
         <v>4.05</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="13">
         <v>3.47</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="14">
         <v>0.58</v>
       </c>
-      <c r="I37" s="13">
+      <c r="I37" s="15">
         <v>16.7</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J37" s="12">
         <v>20.063</v>
       </c>
-      <c r="K37" s="14">
+      <c r="K37" s="16">
         <v>-16.013</v>
       </c>
-      <c r="L37" s="13">
+      <c r="L37" s="15">
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -9806,31 +9840,31 @@
         <v>240</v>
       </c>
       <c r="E38" t="s">
-        <v>427</v>
-      </c>
-      <c r="F38" s="10">
+        <v>432</v>
+      </c>
+      <c r="F38" s="12">
         <v>8.2</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="13">
         <v>6.351</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="14">
         <v>1.849</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="15">
         <v>29.1</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="12">
         <v>57.8</v>
       </c>
-      <c r="K38" s="14">
+      <c r="K38" s="16">
         <v>-49.6</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="15">
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -9847,31 +9881,31 @@
         <v>240</v>
       </c>
       <c r="E39" t="s">
-        <v>445</v>
-      </c>
-      <c r="F39" s="10">
+        <v>431</v>
+      </c>
+      <c r="F39" s="12">
         <v>18</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="13">
         <v>12.91</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="14">
         <v>5.09</v>
       </c>
-      <c r="I39" s="13">
+      <c r="I39" s="15">
         <v>39.4</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J39" s="12">
         <v>143</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="16">
         <v>-125</v>
       </c>
-      <c r="L39" s="13">
+      <c r="L39" s="15">
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -9888,31 +9922,31 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>447</v>
-      </c>
-      <c r="F40" s="10">
+        <v>450</v>
+      </c>
+      <c r="F40" s="12">
         <v>36</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="13">
         <v>28.873</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="14">
         <v>7.127</v>
       </c>
-      <c r="I40" s="13">
+      <c r="I40" s="15">
         <v>24.7</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J40" s="12">
         <v>188</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="16">
         <v>-152</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="15">
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -9929,31 +9963,31 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>449</v>
-      </c>
-      <c r="F41" s="10">
+        <v>452</v>
+      </c>
+      <c r="F41" s="12">
         <v>60</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="13">
         <v>53.075</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="14">
         <v>6.925</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="15">
         <v>13.1</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J41" s="12">
         <v>374</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="16">
         <v>-314</v>
       </c>
-      <c r="L41" s="13">
+      <c r="L41" s="15">
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9970,23 +10004,23 @@
         <v>244</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F42" s="6">
+        <v>425</v>
+      </c>
+      <c r="F42" s="8">
         <v>16</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8">
+      <c r="G42" s="9"/>
+      <c r="H42" s="10">
         <v>2.454</v>
       </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="8">
+      <c r="I42" s="11"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="10">
         <v>-5</v>
       </c>
-      <c r="L42" s="9"/>
+      <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -10005,29 +10039,29 @@
       <c r="E43" t="s">
         <v>426</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="12">
         <v>5.8</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="13">
         <v>5.294</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="14">
         <v>0.506</v>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="15">
         <v>9.6</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J43" s="12">
         <v>12.75</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="16">
         <v>-6.95</v>
       </c>
-      <c r="L43" s="13">
+      <c r="L43" s="15">
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -10044,31 +10078,31 @@
         <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>423</v>
-      </c>
-      <c r="F44" s="10">
+        <v>424</v>
+      </c>
+      <c r="F44" s="12">
         <v>3.8</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="13">
         <v>3.622</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="14">
         <v>0.178</v>
       </c>
-      <c r="I44" s="13">
+      <c r="I44" s="15">
         <v>4.9</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J44" s="12">
         <v>17.75</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="16">
         <v>-13.95</v>
       </c>
-      <c r="L44" s="13">
+      <c r="L44" s="15">
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -10085,31 +10119,31 @@
         <v>244</v>
       </c>
       <c r="E45" t="s">
-        <v>442</v>
-      </c>
-      <c r="F45" s="10">
+        <v>423</v>
+      </c>
+      <c r="F45" s="12">
         <v>3.55</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="13">
         <v>3.229</v>
       </c>
-      <c r="H45" s="12">
+      <c r="H45" s="14">
         <v>0.321</v>
       </c>
-      <c r="I45" s="13">
+      <c r="I45" s="15">
         <v>9.9</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J45" s="12">
         <v>33.563</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="16">
         <v>-30.013</v>
       </c>
-      <c r="L45" s="13">
+      <c r="L45" s="15">
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -10126,31 +10160,31 @@
         <v>244</v>
       </c>
       <c r="E46" t="s">
-        <v>427</v>
-      </c>
-      <c r="F46" s="10">
+        <v>432</v>
+      </c>
+      <c r="F46" s="12">
         <v>5</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="13">
         <v>4.404</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="14">
         <v>0.596</v>
       </c>
-      <c r="I46" s="13">
+      <c r="I46" s="15">
         <v>13.5</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="12">
         <v>78.4</v>
       </c>
-      <c r="K46" s="14">
+      <c r="K46" s="16">
         <v>-73.4</v>
       </c>
-      <c r="L46" s="13">
+      <c r="L46" s="15">
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -10167,31 +10201,31 @@
         <v>244</v>
       </c>
       <c r="E47" t="s">
-        <v>445</v>
-      </c>
-      <c r="F47" s="10">
+        <v>431</v>
+      </c>
+      <c r="F47" s="12">
         <v>8.3</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="13">
         <v>6.601</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="14">
         <v>1.699</v>
       </c>
-      <c r="I47" s="13">
+      <c r="I47" s="15">
         <v>25.7</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="12">
         <v>175.833</v>
       </c>
-      <c r="K47" s="14">
+      <c r="K47" s="16">
         <v>-167.533</v>
       </c>
-      <c r="L47" s="13">
+      <c r="L47" s="15">
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -10208,31 +10242,31 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>447</v>
-      </c>
-      <c r="F48" s="10">
+        <v>450</v>
+      </c>
+      <c r="F48" s="12">
         <v>15.5</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="13">
         <v>14.504</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="14">
         <v>0.996</v>
       </c>
-      <c r="I48" s="13">
+      <c r="I48" s="15">
         <v>6.9</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J48" s="12">
         <v>175.4</v>
       </c>
-      <c r="K48" s="14">
+      <c r="K48" s="16">
         <v>-159.9</v>
       </c>
-      <c r="L48" s="13">
+      <c r="L48" s="15">
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -10249,31 +10283,31 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>449</v>
-      </c>
-      <c r="F49" s="10">
+        <v>452</v>
+      </c>
+      <c r="F49" s="12">
         <v>25</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="13">
         <v>18.237</v>
       </c>
-      <c r="H49" s="12">
+      <c r="H49" s="14">
         <v>6.763</v>
       </c>
-      <c r="I49" s="13">
+      <c r="I49" s="15">
         <v>37.1</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="12">
         <v>239</v>
       </c>
-      <c r="K49" s="14">
+      <c r="K49" s="16">
         <v>-214</v>
       </c>
-      <c r="L49" s="13">
+      <c r="L49" s="15">
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10290,23 +10324,23 @@
         <v>254</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="F50" s="6">
+        <v>425</v>
+      </c>
+      <c r="F50" s="8">
         <v>14</v>
       </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8">
+      <c r="G50" s="9"/>
+      <c r="H50" s="10">
         <v>2.619</v>
       </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="8">
+      <c r="I50" s="11"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="10">
         <v>-4.486</v>
       </c>
-      <c r="L50" s="9"/>
+      <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -10325,29 +10359,29 @@
       <c r="E51" t="s">
         <v>426</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="12">
         <v>5.4</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="13">
         <v>4.95</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="14">
         <v>0.45</v>
       </c>
-      <c r="I51" s="13">
+      <c r="I51" s="15">
         <v>9.1</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="12">
         <v>10</v>
       </c>
-      <c r="K51" s="14">
+      <c r="K51" s="16">
         <v>-4.6</v>
       </c>
-      <c r="L51" s="13">
+      <c r="L51" s="15">
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -10364,31 +10398,31 @@
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>423</v>
-      </c>
-      <c r="F52" s="10">
+        <v>424</v>
+      </c>
+      <c r="F52" s="12">
         <v>3.3</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="13">
         <v>3.238</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="14">
         <v>0.062</v>
       </c>
-      <c r="I52" s="13">
+      <c r="I52" s="15">
         <v>1.9</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="12">
         <v>11.667</v>
       </c>
-      <c r="K52" s="14">
+      <c r="K52" s="16">
         <v>-8.367</v>
       </c>
-      <c r="L52" s="13">
+      <c r="L52" s="15">
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -10405,31 +10439,31 @@
         <v>254</v>
       </c>
       <c r="E53" t="s">
-        <v>442</v>
-      </c>
-      <c r="F53" s="10">
+        <v>423</v>
+      </c>
+      <c r="F53" s="12">
         <v>3.5</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="13">
         <v>3.201</v>
       </c>
-      <c r="H53" s="12">
+      <c r="H53" s="14">
         <v>0.299</v>
       </c>
-      <c r="I53" s="13">
+      <c r="I53" s="15">
         <v>9.3</v>
       </c>
-      <c r="J53" s="10">
+      <c r="J53" s="12">
         <v>18.25</v>
       </c>
-      <c r="K53" s="14">
+      <c r="K53" s="16">
         <v>-14.75</v>
       </c>
-      <c r="L53" s="13">
+      <c r="L53" s="15">
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -10446,31 +10480,31 @@
         <v>254</v>
       </c>
       <c r="E54" t="s">
-        <v>427</v>
-      </c>
-      <c r="F54" s="10">
+        <v>432</v>
+      </c>
+      <c r="F54" s="12">
         <v>5.5</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="13">
         <v>4.699</v>
       </c>
-      <c r="H54" s="12">
+      <c r="H54" s="14">
         <v>0.801</v>
       </c>
-      <c r="I54" s="13">
+      <c r="I54" s="15">
         <v>17.1</v>
       </c>
-      <c r="J54" s="10">
+      <c r="J54" s="12">
         <v>38.3</v>
       </c>
-      <c r="K54" s="14">
+      <c r="K54" s="16">
         <v>-32.8</v>
       </c>
-      <c r="L54" s="13">
+      <c r="L54" s="15">
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -10487,31 +10521,31 @@
         <v>254</v>
       </c>
       <c r="E55" t="s">
-        <v>445</v>
-      </c>
-      <c r="F55" s="10">
+        <v>431</v>
+      </c>
+      <c r="F55" s="12">
         <v>10</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="13">
         <v>7.992</v>
       </c>
-      <c r="H55" s="12">
+      <c r="H55" s="14">
         <v>2.008</v>
       </c>
-      <c r="I55" s="13">
+      <c r="I55" s="15">
         <v>25.1</v>
       </c>
-      <c r="J55" s="10">
+      <c r="J55" s="12">
         <v>102.333</v>
       </c>
-      <c r="K55" s="14">
+      <c r="K55" s="16">
         <v>-92.333</v>
       </c>
-      <c r="L55" s="13">
+      <c r="L55" s="15">
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -10528,31 +10562,31 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>447</v>
-      </c>
-      <c r="F56" s="10">
-        <v>21</v>
-      </c>
-      <c r="G56" s="11">
+        <v>450</v>
+      </c>
+      <c r="F56" s="12">
+        <v>21</v>
+      </c>
+      <c r="G56" s="13">
         <v>15.293</v>
       </c>
-      <c r="H56" s="12">
+      <c r="H56" s="14">
         <v>5.707</v>
       </c>
-      <c r="I56" s="13">
+      <c r="I56" s="15">
         <v>37.3</v>
       </c>
-      <c r="J56" s="10">
+      <c r="J56" s="12">
         <v>107</v>
       </c>
-      <c r="K56" s="14">
+      <c r="K56" s="16">
         <v>-86</v>
       </c>
-      <c r="L56" s="13">
+      <c r="L56" s="15">
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -10569,31 +10603,31 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>449</v>
-      </c>
-      <c r="F57" s="10">
+        <v>452</v>
+      </c>
+      <c r="F57" s="12">
         <v>34</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="13">
         <v>24.49</v>
       </c>
-      <c r="H57" s="12">
+      <c r="H57" s="14">
         <v>9.51</v>
       </c>
-      <c r="I57" s="13">
+      <c r="I57" s="15">
         <v>38.8</v>
       </c>
-      <c r="J57" s="10">
+      <c r="J57" s="12">
         <v>188</v>
       </c>
-      <c r="K57" s="14">
+      <c r="K57" s="16">
         <v>-154</v>
       </c>
-      <c r="L57" s="13">
+      <c r="L57" s="15">
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -10612,146 +10646,146 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>500</v>
+    <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B7" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>508</v>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B14" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B15" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>513</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>21</v>
+      <c r="A20" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>528</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -10762,11 +10796,11 @@
       <c r="E20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>21</v>
+      <c r="F20" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>530</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>21</v>
@@ -10776,20 +10810,20 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="19" t="s">
         <v>426</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>21</v>
+      <c r="C21" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>532</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
@@ -10805,49 +10839,49 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>442</v>
-      </c>
       <c r="B23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>21</v>
+      <c r="C23" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>529</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -10863,11 +10897,11 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>21</v>
+      <c r="A24" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>532</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
@@ -10875,11 +10909,11 @@
       <c r="D24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>21</v>
+      <c r="E24" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>529</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -10892,8 +10926,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
-        <v>445</v>
+      <c r="A25" s="19" t="s">
+        <v>431</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>21</v>
@@ -10907,22 +10941,22 @@
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>21</v>
+      <c r="F25" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>529</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>447</v>
+      <c r="A26" s="19" t="s">
+        <v>450</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>21</v>
@@ -10939,19 +10973,19 @@
       <c r="F26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>21</v>
+      <c r="G26" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>449</v>
+      <c r="A27" s="19" t="s">
+        <v>452</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -10971,16 +11005,16 @@
       <c r="G27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>21</v>
+      <c r="H27" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -10991,7 +11025,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -11003,105 +11037,111 @@
     <col min="11" max="12" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>527</v>
+    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="18">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19"/>
+        <v>2350</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1650</v>
+      </c>
+      <c r="G5" s="21">
+        <v>2.357142857142857</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0</v>
-      </c>
-      <c r="G6" s="19"/>
+        <v>1170</v>
+      </c>
+      <c r="F6" s="7">
+        <v>470</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0.6714285714285714</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="18">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="9" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>538</v>
+        <v>1220</v>
+      </c>
+      <c r="F7" s="7">
+        <v>520</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0.7428571428571429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11109,7 +11149,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -11121,63 +11161,342 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
+        <v>425</v>
+      </c>
+      <c r="G11" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>423</v>
+      </c>
+      <c r="I11" s="22">
+        <v>-100</v>
+      </c>
+      <c r="J11" s="23">
+        <v>-100</v>
+      </c>
+      <c r="K11" s="24">
+        <v>-100</v>
+      </c>
+      <c r="L11" s="24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B12" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" t="s">
+        <v>248</v>
+      </c>
+      <c r="F12" t="s">
+        <v>425</v>
+      </c>
+      <c r="G12" s="12">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>431</v>
+      </c>
+      <c r="I12" s="22">
+        <v>-100</v>
+      </c>
+      <c r="J12" s="23">
+        <v>-200</v>
+      </c>
+      <c r="K12" s="24">
+        <v>-100</v>
+      </c>
+      <c r="L12" s="24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" t="s">
+        <v>260</v>
+      </c>
+      <c r="F13" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" s="12">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>426</v>
+      </c>
+      <c r="I13" s="22">
+        <v>-100</v>
+      </c>
+      <c r="J13" s="23">
+        <v>-300</v>
+      </c>
+      <c r="K13" s="24">
+        <v>-100</v>
+      </c>
+      <c r="L13" s="24">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>421</v>
+      </c>
+      <c r="B14" t="s">
+        <v>380</v>
+      </c>
+      <c r="C14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" t="s">
+        <v>247</v>
+      </c>
+      <c r="E14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" t="s">
+        <v>425</v>
+      </c>
+      <c r="G14" s="12">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
+        <v>432</v>
+      </c>
+      <c r="I14" s="22">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="23">
+        <v>-400</v>
+      </c>
+      <c r="K14" s="24">
+        <v>320</v>
+      </c>
+      <c r="L14" s="24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>421</v>
+      </c>
+      <c r="B15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" t="s">
+        <v>425</v>
+      </c>
+      <c r="G15" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>425</v>
+      </c>
+      <c r="I15" s="25">
+        <v>650</v>
+      </c>
+      <c r="J15" s="26">
+        <v>250</v>
+      </c>
+      <c r="K15" s="24">
+        <v>650</v>
+      </c>
+      <c r="L15" s="24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B16" t="s">
+        <v>383</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" t="s">
+        <v>251</v>
+      </c>
+      <c r="E16" t="s">
+        <v>244</v>
+      </c>
+      <c r="F16" t="s">
+        <v>425</v>
+      </c>
+      <c r="G16" s="12">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s">
+        <v>425</v>
+      </c>
+      <c r="I16" s="25">
+        <v>1500</v>
+      </c>
+      <c r="J16" s="26">
+        <v>1750</v>
+      </c>
+      <c r="K16" s="24">
+        <v>-100</v>
+      </c>
+      <c r="L16" s="24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>421</v>
+      </c>
+      <c r="B17" t="s">
+        <v>384</v>
+      </c>
+      <c r="C17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" t="s">
+        <v>255</v>
+      </c>
+      <c r="E17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" t="s">
+        <v>425</v>
+      </c>
+      <c r="G17" s="12">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>426</v>
+      </c>
+      <c r="I17" s="22">
+        <v>-100</v>
+      </c>
+      <c r="J17" s="26">
+        <v>1650</v>
+      </c>
+      <c r="K17" s="24">
+        <v>-100</v>
+      </c>
+      <c r="L17" s="24">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>552</v>
+      <c r="D20" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>421</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" s="24">
+        <v>1650</v>
+      </c>
+      <c r="E21" s="24">
+        <v>1650</v>
+      </c>
+      <c r="F21" s="24">
+        <v>470</v>
+      </c>
+      <c r="G21" s="24">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -11197,36 +11516,36 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>426</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -11238,7 +11557,7 @@
         <v>69</v>
       </c>
       <c r="F2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>52</v>
@@ -11249,10 +11568,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B3">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -11270,21 +11589,21 @@
         <v>45</v>
       </c>
       <c r="H3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B4">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C4">
         <v>22</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4">
         <v>68</v>
@@ -11301,10 +11620,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="B5">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -11319,7 +11638,7 @@
         <v>52</v>
       </c>
       <c r="G5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5">
         <v>49</v>
@@ -11327,13 +11646,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B6">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -11353,13 +11672,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -11379,16 +11698,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8">
         <v>67</v>
@@ -11405,7 +11724,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -11431,7 +11750,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -11457,7 +11776,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -11495,242 +11814,242 @@
     <col min="1" max="1" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>566</v>
+    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="C5" s="20">
-        <v>34</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="E5" s="20">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="C5" s="27">
+        <v>35</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="E5" s="27">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>571</v>
+    <row r="7" spans="1:1" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>426</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
-      </c>
-      <c r="C9" s="22">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="C9" s="29">
+        <v>22</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4</v>
+      </c>
+      <c r="F10" s="29">
+        <v>19</v>
+      </c>
+      <c r="G10" s="3">
         <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3</v>
-      </c>
-      <c r="F10" s="22">
-        <v>18</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="B11" s="22">
-        <v>21</v>
+        <v>564</v>
+      </c>
+      <c r="B11" s="29">
+        <v>22</v>
       </c>
       <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="29">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3">
         <v>2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22">
-        <v>28</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="B12" s="23">
-        <v>34</v>
+        <v>565</v>
+      </c>
+      <c r="B12" s="30">
+        <v>35</v>
       </c>
       <c r="C12" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="29">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="22">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3</v>
-      </c>
       <c r="G12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3">
         <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>8</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>9</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B14" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3">
         <v>4</v>
       </c>
-      <c r="D14" s="3">
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="B15" s="22">
-        <v>19</v>
+        <v>568</v>
+      </c>
+      <c r="B15" s="29">
+        <v>20</v>
       </c>
       <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3">
         <v>2</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
       <c r="G15" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -11753,9 +12072,9 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="B17" s="22">
+        <v>570</v>
+      </c>
+      <c r="B17" s="29">
         <v>26</v>
       </c>
       <c r="C17" s="3">
@@ -11767,7 +12086,7 @@
       <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="29">
         <v>27</v>
       </c>
       <c r="G17" s="3">
@@ -11776,12 +12095,12 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="29">
         <v>19</v>
       </c>
       <c r="D18" s="3">
@@ -11811,9 +12130,9 @@
     <col min="1" max="1" width="112" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>572</v>
+    <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -11821,64 +12140,64 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>573</v>
+    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -11886,34 +12205,34 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>585</v>
+    <row r="16" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -11921,24 +12240,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>591</v>
+    <row r="23" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -11946,24 +12265,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>595</v>
+    <row r="28" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -11971,14 +12290,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:1" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>599</v>
+    <row r="33" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="716">
   <si>
     <t>日期</t>
   </si>
@@ -1322,6 +1322,48 @@
     <t>✓</t>
   </si>
   <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>乌兹别克</t>
+  </si>
+  <si>
+    <t>10-06 19:00</t>
+  </si>
+  <si>
+    <t>10-06 17:00</t>
+  </si>
+  <si>
+    <t>塔吉克</t>
+  </si>
+  <si>
+    <t>10-06 19:35</t>
+  </si>
+  <si>
+    <t>10-06 22:00</t>
+  </si>
+  <si>
+    <t>10-07 02:45</t>
+  </si>
+  <si>
+    <t>6球</t>
+  </si>
+  <si>
+    <t>摩尔多瓦</t>
+  </si>
+  <si>
+    <t>10-07 08:00</t>
+  </si>
+  <si>
+    <t>芝加哥</t>
+  </si>
+  <si>
+    <t>温哥华</t>
+  </si>
+  <si>
+    <t>10-07 08:30</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1370,9 +1412,6 @@
     <t>0:5=1000 1:4=250 2:3=55 3:2=29 4:1=29 5:0=55</t>
   </si>
   <si>
-    <t>6球</t>
-  </si>
-  <si>
     <t>1:5=800 2:4=300 3:3=90 4:2=70 5:1=70</t>
   </si>
   <si>
@@ -1526,7 +1565,292 @@
     <t>2:5=200 5:2=300 负其他=60 平其他=300 胜其他=80</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-06T11:00:08+08:00）</t>
+    <t>0:0=15</t>
+  </si>
+  <si>
+    <t>0:1=15.5 1:0=7.5</t>
+  </si>
+  <si>
+    <t>0:2=29 1:1=8.25 2:0=6.8</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=15 2:1=6.5 3:0=12</t>
+  </si>
+  <si>
+    <t>0:4=250 1:3=50 2:2=16 3:1=11 4:0=25</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=150 2:3=50 3:2=23 4:1=23 5:0=55</t>
+  </si>
+  <si>
+    <t>1:5=550 2:4=180 3:3=60 4:2=45 5:1=65</t>
+  </si>
+  <si>
+    <t>2:5=500 5:2=110 负其他=160 平其他=350 胜其他=42</t>
+  </si>
+  <si>
+    <t>0:0=9</t>
+  </si>
+  <si>
+    <t>0:1=9.75 1:0=6.6</t>
+  </si>
+  <si>
+    <t>0:2=22 1:1=6.35 2:0=6.6</t>
+  </si>
+  <si>
+    <t>0:3=60 1:2=14 2:1=7.5 3:0=15</t>
+  </si>
+  <si>
+    <t>0:4=175 1:3=50 2:2=18 3:1=17 4:0=36</t>
+  </si>
+  <si>
+    <t>0:5=300 1:4=120 2:3=55 3:2=34 4:1=38 5:0=100</t>
+  </si>
+  <si>
+    <t>1:5=250 2:4=150 3:3=80 4:2=95 5:1=125</t>
+  </si>
+  <si>
+    <t>2:5=350 5:2=200 负其他=175 平其他=500 胜其他=90</t>
+  </si>
+  <si>
+    <t>0:1=7.5 1:0=7</t>
+  </si>
+  <si>
+    <t>0:2=14 1:1=5.4 2:0=10.5</t>
+  </si>
+  <si>
+    <t>0:3=37 1:2=10 2:1=9 3:0=28</t>
+  </si>
+  <si>
+    <t>0:4=100 1:3=29 2:2=17 3:1=23 4:0=90</t>
+  </si>
+  <si>
+    <t>0:5=350 1:4=80 2:3=40 3:2=35 4:1=75 5:0=250</t>
+  </si>
+  <si>
+    <t>1:5=300 2:4=120 3:3=80 4:2=90 5:1=200</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=300 负其他=175 平其他=550 胜其他=150</t>
+  </si>
+  <si>
+    <t>0:0=12</t>
+  </si>
+  <si>
+    <t>0:1=6.75 1:0=13</t>
+  </si>
+  <si>
+    <t>0:2=7 1:1=7.75 2:0=28</t>
+  </si>
+  <si>
+    <t>0:3=12.5 1:2=6.75 2:1=14 3:0=80</t>
+  </si>
+  <si>
+    <t>0:4=28 1:3=13 2:2=16 3:1=39 4:0=300</t>
+  </si>
+  <si>
+    <t>0:5=70 1:4=29 2:3=26 3:2=45 4:1=175 5:0=800</t>
+  </si>
+  <si>
+    <t>1:5=70 2:4=55 3:3=80 4:2=250 5:1=700</t>
+  </si>
+  <si>
+    <t>2:5=120 5:2=700 负其他=45 平其他=450 胜其他=250</t>
+  </si>
+  <si>
+    <t>0:0=8.5</t>
+  </si>
+  <si>
+    <t>0:1=8 1:0=5.5</t>
+  </si>
+  <si>
+    <t>0:2=21 1:1=6.5 2:0=8.5</t>
+  </si>
+  <si>
+    <t>0:3=55 1:2=12 2:1=7.75 3:0=18</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=40 2:2=18 3:1=18 4:0=55</t>
+  </si>
+  <si>
+    <t>0:5=600 1:4=150 2:3=50 3:2=30 4:1=45 5:0=150</t>
+  </si>
+  <si>
+    <t>1:5=400 2:4=200 3:3=100 4:2=90 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=600 5:2=250 负其他=250 平其他=700 胜其他=90</t>
+  </si>
+  <si>
+    <t>0:0=8</t>
+  </si>
+  <si>
+    <t>0:1=10 1:0=5.75</t>
+  </si>
+  <si>
+    <t>0:2=23 1:1=7.25 2:0=6.75</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=14 2:1=7.5 3:0=15</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=50 2:2=18 3:1=16 4:0=33</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=200 2:3=60 3:2=33 4:1=40 5:0=100</t>
+  </si>
+  <si>
+    <t>1:5=500 2:4=200 3:3=90 4:2=70 5:1=100</t>
+  </si>
+  <si>
+    <t>2:5=600 5:2=175 负其他=300 平其他=550 胜其他=80</t>
+  </si>
+  <si>
+    <t>0:0=35</t>
+  </si>
+  <si>
+    <t>0:1=50 1:0=11</t>
+  </si>
+  <si>
+    <t>0:2=140 1:1=17 2:0=6.75</t>
+  </si>
+  <si>
+    <t>0:3=450 1:2=48 2:1=10 3:0=6.5</t>
+  </si>
+  <si>
+    <t>0:4=1000 1:3=200 2:2=30 3:1=9.75 4:0=8.5</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=700 2:3=95 3:2=28 4:1=13 5:0=13</t>
+  </si>
+  <si>
+    <t>1:5=1000 2:4=450 3:3=90 4:2=40 5:1=21</t>
+  </si>
+  <si>
+    <t>2:5=1000 5:2=65 负其他=450 平其他=450 胜其他=7.2</t>
+  </si>
+  <si>
+    <t>0:0=24</t>
+  </si>
+  <si>
+    <t>0:1=9.5 1:0=29</t>
+  </si>
+  <si>
+    <t>0:2=7.25 1:1=10.5 2:0=60</t>
+  </si>
+  <si>
+    <t>0:3=8.5 1:2=8.5 2:1=26 3:0=150</t>
+  </si>
+  <si>
+    <t>0:4=13.5 1:3=9 2:2=19 3:1=80 4:0=450</t>
+  </si>
+  <si>
+    <t>0:5=26 1:4=15 2:3=20 3:2=55 4:1=250 5:0=1000</t>
+  </si>
+  <si>
+    <t>1:5=29 2:4=30 3:3=60 4:2=175 5:1=700</t>
+  </si>
+  <si>
+    <t>2:5=55 5:2=550 负其他=13.5 平其他=300 胜其他=150</t>
+  </si>
+  <si>
+    <t>0:0=31</t>
+  </si>
+  <si>
+    <t>0:1=55 1:0=9</t>
+  </si>
+  <si>
+    <t>0:2=175 1:1=18.5 2:0=5.8</t>
+  </si>
+  <si>
+    <t>0:3=700 1:2=70 2:1=10.5 3:0=6</t>
+  </si>
+  <si>
+    <t>0:4=1000 1:3=250 2:2=40 3:1=11 4:0=7.5</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=1000 2:3=250 3:2=38 4:1=14 5:0=11</t>
+  </si>
+  <si>
+    <t>1:5=1000 2:4=900 3:3=200 4:2=55 5:1=23</t>
+  </si>
+  <si>
+    <t>2:5=1000 5:2=80 负其他=800 平其他=700 胜其他=7.5</t>
+  </si>
+  <si>
+    <t>0:0=13.5</t>
+  </si>
+  <si>
+    <t>0:1=6.75 1:0=18</t>
+  </si>
+  <si>
+    <t>0:2=5.6 1:1=9 2:0=40</t>
+  </si>
+  <si>
+    <t>0:3=9.25 1:2=7 2:1=21 3:0=120</t>
+  </si>
+  <si>
+    <t>0:4=17 1:3=11 2:2=20 3:1=75 4:0=550</t>
+  </si>
+  <si>
+    <t>0:5=38 1:4=23 2:3=28 3:2=70 4:1=300 5:0=1000</t>
+  </si>
+  <si>
+    <t>1:5=45 2:4=55 3:3=90 4:2=300 5:1=1000</t>
+  </si>
+  <si>
+    <t>2:5=120 5:2=1000 负其他=33 平其他=550 胜其他=350</t>
+  </si>
+  <si>
+    <t>0:0=18</t>
+  </si>
+  <si>
+    <t>0:1=14.5 1:0=10</t>
+  </si>
+  <si>
+    <t>0:2=27 1:1=8.25 2:0=9.75</t>
+  </si>
+  <si>
+    <t>0:3=50 1:2=12 2:1=7 3:0=15</t>
+  </si>
+  <si>
+    <t>0:4=120 1:3=28 2:2=12.5 3:1=11.5 4:0=32</t>
+  </si>
+  <si>
+    <t>0:5=450 1:4=90 2:3=28 3:2=19 4:1=25 5:0=70</t>
+  </si>
+  <si>
+    <t>1:5=300 2:4=80 3:3=40 4:2=40 5:1=70</t>
+  </si>
+  <si>
+    <t>2:5=300 5:2=90 负其他=85 平其他=200 胜其他=32</t>
+  </si>
+  <si>
+    <t>0:0=26</t>
+  </si>
+  <si>
+    <t>0:1=14 1:0=15.5</t>
+  </si>
+  <si>
+    <t>0:2=15.5 1:1=8 2:0=19.5</t>
+  </si>
+  <si>
+    <t>0:3=24 1:2=8 2:1=8.75 3:0=34</t>
+  </si>
+  <si>
+    <t>0:4=55 1:3=15 2:2=10.5 3:1=17.5 4:0=80</t>
+  </si>
+  <si>
+    <t>0:5=150 1:4=33 2:3=17 3:2=19 4:1=45 5:0=250</t>
+  </si>
+  <si>
+    <t>1:5=85 2:4=38 3:3=30 4:2=45 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
+  </si>
+  <si>
+    <t>进球数预测 · 模型统计（截至 2026-10-06T17:00:06+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -1939,7 +2263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1961,6 +2285,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7935,7 +8260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8324,6 +8649,570 @@
         <v>429</v>
       </c>
     </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" t="s">
+        <v>435</v>
+      </c>
+      <c r="F9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>437</v>
+      </c>
+      <c r="O9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F10" t="s">
+        <v>439</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>437</v>
+      </c>
+      <c r="O10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" t="s">
+        <v>301</v>
+      </c>
+      <c r="F11" t="s">
+        <v>440</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>437</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" t="s">
+        <v>305</v>
+      </c>
+      <c r="F12" t="s">
+        <v>441</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>437</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F13" t="s">
+        <v>441</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>437</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B14" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" t="s">
+        <v>294</v>
+      </c>
+      <c r="E14" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" t="s">
+        <v>441</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>437</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" t="s">
+        <v>441</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>437</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B16" t="s">
+        <v>405</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" t="s">
+        <v>316</v>
+      </c>
+      <c r="E16" t="s">
+        <v>323</v>
+      </c>
+      <c r="F16" t="s">
+        <v>441</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>437</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" t="s">
+        <v>407</v>
+      </c>
+      <c r="C17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" t="s">
+        <v>320</v>
+      </c>
+      <c r="E17" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" t="s">
+        <v>441</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" t="s">
+        <v>437</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>434</v>
+      </c>
+      <c r="B18" t="s">
+        <v>408</v>
+      </c>
+      <c r="C18" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" t="s">
+        <v>443</v>
+      </c>
+      <c r="E18" t="s">
+        <v>410</v>
+      </c>
+      <c r="F18" t="s">
+        <v>441</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
+        <v>437</v>
+      </c>
+      <c r="O18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B19" t="s">
+        <v>409</v>
+      </c>
+      <c r="C19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F19" t="s">
+        <v>444</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" t="s">
+        <v>437</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>434</v>
+      </c>
+      <c r="B20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" t="s">
+        <v>445</v>
+      </c>
+      <c r="E20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F20" t="s">
+        <v>447</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" t="s">
+        <v>437</v>
+      </c>
+      <c r="O20" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8333,7 +9222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8354,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -8363,31 +9252,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -8420,7 +9309,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -8461,7 +9350,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -8502,7 +9391,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -8543,7 +9432,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -8584,7 +9473,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -8625,7 +9514,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -8642,7 +9531,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -8666,7 +9555,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8683,7 +9572,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -8707,7 +9596,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -8740,7 +9629,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8781,7 +9670,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8822,7 +9711,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8863,7 +9752,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8904,7 +9793,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8945,7 +9834,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8962,7 +9851,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -8986,7 +9875,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -9003,7 +9892,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -9027,7 +9916,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9060,7 +9949,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -9101,7 +9990,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -9142,7 +10031,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -9183,7 +10072,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -9224,7 +10113,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -9265,7 +10154,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -9282,7 +10171,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -9306,7 +10195,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -9323,7 +10212,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -9347,7 +10236,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9380,7 +10269,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -9421,7 +10310,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -9462,7 +10351,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -9503,7 +10392,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -9544,7 +10433,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -9585,7 +10474,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -9602,7 +10491,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -9626,7 +10515,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -9643,7 +10532,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -9667,7 +10556,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9700,7 +10589,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -9741,7 +10630,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -9782,7 +10671,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -9823,7 +10712,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -9864,7 +10753,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -9905,7 +10794,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -9922,7 +10811,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -9946,7 +10835,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -9963,7 +10852,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -9987,7 +10876,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10020,7 +10909,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -10061,7 +10950,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -10102,7 +10991,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -10143,7 +11032,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -10184,7 +11073,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -10225,7 +11114,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -10242,7 +11131,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -10266,7 +11155,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -10283,7 +11172,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -10307,7 +11196,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10340,7 +11229,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -10381,7 +11270,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -10422,7 +11311,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -10463,7 +11352,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -10504,7 +11393,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -10545,7 +11434,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -10562,7 +11451,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -10586,7 +11475,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -10603,7 +11492,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -10627,7 +11516,3847 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>501</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F58" s="8">
+        <v>15</v>
+      </c>
+      <c r="G58" s="9"/>
+      <c r="H58" s="10">
+        <v>0.774</v>
+      </c>
+      <c r="I58" s="11"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L58" s="11"/>
+      <c r="M58" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>434</v>
+      </c>
+      <c r="B59" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" t="s">
+        <v>196</v>
+      </c>
+      <c r="D59" t="s">
+        <v>435</v>
+      </c>
+      <c r="E59" t="s">
+        <v>426</v>
+      </c>
+      <c r="F59" s="12">
+        <v>5.8</v>
+      </c>
+      <c r="G59" s="13">
+        <v>5.054</v>
+      </c>
+      <c r="H59" s="14">
+        <v>0.746</v>
+      </c>
+      <c r="I59" s="15">
+        <v>14.8</v>
+      </c>
+      <c r="J59" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="K59" s="16">
+        <v>-5.7</v>
+      </c>
+      <c r="L59" s="15">
+        <v>-49.6</v>
+      </c>
+      <c r="M59" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>434</v>
+      </c>
+      <c r="B60" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" t="s">
+        <v>435</v>
+      </c>
+      <c r="E60" t="s">
+        <v>424</v>
+      </c>
+      <c r="F60" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G60" s="13">
+        <v>3.303</v>
+      </c>
+      <c r="H60" s="14">
+        <v>0.397</v>
+      </c>
+      <c r="I60" s="15">
+        <v>12</v>
+      </c>
+      <c r="J60" s="12">
+        <v>14.683</v>
+      </c>
+      <c r="K60" s="16">
+        <v>-10.983</v>
+      </c>
+      <c r="L60" s="15">
+        <v>-74.8</v>
+      </c>
+      <c r="M60" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>434</v>
+      </c>
+      <c r="B61" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D61" t="s">
+        <v>435</v>
+      </c>
+      <c r="E61" t="s">
+        <v>423</v>
+      </c>
+      <c r="F61" s="12">
+        <v>3.35</v>
+      </c>
+      <c r="G61" s="13">
+        <v>3.161</v>
+      </c>
+      <c r="H61" s="14">
+        <v>0.189</v>
+      </c>
+      <c r="I61" s="15">
+        <v>6</v>
+      </c>
+      <c r="J61" s="12">
+        <v>28.375</v>
+      </c>
+      <c r="K61" s="16">
+        <v>-25.025</v>
+      </c>
+      <c r="L61" s="15">
+        <v>-88.2</v>
+      </c>
+      <c r="M61" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>434</v>
+      </c>
+      <c r="B62" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" t="s">
+        <v>435</v>
+      </c>
+      <c r="E62" t="s">
+        <v>432</v>
+      </c>
+      <c r="F62" s="12">
+        <v>5.15</v>
+      </c>
+      <c r="G62" s="13">
+        <v>4.6</v>
+      </c>
+      <c r="H62" s="14">
+        <v>0.55</v>
+      </c>
+      <c r="I62" s="15">
+        <v>12</v>
+      </c>
+      <c r="J62" s="12">
+        <v>70.4</v>
+      </c>
+      <c r="K62" s="16">
+        <v>-65.25</v>
+      </c>
+      <c r="L62" s="15">
+        <v>-92.7</v>
+      </c>
+      <c r="M62" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>434</v>
+      </c>
+      <c r="B63" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" t="s">
+        <v>196</v>
+      </c>
+      <c r="D63" t="s">
+        <v>435</v>
+      </c>
+      <c r="E63" t="s">
+        <v>431</v>
+      </c>
+      <c r="F63" s="12">
+        <v>9.25</v>
+      </c>
+      <c r="G63" s="13">
+        <v>7.516</v>
+      </c>
+      <c r="H63" s="14">
+        <v>1.734</v>
+      </c>
+      <c r="I63" s="15">
+        <v>23.1</v>
+      </c>
+      <c r="J63" s="12">
+        <v>183.5</v>
+      </c>
+      <c r="K63" s="16">
+        <v>-174.25</v>
+      </c>
+      <c r="L63" s="15">
+        <v>-95</v>
+      </c>
+      <c r="M63" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>434</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" t="s">
+        <v>435</v>
+      </c>
+      <c r="E64" t="s">
+        <v>442</v>
+      </c>
+      <c r="F64" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="G64" s="13">
+        <v>16.221</v>
+      </c>
+      <c r="H64" s="14">
+        <v>2.279</v>
+      </c>
+      <c r="I64" s="15">
+        <v>14.1</v>
+      </c>
+      <c r="J64" s="12">
+        <v>180</v>
+      </c>
+      <c r="K64" s="16">
+        <v>-161.5</v>
+      </c>
+      <c r="L64" s="15">
+        <v>-89.7</v>
+      </c>
+      <c r="M64" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>434</v>
+      </c>
+      <c r="B65" t="s">
+        <v>157</v>
+      </c>
+      <c r="C65" t="s">
+        <v>196</v>
+      </c>
+      <c r="D65" t="s">
+        <v>435</v>
+      </c>
+      <c r="E65" t="s">
+        <v>465</v>
+      </c>
+      <c r="F65" s="12">
+        <v>25</v>
+      </c>
+      <c r="G65" s="13">
+        <v>22.723</v>
+      </c>
+      <c r="H65" s="14">
+        <v>2.277</v>
+      </c>
+      <c r="I65" s="15">
+        <v>10</v>
+      </c>
+      <c r="J65" s="12">
+        <v>232.4</v>
+      </c>
+      <c r="K65" s="16">
+        <v>-207.4</v>
+      </c>
+      <c r="L65" s="15">
+        <v>-89.2</v>
+      </c>
+      <c r="M65" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F66" s="8">
+        <v>9</v>
+      </c>
+      <c r="G66" s="9"/>
+      <c r="H66" s="10">
+        <v>0.671</v>
+      </c>
+      <c r="I66" s="11"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="10">
+        <v>-4.004</v>
+      </c>
+      <c r="L66" s="11"/>
+      <c r="M66" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>434</v>
+      </c>
+      <c r="B67" t="s">
+        <v>163</v>
+      </c>
+      <c r="C67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" t="s">
+        <v>438</v>
+      </c>
+      <c r="E67" t="s">
+        <v>426</v>
+      </c>
+      <c r="F67" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="G67" s="13">
+        <v>3.936</v>
+      </c>
+      <c r="H67" s="14">
+        <v>0.014</v>
+      </c>
+      <c r="I67" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="J67" s="12">
+        <v>8.175</v>
+      </c>
+      <c r="K67" s="16">
+        <v>-4.225</v>
+      </c>
+      <c r="L67" s="15">
+        <v>-51.7</v>
+      </c>
+      <c r="M67" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>434</v>
+      </c>
+      <c r="B68" t="s">
+        <v>163</v>
+      </c>
+      <c r="C68" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" t="s">
+        <v>438</v>
+      </c>
+      <c r="E68" t="s">
+        <v>424</v>
+      </c>
+      <c r="F68" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="G68" s="13">
+        <v>2.821</v>
+      </c>
+      <c r="H68" s="14">
+        <v>0.279</v>
+      </c>
+      <c r="I68" s="15">
+        <v>9.9</v>
+      </c>
+      <c r="J68" s="12">
+        <v>11.65</v>
+      </c>
+      <c r="K68" s="16">
+        <v>-8.55</v>
+      </c>
+      <c r="L68" s="15">
+        <v>-73.4</v>
+      </c>
+      <c r="M68" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>434</v>
+      </c>
+      <c r="B69" t="s">
+        <v>163</v>
+      </c>
+      <c r="C69" t="s">
+        <v>200</v>
+      </c>
+      <c r="D69" t="s">
+        <v>438</v>
+      </c>
+      <c r="E69" t="s">
+        <v>423</v>
+      </c>
+      <c r="F69" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="G69" s="13">
+        <v>3.471</v>
+      </c>
+      <c r="H69" s="14">
+        <v>0.579</v>
+      </c>
+      <c r="I69" s="15">
+        <v>16.7</v>
+      </c>
+      <c r="J69" s="12">
+        <v>24.125</v>
+      </c>
+      <c r="K69" s="16">
+        <v>-20.075</v>
+      </c>
+      <c r="L69" s="15">
+        <v>-83.2</v>
+      </c>
+      <c r="M69" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>434</v>
+      </c>
+      <c r="B70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" t="s">
+        <v>438</v>
+      </c>
+      <c r="E70" t="s">
+        <v>432</v>
+      </c>
+      <c r="F70" s="12">
+        <v>7</v>
+      </c>
+      <c r="G70" s="13">
+        <v>5.957</v>
+      </c>
+      <c r="H70" s="14">
+        <v>1.043</v>
+      </c>
+      <c r="I70" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="J70" s="12">
+        <v>59.2</v>
+      </c>
+      <c r="K70" s="16">
+        <v>-52.2</v>
+      </c>
+      <c r="L70" s="15">
+        <v>-88.2</v>
+      </c>
+      <c r="M70" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>434</v>
+      </c>
+      <c r="B71" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" t="s">
+        <v>438</v>
+      </c>
+      <c r="E71" t="s">
+        <v>431</v>
+      </c>
+      <c r="F71" s="12">
+        <v>14.5</v>
+      </c>
+      <c r="G71" s="13">
+        <v>10.463</v>
+      </c>
+      <c r="H71" s="14">
+        <v>4.037</v>
+      </c>
+      <c r="I71" s="15">
+        <v>38.6</v>
+      </c>
+      <c r="J71" s="12">
+        <v>107.833</v>
+      </c>
+      <c r="K71" s="16">
+        <v>-93.333</v>
+      </c>
+      <c r="L71" s="15">
+        <v>-86.5</v>
+      </c>
+      <c r="M71" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>434</v>
+      </c>
+      <c r="B72" t="s">
+        <v>163</v>
+      </c>
+      <c r="C72" t="s">
+        <v>200</v>
+      </c>
+      <c r="D72" t="s">
+        <v>438</v>
+      </c>
+      <c r="E72" t="s">
+        <v>442</v>
+      </c>
+      <c r="F72" s="12">
+        <v>27</v>
+      </c>
+      <c r="G72" s="13">
+        <v>23.985</v>
+      </c>
+      <c r="H72" s="14">
+        <v>3.015</v>
+      </c>
+      <c r="I72" s="15">
+        <v>12.6</v>
+      </c>
+      <c r="J72" s="12">
+        <v>140</v>
+      </c>
+      <c r="K72" s="16">
+        <v>-113</v>
+      </c>
+      <c r="L72" s="15">
+        <v>-80.7</v>
+      </c>
+      <c r="M72" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>434</v>
+      </c>
+      <c r="B73" t="s">
+        <v>163</v>
+      </c>
+      <c r="C73" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" t="s">
+        <v>438</v>
+      </c>
+      <c r="E73" t="s">
+        <v>465</v>
+      </c>
+      <c r="F73" s="12">
+        <v>45</v>
+      </c>
+      <c r="G73" s="13">
+        <v>37.478</v>
+      </c>
+      <c r="H73" s="14">
+        <v>7.522</v>
+      </c>
+      <c r="I73" s="15">
+        <v>20.1</v>
+      </c>
+      <c r="J73" s="12">
+        <v>263</v>
+      </c>
+      <c r="K73" s="16">
+        <v>-218</v>
+      </c>
+      <c r="L73" s="15">
+        <v>-82.9</v>
+      </c>
+      <c r="M73" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F74" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="G74" s="9"/>
+      <c r="H74" s="10">
+        <v>2.178</v>
+      </c>
+      <c r="I74" s="11"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="10">
+        <v>-3.071</v>
+      </c>
+      <c r="L74" s="11"/>
+      <c r="M74" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>434</v>
+      </c>
+      <c r="B75" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" t="s">
+        <v>302</v>
+      </c>
+      <c r="D75" t="s">
+        <v>301</v>
+      </c>
+      <c r="E75" t="s">
+        <v>426</v>
+      </c>
+      <c r="F75" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="G75" s="13">
+        <v>3.621</v>
+      </c>
+      <c r="H75" s="14">
+        <v>0.129</v>
+      </c>
+      <c r="I75" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="J75" s="12">
+        <v>7.25</v>
+      </c>
+      <c r="K75" s="16">
+        <v>-3.5</v>
+      </c>
+      <c r="L75" s="15">
+        <v>-48.3</v>
+      </c>
+      <c r="M75" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>434</v>
+      </c>
+      <c r="B76" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" t="s">
+        <v>302</v>
+      </c>
+      <c r="D76" t="s">
+        <v>301</v>
+      </c>
+      <c r="E76" t="s">
+        <v>424</v>
+      </c>
+      <c r="F76" s="12">
+        <v>3.15</v>
+      </c>
+      <c r="G76" s="13">
+        <v>2.842</v>
+      </c>
+      <c r="H76" s="14">
+        <v>0.308</v>
+      </c>
+      <c r="I76" s="15">
+        <v>10.8</v>
+      </c>
+      <c r="J76" s="12">
+        <v>9.967</v>
+      </c>
+      <c r="K76" s="16">
+        <v>-6.817</v>
+      </c>
+      <c r="L76" s="15">
+        <v>-68.4</v>
+      </c>
+      <c r="M76" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>434</v>
+      </c>
+      <c r="B77" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" t="s">
+        <v>302</v>
+      </c>
+      <c r="D77" t="s">
+        <v>301</v>
+      </c>
+      <c r="E77" t="s">
+        <v>423</v>
+      </c>
+      <c r="F77" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="G77" s="13">
+        <v>3.652</v>
+      </c>
+      <c r="H77" s="14">
+        <v>0.448</v>
+      </c>
+      <c r="I77" s="15">
+        <v>12.3</v>
+      </c>
+      <c r="J77" s="12">
+        <v>21</v>
+      </c>
+      <c r="K77" s="16">
+        <v>-16.9</v>
+      </c>
+      <c r="L77" s="15">
+        <v>-80.5</v>
+      </c>
+      <c r="M77" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>434</v>
+      </c>
+      <c r="B78" t="s">
+        <v>168</v>
+      </c>
+      <c r="C78" t="s">
+        <v>302</v>
+      </c>
+      <c r="D78" t="s">
+        <v>301</v>
+      </c>
+      <c r="E78" t="s">
+        <v>432</v>
+      </c>
+      <c r="F78" s="12">
+        <v>7</v>
+      </c>
+      <c r="G78" s="13">
+        <v>6.333</v>
+      </c>
+      <c r="H78" s="14">
+        <v>0.667</v>
+      </c>
+      <c r="I78" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="J78" s="12">
+        <v>51.8</v>
+      </c>
+      <c r="K78" s="16">
+        <v>-44.8</v>
+      </c>
+      <c r="L78" s="15">
+        <v>-86.5</v>
+      </c>
+      <c r="M78" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>434</v>
+      </c>
+      <c r="B79" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" t="s">
+        <v>302</v>
+      </c>
+      <c r="D79" t="s">
+        <v>301</v>
+      </c>
+      <c r="E79" t="s">
+        <v>431</v>
+      </c>
+      <c r="F79" s="12">
+        <v>17</v>
+      </c>
+      <c r="G79" s="13">
+        <v>11.593</v>
+      </c>
+      <c r="H79" s="14">
+        <v>5.407</v>
+      </c>
+      <c r="I79" s="15">
+        <v>46.6</v>
+      </c>
+      <c r="J79" s="12">
+        <v>138.333</v>
+      </c>
+      <c r="K79" s="16">
+        <v>-121.333</v>
+      </c>
+      <c r="L79" s="15">
+        <v>-87.7</v>
+      </c>
+      <c r="M79" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>434</v>
+      </c>
+      <c r="B80" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" t="s">
+        <v>302</v>
+      </c>
+      <c r="D80" t="s">
+        <v>301</v>
+      </c>
+      <c r="E80" t="s">
+        <v>442</v>
+      </c>
+      <c r="F80" s="12">
+        <v>38</v>
+      </c>
+      <c r="G80" s="13">
+        <v>24.828</v>
+      </c>
+      <c r="H80" s="14">
+        <v>13.172</v>
+      </c>
+      <c r="I80" s="15">
+        <v>53.1</v>
+      </c>
+      <c r="J80" s="12">
+        <v>158</v>
+      </c>
+      <c r="K80" s="16">
+        <v>-120</v>
+      </c>
+      <c r="L80" s="15">
+        <v>-75.9</v>
+      </c>
+      <c r="M80" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>434</v>
+      </c>
+      <c r="B81" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" t="s">
+        <v>302</v>
+      </c>
+      <c r="D81" t="s">
+        <v>301</v>
+      </c>
+      <c r="E81" t="s">
+        <v>465</v>
+      </c>
+      <c r="F81" s="12">
+        <v>70</v>
+      </c>
+      <c r="G81" s="13">
+        <v>50.621</v>
+      </c>
+      <c r="H81" s="14">
+        <v>19.379</v>
+      </c>
+      <c r="I81" s="15">
+        <v>38.3</v>
+      </c>
+      <c r="J81" s="12">
+        <v>325</v>
+      </c>
+      <c r="K81" s="16">
+        <v>-255</v>
+      </c>
+      <c r="L81" s="15">
+        <v>-78.5</v>
+      </c>
+      <c r="M81" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F82" s="8">
+        <v>12</v>
+      </c>
+      <c r="G82" s="9"/>
+      <c r="H82" s="10">
+        <v>2.286</v>
+      </c>
+      <c r="I82" s="11"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L82" s="11"/>
+      <c r="M82" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>434</v>
+      </c>
+      <c r="B83" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83" t="s">
+        <v>305</v>
+      </c>
+      <c r="E83" t="s">
+        <v>426</v>
+      </c>
+      <c r="F83" s="12">
+        <v>4.85</v>
+      </c>
+      <c r="G83" s="13">
+        <v>4.443</v>
+      </c>
+      <c r="H83" s="14">
+        <v>0.407</v>
+      </c>
+      <c r="I83" s="15">
+        <v>9.2</v>
+      </c>
+      <c r="J83" s="12">
+        <v>9.875</v>
+      </c>
+      <c r="K83" s="16">
+        <v>-5.025</v>
+      </c>
+      <c r="L83" s="15">
+        <v>-50.9</v>
+      </c>
+      <c r="M83" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>434</v>
+      </c>
+      <c r="B84" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" t="s">
+        <v>306</v>
+      </c>
+      <c r="D84" t="s">
+        <v>305</v>
+      </c>
+      <c r="E84" t="s">
+        <v>424</v>
+      </c>
+      <c r="F84" s="12">
+        <v>3.35</v>
+      </c>
+      <c r="G84" s="13">
+        <v>3.251</v>
+      </c>
+      <c r="H84" s="14">
+        <v>0.099</v>
+      </c>
+      <c r="I84" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="J84" s="12">
+        <v>14.25</v>
+      </c>
+      <c r="K84" s="16">
+        <v>-10.9</v>
+      </c>
+      <c r="L84" s="15">
+        <v>-76.5</v>
+      </c>
+      <c r="M84" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>434</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" t="s">
+        <v>306</v>
+      </c>
+      <c r="D85" t="s">
+        <v>305</v>
+      </c>
+      <c r="E85" t="s">
+        <v>423</v>
+      </c>
+      <c r="F85" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G85" s="13">
+        <v>3.204</v>
+      </c>
+      <c r="H85" s="14">
+        <v>0.346</v>
+      </c>
+      <c r="I85" s="15">
+        <v>10.8</v>
+      </c>
+      <c r="J85" s="12">
+        <v>28.313</v>
+      </c>
+      <c r="K85" s="16">
+        <v>-24.763</v>
+      </c>
+      <c r="L85" s="15">
+        <v>-87.5</v>
+      </c>
+      <c r="M85" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>434</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D86" t="s">
+        <v>305</v>
+      </c>
+      <c r="E86" t="s">
+        <v>432</v>
+      </c>
+      <c r="F86" s="12">
+        <v>5.8</v>
+      </c>
+      <c r="G86" s="13">
+        <v>4.899</v>
+      </c>
+      <c r="H86" s="14">
+        <v>0.901</v>
+      </c>
+      <c r="I86" s="15">
+        <v>18.4</v>
+      </c>
+      <c r="J86" s="12">
+        <v>79.2</v>
+      </c>
+      <c r="K86" s="16">
+        <v>-73.4</v>
+      </c>
+      <c r="L86" s="15">
+        <v>-92.7</v>
+      </c>
+      <c r="M86" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>434</v>
+      </c>
+      <c r="B87" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" t="s">
+        <v>306</v>
+      </c>
+      <c r="D87" t="s">
+        <v>305</v>
+      </c>
+      <c r="E87" t="s">
+        <v>431</v>
+      </c>
+      <c r="F87" s="12">
+        <v>11</v>
+      </c>
+      <c r="G87" s="13">
+        <v>8.59</v>
+      </c>
+      <c r="H87" s="14">
+        <v>2.41</v>
+      </c>
+      <c r="I87" s="15">
+        <v>28.1</v>
+      </c>
+      <c r="J87" s="12">
+        <v>190.833</v>
+      </c>
+      <c r="K87" s="16">
+        <v>-179.833</v>
+      </c>
+      <c r="L87" s="15">
+        <v>-94.2</v>
+      </c>
+      <c r="M87" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>434</v>
+      </c>
+      <c r="B88" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" t="s">
+        <v>306</v>
+      </c>
+      <c r="D88" t="s">
+        <v>305</v>
+      </c>
+      <c r="E88" t="s">
+        <v>442</v>
+      </c>
+      <c r="F88" s="12">
+        <v>24</v>
+      </c>
+      <c r="G88" s="13">
+        <v>19.843</v>
+      </c>
+      <c r="H88" s="14">
+        <v>4.157</v>
+      </c>
+      <c r="I88" s="15">
+        <v>21</v>
+      </c>
+      <c r="J88" s="12">
+        <v>231</v>
+      </c>
+      <c r="K88" s="16">
+        <v>-207</v>
+      </c>
+      <c r="L88" s="15">
+        <v>-89.6</v>
+      </c>
+      <c r="M88" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>434</v>
+      </c>
+      <c r="B89" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" t="s">
+        <v>306</v>
+      </c>
+      <c r="D89" t="s">
+        <v>305</v>
+      </c>
+      <c r="E89" t="s">
+        <v>465</v>
+      </c>
+      <c r="F89" s="12">
+        <v>35</v>
+      </c>
+      <c r="G89" s="13">
+        <v>26.174</v>
+      </c>
+      <c r="H89" s="14">
+        <v>8.826</v>
+      </c>
+      <c r="I89" s="15">
+        <v>33.7</v>
+      </c>
+      <c r="J89" s="12">
+        <v>313</v>
+      </c>
+      <c r="K89" s="16">
+        <v>-278</v>
+      </c>
+      <c r="L89" s="15">
+        <v>-88.8</v>
+      </c>
+      <c r="M89" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F90" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G90" s="9"/>
+      <c r="H90" s="10">
+        <v>0.728</v>
+      </c>
+      <c r="I90" s="11"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="10">
+        <v>-3.007</v>
+      </c>
+      <c r="L90" s="11"/>
+      <c r="M90" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>434</v>
+      </c>
+      <c r="B91" t="s">
+        <v>397</v>
+      </c>
+      <c r="C91" t="s">
+        <v>309</v>
+      </c>
+      <c r="D91" t="s">
+        <v>308</v>
+      </c>
+      <c r="E91" t="s">
+        <v>426</v>
+      </c>
+      <c r="F91" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G91" s="13">
+        <v>3.259</v>
+      </c>
+      <c r="H91" s="14">
+        <v>0.041</v>
+      </c>
+      <c r="I91" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="J91" s="12">
+        <v>6.75</v>
+      </c>
+      <c r="K91" s="16">
+        <v>-3.45</v>
+      </c>
+      <c r="L91" s="15">
+        <v>-51.1</v>
+      </c>
+      <c r="M91" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>434</v>
+      </c>
+      <c r="B92" t="s">
+        <v>397</v>
+      </c>
+      <c r="C92" t="s">
+        <v>309</v>
+      </c>
+      <c r="D92" t="s">
+        <v>308</v>
+      </c>
+      <c r="E92" t="s">
+        <v>424</v>
+      </c>
+      <c r="F92" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G92" s="13">
+        <v>3.134</v>
+      </c>
+      <c r="H92" s="14">
+        <v>0.166</v>
+      </c>
+      <c r="I92" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="J92" s="12">
+        <v>12</v>
+      </c>
+      <c r="K92" s="16">
+        <v>-8.7</v>
+      </c>
+      <c r="L92" s="15">
+        <v>-72.5</v>
+      </c>
+      <c r="M92" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>434</v>
+      </c>
+      <c r="B93" t="s">
+        <v>397</v>
+      </c>
+      <c r="C93" t="s">
+        <v>309</v>
+      </c>
+      <c r="D93" t="s">
+        <v>308</v>
+      </c>
+      <c r="E93" t="s">
+        <v>423</v>
+      </c>
+      <c r="F93" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G93" s="13">
+        <v>3.495</v>
+      </c>
+      <c r="H93" s="14">
+        <v>0.305</v>
+      </c>
+      <c r="I93" s="15">
+        <v>8.7</v>
+      </c>
+      <c r="J93" s="12">
+        <v>23.188</v>
+      </c>
+      <c r="K93" s="16">
+        <v>-19.388</v>
+      </c>
+      <c r="L93" s="15">
+        <v>-83.6</v>
+      </c>
+      <c r="M93" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>434</v>
+      </c>
+      <c r="B94" t="s">
+        <v>397</v>
+      </c>
+      <c r="C94" t="s">
+        <v>309</v>
+      </c>
+      <c r="D94" t="s">
+        <v>308</v>
+      </c>
+      <c r="E94" t="s">
+        <v>432</v>
+      </c>
+      <c r="F94" s="12">
+        <v>8</v>
+      </c>
+      <c r="G94" s="13">
+        <v>6.278</v>
+      </c>
+      <c r="H94" s="14">
+        <v>1.722</v>
+      </c>
+      <c r="I94" s="15">
+        <v>27.4</v>
+      </c>
+      <c r="J94" s="12">
+        <v>66.2</v>
+      </c>
+      <c r="K94" s="16">
+        <v>-58.2</v>
+      </c>
+      <c r="L94" s="15">
+        <v>-87.9</v>
+      </c>
+      <c r="M94" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>434</v>
+      </c>
+      <c r="B95" t="s">
+        <v>397</v>
+      </c>
+      <c r="C95" t="s">
+        <v>309</v>
+      </c>
+      <c r="D95" t="s">
+        <v>308</v>
+      </c>
+      <c r="E95" t="s">
+        <v>431</v>
+      </c>
+      <c r="F95" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="G95" s="13">
+        <v>11.043</v>
+      </c>
+      <c r="H95" s="14">
+        <v>7.457</v>
+      </c>
+      <c r="I95" s="15">
+        <v>67.5</v>
+      </c>
+      <c r="J95" s="12">
+        <v>170.833</v>
+      </c>
+      <c r="K95" s="16">
+        <v>-152.333</v>
+      </c>
+      <c r="L95" s="15">
+        <v>-89.2</v>
+      </c>
+      <c r="M95" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>434</v>
+      </c>
+      <c r="B96" t="s">
+        <v>397</v>
+      </c>
+      <c r="C96" t="s">
+        <v>309</v>
+      </c>
+      <c r="D96" t="s">
+        <v>308</v>
+      </c>
+      <c r="E96" t="s">
+        <v>442</v>
+      </c>
+      <c r="F96" s="12">
+        <v>40</v>
+      </c>
+      <c r="G96" s="13">
+        <v>27.068</v>
+      </c>
+      <c r="H96" s="14">
+        <v>12.932</v>
+      </c>
+      <c r="I96" s="15">
+        <v>47.8</v>
+      </c>
+      <c r="J96" s="12">
+        <v>182</v>
+      </c>
+      <c r="K96" s="16">
+        <v>-142</v>
+      </c>
+      <c r="L96" s="15">
+        <v>-78</v>
+      </c>
+      <c r="M96" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>434</v>
+      </c>
+      <c r="B97" t="s">
+        <v>397</v>
+      </c>
+      <c r="C97" t="s">
+        <v>309</v>
+      </c>
+      <c r="D97" t="s">
+        <v>308</v>
+      </c>
+      <c r="E97" t="s">
+        <v>465</v>
+      </c>
+      <c r="F97" s="12">
+        <v>80</v>
+      </c>
+      <c r="G97" s="13">
+        <v>45.032</v>
+      </c>
+      <c r="H97" s="14">
+        <v>34.968</v>
+      </c>
+      <c r="I97" s="15">
+        <v>77.7</v>
+      </c>
+      <c r="J97" s="12">
+        <v>378</v>
+      </c>
+      <c r="K97" s="16">
+        <v>-298</v>
+      </c>
+      <c r="L97" s="15">
+        <v>-78.8</v>
+      </c>
+      <c r="M97" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F98" s="8">
+        <v>8</v>
+      </c>
+      <c r="G98" s="9"/>
+      <c r="H98" s="10">
+        <v>2.425</v>
+      </c>
+      <c r="I98" s="11"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="10">
+        <v>-3.875</v>
+      </c>
+      <c r="L98" s="11"/>
+      <c r="M98" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>434</v>
+      </c>
+      <c r="B99" t="s">
+        <v>399</v>
+      </c>
+      <c r="C99" t="s">
+        <v>294</v>
+      </c>
+      <c r="D99" t="s">
+        <v>293</v>
+      </c>
+      <c r="E99" t="s">
+        <v>426</v>
+      </c>
+      <c r="F99" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="G99" s="13">
+        <v>3.651</v>
+      </c>
+      <c r="H99" s="14">
+        <v>0.099</v>
+      </c>
+      <c r="I99" s="15">
+        <v>2.7</v>
+      </c>
+      <c r="J99" s="12">
+        <v>7.875</v>
+      </c>
+      <c r="K99" s="16">
+        <v>-4.125</v>
+      </c>
+      <c r="L99" s="15">
+        <v>-52.4</v>
+      </c>
+      <c r="M99" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>434</v>
+      </c>
+      <c r="B100" t="s">
+        <v>399</v>
+      </c>
+      <c r="C100" t="s">
+        <v>294</v>
+      </c>
+      <c r="D100" t="s">
+        <v>293</v>
+      </c>
+      <c r="E100" t="s">
+        <v>424</v>
+      </c>
+      <c r="F100" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G100" s="13">
+        <v>3.034</v>
+      </c>
+      <c r="H100" s="14">
+        <v>0.166</v>
+      </c>
+      <c r="I100" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="J100" s="12">
+        <v>12.333</v>
+      </c>
+      <c r="K100" s="16">
+        <v>-9.133</v>
+      </c>
+      <c r="L100" s="15">
+        <v>-74</v>
+      </c>
+      <c r="M100" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>434</v>
+      </c>
+      <c r="B101" t="s">
+        <v>399</v>
+      </c>
+      <c r="C101" t="s">
+        <v>294</v>
+      </c>
+      <c r="D101" t="s">
+        <v>293</v>
+      </c>
+      <c r="E101" t="s">
+        <v>423</v>
+      </c>
+      <c r="F101" s="12">
+        <v>4</v>
+      </c>
+      <c r="G101" s="13">
+        <v>3.522</v>
+      </c>
+      <c r="H101" s="14">
+        <v>0.478</v>
+      </c>
+      <c r="I101" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="J101" s="12">
+        <v>29.125</v>
+      </c>
+      <c r="K101" s="16">
+        <v>-25.125</v>
+      </c>
+      <c r="L101" s="15">
+        <v>-86.3</v>
+      </c>
+      <c r="M101" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>434</v>
+      </c>
+      <c r="B102" t="s">
+        <v>399</v>
+      </c>
+      <c r="C102" t="s">
+        <v>294</v>
+      </c>
+      <c r="D102" t="s">
+        <v>293</v>
+      </c>
+      <c r="E102" t="s">
+        <v>432</v>
+      </c>
+      <c r="F102" s="12">
+        <v>7</v>
+      </c>
+      <c r="G102" s="13">
+        <v>5.824</v>
+      </c>
+      <c r="H102" s="14">
+        <v>1.176</v>
+      </c>
+      <c r="I102" s="15">
+        <v>20.2</v>
+      </c>
+      <c r="J102" s="12">
+        <v>83.4</v>
+      </c>
+      <c r="K102" s="16">
+        <v>-76.4</v>
+      </c>
+      <c r="L102" s="15">
+        <v>-91.6</v>
+      </c>
+      <c r="M102" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>434</v>
+      </c>
+      <c r="B103" t="s">
+        <v>399</v>
+      </c>
+      <c r="C103" t="s">
+        <v>294</v>
+      </c>
+      <c r="D103" t="s">
+        <v>293</v>
+      </c>
+      <c r="E103" t="s">
+        <v>431</v>
+      </c>
+      <c r="F103" s="12">
+        <v>16</v>
+      </c>
+      <c r="G103" s="13">
+        <v>11.335</v>
+      </c>
+      <c r="H103" s="14">
+        <v>4.665</v>
+      </c>
+      <c r="I103" s="15">
+        <v>41.2</v>
+      </c>
+      <c r="J103" s="12">
+        <v>205.5</v>
+      </c>
+      <c r="K103" s="16">
+        <v>-189.5</v>
+      </c>
+      <c r="L103" s="15">
+        <v>-92.2</v>
+      </c>
+      <c r="M103" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>434</v>
+      </c>
+      <c r="B104" t="s">
+        <v>399</v>
+      </c>
+      <c r="C104" t="s">
+        <v>294</v>
+      </c>
+      <c r="D104" t="s">
+        <v>293</v>
+      </c>
+      <c r="E104" t="s">
+        <v>442</v>
+      </c>
+      <c r="F104" s="12">
+        <v>35</v>
+      </c>
+      <c r="G104" s="13">
+        <v>23.587</v>
+      </c>
+      <c r="H104" s="14">
+        <v>11.413</v>
+      </c>
+      <c r="I104" s="15">
+        <v>48.4</v>
+      </c>
+      <c r="J104" s="12">
+        <v>192</v>
+      </c>
+      <c r="K104" s="16">
+        <v>-157</v>
+      </c>
+      <c r="L104" s="15">
+        <v>-81.8</v>
+      </c>
+      <c r="M104" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>434</v>
+      </c>
+      <c r="B105" t="s">
+        <v>399</v>
+      </c>
+      <c r="C105" t="s">
+        <v>294</v>
+      </c>
+      <c r="D105" t="s">
+        <v>293</v>
+      </c>
+      <c r="E105" t="s">
+        <v>465</v>
+      </c>
+      <c r="F105" s="12">
+        <v>60</v>
+      </c>
+      <c r="G105" s="13">
+        <v>39.948</v>
+      </c>
+      <c r="H105" s="14">
+        <v>20.052</v>
+      </c>
+      <c r="I105" s="15">
+        <v>50.2</v>
+      </c>
+      <c r="J105" s="12">
+        <v>341</v>
+      </c>
+      <c r="K105" s="16">
+        <v>-281</v>
+      </c>
+      <c r="L105" s="15">
+        <v>-82.4</v>
+      </c>
+      <c r="M105" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F106" s="8">
+        <v>35</v>
+      </c>
+      <c r="G106" s="9"/>
+      <c r="H106" s="10">
+        <v>3.121</v>
+      </c>
+      <c r="I106" s="11"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L106" s="11"/>
+      <c r="M106" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>434</v>
+      </c>
+      <c r="B107" t="s">
+        <v>402</v>
+      </c>
+      <c r="C107" t="s">
+        <v>322</v>
+      </c>
+      <c r="D107" t="s">
+        <v>315</v>
+      </c>
+      <c r="E107" t="s">
+        <v>426</v>
+      </c>
+      <c r="F107" s="12">
+        <v>10.25</v>
+      </c>
+      <c r="G107" s="13">
+        <v>9.016</v>
+      </c>
+      <c r="H107" s="14">
+        <v>1.234</v>
+      </c>
+      <c r="I107" s="15">
+        <v>13.7</v>
+      </c>
+      <c r="J107" s="12">
+        <v>30.5</v>
+      </c>
+      <c r="K107" s="16">
+        <v>-20.25</v>
+      </c>
+      <c r="L107" s="15">
+        <v>-66.4</v>
+      </c>
+      <c r="M107" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>434</v>
+      </c>
+      <c r="B108" t="s">
+        <v>402</v>
+      </c>
+      <c r="C108" t="s">
+        <v>322</v>
+      </c>
+      <c r="D108" t="s">
+        <v>315</v>
+      </c>
+      <c r="E108" t="s">
+        <v>424</v>
+      </c>
+      <c r="F108" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="G108" s="13">
+        <v>4.67</v>
+      </c>
+      <c r="H108" s="14">
+        <v>0.93</v>
+      </c>
+      <c r="I108" s="15">
+        <v>19.9</v>
+      </c>
+      <c r="J108" s="12">
+        <v>54.583</v>
+      </c>
+      <c r="K108" s="16">
+        <v>-48.983</v>
+      </c>
+      <c r="L108" s="15">
+        <v>-89.7</v>
+      </c>
+      <c r="M108" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>434</v>
+      </c>
+      <c r="B109" t="s">
+        <v>402</v>
+      </c>
+      <c r="C109" t="s">
+        <v>322</v>
+      </c>
+      <c r="D109" t="s">
+        <v>315</v>
+      </c>
+      <c r="E109" t="s">
+        <v>423</v>
+      </c>
+      <c r="F109" s="12">
+        <v>4</v>
+      </c>
+      <c r="G109" s="13">
+        <v>3.611</v>
+      </c>
+      <c r="H109" s="14">
+        <v>0.389</v>
+      </c>
+      <c r="I109" s="15">
+        <v>10.8</v>
+      </c>
+      <c r="J109" s="12">
+        <v>128.625</v>
+      </c>
+      <c r="K109" s="16">
+        <v>-124.625</v>
+      </c>
+      <c r="L109" s="15">
+        <v>-96.9</v>
+      </c>
+      <c r="M109" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>434</v>
+      </c>
+      <c r="B110" t="s">
+        <v>402</v>
+      </c>
+      <c r="C110" t="s">
+        <v>322</v>
+      </c>
+      <c r="D110" t="s">
+        <v>315</v>
+      </c>
+      <c r="E110" t="s">
+        <v>432</v>
+      </c>
+      <c r="F110" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="G110" s="13">
+        <v>3.853</v>
+      </c>
+      <c r="H110" s="14">
+        <v>0.197</v>
+      </c>
+      <c r="I110" s="15">
+        <v>5.1</v>
+      </c>
+      <c r="J110" s="12">
+        <v>249.65</v>
+      </c>
+      <c r="K110" s="16">
+        <v>-245.6</v>
+      </c>
+      <c r="L110" s="15">
+        <v>-98.4</v>
+      </c>
+      <c r="M110" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>434</v>
+      </c>
+      <c r="B111" t="s">
+        <v>402</v>
+      </c>
+      <c r="C111" t="s">
+        <v>322</v>
+      </c>
+      <c r="D111" t="s">
+        <v>315</v>
+      </c>
+      <c r="E111" t="s">
+        <v>431</v>
+      </c>
+      <c r="F111" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="G111" s="13">
+        <v>4.938</v>
+      </c>
+      <c r="H111" s="14">
+        <v>0.662</v>
+      </c>
+      <c r="I111" s="15">
+        <v>13.4</v>
+      </c>
+      <c r="J111" s="12">
+        <v>308.167</v>
+      </c>
+      <c r="K111" s="16">
+        <v>-302.567</v>
+      </c>
+      <c r="L111" s="15">
+        <v>-98.2</v>
+      </c>
+      <c r="M111" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>434</v>
+      </c>
+      <c r="B112" t="s">
+        <v>402</v>
+      </c>
+      <c r="C112" t="s">
+        <v>322</v>
+      </c>
+      <c r="D112" t="s">
+        <v>315</v>
+      </c>
+      <c r="E112" t="s">
+        <v>442</v>
+      </c>
+      <c r="F112" s="12">
+        <v>8.8</v>
+      </c>
+      <c r="G112" s="13">
+        <v>11.501</v>
+      </c>
+      <c r="H112" s="17">
+        <v>-2.701</v>
+      </c>
+      <c r="I112" s="15">
+        <v>-23.5</v>
+      </c>
+      <c r="J112" s="12">
+        <v>320.2</v>
+      </c>
+      <c r="K112" s="16">
+        <v>-311.4</v>
+      </c>
+      <c r="L112" s="15">
+        <v>-97.2</v>
+      </c>
+      <c r="M112" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>434</v>
+      </c>
+      <c r="B113" t="s">
+        <v>402</v>
+      </c>
+      <c r="C113" t="s">
+        <v>322</v>
+      </c>
+      <c r="D113" t="s">
+        <v>315</v>
+      </c>
+      <c r="E113" t="s">
+        <v>465</v>
+      </c>
+      <c r="F113" s="12">
+        <v>9</v>
+      </c>
+      <c r="G113" s="13">
+        <v>6.261</v>
+      </c>
+      <c r="H113" s="14">
+        <v>2.739</v>
+      </c>
+      <c r="I113" s="15">
+        <v>43.8</v>
+      </c>
+      <c r="J113" s="12">
+        <v>394.44</v>
+      </c>
+      <c r="K113" s="16">
+        <v>-385.44</v>
+      </c>
+      <c r="L113" s="15">
+        <v>-97.7</v>
+      </c>
+      <c r="M113" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F114" s="8">
+        <v>24</v>
+      </c>
+      <c r="G114" s="9"/>
+      <c r="H114" s="10">
+        <v>2.613</v>
+      </c>
+      <c r="I114" s="11"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L114" s="11"/>
+      <c r="M114" s="4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>434</v>
+      </c>
+      <c r="B115" t="s">
+        <v>405</v>
+      </c>
+      <c r="C115" t="s">
+        <v>316</v>
+      </c>
+      <c r="D115" t="s">
+        <v>323</v>
+      </c>
+      <c r="E115" t="s">
+        <v>426</v>
+      </c>
+      <c r="F115" s="12">
+        <v>8</v>
+      </c>
+      <c r="G115" s="13">
+        <v>7.156</v>
+      </c>
+      <c r="H115" s="14">
+        <v>0.844</v>
+      </c>
+      <c r="I115" s="15">
+        <v>11.8</v>
+      </c>
+      <c r="J115" s="12">
+        <v>19.25</v>
+      </c>
+      <c r="K115" s="16">
+        <v>-11.25</v>
+      </c>
+      <c r="L115" s="15">
+        <v>-58.4</v>
+      </c>
+      <c r="M115" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>434</v>
+      </c>
+      <c r="B116" t="s">
+        <v>405</v>
+      </c>
+      <c r="C116" t="s">
+        <v>316</v>
+      </c>
+      <c r="D116" t="s">
+        <v>323</v>
+      </c>
+      <c r="E116" t="s">
+        <v>424</v>
+      </c>
+      <c r="F116" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="G116" s="13">
+        <v>4.003</v>
+      </c>
+      <c r="H116" s="14">
+        <v>0.747</v>
+      </c>
+      <c r="I116" s="15">
+        <v>18.7</v>
+      </c>
+      <c r="J116" s="12">
+        <v>25.917</v>
+      </c>
+      <c r="K116" s="16">
+        <v>-21.167</v>
+      </c>
+      <c r="L116" s="15">
+        <v>-81.7</v>
+      </c>
+      <c r="M116" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>434</v>
+      </c>
+      <c r="B117" t="s">
+        <v>405</v>
+      </c>
+      <c r="C117" t="s">
+        <v>316</v>
+      </c>
+      <c r="D117" t="s">
+        <v>323</v>
+      </c>
+      <c r="E117" t="s">
+        <v>423</v>
+      </c>
+      <c r="F117" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="G117" s="13">
+        <v>3.566</v>
+      </c>
+      <c r="H117" s="14">
+        <v>0.084</v>
+      </c>
+      <c r="I117" s="15">
+        <v>2.4</v>
+      </c>
+      <c r="J117" s="12">
+        <v>48.25</v>
+      </c>
+      <c r="K117" s="16">
+        <v>-44.6</v>
+      </c>
+      <c r="L117" s="15">
+        <v>-92.4</v>
+      </c>
+      <c r="M117" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>434</v>
+      </c>
+      <c r="B118" t="s">
+        <v>405</v>
+      </c>
+      <c r="C118" t="s">
+        <v>316</v>
+      </c>
+      <c r="D118" t="s">
+        <v>323</v>
+      </c>
+      <c r="E118" t="s">
+        <v>432</v>
+      </c>
+      <c r="F118" s="12">
+        <v>4</v>
+      </c>
+      <c r="G118" s="13">
+        <v>3.96</v>
+      </c>
+      <c r="H118" s="14">
+        <v>0.04</v>
+      </c>
+      <c r="I118" s="15">
+        <v>1</v>
+      </c>
+      <c r="J118" s="12">
+        <v>114.3</v>
+      </c>
+      <c r="K118" s="16">
+        <v>-110.3</v>
+      </c>
+      <c r="L118" s="15">
+        <v>-96.5</v>
+      </c>
+      <c r="M118" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>434</v>
+      </c>
+      <c r="B119" t="s">
+        <v>405</v>
+      </c>
+      <c r="C119" t="s">
+        <v>316</v>
+      </c>
+      <c r="D119" t="s">
+        <v>323</v>
+      </c>
+      <c r="E119" t="s">
+        <v>431</v>
+      </c>
+      <c r="F119" s="12">
+        <v>6.75</v>
+      </c>
+      <c r="G119" s="13">
+        <v>5.608</v>
+      </c>
+      <c r="H119" s="14">
+        <v>1.142</v>
+      </c>
+      <c r="I119" s="15">
+        <v>20.4</v>
+      </c>
+      <c r="J119" s="12">
+        <v>227.667</v>
+      </c>
+      <c r="K119" s="16">
+        <v>-220.917</v>
+      </c>
+      <c r="L119" s="15">
+        <v>-97</v>
+      </c>
+      <c r="M119" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>434</v>
+      </c>
+      <c r="B120" t="s">
+        <v>405</v>
+      </c>
+      <c r="C120" t="s">
+        <v>316</v>
+      </c>
+      <c r="D120" t="s">
+        <v>323</v>
+      </c>
+      <c r="E120" t="s">
+        <v>442</v>
+      </c>
+      <c r="F120" s="12">
+        <v>12</v>
+      </c>
+      <c r="G120" s="13">
+        <v>10.914</v>
+      </c>
+      <c r="H120" s="14">
+        <v>1.086</v>
+      </c>
+      <c r="I120" s="15">
+        <v>10</v>
+      </c>
+      <c r="J120" s="12">
+        <v>198.8</v>
+      </c>
+      <c r="K120" s="16">
+        <v>-186.8</v>
+      </c>
+      <c r="L120" s="15">
+        <v>-94</v>
+      </c>
+      <c r="M120" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>434</v>
+      </c>
+      <c r="B121" t="s">
+        <v>405</v>
+      </c>
+      <c r="C121" t="s">
+        <v>316</v>
+      </c>
+      <c r="D121" t="s">
+        <v>323</v>
+      </c>
+      <c r="E121" t="s">
+        <v>465</v>
+      </c>
+      <c r="F121" s="12">
+        <v>14</v>
+      </c>
+      <c r="G121" s="13">
+        <v>9.609</v>
+      </c>
+      <c r="H121" s="14">
+        <v>4.391</v>
+      </c>
+      <c r="I121" s="15">
+        <v>45.7</v>
+      </c>
+      <c r="J121" s="12">
+        <v>213.7</v>
+      </c>
+      <c r="K121" s="16">
+        <v>-199.7</v>
+      </c>
+      <c r="L121" s="15">
+        <v>-93.4</v>
+      </c>
+      <c r="M121" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F122" s="8">
+        <v>31</v>
+      </c>
+      <c r="G122" s="9"/>
+      <c r="H122" s="10">
+        <v>3.209</v>
+      </c>
+      <c r="I122" s="11"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L122" s="11"/>
+      <c r="M122" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>434</v>
+      </c>
+      <c r="B123" t="s">
+        <v>407</v>
+      </c>
+      <c r="C123" t="s">
+        <v>320</v>
+      </c>
+      <c r="D123" t="s">
+        <v>319</v>
+      </c>
+      <c r="E123" t="s">
+        <v>426</v>
+      </c>
+      <c r="F123" s="12">
+        <v>8.25</v>
+      </c>
+      <c r="G123" s="13">
+        <v>7.734</v>
+      </c>
+      <c r="H123" s="14">
+        <v>0.516</v>
+      </c>
+      <c r="I123" s="15">
+        <v>6.7</v>
+      </c>
+      <c r="J123" s="12">
+        <v>32</v>
+      </c>
+      <c r="K123" s="16">
+        <v>-23.75</v>
+      </c>
+      <c r="L123" s="15">
+        <v>-74.2</v>
+      </c>
+      <c r="M123" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>434</v>
+      </c>
+      <c r="B124" t="s">
+        <v>407</v>
+      </c>
+      <c r="C124" t="s">
+        <v>320</v>
+      </c>
+      <c r="D124" t="s">
+        <v>319</v>
+      </c>
+      <c r="E124" t="s">
+        <v>424</v>
+      </c>
+      <c r="F124" s="12">
+        <v>5.1</v>
+      </c>
+      <c r="G124" s="13">
+        <v>4.307</v>
+      </c>
+      <c r="H124" s="14">
+        <v>0.793</v>
+      </c>
+      <c r="I124" s="15">
+        <v>18.4</v>
+      </c>
+      <c r="J124" s="12">
+        <v>66.433</v>
+      </c>
+      <c r="K124" s="16">
+        <v>-61.333</v>
+      </c>
+      <c r="L124" s="15">
+        <v>-92.3</v>
+      </c>
+      <c r="M124" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>434</v>
+      </c>
+      <c r="B125" t="s">
+        <v>407</v>
+      </c>
+      <c r="C125" t="s">
+        <v>320</v>
+      </c>
+      <c r="D125" t="s">
+        <v>319</v>
+      </c>
+      <c r="E125" t="s">
+        <v>423</v>
+      </c>
+      <c r="F125" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="G125" s="13">
+        <v>3.602</v>
+      </c>
+      <c r="H125" s="14">
+        <v>0.048</v>
+      </c>
+      <c r="I125" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="J125" s="12">
+        <v>196.625</v>
+      </c>
+      <c r="K125" s="16">
+        <v>-192.975</v>
+      </c>
+      <c r="L125" s="15">
+        <v>-98.1</v>
+      </c>
+      <c r="M125" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>434</v>
+      </c>
+      <c r="B126" t="s">
+        <v>407</v>
+      </c>
+      <c r="C126" t="s">
+        <v>320</v>
+      </c>
+      <c r="D126" t="s">
+        <v>319</v>
+      </c>
+      <c r="E126" t="s">
+        <v>432</v>
+      </c>
+      <c r="F126" s="12">
+        <v>4</v>
+      </c>
+      <c r="G126" s="13">
+        <v>3.933</v>
+      </c>
+      <c r="H126" s="14">
+        <v>0.067</v>
+      </c>
+      <c r="I126" s="15">
+        <v>1.7</v>
+      </c>
+      <c r="J126" s="12">
+        <v>261.7</v>
+      </c>
+      <c r="K126" s="16">
+        <v>-257.7</v>
+      </c>
+      <c r="L126" s="15">
+        <v>-98.5</v>
+      </c>
+      <c r="M126" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>434</v>
+      </c>
+      <c r="B127" t="s">
+        <v>407</v>
+      </c>
+      <c r="C127" t="s">
+        <v>320</v>
+      </c>
+      <c r="D127" t="s">
+        <v>319</v>
+      </c>
+      <c r="E127" t="s">
+        <v>431</v>
+      </c>
+      <c r="F127" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="G127" s="13">
+        <v>5.137</v>
+      </c>
+      <c r="H127" s="14">
+        <v>1.263</v>
+      </c>
+      <c r="I127" s="15">
+        <v>24.6</v>
+      </c>
+      <c r="J127" s="12">
+        <v>385.5</v>
+      </c>
+      <c r="K127" s="16">
+        <v>-379.1</v>
+      </c>
+      <c r="L127" s="15">
+        <v>-98.3</v>
+      </c>
+      <c r="M127" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>434</v>
+      </c>
+      <c r="B128" t="s">
+        <v>407</v>
+      </c>
+      <c r="C128" t="s">
+        <v>320</v>
+      </c>
+      <c r="D128" t="s">
+        <v>319</v>
+      </c>
+      <c r="E128" t="s">
+        <v>442</v>
+      </c>
+      <c r="F128" s="12">
+        <v>11</v>
+      </c>
+      <c r="G128" s="13">
+        <v>14.541</v>
+      </c>
+      <c r="H128" s="17">
+        <v>-3.541</v>
+      </c>
+      <c r="I128" s="15">
+        <v>-24.3</v>
+      </c>
+      <c r="J128" s="12">
+        <v>435.6</v>
+      </c>
+      <c r="K128" s="16">
+        <v>-424.6</v>
+      </c>
+      <c r="L128" s="15">
+        <v>-97.5</v>
+      </c>
+      <c r="M128" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>434</v>
+      </c>
+      <c r="B129" t="s">
+        <v>407</v>
+      </c>
+      <c r="C129" t="s">
+        <v>320</v>
+      </c>
+      <c r="D129" t="s">
+        <v>319</v>
+      </c>
+      <c r="E129" t="s">
+        <v>465</v>
+      </c>
+      <c r="F129" s="12">
+        <v>12</v>
+      </c>
+      <c r="G129" s="13">
+        <v>6.688</v>
+      </c>
+      <c r="H129" s="14">
+        <v>5.312</v>
+      </c>
+      <c r="I129" s="15">
+        <v>79.4</v>
+      </c>
+      <c r="J129" s="12">
+        <v>517.5</v>
+      </c>
+      <c r="K129" s="16">
+        <v>-505.5</v>
+      </c>
+      <c r="L129" s="15">
+        <v>-97.7</v>
+      </c>
+      <c r="M129" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F130" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="G130" s="9"/>
+      <c r="H130" s="10">
+        <v>2.047</v>
+      </c>
+      <c r="I130" s="11"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L130" s="11"/>
+      <c r="M130" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>434</v>
+      </c>
+      <c r="B131" t="s">
+        <v>408</v>
+      </c>
+      <c r="C131" t="s">
+        <v>443</v>
+      </c>
+      <c r="D131" t="s">
+        <v>410</v>
+      </c>
+      <c r="E131" t="s">
+        <v>426</v>
+      </c>
+      <c r="F131" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="G131" s="13">
+        <v>4.909</v>
+      </c>
+      <c r="H131" s="14">
+        <v>0.291</v>
+      </c>
+      <c r="I131" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="J131" s="12">
+        <v>12.375</v>
+      </c>
+      <c r="K131" s="16">
+        <v>-7.175</v>
+      </c>
+      <c r="L131" s="15">
+        <v>-58</v>
+      </c>
+      <c r="M131" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>434</v>
+      </c>
+      <c r="B132" t="s">
+        <v>408</v>
+      </c>
+      <c r="C132" t="s">
+        <v>443</v>
+      </c>
+      <c r="D132" t="s">
+        <v>410</v>
+      </c>
+      <c r="E132" t="s">
+        <v>424</v>
+      </c>
+      <c r="F132" s="12">
+        <v>3.35</v>
+      </c>
+      <c r="G132" s="13">
+        <v>3.178</v>
+      </c>
+      <c r="H132" s="14">
+        <v>0.172</v>
+      </c>
+      <c r="I132" s="15">
+        <v>5.4</v>
+      </c>
+      <c r="J132" s="12">
+        <v>18.2</v>
+      </c>
+      <c r="K132" s="16">
+        <v>-14.85</v>
+      </c>
+      <c r="L132" s="15">
+        <v>-81.6</v>
+      </c>
+      <c r="M132" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>434</v>
+      </c>
+      <c r="B133" t="s">
+        <v>408</v>
+      </c>
+      <c r="C133" t="s">
+        <v>443</v>
+      </c>
+      <c r="D133" t="s">
+        <v>410</v>
+      </c>
+      <c r="E133" t="s">
+        <v>423</v>
+      </c>
+      <c r="F133" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G133" s="13">
+        <v>3.258</v>
+      </c>
+      <c r="H133" s="14">
+        <v>0.342</v>
+      </c>
+      <c r="I133" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="J133" s="12">
+        <v>39.313</v>
+      </c>
+      <c r="K133" s="16">
+        <v>-35.713</v>
+      </c>
+      <c r="L133" s="15">
+        <v>-90.8</v>
+      </c>
+      <c r="M133" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>434</v>
+      </c>
+      <c r="B134" t="s">
+        <v>408</v>
+      </c>
+      <c r="C134" t="s">
+        <v>443</v>
+      </c>
+      <c r="D134" t="s">
+        <v>410</v>
+      </c>
+      <c r="E134" t="s">
+        <v>432</v>
+      </c>
+      <c r="F134" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="G134" s="13">
+        <v>4.654</v>
+      </c>
+      <c r="H134" s="14">
+        <v>0.946</v>
+      </c>
+      <c r="I134" s="15">
+        <v>20.3</v>
+      </c>
+      <c r="J134" s="12">
+        <v>134.6</v>
+      </c>
+      <c r="K134" s="16">
+        <v>-129</v>
+      </c>
+      <c r="L134" s="15">
+        <v>-95.8</v>
+      </c>
+      <c r="M134" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>434</v>
+      </c>
+      <c r="B135" t="s">
+        <v>408</v>
+      </c>
+      <c r="C135" t="s">
+        <v>443</v>
+      </c>
+      <c r="D135" t="s">
+        <v>410</v>
+      </c>
+      <c r="E135" t="s">
+        <v>431</v>
+      </c>
+      <c r="F135" s="12">
+        <v>10</v>
+      </c>
+      <c r="G135" s="13">
+        <v>8.056</v>
+      </c>
+      <c r="H135" s="14">
+        <v>1.944</v>
+      </c>
+      <c r="I135" s="15">
+        <v>24.1</v>
+      </c>
+      <c r="J135" s="12">
+        <v>243.167</v>
+      </c>
+      <c r="K135" s="16">
+        <v>-233.167</v>
+      </c>
+      <c r="L135" s="15">
+        <v>-95.9</v>
+      </c>
+      <c r="M135" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>434</v>
+      </c>
+      <c r="B136" t="s">
+        <v>408</v>
+      </c>
+      <c r="C136" t="s">
+        <v>443</v>
+      </c>
+      <c r="D136" t="s">
+        <v>410</v>
+      </c>
+      <c r="E136" t="s">
+        <v>442</v>
+      </c>
+      <c r="F136" s="12">
+        <v>20</v>
+      </c>
+      <c r="G136" s="13">
+        <v>17.906</v>
+      </c>
+      <c r="H136" s="14">
+        <v>2.094</v>
+      </c>
+      <c r="I136" s="15">
+        <v>11.7</v>
+      </c>
+      <c r="J136" s="12">
+        <v>298</v>
+      </c>
+      <c r="K136" s="16">
+        <v>-278</v>
+      </c>
+      <c r="L136" s="15">
+        <v>-93.3</v>
+      </c>
+      <c r="M136" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>434</v>
+      </c>
+      <c r="B137" t="s">
+        <v>408</v>
+      </c>
+      <c r="C137" t="s">
+        <v>443</v>
+      </c>
+      <c r="D137" t="s">
+        <v>410</v>
+      </c>
+      <c r="E137" t="s">
+        <v>465</v>
+      </c>
+      <c r="F137" s="12">
+        <v>30</v>
+      </c>
+      <c r="G137" s="13">
+        <v>22.567</v>
+      </c>
+      <c r="H137" s="14">
+        <v>7.433</v>
+      </c>
+      <c r="I137" s="15">
+        <v>32.9</v>
+      </c>
+      <c r="J137" s="12">
+        <v>410.6</v>
+      </c>
+      <c r="K137" s="16">
+        <v>-380.6</v>
+      </c>
+      <c r="L137" s="15">
+        <v>-92.7</v>
+      </c>
+      <c r="M137" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F138" s="8">
+        <v>18</v>
+      </c>
+      <c r="G138" s="9"/>
+      <c r="H138" s="10">
+        <v>1.458</v>
+      </c>
+      <c r="I138" s="11"/>
+      <c r="J138" s="8"/>
+      <c r="K138" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L138" s="11"/>
+      <c r="M138" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>434</v>
+      </c>
+      <c r="B139" t="s">
+        <v>409</v>
+      </c>
+      <c r="C139" t="s">
+        <v>325</v>
+      </c>
+      <c r="D139" t="s">
+        <v>329</v>
+      </c>
+      <c r="E139" t="s">
+        <v>426</v>
+      </c>
+      <c r="F139" s="12">
+        <v>6.25</v>
+      </c>
+      <c r="G139" s="13">
+        <v>5.918</v>
+      </c>
+      <c r="H139" s="14">
+        <v>0.332</v>
+      </c>
+      <c r="I139" s="15">
+        <v>5.6</v>
+      </c>
+      <c r="J139" s="12">
+        <v>12.25</v>
+      </c>
+      <c r="K139" s="16">
+        <v>-6</v>
+      </c>
+      <c r="L139" s="15">
+        <v>-49</v>
+      </c>
+      <c r="M139" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>434</v>
+      </c>
+      <c r="B140" t="s">
+        <v>409</v>
+      </c>
+      <c r="C140" t="s">
+        <v>325</v>
+      </c>
+      <c r="D140" t="s">
+        <v>329</v>
+      </c>
+      <c r="E140" t="s">
+        <v>424</v>
+      </c>
+      <c r="F140" s="12">
+        <v>4.15</v>
+      </c>
+      <c r="G140" s="13">
+        <v>3.834</v>
+      </c>
+      <c r="H140" s="14">
+        <v>0.316</v>
+      </c>
+      <c r="I140" s="15">
+        <v>8.2</v>
+      </c>
+      <c r="J140" s="12">
+        <v>15</v>
+      </c>
+      <c r="K140" s="16">
+        <v>-10.85</v>
+      </c>
+      <c r="L140" s="15">
+        <v>-72.3</v>
+      </c>
+      <c r="M140" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>434</v>
+      </c>
+      <c r="B141" t="s">
+        <v>409</v>
+      </c>
+      <c r="C141" t="s">
+        <v>325</v>
+      </c>
+      <c r="D141" t="s">
+        <v>329</v>
+      </c>
+      <c r="E141" t="s">
+        <v>423</v>
+      </c>
+      <c r="F141" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="G141" s="13">
+        <v>3.196</v>
+      </c>
+      <c r="H141" s="14">
+        <v>0.254</v>
+      </c>
+      <c r="I141" s="15">
+        <v>8</v>
+      </c>
+      <c r="J141" s="12">
+        <v>21</v>
+      </c>
+      <c r="K141" s="16">
+        <v>-17.55</v>
+      </c>
+      <c r="L141" s="15">
+        <v>-83.6</v>
+      </c>
+      <c r="M141" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>434</v>
+      </c>
+      <c r="B142" t="s">
+        <v>409</v>
+      </c>
+      <c r="C142" t="s">
+        <v>325</v>
+      </c>
+      <c r="D142" t="s">
+        <v>329</v>
+      </c>
+      <c r="E142" t="s">
+        <v>432</v>
+      </c>
+      <c r="F142" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="G142" s="13">
+        <v>4.128</v>
+      </c>
+      <c r="H142" s="14">
+        <v>0.472</v>
+      </c>
+      <c r="I142" s="15">
+        <v>11.4</v>
+      </c>
+      <c r="J142" s="12">
+        <v>40.8</v>
+      </c>
+      <c r="K142" s="16">
+        <v>-36.2</v>
+      </c>
+      <c r="L142" s="15">
+        <v>-88.7</v>
+      </c>
+      <c r="M142" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>434</v>
+      </c>
+      <c r="B143" t="s">
+        <v>409</v>
+      </c>
+      <c r="C143" t="s">
+        <v>325</v>
+      </c>
+      <c r="D143" t="s">
+        <v>329</v>
+      </c>
+      <c r="E143" t="s">
+        <v>431</v>
+      </c>
+      <c r="F143" s="12">
+        <v>7.75</v>
+      </c>
+      <c r="G143" s="13">
+        <v>6.412</v>
+      </c>
+      <c r="H143" s="14">
+        <v>1.338</v>
+      </c>
+      <c r="I143" s="15">
+        <v>20.9</v>
+      </c>
+      <c r="J143" s="12">
+        <v>113.667</v>
+      </c>
+      <c r="K143" s="16">
+        <v>-105.917</v>
+      </c>
+      <c r="L143" s="15">
+        <v>-93.2</v>
+      </c>
+      <c r="M143" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>434</v>
+      </c>
+      <c r="B144" t="s">
+        <v>409</v>
+      </c>
+      <c r="C144" t="s">
+        <v>325</v>
+      </c>
+      <c r="D144" t="s">
+        <v>329</v>
+      </c>
+      <c r="E144" t="s">
+        <v>442</v>
+      </c>
+      <c r="F144" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G144" s="13">
+        <v>12.481</v>
+      </c>
+      <c r="H144" s="14">
+        <v>3.019</v>
+      </c>
+      <c r="I144" s="15">
+        <v>24.2</v>
+      </c>
+      <c r="J144" s="12">
+        <v>106</v>
+      </c>
+      <c r="K144" s="16">
+        <v>-90.5</v>
+      </c>
+      <c r="L144" s="15">
+        <v>-85.4</v>
+      </c>
+      <c r="M144" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>434</v>
+      </c>
+      <c r="B145" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" t="s">
+        <v>325</v>
+      </c>
+      <c r="D145" t="s">
+        <v>329</v>
+      </c>
+      <c r="E145" t="s">
+        <v>465</v>
+      </c>
+      <c r="F145" s="12">
+        <v>21</v>
+      </c>
+      <c r="G145" s="13">
+        <v>16.01</v>
+      </c>
+      <c r="H145" s="14">
+        <v>4.99</v>
+      </c>
+      <c r="I145" s="15">
+        <v>31.2</v>
+      </c>
+      <c r="J145" s="12">
+        <v>141.4</v>
+      </c>
+      <c r="K145" s="16">
+        <v>-120.4</v>
+      </c>
+      <c r="L145" s="15">
+        <v>-85.1</v>
+      </c>
+      <c r="M145" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F146" s="8">
+        <v>26</v>
+      </c>
+      <c r="G146" s="9"/>
+      <c r="H146" s="10">
+        <v>1.366</v>
+      </c>
+      <c r="I146" s="11"/>
+      <c r="J146" s="8"/>
+      <c r="K146" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L146" s="11"/>
+      <c r="M146" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>434</v>
+      </c>
+      <c r="B147" t="s">
+        <v>411</v>
+      </c>
+      <c r="C147" t="s">
+        <v>445</v>
+      </c>
+      <c r="D147" t="s">
+        <v>446</v>
+      </c>
+      <c r="E147" t="s">
+        <v>426</v>
+      </c>
+      <c r="F147" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="G147" s="13">
+        <v>7.356</v>
+      </c>
+      <c r="H147" s="14">
+        <v>0.844</v>
+      </c>
+      <c r="I147" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="J147" s="12">
+        <v>14.75</v>
+      </c>
+      <c r="K147" s="16">
+        <v>-6.55</v>
+      </c>
+      <c r="L147" s="15">
+        <v>-44.4</v>
+      </c>
+      <c r="M147" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>434</v>
+      </c>
+      <c r="B148" t="s">
+        <v>411</v>
+      </c>
+      <c r="C148" t="s">
+        <v>445</v>
+      </c>
+      <c r="D148" t="s">
+        <v>446</v>
+      </c>
+      <c r="E148" t="s">
+        <v>424</v>
+      </c>
+      <c r="F148" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="G148" s="13">
+        <v>4.153</v>
+      </c>
+      <c r="H148" s="14">
+        <v>0.447</v>
+      </c>
+      <c r="I148" s="15">
+        <v>10.8</v>
+      </c>
+      <c r="J148" s="12">
+        <v>14.333</v>
+      </c>
+      <c r="K148" s="16">
+        <v>-9.733</v>
+      </c>
+      <c r="L148" s="15">
+        <v>-67.9</v>
+      </c>
+      <c r="M148" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>434</v>
+      </c>
+      <c r="B149" t="s">
+        <v>411</v>
+      </c>
+      <c r="C149" t="s">
+        <v>445</v>
+      </c>
+      <c r="D149" t="s">
+        <v>446</v>
+      </c>
+      <c r="E149" t="s">
+        <v>423</v>
+      </c>
+      <c r="F149" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G149" s="13">
+        <v>3.222</v>
+      </c>
+      <c r="H149" s="14">
+        <v>0.478</v>
+      </c>
+      <c r="I149" s="15">
+        <v>14.8</v>
+      </c>
+      <c r="J149" s="12">
+        <v>18.688</v>
+      </c>
+      <c r="K149" s="16">
+        <v>-14.988</v>
+      </c>
+      <c r="L149" s="15">
+        <v>-80.2</v>
+      </c>
+      <c r="M149" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>434</v>
+      </c>
+      <c r="B150" t="s">
+        <v>411</v>
+      </c>
+      <c r="C150" t="s">
+        <v>445</v>
+      </c>
+      <c r="D150" t="s">
+        <v>446</v>
+      </c>
+      <c r="E150" t="s">
+        <v>432</v>
+      </c>
+      <c r="F150" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G150" s="13">
+        <v>4.004</v>
+      </c>
+      <c r="H150" s="14">
+        <v>0.496</v>
+      </c>
+      <c r="I150" s="15">
+        <v>12.4</v>
+      </c>
+      <c r="J150" s="12">
+        <v>35.6</v>
+      </c>
+      <c r="K150" s="16">
+        <v>-31.1</v>
+      </c>
+      <c r="L150" s="15">
+        <v>-87.4</v>
+      </c>
+      <c r="M150" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>434</v>
+      </c>
+      <c r="B151" t="s">
+        <v>411</v>
+      </c>
+      <c r="C151" t="s">
+        <v>445</v>
+      </c>
+      <c r="D151" t="s">
+        <v>446</v>
+      </c>
+      <c r="E151" t="s">
+        <v>431</v>
+      </c>
+      <c r="F151" s="12">
+        <v>6.35</v>
+      </c>
+      <c r="G151" s="13">
+        <v>5.726</v>
+      </c>
+      <c r="H151" s="14">
+        <v>0.624</v>
+      </c>
+      <c r="I151" s="15">
+        <v>10.9</v>
+      </c>
+      <c r="J151" s="12">
+        <v>85.667</v>
+      </c>
+      <c r="K151" s="16">
+        <v>-79.317</v>
+      </c>
+      <c r="L151" s="15">
+        <v>-92.6</v>
+      </c>
+      <c r="M151" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>434</v>
+      </c>
+      <c r="B152" t="s">
+        <v>411</v>
+      </c>
+      <c r="C152" t="s">
+        <v>445</v>
+      </c>
+      <c r="D152" t="s">
+        <v>446</v>
+      </c>
+      <c r="E152" t="s">
+        <v>442</v>
+      </c>
+      <c r="F152" s="12">
+        <v>10</v>
+      </c>
+      <c r="G152" s="13">
+        <v>9.807</v>
+      </c>
+      <c r="H152" s="14">
+        <v>0.193</v>
+      </c>
+      <c r="I152" s="15">
+        <v>2</v>
+      </c>
+      <c r="J152" s="12">
+        <v>63.6</v>
+      </c>
+      <c r="K152" s="16">
+        <v>-53.6</v>
+      </c>
+      <c r="L152" s="15">
+        <v>-84.3</v>
+      </c>
+      <c r="M152" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>434</v>
+      </c>
+      <c r="B153" t="s">
+        <v>411</v>
+      </c>
+      <c r="C153" t="s">
+        <v>445</v>
+      </c>
+      <c r="D153" t="s">
+        <v>446</v>
+      </c>
+      <c r="E153" t="s">
+        <v>465</v>
+      </c>
+      <c r="F153" s="12">
+        <v>13</v>
+      </c>
+      <c r="G153" s="13">
+        <v>11.448</v>
+      </c>
+      <c r="H153" s="14">
+        <v>1.552</v>
+      </c>
+      <c r="I153" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="J153" s="12">
+        <v>85</v>
+      </c>
+      <c r="K153" s="16">
+        <v>-72</v>
+      </c>
+      <c r="L153" s="15">
+        <v>-84.7</v>
+      </c>
+      <c r="M153" t="s">
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -10646,19 +15375,19 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>503</v>
+    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>612</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -10666,7 +15395,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>505</v>
+        <v>613</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -10674,41 +15403,41 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>614</v>
       </c>
       <c r="B6" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>616</v>
       </c>
       <c r="B7" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>509</v>
+        <v>617</v>
       </c>
       <c r="B8" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>511</v>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>512</v>
+        <v>620</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -10716,76 +15445,76 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>513</v>
+        <v>621</v>
       </c>
       <c r="B13" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>514</v>
+        <v>622</v>
       </c>
       <c r="B14" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>515</v>
+        <v>623</v>
       </c>
       <c r="B15" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>516</v>
+        <v>615</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>517</v>
+        <v>625</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>518</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>519</v>
+        <v>627</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>520</v>
+        <v>628</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>521</v>
+        <v>629</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>522</v>
+        <v>630</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>523</v>
+        <v>631</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>524</v>
+        <v>632</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>525</v>
+        <v>633</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>526</v>
+        <v>634</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>527</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>528</v>
+      <c r="B20" s="21" t="s">
+        <v>636</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -10796,11 +15525,11 @@
       <c r="E20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>530</v>
+      <c r="F20" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>638</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>21</v>
@@ -10810,20 +15539,20 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="20" t="s">
         <v>426</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>528</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>532</v>
+      <c r="C21" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>640</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
@@ -10839,17 +15568,17 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>531</v>
+      <c r="B22" s="21" t="s">
+        <v>639</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>530</v>
+      <c r="D22" s="21" t="s">
+        <v>638</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
@@ -10868,20 +15597,20 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>423</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>530</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>528</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>529</v>
+      <c r="C23" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>637</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -10897,11 +15626,11 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>532</v>
+      <c r="B24" s="21" t="s">
+        <v>640</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
@@ -10909,11 +15638,11 @@
       <c r="D24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>529</v>
+      <c r="E24" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>637</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -10926,7 +15655,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>431</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -10941,22 +15670,22 @@
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>530</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>529</v>
+      <c r="F25" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>637</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>450</v>
+      <c r="A26" s="20" t="s">
+        <v>442</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>21</v>
@@ -10973,19 +15702,19 @@
       <c r="F26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>530</v>
-      </c>
-      <c r="I26" s="20" t="s">
-        <v>529</v>
+      <c r="G26" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>452</v>
+      <c r="A27" s="20" t="s">
+        <v>465</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -11005,16 +15734,16 @@
       <c r="G27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>533</v>
+      <c r="H27" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>534</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>
@@ -11037,42 +15766,42 @@
     <col min="11" max="12" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>536</v>
+    <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>537</v>
+        <v>645</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>538</v>
+        <v>646</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>539</v>
+        <v>647</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>541</v>
+        <v>649</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>542</v>
+        <v>650</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>543</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>544</v>
+        <v>652</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -11089,13 +15818,13 @@
       <c r="F5" s="7">
         <v>1650</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="22">
         <v>2.357142857142857</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>545</v>
+        <v>653</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -11112,13 +15841,13 @@
       <c r="F6" s="7">
         <v>470</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="22">
         <v>0.6714285714285714</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>546</v>
+        <v>654</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -11135,13 +15864,13 @@
       <c r="F7" s="7">
         <v>520</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <v>0.7428571428571429</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>547</v>
+    <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11149,7 +15878,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -11161,25 +15890,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>548</v>
+        <v>656</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>549</v>
+        <v>657</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>550</v>
+        <v>658</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>551</v>
+        <v>659</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>552</v>
+        <v>660</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>553</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -11207,16 +15936,16 @@
       <c r="H11" t="s">
         <v>423</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="23">
         <v>-100</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="24">
         <v>-100</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="25">
         <v>-100</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="25">
         <v>-100</v>
       </c>
     </row>
@@ -11245,16 +15974,16 @@
       <c r="H12" t="s">
         <v>431</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="23">
         <v>-100</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="24">
         <v>-200</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="25">
         <v>-100</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="25">
         <v>-100</v>
       </c>
     </row>
@@ -11283,16 +16012,16 @@
       <c r="H13" t="s">
         <v>426</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="23">
         <v>-100</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="24">
         <v>-300</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="25">
         <v>-100</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="25">
         <v>580</v>
       </c>
     </row>
@@ -11321,16 +16050,16 @@
       <c r="H14" t="s">
         <v>432</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="23">
         <v>-100</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="24">
         <v>-400</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="25">
         <v>320</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="25">
         <v>-100</v>
       </c>
     </row>
@@ -11359,16 +16088,16 @@
       <c r="H15" t="s">
         <v>425</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="26">
         <v>650</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="27">
         <v>250</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="25">
         <v>650</v>
       </c>
-      <c r="L15" s="24">
+      <c r="L15" s="25">
         <v>-100</v>
       </c>
     </row>
@@ -11397,16 +16126,16 @@
       <c r="H16" t="s">
         <v>425</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="26">
         <v>1500</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="27">
         <v>1750</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K16" s="25">
         <v>-100</v>
       </c>
-      <c r="L16" s="24">
+      <c r="L16" s="25">
         <v>-100</v>
       </c>
     </row>
@@ -11435,22 +16164,22 @@
       <c r="H17" t="s">
         <v>426</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="23">
         <v>-100</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="27">
         <v>1650</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="25">
         <v>-100</v>
       </c>
-      <c r="L17" s="24">
+      <c r="L17" s="25">
         <v>440</v>
       </c>
     </row>
-    <row r="19" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>554</v>
+    <row r="19" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11458,22 +16187,22 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>555</v>
+        <v>663</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>556</v>
+        <v>664</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>557</v>
+        <v>665</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>558</v>
+        <v>666</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>559</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -11486,16 +16215,16 @@
       <c r="C21">
         <v>2</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>1650</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>1650</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>470</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="25">
         <v>520</v>
       </c>
     </row>
@@ -11516,10 +16245,10 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>560</v>
+        <v>668</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>425</v>
@@ -11537,12 +16266,12 @@
         <v>432</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>561</v>
+        <v>669</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>562</v>
+        <v>670</v>
       </c>
       <c r="B2">
         <v>331</v>
@@ -11568,7 +16297,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>563</v>
+        <v>671</v>
       </c>
       <c r="B3">
         <v>330</v>
@@ -11594,7 +16323,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>564</v>
+        <v>672</v>
       </c>
       <c r="B4">
         <v>321</v>
@@ -11620,7 +16349,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>565</v>
+        <v>673</v>
       </c>
       <c r="B5">
         <v>313</v>
@@ -11646,7 +16375,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>566</v>
+        <v>674</v>
       </c>
       <c r="B6">
         <v>305</v>
@@ -11672,7 +16401,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>567</v>
+        <v>675</v>
       </c>
       <c r="B7">
         <v>287</v>
@@ -11698,7 +16427,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>568</v>
+        <v>676</v>
       </c>
       <c r="B8">
         <v>278</v>
@@ -11724,7 +16453,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>569</v>
+        <v>677</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -11750,7 +16479,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>570</v>
+        <v>678</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -11776,7 +16505,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>571</v>
+        <v>679</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -11814,58 +16543,58 @@
     <col min="1" max="1" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>573</v>
+    <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>574</v>
+        <v>682</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>575</v>
+        <v>683</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
-        <v>565</v>
-      </c>
-      <c r="B5" s="27" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>673</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>425</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <v>35</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>577</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="D5" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="E5" s="28">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
-        <v>578</v>
+    <row r="7" spans="1:1" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>425</v>
@@ -11883,17 +16612,17 @@
         <v>432</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>561</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>562</v>
+        <v>670</v>
       </c>
       <c r="B9" s="3">
         <v>4</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>22</v>
       </c>
       <c r="D9" s="3">
@@ -11911,7 +16640,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>563</v>
+        <v>671</v>
       </c>
       <c r="B10" s="3">
         <v>6</v>
@@ -11925,7 +16654,7 @@
       <c r="E10" s="3">
         <v>4</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>19</v>
       </c>
       <c r="G10" s="3">
@@ -11934,9 +16663,9 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="B11" s="29">
+        <v>672</v>
+      </c>
+      <c r="B11" s="30">
         <v>22</v>
       </c>
       <c r="C11" s="3">
@@ -11948,7 +16677,7 @@
       <c r="E11" s="3">
         <v>1</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>29</v>
       </c>
       <c r="G11" s="3">
@@ -11957,9 +16686,9 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="B12" s="30">
+        <v>673</v>
+      </c>
+      <c r="B12" s="31">
         <v>35</v>
       </c>
       <c r="C12" s="3">
@@ -11968,7 +16697,7 @@
       <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>26</v>
       </c>
       <c r="F12" s="3">
@@ -11980,7 +16709,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>566</v>
+        <v>674</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -12003,7 +16732,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>567</v>
+        <v>675</v>
       </c>
       <c r="B14" s="3">
         <v>0</v>
@@ -12026,9 +16755,9 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="B15" s="29">
+        <v>676</v>
+      </c>
+      <c r="B15" s="30">
         <v>20</v>
       </c>
       <c r="C15" s="3">
@@ -12049,7 +16778,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>569</v>
+        <v>677</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -12072,9 +16801,9 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="B17" s="29">
+        <v>678</v>
+      </c>
+      <c r="B17" s="30">
         <v>26</v>
       </c>
       <c r="C17" s="3">
@@ -12086,7 +16815,7 @@
       <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>27</v>
       </c>
       <c r="G17" s="3">
@@ -12095,12 +16824,12 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>571</v>
+        <v>679</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>19</v>
       </c>
       <c r="D18" s="3">
@@ -12130,9 +16859,9 @@
     <col min="1" max="1" width="112" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>579</v>
+    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -12140,64 +16869,64 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>580</v>
+    <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>581</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>582</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>583</v>
+        <v>691</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>584</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>585</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>586</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>587</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>588</v>
+        <v>696</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>589</v>
+        <v>697</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>590</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>591</v>
+        <v>699</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -12205,34 +16934,34 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>592</v>
+    <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>593</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>594</v>
+        <v>702</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>595</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>596</v>
+        <v>704</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>597</v>
+        <v>705</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -12240,24 +16969,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>598</v>
+    <row r="23" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>599</v>
+        <v>707</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>600</v>
+        <v>708</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>601</v>
+        <v>709</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -12265,24 +16994,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>602</v>
+    <row r="28" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>603</v>
+        <v>711</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>604</v>
+        <v>712</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>605</v>
+        <v>713</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -12290,14 +17019,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>606</v>
+    <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>607</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3278" uniqueCount="745">
   <si>
     <t>日期</t>
   </si>
@@ -1292,126 +1292,210 @@
     <t>3球</t>
   </si>
   <si>
+    <t>2球 @3.2</t>
+  </si>
+  <si>
+    <t>0球 @10.5</t>
+  </si>
+  <si>
+    <t>1球 @4.4</t>
+  </si>
+  <si>
+    <t>✗</t>
+  </si>
+  <si>
+    <t>10-05 17:00</t>
+  </si>
+  <si>
+    <t>10-06 11:00</t>
+  </si>
+  <si>
+    <t>10-06 02:45</t>
+  </si>
+  <si>
+    <t>5球</t>
+  </si>
+  <si>
+    <t>1球 @7.5</t>
+  </si>
+  <si>
+    <t>0球 @25</t>
+  </si>
+  <si>
+    <t>1球</t>
+  </si>
+  <si>
+    <t>4球 @4.25</t>
+  </si>
+  <si>
+    <t>0球 @20</t>
+  </si>
+  <si>
+    <t>1球 @6.8</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>4球</t>
+  </si>
+  <si>
+    <t>4球 @4.2</t>
+  </si>
+  <si>
+    <t>0球 @23</t>
+  </si>
+  <si>
+    <t>0球</t>
+  </si>
+  <si>
+    <t>0球 @7.5</t>
+  </si>
+  <si>
+    <t>1球 @3.45</t>
+  </si>
+  <si>
+    <t>2球 @3.8</t>
+  </si>
+  <si>
+    <t>0球 @16</t>
+  </si>
+  <si>
+    <t>1球 @5.8</t>
+  </si>
+  <si>
+    <t>2球 @3.3</t>
+  </si>
+  <si>
+    <t>0球 @14</t>
+  </si>
+  <si>
+    <t>1球 @5.4</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>乌兹别克</t>
+  </si>
+  <si>
+    <t>10-06 19:00</t>
+  </si>
+  <si>
+    <t>3球 @3.35</t>
+  </si>
+  <si>
+    <t>10-06 17:00</t>
+  </si>
+  <si>
+    <t>塔吉克</t>
+  </si>
+  <si>
+    <t>10-06 19:35</t>
+  </si>
+  <si>
+    <t>1球 @3.95</t>
+  </si>
+  <si>
+    <t>10-06 22:00</t>
+  </si>
+  <si>
+    <t>1球 @3.75</t>
+  </si>
+  <si>
+    <t>10-07 02:45</t>
+  </si>
+  <si>
+    <t>2球 @3.35</t>
+  </si>
+  <si>
+    <t>1球 @3.3</t>
+  </si>
+  <si>
+    <t>6球 @8.8</t>
+  </si>
+  <si>
+    <t>4球 @4</t>
+  </si>
+  <si>
+    <t>6球 @11</t>
+  </si>
+  <si>
+    <t>摩尔多瓦</t>
+  </si>
+  <si>
+    <t>10-07 08:00</t>
+  </si>
+  <si>
+    <t>3球 @3.45</t>
+  </si>
+  <si>
+    <t>芝加哥</t>
+  </si>
+  <si>
+    <t>温哥华</t>
+  </si>
+  <si>
+    <t>10-07 08:30</t>
+  </si>
+  <si>
+    <t>6球 @10</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>进球数</t>
+  </si>
+  <si>
+    <t>总进球赔率</t>
+  </si>
+  <si>
+    <t>优化赔率A(多选)</t>
+  </si>
+  <si>
+    <t>差值A</t>
+  </si>
+  <si>
+    <t>相对差值A(%)</t>
+  </si>
+  <si>
+    <t>平均赔率B</t>
+  </si>
+  <si>
+    <t>差值B</t>
+  </si>
+  <si>
+    <t>相对差值B(%)</t>
+  </si>
+  <si>
+    <t>比分(赔率)</t>
+  </si>
+  <si>
+    <t>0:0=10.5</t>
+  </si>
+  <si>
+    <t>0:1=14 1:0=6</t>
+  </si>
+  <si>
     <t>2球</t>
   </si>
   <si>
-    <t>0球</t>
-  </si>
-  <si>
-    <t>1球</t>
-  </si>
-  <si>
-    <t>✗</t>
-  </si>
-  <si>
-    <t>10-05 17:00</t>
-  </si>
-  <si>
-    <t>10-06 11:00</t>
-  </si>
-  <si>
-    <t>10-06 02:45</t>
-  </si>
-  <si>
-    <t>5球</t>
-  </si>
-  <si>
-    <t>4球</t>
-  </si>
-  <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>乌兹别克</t>
-  </si>
-  <si>
-    <t>10-06 19:00</t>
-  </si>
-  <si>
-    <t>10-06 17:00</t>
-  </si>
-  <si>
-    <t>塔吉克</t>
-  </si>
-  <si>
-    <t>10-06 19:35</t>
-  </si>
-  <si>
-    <t>10-06 22:00</t>
-  </si>
-  <si>
-    <t>10-07 02:45</t>
+    <t>0:2=35 1:1=7 2:0=6.5</t>
+  </si>
+  <si>
+    <t>0:3=90 1:2=17 2:1=7 3:0=11</t>
+  </si>
+  <si>
+    <t>0:4=350 1:3=55 2:2=19 3:1=13.5 4:0=23</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=250 2:3=55 3:2=29 4:1=29 5:0=55</t>
   </si>
   <si>
     <t>6球</t>
   </si>
   <si>
-    <t>摩尔多瓦</t>
-  </si>
-  <si>
-    <t>10-07 08:00</t>
-  </si>
-  <si>
-    <t>芝加哥</t>
-  </si>
-  <si>
-    <t>温哥华</t>
-  </si>
-  <si>
-    <t>10-07 08:30</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>进球数</t>
-  </si>
-  <si>
-    <t>总进球赔率</t>
-  </si>
-  <si>
-    <t>优化赔率A(多选)</t>
-  </si>
-  <si>
-    <t>差值A</t>
-  </si>
-  <si>
-    <t>相对差值A(%)</t>
-  </si>
-  <si>
-    <t>平均赔率B</t>
-  </si>
-  <si>
-    <t>差值B</t>
-  </si>
-  <si>
-    <t>相对差值B(%)</t>
-  </si>
-  <si>
-    <t>比分(赔率)</t>
-  </si>
-  <si>
-    <t>0:0=10.5</t>
-  </si>
-  <si>
-    <t>0:1=14 1:0=6</t>
-  </si>
-  <si>
-    <t>0:2=35 1:1=7 2:0=6.5</t>
-  </si>
-  <si>
-    <t>0:3=90 1:2=17 2:1=7 3:0=11</t>
-  </si>
-  <si>
-    <t>0:4=350 1:3=55 2:2=19 3:1=13.5 4:0=23</t>
-  </si>
-  <si>
-    <t>0:5=1000 1:4=250 2:3=55 3:2=29 4:1=29 5:0=55</t>
-  </si>
-  <si>
     <t>1:5=800 2:4=300 3:3=90 4:2=70 5:1=70</t>
   </si>
   <si>
@@ -1850,7 +1934,7 @@
     <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-06T17:00:06+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-06T17:12:55+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2154,6 +2238,9 @@
   </si>
   <si>
     <t xml:space="preserve">  · 赔率、赛果来自中国体育彩票官方 Web API；每次抓取保留完整玩法池（总进球0-7+、比分矩阵）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 预测列格式"X球 @赔率"：@后为该预测进球数对应的赔率（该场最后一次记录），便于核对与回测对照。</t>
   </si>
   <si>
     <t xml:space="preserve">  · 凌晨开赛的比赛属于前一"销售日"（预测窗口按销售日切分）。</t>
@@ -8393,13 +8480,13 @@
         <v>431</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>427</v>
@@ -8437,22 +8524,22 @@
         <v>55</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>427</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N4" t="s">
         <v>428</v>
@@ -8484,16 +8571,16 @@
         <v>55</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>427</v>
@@ -8531,19 +8618,19 @@
         <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>427</v>
@@ -8578,19 +8665,19 @@
         <v>55</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>427</v>
@@ -8625,22 +8712,22 @@
         <v>55</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>427</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N8" t="s">
         <v>428</v>
@@ -8651,7 +8738,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B9" t="s">
         <v>157</v>
@@ -8663,10 +8750,10 @@
         <v>196</v>
       </c>
       <c r="E9" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F9" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>55</v>
@@ -8675,7 +8762,7 @@
         <v>21</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>423</v>
+        <v>454</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>21</v>
@@ -8690,7 +8777,7 @@
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O9" t="s">
         <v>21</v>
@@ -8698,7 +8785,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B10" t="s">
         <v>163</v>
@@ -8710,10 +8797,10 @@
         <v>200</v>
       </c>
       <c r="E10" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="F10" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>70</v>
@@ -8722,7 +8809,7 @@
         <v>21</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>21</v>
@@ -8737,7 +8824,7 @@
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -8745,7 +8832,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B11" t="s">
         <v>168</v>
@@ -8760,7 +8847,7 @@
         <v>301</v>
       </c>
       <c r="F11" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>55</v>
@@ -8769,7 +8856,7 @@
         <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>21</v>
@@ -8784,7 +8871,7 @@
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O11" t="s">
         <v>21</v>
@@ -8792,7 +8879,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B12" t="s">
         <v>171</v>
@@ -8807,7 +8894,7 @@
         <v>305</v>
       </c>
       <c r="F12" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>55</v>
@@ -8816,7 +8903,7 @@
         <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>21</v>
@@ -8831,7 +8918,7 @@
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O12" t="s">
         <v>21</v>
@@ -8839,7 +8926,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B13" t="s">
         <v>397</v>
@@ -8854,7 +8941,7 @@
         <v>308</v>
       </c>
       <c r="F13" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>55</v>
@@ -8863,7 +8950,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>21</v>
@@ -8878,7 +8965,7 @@
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O13" t="s">
         <v>21</v>
@@ -8886,7 +8973,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B14" t="s">
         <v>399</v>
@@ -8901,7 +8988,7 @@
         <v>293</v>
       </c>
       <c r="F14" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>55</v>
@@ -8910,7 +8997,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>21</v>
@@ -8925,7 +9012,7 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O14" t="s">
         <v>21</v>
@@ -8933,7 +9020,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B15" t="s">
         <v>402</v>
@@ -8948,7 +9035,7 @@
         <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G15" t="s">
         <v>21</v>
@@ -8957,7 +9044,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>21</v>
@@ -8972,7 +9059,7 @@
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O15" t="s">
         <v>21</v>
@@ -8980,7 +9067,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B16" t="s">
         <v>405</v>
@@ -8995,7 +9082,7 @@
         <v>323</v>
       </c>
       <c r="F16" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>70</v>
@@ -9004,7 +9091,7 @@
         <v>21</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>21</v>
@@ -9019,7 +9106,7 @@
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
@@ -9027,7 +9114,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B17" t="s">
         <v>407</v>
@@ -9042,7 +9129,7 @@
         <v>319</v>
       </c>
       <c r="F17" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G17" t="s">
         <v>21</v>
@@ -9051,7 +9138,7 @@
         <v>21</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>21</v>
@@ -9066,7 +9153,7 @@
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
@@ -9074,7 +9161,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B18" t="s">
         <v>408</v>
@@ -9083,13 +9170,13 @@
         <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="E18" t="s">
         <v>410</v>
       </c>
       <c r="F18" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>55</v>
@@ -9098,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>21</v>
@@ -9113,7 +9200,7 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
@@ -9121,7 +9208,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B19" t="s">
         <v>409</v>
@@ -9136,7 +9223,7 @@
         <v>329</v>
       </c>
       <c r="F19" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>55</v>
@@ -9145,7 +9232,7 @@
         <v>21</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>21</v>
@@ -9160,7 +9247,7 @@
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O19" t="s">
         <v>21</v>
@@ -9168,7 +9255,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B20" t="s">
         <v>411</v>
@@ -9177,13 +9264,13 @@
         <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="E20" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="F20" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>55</v>
@@ -9192,7 +9279,7 @@
         <v>21</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>21</v>
@@ -9207,7 +9294,7 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="O20" t="s">
         <v>21</v>
@@ -9243,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -9252,31 +9339,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9293,7 +9380,7 @@
         <v>245</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F2" s="8">
         <v>10.5</v>
@@ -9309,7 +9396,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -9326,7 +9413,7 @@
         <v>245</v>
       </c>
       <c r="E3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F3" s="12">
         <v>4.4</v>
@@ -9350,7 +9437,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -9367,7 +9454,7 @@
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F4" s="12">
         <v>3.2</v>
@@ -9391,7 +9478,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -9432,7 +9519,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -9449,7 +9536,7 @@
         <v>245</v>
       </c>
       <c r="E6" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F6" s="12">
         <v>6.2</v>
@@ -9473,7 +9560,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -9514,7 +9601,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -9531,7 +9618,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -9555,7 +9642,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -9572,7 +9659,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -9596,7 +9683,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9613,7 +9700,7 @@
         <v>248</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F10" s="8">
         <v>25</v>
@@ -9629,7 +9716,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -9646,7 +9733,7 @@
         <v>248</v>
       </c>
       <c r="E11" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F11" s="12">
         <v>7.5</v>
@@ -9670,7 +9757,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -9687,7 +9774,7 @@
         <v>248</v>
       </c>
       <c r="E12" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F12" s="12">
         <v>4.35</v>
@@ -9711,7 +9798,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -9752,7 +9839,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -9769,7 +9856,7 @@
         <v>248</v>
       </c>
       <c r="E14" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F14" s="12">
         <v>4.5</v>
@@ -9793,7 +9880,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -9834,7 +9921,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -9851,7 +9938,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -9875,7 +9962,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -9892,7 +9979,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -9916,7 +10003,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9933,7 +10020,7 @@
         <v>260</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F18" s="8">
         <v>20</v>
@@ -9949,7 +10036,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -9966,7 +10053,7 @@
         <v>260</v>
       </c>
       <c r="E19" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F19" s="12">
         <v>6.8</v>
@@ -9990,7 +10077,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -10007,7 +10094,7 @@
         <v>260</v>
       </c>
       <c r="E20" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F20" s="12">
         <v>4.2</v>
@@ -10031,7 +10118,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -10072,7 +10159,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -10089,7 +10176,7 @@
         <v>260</v>
       </c>
       <c r="E22" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F22" s="12">
         <v>4.25</v>
@@ -10113,7 +10200,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -10154,7 +10241,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -10171,7 +10258,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -10195,7 +10282,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -10212,7 +10299,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -10236,7 +10323,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10253,7 +10340,7 @@
         <v>257</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F26" s="8">
         <v>23</v>
@@ -10269,7 +10356,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -10286,7 +10373,7 @@
         <v>257</v>
       </c>
       <c r="E27" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F27" s="12">
         <v>7.5</v>
@@ -10310,7 +10397,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -10327,7 +10414,7 @@
         <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F28" s="12">
         <v>4.4</v>
@@ -10351,7 +10438,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>485</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -10392,7 +10479,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>486</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -10409,7 +10496,7 @@
         <v>257</v>
       </c>
       <c r="E30" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F30" s="12">
         <v>4.2</v>
@@ -10433,7 +10520,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -10474,7 +10561,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>488</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -10491,7 +10578,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -10515,7 +10602,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>489</v>
+        <v>517</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -10532,7 +10619,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -10556,7 +10643,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>490</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10573,7 +10660,7 @@
         <v>240</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F34" s="8">
         <v>7.5</v>
@@ -10589,7 +10676,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>491</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -10606,7 +10693,7 @@
         <v>240</v>
       </c>
       <c r="E35" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F35" s="12">
         <v>3.45</v>
@@ -10630,7 +10717,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>492</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -10647,7 +10734,7 @@
         <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F36" s="12">
         <v>3.2</v>
@@ -10671,7 +10758,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>493</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -10712,7 +10799,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>494</v>
+        <v>522</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -10729,7 +10816,7 @@
         <v>240</v>
       </c>
       <c r="E38" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F38" s="12">
         <v>8.2</v>
@@ -10753,7 +10840,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>495</v>
+        <v>523</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -10794,7 +10881,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -10811,7 +10898,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -10835,7 +10922,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -10852,7 +10939,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -10876,7 +10963,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10893,7 +10980,7 @@
         <v>244</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F42" s="8">
         <v>16</v>
@@ -10909,7 +10996,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -10926,7 +11013,7 @@
         <v>244</v>
       </c>
       <c r="E43" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F43" s="12">
         <v>5.8</v>
@@ -10950,7 +11037,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -10967,7 +11054,7 @@
         <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F44" s="12">
         <v>3.8</v>
@@ -10991,7 +11078,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -11032,7 +11119,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>502</v>
+        <v>530</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -11049,7 +11136,7 @@
         <v>244</v>
       </c>
       <c r="E46" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F46" s="12">
         <v>5</v>
@@ -11073,7 +11160,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -11114,7 +11201,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>504</v>
+        <v>532</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -11131,7 +11218,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -11155,7 +11242,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>505</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -11172,7 +11259,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -11196,7 +11283,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11213,7 +11300,7 @@
         <v>254</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F50" s="8">
         <v>14</v>
@@ -11229,7 +11316,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -11246,7 +11333,7 @@
         <v>254</v>
       </c>
       <c r="E51" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F51" s="12">
         <v>5.4</v>
@@ -11270,7 +11357,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -11287,7 +11374,7 @@
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F52" s="12">
         <v>3.3</v>
@@ -11311,7 +11398,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -11352,7 +11439,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -11369,7 +11456,7 @@
         <v>254</v>
       </c>
       <c r="E54" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F54" s="12">
         <v>5.5</v>
@@ -11393,7 +11480,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -11434,7 +11521,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -11451,7 +11538,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -11475,7 +11562,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -11492,7 +11579,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -11516,12 +11603,12 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>157</v>
@@ -11530,10 +11617,10 @@
         <v>196</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F58" s="8">
         <v>15</v>
@@ -11549,12 +11636,12 @@
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="4" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s">
         <v>157</v>
@@ -11563,10 +11650,10 @@
         <v>196</v>
       </c>
       <c r="D59" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E59" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F59" s="12">
         <v>5.8</v>
@@ -11590,12 +11677,12 @@
         <v>-49.6</v>
       </c>
       <c r="M59" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s">
         <v>157</v>
@@ -11604,10 +11691,10 @@
         <v>196</v>
       </c>
       <c r="D60" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E60" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F60" s="12">
         <v>3.7</v>
@@ -11631,12 +11718,12 @@
         <v>-74.8</v>
       </c>
       <c r="M60" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s">
         <v>157</v>
@@ -11645,7 +11732,7 @@
         <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E61" t="s">
         <v>423</v>
@@ -11672,12 +11759,12 @@
         <v>-88.2</v>
       </c>
       <c r="M61" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s">
         <v>157</v>
@@ -11686,10 +11773,10 @@
         <v>196</v>
       </c>
       <c r="D62" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E62" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F62" s="12">
         <v>5.15</v>
@@ -11713,12 +11800,12 @@
         <v>-92.7</v>
       </c>
       <c r="M62" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B63" t="s">
         <v>157</v>
@@ -11727,7 +11814,7 @@
         <v>196</v>
       </c>
       <c r="D63" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E63" t="s">
         <v>431</v>
@@ -11754,12 +11841,12 @@
         <v>-95</v>
       </c>
       <c r="M63" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s">
         <v>157</v>
@@ -11768,10 +11855,10 @@
         <v>196</v>
       </c>
       <c r="D64" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E64" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F64" s="12">
         <v>18.5</v>
@@ -11795,12 +11882,12 @@
         <v>-89.7</v>
       </c>
       <c r="M64" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s">
         <v>157</v>
@@ -11809,10 +11896,10 @@
         <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="E65" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F65" s="12">
         <v>25</v>
@@ -11836,12 +11923,12 @@
         <v>-89.2</v>
       </c>
       <c r="M65" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>163</v>
@@ -11850,10 +11937,10 @@
         <v>200</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F66" s="8">
         <v>9</v>
@@ -11869,12 +11956,12 @@
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="4" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s">
         <v>163</v>
@@ -11883,10 +11970,10 @@
         <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E67" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F67" s="12">
         <v>3.95</v>
@@ -11910,12 +11997,12 @@
         <v>-51.7</v>
       </c>
       <c r="M67" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s">
         <v>163</v>
@@ -11924,10 +12011,10 @@
         <v>200</v>
       </c>
       <c r="D68" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E68" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F68" s="12">
         <v>3.1</v>
@@ -11951,12 +12038,12 @@
         <v>-73.4</v>
       </c>
       <c r="M68" t="s">
-        <v>525</v>
+        <v>553</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s">
         <v>163</v>
@@ -11965,7 +12052,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E69" t="s">
         <v>423</v>
@@ -11992,12 +12079,12 @@
         <v>-83.2</v>
       </c>
       <c r="M69" t="s">
-        <v>526</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s">
         <v>163</v>
@@ -12006,10 +12093,10 @@
         <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E70" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F70" s="12">
         <v>7</v>
@@ -12033,12 +12120,12 @@
         <v>-88.2</v>
       </c>
       <c r="M70" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s">
         <v>163</v>
@@ -12047,7 +12134,7 @@
         <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E71" t="s">
         <v>431</v>
@@ -12074,12 +12161,12 @@
         <v>-86.5</v>
       </c>
       <c r="M71" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B72" t="s">
         <v>163</v>
@@ -12088,10 +12175,10 @@
         <v>200</v>
       </c>
       <c r="D72" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E72" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F72" s="12">
         <v>27</v>
@@ -12115,12 +12202,12 @@
         <v>-80.7</v>
       </c>
       <c r="M72" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s">
         <v>163</v>
@@ -12129,10 +12216,10 @@
         <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E73" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F73" s="12">
         <v>45</v>
@@ -12156,12 +12243,12 @@
         <v>-82.9</v>
       </c>
       <c r="M73" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>168</v>
@@ -12173,7 +12260,7 @@
         <v>301</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F74" s="8">
         <v>7.5</v>
@@ -12189,12 +12276,12 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="4" t="s">
-        <v>491</v>
+        <v>519</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s">
         <v>168</v>
@@ -12206,7 +12293,7 @@
         <v>301</v>
       </c>
       <c r="E75" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F75" s="12">
         <v>3.75</v>
@@ -12230,12 +12317,12 @@
         <v>-48.3</v>
       </c>
       <c r="M75" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B76" t="s">
         <v>168</v>
@@ -12247,7 +12334,7 @@
         <v>301</v>
       </c>
       <c r="E76" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F76" s="12">
         <v>3.15</v>
@@ -12271,12 +12358,12 @@
         <v>-68.4</v>
       </c>
       <c r="M76" t="s">
-        <v>532</v>
+        <v>560</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s">
         <v>168</v>
@@ -12312,12 +12399,12 @@
         <v>-80.5</v>
       </c>
       <c r="M77" t="s">
-        <v>533</v>
+        <v>561</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B78" t="s">
         <v>168</v>
@@ -12329,7 +12416,7 @@
         <v>301</v>
       </c>
       <c r="E78" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F78" s="12">
         <v>7</v>
@@ -12353,12 +12440,12 @@
         <v>-86.5</v>
       </c>
       <c r="M78" t="s">
-        <v>534</v>
+        <v>562</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s">
         <v>168</v>
@@ -12394,12 +12481,12 @@
         <v>-87.7</v>
       </c>
       <c r="M79" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B80" t="s">
         <v>168</v>
@@ -12411,7 +12498,7 @@
         <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F80" s="12">
         <v>38</v>
@@ -12435,12 +12522,12 @@
         <v>-75.9</v>
       </c>
       <c r="M80" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s">
         <v>168</v>
@@ -12452,7 +12539,7 @@
         <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F81" s="12">
         <v>70</v>
@@ -12476,12 +12563,12 @@
         <v>-78.5</v>
       </c>
       <c r="M81" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>171</v>
@@ -12493,7 +12580,7 @@
         <v>305</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F82" s="8">
         <v>12</v>
@@ -12509,12 +12596,12 @@
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="4" t="s">
-        <v>538</v>
+        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B83" t="s">
         <v>171</v>
@@ -12526,7 +12613,7 @@
         <v>305</v>
       </c>
       <c r="E83" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F83" s="12">
         <v>4.85</v>
@@ -12550,12 +12637,12 @@
         <v>-50.9</v>
       </c>
       <c r="M83" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s">
         <v>171</v>
@@ -12567,7 +12654,7 @@
         <v>305</v>
       </c>
       <c r="E84" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F84" s="12">
         <v>3.35</v>
@@ -12591,12 +12678,12 @@
         <v>-76.5</v>
       </c>
       <c r="M84" t="s">
-        <v>540</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B85" t="s">
         <v>171</v>
@@ -12632,12 +12719,12 @@
         <v>-87.5</v>
       </c>
       <c r="M85" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B86" t="s">
         <v>171</v>
@@ -12649,7 +12736,7 @@
         <v>305</v>
       </c>
       <c r="E86" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F86" s="12">
         <v>5.8</v>
@@ -12673,12 +12760,12 @@
         <v>-92.7</v>
       </c>
       <c r="M86" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B87" t="s">
         <v>171</v>
@@ -12714,12 +12801,12 @@
         <v>-94.2</v>
       </c>
       <c r="M87" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B88" t="s">
         <v>171</v>
@@ -12731,7 +12818,7 @@
         <v>305</v>
       </c>
       <c r="E88" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F88" s="12">
         <v>24</v>
@@ -12755,12 +12842,12 @@
         <v>-89.6</v>
       </c>
       <c r="M88" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B89" t="s">
         <v>171</v>
@@ -12772,7 +12859,7 @@
         <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F89" s="12">
         <v>35</v>
@@ -12796,12 +12883,12 @@
         <v>-88.8</v>
       </c>
       <c r="M89" t="s">
-        <v>545</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>397</v>
@@ -12813,7 +12900,7 @@
         <v>308</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F90" s="8">
         <v>8.5</v>
@@ -12829,12 +12916,12 @@
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="4" t="s">
-        <v>546</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B91" t="s">
         <v>397</v>
@@ -12846,7 +12933,7 @@
         <v>308</v>
       </c>
       <c r="E91" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F91" s="12">
         <v>3.3</v>
@@ -12870,12 +12957,12 @@
         <v>-51.1</v>
       </c>
       <c r="M91" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B92" t="s">
         <v>397</v>
@@ -12887,7 +12974,7 @@
         <v>308</v>
       </c>
       <c r="E92" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F92" s="12">
         <v>3.3</v>
@@ -12911,12 +12998,12 @@
         <v>-72.5</v>
       </c>
       <c r="M92" t="s">
-        <v>548</v>
+        <v>576</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B93" t="s">
         <v>397</v>
@@ -12952,12 +13039,12 @@
         <v>-83.6</v>
       </c>
       <c r="M93" t="s">
-        <v>549</v>
+        <v>577</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B94" t="s">
         <v>397</v>
@@ -12969,7 +13056,7 @@
         <v>308</v>
       </c>
       <c r="E94" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F94" s="12">
         <v>8</v>
@@ -12993,12 +13080,12 @@
         <v>-87.9</v>
       </c>
       <c r="M94" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B95" t="s">
         <v>397</v>
@@ -13034,12 +13121,12 @@
         <v>-89.2</v>
       </c>
       <c r="M95" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B96" t="s">
         <v>397</v>
@@ -13051,7 +13138,7 @@
         <v>308</v>
       </c>
       <c r="E96" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F96" s="12">
         <v>40</v>
@@ -13075,12 +13162,12 @@
         <v>-78</v>
       </c>
       <c r="M96" t="s">
-        <v>552</v>
+        <v>580</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B97" t="s">
         <v>397</v>
@@ -13092,7 +13179,7 @@
         <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F97" s="12">
         <v>80</v>
@@ -13116,12 +13203,12 @@
         <v>-78.8</v>
       </c>
       <c r="M97" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>399</v>
@@ -13133,7 +13220,7 @@
         <v>293</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F98" s="8">
         <v>8</v>
@@ -13149,12 +13236,12 @@
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="4" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B99" t="s">
         <v>399</v>
@@ -13166,7 +13253,7 @@
         <v>293</v>
       </c>
       <c r="E99" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F99" s="12">
         <v>3.75</v>
@@ -13190,12 +13277,12 @@
         <v>-52.4</v>
       </c>
       <c r="M99" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B100" t="s">
         <v>399</v>
@@ -13207,7 +13294,7 @@
         <v>293</v>
       </c>
       <c r="E100" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F100" s="12">
         <v>3.2</v>
@@ -13231,12 +13318,12 @@
         <v>-74</v>
       </c>
       <c r="M100" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B101" t="s">
         <v>399</v>
@@ -13272,12 +13359,12 @@
         <v>-86.3</v>
       </c>
       <c r="M101" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B102" t="s">
         <v>399</v>
@@ -13289,7 +13376,7 @@
         <v>293</v>
       </c>
       <c r="E102" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F102" s="12">
         <v>7</v>
@@ -13313,12 +13400,12 @@
         <v>-91.6</v>
       </c>
       <c r="M102" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B103" t="s">
         <v>399</v>
@@ -13354,12 +13441,12 @@
         <v>-92.2</v>
       </c>
       <c r="M103" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B104" t="s">
         <v>399</v>
@@ -13371,7 +13458,7 @@
         <v>293</v>
       </c>
       <c r="E104" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F104" s="12">
         <v>35</v>
@@ -13395,12 +13482,12 @@
         <v>-81.8</v>
       </c>
       <c r="M104" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B105" t="s">
         <v>399</v>
@@ -13412,7 +13499,7 @@
         <v>293</v>
       </c>
       <c r="E105" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F105" s="12">
         <v>60</v>
@@ -13436,12 +13523,12 @@
         <v>-82.4</v>
       </c>
       <c r="M105" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>402</v>
@@ -13453,7 +13540,7 @@
         <v>315</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F106" s="8">
         <v>35</v>
@@ -13469,12 +13556,12 @@
       </c>
       <c r="L106" s="11"/>
       <c r="M106" s="4" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B107" t="s">
         <v>402</v>
@@ -13486,7 +13573,7 @@
         <v>315</v>
       </c>
       <c r="E107" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F107" s="12">
         <v>10.25</v>
@@ -13510,12 +13597,12 @@
         <v>-66.4</v>
       </c>
       <c r="M107" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B108" t="s">
         <v>402</v>
@@ -13527,7 +13614,7 @@
         <v>315</v>
       </c>
       <c r="E108" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F108" s="12">
         <v>5.6</v>
@@ -13551,12 +13638,12 @@
         <v>-89.7</v>
       </c>
       <c r="M108" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B109" t="s">
         <v>402</v>
@@ -13592,12 +13679,12 @@
         <v>-96.9</v>
       </c>
       <c r="M109" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B110" t="s">
         <v>402</v>
@@ -13609,7 +13696,7 @@
         <v>315</v>
       </c>
       <c r="E110" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F110" s="12">
         <v>4.05</v>
@@ -13633,12 +13720,12 @@
         <v>-98.4</v>
       </c>
       <c r="M110" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B111" t="s">
         <v>402</v>
@@ -13674,12 +13761,12 @@
         <v>-98.2</v>
       </c>
       <c r="M111" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B112" t="s">
         <v>402</v>
@@ -13691,7 +13778,7 @@
         <v>315</v>
       </c>
       <c r="E112" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F112" s="12">
         <v>8.8</v>
@@ -13715,12 +13802,12 @@
         <v>-97.2</v>
       </c>
       <c r="M112" t="s">
-        <v>568</v>
+        <v>596</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B113" t="s">
         <v>402</v>
@@ -13732,7 +13819,7 @@
         <v>315</v>
       </c>
       <c r="E113" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F113" s="12">
         <v>9</v>
@@ -13756,12 +13843,12 @@
         <v>-97.7</v>
       </c>
       <c r="M113" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>405</v>
@@ -13773,7 +13860,7 @@
         <v>323</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F114" s="8">
         <v>24</v>
@@ -13789,12 +13876,12 @@
       </c>
       <c r="L114" s="11"/>
       <c r="M114" s="4" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B115" t="s">
         <v>405</v>
@@ -13806,7 +13893,7 @@
         <v>323</v>
       </c>
       <c r="E115" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F115" s="12">
         <v>8</v>
@@ -13830,12 +13917,12 @@
         <v>-58.4</v>
       </c>
       <c r="M115" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B116" t="s">
         <v>405</v>
@@ -13847,7 +13934,7 @@
         <v>323</v>
       </c>
       <c r="E116" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F116" s="12">
         <v>4.75</v>
@@ -13871,12 +13958,12 @@
         <v>-81.7</v>
       </c>
       <c r="M116" t="s">
-        <v>572</v>
+        <v>600</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B117" t="s">
         <v>405</v>
@@ -13912,12 +13999,12 @@
         <v>-92.4</v>
       </c>
       <c r="M117" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B118" t="s">
         <v>405</v>
@@ -13929,7 +14016,7 @@
         <v>323</v>
       </c>
       <c r="E118" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F118" s="12">
         <v>4</v>
@@ -13953,12 +14040,12 @@
         <v>-96.5</v>
       </c>
       <c r="M118" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B119" t="s">
         <v>405</v>
@@ -13994,12 +14081,12 @@
         <v>-97</v>
       </c>
       <c r="M119" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B120" t="s">
         <v>405</v>
@@ -14011,7 +14098,7 @@
         <v>323</v>
       </c>
       <c r="E120" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F120" s="12">
         <v>12</v>
@@ -14035,12 +14122,12 @@
         <v>-94</v>
       </c>
       <c r="M120" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B121" t="s">
         <v>405</v>
@@ -14052,7 +14139,7 @@
         <v>323</v>
       </c>
       <c r="E121" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F121" s="12">
         <v>14</v>
@@ -14076,12 +14163,12 @@
         <v>-93.4</v>
       </c>
       <c r="M121" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>407</v>
@@ -14093,7 +14180,7 @@
         <v>319</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F122" s="8">
         <v>31</v>
@@ -14109,12 +14196,12 @@
       </c>
       <c r="L122" s="11"/>
       <c r="M122" s="4" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B123" t="s">
         <v>407</v>
@@ -14126,7 +14213,7 @@
         <v>319</v>
       </c>
       <c r="E123" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F123" s="12">
         <v>8.25</v>
@@ -14150,12 +14237,12 @@
         <v>-74.2</v>
       </c>
       <c r="M123" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B124" t="s">
         <v>407</v>
@@ -14167,7 +14254,7 @@
         <v>319</v>
       </c>
       <c r="E124" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F124" s="12">
         <v>5.1</v>
@@ -14191,12 +14278,12 @@
         <v>-92.3</v>
       </c>
       <c r="M124" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B125" t="s">
         <v>407</v>
@@ -14232,12 +14319,12 @@
         <v>-98.1</v>
       </c>
       <c r="M125" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B126" t="s">
         <v>407</v>
@@ -14249,7 +14336,7 @@
         <v>319</v>
       </c>
       <c r="E126" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F126" s="12">
         <v>4</v>
@@ -14273,12 +14360,12 @@
         <v>-98.5</v>
       </c>
       <c r="M126" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B127" t="s">
         <v>407</v>
@@ -14314,12 +14401,12 @@
         <v>-98.3</v>
       </c>
       <c r="M127" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B128" t="s">
         <v>407</v>
@@ -14331,7 +14418,7 @@
         <v>319</v>
       </c>
       <c r="E128" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F128" s="12">
         <v>11</v>
@@ -14355,12 +14442,12 @@
         <v>-97.5</v>
       </c>
       <c r="M128" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B129" t="s">
         <v>407</v>
@@ -14372,7 +14459,7 @@
         <v>319</v>
       </c>
       <c r="E129" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F129" s="12">
         <v>12</v>
@@ -14396,24 +14483,24 @@
         <v>-97.7</v>
       </c>
       <c r="M129" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
     </row>
     <row r="130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>408</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>410</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F130" s="8">
         <v>13.5</v>
@@ -14429,24 +14516,24 @@
       </c>
       <c r="L130" s="11"/>
       <c r="M130" s="4" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B131" t="s">
         <v>408</v>
       </c>
       <c r="C131" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D131" t="s">
         <v>410</v>
       </c>
       <c r="E131" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F131" s="12">
         <v>5.2</v>
@@ -14470,24 +14557,24 @@
         <v>-58</v>
       </c>
       <c r="M131" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B132" t="s">
         <v>408</v>
       </c>
       <c r="C132" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D132" t="s">
         <v>410</v>
       </c>
       <c r="E132" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F132" s="12">
         <v>3.35</v>
@@ -14511,18 +14598,18 @@
         <v>-81.6</v>
       </c>
       <c r="M132" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B133" t="s">
         <v>408</v>
       </c>
       <c r="C133" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D133" t="s">
         <v>410</v>
@@ -14552,24 +14639,24 @@
         <v>-90.8</v>
       </c>
       <c r="M133" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B134" t="s">
         <v>408</v>
       </c>
       <c r="C134" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D134" t="s">
         <v>410</v>
       </c>
       <c r="E134" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F134" s="12">
         <v>5.6</v>
@@ -14593,18 +14680,18 @@
         <v>-95.8</v>
       </c>
       <c r="M134" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B135" t="s">
         <v>408</v>
       </c>
       <c r="C135" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D135" t="s">
         <v>410</v>
@@ -14634,24 +14721,24 @@
         <v>-95.9</v>
       </c>
       <c r="M135" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B136" t="s">
         <v>408</v>
       </c>
       <c r="C136" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D136" t="s">
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F136" s="12">
         <v>20</v>
@@ -14675,24 +14762,24 @@
         <v>-93.3</v>
       </c>
       <c r="M136" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B137" t="s">
         <v>408</v>
       </c>
       <c r="C137" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D137" t="s">
         <v>410</v>
       </c>
       <c r="E137" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F137" s="12">
         <v>30</v>
@@ -14716,12 +14803,12 @@
         <v>-92.7</v>
       </c>
       <c r="M137" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
     </row>
     <row r="138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>409</v>
@@ -14733,7 +14820,7 @@
         <v>329</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F138" s="8">
         <v>18</v>
@@ -14749,12 +14836,12 @@
       </c>
       <c r="L138" s="11"/>
       <c r="M138" s="4" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B139" t="s">
         <v>409</v>
@@ -14766,7 +14853,7 @@
         <v>329</v>
       </c>
       <c r="E139" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F139" s="12">
         <v>6.25</v>
@@ -14790,12 +14877,12 @@
         <v>-49</v>
       </c>
       <c r="M139" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B140" t="s">
         <v>409</v>
@@ -14807,7 +14894,7 @@
         <v>329</v>
       </c>
       <c r="E140" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F140" s="12">
         <v>4.15</v>
@@ -14831,12 +14918,12 @@
         <v>-72.3</v>
       </c>
       <c r="M140" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B141" t="s">
         <v>409</v>
@@ -14872,12 +14959,12 @@
         <v>-83.6</v>
       </c>
       <c r="M141" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B142" t="s">
         <v>409</v>
@@ -14889,7 +14976,7 @@
         <v>329</v>
       </c>
       <c r="E142" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F142" s="12">
         <v>4.6</v>
@@ -14913,12 +15000,12 @@
         <v>-88.7</v>
       </c>
       <c r="M142" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B143" t="s">
         <v>409</v>
@@ -14954,12 +15041,12 @@
         <v>-93.2</v>
       </c>
       <c r="M143" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B144" t="s">
         <v>409</v>
@@ -14971,7 +15058,7 @@
         <v>329</v>
       </c>
       <c r="E144" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F144" s="12">
         <v>15.5</v>
@@ -14995,12 +15082,12 @@
         <v>-85.4</v>
       </c>
       <c r="M144" t="s">
-        <v>600</v>
+        <v>628</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B145" t="s">
         <v>409</v>
@@ -15012,7 +15099,7 @@
         <v>329</v>
       </c>
       <c r="E145" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F145" s="12">
         <v>21</v>
@@ -15036,24 +15123,24 @@
         <v>-85.1</v>
       </c>
       <c r="M145" t="s">
-        <v>601</v>
+        <v>629</v>
       </c>
     </row>
     <row r="146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>411</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F146" s="8">
         <v>26</v>
@@ -15069,24 +15156,24 @@
       </c>
       <c r="L146" s="11"/>
       <c r="M146" s="4" t="s">
-        <v>602</v>
+        <v>630</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B147" t="s">
         <v>411</v>
       </c>
       <c r="C147" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D147" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E147" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F147" s="12">
         <v>8.2</v>
@@ -15110,24 +15197,24 @@
         <v>-44.4</v>
       </c>
       <c r="M147" t="s">
-        <v>603</v>
+        <v>631</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B148" t="s">
         <v>411</v>
       </c>
       <c r="C148" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D148" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E148" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F148" s="12">
         <v>4.6</v>
@@ -15151,21 +15238,21 @@
         <v>-67.9</v>
       </c>
       <c r="M148" t="s">
-        <v>604</v>
+        <v>632</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B149" t="s">
         <v>411</v>
       </c>
       <c r="C149" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D149" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E149" t="s">
         <v>423</v>
@@ -15192,24 +15279,24 @@
         <v>-80.2</v>
       </c>
       <c r="M149" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B150" t="s">
         <v>411</v>
       </c>
       <c r="C150" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D150" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E150" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F150" s="12">
         <v>4.5</v>
@@ -15233,21 +15320,21 @@
         <v>-87.4</v>
       </c>
       <c r="M150" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B151" t="s">
         <v>411</v>
       </c>
       <c r="C151" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D151" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E151" t="s">
         <v>431</v>
@@ -15274,24 +15361,24 @@
         <v>-92.6</v>
       </c>
       <c r="M151" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B152" t="s">
         <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D152" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E152" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -15315,24 +15402,24 @@
         <v>-84.3</v>
       </c>
       <c r="M152" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="B153" t="s">
         <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="D153" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E153" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F153" s="12">
         <v>13</v>
@@ -15356,7 +15443,7 @@
         <v>-84.7</v>
       </c>
       <c r="M153" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -15377,17 +15464,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -15395,7 +15482,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -15403,41 +15490,41 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>614</v>
+        <v>642</v>
       </c>
       <c r="B6" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="B7" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="B8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>619</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -15445,76 +15532,76 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="B13" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="B14" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="B15" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>624</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>635</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -15526,10 +15613,10 @@
         <v>21</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>21</v>
@@ -15540,19 +15627,19 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
@@ -15569,16 +15656,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
@@ -15604,13 +15691,13 @@
         <v>21</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -15627,10 +15714,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
@@ -15639,10 +15726,10 @@
         <v>21</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -15671,13 +15758,13 @@
         <v>21</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -15685,7 +15772,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>21</v>
@@ -15703,18 +15790,18 @@
         <v>21</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -15735,15 +15822,15 @@
         <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>642</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -15768,40 +15855,40 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>643</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>644</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -15824,7 +15911,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -15847,7 +15934,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -15870,7 +15957,7 @@
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -15878,7 +15965,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -15890,25 +15977,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>656</v>
+        <v>684</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>658</v>
+        <v>686</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -15928,7 +16015,7 @@
         <v>245</v>
       </c>
       <c r="F11" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G11" s="12">
         <v>10.5</v>
@@ -15966,7 +16053,7 @@
         <v>248</v>
       </c>
       <c r="F12" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G12" s="12">
         <v>25</v>
@@ -16004,13 +16091,13 @@
         <v>260</v>
       </c>
       <c r="F13" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G13" s="12">
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="I13" s="23">
         <v>-100</v>
@@ -16042,13 +16129,13 @@
         <v>257</v>
       </c>
       <c r="F14" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G14" s="12">
         <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="I14" s="23">
         <v>-100</v>
@@ -16080,13 +16167,13 @@
         <v>240</v>
       </c>
       <c r="F15" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G15" s="12">
         <v>7.5</v>
       </c>
       <c r="H15" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="I15" s="26">
         <v>650</v>
@@ -16118,13 +16205,13 @@
         <v>244</v>
       </c>
       <c r="F16" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G16" s="12">
         <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="I16" s="26">
         <v>1500</v>
@@ -16156,13 +16243,13 @@
         <v>254</v>
       </c>
       <c r="F17" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="G17" s="12">
         <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="I17" s="23">
         <v>-100</v>
@@ -16179,7 +16266,7 @@
     </row>
     <row r="19" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>662</v>
+        <v>690</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -16187,22 +16274,22 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>667</v>
+        <v>695</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -16245,33 +16332,33 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>423</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>669</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>670</v>
+        <v>698</v>
       </c>
       <c r="B2">
         <v>331</v>
@@ -16297,7 +16384,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="B3">
         <v>330</v>
@@ -16323,7 +16410,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="B4">
         <v>321</v>
@@ -16349,7 +16436,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="B5">
         <v>313</v>
@@ -16375,7 +16462,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="B6">
         <v>305</v>
@@ -16401,7 +16488,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="B7">
         <v>287</v>
@@ -16427,7 +16514,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="B8">
         <v>278</v>
@@ -16453,7 +16540,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -16479,7 +16566,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -16505,7 +16592,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -16545,43 +16632,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>680</v>
+        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>681</v>
+        <v>709</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>684</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="C5" s="28">
         <v>35</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>685</v>
+        <v>713</v>
       </c>
       <c r="E5" s="28">
         <v>15</v>
@@ -16589,35 +16676,35 @@
     </row>
     <row r="7" spans="1:1" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>686</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>423</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>669</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>670</v>
+        <v>698</v>
       </c>
       <c r="B9" s="3">
         <v>4</v>
@@ -16640,7 +16727,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="B10" s="3">
         <v>6</v>
@@ -16663,7 +16750,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="B11" s="30">
         <v>22</v>
@@ -16686,7 +16773,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="B12" s="31">
         <v>35</v>
@@ -16709,7 +16796,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -16732,7 +16819,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="B14" s="3">
         <v>0</v>
@@ -16755,7 +16842,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="B15" s="30">
         <v>20</v>
@@ -16778,7 +16865,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -16801,7 +16888,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B17" s="30">
         <v>26</v>
@@ -16824,7 +16911,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -16853,7 +16940,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
@@ -16861,7 +16948,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>687</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -16871,62 +16958,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>688</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>689</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>690</v>
+        <v>718</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>692</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>693</v>
+        <v>721</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>694</v>
+        <v>722</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>696</v>
+        <v>724</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>697</v>
+        <v>725</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>699</v>
+        <v>727</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -16936,32 +17023,32 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>700</v>
+        <v>728</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>701</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>703</v>
+        <v>731</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>704</v>
+        <v>732</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>705</v>
+        <v>733</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -16971,22 +17058,22 @@
     </row>
     <row r="23" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>706</v>
+        <v>734</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>707</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>708</v>
+        <v>736</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>709</v>
+        <v>737</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -16996,37 +17083,42 @@
     </row>
     <row r="28" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>710</v>
+        <v>738</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>711</v>
+        <v>739</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>712</v>
+        <v>740</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>713</v>
+        <v>741</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>715</v>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3278" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3278" uniqueCount="762">
   <si>
     <t>日期</t>
   </si>
@@ -1385,6 +1385,12 @@
     <t>3球 @3.35</t>
   </si>
   <si>
+    <t>1球 @5.8 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.35 ⚡</t>
+  </si>
+  <si>
     <t>10-06 17:00</t>
   </si>
   <si>
@@ -1397,39 +1403,81 @@
     <t>1球 @3.95</t>
   </si>
   <si>
+    <t>3球 @4.05 ⚡</t>
+  </si>
+  <si>
     <t>10-06 22:00</t>
   </si>
   <si>
     <t>1球 @3.75</t>
   </si>
   <si>
+    <t>3球 @4.1 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @7 ⚡</t>
+  </si>
+  <si>
     <t>10-07 02:45</t>
   </si>
   <si>
     <t>2球 @3.35</t>
   </si>
   <si>
+    <t>1球 @4.85 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
     <t>1球 @3.3</t>
   </si>
   <si>
+    <t>3球 @3.8 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @8 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @4 ⚡</t>
+  </si>
+  <si>
     <t>6球 @8.8</t>
   </si>
   <si>
     <t>4球 @4</t>
   </si>
   <si>
+    <t>1球 @8 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.65 ⚡</t>
+  </si>
+  <si>
     <t>6球 @11</t>
   </si>
   <si>
+    <t>1球 @8.25 ⚡</t>
+  </si>
+  <si>
     <t>摩尔多瓦</t>
   </si>
   <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
     <t>10-07 08:00</t>
   </si>
   <si>
     <t>3球 @3.45</t>
   </si>
   <si>
+    <t>1球 @6.25 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.45 ⚡</t>
+  </si>
+  <si>
     <t>芝加哥</t>
   </si>
   <si>
@@ -1442,6 +1490,9 @@
     <t>6球 @10</t>
   </si>
   <si>
+    <t>3球 @3.7 ⚡</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1934,7 +1985,7 @@
     <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-06T17:12:55+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-06T17:43:02+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2240,7 +2291,7 @@
     <t xml:space="preserve">  · 赔率、赛果来自中国体育彩票官方 Web API；每次抓取保留完整玩法池（总进球0-7+、比分矩阵）。</t>
   </si>
   <si>
-    <t xml:space="preserve">  · 预测列格式"X球 @赔率"：@后为该预测进球数对应的赔率（该场最后一次记录），便于核对与回测对照。</t>
+    <t xml:space="preserve">  · 预测列格式"X球 @赔率"：@后为该预测进球数对应的赔率（该场最后一次记录），便于核对与回测对照；带 ⚡ 的为未结算场次的实时模型预测（同算法），结算时冻结存档。</t>
   </si>
   <si>
     <t xml:space="preserve">  · 凌晨开赛的比赛属于前一"销售日"（预测窗口按销售日切分）。</t>
@@ -8765,10 +8816,10 @@
         <v>454</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="L9" t="s">
         <v>21</v>
@@ -8777,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O9" t="s">
         <v>21</v>
@@ -8797,10 +8848,10 @@
         <v>200</v>
       </c>
       <c r="E10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>70</v>
@@ -8809,13 +8860,13 @@
         <v>21</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="L10" t="s">
         <v>21</v>
@@ -8824,7 +8875,7 @@
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -8847,7 +8898,7 @@
         <v>301</v>
       </c>
       <c r="F11" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>55</v>
@@ -8856,13 +8907,13 @@
         <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="L11" t="s">
         <v>21</v>
@@ -8871,7 +8922,7 @@
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O11" t="s">
         <v>21</v>
@@ -8894,7 +8945,7 @@
         <v>305</v>
       </c>
       <c r="F12" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>55</v>
@@ -8903,13 +8954,13 @@
         <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>21</v>
+        <v>468</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>21</v>
+        <v>469</v>
       </c>
       <c r="L12" t="s">
         <v>21</v>
@@ -8918,7 +8969,7 @@
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O12" t="s">
         <v>21</v>
@@ -8941,7 +8992,7 @@
         <v>308</v>
       </c>
       <c r="F13" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>55</v>
@@ -8950,13 +9001,13 @@
         <v>21</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>21</v>
+        <v>472</v>
       </c>
       <c r="L13" t="s">
         <v>21</v>
@@ -8965,7 +9016,7 @@
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O13" t="s">
         <v>21</v>
@@ -8988,7 +9039,7 @@
         <v>293</v>
       </c>
       <c r="F14" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>55</v>
@@ -8997,13 +9048,13 @@
         <v>21</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="L14" t="s">
         <v>21</v>
@@ -9012,7 +9063,7 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O14" t="s">
         <v>21</v>
@@ -9035,7 +9086,7 @@
         <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G15" t="s">
         <v>21</v>
@@ -9044,13 +9095,13 @@
         <v>21</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="L15" t="s">
         <v>21</v>
@@ -9059,7 +9110,7 @@
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O15" t="s">
         <v>21</v>
@@ -9082,7 +9133,7 @@
         <v>323</v>
       </c>
       <c r="F16" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>70</v>
@@ -9091,13 +9142,13 @@
         <v>21</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="L16" t="s">
         <v>21</v>
@@ -9106,7 +9157,7 @@
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
@@ -9129,7 +9180,7 @@
         <v>319</v>
       </c>
       <c r="F17" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G17" t="s">
         <v>21</v>
@@ -9138,13 +9189,13 @@
         <v>21</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>21</v>
+        <v>479</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="L17" t="s">
         <v>21</v>
@@ -9153,7 +9204,7 @@
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
@@ -9170,13 +9221,13 @@
         <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="E18" t="s">
         <v>410</v>
       </c>
       <c r="F18" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>55</v>
@@ -9185,13 +9236,13 @@
         <v>21</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="L18" t="s">
         <v>21</v>
@@ -9200,7 +9251,7 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
@@ -9223,7 +9274,7 @@
         <v>329</v>
       </c>
       <c r="F19" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>55</v>
@@ -9232,13 +9283,13 @@
         <v>21</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>21</v>
+        <v>484</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>21</v>
+        <v>485</v>
       </c>
       <c r="L19" t="s">
         <v>21</v>
@@ -9247,7 +9298,7 @@
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O19" t="s">
         <v>21</v>
@@ -9264,13 +9315,13 @@
         <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="E20" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F20" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>55</v>
@@ -9279,13 +9330,13 @@
         <v>21</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
@@ -9294,7 +9345,7 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O20" t="s">
         <v>21</v>
@@ -9330,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -9339,31 +9390,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9396,7 +9447,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -9437,7 +9488,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -9454,7 +9505,7 @@
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F4" s="12">
         <v>3.2</v>
@@ -9478,7 +9529,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -9519,7 +9570,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -9560,7 +9611,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -9601,7 +9652,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -9618,7 +9669,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -9642,7 +9693,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -9659,7 +9710,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -9683,7 +9734,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9716,7 +9767,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -9757,7 +9808,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -9774,7 +9825,7 @@
         <v>248</v>
       </c>
       <c r="E12" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F12" s="12">
         <v>4.35</v>
@@ -9798,7 +9849,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -9839,7 +9890,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -9880,7 +9931,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -9921,7 +9972,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -9938,7 +9989,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -9962,7 +10013,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -9979,7 +10030,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -10003,7 +10054,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10036,7 +10087,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -10077,7 +10128,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -10094,7 +10145,7 @@
         <v>260</v>
       </c>
       <c r="E20" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F20" s="12">
         <v>4.2</v>
@@ -10118,7 +10169,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -10159,7 +10210,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -10200,7 +10251,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -10241,7 +10292,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -10258,7 +10309,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -10282,7 +10333,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -10299,7 +10350,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -10323,7 +10374,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10356,7 +10407,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -10397,7 +10448,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -10414,7 +10465,7 @@
         <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F28" s="12">
         <v>4.4</v>
@@ -10438,7 +10489,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -10479,7 +10530,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -10520,7 +10571,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -10561,7 +10612,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -10578,7 +10629,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -10602,7 +10653,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -10619,7 +10670,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -10643,7 +10694,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10676,7 +10727,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -10717,7 +10768,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -10734,7 +10785,7 @@
         <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F36" s="12">
         <v>3.2</v>
@@ -10758,7 +10809,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -10799,7 +10850,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -10840,7 +10891,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -10881,7 +10932,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -10898,7 +10949,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -10922,7 +10973,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -10939,7 +10990,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -10963,7 +11014,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10996,7 +11047,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -11037,7 +11088,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -11054,7 +11105,7 @@
         <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F44" s="12">
         <v>3.8</v>
@@ -11078,7 +11129,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -11119,7 +11170,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -11160,7 +11211,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -11201,7 +11252,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -11218,7 +11269,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -11242,7 +11293,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -11259,7 +11310,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -11283,7 +11334,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11316,7 +11367,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -11357,7 +11408,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -11374,7 +11425,7 @@
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F52" s="12">
         <v>3.3</v>
@@ -11398,7 +11449,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -11439,7 +11490,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -11480,7 +11531,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -11521,7 +11572,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -11538,7 +11589,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -11562,7 +11613,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -11579,7 +11630,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -11603,7 +11654,7 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11636,7 +11687,7 @@
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="4" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -11677,7 +11728,7 @@
         <v>-49.6</v>
       </c>
       <c r="M59" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -11694,7 +11745,7 @@
         <v>452</v>
       </c>
       <c r="E60" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F60" s="12">
         <v>3.7</v>
@@ -11718,7 +11769,7 @@
         <v>-74.8</v>
       </c>
       <c r="M60" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -11759,7 +11810,7 @@
         <v>-88.2</v>
       </c>
       <c r="M61" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -11800,7 +11851,7 @@
         <v>-92.7</v>
       </c>
       <c r="M62" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -11841,7 +11892,7 @@
         <v>-95</v>
       </c>
       <c r="M63" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -11858,7 +11909,7 @@
         <v>452</v>
       </c>
       <c r="E64" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F64" s="12">
         <v>18.5</v>
@@ -11882,7 +11933,7 @@
         <v>-89.7</v>
       </c>
       <c r="M64" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -11899,7 +11950,7 @@
         <v>452</v>
       </c>
       <c r="E65" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F65" s="12">
         <v>25</v>
@@ -11923,7 +11974,7 @@
         <v>-89.2</v>
       </c>
       <c r="M65" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11937,7 +11988,7 @@
         <v>200</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>442</v>
@@ -11956,7 +12007,7 @@
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="4" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -11970,7 +12021,7 @@
         <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E67" t="s">
         <v>434</v>
@@ -11997,7 +12048,7 @@
         <v>-51.7</v>
       </c>
       <c r="M67" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -12011,10 +12062,10 @@
         <v>200</v>
       </c>
       <c r="D68" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E68" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F68" s="12">
         <v>3.1</v>
@@ -12038,7 +12089,7 @@
         <v>-73.4</v>
       </c>
       <c r="M68" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -12052,7 +12103,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E69" t="s">
         <v>423</v>
@@ -12079,7 +12130,7 @@
         <v>-83.2</v>
       </c>
       <c r="M69" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -12093,7 +12144,7 @@
         <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E70" t="s">
         <v>439</v>
@@ -12120,7 +12171,7 @@
         <v>-88.2</v>
       </c>
       <c r="M70" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -12134,7 +12185,7 @@
         <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E71" t="s">
         <v>431</v>
@@ -12161,7 +12212,7 @@
         <v>-86.5</v>
       </c>
       <c r="M71" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -12175,10 +12226,10 @@
         <v>200</v>
       </c>
       <c r="D72" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E72" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F72" s="12">
         <v>27</v>
@@ -12202,7 +12253,7 @@
         <v>-80.7</v>
       </c>
       <c r="M72" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -12216,10 +12267,10 @@
         <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E73" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F73" s="12">
         <v>45</v>
@@ -12243,7 +12294,7 @@
         <v>-82.9</v>
       </c>
       <c r="M73" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12276,7 +12327,7 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="4" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -12317,7 +12368,7 @@
         <v>-48.3</v>
       </c>
       <c r="M75" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -12334,7 +12385,7 @@
         <v>301</v>
       </c>
       <c r="E76" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F76" s="12">
         <v>3.15</v>
@@ -12358,7 +12409,7 @@
         <v>-68.4</v>
       </c>
       <c r="M76" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -12399,7 +12450,7 @@
         <v>-80.5</v>
       </c>
       <c r="M77" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -12440,7 +12491,7 @@
         <v>-86.5</v>
       </c>
       <c r="M78" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -12481,7 +12532,7 @@
         <v>-87.7</v>
       </c>
       <c r="M79" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -12498,7 +12549,7 @@
         <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F80" s="12">
         <v>38</v>
@@ -12522,7 +12573,7 @@
         <v>-75.9</v>
       </c>
       <c r="M80" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -12539,7 +12590,7 @@
         <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F81" s="12">
         <v>70</v>
@@ -12563,7 +12614,7 @@
         <v>-78.5</v>
       </c>
       <c r="M81" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12596,7 +12647,7 @@
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="4" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -12637,7 +12688,7 @@
         <v>-50.9</v>
       </c>
       <c r="M83" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -12654,7 +12705,7 @@
         <v>305</v>
       </c>
       <c r="E84" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F84" s="12">
         <v>3.35</v>
@@ -12678,7 +12729,7 @@
         <v>-76.5</v>
       </c>
       <c r="M84" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -12719,7 +12770,7 @@
         <v>-87.5</v>
       </c>
       <c r="M85" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -12760,7 +12811,7 @@
         <v>-92.7</v>
       </c>
       <c r="M86" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -12801,7 +12852,7 @@
         <v>-94.2</v>
       </c>
       <c r="M87" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -12818,7 +12869,7 @@
         <v>305</v>
       </c>
       <c r="E88" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F88" s="12">
         <v>24</v>
@@ -12842,7 +12893,7 @@
         <v>-89.6</v>
       </c>
       <c r="M88" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -12859,7 +12910,7 @@
         <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F89" s="12">
         <v>35</v>
@@ -12883,7 +12934,7 @@
         <v>-88.8</v>
       </c>
       <c r="M89" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12916,7 +12967,7 @@
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="4" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -12957,7 +13008,7 @@
         <v>-51.1</v>
       </c>
       <c r="M91" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -12974,7 +13025,7 @@
         <v>308</v>
       </c>
       <c r="E92" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F92" s="12">
         <v>3.3</v>
@@ -12998,7 +13049,7 @@
         <v>-72.5</v>
       </c>
       <c r="M92" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -13039,7 +13090,7 @@
         <v>-83.6</v>
       </c>
       <c r="M93" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -13080,7 +13131,7 @@
         <v>-87.9</v>
       </c>
       <c r="M94" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -13121,7 +13172,7 @@
         <v>-89.2</v>
       </c>
       <c r="M95" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -13138,7 +13189,7 @@
         <v>308</v>
       </c>
       <c r="E96" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F96" s="12">
         <v>40</v>
@@ -13162,7 +13213,7 @@
         <v>-78</v>
       </c>
       <c r="M96" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -13179,7 +13230,7 @@
         <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F97" s="12">
         <v>80</v>
@@ -13203,7 +13254,7 @@
         <v>-78.8</v>
       </c>
       <c r="M97" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13236,7 +13287,7 @@
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="4" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -13277,7 +13328,7 @@
         <v>-52.4</v>
       </c>
       <c r="M99" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -13294,7 +13345,7 @@
         <v>293</v>
       </c>
       <c r="E100" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F100" s="12">
         <v>3.2</v>
@@ -13318,7 +13369,7 @@
         <v>-74</v>
       </c>
       <c r="M100" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -13359,7 +13410,7 @@
         <v>-86.3</v>
       </c>
       <c r="M101" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -13400,7 +13451,7 @@
         <v>-91.6</v>
       </c>
       <c r="M102" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -13441,7 +13492,7 @@
         <v>-92.2</v>
       </c>
       <c r="M103" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -13458,7 +13509,7 @@
         <v>293</v>
       </c>
       <c r="E104" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F104" s="12">
         <v>35</v>
@@ -13482,7 +13533,7 @@
         <v>-81.8</v>
       </c>
       <c r="M104" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -13499,7 +13550,7 @@
         <v>293</v>
       </c>
       <c r="E105" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F105" s="12">
         <v>60</v>
@@ -13523,7 +13574,7 @@
         <v>-82.4</v>
       </c>
       <c r="M105" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13556,7 +13607,7 @@
       </c>
       <c r="L106" s="11"/>
       <c r="M106" s="4" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -13597,7 +13648,7 @@
         <v>-66.4</v>
       </c>
       <c r="M107" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
@@ -13614,7 +13665,7 @@
         <v>315</v>
       </c>
       <c r="E108" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F108" s="12">
         <v>5.6</v>
@@ -13638,7 +13689,7 @@
         <v>-89.7</v>
       </c>
       <c r="M108" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
@@ -13679,7 +13730,7 @@
         <v>-96.9</v>
       </c>
       <c r="M109" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
@@ -13720,7 +13771,7 @@
         <v>-98.4</v>
       </c>
       <c r="M110" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -13761,7 +13812,7 @@
         <v>-98.2</v>
       </c>
       <c r="M111" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -13778,7 +13829,7 @@
         <v>315</v>
       </c>
       <c r="E112" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F112" s="12">
         <v>8.8</v>
@@ -13802,7 +13853,7 @@
         <v>-97.2</v>
       </c>
       <c r="M112" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
@@ -13819,7 +13870,7 @@
         <v>315</v>
       </c>
       <c r="E113" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F113" s="12">
         <v>9</v>
@@ -13843,7 +13894,7 @@
         <v>-97.7</v>
       </c>
       <c r="M113" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13876,7 +13927,7 @@
       </c>
       <c r="L114" s="11"/>
       <c r="M114" s="4" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
@@ -13917,7 +13968,7 @@
         <v>-58.4</v>
       </c>
       <c r="M115" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -13934,7 +13985,7 @@
         <v>323</v>
       </c>
       <c r="E116" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F116" s="12">
         <v>4.75</v>
@@ -13958,7 +14009,7 @@
         <v>-81.7</v>
       </c>
       <c r="M116" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
@@ -13999,7 +14050,7 @@
         <v>-92.4</v>
       </c>
       <c r="M117" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
@@ -14040,7 +14091,7 @@
         <v>-96.5</v>
       </c>
       <c r="M118" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -14081,7 +14132,7 @@
         <v>-97</v>
       </c>
       <c r="M119" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -14098,7 +14149,7 @@
         <v>323</v>
       </c>
       <c r="E120" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F120" s="12">
         <v>12</v>
@@ -14122,7 +14173,7 @@
         <v>-94</v>
       </c>
       <c r="M120" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -14139,7 +14190,7 @@
         <v>323</v>
       </c>
       <c r="E121" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F121" s="12">
         <v>14</v>
@@ -14163,7 +14214,7 @@
         <v>-93.4</v>
       </c>
       <c r="M121" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14196,7 +14247,7 @@
       </c>
       <c r="L122" s="11"/>
       <c r="M122" s="4" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -14237,7 +14288,7 @@
         <v>-74.2</v>
       </c>
       <c r="M123" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -14254,7 +14305,7 @@
         <v>319</v>
       </c>
       <c r="E124" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F124" s="12">
         <v>5.1</v>
@@ -14278,7 +14329,7 @@
         <v>-92.3</v>
       </c>
       <c r="M124" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -14319,7 +14370,7 @@
         <v>-98.1</v>
       </c>
       <c r="M125" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -14360,7 +14411,7 @@
         <v>-98.5</v>
       </c>
       <c r="M126" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -14401,7 +14452,7 @@
         <v>-98.3</v>
       </c>
       <c r="M127" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -14418,7 +14469,7 @@
         <v>319</v>
       </c>
       <c r="E128" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F128" s="12">
         <v>11</v>
@@ -14442,7 +14493,7 @@
         <v>-97.5</v>
       </c>
       <c r="M128" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -14459,7 +14510,7 @@
         <v>319</v>
       </c>
       <c r="E129" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F129" s="12">
         <v>12</v>
@@ -14483,7 +14534,7 @@
         <v>-97.7</v>
       </c>
       <c r="M129" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
     </row>
     <row r="130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14494,7 +14545,7 @@
         <v>408</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>410</v>
@@ -14516,7 +14567,7 @@
       </c>
       <c r="L130" s="11"/>
       <c r="M130" s="4" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -14527,7 +14578,7 @@
         <v>408</v>
       </c>
       <c r="C131" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D131" t="s">
         <v>410</v>
@@ -14557,7 +14608,7 @@
         <v>-58</v>
       </c>
       <c r="M131" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -14568,13 +14619,13 @@
         <v>408</v>
       </c>
       <c r="C132" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D132" t="s">
         <v>410</v>
       </c>
       <c r="E132" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F132" s="12">
         <v>3.35</v>
@@ -14598,7 +14649,7 @@
         <v>-81.6</v>
       </c>
       <c r="M132" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -14609,7 +14660,7 @@
         <v>408</v>
       </c>
       <c r="C133" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D133" t="s">
         <v>410</v>
@@ -14639,7 +14690,7 @@
         <v>-90.8</v>
       </c>
       <c r="M133" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -14650,7 +14701,7 @@
         <v>408</v>
       </c>
       <c r="C134" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D134" t="s">
         <v>410</v>
@@ -14680,7 +14731,7 @@
         <v>-95.8</v>
       </c>
       <c r="M134" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -14691,7 +14742,7 @@
         <v>408</v>
       </c>
       <c r="C135" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D135" t="s">
         <v>410</v>
@@ -14721,7 +14772,7 @@
         <v>-95.9</v>
       </c>
       <c r="M135" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -14732,13 +14783,13 @@
         <v>408</v>
       </c>
       <c r="C136" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D136" t="s">
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F136" s="12">
         <v>20</v>
@@ -14762,7 +14813,7 @@
         <v>-93.3</v>
       </c>
       <c r="M136" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -14773,13 +14824,13 @@
         <v>408</v>
       </c>
       <c r="C137" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D137" t="s">
         <v>410</v>
       </c>
       <c r="E137" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F137" s="12">
         <v>30</v>
@@ -14803,7 +14854,7 @@
         <v>-92.7</v>
       </c>
       <c r="M137" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
     </row>
     <row r="138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14836,7 +14887,7 @@
       </c>
       <c r="L138" s="11"/>
       <c r="M138" s="4" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -14877,7 +14928,7 @@
         <v>-49</v>
       </c>
       <c r="M139" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -14894,7 +14945,7 @@
         <v>329</v>
       </c>
       <c r="E140" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F140" s="12">
         <v>4.15</v>
@@ -14918,7 +14969,7 @@
         <v>-72.3</v>
       </c>
       <c r="M140" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -14959,7 +15010,7 @@
         <v>-83.6</v>
       </c>
       <c r="M141" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -15000,7 +15051,7 @@
         <v>-88.7</v>
       </c>
       <c r="M142" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -15041,7 +15092,7 @@
         <v>-93.2</v>
       </c>
       <c r="M143" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -15058,7 +15109,7 @@
         <v>329</v>
       </c>
       <c r="E144" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F144" s="12">
         <v>15.5</v>
@@ -15082,7 +15133,7 @@
         <v>-85.4</v>
       </c>
       <c r="M144" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -15099,7 +15150,7 @@
         <v>329</v>
       </c>
       <c r="E145" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F145" s="12">
         <v>21</v>
@@ -15123,7 +15174,7 @@
         <v>-85.1</v>
       </c>
       <c r="M145" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
     </row>
     <row r="146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15134,10 +15185,10 @@
         <v>411</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>442</v>
@@ -15156,7 +15207,7 @@
       </c>
       <c r="L146" s="11"/>
       <c r="M146" s="4" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -15167,10 +15218,10 @@
         <v>411</v>
       </c>
       <c r="C147" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D147" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E147" t="s">
         <v>434</v>
@@ -15197,7 +15248,7 @@
         <v>-44.4</v>
       </c>
       <c r="M147" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -15208,13 +15259,13 @@
         <v>411</v>
       </c>
       <c r="C148" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D148" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E148" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F148" s="12">
         <v>4.6</v>
@@ -15238,7 +15289,7 @@
         <v>-67.9</v>
       </c>
       <c r="M148" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -15249,10 +15300,10 @@
         <v>411</v>
       </c>
       <c r="C149" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D149" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E149" t="s">
         <v>423</v>
@@ -15279,7 +15330,7 @@
         <v>-80.2</v>
       </c>
       <c r="M149" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -15290,10 +15341,10 @@
         <v>411</v>
       </c>
       <c r="C150" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D150" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E150" t="s">
         <v>439</v>
@@ -15320,7 +15371,7 @@
         <v>-87.4</v>
       </c>
       <c r="M150" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -15331,10 +15382,10 @@
         <v>411</v>
       </c>
       <c r="C151" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D151" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E151" t="s">
         <v>431</v>
@@ -15361,7 +15412,7 @@
         <v>-92.6</v>
       </c>
       <c r="M151" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -15372,13 +15423,13 @@
         <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D152" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E152" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -15402,7 +15453,7 @@
         <v>-84.3</v>
       </c>
       <c r="M152" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -15413,13 +15464,13 @@
         <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="D153" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E153" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F153" s="12">
         <v>13</v>
@@ -15443,7 +15494,7 @@
         <v>-84.7</v>
       </c>
       <c r="M153" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -15464,17 +15515,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -15482,7 +15533,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -15490,41 +15541,41 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
       <c r="B6" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="B7" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="B8" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -15532,68 +15583,68 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="B13" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="B14" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
       <c r="B15" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -15601,7 +15652,7 @@
         <v>442</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -15613,10 +15664,10 @@
         <v>21</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>21</v>
@@ -15633,13 +15684,13 @@
         <v>21</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
@@ -15656,16 +15707,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
@@ -15691,13 +15742,13 @@
         <v>21</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -15717,7 +15768,7 @@
         <v>439</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
@@ -15726,10 +15777,10 @@
         <v>21</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -15758,13 +15809,13 @@
         <v>21</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -15772,7 +15823,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>21</v>
@@ -15790,18 +15841,18 @@
         <v>21</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -15822,15 +15873,15 @@
         <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -15855,40 +15906,40 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -15911,7 +15962,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -15934,7 +15985,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -15957,7 +16008,7 @@
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -15965,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -15977,25 +16028,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -16266,7 +16317,7 @@
     </row>
     <row r="19" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -16274,22 +16325,22 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -16332,10 +16383,10 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>442</v>
@@ -16344,7 +16395,7 @@
         <v>434</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>423</v>
@@ -16353,12 +16404,12 @@
         <v>439</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="B2">
         <v>331</v>
@@ -16384,7 +16435,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="B3">
         <v>330</v>
@@ -16410,7 +16461,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="B4">
         <v>321</v>
@@ -16436,7 +16487,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="B5">
         <v>313</v>
@@ -16462,7 +16513,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="B6">
         <v>305</v>
@@ -16488,7 +16539,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="B7">
         <v>287</v>
@@ -16514,7 +16565,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="B8">
         <v>278</v>
@@ -16540,7 +16591,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -16566,7 +16617,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -16592,7 +16643,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -16632,34 +16683,34 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="B5" s="28" t="s">
         <v>442</v>
@@ -16668,7 +16719,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
       <c r="E5" s="28">
         <v>15</v>
@@ -16676,12 +16727,12 @@
     </row>
     <row r="7" spans="1:1" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>442</v>
@@ -16690,7 +16741,7 @@
         <v>434</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>423</v>
@@ -16699,12 +16750,12 @@
         <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="B9" s="3">
         <v>4</v>
@@ -16727,7 +16778,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="B10" s="3">
         <v>6</v>
@@ -16750,7 +16801,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="B11" s="30">
         <v>22</v>
@@ -16773,7 +16824,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="B12" s="31">
         <v>35</v>
@@ -16796,7 +16847,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -16819,7 +16870,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="B14" s="3">
         <v>0</v>
@@ -16842,7 +16893,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="B15" s="30">
         <v>20</v>
@@ -16865,7 +16916,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -16888,7 +16939,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="B17" s="30">
         <v>26</v>
@@ -16911,7 +16962,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -16948,7 +16999,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -16958,62 +17009,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -17023,32 +17074,32 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -17058,22 +17109,22 @@
     </row>
     <row r="23" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>736</v>
+        <v>753</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>737</v>
+        <v>754</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -17083,27 +17134,27 @@
     </row>
     <row r="28" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>738</v>
+        <v>755</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>739</v>
+        <v>756</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>740</v>
+        <v>757</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
@@ -17113,12 +17164,12 @@
     </row>
     <row r="34" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>743</v>
+        <v>760</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3278" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="764">
   <si>
     <t>日期</t>
   </si>
@@ -1985,7 +1985,7 @@
     <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-06T17:43:02+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-06T17:49:45+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2271,6 +2271,12 @@
   </si>
   <si>
     <t xml:space="preserve">  每场比赛的预测在其赛果落定时冻结（只使用该场之前的数据，杜绝未来数据泄漏），两轨同场对比。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 竞彩比赛开赛即封盘：到开赛时间后，最后一份赔率算出的预测即最终存档值（无需等赛果）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 取消或推迟补赛的场次：结果照常记录与展示，但不纳入模型学习与模拟投注回测（意外情况造成偏差）。</t>
   </si>
   <si>
     <t>【模拟投注】</t>
@@ -16991,7 +16997,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
@@ -17104,21 +17110,21 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
         <v>751</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
         <v>753</v>
       </c>
     </row>
@@ -17129,21 +17135,21 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
         <v>755</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
         <v>757</v>
       </c>
     </row>
@@ -17159,17 +17165,27 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
         <v>760</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>761</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>763</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -1382,61 +1382,64 @@
     <t>10-06 19:00</t>
   </si>
   <si>
-    <t>3球 @3.35</t>
-  </si>
-  <si>
-    <t>1球 @5.8 ⚡</t>
+    <t>7+球 @18</t>
+  </si>
+  <si>
+    <t>0球 @17 ⚡</t>
   </si>
   <si>
     <t>3球 @3.35 ⚡</t>
   </si>
   <si>
+    <t>10-06 18:11</t>
+  </si>
+  <si>
+    <t>塔吉克</t>
+  </si>
+  <si>
+    <t>10-06 19:35</t>
+  </si>
+  <si>
+    <t>1球 @3.95</t>
+  </si>
+  <si>
+    <t>3球 @4.05 ⚡</t>
+  </si>
+  <si>
+    <t>10-06 22:00</t>
+  </si>
+  <si>
+    <t>1球 @3.75</t>
+  </si>
+  <si>
+    <t>3球 @4.1 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @7 ⚡</t>
+  </si>
+  <si>
+    <t>10-07 02:45</t>
+  </si>
+  <si>
+    <t>2球 @3.35</t>
+  </si>
+  <si>
+    <t>1球 @4.85 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
     <t>10-06 17:00</t>
   </si>
   <si>
-    <t>塔吉克</t>
-  </si>
-  <si>
-    <t>10-06 19:35</t>
-  </si>
-  <si>
-    <t>1球 @3.95</t>
-  </si>
-  <si>
-    <t>3球 @4.05 ⚡</t>
-  </si>
-  <si>
-    <t>10-06 22:00</t>
-  </si>
-  <si>
-    <t>1球 @3.75</t>
-  </si>
-  <si>
-    <t>3球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @7 ⚡</t>
-  </si>
-  <si>
-    <t>10-07 02:45</t>
-  </si>
-  <si>
-    <t>2球 @3.35</t>
-  </si>
-  <si>
-    <t>1球 @4.85 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.55 ⚡</t>
-  </si>
-  <si>
-    <t>1球 @3.3</t>
-  </si>
-  <si>
-    <t>3球 @3.8 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @8 ⚡</t>
+    <t>1球 @3.2</t>
+  </si>
+  <si>
+    <t>0球 @8 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @8.25 ⚡</t>
   </si>
   <si>
     <t>3球 @4 ⚡</t>
@@ -1700,28 +1703,28 @@
     <t>2:5=200 5:2=300 负其他=60 平其他=300 胜其他=80</t>
   </si>
   <si>
-    <t>0:0=15</t>
-  </si>
-  <si>
-    <t>0:1=15.5 1:0=7.5</t>
-  </si>
-  <si>
-    <t>0:2=29 1:1=8.25 2:0=6.8</t>
-  </si>
-  <si>
-    <t>0:3=80 1:2=15 2:1=6.5 3:0=12</t>
-  </si>
-  <si>
-    <t>0:4=250 1:3=50 2:2=16 3:1=11 4:0=25</t>
-  </si>
-  <si>
-    <t>0:5=800 1:4=150 2:3=50 3:2=23 4:1=23 5:0=55</t>
-  </si>
-  <si>
-    <t>1:5=550 2:4=180 3:3=60 4:2=45 5:1=65</t>
-  </si>
-  <si>
-    <t>2:5=500 5:2=110 负其他=160 平其他=350 胜其他=42</t>
+    <t>0:0=17</t>
+  </si>
+  <si>
+    <t>0:1=17 1:0=8</t>
+  </si>
+  <si>
+    <t>0:2=34 1:1=8.25 2:0=6.8</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=16 2:1=6.5 3:0=11.5</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=50 2:2=16 3:1=10.5 4:0=23</t>
+  </si>
+  <si>
+    <t>0:5=700 1:4=125 2:3=50 3:2=21 4:1=23 5:0=55</t>
+  </si>
+  <si>
+    <t>1:5=450 2:4=150 3:3=60 4:2=40 5:1=60</t>
+  </si>
+  <si>
+    <t>2:5=400 5:2=100 负其他=160 平其他=350 胜其他=34</t>
   </si>
   <si>
     <t>0:0=9</t>
@@ -1793,33 +1796,30 @@
     <t>2:5=120 5:2=700 负其他=45 平其他=450 胜其他=250</t>
   </si>
   <si>
-    <t>0:0=8.5</t>
-  </si>
-  <si>
-    <t>0:1=8 1:0=5.5</t>
-  </si>
-  <si>
-    <t>0:2=21 1:1=6.5 2:0=8.5</t>
-  </si>
-  <si>
-    <t>0:3=55 1:2=12 2:1=7.75 3:0=18</t>
-  </si>
-  <si>
-    <t>0:4=200 1:3=40 2:2=18 3:1=18 4:0=55</t>
-  </si>
-  <si>
-    <t>0:5=600 1:4=150 2:3=50 3:2=30 4:1=45 5:0=150</t>
-  </si>
-  <si>
-    <t>1:5=400 2:4=200 3:3=100 4:2=90 5:1=120</t>
-  </si>
-  <si>
-    <t>2:5=600 5:2=250 负其他=250 平其他=700 胜其他=90</t>
-  </si>
-  <si>
     <t>0:0=8</t>
   </si>
   <si>
+    <t>0:1=7.5 1:0=5.5</t>
+  </si>
+  <si>
+    <t>0:2=18 1:1=6.15 2:0=8.5</t>
+  </si>
+  <si>
+    <t>0:3=55 1:2=12 2:1=7.75 3:0=20</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=40 2:2=18 3:1=21 4:0=60</t>
+  </si>
+  <si>
+    <t>0:5=600 1:4=150 2:3=50 3:2=35 4:1=55 5:0=175</t>
+  </si>
+  <si>
+    <t>1:5=400 2:4=200 3:3=100 4:2=100 5:1=175</t>
+  </si>
+  <si>
+    <t>2:5=600 5:2=300 负其他=250 平其他=700 胜其他=125</t>
+  </si>
+  <si>
     <t>0:1=10 1:0=5.75</t>
   </si>
   <si>
@@ -1985,7 +1985,7 @@
     <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-06T17:49:45+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-06T18:11:35+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -8975,7 +8975,7 @@
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O12" t="s">
         <v>21</v>
@@ -9007,13 +9007,13 @@
         <v>21</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L13" t="s">
         <v>21</v>
@@ -9057,7 +9057,7 @@
         <v>463</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>465</v>
@@ -9069,7 +9069,7 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O14" t="s">
         <v>21</v>
@@ -9101,13 +9101,13 @@
         <v>21</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>473</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L15" t="s">
         <v>21</v>
@@ -9116,7 +9116,7 @@
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O15" t="s">
         <v>21</v>
@@ -9148,13 +9148,13 @@
         <v>21</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L16" t="s">
         <v>21</v>
@@ -9163,7 +9163,7 @@
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
@@ -9195,14 +9195,14 @@
         <v>21</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="L17" t="s">
         <v>21</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
@@ -9227,7 +9227,7 @@
         <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E18" t="s">
         <v>410</v>
@@ -9245,10 +9245,10 @@
         <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L18" t="s">
         <v>21</v>
@@ -9257,7 +9257,7 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
@@ -9280,7 +9280,7 @@
         <v>329</v>
       </c>
       <c r="F19" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>55</v>
@@ -9289,13 +9289,13 @@
         <v>21</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L19" t="s">
         <v>21</v>
@@ -9321,13 +9321,13 @@
         <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E20" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F20" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>55</v>
@@ -9336,13 +9336,13 @@
         <v>21</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
@@ -9351,7 +9351,7 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="O20" t="s">
         <v>21</v>
@@ -9387,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -9396,31 +9396,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -9494,7 +9494,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -9511,7 +9511,7 @@
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F4" s="12">
         <v>3.2</v>
@@ -9535,7 +9535,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -9576,7 +9576,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -9617,7 +9617,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -9658,7 +9658,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -9675,7 +9675,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -9699,7 +9699,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -9716,7 +9716,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -9740,7 +9740,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -9814,7 +9814,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -9831,7 +9831,7 @@
         <v>248</v>
       </c>
       <c r="E12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F12" s="12">
         <v>4.35</v>
@@ -9855,7 +9855,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -9896,7 +9896,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -9937,7 +9937,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -9978,7 +9978,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -9995,7 +9995,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -10019,7 +10019,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -10036,7 +10036,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -10060,7 +10060,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -10134,7 +10134,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -10151,7 +10151,7 @@
         <v>260</v>
       </c>
       <c r="E20" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F20" s="12">
         <v>4.2</v>
@@ -10175,7 +10175,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -10216,7 +10216,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -10257,7 +10257,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -10298,7 +10298,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -10315,7 +10315,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -10339,7 +10339,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -10356,7 +10356,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -10380,7 +10380,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -10454,7 +10454,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -10471,7 +10471,7 @@
         <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F28" s="12">
         <v>4.4</v>
@@ -10495,7 +10495,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -10536,7 +10536,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -10577,7 +10577,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -10618,7 +10618,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -10635,7 +10635,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -10659,7 +10659,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -10676,7 +10676,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -10700,7 +10700,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -10774,7 +10774,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -10791,7 +10791,7 @@
         <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F36" s="12">
         <v>3.2</v>
@@ -10815,7 +10815,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -10856,7 +10856,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -10897,7 +10897,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -10938,7 +10938,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -10955,7 +10955,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -10979,7 +10979,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -10996,7 +10996,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -11020,7 +11020,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -11094,7 +11094,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -11111,7 +11111,7 @@
         <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F44" s="12">
         <v>3.8</v>
@@ -11135,7 +11135,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -11176,7 +11176,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -11217,7 +11217,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -11258,7 +11258,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -11275,7 +11275,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -11299,7 +11299,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -11316,7 +11316,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -11340,7 +11340,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -11414,7 +11414,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -11431,7 +11431,7 @@
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F52" s="12">
         <v>3.3</v>
@@ -11455,7 +11455,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -11496,7 +11496,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -11537,7 +11537,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -11578,7 +11578,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -11595,7 +11595,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -11619,7 +11619,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -11636,7 +11636,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -11660,7 +11660,7 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11680,11 +11680,11 @@
         <v>442</v>
       </c>
       <c r="F58" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="10">
-        <v>0.774</v>
+        <v>-0.001</v>
       </c>
       <c r="I58" s="11"/>
       <c r="J58" s="8"/>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -11713,28 +11713,28 @@
         <v>434</v>
       </c>
       <c r="F59" s="12">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="G59" s="13">
-        <v>5.054</v>
+        <v>5.44</v>
       </c>
       <c r="H59" s="14">
-        <v>0.746</v>
+        <v>0.86</v>
       </c>
       <c r="I59" s="15">
-        <v>14.8</v>
+        <v>15.8</v>
       </c>
       <c r="J59" s="12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="K59" s="16">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="L59" s="15">
         <v>-49.6</v>
       </c>
       <c r="M59" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -11751,31 +11751,31 @@
         <v>452</v>
       </c>
       <c r="E60" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F60" s="12">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G60" s="13">
-        <v>3.303</v>
+        <v>3.359</v>
       </c>
       <c r="H60" s="14">
-        <v>0.397</v>
+        <v>0.741</v>
       </c>
       <c r="I60" s="15">
-        <v>12</v>
+        <v>22.1</v>
       </c>
       <c r="J60" s="12">
-        <v>14.683</v>
+        <v>16.35</v>
       </c>
       <c r="K60" s="16">
-        <v>-10.983</v>
+        <v>-12.25</v>
       </c>
       <c r="L60" s="15">
-        <v>-74.8</v>
+        <v>-74.9</v>
       </c>
       <c r="M60" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -11798,25 +11798,25 @@
         <v>3.35</v>
       </c>
       <c r="G61" s="13">
-        <v>3.161</v>
+        <v>3.167</v>
       </c>
       <c r="H61" s="14">
-        <v>0.189</v>
+        <v>0.183</v>
       </c>
       <c r="I61" s="15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J61" s="12">
-        <v>28.375</v>
+        <v>28.5</v>
       </c>
       <c r="K61" s="16">
-        <v>-25.025</v>
+        <v>-25.15</v>
       </c>
       <c r="L61" s="15">
         <v>-88.2</v>
       </c>
       <c r="M61" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -11836,28 +11836,28 @@
         <v>439</v>
       </c>
       <c r="F62" s="12">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="G62" s="13">
-        <v>4.6</v>
+        <v>4.421</v>
       </c>
       <c r="H62" s="14">
-        <v>0.55</v>
+        <v>0.579</v>
       </c>
       <c r="I62" s="15">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="J62" s="12">
-        <v>70.4</v>
+        <v>59.9</v>
       </c>
       <c r="K62" s="16">
-        <v>-65.25</v>
+        <v>-54.9</v>
       </c>
       <c r="L62" s="15">
-        <v>-92.7</v>
+        <v>-91.6</v>
       </c>
       <c r="M62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -11877,28 +11877,28 @@
         <v>431</v>
       </c>
       <c r="F63" s="12">
-        <v>9.25</v>
+        <v>8.25</v>
       </c>
       <c r="G63" s="13">
-        <v>7.516</v>
+        <v>7.209</v>
       </c>
       <c r="H63" s="14">
-        <v>1.734</v>
+        <v>1.041</v>
       </c>
       <c r="I63" s="15">
-        <v>23.1</v>
+        <v>14.4</v>
       </c>
       <c r="J63" s="12">
-        <v>183.5</v>
+        <v>162.333</v>
       </c>
       <c r="K63" s="16">
-        <v>-174.25</v>
+        <v>-154.083</v>
       </c>
       <c r="L63" s="15">
-        <v>-95</v>
+        <v>-94.9</v>
       </c>
       <c r="M63" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -11915,31 +11915,31 @@
         <v>452</v>
       </c>
       <c r="E64" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F64" s="12">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="G64" s="13">
-        <v>16.221</v>
+        <v>14.876</v>
       </c>
       <c r="H64" s="14">
-        <v>2.279</v>
+        <v>0.124</v>
       </c>
       <c r="I64" s="15">
-        <v>14.1</v>
+        <v>0.8</v>
       </c>
       <c r="J64" s="12">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="K64" s="16">
-        <v>-161.5</v>
+        <v>-137</v>
       </c>
       <c r="L64" s="15">
-        <v>-89.7</v>
+        <v>-90.1</v>
       </c>
       <c r="M64" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -11956,31 +11956,31 @@
         <v>452</v>
       </c>
       <c r="E65" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F65" s="12">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G65" s="13">
-        <v>22.723</v>
-      </c>
-      <c r="H65" s="14">
-        <v>2.277</v>
+        <v>19.601</v>
+      </c>
+      <c r="H65" s="17">
+        <v>-1.601</v>
       </c>
       <c r="I65" s="15">
-        <v>10</v>
+        <v>-8.2</v>
       </c>
       <c r="J65" s="12">
-        <v>232.4</v>
+        <v>208.8</v>
       </c>
       <c r="K65" s="16">
-        <v>-207.4</v>
+        <v>-190.8</v>
       </c>
       <c r="L65" s="15">
-        <v>-89.2</v>
+        <v>-91.4</v>
       </c>
       <c r="M65" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -12054,7 +12054,7 @@
         <v>-51.7</v>
       </c>
       <c r="M67" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -12071,7 +12071,7 @@
         <v>458</v>
       </c>
       <c r="E68" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F68" s="12">
         <v>3.1</v>
@@ -12095,7 +12095,7 @@
         <v>-73.4</v>
       </c>
       <c r="M68" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -12136,7 +12136,7 @@
         <v>-83.2</v>
       </c>
       <c r="M69" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -12177,7 +12177,7 @@
         <v>-88.2</v>
       </c>
       <c r="M70" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -12218,7 +12218,7 @@
         <v>-86.5</v>
       </c>
       <c r="M71" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -12235,7 +12235,7 @@
         <v>458</v>
       </c>
       <c r="E72" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F72" s="12">
         <v>27</v>
@@ -12259,7 +12259,7 @@
         <v>-80.7</v>
       </c>
       <c r="M72" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -12276,7 +12276,7 @@
         <v>458</v>
       </c>
       <c r="E73" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F73" s="12">
         <v>45</v>
@@ -12300,7 +12300,7 @@
         <v>-82.9</v>
       </c>
       <c r="M73" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -12374,7 +12374,7 @@
         <v>-48.3</v>
       </c>
       <c r="M75" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -12391,7 +12391,7 @@
         <v>301</v>
       </c>
       <c r="E76" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F76" s="12">
         <v>3.15</v>
@@ -12415,7 +12415,7 @@
         <v>-68.4</v>
       </c>
       <c r="M76" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -12456,7 +12456,7 @@
         <v>-80.5</v>
       </c>
       <c r="M77" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -12497,7 +12497,7 @@
         <v>-86.5</v>
       </c>
       <c r="M78" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -12538,7 +12538,7 @@
         <v>-87.7</v>
       </c>
       <c r="M79" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -12555,7 +12555,7 @@
         <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F80" s="12">
         <v>38</v>
@@ -12579,7 +12579,7 @@
         <v>-75.9</v>
       </c>
       <c r="M80" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -12596,7 +12596,7 @@
         <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F81" s="12">
         <v>70</v>
@@ -12620,7 +12620,7 @@
         <v>-78.5</v>
       </c>
       <c r="M81" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -12694,7 +12694,7 @@
         <v>-50.9</v>
       </c>
       <c r="M83" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -12711,7 +12711,7 @@
         <v>305</v>
       </c>
       <c r="E84" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F84" s="12">
         <v>3.35</v>
@@ -12735,7 +12735,7 @@
         <v>-76.5</v>
       </c>
       <c r="M84" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -12776,7 +12776,7 @@
         <v>-87.5</v>
       </c>
       <c r="M85" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -12817,7 +12817,7 @@
         <v>-92.7</v>
       </c>
       <c r="M86" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -12858,7 +12858,7 @@
         <v>-94.2</v>
       </c>
       <c r="M87" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -12875,7 +12875,7 @@
         <v>305</v>
       </c>
       <c r="E88" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F88" s="12">
         <v>24</v>
@@ -12899,7 +12899,7 @@
         <v>-89.6</v>
       </c>
       <c r="M88" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -12916,7 +12916,7 @@
         <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F89" s="12">
         <v>35</v>
@@ -12940,7 +12940,7 @@
         <v>-88.8</v>
       </c>
       <c r="M89" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12960,20 +12960,20 @@
         <v>442</v>
       </c>
       <c r="F90" s="8">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="10">
-        <v>0.728</v>
+        <v>1.397</v>
       </c>
       <c r="I90" s="11"/>
       <c r="J90" s="8"/>
       <c r="K90" s="10">
-        <v>-3.007</v>
+        <v>-2.814</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -12993,28 +12993,28 @@
         <v>434</v>
       </c>
       <c r="F91" s="12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G91" s="13">
-        <v>3.259</v>
+        <v>3.173</v>
       </c>
       <c r="H91" s="14">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="I91" s="15">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J91" s="12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="K91" s="16">
-        <v>-3.45</v>
+        <v>-3.3</v>
       </c>
       <c r="L91" s="15">
-        <v>-51.1</v>
+        <v>-50.8</v>
       </c>
       <c r="M91" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -13031,31 +13031,31 @@
         <v>308</v>
       </c>
       <c r="E92" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F92" s="12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G92" s="13">
-        <v>3.134</v>
+        <v>2.978</v>
       </c>
       <c r="H92" s="14">
-        <v>0.166</v>
+        <v>0.422</v>
       </c>
       <c r="I92" s="15">
-        <v>5.3</v>
+        <v>14.2</v>
       </c>
       <c r="J92" s="12">
-        <v>12</v>
+        <v>10.883</v>
       </c>
       <c r="K92" s="16">
-        <v>-8.7</v>
+        <v>-7.483</v>
       </c>
       <c r="L92" s="15">
-        <v>-72.5</v>
+        <v>-68.8</v>
       </c>
       <c r="M92" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -13078,25 +13078,25 @@
         <v>3.8</v>
       </c>
       <c r="G93" s="13">
-        <v>3.495</v>
+        <v>3.564</v>
       </c>
       <c r="H93" s="14">
-        <v>0.305</v>
+        <v>0.236</v>
       </c>
       <c r="I93" s="15">
-        <v>8.7</v>
+        <v>6.6</v>
       </c>
       <c r="J93" s="12">
-        <v>23.188</v>
+        <v>23.688</v>
       </c>
       <c r="K93" s="16">
-        <v>-19.388</v>
+        <v>-19.888</v>
       </c>
       <c r="L93" s="15">
-        <v>-83.6</v>
+        <v>-84</v>
       </c>
       <c r="M93" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -13116,28 +13116,28 @@
         <v>439</v>
       </c>
       <c r="F94" s="12">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="G94" s="13">
-        <v>6.278</v>
+        <v>6.674</v>
       </c>
       <c r="H94" s="14">
-        <v>1.722</v>
+        <v>1.576</v>
       </c>
       <c r="I94" s="15">
-        <v>27.4</v>
+        <v>23.6</v>
       </c>
       <c r="J94" s="12">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="K94" s="16">
-        <v>-58.2</v>
+        <v>-59.55</v>
       </c>
       <c r="L94" s="15">
-        <v>-87.9</v>
+        <v>-87.8</v>
       </c>
       <c r="M94" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -13157,28 +13157,28 @@
         <v>431</v>
       </c>
       <c r="F95" s="12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="G95" s="13">
-        <v>11.043</v>
+        <v>12.376</v>
       </c>
       <c r="H95" s="14">
-        <v>7.457</v>
+        <v>6.624</v>
       </c>
       <c r="I95" s="15">
-        <v>67.5</v>
+        <v>53.5</v>
       </c>
       <c r="J95" s="12">
-        <v>170.833</v>
+        <v>177.5</v>
       </c>
       <c r="K95" s="16">
-        <v>-152.333</v>
+        <v>-158.5</v>
       </c>
       <c r="L95" s="15">
-        <v>-89.2</v>
+        <v>-89.3</v>
       </c>
       <c r="M95" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -13195,31 +13195,31 @@
         <v>308</v>
       </c>
       <c r="E96" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F96" s="12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G96" s="13">
-        <v>27.068</v>
+        <v>30.108</v>
       </c>
       <c r="H96" s="14">
-        <v>12.932</v>
+        <v>11.892</v>
       </c>
       <c r="I96" s="15">
-        <v>47.8</v>
+        <v>39.5</v>
       </c>
       <c r="J96" s="12">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="K96" s="16">
-        <v>-142</v>
+        <v>-153</v>
       </c>
       <c r="L96" s="15">
-        <v>-78</v>
+        <v>-78.5</v>
       </c>
       <c r="M96" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -13236,31 +13236,31 @@
         <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F97" s="12">
         <v>80</v>
       </c>
       <c r="G97" s="13">
-        <v>45.032</v>
+        <v>54.264</v>
       </c>
       <c r="H97" s="14">
-        <v>34.968</v>
+        <v>25.736</v>
       </c>
       <c r="I97" s="15">
-        <v>77.7</v>
+        <v>47.4</v>
       </c>
       <c r="J97" s="12">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="K97" s="16">
-        <v>-298</v>
+        <v>-315</v>
       </c>
       <c r="L97" s="15">
-        <v>-78.8</v>
+        <v>-79.7</v>
       </c>
       <c r="M97" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="4" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -13351,7 +13351,7 @@
         <v>293</v>
       </c>
       <c r="E100" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F100" s="12">
         <v>3.2</v>
@@ -13515,7 +13515,7 @@
         <v>293</v>
       </c>
       <c r="E104" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F104" s="12">
         <v>35</v>
@@ -13556,7 +13556,7 @@
         <v>293</v>
       </c>
       <c r="E105" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F105" s="12">
         <v>60</v>
@@ -13671,7 +13671,7 @@
         <v>315</v>
       </c>
       <c r="E108" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F108" s="12">
         <v>5.6</v>
@@ -13835,7 +13835,7 @@
         <v>315</v>
       </c>
       <c r="E112" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F112" s="12">
         <v>8.8</v>
@@ -13876,7 +13876,7 @@
         <v>315</v>
       </c>
       <c r="E113" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F113" s="12">
         <v>9</v>
@@ -13991,7 +13991,7 @@
         <v>323</v>
       </c>
       <c r="E116" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F116" s="12">
         <v>4.75</v>
@@ -14155,7 +14155,7 @@
         <v>323</v>
       </c>
       <c r="E120" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F120" s="12">
         <v>12</v>
@@ -14196,7 +14196,7 @@
         <v>323</v>
       </c>
       <c r="E121" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F121" s="12">
         <v>14</v>
@@ -14311,7 +14311,7 @@
         <v>319</v>
       </c>
       <c r="E124" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F124" s="12">
         <v>5.1</v>
@@ -14475,7 +14475,7 @@
         <v>319</v>
       </c>
       <c r="E128" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F128" s="12">
         <v>11</v>
@@ -14516,7 +14516,7 @@
         <v>319</v>
       </c>
       <c r="E129" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F129" s="12">
         <v>12</v>
@@ -14551,7 +14551,7 @@
         <v>408</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>410</v>
@@ -14584,7 +14584,7 @@
         <v>408</v>
       </c>
       <c r="C131" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D131" t="s">
         <v>410</v>
@@ -14625,13 +14625,13 @@
         <v>408</v>
       </c>
       <c r="C132" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D132" t="s">
         <v>410</v>
       </c>
       <c r="E132" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F132" s="12">
         <v>3.35</v>
@@ -14666,7 +14666,7 @@
         <v>408</v>
       </c>
       <c r="C133" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D133" t="s">
         <v>410</v>
@@ -14707,7 +14707,7 @@
         <v>408</v>
       </c>
       <c r="C134" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D134" t="s">
         <v>410</v>
@@ -14748,7 +14748,7 @@
         <v>408</v>
       </c>
       <c r="C135" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D135" t="s">
         <v>410</v>
@@ -14789,13 +14789,13 @@
         <v>408</v>
       </c>
       <c r="C136" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D136" t="s">
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F136" s="12">
         <v>20</v>
@@ -14830,13 +14830,13 @@
         <v>408</v>
       </c>
       <c r="C137" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D137" t="s">
         <v>410</v>
       </c>
       <c r="E137" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F137" s="12">
         <v>30</v>
@@ -14951,7 +14951,7 @@
         <v>329</v>
       </c>
       <c r="E140" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F140" s="12">
         <v>4.15</v>
@@ -15115,7 +15115,7 @@
         <v>329</v>
       </c>
       <c r="E144" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F144" s="12">
         <v>15.5</v>
@@ -15156,7 +15156,7 @@
         <v>329</v>
       </c>
       <c r="E145" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F145" s="12">
         <v>21</v>
@@ -15191,10 +15191,10 @@
         <v>411</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>442</v>
@@ -15224,10 +15224,10 @@
         <v>411</v>
       </c>
       <c r="C147" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D147" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E147" t="s">
         <v>434</v>
@@ -15265,13 +15265,13 @@
         <v>411</v>
       </c>
       <c r="C148" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D148" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E148" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F148" s="12">
         <v>4.6</v>
@@ -15306,10 +15306,10 @@
         <v>411</v>
       </c>
       <c r="C149" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D149" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E149" t="s">
         <v>423</v>
@@ -15347,10 +15347,10 @@
         <v>411</v>
       </c>
       <c r="C150" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D150" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E150" t="s">
         <v>439</v>
@@ -15388,10 +15388,10 @@
         <v>411</v>
       </c>
       <c r="C151" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D151" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E151" t="s">
         <v>431</v>
@@ -15429,13 +15429,13 @@
         <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D152" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E152" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -15470,13 +15470,13 @@
         <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D153" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E153" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F153" s="12">
         <v>13</v>
@@ -15713,7 +15713,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>684</v>
@@ -15829,7 +15829,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>21</v>
@@ -15858,7 +15858,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -16022,7 +16022,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -16389,7 +16389,7 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>713</v>
@@ -16401,7 +16401,7 @@
         <v>434</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>423</v>
@@ -16699,10 +16699,10 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>727</v>
@@ -16738,7 +16738,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>442</v>
@@ -16747,7 +16747,7 @@
         <v>434</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>423</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="775">
   <si>
     <t>日期</t>
   </si>
@@ -1382,18 +1382,24 @@
     <t>10-06 19:00</t>
   </si>
   <si>
+    <t>2球</t>
+  </si>
+  <si>
     <t>7+球 @18</t>
   </si>
   <si>
-    <t>0球 @17 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.35 ⚡</t>
+    <t>0球 @17</t>
+  </si>
+  <si>
+    <t>3球 @3.35</t>
   </si>
   <si>
     <t>10-06 18:11</t>
   </si>
   <si>
+    <t>10-07 11:00</t>
+  </si>
+  <si>
     <t>塔吉克</t>
   </si>
   <si>
@@ -1403,7 +1409,7 @@
     <t>1球 @3.95</t>
   </si>
   <si>
-    <t>3球 @4.05 ⚡</t>
+    <t>3球 @4.05</t>
   </si>
   <si>
     <t>10-06 22:00</t>
@@ -1412,10 +1418,10 @@
     <t>1球 @3.75</t>
   </si>
   <si>
-    <t>3球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @7 ⚡</t>
+    <t>3球 @4.1</t>
+  </si>
+  <si>
+    <t>4球 @7</t>
   </si>
   <si>
     <t>10-07 02:45</t>
@@ -1424,10 +1430,10 @@
     <t>2球 @3.35</t>
   </si>
   <si>
-    <t>1球 @4.85 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.55 ⚡</t>
+    <t>1球 @4.85</t>
+  </si>
+  <si>
+    <t>3球 @3.55</t>
   </si>
   <si>
     <t>10-06 17:00</t>
@@ -1436,13 +1442,13 @@
     <t>1球 @3.2</t>
   </si>
   <si>
-    <t>0球 @8 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @8.25 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @4 ⚡</t>
+    <t>0球 @8</t>
+  </si>
+  <si>
+    <t>4球 @8.25</t>
+  </si>
+  <si>
+    <t>3球 @4</t>
   </si>
   <si>
     <t>6球 @8.8</t>
@@ -1451,22 +1457,22 @@
     <t>4球 @4</t>
   </si>
   <si>
-    <t>1球 @8 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.65 ⚡</t>
+    <t>1球 @8</t>
+  </si>
+  <si>
+    <t>3球 @3.65</t>
   </si>
   <si>
     <t>6球 @11</t>
   </si>
   <si>
-    <t>1球 @8.25 ⚡</t>
+    <t>1球 @8.25</t>
   </si>
   <si>
     <t>摩尔多瓦</t>
   </si>
   <si>
-    <t>3球 @3.6 ⚡</t>
+    <t>3球 @3.6</t>
   </si>
   <si>
     <t>10-07 08:00</t>
@@ -1475,10 +1481,7 @@
     <t>3球 @3.45</t>
   </si>
   <si>
-    <t>1球 @6.25 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.45 ⚡</t>
+    <t>1球 @6.25</t>
   </si>
   <si>
     <t>芝加哥</t>
@@ -1493,7 +1496,7 @@
     <t>6球 @10</t>
   </si>
   <si>
-    <t>3球 @3.7 ⚡</t>
+    <t>3球 @3.7</t>
   </si>
   <si>
     <t>编号</t>
@@ -1532,9 +1535,6 @@
     <t>0:1=14 1:0=6</t>
   </si>
   <si>
-    <t>2球</t>
-  </si>
-  <si>
     <t>0:2=35 1:1=7 2:0=6.5</t>
   </si>
   <si>
@@ -1985,7 +1985,7 @@
     <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-06T18:11:35+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-07T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2000,19 +2000,25 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>2/7 = 28.6%</t>
+    <t>3/17 = 17.6%</t>
   </si>
   <si>
     <t>模型A 命中率（自修正）</t>
   </si>
   <si>
+    <t>4/17 = 23.5%</t>
+  </si>
+  <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
+    <t>6/17 = 35.3%</t>
+  </si>
+  <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-06 ~ 2026-10-06）</t>
+    <t>近 30 天窗口（2026-09-07 ~ 2026-10-07）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>
@@ -2033,7 +2039,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>5 场（另剔除爆冷 2 场）</t>
+    <t>14 场（另剔除爆冷 3 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -2066,19 +2072,46 @@
     <t>100% (1/1)</t>
   </si>
   <si>
+    <t>0% (0/2)</t>
+  </si>
+  <si>
+    <t>25% (1/4)</t>
+  </si>
+  <si>
+    <t>0% (0/4)</t>
+  </si>
+  <si>
     <t>0% (0/1)</t>
   </si>
   <si>
     <t>0% (0/3)</t>
   </si>
   <si>
-    <t>0% (0/2)</t>
-  </si>
-  <si>
     <t>50% (1/2)</t>
   </si>
   <si>
-    <t>0% (0/4)</t>
+    <t>20% (1/5)</t>
+  </si>
+  <si>
+    <t>29% (2/7)</t>
+  </si>
+  <si>
+    <t>50% (3/6)</t>
+  </si>
+  <si>
+    <t>33% (1/3)</t>
+  </si>
+  <si>
+    <t>33% (2/6)</t>
+  </si>
+  <si>
+    <t>0% (0/7)</t>
+  </si>
+  <si>
+    <t>0% (0/8)</t>
+  </si>
+  <si>
+    <t>0% (0/12)</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -2195,7 +2228,7 @@
     <t>010</t>
   </si>
   <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-05，警戒线 30 次）</t>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-06，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -2210,7 +2243,7 @@
     <t>历史次数</t>
   </si>
   <si>
-    <t>2026-08-24</t>
+    <t>（当前没有项目超过警戒线）</t>
   </si>
   <si>
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
@@ -2372,7 +2405,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2387,11 +2420,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDEBD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2436,18 +2464,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8816,28 +8844,28 @@
         <v>55</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
+        <v>457</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -8854,37 +8882,37 @@
         <v>200</v>
       </c>
       <c r="E10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>21</v>
+        <v>463</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -8904,34 +8932,34 @@
         <v>301</v>
       </c>
       <c r="F11" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
+        <v>467</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="N11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O11" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -8951,34 +8979,34 @@
         <v>305</v>
       </c>
       <c r="F12" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>21</v>
+        <v>471</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O12" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -8998,34 +9026,34 @@
         <v>308</v>
       </c>
       <c r="F13" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>21</v>
+        <v>475</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O13" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -9045,34 +9073,34 @@
         <v>293</v>
       </c>
       <c r="F14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="L14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" t="s">
-        <v>21</v>
+        <v>467</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N14" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O14" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -9092,34 +9120,34 @@
         <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G15" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>21</v>
+        <v>476</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="N15" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -9139,34 +9167,34 @@
         <v>323</v>
       </c>
       <c r="F16" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
+        <v>480</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="N16" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -9186,34 +9214,34 @@
         <v>319</v>
       </c>
       <c r="F17" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G17" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="s">
-        <v>21</v>
+      <c r="L17" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="N17" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O17" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -9227,40 +9255,40 @@
         <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E18" t="s">
         <v>410</v>
       </c>
       <c r="F18" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
+        <v>484</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O18" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -9280,7 +9308,7 @@
         <v>329</v>
       </c>
       <c r="F19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>55</v>
@@ -9289,10 +9317,10 @@
         <v>21</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>486</v>
@@ -9304,7 +9332,7 @@
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O19" t="s">
         <v>21</v>
@@ -9321,13 +9349,13 @@
         <v>184</v>
       </c>
       <c r="D20" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E20" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F20" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>55</v>
@@ -9336,13 +9364,13 @@
         <v>21</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
@@ -9351,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O20" t="s">
         <v>21</v>
@@ -9387,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -9396,31 +9424,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9453,7 +9481,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -9494,7 +9522,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -9511,7 +9539,7 @@
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F4" s="12">
         <v>3.2</v>
@@ -9831,7 +9859,7 @@
         <v>248</v>
       </c>
       <c r="E12" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F12" s="12">
         <v>4.35</v>
@@ -10151,7 +10179,7 @@
         <v>260</v>
       </c>
       <c r="E20" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F20" s="12">
         <v>4.2</v>
@@ -10471,7 +10499,7 @@
         <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F28" s="12">
         <v>4.4</v>
@@ -10791,7 +10819,7 @@
         <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F36" s="12">
         <v>3.2</v>
@@ -11111,7 +11139,7 @@
         <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F44" s="12">
         <v>3.8</v>
@@ -11431,7 +11459,7 @@
         <v>254</v>
       </c>
       <c r="E52" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F52" s="12">
         <v>3.3</v>
@@ -11751,7 +11779,7 @@
         <v>452</v>
       </c>
       <c r="E60" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F60" s="12">
         <v>4.1</v>
@@ -11994,7 +12022,7 @@
         <v>200</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>442</v>
@@ -12027,7 +12055,7 @@
         <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E67" t="s">
         <v>434</v>
@@ -12068,10 +12096,10 @@
         <v>200</v>
       </c>
       <c r="D68" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E68" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F68" s="12">
         <v>3.1</v>
@@ -12109,7 +12137,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E69" t="s">
         <v>423</v>
@@ -12150,7 +12178,7 @@
         <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E70" t="s">
         <v>439</v>
@@ -12191,7 +12219,7 @@
         <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E71" t="s">
         <v>431</v>
@@ -12232,7 +12260,7 @@
         <v>200</v>
       </c>
       <c r="D72" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E72" t="s">
         <v>509</v>
@@ -12273,7 +12301,7 @@
         <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E73" t="s">
         <v>511</v>
@@ -12391,7 +12419,7 @@
         <v>301</v>
       </c>
       <c r="E76" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F76" s="12">
         <v>3.15</v>
@@ -12711,7 +12739,7 @@
         <v>305</v>
       </c>
       <c r="E84" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F84" s="12">
         <v>3.35</v>
@@ -13031,7 +13059,7 @@
         <v>308</v>
       </c>
       <c r="E92" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F92" s="12">
         <v>3.4</v>
@@ -13351,7 +13379,7 @@
         <v>293</v>
       </c>
       <c r="E100" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F100" s="12">
         <v>3.2</v>
@@ -13671,7 +13699,7 @@
         <v>315</v>
       </c>
       <c r="E108" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F108" s="12">
         <v>5.6</v>
@@ -13991,7 +14019,7 @@
         <v>323</v>
       </c>
       <c r="E116" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F116" s="12">
         <v>4.75</v>
@@ -14311,7 +14339,7 @@
         <v>319</v>
       </c>
       <c r="E124" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F124" s="12">
         <v>5.1</v>
@@ -14551,7 +14579,7 @@
         <v>408</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>410</v>
@@ -14584,7 +14612,7 @@
         <v>408</v>
       </c>
       <c r="C131" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D131" t="s">
         <v>410</v>
@@ -14625,13 +14653,13 @@
         <v>408</v>
       </c>
       <c r="C132" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D132" t="s">
         <v>410</v>
       </c>
       <c r="E132" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F132" s="12">
         <v>3.35</v>
@@ -14666,7 +14694,7 @@
         <v>408</v>
       </c>
       <c r="C133" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D133" t="s">
         <v>410</v>
@@ -14707,7 +14735,7 @@
         <v>408</v>
       </c>
       <c r="C134" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D134" t="s">
         <v>410</v>
@@ -14748,7 +14776,7 @@
         <v>408</v>
       </c>
       <c r="C135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D135" t="s">
         <v>410</v>
@@ -14789,7 +14817,7 @@
         <v>408</v>
       </c>
       <c r="C136" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D136" t="s">
         <v>410</v>
@@ -14830,7 +14858,7 @@
         <v>408</v>
       </c>
       <c r="C137" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D137" t="s">
         <v>410</v>
@@ -14951,7 +14979,7 @@
         <v>329</v>
       </c>
       <c r="E140" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F140" s="12">
         <v>4.15</v>
@@ -15191,10 +15219,10 @@
         <v>411</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>442</v>
@@ -15224,10 +15252,10 @@
         <v>411</v>
       </c>
       <c r="C147" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D147" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E147" t="s">
         <v>434</v>
@@ -15265,13 +15293,13 @@
         <v>411</v>
       </c>
       <c r="C148" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D148" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E148" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F148" s="12">
         <v>4.6</v>
@@ -15306,10 +15334,10 @@
         <v>411</v>
       </c>
       <c r="C149" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D149" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E149" t="s">
         <v>423</v>
@@ -15347,10 +15375,10 @@
         <v>411</v>
       </c>
       <c r="C150" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D150" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E150" t="s">
         <v>439</v>
@@ -15388,10 +15416,10 @@
         <v>411</v>
       </c>
       <c r="C151" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D151" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E151" t="s">
         <v>431</v>
@@ -15429,10 +15457,10 @@
         <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D152" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E152" t="s">
         <v>509</v>
@@ -15470,10 +15498,10 @@
         <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D153" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E153" t="s">
         <v>511</v>
@@ -15534,7 +15562,7 @@
         <v>657</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -15542,7 +15570,7 @@
         <v>658</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -15558,38 +15586,38 @@
         <v>661</v>
       </c>
       <c r="B7" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B8" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B13" t="s">
         <v>660</v>
@@ -15597,60 +15625,60 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B14" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B15" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -15658,7 +15686,7 @@
         <v>442</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -15666,34 +15694,34 @@
       <c r="D20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>21</v>
+      <c r="E20" s="21" t="s">
+        <v>684</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>683</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>21</v>
+        <v>686</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>684</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>21</v>
+      <c r="B21" s="21" t="s">
+        <v>685</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="E21" s="21" t="s">
         <v>685</v>
@@ -15701,8 +15729,8 @@
       <c r="F21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>21</v>
+      <c r="G21" s="21" t="s">
+        <v>687</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>21</v>
@@ -15713,22 +15741,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="B22" s="21" t="s">
+        <v>686</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>688</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>690</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>684</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>683</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>21</v>
@@ -15748,13 +15776,13 @@
         <v>21</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>683</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>681</v>
+        <v>691</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>692</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -15774,19 +15802,19 @@
         <v>439</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>685</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>21</v>
+        <v>693</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>687</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>687</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -15811,17 +15839,17 @@
       <c r="D25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>21</v>
+      <c r="E25" s="21" t="s">
+        <v>687</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -15831,8 +15859,8 @@
       <c r="A26" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>21</v>
+      <c r="B26" s="21" t="s">
+        <v>684</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
@@ -15843,17 +15871,17 @@
       <c r="E26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>21</v>
+      <c r="F26" s="21" t="s">
+        <v>687</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -15879,15 +15907,15 @@
         <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -15898,7 +15926,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -15912,109 +15940,109 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="E5">
-        <v>2350</v>
+        <v>3150</v>
       </c>
       <c r="F5" s="7">
-        <v>1650</v>
-      </c>
-      <c r="G5" s="22">
-        <v>2.357142857142857</v>
+        <v>1450</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0.8529411764705882</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="E6">
-        <v>1170</v>
-      </c>
-      <c r="F6" s="7">
-        <v>470</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.6714285714285714</v>
+        <v>1565</v>
+      </c>
+      <c r="F6" s="24">
+        <v>-135</v>
+      </c>
+      <c r="G6" s="23">
+        <v>-0.07941176470588235</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="E7">
-        <v>1220</v>
+        <v>3050</v>
       </c>
       <c r="F7" s="7">
-        <v>520</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.7428571428571429</v>
+        <v>1350</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0.7941176470588235</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -16022,7 +16050,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -16034,25 +16062,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -16080,16 +16108,16 @@
       <c r="H11" t="s">
         <v>423</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="25">
         <v>-100</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="26">
         <v>-100</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="27">
         <v>-100</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="27">
         <v>-100</v>
       </c>
     </row>
@@ -16118,16 +16146,16 @@
       <c r="H12" t="s">
         <v>431</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="25">
         <v>-100</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="26">
         <v>-200</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="27">
         <v>-100</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="27">
         <v>-100</v>
       </c>
     </row>
@@ -16156,16 +16184,16 @@
       <c r="H13" t="s">
         <v>434</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="25">
         <v>-100</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="26">
         <v>-300</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="27">
         <v>-100</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="27">
         <v>580</v>
       </c>
     </row>
@@ -16194,16 +16222,16 @@
       <c r="H14" t="s">
         <v>439</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="25">
         <v>-100</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="26">
         <v>-400</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="27">
         <v>320</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="27">
         <v>-100</v>
       </c>
     </row>
@@ -16232,16 +16260,16 @@
       <c r="H15" t="s">
         <v>442</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="28">
         <v>650</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="29">
         <v>250</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="27">
         <v>650</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="27">
         <v>-100</v>
       </c>
     </row>
@@ -16270,16 +16298,16 @@
       <c r="H16" t="s">
         <v>442</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="28">
         <v>1500</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="29">
         <v>1750</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="27">
         <v>-100</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="27">
         <v>-100</v>
       </c>
     </row>
@@ -16308,68 +16336,471 @@
       <c r="H17" t="s">
         <v>434</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="25">
         <v>-100</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="29">
         <v>1650</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="27">
         <v>-100</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="27">
         <v>440</v>
       </c>
     </row>
-    <row r="19" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>451</v>
+      </c>
+      <c r="B18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" t="s">
+        <v>452</v>
+      </c>
+      <c r="F18" t="s">
+        <v>442</v>
+      </c>
+      <c r="G18" s="12">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
+        <v>454</v>
+      </c>
+      <c r="I18" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J18" s="29">
+        <v>1550</v>
+      </c>
+      <c r="K18" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>451</v>
+      </c>
+      <c r="B19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" t="s">
+        <v>460</v>
+      </c>
+      <c r="F19" t="s">
+        <v>423</v>
+      </c>
+      <c r="G19" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="H19" t="s">
+        <v>434</v>
+      </c>
+      <c r="I19" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J19" s="29">
+        <v>1450</v>
+      </c>
+      <c r="K19" s="27">
+        <v>295</v>
+      </c>
+      <c r="L19" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" t="s">
+        <v>302</v>
+      </c>
+      <c r="E20" t="s">
+        <v>301</v>
+      </c>
+      <c r="F20" t="s">
+        <v>423</v>
+      </c>
+      <c r="G20" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>439</v>
+      </c>
+      <c r="I20" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="29">
+        <v>1350</v>
+      </c>
+      <c r="K20" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="27">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>451</v>
+      </c>
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" t="s">
+        <v>306</v>
+      </c>
+      <c r="E21" t="s">
+        <v>305</v>
+      </c>
+      <c r="F21" t="s">
+        <v>434</v>
+      </c>
+      <c r="G21" s="12">
+        <v>4.85</v>
+      </c>
+      <c r="H21" t="s">
+        <v>442</v>
+      </c>
+      <c r="I21" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J21" s="29">
+        <v>1250</v>
+      </c>
+      <c r="K21" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>451</v>
+      </c>
+      <c r="B22" t="s">
+        <v>397</v>
+      </c>
+      <c r="C22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" t="s">
+        <v>309</v>
+      </c>
+      <c r="E22" t="s">
+        <v>308</v>
+      </c>
+      <c r="F22" t="s">
+        <v>442</v>
+      </c>
+      <c r="G22" s="12">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>454</v>
+      </c>
+      <c r="I22" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J22" s="29">
+        <v>1150</v>
+      </c>
+      <c r="K22" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L22" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>451</v>
+      </c>
+      <c r="B23" t="s">
+        <v>399</v>
+      </c>
+      <c r="C23" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" t="s">
+        <v>294</v>
+      </c>
+      <c r="E23" t="s">
+        <v>293</v>
+      </c>
+      <c r="F23" t="s">
+        <v>423</v>
+      </c>
+      <c r="G23" s="12">
+        <v>4</v>
+      </c>
+      <c r="H23" t="s">
+        <v>423</v>
+      </c>
+      <c r="I23" s="28">
+        <v>300</v>
+      </c>
+      <c r="J23" s="29">
+        <v>1450</v>
+      </c>
+      <c r="K23" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>451</v>
+      </c>
+      <c r="B24" t="s">
+        <v>402</v>
+      </c>
+      <c r="C24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" t="s">
+        <v>322</v>
+      </c>
+      <c r="E24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" t="s">
+        <v>423</v>
+      </c>
+      <c r="G24" s="12">
+        <v>4</v>
+      </c>
+      <c r="H24" t="s">
+        <v>423</v>
+      </c>
+      <c r="I24" s="28">
+        <v>300</v>
+      </c>
+      <c r="J24" s="29">
+        <v>1750</v>
+      </c>
+      <c r="K24" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L24" s="27">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>451</v>
+      </c>
+      <c r="B25" t="s">
+        <v>405</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>316</v>
+      </c>
+      <c r="E25" t="s">
+        <v>323</v>
+      </c>
+      <c r="F25" t="s">
+        <v>434</v>
+      </c>
+      <c r="G25" s="12">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>423</v>
+      </c>
+      <c r="I25" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J25" s="29">
+        <v>1650</v>
+      </c>
+      <c r="K25" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L25" s="27">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>451</v>
+      </c>
+      <c r="B26" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" t="s">
+        <v>320</v>
+      </c>
+      <c r="E26" t="s">
+        <v>319</v>
+      </c>
+      <c r="F26" t="s">
+        <v>434</v>
+      </c>
+      <c r="G26" s="12">
+        <v>8.25</v>
+      </c>
+      <c r="H26" t="s">
+        <v>423</v>
+      </c>
+      <c r="I26" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J26" s="29">
+        <v>1550</v>
+      </c>
+      <c r="K26" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="27">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>451</v>
+      </c>
+      <c r="B27" t="s">
+        <v>408</v>
+      </c>
+      <c r="C27" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" t="s">
+        <v>483</v>
+      </c>
+      <c r="E27" t="s">
+        <v>410</v>
+      </c>
+      <c r="F27" t="s">
+        <v>423</v>
+      </c>
+      <c r="G27" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H27" t="s">
+        <v>439</v>
+      </c>
+      <c r="I27" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J27" s="29">
+        <v>1450</v>
+      </c>
+      <c r="K27" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D30" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>421</v>
       </c>
-      <c r="B21">
+      <c r="B31">
         <v>7</v>
       </c>
-      <c r="C21">
+      <c r="C31">
         <v>2</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D31" s="27">
         <v>1650</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E31" s="27">
         <v>1650</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F31" s="27">
         <v>470</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G31" s="27">
         <v>520</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>451</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" s="27">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="27">
+        <v>1450</v>
+      </c>
+      <c r="F32" s="27">
+        <v>-135</v>
+      </c>
+      <c r="G32" s="27">
+        <v>1350</v>
       </c>
     </row>
   </sheetData>
@@ -16389,10 +16820,10 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>442</v>
@@ -16401,7 +16832,7 @@
         <v>434</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>423</v>
@@ -16410,15 +16841,15 @@
         <v>439</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="B2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -16427,7 +16858,7 @@
         <v>57</v>
       </c>
       <c r="E2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2">
         <v>72</v>
@@ -16441,16 +16872,16 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="B3">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C3">
         <v>26</v>
       </c>
       <c r="D3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3">
         <v>88</v>
@@ -16467,10 +16898,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="B4">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -16485,7 +16916,7 @@
         <v>69</v>
       </c>
       <c r="G4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4">
         <v>67</v>
@@ -16493,13 +16924,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="B5">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>52</v>
@@ -16519,10 +16950,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="B6">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -16531,7 +16962,7 @@
         <v>60</v>
       </c>
       <c r="E6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6">
         <v>67</v>
@@ -16545,10 +16976,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="B7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7">
         <v>18</v>
@@ -16560,7 +16991,7 @@
         <v>64</v>
       </c>
       <c r="F7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7">
         <v>53</v>
@@ -16571,10 +17002,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="B8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -16586,7 +17017,7 @@
         <v>67</v>
       </c>
       <c r="F8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>46</v>
@@ -16597,10 +17028,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="B9">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -16612,7 +17043,7 @@
         <v>63</v>
       </c>
       <c r="F9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>25</v>
@@ -16623,10 +17054,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="B10">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C10">
         <v>11</v>
@@ -16638,7 +17069,7 @@
         <v>56</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>27</v>
@@ -16649,10 +17080,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="B11">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -16667,7 +17098,7 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11">
         <v>33</v>
@@ -16689,56 +17120,44 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>718</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>442</v>
-      </c>
-      <c r="C5" s="28">
-        <v>35</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>730</v>
-      </c>
-      <c r="E5" s="28">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>731</v>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>442</v>
@@ -16747,7 +17166,7 @@
         <v>434</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>423</v>
@@ -16756,237 +17175,237 @@
         <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="B9" s="3">
-        <v>4</v>
-      </c>
-      <c r="C9" s="30">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="C9" s="31">
+        <v>23</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="B10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="31">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3">
         <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>4</v>
-      </c>
-      <c r="F10" s="30">
-        <v>19</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="B11" s="30">
-        <v>22</v>
+        <v>728</v>
+      </c>
+      <c r="B11" s="31">
+        <v>23</v>
       </c>
       <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="D11" s="3">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="30">
-        <v>29</v>
-      </c>
       <c r="G11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="B12" s="31">
-        <v>35</v>
+        <v>729</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="31">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="30">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
       <c r="G12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="E13" s="3">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3">
+        <v>11</v>
+      </c>
+      <c r="G13" s="3">
         <v>2</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3">
-        <v>3</v>
-      </c>
-      <c r="F13" s="3">
-        <v>10</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="C14" s="3">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="F14" s="3">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="B15" s="30">
-        <v>20</v>
+        <v>732</v>
+      </c>
+      <c r="B15" s="31">
+        <v>21</v>
       </c>
       <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
         <v>0</v>
       </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
-        <v>6</v>
-      </c>
       <c r="F15" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="B17" s="30">
-        <v>26</v>
+        <v>734</v>
+      </c>
+      <c r="B17" s="31">
+        <v>27</v>
       </c>
       <c r="C17" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
         <v>0</v>
       </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="30">
-        <v>27</v>
+      <c r="F17" s="31">
+        <v>28</v>
       </c>
       <c r="G17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
-      </c>
-      <c r="C18" s="30">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="C18" s="31">
+        <v>20</v>
       </c>
       <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3">
         <v>0</v>
       </c>
-      <c r="E18" s="3">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
-        <v>6</v>
-      </c>
       <c r="G18" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -17005,7 +17424,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -17015,62 +17434,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -17080,42 +17499,42 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -17125,22 +17544,22 @@
     </row>
     <row r="25" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -17150,27 +17569,27 @@
     </row>
     <row r="30" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
@@ -17180,12 +17599,12 @@
     </row>
     <row r="36" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4119" uniqueCount="927">
   <si>
     <t>日期</t>
   </si>
@@ -1397,7 +1397,7 @@
     <t>10-06 18:11</t>
   </si>
   <si>
-    <t>10-07 11:00</t>
+    <t>10-07 17:00</t>
   </si>
   <si>
     <t>塔吉克</t>
@@ -1499,6 +1499,192 @@
     <t>3球 @3.7</t>
   </si>
   <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>芬超</t>
+  </si>
+  <si>
+    <t>赫尔火花</t>
+  </si>
+  <si>
+    <t>国际图尔</t>
+  </si>
+  <si>
+    <t>10-08 00:00</t>
+  </si>
+  <si>
+    <t>2球 @3.5</t>
+  </si>
+  <si>
+    <t>1球 @6.25 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.45 ⚡</t>
+  </si>
+  <si>
+    <t>巴西国际</t>
+  </si>
+  <si>
+    <t>科林蒂安</t>
+  </si>
+  <si>
+    <t>10-08 06:30</t>
+  </si>
+  <si>
+    <t>4球 @7 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
+    <t>里莫</t>
+  </si>
+  <si>
+    <t>格雷米奥</t>
+  </si>
+  <si>
+    <t>1球 @5.05 ⚡</t>
+  </si>
+  <si>
+    <t>周三004</t>
+  </si>
+  <si>
+    <t>布拉干RB</t>
+  </si>
+  <si>
+    <t>米拉索尔</t>
+  </si>
+  <si>
+    <t>4球 @5.5 ⚡</t>
+  </si>
+  <si>
+    <t>周三005</t>
+  </si>
+  <si>
+    <t>维多利亚</t>
+  </si>
+  <si>
+    <t>沙佩科</t>
+  </si>
+  <si>
+    <t>10-08 07:00</t>
+  </si>
+  <si>
+    <t>2球 @3.45</t>
+  </si>
+  <si>
+    <t>1球 @5.1 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.6 ⚡</t>
+  </si>
+  <si>
+    <t>周三006</t>
+  </si>
+  <si>
+    <t>博塔弗戈</t>
+  </si>
+  <si>
+    <t>达伽马</t>
+  </si>
+  <si>
+    <t>10-08 07:30</t>
+  </si>
+  <si>
+    <t>1球 @5.7 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.35 ⚡</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>赫尔辛基</t>
+  </si>
+  <si>
+    <t>瓦萨</t>
+  </si>
+  <si>
+    <t>10-08 23:00</t>
+  </si>
+  <si>
+    <t>4球 @4.75 ⚡</t>
+  </si>
+  <si>
+    <t>库奥皮奥</t>
+  </si>
+  <si>
+    <t>AC奥卢</t>
+  </si>
+  <si>
+    <t>10-09 00:00</t>
+  </si>
+  <si>
+    <t>2球 @3.4</t>
+  </si>
+  <si>
+    <t>3球 @3.65 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.75 ⚡</t>
+  </si>
+  <si>
+    <t>桑托斯</t>
+  </si>
+  <si>
+    <t>弗拉门戈</t>
+  </si>
+  <si>
+    <t>10-09 06:30</t>
+  </si>
+  <si>
+    <t>2球 @3.7</t>
+  </si>
+  <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.25 ⚡</t>
+  </si>
+  <si>
+    <t>米竞技</t>
+  </si>
+  <si>
+    <t>10-09 07:00</t>
+  </si>
+  <si>
+    <t>3球 @3.7 ⚡</t>
+  </si>
+  <si>
+    <t>弗鲁米嫩</t>
+  </si>
+  <si>
+    <t>科里蒂巴</t>
+  </si>
+  <si>
+    <t>10-09 08:30</t>
+  </si>
+  <si>
+    <t>6球 @17</t>
+  </si>
+  <si>
+    <t>4球 @5.3 ⚡</t>
+  </si>
+  <si>
+    <t>帕梅拉斯</t>
+  </si>
+  <si>
+    <t>2球 @3.65</t>
+  </si>
+  <si>
+    <t>1球 @5.5 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.1 ⚡</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1985,7 +2171,271 @@
     <t>2:5=110 5:2=125 负其他=29 平其他=125 胜其他=36</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-07T11:00:04+08:00）</t>
+    <t>0:1=8.75 1:0=16</t>
+  </si>
+  <si>
+    <t>0:2=9.25 1:1=7 2:0=27</t>
+  </si>
+  <si>
+    <t>0:3=14.5 1:2=6.75 2:1=13.5 3:0=70</t>
+  </si>
+  <si>
+    <t>0:4=33 1:3=11.5 2:2=13 3:1=35 4:0=200</t>
+  </si>
+  <si>
+    <t>0:5=80 1:4=24 2:3=19 3:2=35 4:1=110 5:0=450</t>
+  </si>
+  <si>
+    <t>1:5=60 2:4=41 3:3=43 4:2=110 5:1=300</t>
+  </si>
+  <si>
+    <t>2:5=80 5:2=300 负其他=37 平其他=200 胜其他=125</t>
+  </si>
+  <si>
+    <t>0:0=9.25</t>
+  </si>
+  <si>
+    <t>0:1=8.5 1:0=6</t>
+  </si>
+  <si>
+    <t>0:2=16.5 1:1=5.5 2:0=10</t>
+  </si>
+  <si>
+    <t>0:3=40 1:2=10.5 2:1=8.5 3:0=22</t>
+  </si>
+  <si>
+    <t>0:4=125 1:3=30 2:2=15 3:1=20 4:0=70</t>
+  </si>
+  <si>
+    <t>0:5=450 1:4=100 2:3=46 3:2=35 4:1=60 5:0=200</t>
+  </si>
+  <si>
+    <t>1:5=350 2:4=125 3:3=80 4:2=100 5:1=150</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=250 负其他=175 平其他=550 胜其他=90</t>
+  </si>
+  <si>
+    <t>0:1=10 1:0=8</t>
+  </si>
+  <si>
+    <t>0:2=16.5 1:1=6 2:0=11</t>
+  </si>
+  <si>
+    <t>0:3=38 1:2=9.75 2:1=7.75 3:0=23</t>
+  </si>
+  <si>
+    <t>0:4=100 1:3=24 2:2=13 3:1=17 4:0=60</t>
+  </si>
+  <si>
+    <t>0:5=300 1:4=80 2:3=30 3:2=25 4:1=45 5:0=150</t>
+  </si>
+  <si>
+    <t>1:5=250 2:4=100 3:3=55 4:2=70 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=300 5:2=175 负其他=100 平其他=350 胜其他=80</t>
+  </si>
+  <si>
+    <t>0:1=14 1:0=8</t>
+  </si>
+  <si>
+    <t>0:2=27 1:1=6.5 2:0=8.25</t>
+  </si>
+  <si>
+    <t>0:3=65 1:2=13 2:1=6.5 3:0=15</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=35 2:2=13.5 3:1=12 4:0=35</t>
+  </si>
+  <si>
+    <t>0:5=550 1:4=120 2:3=40 3:2=24 4:1=30 5:0=85</t>
+  </si>
+  <si>
+    <t>1:5=450 2:4=120 3:3=55 4:2=50 5:1=75</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=120 负其他=130 平其他=350 胜其他=45</t>
+  </si>
+  <si>
+    <t>0:1=14 1:0=7</t>
+  </si>
+  <si>
+    <t>0:2=31 1:1=8 2:0=7</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=17 2:1=6.5 3:0=12</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=50 2:2=16.5 3:1=11 4:0=25</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=175 2:3=50 3:2=23 4:1=25 5:0=60</t>
+  </si>
+  <si>
+    <t>1:5=700 2:4=175 3:3=70 4:2=55 5:1=55</t>
+  </si>
+  <si>
+    <t>2:5=700 5:2=120 负其他=250 平其他=450 胜其他=38</t>
+  </si>
+  <si>
+    <t>0:1=9.75 1:0=11</t>
+  </si>
+  <si>
+    <t>0:2=12.5 1:1=6 2:0=15.5</t>
+  </si>
+  <si>
+    <t>0:3=26 1:2=7.75 2:1=9.25 3:0=33</t>
+  </si>
+  <si>
+    <t>0:4=70 1:3=16.5 2:2=11.5 3:1=22 4:0=95</t>
+  </si>
+  <si>
+    <t>0:5=175 1:4=45 2:3=23 3:2=26 4:1=55 5:0=250</t>
+  </si>
+  <si>
+    <t>1:5=120 2:4=65 3:3=40 4:2=75 5:1=175</t>
+  </si>
+  <si>
+    <t>2:5=175 5:2=250 负其他=70 平其他=300 胜其他=80</t>
+  </si>
+  <si>
+    <t>0:1=16 1:0=8.5</t>
+  </si>
+  <si>
+    <t>0:2=33 1:1=8.75 2:0=7.5</t>
+  </si>
+  <si>
+    <t>0:3=90 1:2=15.5 2:1=7 3:0=12</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=45 2:2=14.5 3:1=10 4:0=23</t>
+  </si>
+  <si>
+    <t>0:5=700 1:4=150 2:3=38 3:2=20 4:1=22 5:0=55</t>
+  </si>
+  <si>
+    <t>1:5=450 2:4=150 3:3=50 4:2=38 5:1=45</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=85 负其他=150 平其他=250 胜其他=28</t>
+  </si>
+  <si>
+    <t>0:0=13</t>
+  </si>
+  <si>
+    <t>0:1=14 1:0=6.75</t>
+  </si>
+  <si>
+    <t>0:2=33 1:1=8.25 2:0=6.25</t>
+  </si>
+  <si>
+    <t>0:3=90 1:2=17.5 2:1=7 3:0=11</t>
+  </si>
+  <si>
+    <t>0:4=350 1:3=50 2:2=19 3:1=11 4:0=22</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=200 2:3=50 3:2=26 4:1=25 5:0=45</t>
+  </si>
+  <si>
+    <t>1:5=800 2:4=250 3:3=80 4:2=55 5:1=55</t>
+  </si>
+  <si>
+    <t>2:5=800 5:2=120 负其他=300 平其他=500 胜其他=45</t>
+  </si>
+  <si>
+    <t>0:1=8 1:0=13.5</t>
+  </si>
+  <si>
+    <t>0:2=8.5 1:1=7.75 2:0=25</t>
+  </si>
+  <si>
+    <t>0:3=15 1:2=6.75 2:1=12.5 3:0=60</t>
+  </si>
+  <si>
+    <t>0:4=35 1:3=12 2:2=13 3:1=33 4:0=175</t>
+  </si>
+  <si>
+    <t>0:5=80 1:4=28 2:3=23 3:2=35 4:1=90 5:0=550</t>
+  </si>
+  <si>
+    <t>1:5=70 2:4=45 3:3=50 4:2=120 5:1=350</t>
+  </si>
+  <si>
+    <t>2:5=120 5:2=450 负其他=45 平其他=250 胜其他=120</t>
+  </si>
+  <si>
+    <t>0:0=11</t>
+  </si>
+  <si>
+    <t>0:1=10 1:0=7.5</t>
+  </si>
+  <si>
+    <t>0:2=17 1:1=6.5 2:0=9.75</t>
+  </si>
+  <si>
+    <t>0:3=45 1:2=10.5 2:1=7.75 3:0=20</t>
+  </si>
+  <si>
+    <t>0:4=120 1:3=28 2:2=14 3:1=16 4:0=45</t>
+  </si>
+  <si>
+    <t>0:5=450 1:4=80 2:3=35 3:2=26 4:1=40 5:0=120</t>
+  </si>
+  <si>
+    <t>1:5=350 2:4=100 3:3=60 4:2=60 5:1=100</t>
+  </si>
+  <si>
+    <t>2:5=450 5:2=200 负其他=120 平其他=400 胜其他=70</t>
+  </si>
+  <si>
+    <t>0:1=17 1:0=6.5</t>
+  </si>
+  <si>
+    <t>0:2=37 1:1=9 2:0=6.5</t>
+  </si>
+  <si>
+    <t>0:3=120 1:2=20 2:1=7 3:0=9.5</t>
+  </si>
+  <si>
+    <t>0:4=450 1:3=65 2:2=19 3:1=10.5 4:0=19</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=300 2:3=65 3:2=25 4:1=21 5:0=37</t>
+  </si>
+  <si>
+    <t>1:5=750 2:4=300 3:3=90 4:2=55 5:1=45</t>
+  </si>
+  <si>
+    <t>2:5=750 5:2=120 负其他=300 平其他=450 胜其他=31</t>
+  </si>
+  <si>
+    <t>0:0=15</t>
+  </si>
+  <si>
+    <t>0:1=16 1:0=7.75</t>
+  </si>
+  <si>
+    <t>0:2=33 1:1=8.5 2:0=7</t>
+  </si>
+  <si>
+    <t>0:3=90 1:2=16.5 2:1=7 3:0=11</t>
+  </si>
+  <si>
+    <t>0:4=300 1:3=40 2:2=15 3:1=10.5 4:0=23</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=175 2:3=45 3:2=23 4:1=23 5:0=45</t>
+  </si>
+  <si>
+    <t>1:5=550 2:4=175 3:3=65 4:2=45 5:1=55</t>
+  </si>
+  <si>
+    <t>2:5=700 5:2=90 负其他=175 平其他=350 胜其他=35</t>
+  </si>
+  <si>
+    <t>进球数预测 · 模型统计（截至 2026-10-07T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2000,19 +2450,19 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>3/17 = 17.6%</t>
+    <t>3/19 = 15.8%</t>
   </si>
   <si>
     <t>模型A 命中率（自修正）</t>
   </si>
   <si>
-    <t>4/17 = 23.5%</t>
+    <t>5/19 = 26.3%</t>
   </si>
   <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
-    <t>6/17 = 35.3%</t>
+    <t>6/19 = 31.6%</t>
   </si>
   <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
@@ -2039,7 +2489,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>14 场（另剔除爆冷 3 场）</t>
+    <t>16 场（另剔除爆冷 3 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -2078,40 +2528,46 @@
     <t>25% (1/4)</t>
   </si>
   <si>
+    <t>0% (0/5)</t>
+  </si>
+  <si>
+    <t>0% (0/3)</t>
+  </si>
+  <si>
+    <t>0% (0/1)</t>
+  </si>
+  <si>
+    <t>67% (2/3)</t>
+  </si>
+  <si>
     <t>0% (0/4)</t>
   </si>
   <si>
-    <t>0% (0/1)</t>
-  </si>
-  <si>
-    <t>0% (0/3)</t>
-  </si>
-  <si>
-    <t>50% (1/2)</t>
-  </si>
-  <si>
     <t>20% (1/5)</t>
   </si>
   <si>
     <t>29% (2/7)</t>
   </si>
   <si>
-    <t>50% (3/6)</t>
+    <t>43% (3/7)</t>
   </si>
   <si>
     <t>33% (1/3)</t>
   </si>
   <si>
-    <t>33% (2/6)</t>
+    <t>38% (3/8)</t>
+  </si>
+  <si>
+    <t>0% (0/6)</t>
   </si>
   <si>
     <t>0% (0/7)</t>
   </si>
   <si>
-    <t>0% (0/8)</t>
-  </si>
-  <si>
-    <t>0% (0/12)</t>
+    <t>0% (0/9)</t>
+  </si>
+  <si>
+    <t>0% (0/14)</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -8432,7 +8888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -9314,7 +9770,7 @@
         <v>55</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>486</v>
@@ -9325,17 +9781,17 @@
       <c r="K19" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>21</v>
+      <c r="L19" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N19" t="s">
         <v>458</v>
       </c>
       <c r="O19" t="s">
-        <v>21</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -9361,7 +9817,7 @@
         <v>55</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>491</v>
@@ -9372,16 +9828,580 @@
       <c r="K20" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>21</v>
+      <c r="L20" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N20" t="s">
         <v>472</v>
       </c>
       <c r="O20" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>493</v>
+      </c>
+      <c r="B21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" t="s">
+        <v>494</v>
+      </c>
+      <c r="D21" t="s">
+        <v>495</v>
+      </c>
+      <c r="E21" t="s">
+        <v>496</v>
+      </c>
+      <c r="F21" t="s">
+        <v>497</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
+        <v>459</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>493</v>
+      </c>
+      <c r="B22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" t="s">
+        <v>501</v>
+      </c>
+      <c r="E22" t="s">
+        <v>502</v>
+      </c>
+      <c r="F22" t="s">
+        <v>503</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" t="s">
+        <v>459</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>493</v>
+      </c>
+      <c r="B23" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" t="s">
+        <v>506</v>
+      </c>
+      <c r="E23" t="s">
+        <v>507</v>
+      </c>
+      <c r="F23" t="s">
+        <v>503</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" t="s">
+        <v>459</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>493</v>
+      </c>
+      <c r="B24" t="s">
+        <v>509</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>510</v>
+      </c>
+      <c r="E24" t="s">
+        <v>511</v>
+      </c>
+      <c r="F24" t="s">
+        <v>503</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="L24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" t="s">
+        <v>459</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>493</v>
+      </c>
+      <c r="B25" t="s">
+        <v>513</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>514</v>
+      </c>
+      <c r="E25" t="s">
+        <v>515</v>
+      </c>
+      <c r="F25" t="s">
+        <v>516</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="L25" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s">
+        <v>459</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>493</v>
+      </c>
+      <c r="B26" t="s">
+        <v>520</v>
+      </c>
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>521</v>
+      </c>
+      <c r="E26" t="s">
+        <v>522</v>
+      </c>
+      <c r="F26" t="s">
+        <v>523</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="L26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" t="s">
+        <v>459</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>526</v>
+      </c>
+      <c r="B27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" t="s">
+        <v>494</v>
+      </c>
+      <c r="D27" t="s">
+        <v>527</v>
+      </c>
+      <c r="E27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F27" t="s">
+        <v>529</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L27" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" t="s">
+        <v>459</v>
+      </c>
+      <c r="O27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>526</v>
+      </c>
+      <c r="B28" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" t="s">
+        <v>494</v>
+      </c>
+      <c r="D28" t="s">
+        <v>531</v>
+      </c>
+      <c r="E28" t="s">
+        <v>532</v>
+      </c>
+      <c r="F28" t="s">
+        <v>533</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="L28" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N28" t="s">
+        <v>459</v>
+      </c>
+      <c r="O28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>526</v>
+      </c>
+      <c r="B29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s">
+        <v>537</v>
+      </c>
+      <c r="E29" t="s">
+        <v>538</v>
+      </c>
+      <c r="F29" t="s">
+        <v>539</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="L29" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" t="s">
+        <v>459</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>526</v>
+      </c>
+      <c r="B30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" t="s">
+        <v>543</v>
+      </c>
+      <c r="F30" t="s">
+        <v>544</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="L30" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" t="s">
+        <v>21</v>
+      </c>
+      <c r="N30" t="s">
+        <v>459</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>526</v>
+      </c>
+      <c r="B31" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="s">
+        <v>546</v>
+      </c>
+      <c r="E31" t="s">
+        <v>547</v>
+      </c>
+      <c r="F31" t="s">
+        <v>548</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="L31" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" t="s">
+        <v>459</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>526</v>
+      </c>
+      <c r="B32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" t="s">
+        <v>551</v>
+      </c>
+      <c r="E32" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" t="s">
+        <v>548</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="L32" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" t="s">
+        <v>459</v>
+      </c>
+      <c r="O32" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9394,7 +10414,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M249"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -9415,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>493</v>
+        <v>555</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -9424,31 +10444,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>494</v>
+        <v>556</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>495</v>
+        <v>557</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>496</v>
+        <v>558</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>497</v>
+        <v>559</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>498</v>
+        <v>560</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>499</v>
+        <v>561</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>500</v>
+        <v>562</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>501</v>
+        <v>563</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>502</v>
+        <v>564</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9481,7 +10501,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>503</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -9522,7 +10542,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>504</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -9563,7 +10583,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>505</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -9604,7 +10624,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>506</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -9645,7 +10665,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>507</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -9686,7 +10706,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>508</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -9703,7 +10723,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -9727,7 +10747,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>510</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -9744,7 +10764,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -9768,7 +10788,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>512</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9801,7 +10821,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>513</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -9842,7 +10862,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>514</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -9883,7 +10903,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>515</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -9924,7 +10944,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>516</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -9965,7 +10985,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>517</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -10006,7 +11026,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>518</v>
+        <v>580</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -10023,7 +11043,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -10047,7 +11067,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>519</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -10064,7 +11084,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -10088,7 +11108,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>520</v>
+        <v>582</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10121,7 +11141,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>521</v>
+        <v>583</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -10162,7 +11182,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>522</v>
+        <v>584</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -10203,7 +11223,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>523</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -10244,7 +11264,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>524</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -10285,7 +11305,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>525</v>
+        <v>587</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -10326,7 +11346,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>526</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -10343,7 +11363,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -10367,7 +11387,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>527</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -10384,7 +11404,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -10408,7 +11428,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>528</v>
+        <v>590</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10441,7 +11461,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>529</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -10482,7 +11502,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>530</v>
+        <v>592</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -10523,7 +11543,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>531</v>
+        <v>593</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -10564,7 +11584,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>532</v>
+        <v>594</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -10605,7 +11625,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>533</v>
+        <v>595</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -10646,7 +11666,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>534</v>
+        <v>596</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -10663,7 +11683,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -10687,7 +11707,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>535</v>
+        <v>597</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -10704,7 +11724,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -10728,7 +11748,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>536</v>
+        <v>598</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10761,7 +11781,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>537</v>
+        <v>599</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -10802,7 +11822,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>538</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -10843,7 +11863,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>539</v>
+        <v>601</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -10884,7 +11904,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>540</v>
+        <v>602</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -10925,7 +11945,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>541</v>
+        <v>603</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -10966,7 +11986,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>542</v>
+        <v>604</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -10983,7 +12003,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -11007,7 +12027,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>543</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -11024,7 +12044,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -11048,7 +12068,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>544</v>
+        <v>606</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11081,7 +12101,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>545</v>
+        <v>607</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -11122,7 +12142,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>546</v>
+        <v>608</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -11163,7 +12183,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>547</v>
+        <v>609</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -11204,7 +12224,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>548</v>
+        <v>610</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -11245,7 +12265,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>549</v>
+        <v>611</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -11286,7 +12306,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>550</v>
+        <v>612</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -11303,7 +12323,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -11327,7 +12347,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>551</v>
+        <v>613</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -11344,7 +12364,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -11368,7 +12388,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>552</v>
+        <v>614</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11401,7 +12421,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>553</v>
+        <v>615</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -11442,7 +12462,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>554</v>
+        <v>616</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -11483,7 +12503,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>555</v>
+        <v>617</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -11524,7 +12544,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>556</v>
+        <v>618</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -11565,7 +12585,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>557</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -11606,7 +12626,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>558</v>
+        <v>620</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -11623,7 +12643,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -11647,7 +12667,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>559</v>
+        <v>621</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -11664,7 +12684,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -11688,7 +12708,7 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>560</v>
+        <v>622</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11721,7 +12741,7 @@
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="4" t="s">
-        <v>561</v>
+        <v>623</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -11762,7 +12782,7 @@
         <v>-49.6</v>
       </c>
       <c r="M59" t="s">
-        <v>562</v>
+        <v>624</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -11803,7 +12823,7 @@
         <v>-74.9</v>
       </c>
       <c r="M60" t="s">
-        <v>563</v>
+        <v>625</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -11844,7 +12864,7 @@
         <v>-88.2</v>
       </c>
       <c r="M61" t="s">
-        <v>564</v>
+        <v>626</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -11885,7 +12905,7 @@
         <v>-91.6</v>
       </c>
       <c r="M62" t="s">
-        <v>565</v>
+        <v>627</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -11926,7 +12946,7 @@
         <v>-94.9</v>
       </c>
       <c r="M63" t="s">
-        <v>566</v>
+        <v>628</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -11943,7 +12963,7 @@
         <v>452</v>
       </c>
       <c r="E64" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F64" s="12">
         <v>15</v>
@@ -11967,7 +12987,7 @@
         <v>-90.1</v>
       </c>
       <c r="M64" t="s">
-        <v>567</v>
+        <v>629</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -11984,7 +13004,7 @@
         <v>452</v>
       </c>
       <c r="E65" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F65" s="12">
         <v>18</v>
@@ -12008,7 +13028,7 @@
         <v>-91.4</v>
       </c>
       <c r="M65" t="s">
-        <v>568</v>
+        <v>630</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12041,7 +13061,7 @@
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="4" t="s">
-        <v>569</v>
+        <v>631</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -12082,7 +13102,7 @@
         <v>-51.7</v>
       </c>
       <c r="M67" t="s">
-        <v>570</v>
+        <v>632</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -12123,7 +13143,7 @@
         <v>-73.4</v>
       </c>
       <c r="M68" t="s">
-        <v>571</v>
+        <v>633</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -12164,7 +13184,7 @@
         <v>-83.2</v>
       </c>
       <c r="M69" t="s">
-        <v>572</v>
+        <v>634</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -12205,7 +13225,7 @@
         <v>-88.2</v>
       </c>
       <c r="M70" t="s">
-        <v>573</v>
+        <v>635</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -12246,7 +13266,7 @@
         <v>-86.5</v>
       </c>
       <c r="M71" t="s">
-        <v>574</v>
+        <v>636</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -12263,7 +13283,7 @@
         <v>460</v>
       </c>
       <c r="E72" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F72" s="12">
         <v>27</v>
@@ -12287,7 +13307,7 @@
         <v>-80.7</v>
       </c>
       <c r="M72" t="s">
-        <v>575</v>
+        <v>637</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -12304,7 +13324,7 @@
         <v>460</v>
       </c>
       <c r="E73" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F73" s="12">
         <v>45</v>
@@ -12328,7 +13348,7 @@
         <v>-82.9</v>
       </c>
       <c r="M73" t="s">
-        <v>576</v>
+        <v>638</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12361,7 +13381,7 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="4" t="s">
-        <v>537</v>
+        <v>599</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -12402,7 +13422,7 @@
         <v>-48.3</v>
       </c>
       <c r="M75" t="s">
-        <v>577</v>
+        <v>639</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -12443,7 +13463,7 @@
         <v>-68.4</v>
       </c>
       <c r="M76" t="s">
-        <v>578</v>
+        <v>640</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -12484,7 +13504,7 @@
         <v>-80.5</v>
       </c>
       <c r="M77" t="s">
-        <v>579</v>
+        <v>641</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -12525,7 +13545,7 @@
         <v>-86.5</v>
       </c>
       <c r="M78" t="s">
-        <v>580</v>
+        <v>642</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -12566,7 +13586,7 @@
         <v>-87.7</v>
       </c>
       <c r="M79" t="s">
-        <v>581</v>
+        <v>643</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -12583,7 +13603,7 @@
         <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F80" s="12">
         <v>38</v>
@@ -12607,7 +13627,7 @@
         <v>-75.9</v>
       </c>
       <c r="M80" t="s">
-        <v>582</v>
+        <v>644</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -12624,7 +13644,7 @@
         <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F81" s="12">
         <v>70</v>
@@ -12648,7 +13668,7 @@
         <v>-78.5</v>
       </c>
       <c r="M81" t="s">
-        <v>583</v>
+        <v>645</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12681,7 +13701,7 @@
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="4" t="s">
-        <v>584</v>
+        <v>646</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -12722,7 +13742,7 @@
         <v>-50.9</v>
       </c>
       <c r="M83" t="s">
-        <v>585</v>
+        <v>647</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -12763,7 +13783,7 @@
         <v>-76.5</v>
       </c>
       <c r="M84" t="s">
-        <v>586</v>
+        <v>648</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -12804,7 +13824,7 @@
         <v>-87.5</v>
       </c>
       <c r="M85" t="s">
-        <v>587</v>
+        <v>649</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -12845,7 +13865,7 @@
         <v>-92.7</v>
       </c>
       <c r="M86" t="s">
-        <v>588</v>
+        <v>650</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -12886,7 +13906,7 @@
         <v>-94.2</v>
       </c>
       <c r="M87" t="s">
-        <v>589</v>
+        <v>651</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -12903,7 +13923,7 @@
         <v>305</v>
       </c>
       <c r="E88" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F88" s="12">
         <v>24</v>
@@ -12927,7 +13947,7 @@
         <v>-89.6</v>
       </c>
       <c r="M88" t="s">
-        <v>590</v>
+        <v>652</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -12944,7 +13964,7 @@
         <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F89" s="12">
         <v>35</v>
@@ -12968,7 +13988,7 @@
         <v>-88.8</v>
       </c>
       <c r="M89" t="s">
-        <v>591</v>
+        <v>653</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13001,7 +14021,7 @@
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="4" t="s">
-        <v>592</v>
+        <v>654</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -13042,7 +14062,7 @@
         <v>-50.8</v>
       </c>
       <c r="M91" t="s">
-        <v>593</v>
+        <v>655</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -13083,7 +14103,7 @@
         <v>-68.8</v>
       </c>
       <c r="M92" t="s">
-        <v>594</v>
+        <v>656</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -13124,7 +14144,7 @@
         <v>-84</v>
       </c>
       <c r="M93" t="s">
-        <v>595</v>
+        <v>657</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -13165,7 +14185,7 @@
         <v>-87.8</v>
       </c>
       <c r="M94" t="s">
-        <v>596</v>
+        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -13206,7 +14226,7 @@
         <v>-89.3</v>
       </c>
       <c r="M95" t="s">
-        <v>597</v>
+        <v>659</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -13223,7 +14243,7 @@
         <v>308</v>
       </c>
       <c r="E96" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F96" s="12">
         <v>42</v>
@@ -13247,7 +14267,7 @@
         <v>-78.5</v>
       </c>
       <c r="M96" t="s">
-        <v>598</v>
+        <v>660</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -13264,7 +14284,7 @@
         <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F97" s="12">
         <v>80</v>
@@ -13288,7 +14308,7 @@
         <v>-79.7</v>
       </c>
       <c r="M97" t="s">
-        <v>599</v>
+        <v>661</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13321,7 +14341,7 @@
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="4" t="s">
-        <v>592</v>
+        <v>654</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -13362,7 +14382,7 @@
         <v>-52.4</v>
       </c>
       <c r="M99" t="s">
-        <v>600</v>
+        <v>662</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -13403,7 +14423,7 @@
         <v>-74</v>
       </c>
       <c r="M100" t="s">
-        <v>601</v>
+        <v>663</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -13444,7 +14464,7 @@
         <v>-86.3</v>
       </c>
       <c r="M101" t="s">
-        <v>602</v>
+        <v>664</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -13485,7 +14505,7 @@
         <v>-91.6</v>
       </c>
       <c r="M102" t="s">
-        <v>603</v>
+        <v>665</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -13526,7 +14546,7 @@
         <v>-92.2</v>
       </c>
       <c r="M103" t="s">
-        <v>604</v>
+        <v>666</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -13543,7 +14563,7 @@
         <v>293</v>
       </c>
       <c r="E104" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F104" s="12">
         <v>35</v>
@@ -13567,7 +14587,7 @@
         <v>-81.8</v>
       </c>
       <c r="M104" t="s">
-        <v>605</v>
+        <v>667</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -13584,7 +14604,7 @@
         <v>293</v>
       </c>
       <c r="E105" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F105" s="12">
         <v>60</v>
@@ -13608,7 +14628,7 @@
         <v>-82.4</v>
       </c>
       <c r="M105" t="s">
-        <v>606</v>
+        <v>668</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13641,7 +14661,7 @@
       </c>
       <c r="L106" s="11"/>
       <c r="M106" s="4" t="s">
-        <v>607</v>
+        <v>669</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -13682,7 +14702,7 @@
         <v>-66.4</v>
       </c>
       <c r="M107" t="s">
-        <v>608</v>
+        <v>670</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
@@ -13723,7 +14743,7 @@
         <v>-89.7</v>
       </c>
       <c r="M108" t="s">
-        <v>609</v>
+        <v>671</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
@@ -13764,7 +14784,7 @@
         <v>-96.9</v>
       </c>
       <c r="M109" t="s">
-        <v>610</v>
+        <v>672</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
@@ -13805,7 +14825,7 @@
         <v>-98.4</v>
       </c>
       <c r="M110" t="s">
-        <v>611</v>
+        <v>673</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -13846,7 +14866,7 @@
         <v>-98.2</v>
       </c>
       <c r="M111" t="s">
-        <v>612</v>
+        <v>674</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -13863,7 +14883,7 @@
         <v>315</v>
       </c>
       <c r="E112" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F112" s="12">
         <v>8.8</v>
@@ -13887,7 +14907,7 @@
         <v>-97.2</v>
       </c>
       <c r="M112" t="s">
-        <v>613</v>
+        <v>675</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
@@ -13904,7 +14924,7 @@
         <v>315</v>
       </c>
       <c r="E113" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F113" s="12">
         <v>9</v>
@@ -13928,7 +14948,7 @@
         <v>-97.7</v>
       </c>
       <c r="M113" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13961,7 +14981,7 @@
       </c>
       <c r="L114" s="11"/>
       <c r="M114" s="4" t="s">
-        <v>615</v>
+        <v>677</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
@@ -14002,7 +15022,7 @@
         <v>-58.4</v>
       </c>
       <c r="M115" t="s">
-        <v>616</v>
+        <v>678</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -14043,7 +15063,7 @@
         <v>-81.7</v>
       </c>
       <c r="M116" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
@@ -14084,7 +15104,7 @@
         <v>-92.4</v>
       </c>
       <c r="M117" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
@@ -14125,7 +15145,7 @@
         <v>-96.5</v>
       </c>
       <c r="M118" t="s">
-        <v>619</v>
+        <v>681</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -14166,7 +15186,7 @@
         <v>-97</v>
       </c>
       <c r="M119" t="s">
-        <v>620</v>
+        <v>682</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -14183,7 +15203,7 @@
         <v>323</v>
       </c>
       <c r="E120" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F120" s="12">
         <v>12</v>
@@ -14207,7 +15227,7 @@
         <v>-94</v>
       </c>
       <c r="M120" t="s">
-        <v>621</v>
+        <v>683</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -14224,7 +15244,7 @@
         <v>323</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F121" s="12">
         <v>14</v>
@@ -14248,7 +15268,7 @@
         <v>-93.4</v>
       </c>
       <c r="M121" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14281,7 +15301,7 @@
       </c>
       <c r="L122" s="11"/>
       <c r="M122" s="4" t="s">
-        <v>623</v>
+        <v>685</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -14322,7 +15342,7 @@
         <v>-74.2</v>
       </c>
       <c r="M123" t="s">
-        <v>624</v>
+        <v>686</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -14363,7 +15383,7 @@
         <v>-92.3</v>
       </c>
       <c r="M124" t="s">
-        <v>625</v>
+        <v>687</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -14404,7 +15424,7 @@
         <v>-98.1</v>
       </c>
       <c r="M125" t="s">
-        <v>626</v>
+        <v>688</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -14445,7 +15465,7 @@
         <v>-98.5</v>
       </c>
       <c r="M126" t="s">
-        <v>627</v>
+        <v>689</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -14486,7 +15506,7 @@
         <v>-98.3</v>
       </c>
       <c r="M127" t="s">
-        <v>628</v>
+        <v>690</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -14503,7 +15523,7 @@
         <v>319</v>
       </c>
       <c r="E128" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F128" s="12">
         <v>11</v>
@@ -14527,7 +15547,7 @@
         <v>-97.5</v>
       </c>
       <c r="M128" t="s">
-        <v>629</v>
+        <v>691</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -14544,7 +15564,7 @@
         <v>319</v>
       </c>
       <c r="E129" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F129" s="12">
         <v>12</v>
@@ -14568,7 +15588,7 @@
         <v>-97.7</v>
       </c>
       <c r="M129" t="s">
-        <v>630</v>
+        <v>692</v>
       </c>
     </row>
     <row r="130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14601,7 +15621,7 @@
       </c>
       <c r="L130" s="11"/>
       <c r="M130" s="4" t="s">
-        <v>631</v>
+        <v>693</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -14642,7 +15662,7 @@
         <v>-58</v>
       </c>
       <c r="M131" t="s">
-        <v>632</v>
+        <v>694</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -14683,7 +15703,7 @@
         <v>-81.6</v>
       </c>
       <c r="M132" t="s">
-        <v>633</v>
+        <v>695</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -14724,7 +15744,7 @@
         <v>-90.8</v>
       </c>
       <c r="M133" t="s">
-        <v>634</v>
+        <v>696</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -14765,7 +15785,7 @@
         <v>-95.8</v>
       </c>
       <c r="M134" t="s">
-        <v>635</v>
+        <v>697</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -14806,7 +15826,7 @@
         <v>-95.9</v>
       </c>
       <c r="M135" t="s">
-        <v>636</v>
+        <v>698</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -14823,7 +15843,7 @@
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F136" s="12">
         <v>20</v>
@@ -14847,7 +15867,7 @@
         <v>-93.3</v>
       </c>
       <c r="M136" t="s">
-        <v>637</v>
+        <v>699</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -14864,7 +15884,7 @@
         <v>410</v>
       </c>
       <c r="E137" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F137" s="12">
         <v>30</v>
@@ -14888,7 +15908,7 @@
         <v>-92.7</v>
       </c>
       <c r="M137" t="s">
-        <v>638</v>
+        <v>700</v>
       </c>
     </row>
     <row r="138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14921,7 +15941,7 @@
       </c>
       <c r="L138" s="11"/>
       <c r="M138" s="4" t="s">
-        <v>639</v>
+        <v>701</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -14962,7 +15982,7 @@
         <v>-49</v>
       </c>
       <c r="M139" t="s">
-        <v>640</v>
+        <v>702</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -15003,7 +16023,7 @@
         <v>-72.3</v>
       </c>
       <c r="M140" t="s">
-        <v>641</v>
+        <v>703</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -15044,7 +16064,7 @@
         <v>-83.6</v>
       </c>
       <c r="M141" t="s">
-        <v>642</v>
+        <v>704</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -15085,7 +16105,7 @@
         <v>-88.7</v>
       </c>
       <c r="M142" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -15126,7 +16146,7 @@
         <v>-93.2</v>
       </c>
       <c r="M143" t="s">
-        <v>644</v>
+        <v>706</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -15143,7 +16163,7 @@
         <v>329</v>
       </c>
       <c r="E144" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F144" s="12">
         <v>15.5</v>
@@ -15167,7 +16187,7 @@
         <v>-85.4</v>
       </c>
       <c r="M144" t="s">
-        <v>645</v>
+        <v>707</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -15184,7 +16204,7 @@
         <v>329</v>
       </c>
       <c r="E145" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F145" s="12">
         <v>21</v>
@@ -15208,7 +16228,7 @@
         <v>-85.1</v>
       </c>
       <c r="M145" t="s">
-        <v>646</v>
+        <v>708</v>
       </c>
     </row>
     <row r="146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15241,7 +16261,7 @@
       </c>
       <c r="L146" s="11"/>
       <c r="M146" s="4" t="s">
-        <v>647</v>
+        <v>709</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -15282,7 +16302,7 @@
         <v>-44.4</v>
       </c>
       <c r="M147" t="s">
-        <v>648</v>
+        <v>710</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -15323,7 +16343,7 @@
         <v>-67.9</v>
       </c>
       <c r="M148" t="s">
-        <v>649</v>
+        <v>711</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -15364,7 +16384,7 @@
         <v>-80.2</v>
       </c>
       <c r="M149" t="s">
-        <v>650</v>
+        <v>712</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -15405,7 +16425,7 @@
         <v>-87.4</v>
       </c>
       <c r="M150" t="s">
-        <v>651</v>
+        <v>713</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -15446,7 +16466,7 @@
         <v>-92.6</v>
       </c>
       <c r="M151" t="s">
-        <v>652</v>
+        <v>714</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -15463,7 +16483,7 @@
         <v>489</v>
       </c>
       <c r="E152" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -15487,7 +16507,7 @@
         <v>-84.3</v>
       </c>
       <c r="M152" t="s">
-        <v>653</v>
+        <v>715</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -15504,7 +16524,7 @@
         <v>489</v>
       </c>
       <c r="E153" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="F153" s="12">
         <v>13</v>
@@ -15528,7 +16548,3847 @@
         <v>-84.7</v>
       </c>
       <c r="M153" t="s">
-        <v>654</v>
+        <v>716</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F154" s="8">
+        <v>16</v>
+      </c>
+      <c r="G154" s="9"/>
+      <c r="H154" s="10">
+        <v>1.571</v>
+      </c>
+      <c r="I154" s="11"/>
+      <c r="J154" s="8"/>
+      <c r="K154" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L154" s="11"/>
+      <c r="M154" s="4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>493</v>
+      </c>
+      <c r="B155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C155" t="s">
+        <v>495</v>
+      </c>
+      <c r="D155" t="s">
+        <v>496</v>
+      </c>
+      <c r="E155" t="s">
+        <v>434</v>
+      </c>
+      <c r="F155" s="12">
+        <v>6.25</v>
+      </c>
+      <c r="G155" s="13">
+        <v>5.657</v>
+      </c>
+      <c r="H155" s="14">
+        <v>0.593</v>
+      </c>
+      <c r="I155" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="J155" s="12">
+        <v>12.375</v>
+      </c>
+      <c r="K155" s="16">
+        <v>-6.125</v>
+      </c>
+      <c r="L155" s="15">
+        <v>-49.5</v>
+      </c>
+      <c r="M155" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>493</v>
+      </c>
+      <c r="B156" t="s">
+        <v>175</v>
+      </c>
+      <c r="C156" t="s">
+        <v>495</v>
+      </c>
+      <c r="D156" t="s">
+        <v>496</v>
+      </c>
+      <c r="E156" t="s">
+        <v>454</v>
+      </c>
+      <c r="F156" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G156" s="13">
+        <v>3.472</v>
+      </c>
+      <c r="H156" s="14">
+        <v>0.028</v>
+      </c>
+      <c r="I156" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="J156" s="12">
+        <v>14.417</v>
+      </c>
+      <c r="K156" s="16">
+        <v>-10.917</v>
+      </c>
+      <c r="L156" s="15">
+        <v>-75.7</v>
+      </c>
+      <c r="M156" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>493</v>
+      </c>
+      <c r="B157" t="s">
+        <v>175</v>
+      </c>
+      <c r="C157" t="s">
+        <v>495</v>
+      </c>
+      <c r="D157" t="s">
+        <v>496</v>
+      </c>
+      <c r="E157" t="s">
+        <v>423</v>
+      </c>
+      <c r="F157" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="G157" s="13">
+        <v>3.274</v>
+      </c>
+      <c r="H157" s="14">
+        <v>0.176</v>
+      </c>
+      <c r="I157" s="15">
+        <v>5.4</v>
+      </c>
+      <c r="J157" s="12">
+        <v>26.188</v>
+      </c>
+      <c r="K157" s="16">
+        <v>-22.738</v>
+      </c>
+      <c r="L157" s="15">
+        <v>-86.8</v>
+      </c>
+      <c r="M157" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>493</v>
+      </c>
+      <c r="B158" t="s">
+        <v>175</v>
+      </c>
+      <c r="C158" t="s">
+        <v>495</v>
+      </c>
+      <c r="D158" t="s">
+        <v>496</v>
+      </c>
+      <c r="E158" t="s">
+        <v>439</v>
+      </c>
+      <c r="F158" s="12">
+        <v>5.15</v>
+      </c>
+      <c r="G158" s="13">
+        <v>4.391</v>
+      </c>
+      <c r="H158" s="14">
+        <v>0.759</v>
+      </c>
+      <c r="I158" s="15">
+        <v>17.3</v>
+      </c>
+      <c r="J158" s="12">
+        <v>58.5</v>
+      </c>
+      <c r="K158" s="16">
+        <v>-53.35</v>
+      </c>
+      <c r="L158" s="15">
+        <v>-91.2</v>
+      </c>
+      <c r="M158" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>493</v>
+      </c>
+      <c r="B159" t="s">
+        <v>175</v>
+      </c>
+      <c r="C159" t="s">
+        <v>495</v>
+      </c>
+      <c r="D159" t="s">
+        <v>496</v>
+      </c>
+      <c r="E159" t="s">
+        <v>431</v>
+      </c>
+      <c r="F159" s="12">
+        <v>9.25</v>
+      </c>
+      <c r="G159" s="13">
+        <v>6.817</v>
+      </c>
+      <c r="H159" s="14">
+        <v>2.433</v>
+      </c>
+      <c r="I159" s="15">
+        <v>35.7</v>
+      </c>
+      <c r="J159" s="12">
+        <v>119.667</v>
+      </c>
+      <c r="K159" s="16">
+        <v>-110.417</v>
+      </c>
+      <c r="L159" s="15">
+        <v>-92.3</v>
+      </c>
+      <c r="M159" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>493</v>
+      </c>
+      <c r="B160" t="s">
+        <v>175</v>
+      </c>
+      <c r="C160" t="s">
+        <v>495</v>
+      </c>
+      <c r="D160" t="s">
+        <v>496</v>
+      </c>
+      <c r="E160" t="s">
+        <v>571</v>
+      </c>
+      <c r="F160" s="12">
+        <v>16</v>
+      </c>
+      <c r="G160" s="13">
+        <v>13.032</v>
+      </c>
+      <c r="H160" s="14">
+        <v>2.968</v>
+      </c>
+      <c r="I160" s="15">
+        <v>22.8</v>
+      </c>
+      <c r="J160" s="12">
+        <v>110.8</v>
+      </c>
+      <c r="K160" s="16">
+        <v>-94.8</v>
+      </c>
+      <c r="L160" s="15">
+        <v>-85.6</v>
+      </c>
+      <c r="M160" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>493</v>
+      </c>
+      <c r="B161" t="s">
+        <v>175</v>
+      </c>
+      <c r="C161" t="s">
+        <v>495</v>
+      </c>
+      <c r="D161" t="s">
+        <v>496</v>
+      </c>
+      <c r="E161" t="s">
+        <v>573</v>
+      </c>
+      <c r="F161" s="12">
+        <v>24</v>
+      </c>
+      <c r="G161" s="13">
+        <v>17.902</v>
+      </c>
+      <c r="H161" s="14">
+        <v>6.098</v>
+      </c>
+      <c r="I161" s="15">
+        <v>34.1</v>
+      </c>
+      <c r="J161" s="12">
+        <v>148.4</v>
+      </c>
+      <c r="K161" s="16">
+        <v>-124.4</v>
+      </c>
+      <c r="L161" s="15">
+        <v>-83.8</v>
+      </c>
+      <c r="M161" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F162" s="8">
+        <v>9.25</v>
+      </c>
+      <c r="G162" s="9"/>
+      <c r="H162" s="10">
+        <v>3.171</v>
+      </c>
+      <c r="I162" s="11"/>
+      <c r="J162" s="8"/>
+      <c r="K162" s="10">
+        <v>-3.329</v>
+      </c>
+      <c r="L162" s="11"/>
+      <c r="M162" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>493</v>
+      </c>
+      <c r="B163" t="s">
+        <v>179</v>
+      </c>
+      <c r="C163" t="s">
+        <v>501</v>
+      </c>
+      <c r="D163" t="s">
+        <v>502</v>
+      </c>
+      <c r="E163" t="s">
+        <v>434</v>
+      </c>
+      <c r="F163" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G163" s="13">
+        <v>3.517</v>
+      </c>
+      <c r="H163" s="14">
+        <v>0.033</v>
+      </c>
+      <c r="I163" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="J163" s="12">
+        <v>7.25</v>
+      </c>
+      <c r="K163" s="16">
+        <v>-3.7</v>
+      </c>
+      <c r="L163" s="15">
+        <v>-51</v>
+      </c>
+      <c r="M163" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>493</v>
+      </c>
+      <c r="B164" t="s">
+        <v>179</v>
+      </c>
+      <c r="C164" t="s">
+        <v>501</v>
+      </c>
+      <c r="D164" t="s">
+        <v>502</v>
+      </c>
+      <c r="E164" t="s">
+        <v>454</v>
+      </c>
+      <c r="F164" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G164" s="13">
+        <v>2.92</v>
+      </c>
+      <c r="H164" s="14">
+        <v>0.63</v>
+      </c>
+      <c r="I164" s="15">
+        <v>21.6</v>
+      </c>
+      <c r="J164" s="12">
+        <v>10.667</v>
+      </c>
+      <c r="K164" s="16">
+        <v>-7.117</v>
+      </c>
+      <c r="L164" s="15">
+        <v>-66.7</v>
+      </c>
+      <c r="M164" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>493</v>
+      </c>
+      <c r="B165" t="s">
+        <v>179</v>
+      </c>
+      <c r="C165" t="s">
+        <v>501</v>
+      </c>
+      <c r="D165" t="s">
+        <v>502</v>
+      </c>
+      <c r="E165" t="s">
+        <v>423</v>
+      </c>
+      <c r="F165" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G165" s="13">
+        <v>3.529</v>
+      </c>
+      <c r="H165" s="14">
+        <v>0.021</v>
+      </c>
+      <c r="I165" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="J165" s="12">
+        <v>20.25</v>
+      </c>
+      <c r="K165" s="16">
+        <v>-16.7</v>
+      </c>
+      <c r="L165" s="15">
+        <v>-82.5</v>
+      </c>
+      <c r="M165" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>493</v>
+      </c>
+      <c r="B166" t="s">
+        <v>179</v>
+      </c>
+      <c r="C166" t="s">
+        <v>501</v>
+      </c>
+      <c r="D166" t="s">
+        <v>502</v>
+      </c>
+      <c r="E166" t="s">
+        <v>439</v>
+      </c>
+      <c r="F166" s="12">
+        <v>7</v>
+      </c>
+      <c r="G166" s="13">
+        <v>5.804</v>
+      </c>
+      <c r="H166" s="14">
+        <v>1.196</v>
+      </c>
+      <c r="I166" s="15">
+        <v>20.6</v>
+      </c>
+      <c r="J166" s="12">
+        <v>52</v>
+      </c>
+      <c r="K166" s="16">
+        <v>-45</v>
+      </c>
+      <c r="L166" s="15">
+        <v>-86.5</v>
+      </c>
+      <c r="M166" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>493</v>
+      </c>
+      <c r="B167" t="s">
+        <v>179</v>
+      </c>
+      <c r="C167" t="s">
+        <v>501</v>
+      </c>
+      <c r="D167" t="s">
+        <v>502</v>
+      </c>
+      <c r="E167" t="s">
+        <v>431</v>
+      </c>
+      <c r="F167" s="12">
+        <v>15</v>
+      </c>
+      <c r="G167" s="13">
+        <v>11.877</v>
+      </c>
+      <c r="H167" s="14">
+        <v>3.123</v>
+      </c>
+      <c r="I167" s="15">
+        <v>26.3</v>
+      </c>
+      <c r="J167" s="12">
+        <v>148.5</v>
+      </c>
+      <c r="K167" s="16">
+        <v>-133.5</v>
+      </c>
+      <c r="L167" s="15">
+        <v>-89.9</v>
+      </c>
+      <c r="M167" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>493</v>
+      </c>
+      <c r="B168" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" t="s">
+        <v>501</v>
+      </c>
+      <c r="D168" t="s">
+        <v>502</v>
+      </c>
+      <c r="E168" t="s">
+        <v>571</v>
+      </c>
+      <c r="F168" s="12">
+        <v>37</v>
+      </c>
+      <c r="G168" s="13">
+        <v>24.985</v>
+      </c>
+      <c r="H168" s="14">
+        <v>12.015</v>
+      </c>
+      <c r="I168" s="15">
+        <v>48.1</v>
+      </c>
+      <c r="J168" s="12">
+        <v>161</v>
+      </c>
+      <c r="K168" s="16">
+        <v>-124</v>
+      </c>
+      <c r="L168" s="15">
+        <v>-77</v>
+      </c>
+      <c r="M168" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>493</v>
+      </c>
+      <c r="B169" t="s">
+        <v>179</v>
+      </c>
+      <c r="C169" t="s">
+        <v>501</v>
+      </c>
+      <c r="D169" t="s">
+        <v>502</v>
+      </c>
+      <c r="E169" t="s">
+        <v>573</v>
+      </c>
+      <c r="F169" s="12">
+        <v>66</v>
+      </c>
+      <c r="G169" s="13">
+        <v>40.216</v>
+      </c>
+      <c r="H169" s="14">
+        <v>25.784</v>
+      </c>
+      <c r="I169" s="15">
+        <v>64.1</v>
+      </c>
+      <c r="J169" s="12">
+        <v>303</v>
+      </c>
+      <c r="K169" s="16">
+        <v>-237</v>
+      </c>
+      <c r="L169" s="15">
+        <v>-78.2</v>
+      </c>
+      <c r="M169" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F170" s="8">
+        <v>12</v>
+      </c>
+      <c r="G170" s="9"/>
+      <c r="H170" s="10">
+        <v>3.158</v>
+      </c>
+      <c r="I170" s="11"/>
+      <c r="J170" s="8"/>
+      <c r="K170" s="10">
+        <v>-3.65</v>
+      </c>
+      <c r="L170" s="11"/>
+      <c r="M170" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>493</v>
+      </c>
+      <c r="B171" t="s">
+        <v>183</v>
+      </c>
+      <c r="C171" t="s">
+        <v>506</v>
+      </c>
+      <c r="D171" t="s">
+        <v>507</v>
+      </c>
+      <c r="E171" t="s">
+        <v>434</v>
+      </c>
+      <c r="F171" s="12">
+        <v>5.05</v>
+      </c>
+      <c r="G171" s="13">
+        <v>4.444</v>
+      </c>
+      <c r="H171" s="14">
+        <v>0.606</v>
+      </c>
+      <c r="I171" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="J171" s="12">
+        <v>9</v>
+      </c>
+      <c r="K171" s="16">
+        <v>-3.95</v>
+      </c>
+      <c r="L171" s="15">
+        <v>-43.9</v>
+      </c>
+      <c r="M171" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>493</v>
+      </c>
+      <c r="B172" t="s">
+        <v>183</v>
+      </c>
+      <c r="C172" t="s">
+        <v>506</v>
+      </c>
+      <c r="D172" t="s">
+        <v>507</v>
+      </c>
+      <c r="E172" t="s">
+        <v>454</v>
+      </c>
+      <c r="F172" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G172" s="13">
+        <v>3.143</v>
+      </c>
+      <c r="H172" s="14">
+        <v>0.157</v>
+      </c>
+      <c r="I172" s="15">
+        <v>5</v>
+      </c>
+      <c r="J172" s="12">
+        <v>11.167</v>
+      </c>
+      <c r="K172" s="16">
+        <v>-7.867</v>
+      </c>
+      <c r="L172" s="15">
+        <v>-70.4</v>
+      </c>
+      <c r="M172" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>493</v>
+      </c>
+      <c r="B173" t="s">
+        <v>183</v>
+      </c>
+      <c r="C173" t="s">
+        <v>506</v>
+      </c>
+      <c r="D173" t="s">
+        <v>507</v>
+      </c>
+      <c r="E173" t="s">
+        <v>423</v>
+      </c>
+      <c r="F173" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G173" s="13">
+        <v>3.318</v>
+      </c>
+      <c r="H173" s="14">
+        <v>0.232</v>
+      </c>
+      <c r="I173" s="15">
+        <v>7</v>
+      </c>
+      <c r="J173" s="12">
+        <v>19.625</v>
+      </c>
+      <c r="K173" s="16">
+        <v>-16.075</v>
+      </c>
+      <c r="L173" s="15">
+        <v>-81.9</v>
+      </c>
+      <c r="M173" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>493</v>
+      </c>
+      <c r="B174" t="s">
+        <v>183</v>
+      </c>
+      <c r="C174" t="s">
+        <v>506</v>
+      </c>
+      <c r="D174" t="s">
+        <v>507</v>
+      </c>
+      <c r="E174" t="s">
+        <v>439</v>
+      </c>
+      <c r="F174" s="12">
+        <v>5.75</v>
+      </c>
+      <c r="G174" s="13">
+        <v>4.9</v>
+      </c>
+      <c r="H174" s="14">
+        <v>0.85</v>
+      </c>
+      <c r="I174" s="15">
+        <v>17.4</v>
+      </c>
+      <c r="J174" s="12">
+        <v>42.8</v>
+      </c>
+      <c r="K174" s="16">
+        <v>-37.05</v>
+      </c>
+      <c r="L174" s="15">
+        <v>-86.6</v>
+      </c>
+      <c r="M174" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>493</v>
+      </c>
+      <c r="B175" t="s">
+        <v>183</v>
+      </c>
+      <c r="C175" t="s">
+        <v>506</v>
+      </c>
+      <c r="D175" t="s">
+        <v>507</v>
+      </c>
+      <c r="E175" t="s">
+        <v>431</v>
+      </c>
+      <c r="F175" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="G175" s="13">
+        <v>8.471</v>
+      </c>
+      <c r="H175" s="14">
+        <v>2.029</v>
+      </c>
+      <c r="I175" s="15">
+        <v>24</v>
+      </c>
+      <c r="J175" s="12">
+        <v>105</v>
+      </c>
+      <c r="K175" s="16">
+        <v>-94.5</v>
+      </c>
+      <c r="L175" s="15">
+        <v>-90</v>
+      </c>
+      <c r="M175" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>493</v>
+      </c>
+      <c r="B176" t="s">
+        <v>183</v>
+      </c>
+      <c r="C176" t="s">
+        <v>506</v>
+      </c>
+      <c r="D176" t="s">
+        <v>507</v>
+      </c>
+      <c r="E176" t="s">
+        <v>571</v>
+      </c>
+      <c r="F176" s="12">
+        <v>23</v>
+      </c>
+      <c r="G176" s="13">
+        <v>18.248</v>
+      </c>
+      <c r="H176" s="14">
+        <v>4.752</v>
+      </c>
+      <c r="I176" s="15">
+        <v>26</v>
+      </c>
+      <c r="J176" s="12">
+        <v>119</v>
+      </c>
+      <c r="K176" s="16">
+        <v>-96</v>
+      </c>
+      <c r="L176" s="15">
+        <v>-80.7</v>
+      </c>
+      <c r="M176" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>493</v>
+      </c>
+      <c r="B177" t="s">
+        <v>183</v>
+      </c>
+      <c r="C177" t="s">
+        <v>506</v>
+      </c>
+      <c r="D177" t="s">
+        <v>507</v>
+      </c>
+      <c r="E177" t="s">
+        <v>573</v>
+      </c>
+      <c r="F177" s="12">
+        <v>39</v>
+      </c>
+      <c r="G177" s="13">
+        <v>29.066</v>
+      </c>
+      <c r="H177" s="14">
+        <v>9.934</v>
+      </c>
+      <c r="I177" s="15">
+        <v>34.2</v>
+      </c>
+      <c r="J177" s="12">
+        <v>201</v>
+      </c>
+      <c r="K177" s="16">
+        <v>-162</v>
+      </c>
+      <c r="L177" s="15">
+        <v>-80.6</v>
+      </c>
+      <c r="M177" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F178" s="8">
+        <v>14</v>
+      </c>
+      <c r="G178" s="9"/>
+      <c r="H178" s="10">
+        <v>2.094</v>
+      </c>
+      <c r="I178" s="11"/>
+      <c r="J178" s="8"/>
+      <c r="K178" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L178" s="11"/>
+      <c r="M178" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>493</v>
+      </c>
+      <c r="B179" t="s">
+        <v>509</v>
+      </c>
+      <c r="C179" t="s">
+        <v>510</v>
+      </c>
+      <c r="D179" t="s">
+        <v>511</v>
+      </c>
+      <c r="E179" t="s">
+        <v>434</v>
+      </c>
+      <c r="F179" s="12">
+        <v>5.4</v>
+      </c>
+      <c r="G179" s="13">
+        <v>5.091</v>
+      </c>
+      <c r="H179" s="14">
+        <v>0.309</v>
+      </c>
+      <c r="I179" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="J179" s="12">
+        <v>11</v>
+      </c>
+      <c r="K179" s="16">
+        <v>-5.6</v>
+      </c>
+      <c r="L179" s="15">
+        <v>-50.9</v>
+      </c>
+      <c r="M179" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>493</v>
+      </c>
+      <c r="B180" t="s">
+        <v>509</v>
+      </c>
+      <c r="C180" t="s">
+        <v>510</v>
+      </c>
+      <c r="D180" t="s">
+        <v>511</v>
+      </c>
+      <c r="E180" t="s">
+        <v>454</v>
+      </c>
+      <c r="F180" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G180" s="13">
+        <v>3.204</v>
+      </c>
+      <c r="H180" s="14">
+        <v>0.396</v>
+      </c>
+      <c r="I180" s="15">
+        <v>12.4</v>
+      </c>
+      <c r="J180" s="12">
+        <v>13.917</v>
+      </c>
+      <c r="K180" s="16">
+        <v>-10.317</v>
+      </c>
+      <c r="L180" s="15">
+        <v>-74.1</v>
+      </c>
+      <c r="M180" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>493</v>
+      </c>
+      <c r="B181" t="s">
+        <v>509</v>
+      </c>
+      <c r="C181" t="s">
+        <v>510</v>
+      </c>
+      <c r="D181" t="s">
+        <v>511</v>
+      </c>
+      <c r="E181" t="s">
+        <v>423</v>
+      </c>
+      <c r="F181" s="12">
+        <v>3.35</v>
+      </c>
+      <c r="G181" s="13">
+        <v>3.197</v>
+      </c>
+      <c r="H181" s="14">
+        <v>0.153</v>
+      </c>
+      <c r="I181" s="15">
+        <v>4.8</v>
+      </c>
+      <c r="J181" s="12">
+        <v>24.875</v>
+      </c>
+      <c r="K181" s="16">
+        <v>-21.525</v>
+      </c>
+      <c r="L181" s="15">
+        <v>-86.5</v>
+      </c>
+      <c r="M181" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>493</v>
+      </c>
+      <c r="B182" t="s">
+        <v>509</v>
+      </c>
+      <c r="C182" t="s">
+        <v>510</v>
+      </c>
+      <c r="D182" t="s">
+        <v>511</v>
+      </c>
+      <c r="E182" t="s">
+        <v>439</v>
+      </c>
+      <c r="F182" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="G182" s="13">
+        <v>4.555</v>
+      </c>
+      <c r="H182" s="14">
+        <v>0.945</v>
+      </c>
+      <c r="I182" s="15">
+        <v>20.8</v>
+      </c>
+      <c r="J182" s="12">
+        <v>59.1</v>
+      </c>
+      <c r="K182" s="16">
+        <v>-53.6</v>
+      </c>
+      <c r="L182" s="15">
+        <v>-90.7</v>
+      </c>
+      <c r="M182" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>493</v>
+      </c>
+      <c r="B183" t="s">
+        <v>509</v>
+      </c>
+      <c r="C183" t="s">
+        <v>510</v>
+      </c>
+      <c r="D183" t="s">
+        <v>511</v>
+      </c>
+      <c r="E183" t="s">
+        <v>431</v>
+      </c>
+      <c r="F183" s="12">
+        <v>9.6</v>
+      </c>
+      <c r="G183" s="13">
+        <v>8.202</v>
+      </c>
+      <c r="H183" s="14">
+        <v>1.398</v>
+      </c>
+      <c r="I183" s="15">
+        <v>17</v>
+      </c>
+      <c r="J183" s="12">
+        <v>141.5</v>
+      </c>
+      <c r="K183" s="16">
+        <v>-131.9</v>
+      </c>
+      <c r="L183" s="15">
+        <v>-93.2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>493</v>
+      </c>
+      <c r="B184" t="s">
+        <v>509</v>
+      </c>
+      <c r="C184" t="s">
+        <v>510</v>
+      </c>
+      <c r="D184" t="s">
+        <v>511</v>
+      </c>
+      <c r="E184" t="s">
+        <v>571</v>
+      </c>
+      <c r="F184" s="12">
+        <v>19</v>
+      </c>
+      <c r="G184" s="13">
+        <v>16.111</v>
+      </c>
+      <c r="H184" s="14">
+        <v>2.889</v>
+      </c>
+      <c r="I184" s="15">
+        <v>17.9</v>
+      </c>
+      <c r="J184" s="12">
+        <v>150</v>
+      </c>
+      <c r="K184" s="16">
+        <v>-131</v>
+      </c>
+      <c r="L184" s="15">
+        <v>-87.3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>493</v>
+      </c>
+      <c r="B185" t="s">
+        <v>509</v>
+      </c>
+      <c r="C185" t="s">
+        <v>510</v>
+      </c>
+      <c r="D185" t="s">
+        <v>511</v>
+      </c>
+      <c r="E185" t="s">
+        <v>573</v>
+      </c>
+      <c r="F185" s="12">
+        <v>30</v>
+      </c>
+      <c r="G185" s="13">
+        <v>23.08</v>
+      </c>
+      <c r="H185" s="14">
+        <v>6.92</v>
+      </c>
+      <c r="I185" s="15">
+        <v>30</v>
+      </c>
+      <c r="J185" s="12">
+        <v>219</v>
+      </c>
+      <c r="K185" s="16">
+        <v>-189</v>
+      </c>
+      <c r="L185" s="15">
+        <v>-86.3</v>
+      </c>
+      <c r="M185" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F186" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="G186" s="9"/>
+      <c r="H186" s="10">
+        <v>2.819</v>
+      </c>
+      <c r="I186" s="11"/>
+      <c r="J186" s="8"/>
+      <c r="K186" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L186" s="11"/>
+      <c r="M186" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>493</v>
+      </c>
+      <c r="B187" t="s">
+        <v>513</v>
+      </c>
+      <c r="C187" t="s">
+        <v>514</v>
+      </c>
+      <c r="D187" t="s">
+        <v>515</v>
+      </c>
+      <c r="E187" t="s">
+        <v>434</v>
+      </c>
+      <c r="F187" s="12">
+        <v>5.1</v>
+      </c>
+      <c r="G187" s="13">
+        <v>4.667</v>
+      </c>
+      <c r="H187" s="14">
+        <v>0.433</v>
+      </c>
+      <c r="I187" s="15">
+        <v>9.3</v>
+      </c>
+      <c r="J187" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="K187" s="16">
+        <v>-5.4</v>
+      </c>
+      <c r="L187" s="15">
+        <v>-51.4</v>
+      </c>
+      <c r="M187" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>493</v>
+      </c>
+      <c r="B188" t="s">
+        <v>513</v>
+      </c>
+      <c r="C188" t="s">
+        <v>514</v>
+      </c>
+      <c r="D188" t="s">
+        <v>515</v>
+      </c>
+      <c r="E188" t="s">
+        <v>454</v>
+      </c>
+      <c r="F188" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="G188" s="13">
+        <v>3.332</v>
+      </c>
+      <c r="H188" s="14">
+        <v>0.118</v>
+      </c>
+      <c r="I188" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="J188" s="12">
+        <v>15.333</v>
+      </c>
+      <c r="K188" s="16">
+        <v>-11.883</v>
+      </c>
+      <c r="L188" s="15">
+        <v>-77.5</v>
+      </c>
+      <c r="M188" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>493</v>
+      </c>
+      <c r="B189" t="s">
+        <v>513</v>
+      </c>
+      <c r="C189" t="s">
+        <v>514</v>
+      </c>
+      <c r="D189" t="s">
+        <v>515</v>
+      </c>
+      <c r="E189" t="s">
+        <v>423</v>
+      </c>
+      <c r="F189" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G189" s="13">
+        <v>3.241</v>
+      </c>
+      <c r="H189" s="14">
+        <v>0.259</v>
+      </c>
+      <c r="I189" s="15">
+        <v>8</v>
+      </c>
+      <c r="J189" s="12">
+        <v>28.875</v>
+      </c>
+      <c r="K189" s="16">
+        <v>-25.375</v>
+      </c>
+      <c r="L189" s="15">
+        <v>-87.9</v>
+      </c>
+      <c r="M189" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>493</v>
+      </c>
+      <c r="B190" t="s">
+        <v>513</v>
+      </c>
+      <c r="C190" t="s">
+        <v>514</v>
+      </c>
+      <c r="D190" t="s">
+        <v>515</v>
+      </c>
+      <c r="E190" t="s">
+        <v>439</v>
+      </c>
+      <c r="F190" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="G190" s="13">
+        <v>4.654</v>
+      </c>
+      <c r="H190" s="14">
+        <v>0.946</v>
+      </c>
+      <c r="I190" s="15">
+        <v>20.3</v>
+      </c>
+      <c r="J190" s="12">
+        <v>80.5</v>
+      </c>
+      <c r="K190" s="16">
+        <v>-74.9</v>
+      </c>
+      <c r="L190" s="15">
+        <v>-93</v>
+      </c>
+      <c r="M190" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>493</v>
+      </c>
+      <c r="B191" t="s">
+        <v>513</v>
+      </c>
+      <c r="C191" t="s">
+        <v>514</v>
+      </c>
+      <c r="D191" t="s">
+        <v>515</v>
+      </c>
+      <c r="E191" t="s">
+        <v>431</v>
+      </c>
+      <c r="F191" s="12">
+        <v>9.8</v>
+      </c>
+      <c r="G191" s="13">
+        <v>7.867</v>
+      </c>
+      <c r="H191" s="14">
+        <v>1.933</v>
+      </c>
+      <c r="I191" s="15">
+        <v>24.6</v>
+      </c>
+      <c r="J191" s="12">
+        <v>188.833</v>
+      </c>
+      <c r="K191" s="16">
+        <v>-179.033</v>
+      </c>
+      <c r="L191" s="15">
+        <v>-94.8</v>
+      </c>
+      <c r="M191" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>493</v>
+      </c>
+      <c r="B192" t="s">
+        <v>513</v>
+      </c>
+      <c r="C192" t="s">
+        <v>514</v>
+      </c>
+      <c r="D192" t="s">
+        <v>515</v>
+      </c>
+      <c r="E192" t="s">
+        <v>571</v>
+      </c>
+      <c r="F192" s="12">
+        <v>21</v>
+      </c>
+      <c r="G192" s="13">
+        <v>17.303</v>
+      </c>
+      <c r="H192" s="14">
+        <v>3.697</v>
+      </c>
+      <c r="I192" s="15">
+        <v>21.4</v>
+      </c>
+      <c r="J192" s="12">
+        <v>211</v>
+      </c>
+      <c r="K192" s="16">
+        <v>-190</v>
+      </c>
+      <c r="L192" s="15">
+        <v>-90</v>
+      </c>
+      <c r="M192" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>493</v>
+      </c>
+      <c r="B193" t="s">
+        <v>513</v>
+      </c>
+      <c r="C193" t="s">
+        <v>514</v>
+      </c>
+      <c r="D193" t="s">
+        <v>515</v>
+      </c>
+      <c r="E193" t="s">
+        <v>573</v>
+      </c>
+      <c r="F193" s="12">
+        <v>33</v>
+      </c>
+      <c r="G193" s="13">
+        <v>23.641</v>
+      </c>
+      <c r="H193" s="14">
+        <v>9.359</v>
+      </c>
+      <c r="I193" s="15">
+        <v>39.6</v>
+      </c>
+      <c r="J193" s="12">
+        <v>311.6</v>
+      </c>
+      <c r="K193" s="16">
+        <v>-278.6</v>
+      </c>
+      <c r="L193" s="15">
+        <v>-89.4</v>
+      </c>
+      <c r="M193" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F194" s="8">
+        <v>14</v>
+      </c>
+      <c r="G194" s="9"/>
+      <c r="H194" s="10">
+        <v>0.834</v>
+      </c>
+      <c r="I194" s="11"/>
+      <c r="J194" s="8"/>
+      <c r="K194" s="10">
+        <v>-4.582</v>
+      </c>
+      <c r="L194" s="11"/>
+      <c r="M194" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>493</v>
+      </c>
+      <c r="B195" t="s">
+        <v>520</v>
+      </c>
+      <c r="C195" t="s">
+        <v>521</v>
+      </c>
+      <c r="D195" t="s">
+        <v>522</v>
+      </c>
+      <c r="E195" t="s">
+        <v>434</v>
+      </c>
+      <c r="F195" s="12">
+        <v>5.7</v>
+      </c>
+      <c r="G195" s="13">
+        <v>5.169</v>
+      </c>
+      <c r="H195" s="14">
+        <v>0.531</v>
+      </c>
+      <c r="I195" s="15">
+        <v>10.3</v>
+      </c>
+      <c r="J195" s="12">
+        <v>10.375</v>
+      </c>
+      <c r="K195" s="16">
+        <v>-4.675</v>
+      </c>
+      <c r="L195" s="15">
+        <v>-45.1</v>
+      </c>
+      <c r="M195" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>493</v>
+      </c>
+      <c r="B196" t="s">
+        <v>520</v>
+      </c>
+      <c r="C196" t="s">
+        <v>521</v>
+      </c>
+      <c r="D196" t="s">
+        <v>522</v>
+      </c>
+      <c r="E196" t="s">
+        <v>454</v>
+      </c>
+      <c r="F196" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G196" s="13">
+        <v>3.214</v>
+      </c>
+      <c r="H196" s="14">
+        <v>0.286</v>
+      </c>
+      <c r="I196" s="15">
+        <v>8.9</v>
+      </c>
+      <c r="J196" s="12">
+        <v>11.333</v>
+      </c>
+      <c r="K196" s="16">
+        <v>-7.833</v>
+      </c>
+      <c r="L196" s="15">
+        <v>-69.1</v>
+      </c>
+      <c r="M196" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>493</v>
+      </c>
+      <c r="B197" t="s">
+        <v>520</v>
+      </c>
+      <c r="C197" t="s">
+        <v>521</v>
+      </c>
+      <c r="D197" t="s">
+        <v>522</v>
+      </c>
+      <c r="E197" t="s">
+        <v>423</v>
+      </c>
+      <c r="F197" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="G197" s="13">
+        <v>3.269</v>
+      </c>
+      <c r="H197" s="14">
+        <v>0.181</v>
+      </c>
+      <c r="I197" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="J197" s="12">
+        <v>19</v>
+      </c>
+      <c r="K197" s="16">
+        <v>-15.55</v>
+      </c>
+      <c r="L197" s="15">
+        <v>-81.8</v>
+      </c>
+      <c r="M197" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>493</v>
+      </c>
+      <c r="B198" t="s">
+        <v>520</v>
+      </c>
+      <c r="C198" t="s">
+        <v>521</v>
+      </c>
+      <c r="D198" t="s">
+        <v>522</v>
+      </c>
+      <c r="E198" t="s">
+        <v>439</v>
+      </c>
+      <c r="F198" s="12">
+        <v>5.35</v>
+      </c>
+      <c r="G198" s="13">
+        <v>4.591</v>
+      </c>
+      <c r="H198" s="14">
+        <v>0.759</v>
+      </c>
+      <c r="I198" s="15">
+        <v>16.5</v>
+      </c>
+      <c r="J198" s="12">
+        <v>43</v>
+      </c>
+      <c r="K198" s="16">
+        <v>-37.65</v>
+      </c>
+      <c r="L198" s="15">
+        <v>-87.6</v>
+      </c>
+      <c r="M198" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>493</v>
+      </c>
+      <c r="B199" t="s">
+        <v>520</v>
+      </c>
+      <c r="C199" t="s">
+        <v>521</v>
+      </c>
+      <c r="D199" t="s">
+        <v>522</v>
+      </c>
+      <c r="E199" t="s">
+        <v>431</v>
+      </c>
+      <c r="F199" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="G199" s="13">
+        <v>7.572</v>
+      </c>
+      <c r="H199" s="14">
+        <v>1.928</v>
+      </c>
+      <c r="I199" s="15">
+        <v>25.5</v>
+      </c>
+      <c r="J199" s="12">
+        <v>95.667</v>
+      </c>
+      <c r="K199" s="16">
+        <v>-86.167</v>
+      </c>
+      <c r="L199" s="15">
+        <v>-90.1</v>
+      </c>
+      <c r="M199" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>493</v>
+      </c>
+      <c r="B200" t="s">
+        <v>520</v>
+      </c>
+      <c r="C200" t="s">
+        <v>521</v>
+      </c>
+      <c r="D200" t="s">
+        <v>522</v>
+      </c>
+      <c r="E200" t="s">
+        <v>571</v>
+      </c>
+      <c r="F200" s="12">
+        <v>18</v>
+      </c>
+      <c r="G200" s="13">
+        <v>14.757</v>
+      </c>
+      <c r="H200" s="14">
+        <v>3.243</v>
+      </c>
+      <c r="I200" s="15">
+        <v>22</v>
+      </c>
+      <c r="J200" s="12">
+        <v>95</v>
+      </c>
+      <c r="K200" s="16">
+        <v>-77</v>
+      </c>
+      <c r="L200" s="15">
+        <v>-81</v>
+      </c>
+      <c r="M200" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>493</v>
+      </c>
+      <c r="B201" t="s">
+        <v>520</v>
+      </c>
+      <c r="C201" t="s">
+        <v>521</v>
+      </c>
+      <c r="D201" t="s">
+        <v>522</v>
+      </c>
+      <c r="E201" t="s">
+        <v>573</v>
+      </c>
+      <c r="F201" s="12">
+        <v>29</v>
+      </c>
+      <c r="G201" s="13">
+        <v>25.105</v>
+      </c>
+      <c r="H201" s="14">
+        <v>3.895</v>
+      </c>
+      <c r="I201" s="15">
+        <v>15.5</v>
+      </c>
+      <c r="J201" s="12">
+        <v>175</v>
+      </c>
+      <c r="K201" s="16">
+        <v>-146</v>
+      </c>
+      <c r="L201" s="15">
+        <v>-83.4</v>
+      </c>
+      <c r="M201" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F202" s="8">
+        <v>18</v>
+      </c>
+      <c r="G202" s="9"/>
+      <c r="H202" s="10">
+        <v>2.022</v>
+      </c>
+      <c r="I202" s="11"/>
+      <c r="J202" s="8"/>
+      <c r="K202" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L202" s="11"/>
+      <c r="M202" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>526</v>
+      </c>
+      <c r="B203" t="s">
+        <v>189</v>
+      </c>
+      <c r="C203" t="s">
+        <v>527</v>
+      </c>
+      <c r="D203" t="s">
+        <v>528</v>
+      </c>
+      <c r="E203" t="s">
+        <v>434</v>
+      </c>
+      <c r="F203" s="12">
+        <v>6</v>
+      </c>
+      <c r="G203" s="13">
+        <v>5.551</v>
+      </c>
+      <c r="H203" s="14">
+        <v>0.449</v>
+      </c>
+      <c r="I203" s="15">
+        <v>8.1</v>
+      </c>
+      <c r="J203" s="12">
+        <v>12.25</v>
+      </c>
+      <c r="K203" s="16">
+        <v>-6.25</v>
+      </c>
+      <c r="L203" s="15">
+        <v>-51</v>
+      </c>
+      <c r="M203" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>526</v>
+      </c>
+      <c r="B204" t="s">
+        <v>189</v>
+      </c>
+      <c r="C204" t="s">
+        <v>527</v>
+      </c>
+      <c r="D204" t="s">
+        <v>528</v>
+      </c>
+      <c r="E204" t="s">
+        <v>454</v>
+      </c>
+      <c r="F204" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="G204" s="13">
+        <v>3.598</v>
+      </c>
+      <c r="H204" s="14">
+        <v>0.502</v>
+      </c>
+      <c r="I204" s="15">
+        <v>14</v>
+      </c>
+      <c r="J204" s="12">
+        <v>16.417</v>
+      </c>
+      <c r="K204" s="16">
+        <v>-12.317</v>
+      </c>
+      <c r="L204" s="15">
+        <v>-75</v>
+      </c>
+      <c r="M204" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>526</v>
+      </c>
+      <c r="B205" t="s">
+        <v>189</v>
+      </c>
+      <c r="C205" t="s">
+        <v>527</v>
+      </c>
+      <c r="D205" t="s">
+        <v>528</v>
+      </c>
+      <c r="E205" t="s">
+        <v>423</v>
+      </c>
+      <c r="F205" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G205" s="13">
+        <v>3.313</v>
+      </c>
+      <c r="H205" s="14">
+        <v>0.237</v>
+      </c>
+      <c r="I205" s="15">
+        <v>7.2</v>
+      </c>
+      <c r="J205" s="12">
+        <v>31.125</v>
+      </c>
+      <c r="K205" s="16">
+        <v>-27.575</v>
+      </c>
+      <c r="L205" s="15">
+        <v>-88.6</v>
+      </c>
+      <c r="M205" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>526</v>
+      </c>
+      <c r="B206" t="s">
+        <v>189</v>
+      </c>
+      <c r="C206" t="s">
+        <v>527</v>
+      </c>
+      <c r="D206" t="s">
+        <v>528</v>
+      </c>
+      <c r="E206" t="s">
+        <v>439</v>
+      </c>
+      <c r="F206" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="G206" s="13">
+        <v>4.202</v>
+      </c>
+      <c r="H206" s="14">
+        <v>0.548</v>
+      </c>
+      <c r="I206" s="15">
+        <v>13</v>
+      </c>
+      <c r="J206" s="12">
+        <v>78.5</v>
+      </c>
+      <c r="K206" s="16">
+        <v>-73.75</v>
+      </c>
+      <c r="L206" s="15">
+        <v>-93.9</v>
+      </c>
+      <c r="M206" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>526</v>
+      </c>
+      <c r="B207" t="s">
+        <v>189</v>
+      </c>
+      <c r="C207" t="s">
+        <v>527</v>
+      </c>
+      <c r="D207" t="s">
+        <v>528</v>
+      </c>
+      <c r="E207" t="s">
+        <v>431</v>
+      </c>
+      <c r="F207" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="G207" s="13">
+        <v>6.755</v>
+      </c>
+      <c r="H207" s="14">
+        <v>0.745</v>
+      </c>
+      <c r="I207" s="15">
+        <v>11</v>
+      </c>
+      <c r="J207" s="12">
+        <v>164.167</v>
+      </c>
+      <c r="K207" s="16">
+        <v>-156.667</v>
+      </c>
+      <c r="L207" s="15">
+        <v>-95.4</v>
+      </c>
+      <c r="M207" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>526</v>
+      </c>
+      <c r="B208" t="s">
+        <v>189</v>
+      </c>
+      <c r="C208" t="s">
+        <v>527</v>
+      </c>
+      <c r="D208" t="s">
+        <v>528</v>
+      </c>
+      <c r="E208" t="s">
+        <v>571</v>
+      </c>
+      <c r="F208" s="12">
+        <v>15</v>
+      </c>
+      <c r="G208" s="13">
+        <v>12.915</v>
+      </c>
+      <c r="H208" s="14">
+        <v>2.085</v>
+      </c>
+      <c r="I208" s="15">
+        <v>16.1</v>
+      </c>
+      <c r="J208" s="12">
+        <v>146.6</v>
+      </c>
+      <c r="K208" s="16">
+        <v>-131.6</v>
+      </c>
+      <c r="L208" s="15">
+        <v>-89.8</v>
+      </c>
+      <c r="M208" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>526</v>
+      </c>
+      <c r="B209" t="s">
+        <v>189</v>
+      </c>
+      <c r="C209" t="s">
+        <v>527</v>
+      </c>
+      <c r="D209" t="s">
+        <v>528</v>
+      </c>
+      <c r="E209" t="s">
+        <v>573</v>
+      </c>
+      <c r="F209" s="12">
+        <v>21.5</v>
+      </c>
+      <c r="G209" s="13">
+        <v>16.565</v>
+      </c>
+      <c r="H209" s="14">
+        <v>4.935</v>
+      </c>
+      <c r="I209" s="15">
+        <v>29.8</v>
+      </c>
+      <c r="J209" s="12">
+        <v>192.6</v>
+      </c>
+      <c r="K209" s="16">
+        <v>-171.1</v>
+      </c>
+      <c r="L209" s="15">
+        <v>-88.8</v>
+      </c>
+      <c r="M209" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F210" s="8">
+        <v>13</v>
+      </c>
+      <c r="G210" s="9"/>
+      <c r="H210" s="10">
+        <v>1.47</v>
+      </c>
+      <c r="I210" s="11"/>
+      <c r="J210" s="8"/>
+      <c r="K210" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L210" s="11"/>
+      <c r="M210" s="4" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>526</v>
+      </c>
+      <c r="B211" t="s">
+        <v>195</v>
+      </c>
+      <c r="C211" t="s">
+        <v>531</v>
+      </c>
+      <c r="D211" t="s">
+        <v>532</v>
+      </c>
+      <c r="E211" t="s">
+        <v>434</v>
+      </c>
+      <c r="F211" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="G211" s="13">
+        <v>4.554</v>
+      </c>
+      <c r="H211" s="14">
+        <v>0.196</v>
+      </c>
+      <c r="I211" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="J211" s="12">
+        <v>10.375</v>
+      </c>
+      <c r="K211" s="16">
+        <v>-5.625</v>
+      </c>
+      <c r="L211" s="15">
+        <v>-54.2</v>
+      </c>
+      <c r="M211" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>526</v>
+      </c>
+      <c r="B212" t="s">
+        <v>195</v>
+      </c>
+      <c r="C212" t="s">
+        <v>531</v>
+      </c>
+      <c r="D212" t="s">
+        <v>532</v>
+      </c>
+      <c r="E212" t="s">
+        <v>454</v>
+      </c>
+      <c r="F212" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G212" s="13">
+        <v>3.21</v>
+      </c>
+      <c r="H212" s="14">
+        <v>0.19</v>
+      </c>
+      <c r="I212" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="J212" s="12">
+        <v>15.833</v>
+      </c>
+      <c r="K212" s="16">
+        <v>-12.433</v>
+      </c>
+      <c r="L212" s="15">
+        <v>-78.5</v>
+      </c>
+      <c r="M212" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>526</v>
+      </c>
+      <c r="B213" t="s">
+        <v>195</v>
+      </c>
+      <c r="C213" t="s">
+        <v>531</v>
+      </c>
+      <c r="D213" t="s">
+        <v>532</v>
+      </c>
+      <c r="E213" t="s">
+        <v>423</v>
+      </c>
+      <c r="F213" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="G213" s="13">
+        <v>3.311</v>
+      </c>
+      <c r="H213" s="14">
+        <v>0.339</v>
+      </c>
+      <c r="I213" s="15">
+        <v>10.2</v>
+      </c>
+      <c r="J213" s="12">
+        <v>31.375</v>
+      </c>
+      <c r="K213" s="16">
+        <v>-27.725</v>
+      </c>
+      <c r="L213" s="15">
+        <v>-88.4</v>
+      </c>
+      <c r="M213" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>526</v>
+      </c>
+      <c r="B214" t="s">
+        <v>195</v>
+      </c>
+      <c r="C214" t="s">
+        <v>531</v>
+      </c>
+      <c r="D214" t="s">
+        <v>532</v>
+      </c>
+      <c r="E214" t="s">
+        <v>439</v>
+      </c>
+      <c r="F214" s="12">
+        <v>5.75</v>
+      </c>
+      <c r="G214" s="13">
+        <v>4.72</v>
+      </c>
+      <c r="H214" s="14">
+        <v>1.03</v>
+      </c>
+      <c r="I214" s="15">
+        <v>21.8</v>
+      </c>
+      <c r="J214" s="12">
+        <v>90.4</v>
+      </c>
+      <c r="K214" s="16">
+        <v>-84.65</v>
+      </c>
+      <c r="L214" s="15">
+        <v>-93.6</v>
+      </c>
+      <c r="M214" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>526</v>
+      </c>
+      <c r="B215" t="s">
+        <v>195</v>
+      </c>
+      <c r="C215" t="s">
+        <v>531</v>
+      </c>
+      <c r="D215" t="s">
+        <v>532</v>
+      </c>
+      <c r="E215" t="s">
+        <v>431</v>
+      </c>
+      <c r="F215" s="12">
+        <v>10</v>
+      </c>
+      <c r="G215" s="13">
+        <v>7.894</v>
+      </c>
+      <c r="H215" s="14">
+        <v>2.106</v>
+      </c>
+      <c r="I215" s="15">
+        <v>26.7</v>
+      </c>
+      <c r="J215" s="12">
+        <v>224.333</v>
+      </c>
+      <c r="K215" s="16">
+        <v>-214.333</v>
+      </c>
+      <c r="L215" s="15">
+        <v>-95.5</v>
+      </c>
+      <c r="M215" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>526</v>
+      </c>
+      <c r="B216" t="s">
+        <v>195</v>
+      </c>
+      <c r="C216" t="s">
+        <v>531</v>
+      </c>
+      <c r="D216" t="s">
+        <v>532</v>
+      </c>
+      <c r="E216" t="s">
+        <v>571</v>
+      </c>
+      <c r="F216" s="12">
+        <v>22</v>
+      </c>
+      <c r="G216" s="13">
+        <v>18.48</v>
+      </c>
+      <c r="H216" s="14">
+        <v>3.52</v>
+      </c>
+      <c r="I216" s="15">
+        <v>19.1</v>
+      </c>
+      <c r="J216" s="12">
+        <v>248</v>
+      </c>
+      <c r="K216" s="16">
+        <v>-226</v>
+      </c>
+      <c r="L216" s="15">
+        <v>-91.1</v>
+      </c>
+      <c r="M216" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>526</v>
+      </c>
+      <c r="B217" t="s">
+        <v>195</v>
+      </c>
+      <c r="C217" t="s">
+        <v>531</v>
+      </c>
+      <c r="D217" t="s">
+        <v>532</v>
+      </c>
+      <c r="E217" t="s">
+        <v>573</v>
+      </c>
+      <c r="F217" s="12">
+        <v>34</v>
+      </c>
+      <c r="G217" s="13">
+        <v>26.926</v>
+      </c>
+      <c r="H217" s="14">
+        <v>7.074</v>
+      </c>
+      <c r="I217" s="15">
+        <v>26.3</v>
+      </c>
+      <c r="J217" s="12">
+        <v>353</v>
+      </c>
+      <c r="K217" s="16">
+        <v>-319</v>
+      </c>
+      <c r="L217" s="15">
+        <v>-90.4</v>
+      </c>
+      <c r="M217" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F218" s="8">
+        <v>14</v>
+      </c>
+      <c r="G218" s="9"/>
+      <c r="H218" s="10">
+        <v>0.59</v>
+      </c>
+      <c r="I218" s="11"/>
+      <c r="J218" s="8"/>
+      <c r="K218" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L218" s="11"/>
+      <c r="M218" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>526</v>
+      </c>
+      <c r="B219" t="s">
+        <v>199</v>
+      </c>
+      <c r="C219" t="s">
+        <v>537</v>
+      </c>
+      <c r="D219" t="s">
+        <v>538</v>
+      </c>
+      <c r="E219" t="s">
+        <v>434</v>
+      </c>
+      <c r="F219" s="12">
+        <v>5.3</v>
+      </c>
+      <c r="G219" s="13">
+        <v>5.023</v>
+      </c>
+      <c r="H219" s="14">
+        <v>0.277</v>
+      </c>
+      <c r="I219" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="J219" s="12">
+        <v>10.75</v>
+      </c>
+      <c r="K219" s="16">
+        <v>-5.45</v>
+      </c>
+      <c r="L219" s="15">
+        <v>-50.7</v>
+      </c>
+      <c r="M219" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>526</v>
+      </c>
+      <c r="B220" t="s">
+        <v>199</v>
+      </c>
+      <c r="C220" t="s">
+        <v>537</v>
+      </c>
+      <c r="D220" t="s">
+        <v>538</v>
+      </c>
+      <c r="E220" t="s">
+        <v>454</v>
+      </c>
+      <c r="F220" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G220" s="13">
+        <v>3.488</v>
+      </c>
+      <c r="H220" s="14">
+        <v>0.212</v>
+      </c>
+      <c r="I220" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="J220" s="12">
+        <v>13.75</v>
+      </c>
+      <c r="K220" s="16">
+        <v>-10.05</v>
+      </c>
+      <c r="L220" s="15">
+        <v>-73.1</v>
+      </c>
+      <c r="M220" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>526</v>
+      </c>
+      <c r="B221" t="s">
+        <v>199</v>
+      </c>
+      <c r="C221" t="s">
+        <v>537</v>
+      </c>
+      <c r="D221" t="s">
+        <v>538</v>
+      </c>
+      <c r="E221" t="s">
+        <v>423</v>
+      </c>
+      <c r="F221" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G221" s="13">
+        <v>3.21</v>
+      </c>
+      <c r="H221" s="14">
+        <v>0.39</v>
+      </c>
+      <c r="I221" s="15">
+        <v>12.2</v>
+      </c>
+      <c r="J221" s="12">
+        <v>23.563</v>
+      </c>
+      <c r="K221" s="16">
+        <v>-19.963</v>
+      </c>
+      <c r="L221" s="15">
+        <v>-84.7</v>
+      </c>
+      <c r="M221" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>526</v>
+      </c>
+      <c r="B222" t="s">
+        <v>199</v>
+      </c>
+      <c r="C222" t="s">
+        <v>537</v>
+      </c>
+      <c r="D222" t="s">
+        <v>538</v>
+      </c>
+      <c r="E222" t="s">
+        <v>439</v>
+      </c>
+      <c r="F222" s="12">
+        <v>5.25</v>
+      </c>
+      <c r="G222" s="13">
+        <v>4.448</v>
+      </c>
+      <c r="H222" s="14">
+        <v>0.802</v>
+      </c>
+      <c r="I222" s="15">
+        <v>18</v>
+      </c>
+      <c r="J222" s="12">
+        <v>53.6</v>
+      </c>
+      <c r="K222" s="16">
+        <v>-48.35</v>
+      </c>
+      <c r="L222" s="15">
+        <v>-90.2</v>
+      </c>
+      <c r="M222" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>526</v>
+      </c>
+      <c r="B223" t="s">
+        <v>199</v>
+      </c>
+      <c r="C223" t="s">
+        <v>537</v>
+      </c>
+      <c r="D223" t="s">
+        <v>538</v>
+      </c>
+      <c r="E223" t="s">
+        <v>431</v>
+      </c>
+      <c r="F223" s="12">
+        <v>9</v>
+      </c>
+      <c r="G223" s="13">
+        <v>7.508</v>
+      </c>
+      <c r="H223" s="14">
+        <v>1.492</v>
+      </c>
+      <c r="I223" s="15">
+        <v>19.9</v>
+      </c>
+      <c r="J223" s="12">
+        <v>134.333</v>
+      </c>
+      <c r="K223" s="16">
+        <v>-125.333</v>
+      </c>
+      <c r="L223" s="15">
+        <v>-93.3</v>
+      </c>
+      <c r="M223" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>526</v>
+      </c>
+      <c r="B224" t="s">
+        <v>199</v>
+      </c>
+      <c r="C224" t="s">
+        <v>537</v>
+      </c>
+      <c r="D224" t="s">
+        <v>538</v>
+      </c>
+      <c r="E224" t="s">
+        <v>571</v>
+      </c>
+      <c r="F224" s="12">
+        <v>18</v>
+      </c>
+      <c r="G224" s="13">
+        <v>14.771</v>
+      </c>
+      <c r="H224" s="14">
+        <v>3.229</v>
+      </c>
+      <c r="I224" s="15">
+        <v>21.9</v>
+      </c>
+      <c r="J224" s="12">
+        <v>127</v>
+      </c>
+      <c r="K224" s="16">
+        <v>-109</v>
+      </c>
+      <c r="L224" s="15">
+        <v>-85.8</v>
+      </c>
+      <c r="M224" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>526</v>
+      </c>
+      <c r="B225" t="s">
+        <v>199</v>
+      </c>
+      <c r="C225" t="s">
+        <v>537</v>
+      </c>
+      <c r="D225" t="s">
+        <v>538</v>
+      </c>
+      <c r="E225" t="s">
+        <v>573</v>
+      </c>
+      <c r="F225" s="12">
+        <v>26</v>
+      </c>
+      <c r="G225" s="13">
+        <v>22.167</v>
+      </c>
+      <c r="H225" s="14">
+        <v>3.833</v>
+      </c>
+      <c r="I225" s="15">
+        <v>17.3</v>
+      </c>
+      <c r="J225" s="12">
+        <v>197</v>
+      </c>
+      <c r="K225" s="16">
+        <v>-171</v>
+      </c>
+      <c r="L225" s="15">
+        <v>-86.8</v>
+      </c>
+      <c r="M225" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F226" s="8">
+        <v>11</v>
+      </c>
+      <c r="G226" s="9"/>
+      <c r="H226" s="10">
+        <v>3.589</v>
+      </c>
+      <c r="I226" s="11"/>
+      <c r="J226" s="8"/>
+      <c r="K226" s="10">
+        <v>-4.1</v>
+      </c>
+      <c r="L226" s="11"/>
+      <c r="M226" s="4" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>526</v>
+      </c>
+      <c r="B227" t="s">
+        <v>203</v>
+      </c>
+      <c r="C227" t="s">
+        <v>145</v>
+      </c>
+      <c r="D227" t="s">
+        <v>543</v>
+      </c>
+      <c r="E227" t="s">
+        <v>434</v>
+      </c>
+      <c r="F227" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="G227" s="13">
+        <v>4.286</v>
+      </c>
+      <c r="H227" s="14">
+        <v>0.164</v>
+      </c>
+      <c r="I227" s="15">
+        <v>3.8</v>
+      </c>
+      <c r="J227" s="12">
+        <v>8.75</v>
+      </c>
+      <c r="K227" s="16">
+        <v>-4.3</v>
+      </c>
+      <c r="L227" s="15">
+        <v>-49.1</v>
+      </c>
+      <c r="M227" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>526</v>
+      </c>
+      <c r="B228" t="s">
+        <v>203</v>
+      </c>
+      <c r="C228" t="s">
+        <v>145</v>
+      </c>
+      <c r="D228" t="s">
+        <v>543</v>
+      </c>
+      <c r="E228" t="s">
+        <v>454</v>
+      </c>
+      <c r="F228" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G228" s="13">
+        <v>3.172</v>
+      </c>
+      <c r="H228" s="14">
+        <v>0.128</v>
+      </c>
+      <c r="I228" s="15">
+        <v>4</v>
+      </c>
+      <c r="J228" s="12">
+        <v>11.083</v>
+      </c>
+      <c r="K228" s="16">
+        <v>-7.783</v>
+      </c>
+      <c r="L228" s="15">
+        <v>-70.2</v>
+      </c>
+      <c r="M228" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>526</v>
+      </c>
+      <c r="B229" t="s">
+        <v>203</v>
+      </c>
+      <c r="C229" t="s">
+        <v>145</v>
+      </c>
+      <c r="D229" t="s">
+        <v>543</v>
+      </c>
+      <c r="E229" t="s">
+        <v>423</v>
+      </c>
+      <c r="F229" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G229" s="13">
+        <v>3.373</v>
+      </c>
+      <c r="H229" s="14">
+        <v>0.327</v>
+      </c>
+      <c r="I229" s="15">
+        <v>9.7</v>
+      </c>
+      <c r="J229" s="12">
+        <v>20.813</v>
+      </c>
+      <c r="K229" s="16">
+        <v>-17.113</v>
+      </c>
+      <c r="L229" s="15">
+        <v>-82.2</v>
+      </c>
+      <c r="M229" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>526</v>
+      </c>
+      <c r="B230" t="s">
+        <v>203</v>
+      </c>
+      <c r="C230" t="s">
+        <v>145</v>
+      </c>
+      <c r="D230" t="s">
+        <v>543</v>
+      </c>
+      <c r="E230" t="s">
+        <v>439</v>
+      </c>
+      <c r="F230" s="12">
+        <v>6</v>
+      </c>
+      <c r="G230" s="13">
+        <v>4.995</v>
+      </c>
+      <c r="H230" s="14">
+        <v>1.005</v>
+      </c>
+      <c r="I230" s="15">
+        <v>20.1</v>
+      </c>
+      <c r="J230" s="12">
+        <v>44.6</v>
+      </c>
+      <c r="K230" s="16">
+        <v>-38.6</v>
+      </c>
+      <c r="L230" s="15">
+        <v>-86.5</v>
+      </c>
+      <c r="M230" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>526</v>
+      </c>
+      <c r="B231" t="s">
+        <v>203</v>
+      </c>
+      <c r="C231" t="s">
+        <v>145</v>
+      </c>
+      <c r="D231" t="s">
+        <v>543</v>
+      </c>
+      <c r="E231" t="s">
+        <v>431</v>
+      </c>
+      <c r="F231" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="G231" s="13">
+        <v>8.689</v>
+      </c>
+      <c r="H231" s="14">
+        <v>2.811</v>
+      </c>
+      <c r="I231" s="15">
+        <v>32.4</v>
+      </c>
+      <c r="J231" s="12">
+        <v>125.167</v>
+      </c>
+      <c r="K231" s="16">
+        <v>-113.667</v>
+      </c>
+      <c r="L231" s="15">
+        <v>-90.8</v>
+      </c>
+      <c r="M231" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>526</v>
+      </c>
+      <c r="B232" t="s">
+        <v>203</v>
+      </c>
+      <c r="C232" t="s">
+        <v>145</v>
+      </c>
+      <c r="D232" t="s">
+        <v>543</v>
+      </c>
+      <c r="E232" t="s">
+        <v>571</v>
+      </c>
+      <c r="F232" s="12">
+        <v>25</v>
+      </c>
+      <c r="G232" s="13">
+        <v>17.797</v>
+      </c>
+      <c r="H232" s="14">
+        <v>7.203</v>
+      </c>
+      <c r="I232" s="15">
+        <v>40.5</v>
+      </c>
+      <c r="J232" s="12">
+        <v>134</v>
+      </c>
+      <c r="K232" s="16">
+        <v>-109</v>
+      </c>
+      <c r="L232" s="15">
+        <v>-81.3</v>
+      </c>
+      <c r="M232" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>526</v>
+      </c>
+      <c r="B233" t="s">
+        <v>203</v>
+      </c>
+      <c r="C233" t="s">
+        <v>145</v>
+      </c>
+      <c r="D233" t="s">
+        <v>543</v>
+      </c>
+      <c r="E233" t="s">
+        <v>573</v>
+      </c>
+      <c r="F233" s="12">
+        <v>45</v>
+      </c>
+      <c r="G233" s="13">
+        <v>30.92</v>
+      </c>
+      <c r="H233" s="14">
+        <v>14.08</v>
+      </c>
+      <c r="I233" s="15">
+        <v>45.5</v>
+      </c>
+      <c r="J233" s="12">
+        <v>248</v>
+      </c>
+      <c r="K233" s="16">
+        <v>-203</v>
+      </c>
+      <c r="L233" s="15">
+        <v>-81.8</v>
+      </c>
+      <c r="M233" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="E234" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F234" s="8">
+        <v>14</v>
+      </c>
+      <c r="G234" s="9"/>
+      <c r="H234" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="I234" s="11"/>
+      <c r="J234" s="8"/>
+      <c r="K234" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L234" s="11"/>
+      <c r="M234" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>526</v>
+      </c>
+      <c r="B235" t="s">
+        <v>208</v>
+      </c>
+      <c r="C235" t="s">
+        <v>546</v>
+      </c>
+      <c r="D235" t="s">
+        <v>547</v>
+      </c>
+      <c r="E235" t="s">
+        <v>434</v>
+      </c>
+      <c r="F235" s="12">
+        <v>5.25</v>
+      </c>
+      <c r="G235" s="13">
+        <v>4.702</v>
+      </c>
+      <c r="H235" s="14">
+        <v>0.548</v>
+      </c>
+      <c r="I235" s="15">
+        <v>11.7</v>
+      </c>
+      <c r="J235" s="12">
+        <v>11.75</v>
+      </c>
+      <c r="K235" s="16">
+        <v>-6.5</v>
+      </c>
+      <c r="L235" s="15">
+        <v>-55.3</v>
+      </c>
+      <c r="M235" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>526</v>
+      </c>
+      <c r="B236" t="s">
+        <v>208</v>
+      </c>
+      <c r="C236" t="s">
+        <v>546</v>
+      </c>
+      <c r="D236" t="s">
+        <v>547</v>
+      </c>
+      <c r="E236" t="s">
+        <v>454</v>
+      </c>
+      <c r="F236" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G236" s="13">
+        <v>3.425</v>
+      </c>
+      <c r="H236" s="14">
+        <v>0.275</v>
+      </c>
+      <c r="I236" s="15">
+        <v>8</v>
+      </c>
+      <c r="J236" s="12">
+        <v>17.5</v>
+      </c>
+      <c r="K236" s="16">
+        <v>-13.8</v>
+      </c>
+      <c r="L236" s="15">
+        <v>-78.9</v>
+      </c>
+      <c r="M236" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>526</v>
+      </c>
+      <c r="B237" t="s">
+        <v>208</v>
+      </c>
+      <c r="C237" t="s">
+        <v>546</v>
+      </c>
+      <c r="D237" t="s">
+        <v>547</v>
+      </c>
+      <c r="E237" t="s">
+        <v>423</v>
+      </c>
+      <c r="F237" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G237" s="13">
+        <v>3.263</v>
+      </c>
+      <c r="H237" s="14">
+        <v>0.337</v>
+      </c>
+      <c r="I237" s="15">
+        <v>10.3</v>
+      </c>
+      <c r="J237" s="12">
+        <v>39.125</v>
+      </c>
+      <c r="K237" s="16">
+        <v>-35.525</v>
+      </c>
+      <c r="L237" s="15">
+        <v>-90.8</v>
+      </c>
+      <c r="M237" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>526</v>
+      </c>
+      <c r="B238" t="s">
+        <v>208</v>
+      </c>
+      <c r="C238" t="s">
+        <v>546</v>
+      </c>
+      <c r="D238" t="s">
+        <v>547</v>
+      </c>
+      <c r="E238" t="s">
+        <v>439</v>
+      </c>
+      <c r="F238" s="12">
+        <v>5.3</v>
+      </c>
+      <c r="G238" s="13">
+        <v>4.585</v>
+      </c>
+      <c r="H238" s="14">
+        <v>0.715</v>
+      </c>
+      <c r="I238" s="15">
+        <v>15.6</v>
+      </c>
+      <c r="J238" s="12">
+        <v>112.7</v>
+      </c>
+      <c r="K238" s="16">
+        <v>-107.4</v>
+      </c>
+      <c r="L238" s="15">
+        <v>-95.3</v>
+      </c>
+      <c r="M238" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>526</v>
+      </c>
+      <c r="B239" t="s">
+        <v>208</v>
+      </c>
+      <c r="C239" t="s">
+        <v>546</v>
+      </c>
+      <c r="D239" t="s">
+        <v>547</v>
+      </c>
+      <c r="E239" t="s">
+        <v>431</v>
+      </c>
+      <c r="F239" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="G239" s="13">
+        <v>7.442</v>
+      </c>
+      <c r="H239" s="14">
+        <v>2.058</v>
+      </c>
+      <c r="I239" s="15">
+        <v>27.7</v>
+      </c>
+      <c r="J239" s="12">
+        <v>241.333</v>
+      </c>
+      <c r="K239" s="16">
+        <v>-231.833</v>
+      </c>
+      <c r="L239" s="15">
+        <v>-96.1</v>
+      </c>
+      <c r="M239" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>526</v>
+      </c>
+      <c r="B240" t="s">
+        <v>208</v>
+      </c>
+      <c r="C240" t="s">
+        <v>546</v>
+      </c>
+      <c r="D240" t="s">
+        <v>547</v>
+      </c>
+      <c r="E240" t="s">
+        <v>571</v>
+      </c>
+      <c r="F240" s="12">
+        <v>17</v>
+      </c>
+      <c r="G240" s="13">
+        <v>17.799</v>
+      </c>
+      <c r="H240" s="17">
+        <v>-0.799</v>
+      </c>
+      <c r="I240" s="15">
+        <v>-4.5</v>
+      </c>
+      <c r="J240" s="12">
+        <v>248</v>
+      </c>
+      <c r="K240" s="16">
+        <v>-231</v>
+      </c>
+      <c r="L240" s="15">
+        <v>-93.1</v>
+      </c>
+      <c r="M240" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" t="s">
+        <v>208</v>
+      </c>
+      <c r="C241" t="s">
+        <v>546</v>
+      </c>
+      <c r="D241" t="s">
+        <v>547</v>
+      </c>
+      <c r="E241" t="s">
+        <v>573</v>
+      </c>
+      <c r="F241" s="12">
+        <v>24</v>
+      </c>
+      <c r="G241" s="13">
+        <v>21.061</v>
+      </c>
+      <c r="H241" s="14">
+        <v>2.939</v>
+      </c>
+      <c r="I241" s="15">
+        <v>14</v>
+      </c>
+      <c r="J241" s="12">
+        <v>330.2</v>
+      </c>
+      <c r="K241" s="16">
+        <v>-306.2</v>
+      </c>
+      <c r="L241" s="15">
+        <v>-92.7</v>
+      </c>
+      <c r="M241" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E242" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F242" s="8">
+        <v>15</v>
+      </c>
+      <c r="G242" s="9"/>
+      <c r="H242" s="10">
+        <v>2.392</v>
+      </c>
+      <c r="I242" s="11"/>
+      <c r="J242" s="8"/>
+      <c r="K242" s="10">
+        <v>-5</v>
+      </c>
+      <c r="L242" s="11"/>
+      <c r="M242" s="4" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>526</v>
+      </c>
+      <c r="B243" t="s">
+        <v>211</v>
+      </c>
+      <c r="C243" t="s">
+        <v>551</v>
+      </c>
+      <c r="D243" t="s">
+        <v>146</v>
+      </c>
+      <c r="E243" t="s">
+        <v>434</v>
+      </c>
+      <c r="F243" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="G243" s="13">
+        <v>5.221</v>
+      </c>
+      <c r="H243" s="14">
+        <v>0.279</v>
+      </c>
+      <c r="I243" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="J243" s="12">
+        <v>11.875</v>
+      </c>
+      <c r="K243" s="16">
+        <v>-6.375</v>
+      </c>
+      <c r="L243" s="15">
+        <v>-53.7</v>
+      </c>
+      <c r="M243" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>526</v>
+      </c>
+      <c r="B244" t="s">
+        <v>211</v>
+      </c>
+      <c r="C244" t="s">
+        <v>551</v>
+      </c>
+      <c r="D244" t="s">
+        <v>146</v>
+      </c>
+      <c r="E244" t="s">
+        <v>454</v>
+      </c>
+      <c r="F244" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="G244" s="13">
+        <v>3.439</v>
+      </c>
+      <c r="H244" s="14">
+        <v>0.211</v>
+      </c>
+      <c r="I244" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="J244" s="12">
+        <v>16.167</v>
+      </c>
+      <c r="K244" s="16">
+        <v>-12.517</v>
+      </c>
+      <c r="L244" s="15">
+        <v>-77.4</v>
+      </c>
+      <c r="M244" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>526</v>
+      </c>
+      <c r="B245" t="s">
+        <v>211</v>
+      </c>
+      <c r="C245" t="s">
+        <v>551</v>
+      </c>
+      <c r="D245" t="s">
+        <v>146</v>
+      </c>
+      <c r="E245" t="s">
+        <v>423</v>
+      </c>
+      <c r="F245" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="G245" s="13">
+        <v>3.274</v>
+      </c>
+      <c r="H245" s="14">
+        <v>0.276</v>
+      </c>
+      <c r="I245" s="15">
+        <v>8.4</v>
+      </c>
+      <c r="J245" s="12">
+        <v>31.125</v>
+      </c>
+      <c r="K245" s="16">
+        <v>-27.575</v>
+      </c>
+      <c r="L245" s="15">
+        <v>-88.6</v>
+      </c>
+      <c r="M245" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>526</v>
+      </c>
+      <c r="B246" t="s">
+        <v>211</v>
+      </c>
+      <c r="C246" t="s">
+        <v>551</v>
+      </c>
+      <c r="D246" t="s">
+        <v>146</v>
+      </c>
+      <c r="E246" t="s">
+        <v>439</v>
+      </c>
+      <c r="F246" s="12">
+        <v>5.1</v>
+      </c>
+      <c r="G246" s="13">
+        <v>4.279</v>
+      </c>
+      <c r="H246" s="14">
+        <v>0.821</v>
+      </c>
+      <c r="I246" s="15">
+        <v>19.2</v>
+      </c>
+      <c r="J246" s="12">
+        <v>77.7</v>
+      </c>
+      <c r="K246" s="16">
+        <v>-72.6</v>
+      </c>
+      <c r="L246" s="15">
+        <v>-93.4</v>
+      </c>
+      <c r="M246" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>526</v>
+      </c>
+      <c r="B247" t="s">
+        <v>211</v>
+      </c>
+      <c r="C247" t="s">
+        <v>551</v>
+      </c>
+      <c r="D247" t="s">
+        <v>146</v>
+      </c>
+      <c r="E247" t="s">
+        <v>431</v>
+      </c>
+      <c r="F247" s="12">
+        <v>8.75</v>
+      </c>
+      <c r="G247" s="13">
+        <v>7.227</v>
+      </c>
+      <c r="H247" s="14">
+        <v>1.523</v>
+      </c>
+      <c r="I247" s="15">
+        <v>21.1</v>
+      </c>
+      <c r="J247" s="12">
+        <v>185.167</v>
+      </c>
+      <c r="K247" s="16">
+        <v>-176.417</v>
+      </c>
+      <c r="L247" s="15">
+        <v>-95.3</v>
+      </c>
+      <c r="M247" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>526</v>
+      </c>
+      <c r="B248" t="s">
+        <v>211</v>
+      </c>
+      <c r="C248" t="s">
+        <v>551</v>
+      </c>
+      <c r="D248" t="s">
+        <v>146</v>
+      </c>
+      <c r="E248" t="s">
+        <v>571</v>
+      </c>
+      <c r="F248" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="G248" s="13">
+        <v>15.793</v>
+      </c>
+      <c r="H248" s="14">
+        <v>2.707</v>
+      </c>
+      <c r="I248" s="15">
+        <v>17.1</v>
+      </c>
+      <c r="J248" s="12">
+        <v>178</v>
+      </c>
+      <c r="K248" s="16">
+        <v>-159.5</v>
+      </c>
+      <c r="L248" s="15">
+        <v>-89.6</v>
+      </c>
+      <c r="M248" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>526</v>
+      </c>
+      <c r="B249" t="s">
+        <v>211</v>
+      </c>
+      <c r="C249" t="s">
+        <v>551</v>
+      </c>
+      <c r="D249" t="s">
+        <v>146</v>
+      </c>
+      <c r="E249" t="s">
+        <v>573</v>
+      </c>
+      <c r="F249" s="12">
+        <v>28</v>
+      </c>
+      <c r="G249" s="13">
+        <v>20.128</v>
+      </c>
+      <c r="H249" s="14">
+        <v>7.872</v>
+      </c>
+      <c r="I249" s="15">
+        <v>39.1</v>
+      </c>
+      <c r="J249" s="12">
+        <v>270</v>
+      </c>
+      <c r="K249" s="16">
+        <v>-242</v>
+      </c>
+      <c r="L249" s="15">
+        <v>-89.6</v>
+      </c>
+      <c r="M249" t="s">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -15549,136 +20409,136 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>655</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>656</v>
+        <v>806</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>657</v>
+        <v>807</v>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>658</v>
+        <v>808</v>
       </c>
       <c r="B5">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>659</v>
+        <v>809</v>
       </c>
       <c r="B6" t="s">
-        <v>660</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>661</v>
+        <v>811</v>
       </c>
       <c r="B7" t="s">
-        <v>662</v>
+        <v>812</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>663</v>
+        <v>813</v>
       </c>
       <c r="B8" t="s">
-        <v>664</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>665</v>
+        <v>815</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>666</v>
+        <v>816</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>667</v>
+        <v>817</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>668</v>
+        <v>818</v>
       </c>
       <c r="B13" t="s">
-        <v>660</v>
+        <v>810</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>669</v>
+        <v>819</v>
       </c>
       <c r="B14" t="s">
-        <v>662</v>
+        <v>812</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>670</v>
+        <v>820</v>
       </c>
       <c r="B15" t="s">
-        <v>664</v>
+        <v>814</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>671</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>672</v>
+        <v>822</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>673</v>
+        <v>823</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>674</v>
+        <v>824</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>675</v>
+        <v>825</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>676</v>
+        <v>826</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>677</v>
+        <v>827</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>678</v>
+        <v>828</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>679</v>
+        <v>829</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>680</v>
+        <v>830</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>681</v>
+        <v>831</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>682</v>
+        <v>832</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -15686,7 +20546,7 @@
         <v>442</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>683</v>
+        <v>833</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -15695,19 +20555,19 @@
         <v>21</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>684</v>
+        <v>834</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>685</v>
+        <v>835</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>686</v>
+        <v>836</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>684</v>
+        <v>837</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -15715,22 +20575,22 @@
         <v>434</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>685</v>
+        <v>835</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>688</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>689</v>
+        <v>837</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>839</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>685</v>
+        <v>835</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>687</v>
+        <v>834</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>21</v>
@@ -15744,19 +20604,19 @@
         <v>454</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>686</v>
+        <v>840</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>688</v>
+        <v>836</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>690</v>
+        <v>841</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>684</v>
+        <v>834</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>21</v>
@@ -15772,17 +20632,17 @@
       <c r="A23" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>21</v>
+      <c r="B23" s="21" t="s">
+        <v>838</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>691</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>692</v>
+        <v>842</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>843</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -15802,19 +20662,19 @@
         <v>439</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>693</v>
+        <v>844</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>694</v>
+        <v>845</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>688</v>
+        <v>837</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -15840,16 +20700,16 @@
         <v>21</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>686</v>
+        <v>846</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>695</v>
+        <v>847</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>684</v>
+        <v>834</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -15857,10 +20717,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>684</v>
+        <v>837</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
@@ -15872,21 +20732,21 @@
         <v>21</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>684</v>
+        <v>834</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>696</v>
+        <v>848</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>687</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -15907,15 +20767,15 @@
         <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>684</v>
+        <v>834</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>697</v>
+        <v>849</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>698</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -15926,7 +20786,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -15940,109 +20800,109 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>699</v>
+        <v>851</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>700</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>701</v>
+        <v>853</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>702</v>
+        <v>854</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>703</v>
+        <v>855</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>704</v>
+        <v>856</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>705</v>
+        <v>857</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>706</v>
+        <v>858</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>707</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>708</v>
+        <v>860</v>
       </c>
       <c r="B5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E5">
-        <v>3150</v>
+        <v>3775</v>
       </c>
       <c r="F5" s="7">
-        <v>1450</v>
+        <v>1875</v>
       </c>
       <c r="G5" s="23">
-        <v>0.8529411764705882</v>
+        <v>0.9868421052631579</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>709</v>
+        <v>861</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E6">
         <v>1565</v>
       </c>
       <c r="F6" s="24">
-        <v>-135</v>
+        <v>-335</v>
       </c>
       <c r="G6" s="23">
-        <v>-0.07941176470588235</v>
+        <v>-0.1763157894736842</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>710</v>
+        <v>862</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E7">
         <v>3050</v>
       </c>
       <c r="F7" s="7">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="G7" s="23">
-        <v>0.7941176470588235</v>
+        <v>0.6052631578947368</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>711</v>
+        <v>863</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -16050,7 +20910,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>493</v>
+        <v>555</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -16062,25 +20922,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>712</v>
+        <v>864</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>713</v>
+        <v>865</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>714</v>
+        <v>866</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>715</v>
+        <v>867</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>716</v>
+        <v>868</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>717</v>
+        <v>869</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -16729,78 +21589,154 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="29" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>451</v>
+      </c>
+      <c r="B28" t="s">
+        <v>409</v>
+      </c>
+      <c r="C28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" t="s">
+        <v>325</v>
+      </c>
+      <c r="E28" t="s">
+        <v>329</v>
+      </c>
+      <c r="F28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G28" s="12">
+        <v>6.25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>434</v>
+      </c>
+      <c r="I28" s="28">
+        <v>525</v>
+      </c>
+      <c r="J28" s="29">
+        <v>1975</v>
+      </c>
+      <c r="K28" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L28" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B29" t="s">
+        <v>411</v>
+      </c>
+      <c r="C29" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" t="s">
+        <v>488</v>
+      </c>
+      <c r="E29" t="s">
+        <v>489</v>
+      </c>
+      <c r="F29" t="s">
+        <v>423</v>
+      </c>
+      <c r="G29" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H29" t="s">
+        <v>439</v>
+      </c>
+      <c r="I29" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J29" s="29">
+        <v>1875</v>
+      </c>
+      <c r="K29" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L29" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D32" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>421</v>
       </c>
-      <c r="B31">
+      <c r="B33">
         <v>7</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>2</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D33" s="27">
         <v>1650</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E33" s="27">
         <v>1650</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F33" s="27">
         <v>470</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G33" s="27">
         <v>520</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>451</v>
       </c>
-      <c r="B32">
-        <v>10</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="D32" s="27">
-        <v>-200</v>
-      </c>
-      <c r="E32" s="27">
-        <v>1450</v>
-      </c>
-      <c r="F32" s="27">
-        <v>-135</v>
-      </c>
-      <c r="G32" s="27">
-        <v>1350</v>
+      <c r="B34">
+        <v>12</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" s="27">
+        <v>225</v>
+      </c>
+      <c r="E34" s="27">
+        <v>1875</v>
+      </c>
+      <c r="F34" s="27">
+        <v>-335</v>
+      </c>
+      <c r="G34" s="27">
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
@@ -16820,10 +21756,10 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>493</v>
+        <v>555</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>724</v>
+        <v>876</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>442</v>
@@ -16841,12 +21777,12 @@
         <v>439</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>725</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>726</v>
+        <v>878</v>
       </c>
       <c r="B2">
         <v>332</v>
@@ -16872,7 +21808,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>727</v>
+        <v>879</v>
       </c>
       <c r="B3">
         <v>331</v>
@@ -16898,7 +21834,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>728</v>
+        <v>880</v>
       </c>
       <c r="B4">
         <v>322</v>
@@ -16924,7 +21860,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>729</v>
+        <v>881</v>
       </c>
       <c r="B5">
         <v>314</v>
@@ -16950,7 +21886,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>730</v>
+        <v>882</v>
       </c>
       <c r="B6">
         <v>306</v>
@@ -16976,7 +21912,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>731</v>
+        <v>883</v>
       </c>
       <c r="B7">
         <v>288</v>
@@ -17002,7 +21938,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>732</v>
+        <v>884</v>
       </c>
       <c r="B8">
         <v>279</v>
@@ -17028,7 +21964,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>733</v>
+        <v>885</v>
       </c>
       <c r="B9">
         <v>257</v>
@@ -17054,7 +21990,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>734</v>
+        <v>886</v>
       </c>
       <c r="B10">
         <v>237</v>
@@ -17080,7 +22016,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>735</v>
+        <v>887</v>
       </c>
       <c r="B11">
         <v>214</v>
@@ -17120,44 +22056,44 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>736</v>
+        <v>888</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>737</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>493</v>
+        <v>555</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>494</v>
+        <v>556</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>738</v>
+        <v>890</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>739</v>
+        <v>891</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>740</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>741</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>742</v>
+        <v>894</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>493</v>
+        <v>555</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>442</v>
@@ -17175,12 +22111,12 @@
         <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>725</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>726</v>
+        <v>878</v>
       </c>
       <c r="B9" s="3">
         <v>5</v>
@@ -17203,7 +22139,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>727</v>
+        <v>879</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
@@ -17226,7 +22162,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>728</v>
+        <v>880</v>
       </c>
       <c r="B11" s="31">
         <v>23</v>
@@ -17249,7 +22185,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>729</v>
+        <v>881</v>
       </c>
       <c r="B12" s="3">
         <v>0</v>
@@ -17272,7 +22208,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>730</v>
+        <v>882</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -17295,7 +22231,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>731</v>
+        <v>883</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -17318,7 +22254,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>732</v>
+        <v>884</v>
       </c>
       <c r="B15" s="31">
         <v>21</v>
@@ -17341,7 +22277,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>733</v>
+        <v>885</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -17364,7 +22300,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>734</v>
+        <v>886</v>
       </c>
       <c r="B17" s="31">
         <v>27</v>
@@ -17387,7 +22323,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>735</v>
+        <v>887</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
@@ -17424,7 +22360,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>743</v>
+        <v>895</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -17434,62 +22370,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>744</v>
+        <v>896</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>745</v>
+        <v>897</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>746</v>
+        <v>898</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>747</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>748</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>749</v>
+        <v>901</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>750</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>751</v>
+        <v>903</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>752</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>753</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>754</v>
+        <v>906</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>755</v>
+        <v>907</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -17499,42 +22435,42 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>756</v>
+        <v>908</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>757</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>758</v>
+        <v>910</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>759</v>
+        <v>911</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>760</v>
+        <v>912</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>761</v>
+        <v>913</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>762</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>763</v>
+        <v>915</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -17544,22 +22480,22 @@
     </row>
     <row r="25" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>764</v>
+        <v>916</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>765</v>
+        <v>917</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>766</v>
+        <v>918</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>767</v>
+        <v>919</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -17569,27 +22505,27 @@
     </row>
     <row r="30" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>768</v>
+        <v>920</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>769</v>
+        <v>921</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>770</v>
+        <v>922</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>771</v>
+        <v>923</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>772</v>
+        <v>924</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
@@ -17599,12 +22535,12 @@
     </row>
     <row r="36" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>773</v>
+        <v>925</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>774</v>
+        <v>926</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4119" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4162" uniqueCount="925">
   <si>
     <t>日期</t>
   </si>
@@ -1517,10 +1517,7 @@
     <t>2球 @3.5</t>
   </si>
   <si>
-    <t>1球 @6.25 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.45 ⚡</t>
+    <t>10-08 11:00</t>
   </si>
   <si>
     <t>巴西国际</t>
@@ -1532,84 +1529,81 @@
     <t>10-08 06:30</t>
   </si>
   <si>
-    <t>4球 @7 ⚡</t>
+    <t>里莫</t>
+  </si>
+  <si>
+    <t>格雷米奥</t>
+  </si>
+  <si>
+    <t>1球 @5.05</t>
+  </si>
+  <si>
+    <t>周三004</t>
+  </si>
+  <si>
+    <t>布拉干RB</t>
+  </si>
+  <si>
+    <t>米拉索尔</t>
+  </si>
+  <si>
+    <t>4球 @5.5</t>
+  </si>
+  <si>
+    <t>周三005</t>
+  </si>
+  <si>
+    <t>维多利亚</t>
+  </si>
+  <si>
+    <t>沙佩科</t>
+  </si>
+  <si>
+    <t>10-08 07:00</t>
+  </si>
+  <si>
+    <t>2球 @3.45</t>
+  </si>
+  <si>
+    <t>1球 @5.1</t>
+  </si>
+  <si>
+    <t>4球 @5.6</t>
+  </si>
+  <si>
+    <t>周三006</t>
+  </si>
+  <si>
+    <t>博塔弗戈</t>
+  </si>
+  <si>
+    <t>达伽马</t>
+  </si>
+  <si>
+    <t>10-08 07:30</t>
+  </si>
+  <si>
+    <t>1球 @5.7</t>
+  </si>
+  <si>
+    <t>4球 @5.35</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>赫尔辛基</t>
+  </si>
+  <si>
+    <t>瓦萨</t>
+  </si>
+  <si>
+    <t>10-08 23:00</t>
   </si>
   <si>
     <t>3球 @3.55 ⚡</t>
   </si>
   <si>
-    <t>里莫</t>
-  </si>
-  <si>
-    <t>格雷米奥</t>
-  </si>
-  <si>
-    <t>1球 @5.05 ⚡</t>
-  </si>
-  <si>
-    <t>周三004</t>
-  </si>
-  <si>
-    <t>布拉干RB</t>
-  </si>
-  <si>
-    <t>米拉索尔</t>
-  </si>
-  <si>
-    <t>4球 @5.5 ⚡</t>
-  </si>
-  <si>
-    <t>周三005</t>
-  </si>
-  <si>
-    <t>维多利亚</t>
-  </si>
-  <si>
-    <t>沙佩科</t>
-  </si>
-  <si>
-    <t>10-08 07:00</t>
-  </si>
-  <si>
-    <t>2球 @3.45</t>
-  </si>
-  <si>
-    <t>1球 @5.1 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5.6 ⚡</t>
-  </si>
-  <si>
-    <t>周三006</t>
-  </si>
-  <si>
-    <t>博塔弗戈</t>
-  </si>
-  <si>
-    <t>达伽马</t>
-  </si>
-  <si>
-    <t>10-08 07:30</t>
-  </si>
-  <si>
-    <t>1球 @5.7 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5.35 ⚡</t>
-  </si>
-  <si>
-    <t>2026-10-08</t>
-  </si>
-  <si>
-    <t>赫尔辛基</t>
-  </si>
-  <si>
-    <t>瓦萨</t>
-  </si>
-  <si>
-    <t>10-08 23:00</t>
-  </si>
-  <si>
     <t>4球 @4.75 ⚡</t>
   </si>
   <si>
@@ -1655,9 +1649,6 @@
     <t>10-09 07:00</t>
   </si>
   <si>
-    <t>3球 @3.7 ⚡</t>
-  </si>
-  <si>
     <t>弗鲁米嫩</t>
   </si>
   <si>
@@ -1679,9 +1670,6 @@
     <t>2球 @3.65</t>
   </si>
   <si>
-    <t>1球 @5.5 ⚡</t>
-  </si>
-  <si>
     <t>4球 @5.1 ⚡</t>
   </si>
   <si>
@@ -2435,7 +2423,7 @@
     <t>2:5=700 5:2=90 负其他=175 平其他=350 胜其他=35</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-07T17:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-08T11:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2450,25 +2438,25 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>3/19 = 15.8%</t>
+    <t>6/25 = 24.0%</t>
   </si>
   <si>
     <t>模型A 命中率（自修正）</t>
   </si>
   <si>
-    <t>5/19 = 26.3%</t>
+    <t>5/25 = 20.0%</t>
   </si>
   <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
-    <t>6/19 = 31.6%</t>
+    <t>8/25 = 32.0%</t>
   </si>
   <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-07 ~ 2026-10-07）</t>
+    <t>近 30 天窗口（2026-09-08 ~ 2026-10-08）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>
@@ -2489,7 +2477,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>16 场（另剔除爆冷 3 场）</t>
+    <t>22 场（另剔除爆冷 3 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -2525,49 +2513,55 @@
     <t>0% (0/2)</t>
   </si>
   <si>
+    <t>33% (2/6)</t>
+  </si>
+  <si>
+    <t>0% (0/9)</t>
+  </si>
+  <si>
+    <t>0% (0/3)</t>
+  </si>
+  <si>
+    <t>0% (0/1)</t>
+  </si>
+  <si>
     <t>25% (1/4)</t>
   </si>
   <si>
     <t>0% (0/5)</t>
   </si>
   <si>
-    <t>0% (0/3)</t>
-  </si>
-  <si>
-    <t>0% (0/1)</t>
-  </si>
-  <si>
-    <t>67% (2/3)</t>
-  </si>
-  <si>
-    <t>0% (0/4)</t>
-  </si>
-  <si>
-    <t>20% (1/5)</t>
-  </si>
-  <si>
     <t>29% (2/7)</t>
   </si>
   <si>
+    <t>14% (1/7)</t>
+  </si>
+  <si>
+    <t>0% (0/6)</t>
+  </si>
+  <si>
+    <t>50% (2/4)</t>
+  </si>
+  <si>
+    <t>20% (2/10)</t>
+  </si>
+  <si>
     <t>43% (3/7)</t>
   </si>
   <si>
     <t>33% (1/3)</t>
   </si>
   <si>
-    <t>38% (3/8)</t>
-  </si>
-  <si>
-    <t>0% (0/6)</t>
-  </si>
-  <si>
-    <t>0% (0/7)</t>
-  </si>
-  <si>
-    <t>0% (0/9)</t>
-  </si>
-  <si>
-    <t>0% (0/14)</t>
+    <t>29% (4/14)</t>
+  </si>
+  <si>
+    <t>0% (0/10)</t>
+  </si>
+  <si>
+    <t>0% (0/15)</t>
+  </si>
+  <si>
+    <t>0% (0/20)</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -2684,7 +2678,7 @@
     <t>010</t>
   </si>
   <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-06，警戒线 30 次）</t>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-07，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -2891,7 +2885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2924,7 +2918,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -9864,28 +9857,28 @@
         <v>55</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>498</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
+        <v>486</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N21" t="s">
         <v>459</v>
       </c>
       <c r="O21" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -9899,40 +9892,40 @@
         <v>144</v>
       </c>
       <c r="D22" t="s">
+        <v>500</v>
+      </c>
+      <c r="E22" t="s">
         <v>501</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>502</v>
-      </c>
-      <c r="F22" t="s">
-        <v>503</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>471</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>21</v>
+        <v>471</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="N22" t="s">
         <v>459</v>
       </c>
       <c r="O22" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -9946,40 +9939,40 @@
         <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F23" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>448</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
+        <v>471</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N23" t="s">
         <v>459</v>
       </c>
       <c r="O23" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -9987,46 +9980,46 @@
         <v>493</v>
       </c>
       <c r="B24" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E24" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>457</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
+        <v>509</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N24" t="s">
         <v>459</v>
       </c>
       <c r="O24" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -10034,46 +10027,46 @@
         <v>493</v>
       </c>
       <c r="B25" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E25" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F25" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>21</v>
+        <v>516</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="N25" t="s">
         <v>459</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -10081,51 +10074,51 @@
         <v>493</v>
       </c>
       <c r="B26" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E26" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F26" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>486</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
+        <v>522</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N26" t="s">
         <v>459</v>
       </c>
       <c r="O26" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B27" t="s">
         <v>189</v>
@@ -10134,13 +10127,13 @@
         <v>494</v>
       </c>
       <c r="D27" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E27" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F27" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>55</v>
@@ -10152,10 +10145,10 @@
         <v>471</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
@@ -10164,7 +10157,7 @@
         <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="O27" t="s">
         <v>21</v>
@@ -10172,7 +10165,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B28" t="s">
         <v>195</v>
@@ -10181,13 +10174,13 @@
         <v>494</v>
       </c>
       <c r="D28" t="s">
+        <v>529</v>
+      </c>
+      <c r="E28" t="s">
+        <v>530</v>
+      </c>
+      <c r="F28" t="s">
         <v>531</v>
-      </c>
-      <c r="E28" t="s">
-        <v>532</v>
-      </c>
-      <c r="F28" t="s">
-        <v>533</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>55</v>
@@ -10196,14 +10189,14 @@
         <v>21</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>536</v>
-      </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
@@ -10211,7 +10204,7 @@
         <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="O28" t="s">
         <v>21</v>
@@ -10219,7 +10212,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B29" t="s">
         <v>199</v>
@@ -10228,29 +10221,29 @@
         <v>144</v>
       </c>
       <c r="D29" t="s">
+        <v>535</v>
+      </c>
+      <c r="E29" t="s">
+        <v>536</v>
+      </c>
+      <c r="F29" t="s">
         <v>537</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="F29" t="s">
+      <c r="J29" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>542</v>
-      </c>
       <c r="L29" t="s">
         <v>21</v>
       </c>
@@ -10258,7 +10251,7 @@
         <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="O29" t="s">
         <v>21</v>
@@ -10266,7 +10259,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B30" t="s">
         <v>203</v>
@@ -10278,10 +10271,10 @@
         <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F30" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>55</v>
@@ -10293,10 +10286,10 @@
         <v>448</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="L30" t="s">
         <v>21</v>
@@ -10305,7 +10298,7 @@
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="O30" t="s">
         <v>21</v>
@@ -10313,7 +10306,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B31" t="s">
         <v>208</v>
@@ -10322,13 +10315,13 @@
         <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E31" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F31" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>55</v>
@@ -10337,13 +10330,13 @@
         <v>21</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="L31" t="s">
         <v>21</v>
@@ -10352,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="O31" t="s">
         <v>21</v>
@@ -10360,7 +10353,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B32" t="s">
         <v>211</v>
@@ -10369,13 +10362,13 @@
         <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E32" t="s">
         <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>55</v>
@@ -10384,13 +10377,13 @@
         <v>21</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="L32" t="s">
         <v>21</v>
@@ -10399,7 +10392,7 @@
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="O32" t="s">
         <v>21</v>
@@ -10435,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -10444,31 +10437,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10501,7 +10494,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -10542,7 +10535,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -10583,7 +10576,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -10624,7 +10617,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -10665,7 +10658,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -10706,7 +10699,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -10723,7 +10716,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -10747,7 +10740,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -10764,7 +10757,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -10788,7 +10781,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -10821,7 +10814,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -10862,7 +10855,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -10903,7 +10896,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -10944,7 +10937,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -10985,7 +10978,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -11026,7 +11019,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -11043,7 +11036,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -11067,7 +11060,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -11084,7 +11077,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -11108,7 +11101,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11141,7 +11134,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -11182,7 +11175,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -11223,7 +11216,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -11264,7 +11257,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -11305,7 +11298,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -11346,7 +11339,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -11363,7 +11356,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -11387,7 +11380,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -11404,7 +11397,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -11428,7 +11421,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11461,7 +11454,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -11502,7 +11495,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -11543,7 +11536,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -11584,7 +11577,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -11625,7 +11618,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -11666,7 +11659,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -11683,7 +11676,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -11707,7 +11700,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -11724,7 +11717,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -11748,7 +11741,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11781,7 +11774,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -11822,7 +11815,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -11863,7 +11856,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -11904,7 +11897,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -11945,7 +11938,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -11986,7 +11979,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -12003,7 +11996,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -12027,7 +12020,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -12044,7 +12037,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -12068,7 +12061,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12101,7 +12094,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -12142,7 +12135,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -12183,7 +12176,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -12224,7 +12217,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -12265,7 +12258,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -12306,7 +12299,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -12323,7 +12316,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -12347,7 +12340,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -12364,7 +12357,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -12388,7 +12381,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12421,7 +12414,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -12462,7 +12455,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -12503,7 +12496,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -12544,7 +12537,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -12585,7 +12578,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -12626,7 +12619,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -12643,7 +12636,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -12667,7 +12660,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -12684,7 +12677,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -12708,7 +12701,7 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12741,7 +12734,7 @@
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -12782,7 +12775,7 @@
         <v>-49.6</v>
       </c>
       <c r="M59" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -12823,7 +12816,7 @@
         <v>-74.9</v>
       </c>
       <c r="M60" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -12864,7 +12857,7 @@
         <v>-88.2</v>
       </c>
       <c r="M61" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -12905,7 +12898,7 @@
         <v>-91.6</v>
       </c>
       <c r="M62" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -12946,7 +12939,7 @@
         <v>-94.9</v>
       </c>
       <c r="M63" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -12963,7 +12956,7 @@
         <v>452</v>
       </c>
       <c r="E64" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F64" s="12">
         <v>15</v>
@@ -12987,7 +12980,7 @@
         <v>-90.1</v>
       </c>
       <c r="M64" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -13004,7 +12997,7 @@
         <v>452</v>
       </c>
       <c r="E65" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F65" s="12">
         <v>18</v>
@@ -13028,7 +13021,7 @@
         <v>-91.4</v>
       </c>
       <c r="M65" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13061,7 +13054,7 @@
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="4" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -13102,7 +13095,7 @@
         <v>-51.7</v>
       </c>
       <c r="M67" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -13143,7 +13136,7 @@
         <v>-73.4</v>
       </c>
       <c r="M68" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -13184,7 +13177,7 @@
         <v>-83.2</v>
       </c>
       <c r="M69" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -13225,7 +13218,7 @@
         <v>-88.2</v>
       </c>
       <c r="M70" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -13266,7 +13259,7 @@
         <v>-86.5</v>
       </c>
       <c r="M71" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -13283,7 +13276,7 @@
         <v>460</v>
       </c>
       <c r="E72" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F72" s="12">
         <v>27</v>
@@ -13307,7 +13300,7 @@
         <v>-80.7</v>
       </c>
       <c r="M72" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -13324,7 +13317,7 @@
         <v>460</v>
       </c>
       <c r="E73" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F73" s="12">
         <v>45</v>
@@ -13348,7 +13341,7 @@
         <v>-82.9</v>
       </c>
       <c r="M73" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13381,7 +13374,7 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="4" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -13422,7 +13415,7 @@
         <v>-48.3</v>
       </c>
       <c r="M75" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -13463,7 +13456,7 @@
         <v>-68.4</v>
       </c>
       <c r="M76" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -13504,7 +13497,7 @@
         <v>-80.5</v>
       </c>
       <c r="M77" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -13545,7 +13538,7 @@
         <v>-86.5</v>
       </c>
       <c r="M78" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -13586,7 +13579,7 @@
         <v>-87.7</v>
       </c>
       <c r="M79" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -13603,7 +13596,7 @@
         <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F80" s="12">
         <v>38</v>
@@ -13627,7 +13620,7 @@
         <v>-75.9</v>
       </c>
       <c r="M80" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -13644,7 +13637,7 @@
         <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F81" s="12">
         <v>70</v>
@@ -13668,7 +13661,7 @@
         <v>-78.5</v>
       </c>
       <c r="M81" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13701,7 +13694,7 @@
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -13742,7 +13735,7 @@
         <v>-50.9</v>
       </c>
       <c r="M83" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -13783,7 +13776,7 @@
         <v>-76.5</v>
       </c>
       <c r="M84" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -13824,7 +13817,7 @@
         <v>-87.5</v>
       </c>
       <c r="M85" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -13865,7 +13858,7 @@
         <v>-92.7</v>
       </c>
       <c r="M86" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -13906,7 +13899,7 @@
         <v>-94.2</v>
       </c>
       <c r="M87" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -13923,7 +13916,7 @@
         <v>305</v>
       </c>
       <c r="E88" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F88" s="12">
         <v>24</v>
@@ -13947,7 +13940,7 @@
         <v>-89.6</v>
       </c>
       <c r="M88" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -13964,7 +13957,7 @@
         <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F89" s="12">
         <v>35</v>
@@ -13988,7 +13981,7 @@
         <v>-88.8</v>
       </c>
       <c r="M89" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14021,7 +14014,7 @@
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="4" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -14062,7 +14055,7 @@
         <v>-50.8</v>
       </c>
       <c r="M91" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -14103,7 +14096,7 @@
         <v>-68.8</v>
       </c>
       <c r="M92" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -14144,7 +14137,7 @@
         <v>-84</v>
       </c>
       <c r="M93" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -14185,7 +14178,7 @@
         <v>-87.8</v>
       </c>
       <c r="M94" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -14226,7 +14219,7 @@
         <v>-89.3</v>
       </c>
       <c r="M95" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -14243,7 +14236,7 @@
         <v>308</v>
       </c>
       <c r="E96" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F96" s="12">
         <v>42</v>
@@ -14267,7 +14260,7 @@
         <v>-78.5</v>
       </c>
       <c r="M96" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -14284,7 +14277,7 @@
         <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F97" s="12">
         <v>80</v>
@@ -14308,7 +14301,7 @@
         <v>-79.7</v>
       </c>
       <c r="M97" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14341,7 +14334,7 @@
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="4" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -14382,7 +14375,7 @@
         <v>-52.4</v>
       </c>
       <c r="M99" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -14423,7 +14416,7 @@
         <v>-74</v>
       </c>
       <c r="M100" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -14464,7 +14457,7 @@
         <v>-86.3</v>
       </c>
       <c r="M101" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -14505,7 +14498,7 @@
         <v>-91.6</v>
       </c>
       <c r="M102" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -14546,7 +14539,7 @@
         <v>-92.2</v>
       </c>
       <c r="M103" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -14563,7 +14556,7 @@
         <v>293</v>
       </c>
       <c r="E104" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F104" s="12">
         <v>35</v>
@@ -14587,7 +14580,7 @@
         <v>-81.8</v>
       </c>
       <c r="M104" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -14604,7 +14597,7 @@
         <v>293</v>
       </c>
       <c r="E105" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F105" s="12">
         <v>60</v>
@@ -14628,7 +14621,7 @@
         <v>-82.4</v>
       </c>
       <c r="M105" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14661,7 +14654,7 @@
       </c>
       <c r="L106" s="11"/>
       <c r="M106" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -14702,7 +14695,7 @@
         <v>-66.4</v>
       </c>
       <c r="M107" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
@@ -14743,7 +14736,7 @@
         <v>-89.7</v>
       </c>
       <c r="M108" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
@@ -14784,7 +14777,7 @@
         <v>-96.9</v>
       </c>
       <c r="M109" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
@@ -14825,7 +14818,7 @@
         <v>-98.4</v>
       </c>
       <c r="M110" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -14866,7 +14859,7 @@
         <v>-98.2</v>
       </c>
       <c r="M111" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -14883,7 +14876,7 @@
         <v>315</v>
       </c>
       <c r="E112" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F112" s="12">
         <v>8.8</v>
@@ -14907,7 +14900,7 @@
         <v>-97.2</v>
       </c>
       <c r="M112" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
@@ -14924,7 +14917,7 @@
         <v>315</v>
       </c>
       <c r="E113" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F113" s="12">
         <v>9</v>
@@ -14948,7 +14941,7 @@
         <v>-97.7</v>
       </c>
       <c r="M113" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14981,7 +14974,7 @@
       </c>
       <c r="L114" s="11"/>
       <c r="M114" s="4" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
@@ -15022,7 +15015,7 @@
         <v>-58.4</v>
       </c>
       <c r="M115" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -15063,7 +15056,7 @@
         <v>-81.7</v>
       </c>
       <c r="M116" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
@@ -15104,7 +15097,7 @@
         <v>-92.4</v>
       </c>
       <c r="M117" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
@@ -15145,7 +15138,7 @@
         <v>-96.5</v>
       </c>
       <c r="M118" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -15186,7 +15179,7 @@
         <v>-97</v>
       </c>
       <c r="M119" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -15203,7 +15196,7 @@
         <v>323</v>
       </c>
       <c r="E120" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F120" s="12">
         <v>12</v>
@@ -15227,7 +15220,7 @@
         <v>-94</v>
       </c>
       <c r="M120" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -15244,7 +15237,7 @@
         <v>323</v>
       </c>
       <c r="E121" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F121" s="12">
         <v>14</v>
@@ -15268,7 +15261,7 @@
         <v>-93.4</v>
       </c>
       <c r="M121" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15301,7 +15294,7 @@
       </c>
       <c r="L122" s="11"/>
       <c r="M122" s="4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -15342,7 +15335,7 @@
         <v>-74.2</v>
       </c>
       <c r="M123" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -15383,7 +15376,7 @@
         <v>-92.3</v>
       </c>
       <c r="M124" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -15424,7 +15417,7 @@
         <v>-98.1</v>
       </c>
       <c r="M125" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -15465,7 +15458,7 @@
         <v>-98.5</v>
       </c>
       <c r="M126" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -15506,7 +15499,7 @@
         <v>-98.3</v>
       </c>
       <c r="M127" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -15523,7 +15516,7 @@
         <v>319</v>
       </c>
       <c r="E128" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F128" s="12">
         <v>11</v>
@@ -15547,7 +15540,7 @@
         <v>-97.5</v>
       </c>
       <c r="M128" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -15564,7 +15557,7 @@
         <v>319</v>
       </c>
       <c r="E129" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F129" s="12">
         <v>12</v>
@@ -15588,7 +15581,7 @@
         <v>-97.7</v>
       </c>
       <c r="M129" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15621,7 +15614,7 @@
       </c>
       <c r="L130" s="11"/>
       <c r="M130" s="4" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -15662,7 +15655,7 @@
         <v>-58</v>
       </c>
       <c r="M131" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -15703,7 +15696,7 @@
         <v>-81.6</v>
       </c>
       <c r="M132" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -15744,7 +15737,7 @@
         <v>-90.8</v>
       </c>
       <c r="M133" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -15785,7 +15778,7 @@
         <v>-95.8</v>
       </c>
       <c r="M134" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -15826,7 +15819,7 @@
         <v>-95.9</v>
       </c>
       <c r="M135" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -15843,7 +15836,7 @@
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F136" s="12">
         <v>20</v>
@@ -15867,7 +15860,7 @@
         <v>-93.3</v>
       </c>
       <c r="M136" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -15884,7 +15877,7 @@
         <v>410</v>
       </c>
       <c r="E137" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F137" s="12">
         <v>30</v>
@@ -15908,7 +15901,7 @@
         <v>-92.7</v>
       </c>
       <c r="M137" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15941,7 +15934,7 @@
       </c>
       <c r="L138" s="11"/>
       <c r="M138" s="4" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -15982,7 +15975,7 @@
         <v>-49</v>
       </c>
       <c r="M139" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -16023,7 +16016,7 @@
         <v>-72.3</v>
       </c>
       <c r="M140" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -16064,7 +16057,7 @@
         <v>-83.6</v>
       </c>
       <c r="M141" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -16105,7 +16098,7 @@
         <v>-88.7</v>
       </c>
       <c r="M142" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -16146,7 +16139,7 @@
         <v>-93.2</v>
       </c>
       <c r="M143" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -16163,7 +16156,7 @@
         <v>329</v>
       </c>
       <c r="E144" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F144" s="12">
         <v>15.5</v>
@@ -16187,7 +16180,7 @@
         <v>-85.4</v>
       </c>
       <c r="M144" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -16204,7 +16197,7 @@
         <v>329</v>
       </c>
       <c r="E145" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F145" s="12">
         <v>21</v>
@@ -16228,7 +16221,7 @@
         <v>-85.1</v>
       </c>
       <c r="M145" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -16261,7 +16254,7 @@
       </c>
       <c r="L146" s="11"/>
       <c r="M146" s="4" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -16302,7 +16295,7 @@
         <v>-44.4</v>
       </c>
       <c r="M147" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -16343,7 +16336,7 @@
         <v>-67.9</v>
       </c>
       <c r="M148" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -16384,7 +16377,7 @@
         <v>-80.2</v>
       </c>
       <c r="M149" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -16425,7 +16418,7 @@
         <v>-87.4</v>
       </c>
       <c r="M150" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -16466,7 +16459,7 @@
         <v>-92.6</v>
       </c>
       <c r="M151" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -16483,7 +16476,7 @@
         <v>489</v>
       </c>
       <c r="E152" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -16507,7 +16500,7 @@
         <v>-84.3</v>
       </c>
       <c r="M152" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -16524,7 +16517,7 @@
         <v>489</v>
       </c>
       <c r="E153" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F153" s="12">
         <v>13</v>
@@ -16548,7 +16541,7 @@
         <v>-84.7</v>
       </c>
       <c r="M153" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -16581,7 +16574,7 @@
       </c>
       <c r="L154" s="11"/>
       <c r="M154" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
@@ -16622,7 +16615,7 @@
         <v>-49.5</v>
       </c>
       <c r="M155" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
@@ -16663,7 +16656,7 @@
         <v>-75.7</v>
       </c>
       <c r="M156" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
@@ -16704,7 +16697,7 @@
         <v>-86.8</v>
       </c>
       <c r="M157" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
@@ -16745,7 +16738,7 @@
         <v>-91.2</v>
       </c>
       <c r="M158" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
@@ -16786,7 +16779,7 @@
         <v>-92.3</v>
       </c>
       <c r="M159" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
@@ -16803,7 +16796,7 @@
         <v>496</v>
       </c>
       <c r="E160" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F160" s="12">
         <v>16</v>
@@ -16827,7 +16820,7 @@
         <v>-85.6</v>
       </c>
       <c r="M160" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
@@ -16844,7 +16837,7 @@
         <v>496</v>
       </c>
       <c r="E161" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F161" s="12">
         <v>24</v>
@@ -16868,7 +16861,7 @@
         <v>-83.8</v>
       </c>
       <c r="M161" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="162" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -16879,10 +16872,10 @@
         <v>179</v>
       </c>
       <c r="C162" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="D162" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>502</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>442</v>
@@ -16901,7 +16894,7 @@
       </c>
       <c r="L162" s="11"/>
       <c r="M162" s="4" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
@@ -16912,10 +16905,10 @@
         <v>179</v>
       </c>
       <c r="C163" t="s">
+        <v>500</v>
+      </c>
+      <c r="D163" t="s">
         <v>501</v>
-      </c>
-      <c r="D163" t="s">
-        <v>502</v>
       </c>
       <c r="E163" t="s">
         <v>434</v>
@@ -16942,7 +16935,7 @@
         <v>-51</v>
       </c>
       <c r="M163" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
@@ -16953,10 +16946,10 @@
         <v>179</v>
       </c>
       <c r="C164" t="s">
+        <v>500</v>
+      </c>
+      <c r="D164" t="s">
         <v>501</v>
-      </c>
-      <c r="D164" t="s">
-        <v>502</v>
       </c>
       <c r="E164" t="s">
         <v>454</v>
@@ -16983,7 +16976,7 @@
         <v>-66.7</v>
       </c>
       <c r="M164" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
@@ -16994,10 +16987,10 @@
         <v>179</v>
       </c>
       <c r="C165" t="s">
+        <v>500</v>
+      </c>
+      <c r="D165" t="s">
         <v>501</v>
-      </c>
-      <c r="D165" t="s">
-        <v>502</v>
       </c>
       <c r="E165" t="s">
         <v>423</v>
@@ -17024,7 +17017,7 @@
         <v>-82.5</v>
       </c>
       <c r="M165" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
@@ -17035,10 +17028,10 @@
         <v>179</v>
       </c>
       <c r="C166" t="s">
+        <v>500</v>
+      </c>
+      <c r="D166" t="s">
         <v>501</v>
-      </c>
-      <c r="D166" t="s">
-        <v>502</v>
       </c>
       <c r="E166" t="s">
         <v>439</v>
@@ -17065,7 +17058,7 @@
         <v>-86.5</v>
       </c>
       <c r="M166" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -17076,10 +17069,10 @@
         <v>179</v>
       </c>
       <c r="C167" t="s">
+        <v>500</v>
+      </c>
+      <c r="D167" t="s">
         <v>501</v>
-      </c>
-      <c r="D167" t="s">
-        <v>502</v>
       </c>
       <c r="E167" t="s">
         <v>431</v>
@@ -17106,7 +17099,7 @@
         <v>-89.9</v>
       </c>
       <c r="M167" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
@@ -17117,13 +17110,13 @@
         <v>179</v>
       </c>
       <c r="C168" t="s">
+        <v>500</v>
+      </c>
+      <c r="D168" t="s">
         <v>501</v>
       </c>
-      <c r="D168" t="s">
-        <v>502</v>
-      </c>
       <c r="E168" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F168" s="12">
         <v>37</v>
@@ -17147,7 +17140,7 @@
         <v>-77</v>
       </c>
       <c r="M168" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
@@ -17158,13 +17151,13 @@
         <v>179</v>
       </c>
       <c r="C169" t="s">
+        <v>500</v>
+      </c>
+      <c r="D169" t="s">
         <v>501</v>
       </c>
-      <c r="D169" t="s">
-        <v>502</v>
-      </c>
       <c r="E169" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F169" s="12">
         <v>66</v>
@@ -17188,7 +17181,7 @@
         <v>-78.2</v>
       </c>
       <c r="M169" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="170" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -17199,10 +17192,10 @@
         <v>183</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>442</v>
@@ -17221,7 +17214,7 @@
       </c>
       <c r="L170" s="11"/>
       <c r="M170" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
@@ -17232,10 +17225,10 @@
         <v>183</v>
       </c>
       <c r="C171" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D171" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E171" t="s">
         <v>434</v>
@@ -17262,7 +17255,7 @@
         <v>-43.9</v>
       </c>
       <c r="M171" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -17273,10 +17266,10 @@
         <v>183</v>
       </c>
       <c r="C172" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D172" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E172" t="s">
         <v>454</v>
@@ -17303,7 +17296,7 @@
         <v>-70.4</v>
       </c>
       <c r="M172" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -17314,10 +17307,10 @@
         <v>183</v>
       </c>
       <c r="C173" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D173" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E173" t="s">
         <v>423</v>
@@ -17344,7 +17337,7 @@
         <v>-81.9</v>
       </c>
       <c r="M173" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -17355,10 +17348,10 @@
         <v>183</v>
       </c>
       <c r="C174" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D174" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E174" t="s">
         <v>439</v>
@@ -17385,7 +17378,7 @@
         <v>-86.6</v>
       </c>
       <c r="M174" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -17396,10 +17389,10 @@
         <v>183</v>
       </c>
       <c r="C175" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D175" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E175" t="s">
         <v>431</v>
@@ -17426,7 +17419,7 @@
         <v>-90</v>
       </c>
       <c r="M175" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -17437,13 +17430,13 @@
         <v>183</v>
       </c>
       <c r="C176" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D176" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E176" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F176" s="12">
         <v>23</v>
@@ -17467,7 +17460,7 @@
         <v>-80.7</v>
       </c>
       <c r="M176" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -17478,13 +17471,13 @@
         <v>183</v>
       </c>
       <c r="C177" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D177" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E177" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F177" s="12">
         <v>39</v>
@@ -17508,7 +17501,7 @@
         <v>-80.6</v>
       </c>
       <c r="M177" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="178" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -17516,13 +17509,13 @@
         <v>493</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>442</v>
@@ -17541,7 +17534,7 @@
       </c>
       <c r="L178" s="11"/>
       <c r="M178" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -17549,13 +17542,13 @@
         <v>493</v>
       </c>
       <c r="B179" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C179" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D179" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E179" t="s">
         <v>434</v>
@@ -17582,7 +17575,7 @@
         <v>-50.9</v>
       </c>
       <c r="M179" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
@@ -17590,13 +17583,13 @@
         <v>493</v>
       </c>
       <c r="B180" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C180" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D180" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E180" t="s">
         <v>454</v>
@@ -17623,7 +17616,7 @@
         <v>-74.1</v>
       </c>
       <c r="M180" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -17631,13 +17624,13 @@
         <v>493</v>
       </c>
       <c r="B181" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C181" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D181" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E181" t="s">
         <v>423</v>
@@ -17664,7 +17657,7 @@
         <v>-86.5</v>
       </c>
       <c r="M181" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
@@ -17672,13 +17665,13 @@
         <v>493</v>
       </c>
       <c r="B182" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C182" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D182" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E182" t="s">
         <v>439</v>
@@ -17705,7 +17698,7 @@
         <v>-90.7</v>
       </c>
       <c r="M182" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
@@ -17713,13 +17706,13 @@
         <v>493</v>
       </c>
       <c r="B183" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C183" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D183" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E183" t="s">
         <v>431</v>
@@ -17746,7 +17739,7 @@
         <v>-93.2</v>
       </c>
       <c r="M183" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -17754,16 +17747,16 @@
         <v>493</v>
       </c>
       <c r="B184" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C184" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D184" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E184" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F184" s="12">
         <v>19</v>
@@ -17787,7 +17780,7 @@
         <v>-87.3</v>
       </c>
       <c r="M184" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -17795,16 +17788,16 @@
         <v>493</v>
       </c>
       <c r="B185" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C185" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D185" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E185" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F185" s="12">
         <v>30</v>
@@ -17828,7 +17821,7 @@
         <v>-86.3</v>
       </c>
       <c r="M185" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="186" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -17836,13 +17829,13 @@
         <v>493</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>442</v>
@@ -17861,7 +17854,7 @@
       </c>
       <c r="L186" s="11"/>
       <c r="M186" s="4" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -17869,13 +17862,13 @@
         <v>493</v>
       </c>
       <c r="B187" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C187" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D187" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E187" t="s">
         <v>434</v>
@@ -17902,7 +17895,7 @@
         <v>-51.4</v>
       </c>
       <c r="M187" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
@@ -17910,13 +17903,13 @@
         <v>493</v>
       </c>
       <c r="B188" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C188" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D188" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E188" t="s">
         <v>454</v>
@@ -17943,7 +17936,7 @@
         <v>-77.5</v>
       </c>
       <c r="M188" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
@@ -17951,13 +17944,13 @@
         <v>493</v>
       </c>
       <c r="B189" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C189" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D189" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E189" t="s">
         <v>423</v>
@@ -17984,7 +17977,7 @@
         <v>-87.9</v>
       </c>
       <c r="M189" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -17992,13 +17985,13 @@
         <v>493</v>
       </c>
       <c r="B190" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C190" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D190" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E190" t="s">
         <v>439</v>
@@ -18025,7 +18018,7 @@
         <v>-93</v>
       </c>
       <c r="M190" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -18033,13 +18026,13 @@
         <v>493</v>
       </c>
       <c r="B191" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C191" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D191" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E191" t="s">
         <v>431</v>
@@ -18066,7 +18059,7 @@
         <v>-94.8</v>
       </c>
       <c r="M191" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
@@ -18074,16 +18067,16 @@
         <v>493</v>
       </c>
       <c r="B192" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C192" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D192" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E192" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F192" s="12">
         <v>21</v>
@@ -18107,7 +18100,7 @@
         <v>-90</v>
       </c>
       <c r="M192" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -18115,16 +18108,16 @@
         <v>493</v>
       </c>
       <c r="B193" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C193" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D193" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E193" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F193" s="12">
         <v>33</v>
@@ -18148,7 +18141,7 @@
         <v>-89.4</v>
       </c>
       <c r="M193" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="194" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -18156,13 +18149,13 @@
         <v>493</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>442</v>
@@ -18181,7 +18174,7 @@
       </c>
       <c r="L194" s="11"/>
       <c r="M194" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
@@ -18189,13 +18182,13 @@
         <v>493</v>
       </c>
       <c r="B195" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C195" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D195" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E195" t="s">
         <v>434</v>
@@ -18222,7 +18215,7 @@
         <v>-45.1</v>
       </c>
       <c r="M195" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
@@ -18230,13 +18223,13 @@
         <v>493</v>
       </c>
       <c r="B196" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C196" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D196" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E196" t="s">
         <v>454</v>
@@ -18263,7 +18256,7 @@
         <v>-69.1</v>
       </c>
       <c r="M196" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -18271,13 +18264,13 @@
         <v>493</v>
       </c>
       <c r="B197" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C197" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D197" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E197" t="s">
         <v>423</v>
@@ -18304,7 +18297,7 @@
         <v>-81.8</v>
       </c>
       <c r="M197" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
@@ -18312,13 +18305,13 @@
         <v>493</v>
       </c>
       <c r="B198" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C198" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D198" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E198" t="s">
         <v>439</v>
@@ -18345,7 +18338,7 @@
         <v>-87.6</v>
       </c>
       <c r="M198" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
@@ -18353,13 +18346,13 @@
         <v>493</v>
       </c>
       <c r="B199" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C199" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D199" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E199" t="s">
         <v>431</v>
@@ -18386,7 +18379,7 @@
         <v>-90.1</v>
       </c>
       <c r="M199" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
@@ -18394,16 +18387,16 @@
         <v>493</v>
       </c>
       <c r="B200" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C200" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D200" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E200" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F200" s="12">
         <v>18</v>
@@ -18427,7 +18420,7 @@
         <v>-81</v>
       </c>
       <c r="M200" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
@@ -18435,16 +18428,16 @@
         <v>493</v>
       </c>
       <c r="B201" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C201" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D201" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E201" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F201" s="12">
         <v>29</v>
@@ -18468,21 +18461,21 @@
         <v>-83.4</v>
       </c>
       <c r="M201" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="202" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>189</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>442</v>
@@ -18501,21 +18494,21 @@
       </c>
       <c r="L202" s="11"/>
       <c r="M202" s="4" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B203" t="s">
         <v>189</v>
       </c>
       <c r="C203" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D203" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E203" t="s">
         <v>434</v>
@@ -18542,21 +18535,21 @@
         <v>-51</v>
       </c>
       <c r="M203" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B204" t="s">
         <v>189</v>
       </c>
       <c r="C204" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D204" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E204" t="s">
         <v>454</v>
@@ -18583,21 +18576,21 @@
         <v>-75</v>
       </c>
       <c r="M204" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B205" t="s">
         <v>189</v>
       </c>
       <c r="C205" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D205" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E205" t="s">
         <v>423</v>
@@ -18624,21 +18617,21 @@
         <v>-88.6</v>
       </c>
       <c r="M205" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B206" t="s">
         <v>189</v>
       </c>
       <c r="C206" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D206" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E206" t="s">
         <v>439</v>
@@ -18665,21 +18658,21 @@
         <v>-93.9</v>
       </c>
       <c r="M206" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B207" t="s">
         <v>189</v>
       </c>
       <c r="C207" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D207" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E207" t="s">
         <v>431</v>
@@ -18706,24 +18699,24 @@
         <v>-95.4</v>
       </c>
       <c r="M207" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B208" t="s">
         <v>189</v>
       </c>
       <c r="C208" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D208" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E208" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F208" s="12">
         <v>15</v>
@@ -18747,24 +18740,24 @@
         <v>-89.8</v>
       </c>
       <c r="M208" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B209" t="s">
         <v>189</v>
       </c>
       <c r="C209" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D209" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E209" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F209" s="12">
         <v>21.5</v>
@@ -18788,21 +18781,21 @@
         <v>-88.8</v>
       </c>
       <c r="M209" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="210" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>442</v>
@@ -18821,21 +18814,21 @@
       </c>
       <c r="L210" s="11"/>
       <c r="M210" s="4" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B211" t="s">
         <v>195</v>
       </c>
       <c r="C211" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D211" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E211" t="s">
         <v>434</v>
@@ -18862,21 +18855,21 @@
         <v>-54.2</v>
       </c>
       <c r="M211" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B212" t="s">
         <v>195</v>
       </c>
       <c r="C212" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D212" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E212" t="s">
         <v>454</v>
@@ -18903,21 +18896,21 @@
         <v>-78.5</v>
       </c>
       <c r="M212" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B213" t="s">
         <v>195</v>
       </c>
       <c r="C213" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D213" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E213" t="s">
         <v>423</v>
@@ -18944,21 +18937,21 @@
         <v>-88.4</v>
       </c>
       <c r="M213" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B214" t="s">
         <v>195</v>
       </c>
       <c r="C214" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D214" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E214" t="s">
         <v>439</v>
@@ -18985,21 +18978,21 @@
         <v>-93.6</v>
       </c>
       <c r="M214" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B215" t="s">
         <v>195</v>
       </c>
       <c r="C215" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D215" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E215" t="s">
         <v>431</v>
@@ -19026,24 +19019,24 @@
         <v>-95.5</v>
       </c>
       <c r="M215" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B216" t="s">
         <v>195</v>
       </c>
       <c r="C216" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D216" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E216" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F216" s="12">
         <v>22</v>
@@ -19067,24 +19060,24 @@
         <v>-91.1</v>
       </c>
       <c r="M216" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B217" t="s">
         <v>195</v>
       </c>
       <c r="C217" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D217" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E217" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F217" s="12">
         <v>34</v>
@@ -19108,21 +19101,21 @@
         <v>-90.4</v>
       </c>
       <c r="M217" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="218" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>199</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>442</v>
@@ -19141,21 +19134,21 @@
       </c>
       <c r="L218" s="11"/>
       <c r="M218" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B219" t="s">
         <v>199</v>
       </c>
       <c r="C219" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D219" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E219" t="s">
         <v>434</v>
@@ -19182,21 +19175,21 @@
         <v>-50.7</v>
       </c>
       <c r="M219" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B220" t="s">
         <v>199</v>
       </c>
       <c r="C220" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D220" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E220" t="s">
         <v>454</v>
@@ -19223,21 +19216,21 @@
         <v>-73.1</v>
       </c>
       <c r="M220" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B221" t="s">
         <v>199</v>
       </c>
       <c r="C221" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D221" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E221" t="s">
         <v>423</v>
@@ -19264,21 +19257,21 @@
         <v>-84.7</v>
       </c>
       <c r="M221" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B222" t="s">
         <v>199</v>
       </c>
       <c r="C222" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D222" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E222" t="s">
         <v>439</v>
@@ -19305,21 +19298,21 @@
         <v>-90.2</v>
       </c>
       <c r="M222" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B223" t="s">
         <v>199</v>
       </c>
       <c r="C223" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D223" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E223" t="s">
         <v>431</v>
@@ -19346,24 +19339,24 @@
         <v>-93.3</v>
       </c>
       <c r="M223" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B224" t="s">
         <v>199</v>
       </c>
       <c r="C224" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D224" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F224" s="12">
         <v>18</v>
@@ -19387,24 +19380,24 @@
         <v>-85.8</v>
       </c>
       <c r="M224" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B225" t="s">
         <v>199</v>
       </c>
       <c r="C225" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D225" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E225" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F225" s="12">
         <v>26</v>
@@ -19428,12 +19421,12 @@
         <v>-86.8</v>
       </c>
       <c r="M225" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="226" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>203</v>
@@ -19442,7 +19435,7 @@
         <v>145</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>442</v>
@@ -19452,21 +19445,21 @@
       </c>
       <c r="G226" s="9"/>
       <c r="H226" s="10">
-        <v>3.589</v>
+        <v>3.31</v>
       </c>
       <c r="I226" s="11"/>
       <c r="J226" s="8"/>
       <c r="K226" s="10">
-        <v>-4.1</v>
+        <v>-4.036</v>
       </c>
       <c r="L226" s="11"/>
       <c r="M226" s="4" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B227" t="s">
         <v>203</v>
@@ -19475,39 +19468,39 @@
         <v>145</v>
       </c>
       <c r="D227" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E227" t="s">
         <v>434</v>
       </c>
       <c r="F227" s="12">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="G227" s="13">
         <v>4.286</v>
       </c>
       <c r="H227" s="14">
-        <v>0.164</v>
+        <v>0.214</v>
       </c>
       <c r="I227" s="15">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J227" s="12">
         <v>8.75</v>
       </c>
       <c r="K227" s="16">
-        <v>-4.3</v>
+        <v>-4.25</v>
       </c>
       <c r="L227" s="15">
-        <v>-49.1</v>
+        <v>-48.6</v>
       </c>
       <c r="M227" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B228" t="s">
         <v>203</v>
@@ -19516,7 +19509,7 @@
         <v>145</v>
       </c>
       <c r="D228" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E228" t="s">
         <v>454</v>
@@ -19543,12 +19536,12 @@
         <v>-70.2</v>
       </c>
       <c r="M228" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B229" t="s">
         <v>203</v>
@@ -19557,39 +19550,39 @@
         <v>145</v>
       </c>
       <c r="D229" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E229" t="s">
         <v>423</v>
       </c>
       <c r="F229" s="12">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G229" s="13">
         <v>3.373</v>
       </c>
       <c r="H229" s="14">
-        <v>0.327</v>
+        <v>0.227</v>
       </c>
       <c r="I229" s="15">
-        <v>9.7</v>
+        <v>6.7</v>
       </c>
       <c r="J229" s="12">
         <v>20.813</v>
       </c>
       <c r="K229" s="16">
-        <v>-17.113</v>
+        <v>-17.213</v>
       </c>
       <c r="L229" s="15">
-        <v>-82.2</v>
+        <v>-82.7</v>
       </c>
       <c r="M229" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B230" t="s">
         <v>203</v>
@@ -19598,7 +19591,7 @@
         <v>145</v>
       </c>
       <c r="D230" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E230" t="s">
         <v>439</v>
@@ -19625,12 +19618,12 @@
         <v>-86.5</v>
       </c>
       <c r="M230" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B231" t="s">
         <v>203</v>
@@ -19639,39 +19632,39 @@
         <v>145</v>
       </c>
       <c r="D231" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E231" t="s">
         <v>431</v>
       </c>
       <c r="F231" s="12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G231" s="13">
         <v>8.689</v>
       </c>
       <c r="H231" s="14">
-        <v>2.811</v>
+        <v>3.311</v>
       </c>
       <c r="I231" s="15">
-        <v>32.4</v>
+        <v>38.1</v>
       </c>
       <c r="J231" s="12">
         <v>125.167</v>
       </c>
       <c r="K231" s="16">
-        <v>-113.667</v>
+        <v>-113.167</v>
       </c>
       <c r="L231" s="15">
-        <v>-90.8</v>
+        <v>-90.4</v>
       </c>
       <c r="M231" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B232" t="s">
         <v>203</v>
@@ -19680,39 +19673,39 @@
         <v>145</v>
       </c>
       <c r="D232" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E232" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F232" s="12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G232" s="13">
         <v>17.797</v>
       </c>
       <c r="H232" s="14">
-        <v>7.203</v>
+        <v>8.203</v>
       </c>
       <c r="I232" s="15">
-        <v>40.5</v>
+        <v>46.1</v>
       </c>
       <c r="J232" s="12">
         <v>134</v>
       </c>
       <c r="K232" s="16">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="L232" s="15">
-        <v>-81.3</v>
+        <v>-80.6</v>
       </c>
       <c r="M232" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B233" t="s">
         <v>203</v>
@@ -19721,10 +19714,10 @@
         <v>145</v>
       </c>
       <c r="D233" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E233" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F233" s="12">
         <v>45</v>
@@ -19748,21 +19741,21 @@
         <v>-81.8</v>
       </c>
       <c r="M233" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="234" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>208</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>442</v>
@@ -19781,21 +19774,21 @@
       </c>
       <c r="L234" s="11"/>
       <c r="M234" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B235" t="s">
         <v>208</v>
       </c>
       <c r="C235" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D235" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E235" t="s">
         <v>434</v>
@@ -19822,21 +19815,21 @@
         <v>-55.3</v>
       </c>
       <c r="M235" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B236" t="s">
         <v>208</v>
       </c>
       <c r="C236" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D236" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E236" t="s">
         <v>454</v>
@@ -19863,21 +19856,21 @@
         <v>-78.9</v>
       </c>
       <c r="M236" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B237" t="s">
         <v>208</v>
       </c>
       <c r="C237" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D237" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -19904,21 +19897,21 @@
         <v>-90.8</v>
       </c>
       <c r="M237" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B238" t="s">
         <v>208</v>
       </c>
       <c r="C238" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D238" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E238" t="s">
         <v>439</v>
@@ -19945,21 +19938,21 @@
         <v>-95.3</v>
       </c>
       <c r="M238" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B239" t="s">
         <v>208</v>
       </c>
       <c r="C239" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D239" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E239" t="s">
         <v>431</v>
@@ -19986,24 +19979,24 @@
         <v>-96.1</v>
       </c>
       <c r="M239" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B240" t="s">
         <v>208</v>
       </c>
       <c r="C240" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D240" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E240" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F240" s="12">
         <v>17</v>
@@ -20027,24 +20020,24 @@
         <v>-93.1</v>
       </c>
       <c r="M240" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B241" t="s">
         <v>208</v>
       </c>
       <c r="C241" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D241" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E241" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F241" s="12">
         <v>24</v>
@@ -20068,18 +20061,18 @@
         <v>-92.7</v>
       </c>
       <c r="M241" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="242" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>211</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>146</v>
@@ -20101,18 +20094,18 @@
       </c>
       <c r="L242" s="11"/>
       <c r="M242" s="4" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B243" t="s">
         <v>211</v>
       </c>
       <c r="C243" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D243" t="s">
         <v>146</v>
@@ -20142,18 +20135,18 @@
         <v>-53.7</v>
       </c>
       <c r="M243" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B244" t="s">
         <v>211</v>
       </c>
       <c r="C244" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D244" t="s">
         <v>146</v>
@@ -20183,18 +20176,18 @@
         <v>-77.4</v>
       </c>
       <c r="M244" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B245" t="s">
         <v>211</v>
       </c>
       <c r="C245" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D245" t="s">
         <v>146</v>
@@ -20224,18 +20217,18 @@
         <v>-88.6</v>
       </c>
       <c r="M245" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B246" t="s">
         <v>211</v>
       </c>
       <c r="C246" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D246" t="s">
         <v>146</v>
@@ -20265,18 +20258,18 @@
         <v>-93.4</v>
       </c>
       <c r="M246" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B247" t="s">
         <v>211</v>
       </c>
       <c r="C247" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D247" t="s">
         <v>146</v>
@@ -20306,24 +20299,24 @@
         <v>-95.3</v>
       </c>
       <c r="M247" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B248" t="s">
         <v>211</v>
       </c>
       <c r="C248" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D248" t="s">
         <v>146</v>
       </c>
       <c r="E248" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F248" s="12">
         <v>18.5</v>
@@ -20347,24 +20340,24 @@
         <v>-89.6</v>
       </c>
       <c r="M248" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B249" t="s">
         <v>211</v>
       </c>
       <c r="C249" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D249" t="s">
         <v>146</v>
       </c>
       <c r="E249" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F249" s="12">
         <v>28</v>
@@ -20388,7 +20381,7 @@
         <v>-89.6</v>
       </c>
       <c r="M249" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -20409,136 +20402,136 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B6" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B7" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B8" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B13" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B14" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B15" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -20546,28 +20539,28 @@
         <v>442</v>
       </c>
       <c r="B20" s="21" t="s">
+        <v>829</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>831</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>832</v>
+      </c>
+      <c r="H20" s="21" t="s">
         <v>833</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="21" t="s">
+      <c r="I20" s="21" t="s">
         <v>834</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>835</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>836</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>837</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -20578,10 +20571,10 @@
         <v>835</v>
       </c>
       <c r="C21" s="21" t="s">
+        <v>836</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>837</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>839</v>
       </c>
       <c r="E21" s="21" t="s">
         <v>835</v>
@@ -20590,7 +20583,7 @@
         <v>21</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>21</v>
@@ -20604,19 +20597,19 @@
         <v>454</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>21</v>
@@ -20632,17 +20625,17 @@
       <c r="A23" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>838</v>
+      <c r="B23" s="22" t="s">
+        <v>840</v>
       </c>
       <c r="C23" s="21" t="s">
+        <v>841</v>
+      </c>
+      <c r="D23" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>843</v>
-      </c>
       <c r="E23" s="21" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -20662,19 +20655,19 @@
         <v>439</v>
       </c>
       <c r="B24" s="21" t="s">
+        <v>843</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>834</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>834</v>
+      </c>
+      <c r="E24" s="21" t="s">
         <v>844</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>838</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>838</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>845</v>
-      </c>
       <c r="F24" s="21" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -20700,16 +20693,16 @@
         <v>21</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -20717,10 +20710,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
@@ -20732,21 +20725,21 @@
         <v>21</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="G26" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>846</v>
+      </c>
+      <c r="I26" s="21" t="s">
         <v>834</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>848</v>
-      </c>
-      <c r="I26" s="21" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -20767,15 +20760,15 @@
         <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -20786,7 +20779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -20800,109 +20793,109 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="E5">
         <v>3775</v>
       </c>
       <c r="F5" s="7">
-        <v>1875</v>
+        <v>1275</v>
       </c>
       <c r="G5" s="23">
-        <v>0.9868421052631579</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="E6">
-        <v>1565</v>
-      </c>
-      <c r="F6" s="24">
-        <v>-335</v>
+        <v>2595</v>
+      </c>
+      <c r="F6" s="7">
+        <v>95</v>
       </c>
       <c r="G6" s="23">
-        <v>-0.1763157894736842</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="E7">
-        <v>3050</v>
+        <v>3965</v>
       </c>
       <c r="F7" s="7">
-        <v>1150</v>
+        <v>1465</v>
       </c>
       <c r="G7" s="23">
-        <v>0.6052631578947368</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -20910,7 +20903,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -20922,25 +20915,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>867</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -20968,16 +20961,16 @@
       <c r="H11" t="s">
         <v>423</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="24">
         <v>-100</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="25">
         <v>-100</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="26">
         <v>-100</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21006,16 +20999,16 @@
       <c r="H12" t="s">
         <v>431</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <v>-100</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="25">
         <v>-200</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="26">
         <v>-100</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21044,16 +21037,16 @@
       <c r="H13" t="s">
         <v>434</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <v>-100</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="25">
         <v>-300</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="26">
         <v>-100</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="26">
         <v>580</v>
       </c>
     </row>
@@ -21082,16 +21075,16 @@
       <c r="H14" t="s">
         <v>439</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <v>-100</v>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="25">
         <v>-400</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="26">
         <v>320</v>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21120,16 +21113,16 @@
       <c r="H15" t="s">
         <v>442</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="27">
         <v>650</v>
       </c>
-      <c r="J15" s="29">
+      <c r="J15" s="28">
         <v>250</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="26">
         <v>650</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21158,16 +21151,16 @@
       <c r="H16" t="s">
         <v>442</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="27">
         <v>1500</v>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="28">
         <v>1750</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="26">
         <v>-100</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21196,16 +21189,16 @@
       <c r="H17" t="s">
         <v>434</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>-100</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="28">
         <v>1650</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="26">
         <v>-100</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="26">
         <v>440</v>
       </c>
     </row>
@@ -21234,16 +21227,16 @@
       <c r="H18" t="s">
         <v>454</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="24">
         <v>-100</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="28">
         <v>1550</v>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="26">
         <v>-100</v>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21272,16 +21265,16 @@
       <c r="H19" t="s">
         <v>434</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="24">
         <v>-100</v>
       </c>
-      <c r="J19" s="29">
+      <c r="J19" s="28">
         <v>1450</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="26">
         <v>295</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L19" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21310,16 +21303,16 @@
       <c r="H20" t="s">
         <v>439</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <v>-100</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="28">
         <v>1350</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="26">
         <v>-100</v>
       </c>
-      <c r="L20" s="27">
+      <c r="L20" s="26">
         <v>600</v>
       </c>
     </row>
@@ -21348,16 +21341,16 @@
       <c r="H21" t="s">
         <v>442</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <v>-100</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="28">
         <v>1250</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K21" s="26">
         <v>-100</v>
       </c>
-      <c r="L21" s="27">
+      <c r="L21" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21386,16 +21379,16 @@
       <c r="H22" t="s">
         <v>454</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="24">
         <v>-100</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="28">
         <v>1150</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="26">
         <v>-100</v>
       </c>
-      <c r="L22" s="27">
+      <c r="L22" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21424,16 +21417,16 @@
       <c r="H23" t="s">
         <v>423</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="27">
         <v>300</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="28">
         <v>1450</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="26">
         <v>-100</v>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21462,16 +21455,16 @@
       <c r="H24" t="s">
         <v>423</v>
       </c>
-      <c r="I24" s="28">
+      <c r="I24" s="27">
         <v>300</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="28">
         <v>1750</v>
       </c>
-      <c r="K24" s="27">
+      <c r="K24" s="26">
         <v>-100</v>
       </c>
-      <c r="L24" s="27">
+      <c r="L24" s="26">
         <v>300</v>
       </c>
     </row>
@@ -21500,16 +21493,16 @@
       <c r="H25" t="s">
         <v>423</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="24">
         <v>-100</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="28">
         <v>1650</v>
       </c>
-      <c r="K25" s="27">
+      <c r="K25" s="26">
         <v>-100</v>
       </c>
-      <c r="L25" s="27">
+      <c r="L25" s="26">
         <v>265</v>
       </c>
     </row>
@@ -21538,16 +21531,16 @@
       <c r="H26" t="s">
         <v>423</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="24">
         <v>-100</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="28">
         <v>1550</v>
       </c>
-      <c r="K26" s="27">
+      <c r="K26" s="26">
         <v>-100</v>
       </c>
-      <c r="L26" s="27">
+      <c r="L26" s="26">
         <v>265</v>
       </c>
     </row>
@@ -21576,16 +21569,16 @@
       <c r="H27" t="s">
         <v>439</v>
       </c>
-      <c r="I27" s="25">
+      <c r="I27" s="24">
         <v>-100</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="28">
         <v>1450</v>
       </c>
-      <c r="K27" s="27">
+      <c r="K27" s="26">
         <v>-100</v>
       </c>
-      <c r="L27" s="27">
+      <c r="L27" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21614,16 +21607,16 @@
       <c r="H28" t="s">
         <v>434</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="27">
         <v>525</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="28">
         <v>1975</v>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="26">
         <v>-100</v>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="26">
         <v>-100</v>
       </c>
     </row>
@@ -21652,91 +21645,342 @@
       <c r="H29" t="s">
         <v>439</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="24">
         <v>-100</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="28">
         <v>1875</v>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="26">
         <v>-100</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="26">
         <v>-100</v>
       </c>
     </row>
-    <row r="31" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>493</v>
+      </c>
+      <c r="B30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" t="s">
+        <v>494</v>
+      </c>
+      <c r="D30" t="s">
+        <v>495</v>
+      </c>
+      <c r="E30" t="s">
+        <v>496</v>
+      </c>
+      <c r="F30" t="s">
+        <v>434</v>
+      </c>
+      <c r="G30" s="12">
+        <v>6.25</v>
+      </c>
+      <c r="H30" t="s">
+        <v>442</v>
+      </c>
+      <c r="I30" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J30" s="28">
+        <v>1775</v>
+      </c>
+      <c r="K30" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L30" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>493</v>
+      </c>
+      <c r="B31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E31" t="s">
+        <v>501</v>
+      </c>
+      <c r="F31" t="s">
+        <v>439</v>
+      </c>
+      <c r="G31" s="12">
+        <v>7</v>
+      </c>
+      <c r="H31" t="s">
+        <v>423</v>
+      </c>
+      <c r="I31" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J31" s="28">
+        <v>1675</v>
+      </c>
+      <c r="K31" s="26">
+        <v>255</v>
+      </c>
+      <c r="L31" s="26">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>493</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" t="s">
+        <v>503</v>
+      </c>
+      <c r="E32" t="s">
+        <v>504</v>
+      </c>
+      <c r="F32" t="s">
+        <v>434</v>
+      </c>
+      <c r="G32" s="12">
+        <v>5.05</v>
+      </c>
+      <c r="H32" t="s">
+        <v>454</v>
+      </c>
+      <c r="I32" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="28">
+        <v>1575</v>
+      </c>
+      <c r="K32" s="26">
+        <v>230</v>
+      </c>
+      <c r="L32" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>493</v>
+      </c>
+      <c r="B33" t="s">
+        <v>506</v>
+      </c>
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>507</v>
+      </c>
+      <c r="E33" t="s">
+        <v>508</v>
+      </c>
+      <c r="F33" t="s">
+        <v>439</v>
+      </c>
+      <c r="G33" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>454</v>
+      </c>
+      <c r="I33" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J33" s="28">
+        <v>1475</v>
+      </c>
+      <c r="K33" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>493</v>
+      </c>
+      <c r="B34" t="s">
+        <v>510</v>
+      </c>
+      <c r="C34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" t="s">
+        <v>511</v>
+      </c>
+      <c r="E34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F34" t="s">
+        <v>434</v>
+      </c>
+      <c r="G34" s="12">
+        <v>5.1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>439</v>
+      </c>
+      <c r="I34" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J34" s="28">
+        <v>1375</v>
+      </c>
+      <c r="K34" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L34" s="26">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>493</v>
+      </c>
+      <c r="B35" t="s">
+        <v>517</v>
+      </c>
+      <c r="C35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" t="s">
+        <v>518</v>
+      </c>
+      <c r="E35" t="s">
+        <v>519</v>
+      </c>
+      <c r="F35" t="s">
+        <v>434</v>
+      </c>
+      <c r="G35" s="12">
+        <v>5.7</v>
+      </c>
+      <c r="H35" t="s">
+        <v>423</v>
+      </c>
+      <c r="I35" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J35" s="28">
+        <v>1275</v>
+      </c>
+      <c r="K35" s="26">
+        <v>245</v>
+      </c>
+      <c r="L35" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="32" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="E38" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>421</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" s="26">
+        <v>1650</v>
+      </c>
+      <c r="E39" s="26">
+        <v>1650</v>
+      </c>
+      <c r="F39" s="26">
+        <v>470</v>
+      </c>
+      <c r="G39" s="26">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>451</v>
+      </c>
+      <c r="B40">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" s="26">
+        <v>225</v>
+      </c>
+      <c r="E40" s="26">
+        <v>1875</v>
+      </c>
+      <c r="F40" s="26">
+        <v>-335</v>
+      </c>
+      <c r="G40" s="26">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>493</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41">
         <v>0</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>421</v>
-      </c>
-      <c r="B33">
-        <v>7</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-      <c r="D33" s="27">
-        <v>1650</v>
-      </c>
-      <c r="E33" s="27">
-        <v>1650</v>
-      </c>
-      <c r="F33" s="27">
-        <v>470</v>
-      </c>
-      <c r="G33" s="27">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>451</v>
-      </c>
-      <c r="B34">
-        <v>12</v>
-      </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34" s="27">
-        <v>225</v>
-      </c>
-      <c r="E34" s="27">
-        <v>1875</v>
-      </c>
-      <c r="F34" s="27">
-        <v>-335</v>
-      </c>
-      <c r="G34" s="27">
-        <v>1150</v>
+      <c r="D41" s="26">
+        <v>-600</v>
+      </c>
+      <c r="E41" s="26">
+        <v>1275</v>
+      </c>
+      <c r="F41" s="26">
+        <v>95</v>
+      </c>
+      <c r="G41" s="26">
+        <v>1465</v>
       </c>
     </row>
   </sheetData>
@@ -21756,10 +22000,10 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>442</v>
@@ -21777,18 +22021,18 @@
         <v>439</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>57</v>
@@ -21808,10 +22052,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B3">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -21823,7 +22067,7 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <v>45</v>
@@ -21834,10 +22078,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B4">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -21846,7 +22090,7 @@
         <v>49</v>
       </c>
       <c r="E4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>69</v>
@@ -21860,10 +22104,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B5">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -21872,7 +22116,7 @@
         <v>52</v>
       </c>
       <c r="E5">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5">
         <v>52</v>
@@ -21886,10 +22130,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B6">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -21904,7 +22148,7 @@
         <v>67</v>
       </c>
       <c r="G6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>45</v>
@@ -21912,10 +22156,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7">
         <v>18</v>
@@ -21927,7 +22171,7 @@
         <v>64</v>
       </c>
       <c r="F7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7">
         <v>53</v>
@@ -21938,7 +22182,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B8">
         <v>279</v>
@@ -21964,7 +22208,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B9">
         <v>257</v>
@@ -21990,7 +22234,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B10">
         <v>237</v>
@@ -22016,7 +22260,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B11">
         <v>214</v>
@@ -22056,44 +22300,44 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
-        <v>894</v>
+        <v>891</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>442</v>
@@ -22111,152 +22355,152 @@
         <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B9" s="3">
-        <v>5</v>
-      </c>
-      <c r="C9" s="31">
-        <v>23</v>
+        <v>0</v>
+      </c>
+      <c r="C9" s="30">
+        <v>24</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="F10" s="30">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3">
         <v>2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5</v>
-      </c>
-      <c r="F10" s="31">
-        <v>20</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="B11" s="31">
-        <v>23</v>
+        <v>878</v>
+      </c>
+      <c r="B11" s="30">
+        <v>24</v>
       </c>
       <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="3">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
       <c r="G11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="C12" s="3">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="E12" s="30">
+        <v>28</v>
+      </c>
+      <c r="F12" s="3">
         <v>2</v>
       </c>
-      <c r="E12" s="31">
-        <v>27</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
       <c r="G12" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4</v>
+      </c>
+      <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="C13" s="3">
+      <c r="E13" s="3">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
         <v>3</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>4</v>
-      </c>
-      <c r="F13" s="3">
-        <v>11</v>
-      </c>
-      <c r="G13" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3">
         <v>6</v>
-      </c>
-      <c r="D14" s="3">
-        <v>5</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="B15" s="31">
+        <v>882</v>
+      </c>
+      <c r="B15" s="30">
         <v>21</v>
       </c>
       <c r="C15" s="3">
@@ -22277,7 +22521,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -22300,9 +22544,9 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="B17" s="31">
+        <v>884</v>
+      </c>
+      <c r="B17" s="30">
         <v>27</v>
       </c>
       <c r="C17" s="3">
@@ -22314,7 +22558,7 @@
       <c r="E17" s="3">
         <v>0</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>28</v>
       </c>
       <c r="G17" s="3">
@@ -22323,12 +22567,12 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>20</v>
       </c>
       <c r="D18" s="3">
@@ -22360,7 +22604,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -22370,62 +22614,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -22435,42 +22679,42 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -22480,22 +22724,22 @@
     </row>
     <row r="25" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -22505,27 +22749,27 @@
     </row>
     <row r="30" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
@@ -22535,12 +22779,12 @@
     </row>
     <row r="36" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4918" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4947" uniqueCount="1066">
   <si>
     <t>日期</t>
   </si>
@@ -1601,15 +1601,21 @@
     <t>10-08 23:00</t>
   </si>
   <si>
+    <t>6球</t>
+  </si>
+  <si>
     <t>1球 @6</t>
   </si>
   <si>
-    <t>4球 @5 ⚡</t>
+    <t>4球 @5</t>
   </si>
   <si>
     <t>10-08 17:00</t>
   </si>
   <si>
+    <t>10-09 11:00</t>
+  </si>
+  <si>
     <t>库奥皮奥</t>
   </si>
   <si>
@@ -1622,10 +1628,7 @@
     <t>3球 @3.5</t>
   </si>
   <si>
-    <t>3球 @3.5 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5.45 ⚡</t>
+    <t>4球 @5.45</t>
   </si>
   <si>
     <t>桑托斯</t>
@@ -1640,18 +1643,12 @@
     <t>3球 @3.4</t>
   </si>
   <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
     <t>米竞技</t>
   </si>
   <si>
     <t>10-09 07:00</t>
   </si>
   <si>
-    <t>3球 @3.45 ⚡</t>
-  </si>
-  <si>
     <t>弗鲁米嫩</t>
   </si>
   <si>
@@ -1664,13 +1661,13 @@
     <t>2球 @3.55</t>
   </si>
   <si>
-    <t>4球 @5.3 ⚡</t>
+    <t>4球 @5.3</t>
   </si>
   <si>
     <t>帕梅拉斯</t>
   </si>
   <si>
-    <t>4球 @5.1 ⚡</t>
+    <t>4球 @5.1</t>
   </si>
   <si>
     <t>2026-10-09</t>
@@ -1736,9 +1733,6 @@
     <t>6球 @13</t>
   </si>
   <si>
-    <t>1球 @6.35 ⚡</t>
-  </si>
-  <si>
     <t>4球 @4.8 ⚡</t>
   </si>
   <si>
@@ -1781,10 +1775,10 @@
     <t>10-10 02:30</t>
   </si>
   <si>
-    <t>1球 @8.6 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @4.25 ⚡</t>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @4 ⚡</t>
   </si>
   <si>
     <t>朗斯</t>
@@ -1799,9 +1793,6 @@
     <t>7+球 @16</t>
   </si>
   <si>
-    <t>0球 @20 ⚡</t>
-  </si>
-  <si>
     <t>西汉姆联</t>
   </si>
   <si>
@@ -1895,9 +1886,6 @@
     <t>0:5=1000 1:4=250 2:3=55 3:2=29 4:1=29 5:0=55</t>
   </si>
   <si>
-    <t>6球</t>
-  </si>
-  <si>
     <t>1:5=800 2:4=300 3:3=90 4:2=70 5:1=70</t>
   </si>
   <si>
@@ -2660,19 +2648,16 @@
     <t>2:5=300 5:2=80 负其他=80 平其他=200 胜其他=33</t>
   </si>
   <si>
-    <t>0:0=19</t>
-  </si>
-  <si>
     <t>0:1=17 1:0=8.75</t>
   </si>
   <si>
-    <t>0:2=28 1:1=8 2:0=8.75</t>
-  </si>
-  <si>
-    <t>0:3=80 1:2=12 2:1=7.25 3:0=12</t>
-  </si>
-  <si>
-    <t>0:4=350 1:3=39 2:2=14 3:1=11.5 4:0=21</t>
+    <t>0:2=29 1:1=8 2:0=8.75</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=12.5 2:1=7 3:0=12</t>
+  </si>
+  <si>
+    <t>0:4=350 1:3=42 2:2=14 3:1=11 4:0=21</t>
   </si>
   <si>
     <t>0:5=750 1:4=175 2:3=32 3:2=19 4:1=21 5:0=55</t>
@@ -2759,22 +2744,22 @@
     <t>0:0=28</t>
   </si>
   <si>
-    <t>0:1=29 1:0=11</t>
-  </si>
-  <si>
-    <t>0:2=55 1:1=11 2:0=8.5</t>
-  </si>
-  <si>
-    <t>0:3=175 1:2=20 2:1=7.25 3:0=10</t>
-  </si>
-  <si>
-    <t>0:4=550 1:3=60 2:2=16 3:1=9 4:0=15</t>
-  </si>
-  <si>
-    <t>0:5=1000 1:4=250 2:3=50 3:2=17 4:1=14 5:0=30</t>
-  </si>
-  <si>
-    <t>1:5=650 2:4=200 3:3=47 4:2=27 5:1=27</t>
+    <t>0:1=34 1:0=11</t>
+  </si>
+  <si>
+    <t>0:2=70 1:1=11.5 2:0=8</t>
+  </si>
+  <si>
+    <t>0:3=200 1:2=25 2:1=7.5 3:0=9</t>
+  </si>
+  <si>
+    <t>0:4=550 1:3=75 2:2=16 3:1=8.5 4:0=15</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=250 2:3=60 3:2=17 4:1=13 5:0=26</t>
+  </si>
+  <si>
+    <t>1:5=650 2:4=200 3:3=55 4:2=25 5:1=27</t>
   </si>
   <si>
     <t>2:5=550 5:2=50 负其他=175 平其他=250 胜其他=13</t>
@@ -2861,7 +2846,7 @@
     <t>2:5=250 5:2=550 负其他=60 平其他=550 胜其他=175</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-08T17:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-09T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -2876,25 +2861,25 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>6/25 = 24.0%</t>
+    <t>6/29 = 20.7%</t>
   </si>
   <si>
     <t>模型A 命中率（自修正）</t>
   </si>
   <si>
-    <t>5/25 = 20.0%</t>
+    <t>5/29 = 17.2%</t>
   </si>
   <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
-    <t>8/25 = 32.0%</t>
+    <t>8/29 = 27.6%</t>
   </si>
   <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
   </si>
   <si>
-    <t>近 30 天窗口（2026-09-08 ~ 2026-10-08）</t>
+    <t>近 30 天窗口（2026-09-09 ~ 2026-10-09）</t>
   </si>
   <si>
     <t>窗口内有预测场次</t>
@@ -2915,7 +2900,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>22 场（另剔除爆冷 3 场）</t>
+    <t>25 场（另剔除爆冷 4 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -2951,10 +2936,10 @@
     <t>0% (0/2)</t>
   </si>
   <si>
-    <t>33% (2/6)</t>
-  </si>
-  <si>
-    <t>0% (0/9)</t>
+    <t>25% (2/8)</t>
+  </si>
+  <si>
+    <t>0% (0/10)</t>
   </si>
   <si>
     <t>0% (0/3)</t>
@@ -2966,21 +2951,21 @@
     <t>25% (1/4)</t>
   </si>
   <si>
-    <t>0% (0/5)</t>
+    <t>0% (0/6)</t>
+  </si>
+  <si>
+    <t>33% (3/9)</t>
+  </si>
+  <si>
+    <t>14% (1/7)</t>
+  </si>
+  <si>
+    <t>0% (0/8)</t>
   </si>
   <si>
     <t>29% (2/7)</t>
   </si>
   <si>
-    <t>14% (1/7)</t>
-  </si>
-  <si>
-    <t>0% (0/6)</t>
-  </si>
-  <si>
-    <t>50% (2/4)</t>
-  </si>
-  <si>
     <t>20% (2/10)</t>
   </si>
   <si>
@@ -2990,16 +2975,16 @@
     <t>33% (1/3)</t>
   </si>
   <si>
-    <t>29% (4/14)</t>
-  </si>
-  <si>
-    <t>0% (0/10)</t>
-  </si>
-  <si>
-    <t>0% (0/15)</t>
-  </si>
-  <si>
-    <t>0% (0/20)</t>
+    <t>35% (6/17)</t>
+  </si>
+  <si>
+    <t>0% (0/11)</t>
+  </si>
+  <si>
+    <t>0% (0/17)</t>
+  </si>
+  <si>
+    <t>0% (0/23)</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -3116,7 +3101,7 @@
     <t>010</t>
   </si>
   <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-07，警戒线 30 次）</t>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-08，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -3352,10 +3337,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -10577,28 +10560,28 @@
         <v>55</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>21</v>
+        <v>527</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="L27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" t="s">
-        <v>21</v>
+        <v>529</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O27" t="s">
-        <v>21</v>
+        <v>531</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -10612,40 +10595,40 @@
         <v>494</v>
       </c>
       <c r="D28" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E28" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F28" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="L28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" t="s">
-        <v>21</v>
+        <v>536</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N28" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O28" t="s">
-        <v>21</v>
+        <v>531</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -10659,22 +10642,22 @@
         <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E29" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F29" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>540</v>
@@ -10682,17 +10665,17 @@
       <c r="K29" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="L29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" t="s">
-        <v>21</v>
+      <c r="L29" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N29" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O29" t="s">
-        <v>21</v>
+        <v>531</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -10718,28 +10701,28 @@
         <v>55</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>486</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>543</v>
+        <v>486</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="L30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" t="s">
-        <v>21</v>
+        <v>486</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="N30" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O30" t="s">
-        <v>21</v>
+        <v>531</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -10753,13 +10736,13 @@
         <v>144</v>
       </c>
       <c r="D31" t="s">
+        <v>543</v>
+      </c>
+      <c r="E31" t="s">
         <v>544</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>545</v>
-      </c>
-      <c r="F31" t="s">
-        <v>546</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>55</v>
@@ -10768,13 +10751,13 @@
         <v>21</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>548</v>
-      </c>
       <c r="K31" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L31" t="s">
         <v>21</v>
@@ -10783,7 +10766,7 @@
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O31" t="s">
         <v>21</v>
@@ -10800,13 +10783,13 @@
         <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E32" t="s">
         <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>55</v>
@@ -10818,10 +10801,10 @@
         <v>486</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>543</v>
+        <v>486</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L32" t="s">
         <v>21</v>
@@ -10830,7 +10813,7 @@
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O32" t="s">
         <v>21</v>
@@ -10838,7 +10821,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B33" t="s">
         <v>221</v>
@@ -10850,10 +10833,10 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
+        <v>551</v>
+      </c>
+      <c r="F33" t="s">
         <v>552</v>
-      </c>
-      <c r="F33" t="s">
-        <v>553</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>55</v>
@@ -10862,14 +10845,14 @@
         <v>21</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="K33" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>556</v>
-      </c>
       <c r="L33" t="s">
         <v>21</v>
       </c>
@@ -10877,7 +10860,7 @@
         <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O33" t="s">
         <v>21</v>
@@ -10885,7 +10868,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B34" t="s">
         <v>225</v>
@@ -10900,23 +10883,23 @@
         <v>31</v>
       </c>
       <c r="F34" t="s">
+        <v>556</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>560</v>
-      </c>
       <c r="L34" t="s">
         <v>21</v>
       </c>
@@ -10924,7 +10907,7 @@
         <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O34" t="s">
         <v>21</v>
@@ -10932,22 +10915,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B35" t="s">
         <v>228</v>
       </c>
       <c r="C35" t="s">
+        <v>560</v>
+      </c>
+      <c r="D35" t="s">
         <v>561</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>562</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>563</v>
-      </c>
-      <c r="F35" t="s">
-        <v>564</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>55</v>
@@ -10956,14 +10939,14 @@
         <v>21</v>
       </c>
       <c r="I35" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>567</v>
-      </c>
       <c r="L35" t="s">
         <v>21</v>
       </c>
@@ -10971,7 +10954,7 @@
         <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O35" t="s">
         <v>21</v>
@@ -10979,7 +10962,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B36" t="s">
         <v>233</v>
@@ -10988,13 +10971,13 @@
         <v>91</v>
       </c>
       <c r="D36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E36" t="s">
         <v>568</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>569</v>
-      </c>
-      <c r="F36" t="s">
-        <v>570</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>55</v>
@@ -11003,13 +10986,13 @@
         <v>21</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>572</v>
-      </c>
       <c r="K36" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L36" t="s">
         <v>21</v>
@@ -11018,7 +11001,7 @@
         <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O36" t="s">
         <v>21</v>
@@ -11026,7 +11009,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B37" t="s">
         <v>236</v>
@@ -11035,13 +11018,13 @@
         <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E37" t="s">
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>55</v>
@@ -11050,14 +11033,14 @@
         <v>21</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>577</v>
-      </c>
       <c r="L37" t="s">
         <v>21</v>
       </c>
@@ -11065,7 +11048,7 @@
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O37" t="s">
         <v>21</v>
@@ -11073,7 +11056,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B38" t="s">
         <v>239</v>
@@ -11085,25 +11068,25 @@
         <v>60</v>
       </c>
       <c r="E38" t="s">
+        <v>576</v>
+      </c>
+      <c r="F38" t="s">
+        <v>577</v>
+      </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="F38" t="s">
+      <c r="J38" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="G38" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>581</v>
-      </c>
       <c r="K38" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L38" t="s">
         <v>21</v>
@@ -11112,7 +11095,7 @@
         <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O38" t="s">
         <v>21</v>
@@ -11120,7 +11103,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B39" t="s">
         <v>243</v>
@@ -11135,7 +11118,7 @@
         <v>312</v>
       </c>
       <c r="F39" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>55</v>
@@ -11144,13 +11127,13 @@
         <v>21</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L39" t="s">
         <v>21</v>
@@ -11159,7 +11142,7 @@
         <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O39" t="s">
         <v>21</v>
@@ -11167,7 +11150,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B40" t="s">
         <v>246</v>
@@ -11176,13 +11159,13 @@
         <v>81</v>
       </c>
       <c r="D40" t="s">
+        <v>582</v>
+      </c>
+      <c r="E40" t="s">
+        <v>583</v>
+      </c>
+      <c r="F40" t="s">
         <v>584</v>
-      </c>
-      <c r="E40" t="s">
-        <v>585</v>
-      </c>
-      <c r="F40" t="s">
-        <v>586</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>55</v>
@@ -11191,13 +11174,13 @@
         <v>21</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>491</v>
+        <v>580</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="L40" t="s">
         <v>21</v>
@@ -11206,7 +11189,7 @@
         <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O40" t="s">
         <v>21</v>
@@ -11214,7 +11197,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B41" t="s">
         <v>250</v>
@@ -11223,28 +11206,28 @@
         <v>101</v>
       </c>
       <c r="D41" t="s">
+        <v>587</v>
+      </c>
+      <c r="E41" t="s">
+        <v>588</v>
+      </c>
+      <c r="F41" t="s">
         <v>589</v>
       </c>
-      <c r="E41" t="s">
+      <c r="G41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="F41" t="s">
-        <v>591</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>592</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L41" t="s">
         <v>21</v>
@@ -11253,7 +11236,7 @@
         <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O41" t="s">
         <v>21</v>
@@ -11261,7 +11244,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B42" t="s">
         <v>253</v>
@@ -11270,13 +11253,13 @@
         <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E42" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F42" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>55</v>
@@ -11285,13 +11268,13 @@
         <v>21</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L42" t="s">
         <v>21</v>
@@ -11300,7 +11283,7 @@
         <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O42" t="s">
         <v>21</v>
@@ -11308,7 +11291,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B43" t="s">
         <v>256</v>
@@ -11320,10 +11303,10 @@
         <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="F43" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>55</v>
@@ -11335,10 +11318,10 @@
         <v>469</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="L43" t="s">
         <v>21</v>
@@ -11347,7 +11330,7 @@
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O43" t="s">
         <v>21</v>
@@ -11355,7 +11338,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B44" t="s">
         <v>259</v>
@@ -11364,13 +11347,13 @@
         <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E44" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F44" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>55</v>
@@ -11379,13 +11362,13 @@
         <v>21</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="L44" t="s">
         <v>21</v>
@@ -11394,7 +11377,7 @@
         <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O44" t="s">
         <v>21</v>
@@ -11430,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -11439,31 +11422,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11496,7 +11479,7 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="4" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -11537,7 +11520,7 @@
         <v>-56</v>
       </c>
       <c r="M3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -11578,7 +11561,7 @@
         <v>-80.2</v>
       </c>
       <c r="M4" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -11619,7 +11602,7 @@
         <v>-87.8</v>
       </c>
       <c r="M5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -11660,7 +11643,7 @@
         <v>-93.3</v>
       </c>
       <c r="M6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -11701,7 +11684,7 @@
         <v>-94.7</v>
       </c>
       <c r="M7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -11718,7 +11701,7 @@
         <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F8" s="12">
         <v>25</v>
@@ -11742,7 +11725,7 @@
         <v>-90.6</v>
       </c>
       <c r="M8" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -11759,7 +11742,7 @@
         <v>245</v>
       </c>
       <c r="E9" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F9" s="12">
         <v>40</v>
@@ -11783,7 +11766,7 @@
         <v>-89.4</v>
       </c>
       <c r="M9" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -11816,7 +11799,7 @@
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -11857,7 +11840,7 @@
         <v>-55.2</v>
       </c>
       <c r="M11" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -11898,7 +11881,7 @@
         <v>-76.7</v>
       </c>
       <c r="M12" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -11939,7 +11922,7 @@
         <v>-88.4</v>
       </c>
       <c r="M13" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -11980,7 +11963,7 @@
         <v>-94.1</v>
       </c>
       <c r="M14" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -12021,7 +12004,7 @@
         <v>-96.2</v>
       </c>
       <c r="M15" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -12038,7 +12021,7 @@
         <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F16" s="12">
         <v>11.5</v>
@@ -12062,7 +12045,7 @@
         <v>-91.9</v>
       </c>
       <c r="M16" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -12079,7 +12062,7 @@
         <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F17" s="12">
         <v>15</v>
@@ -12103,7 +12086,7 @@
         <v>-91.6</v>
       </c>
       <c r="M17" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12136,7 +12119,7 @@
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="4" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -12177,7 +12160,7 @@
         <v>-48.7</v>
       </c>
       <c r="M19" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -12218,7 +12201,7 @@
         <v>-72.3</v>
       </c>
       <c r="M20" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -12259,7 +12242,7 @@
         <v>-84</v>
       </c>
       <c r="M21" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -12300,7 +12283,7 @@
         <v>-91</v>
       </c>
       <c r="M22" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -12341,7 +12324,7 @@
         <v>-91.6</v>
       </c>
       <c r="M23" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -12358,7 +12341,7 @@
         <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F24" s="12">
         <v>15</v>
@@ -12382,7 +12365,7 @@
         <v>-83.9</v>
       </c>
       <c r="M24" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -12399,7 +12382,7 @@
         <v>260</v>
       </c>
       <c r="E25" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F25" s="12">
         <v>21</v>
@@ -12423,7 +12406,7 @@
         <v>-84</v>
       </c>
       <c r="M25" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12456,7 +12439,7 @@
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="4" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -12497,7 +12480,7 @@
         <v>-58.3</v>
       </c>
       <c r="M27" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -12538,7 +12521,7 @@
         <v>-80.7</v>
       </c>
       <c r="M28" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -12579,7 +12562,7 @@
         <v>-90.3</v>
       </c>
       <c r="M29" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -12620,7 +12603,7 @@
         <v>-94.8</v>
       </c>
       <c r="M30" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -12661,7 +12644,7 @@
         <v>-95.2</v>
       </c>
       <c r="M31" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -12678,7 +12661,7 @@
         <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F32" s="12">
         <v>13.5</v>
@@ -12702,7 +12685,7 @@
         <v>-90.5</v>
       </c>
       <c r="M32" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -12719,7 +12702,7 @@
         <v>257</v>
       </c>
       <c r="E33" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F33" s="12">
         <v>17.5</v>
@@ -12743,7 +12726,7 @@
         <v>-90.1</v>
       </c>
       <c r="M33" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -12776,7 +12759,7 @@
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -12817,7 +12800,7 @@
         <v>-49.8</v>
       </c>
       <c r="M35" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -12858,7 +12841,7 @@
         <v>-68.8</v>
       </c>
       <c r="M36" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -12899,7 +12882,7 @@
         <v>-79.8</v>
       </c>
       <c r="M37" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -12940,7 +12923,7 @@
         <v>-85.8</v>
       </c>
       <c r="M38" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -12981,7 +12964,7 @@
         <v>-87.4</v>
       </c>
       <c r="M39" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -12998,7 +12981,7 @@
         <v>240</v>
       </c>
       <c r="E40" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F40" s="12">
         <v>36</v>
@@ -13022,7 +13005,7 @@
         <v>-80.8</v>
       </c>
       <c r="M40" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -13039,7 +13022,7 @@
         <v>240</v>
       </c>
       <c r="E41" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F41" s="12">
         <v>60</v>
@@ -13063,7 +13046,7 @@
         <v>-84</v>
       </c>
       <c r="M41" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13096,7 +13079,7 @@
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="4" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -13137,7 +13120,7 @@
         <v>-54.5</v>
       </c>
       <c r="M43" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -13178,7 +13161,7 @@
         <v>-78.6</v>
       </c>
       <c r="M44" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -13219,7 +13202,7 @@
         <v>-89.4</v>
       </c>
       <c r="M45" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -13260,7 +13243,7 @@
         <v>-93.6</v>
       </c>
       <c r="M46" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -13301,7 +13284,7 @@
         <v>-95.3</v>
       </c>
       <c r="M47" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -13318,7 +13301,7 @@
         <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F48" s="12">
         <v>15.5</v>
@@ -13342,7 +13325,7 @@
         <v>-91.2</v>
       </c>
       <c r="M48" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -13359,7 +13342,7 @@
         <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F49" s="12">
         <v>25</v>
@@ -13383,7 +13366,7 @@
         <v>-89.5</v>
       </c>
       <c r="M49" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13416,7 +13399,7 @@
       </c>
       <c r="L50" s="11"/>
       <c r="M50" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -13457,7 +13440,7 @@
         <v>-46</v>
       </c>
       <c r="M51" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -13498,7 +13481,7 @@
         <v>-71.7</v>
       </c>
       <c r="M52" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -13539,7 +13522,7 @@
         <v>-80.8</v>
       </c>
       <c r="M53" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -13580,7 +13563,7 @@
         <v>-85.6</v>
       </c>
       <c r="M54" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -13621,7 +13604,7 @@
         <v>-90.2</v>
       </c>
       <c r="M55" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -13638,7 +13621,7 @@
         <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F56" s="12">
         <v>21</v>
@@ -13662,7 +13645,7 @@
         <v>-80.4</v>
       </c>
       <c r="M56" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -13679,7 +13662,7 @@
         <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F57" s="12">
         <v>34</v>
@@ -13703,7 +13686,7 @@
         <v>-81.9</v>
       </c>
       <c r="M57" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13736,7 +13719,7 @@
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="4" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -13777,7 +13760,7 @@
         <v>-49.6</v>
       </c>
       <c r="M59" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -13818,7 +13801,7 @@
         <v>-74.9</v>
       </c>
       <c r="M60" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -13859,7 +13842,7 @@
         <v>-88.2</v>
       </c>
       <c r="M61" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -13900,7 +13883,7 @@
         <v>-91.6</v>
       </c>
       <c r="M62" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -13941,7 +13924,7 @@
         <v>-94.9</v>
       </c>
       <c r="M63" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -13958,7 +13941,7 @@
         <v>452</v>
       </c>
       <c r="E64" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F64" s="12">
         <v>15</v>
@@ -13982,7 +13965,7 @@
         <v>-90.1</v>
       </c>
       <c r="M64" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -13999,7 +13982,7 @@
         <v>452</v>
       </c>
       <c r="E65" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F65" s="12">
         <v>18</v>
@@ -14023,7 +14006,7 @@
         <v>-91.4</v>
       </c>
       <c r="M65" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14056,7 +14039,7 @@
       </c>
       <c r="L66" s="11"/>
       <c r="M66" s="4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -14097,7 +14080,7 @@
         <v>-51.7</v>
       </c>
       <c r="M67" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -14138,7 +14121,7 @@
         <v>-73.4</v>
       </c>
       <c r="M68" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -14179,7 +14162,7 @@
         <v>-83.2</v>
       </c>
       <c r="M69" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -14220,7 +14203,7 @@
         <v>-88.2</v>
       </c>
       <c r="M70" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -14261,7 +14244,7 @@
         <v>-86.5</v>
       </c>
       <c r="M71" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -14278,7 +14261,7 @@
         <v>460</v>
       </c>
       <c r="E72" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F72" s="12">
         <v>27</v>
@@ -14302,7 +14285,7 @@
         <v>-80.7</v>
       </c>
       <c r="M72" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -14319,7 +14302,7 @@
         <v>460</v>
       </c>
       <c r="E73" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F73" s="12">
         <v>45</v>
@@ -14343,7 +14326,7 @@
         <v>-82.9</v>
       </c>
       <c r="M73" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14376,7 +14359,7 @@
       </c>
       <c r="L74" s="11"/>
       <c r="M74" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -14417,7 +14400,7 @@
         <v>-48.3</v>
       </c>
       <c r="M75" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -14458,7 +14441,7 @@
         <v>-68.4</v>
       </c>
       <c r="M76" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -14499,7 +14482,7 @@
         <v>-80.5</v>
       </c>
       <c r="M77" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -14540,7 +14523,7 @@
         <v>-86.5</v>
       </c>
       <c r="M78" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -14581,7 +14564,7 @@
         <v>-87.7</v>
       </c>
       <c r="M79" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -14598,7 +14581,7 @@
         <v>301</v>
       </c>
       <c r="E80" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F80" s="12">
         <v>38</v>
@@ -14622,7 +14605,7 @@
         <v>-75.9</v>
       </c>
       <c r="M80" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -14639,7 +14622,7 @@
         <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F81" s="12">
         <v>70</v>
@@ -14663,7 +14646,7 @@
         <v>-78.5</v>
       </c>
       <c r="M81" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -14696,7 +14679,7 @@
       </c>
       <c r="L82" s="11"/>
       <c r="M82" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -14737,7 +14720,7 @@
         <v>-50.9</v>
       </c>
       <c r="M83" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -14778,7 +14761,7 @@
         <v>-76.5</v>
       </c>
       <c r="M84" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -14819,7 +14802,7 @@
         <v>-87.5</v>
       </c>
       <c r="M85" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -14860,7 +14843,7 @@
         <v>-92.7</v>
       </c>
       <c r="M86" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -14901,7 +14884,7 @@
         <v>-94.2</v>
       </c>
       <c r="M87" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -14918,7 +14901,7 @@
         <v>305</v>
       </c>
       <c r="E88" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F88" s="12">
         <v>24</v>
@@ -14942,7 +14925,7 @@
         <v>-89.6</v>
       </c>
       <c r="M88" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -14959,7 +14942,7 @@
         <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F89" s="12">
         <v>35</v>
@@ -14983,7 +14966,7 @@
         <v>-88.8</v>
       </c>
       <c r="M89" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15016,7 +14999,7 @@
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="4" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -15057,7 +15040,7 @@
         <v>-50.8</v>
       </c>
       <c r="M91" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -15098,7 +15081,7 @@
         <v>-68.8</v>
       </c>
       <c r="M92" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -15139,7 +15122,7 @@
         <v>-84</v>
       </c>
       <c r="M93" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -15180,7 +15163,7 @@
         <v>-87.8</v>
       </c>
       <c r="M94" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -15221,7 +15204,7 @@
         <v>-89.3</v>
       </c>
       <c r="M95" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -15238,7 +15221,7 @@
         <v>308</v>
       </c>
       <c r="E96" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F96" s="12">
         <v>42</v>
@@ -15262,7 +15245,7 @@
         <v>-78.5</v>
       </c>
       <c r="M96" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -15279,7 +15262,7 @@
         <v>308</v>
       </c>
       <c r="E97" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F97" s="12">
         <v>80</v>
@@ -15303,7 +15286,7 @@
         <v>-79.7</v>
       </c>
       <c r="M97" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15336,7 +15319,7 @@
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="4" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -15377,7 +15360,7 @@
         <v>-52.4</v>
       </c>
       <c r="M99" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -15418,7 +15401,7 @@
         <v>-74</v>
       </c>
       <c r="M100" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -15459,7 +15442,7 @@
         <v>-86.3</v>
       </c>
       <c r="M101" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -15500,7 +15483,7 @@
         <v>-91.6</v>
       </c>
       <c r="M102" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -15541,7 +15524,7 @@
         <v>-92.2</v>
       </c>
       <c r="M103" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -15558,7 +15541,7 @@
         <v>293</v>
       </c>
       <c r="E104" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F104" s="12">
         <v>35</v>
@@ -15582,7 +15565,7 @@
         <v>-81.8</v>
       </c>
       <c r="M104" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -15599,7 +15582,7 @@
         <v>293</v>
       </c>
       <c r="E105" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F105" s="12">
         <v>60</v>
@@ -15623,7 +15606,7 @@
         <v>-82.4</v>
       </c>
       <c r="M105" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15656,7 +15639,7 @@
       </c>
       <c r="L106" s="11"/>
       <c r="M106" s="4" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -15697,7 +15680,7 @@
         <v>-66.4</v>
       </c>
       <c r="M107" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
@@ -15738,7 +15721,7 @@
         <v>-89.7</v>
       </c>
       <c r="M108" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
@@ -15779,7 +15762,7 @@
         <v>-96.9</v>
       </c>
       <c r="M109" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
@@ -15820,7 +15803,7 @@
         <v>-98.4</v>
       </c>
       <c r="M110" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -15861,7 +15844,7 @@
         <v>-98.2</v>
       </c>
       <c r="M111" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -15878,7 +15861,7 @@
         <v>315</v>
       </c>
       <c r="E112" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F112" s="12">
         <v>8.8</v>
@@ -15902,7 +15885,7 @@
         <v>-97.2</v>
       </c>
       <c r="M112" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
@@ -15919,7 +15902,7 @@
         <v>315</v>
       </c>
       <c r="E113" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F113" s="12">
         <v>9</v>
@@ -15943,7 +15926,7 @@
         <v>-97.7</v>
       </c>
       <c r="M113" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -15976,7 +15959,7 @@
       </c>
       <c r="L114" s="11"/>
       <c r="M114" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
@@ -16017,7 +16000,7 @@
         <v>-58.4</v>
       </c>
       <c r="M115" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -16058,7 +16041,7 @@
         <v>-81.7</v>
       </c>
       <c r="M116" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
@@ -16099,7 +16082,7 @@
         <v>-92.4</v>
       </c>
       <c r="M117" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
@@ -16140,7 +16123,7 @@
         <v>-96.5</v>
       </c>
       <c r="M118" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -16181,7 +16164,7 @@
         <v>-97</v>
       </c>
       <c r="M119" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -16198,7 +16181,7 @@
         <v>323</v>
       </c>
       <c r="E120" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F120" s="12">
         <v>12</v>
@@ -16222,7 +16205,7 @@
         <v>-94</v>
       </c>
       <c r="M120" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -16239,7 +16222,7 @@
         <v>323</v>
       </c>
       <c r="E121" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F121" s="12">
         <v>14</v>
@@ -16263,7 +16246,7 @@
         <v>-93.4</v>
       </c>
       <c r="M121" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -16296,7 +16279,7 @@
       </c>
       <c r="L122" s="11"/>
       <c r="M122" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -16337,7 +16320,7 @@
         <v>-74.2</v>
       </c>
       <c r="M123" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -16378,7 +16361,7 @@
         <v>-92.3</v>
       </c>
       <c r="M124" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -16419,7 +16402,7 @@
         <v>-98.1</v>
       </c>
       <c r="M125" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -16460,7 +16443,7 @@
         <v>-98.5</v>
       </c>
       <c r="M126" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -16501,7 +16484,7 @@
         <v>-98.3</v>
       </c>
       <c r="M127" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -16518,7 +16501,7 @@
         <v>319</v>
       </c>
       <c r="E128" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F128" s="12">
         <v>11</v>
@@ -16542,7 +16525,7 @@
         <v>-97.5</v>
       </c>
       <c r="M128" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -16559,7 +16542,7 @@
         <v>319</v>
       </c>
       <c r="E129" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F129" s="12">
         <v>12</v>
@@ -16583,7 +16566,7 @@
         <v>-97.7</v>
       </c>
       <c r="M129" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -16616,7 +16599,7 @@
       </c>
       <c r="L130" s="11"/>
       <c r="M130" s="4" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -16657,7 +16640,7 @@
         <v>-58</v>
       </c>
       <c r="M131" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -16698,7 +16681,7 @@
         <v>-81.6</v>
       </c>
       <c r="M132" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -16739,7 +16722,7 @@
         <v>-90.8</v>
       </c>
       <c r="M133" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -16780,7 +16763,7 @@
         <v>-95.8</v>
       </c>
       <c r="M134" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -16821,7 +16804,7 @@
         <v>-95.9</v>
       </c>
       <c r="M135" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -16838,7 +16821,7 @@
         <v>410</v>
       </c>
       <c r="E136" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F136" s="12">
         <v>20</v>
@@ -16862,7 +16845,7 @@
         <v>-93.3</v>
       </c>
       <c r="M136" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -16879,7 +16862,7 @@
         <v>410</v>
       </c>
       <c r="E137" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F137" s="12">
         <v>30</v>
@@ -16903,7 +16886,7 @@
         <v>-92.7</v>
       </c>
       <c r="M137" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -16936,7 +16919,7 @@
       </c>
       <c r="L138" s="11"/>
       <c r="M138" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -16977,7 +16960,7 @@
         <v>-49</v>
       </c>
       <c r="M139" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -17018,7 +17001,7 @@
         <v>-72.3</v>
       </c>
       <c r="M140" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -17059,7 +17042,7 @@
         <v>-83.6</v>
       </c>
       <c r="M141" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -17100,7 +17083,7 @@
         <v>-88.7</v>
       </c>
       <c r="M142" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -17141,7 +17124,7 @@
         <v>-93.2</v>
       </c>
       <c r="M143" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -17158,7 +17141,7 @@
         <v>329</v>
       </c>
       <c r="E144" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F144" s="12">
         <v>15.5</v>
@@ -17182,7 +17165,7 @@
         <v>-85.4</v>
       </c>
       <c r="M144" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -17199,7 +17182,7 @@
         <v>329</v>
       </c>
       <c r="E145" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F145" s="12">
         <v>21</v>
@@ -17223,7 +17206,7 @@
         <v>-85.1</v>
       </c>
       <c r="M145" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -17256,7 +17239,7 @@
       </c>
       <c r="L146" s="11"/>
       <c r="M146" s="4" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -17297,7 +17280,7 @@
         <v>-44.4</v>
       </c>
       <c r="M147" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -17338,7 +17321,7 @@
         <v>-67.9</v>
       </c>
       <c r="M148" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -17379,7 +17362,7 @@
         <v>-80.2</v>
       </c>
       <c r="M149" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -17420,7 +17403,7 @@
         <v>-87.4</v>
       </c>
       <c r="M150" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -17461,7 +17444,7 @@
         <v>-92.6</v>
       </c>
       <c r="M151" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -17478,7 +17461,7 @@
         <v>489</v>
       </c>
       <c r="E152" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F152" s="12">
         <v>10</v>
@@ -17502,7 +17485,7 @@
         <v>-84.3</v>
       </c>
       <c r="M152" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -17519,7 +17502,7 @@
         <v>489</v>
       </c>
       <c r="E153" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F153" s="12">
         <v>13</v>
@@ -17543,7 +17526,7 @@
         <v>-84.7</v>
       </c>
       <c r="M153" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -17576,7 +17559,7 @@
       </c>
       <c r="L154" s="11"/>
       <c r="M154" s="4" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
@@ -17617,7 +17600,7 @@
         <v>-49.5</v>
       </c>
       <c r="M155" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
@@ -17658,7 +17641,7 @@
         <v>-75.7</v>
       </c>
       <c r="M156" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
@@ -17699,7 +17682,7 @@
         <v>-86.8</v>
       </c>
       <c r="M157" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
@@ -17740,7 +17723,7 @@
         <v>-91.2</v>
       </c>
       <c r="M158" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
@@ -17781,7 +17764,7 @@
         <v>-92.3</v>
       </c>
       <c r="M159" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
@@ -17798,7 +17781,7 @@
         <v>496</v>
       </c>
       <c r="E160" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F160" s="12">
         <v>16</v>
@@ -17822,7 +17805,7 @@
         <v>-85.6</v>
       </c>
       <c r="M160" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
@@ -17839,7 +17822,7 @@
         <v>496</v>
       </c>
       <c r="E161" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F161" s="12">
         <v>24</v>
@@ -17863,7 +17846,7 @@
         <v>-83.8</v>
       </c>
       <c r="M161" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="162" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -17896,7 +17879,7 @@
       </c>
       <c r="L162" s="11"/>
       <c r="M162" s="4" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
@@ -17937,7 +17920,7 @@
         <v>-51</v>
       </c>
       <c r="M163" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
@@ -17978,7 +17961,7 @@
         <v>-66.7</v>
       </c>
       <c r="M164" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
@@ -18019,7 +18002,7 @@
         <v>-82.5</v>
       </c>
       <c r="M165" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
@@ -18060,7 +18043,7 @@
         <v>-86.5</v>
       </c>
       <c r="M166" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -18101,7 +18084,7 @@
         <v>-89.9</v>
       </c>
       <c r="M167" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
@@ -18118,7 +18101,7 @@
         <v>501</v>
       </c>
       <c r="E168" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F168" s="12">
         <v>37</v>
@@ -18142,7 +18125,7 @@
         <v>-77</v>
       </c>
       <c r="M168" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
@@ -18159,7 +18142,7 @@
         <v>501</v>
       </c>
       <c r="E169" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F169" s="12">
         <v>66</v>
@@ -18183,7 +18166,7 @@
         <v>-78.2</v>
       </c>
       <c r="M169" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="170" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -18216,7 +18199,7 @@
       </c>
       <c r="L170" s="11"/>
       <c r="M170" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
@@ -18257,7 +18240,7 @@
         <v>-43.9</v>
       </c>
       <c r="M171" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -18298,7 +18281,7 @@
         <v>-70.4</v>
       </c>
       <c r="M172" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -18339,7 +18322,7 @@
         <v>-81.9</v>
       </c>
       <c r="M173" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -18380,7 +18363,7 @@
         <v>-86.6</v>
       </c>
       <c r="M174" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -18421,7 +18404,7 @@
         <v>-90</v>
       </c>
       <c r="M175" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -18438,7 +18421,7 @@
         <v>504</v>
       </c>
       <c r="E176" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F176" s="12">
         <v>23</v>
@@ -18462,7 +18445,7 @@
         <v>-80.7</v>
       </c>
       <c r="M176" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -18479,7 +18462,7 @@
         <v>504</v>
       </c>
       <c r="E177" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F177" s="12">
         <v>39</v>
@@ -18503,7 +18486,7 @@
         <v>-80.6</v>
       </c>
       <c r="M177" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="178" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -18536,7 +18519,7 @@
       </c>
       <c r="L178" s="11"/>
       <c r="M178" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -18577,7 +18560,7 @@
         <v>-50.9</v>
       </c>
       <c r="M179" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
@@ -18618,7 +18601,7 @@
         <v>-74.1</v>
       </c>
       <c r="M180" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -18659,7 +18642,7 @@
         <v>-86.5</v>
       </c>
       <c r="M181" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
@@ -18700,7 +18683,7 @@
         <v>-90.7</v>
       </c>
       <c r="M182" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
@@ -18741,7 +18724,7 @@
         <v>-93.2</v>
       </c>
       <c r="M183" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -18758,7 +18741,7 @@
         <v>508</v>
       </c>
       <c r="E184" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F184" s="12">
         <v>19</v>
@@ -18782,7 +18765,7 @@
         <v>-87.3</v>
       </c>
       <c r="M184" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -18799,7 +18782,7 @@
         <v>508</v>
       </c>
       <c r="E185" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F185" s="12">
         <v>30</v>
@@ -18823,7 +18806,7 @@
         <v>-86.3</v>
       </c>
       <c r="M185" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="186" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -18856,7 +18839,7 @@
       </c>
       <c r="L186" s="11"/>
       <c r="M186" s="4" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -18897,7 +18880,7 @@
         <v>-51.4</v>
       </c>
       <c r="M187" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
@@ -18938,7 +18921,7 @@
         <v>-77.5</v>
       </c>
       <c r="M188" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
@@ -18979,7 +18962,7 @@
         <v>-87.9</v>
       </c>
       <c r="M189" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -19020,7 +19003,7 @@
         <v>-93</v>
       </c>
       <c r="M190" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -19061,7 +19044,7 @@
         <v>-94.8</v>
       </c>
       <c r="M191" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
@@ -19078,7 +19061,7 @@
         <v>512</v>
       </c>
       <c r="E192" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F192" s="12">
         <v>21</v>
@@ -19102,7 +19085,7 @@
         <v>-90</v>
       </c>
       <c r="M192" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -19119,7 +19102,7 @@
         <v>512</v>
       </c>
       <c r="E193" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F193" s="12">
         <v>33</v>
@@ -19143,7 +19126,7 @@
         <v>-89.4</v>
       </c>
       <c r="M193" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="194" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -19176,7 +19159,7 @@
       </c>
       <c r="L194" s="11"/>
       <c r="M194" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
@@ -19217,7 +19200,7 @@
         <v>-45.1</v>
       </c>
       <c r="M195" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
@@ -19258,7 +19241,7 @@
         <v>-69.1</v>
       </c>
       <c r="M196" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -19299,7 +19282,7 @@
         <v>-81.8</v>
       </c>
       <c r="M197" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
@@ -19340,7 +19323,7 @@
         <v>-87.6</v>
       </c>
       <c r="M198" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
@@ -19381,7 +19364,7 @@
         <v>-90.1</v>
       </c>
       <c r="M199" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
@@ -19398,7 +19381,7 @@
         <v>519</v>
       </c>
       <c r="E200" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F200" s="12">
         <v>18</v>
@@ -19422,7 +19405,7 @@
         <v>-81</v>
       </c>
       <c r="M200" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
@@ -19439,7 +19422,7 @@
         <v>519</v>
       </c>
       <c r="E201" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F201" s="12">
         <v>29</v>
@@ -19463,7 +19446,7 @@
         <v>-83.4</v>
       </c>
       <c r="M201" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="202" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -19496,7 +19479,7 @@
       </c>
       <c r="L202" s="11"/>
       <c r="M202" s="4" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.25">
@@ -19537,7 +19520,7 @@
         <v>-56.4</v>
       </c>
       <c r="M203" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.25">
@@ -19578,7 +19561,7 @@
         <v>-78.1</v>
       </c>
       <c r="M204" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.25">
@@ -19619,7 +19602,7 @@
         <v>-89.1</v>
       </c>
       <c r="M205" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
@@ -19660,7 +19643,7 @@
         <v>-93.7</v>
       </c>
       <c r="M206" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
@@ -19701,7 +19684,7 @@
         <v>-94.9</v>
       </c>
       <c r="M207" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
@@ -19718,7 +19701,7 @@
         <v>525</v>
       </c>
       <c r="E208" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F208" s="12">
         <v>16.5</v>
@@ -19742,7 +19725,7 @@
         <v>-89.2</v>
       </c>
       <c r="M208" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.25">
@@ -19759,7 +19742,7 @@
         <v>525</v>
       </c>
       <c r="E209" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F209" s="12">
         <v>25</v>
@@ -19783,7 +19766,7 @@
         <v>-87.3</v>
       </c>
       <c r="M209" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="210" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -19794,10 +19777,10 @@
         <v>195</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>442</v>
@@ -19816,7 +19799,7 @@
       </c>
       <c r="L210" s="11"/>
       <c r="M210" s="4" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.25">
@@ -19827,10 +19810,10 @@
         <v>195</v>
       </c>
       <c r="C211" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D211" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E211" t="s">
         <v>434</v>
@@ -19857,7 +19840,7 @@
         <v>-50.8</v>
       </c>
       <c r="M211" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.25">
@@ -19868,10 +19851,10 @@
         <v>195</v>
       </c>
       <c r="C212" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D212" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E212" t="s">
         <v>454</v>
@@ -19898,7 +19881,7 @@
         <v>-78.7</v>
       </c>
       <c r="M212" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
@@ -19909,10 +19892,10 @@
         <v>195</v>
       </c>
       <c r="C213" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D213" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E213" t="s">
         <v>423</v>
@@ -19939,7 +19922,7 @@
         <v>-88.9</v>
       </c>
       <c r="M213" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.25">
@@ -19950,10 +19933,10 @@
         <v>195</v>
       </c>
       <c r="C214" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D214" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E214" t="s">
         <v>439</v>
@@ -19980,7 +19963,7 @@
         <v>-94.1</v>
       </c>
       <c r="M214" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.25">
@@ -19991,10 +19974,10 @@
         <v>195</v>
       </c>
       <c r="C215" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D215" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E215" t="s">
         <v>431</v>
@@ -20021,7 +20004,7 @@
         <v>-95.7</v>
       </c>
       <c r="M215" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.25">
@@ -20032,13 +20015,13 @@
         <v>195</v>
       </c>
       <c r="C216" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D216" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E216" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F216" s="12">
         <v>20</v>
@@ -20062,7 +20045,7 @@
         <v>-92</v>
       </c>
       <c r="M216" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
@@ -20073,13 +20056,13 @@
         <v>195</v>
       </c>
       <c r="C217" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D217" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E217" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F217" s="12">
         <v>30</v>
@@ -20103,7 +20086,7 @@
         <v>-91.5</v>
       </c>
       <c r="M217" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="218" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -20114,10 +20097,10 @@
         <v>199</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>442</v>
@@ -20136,7 +20119,7 @@
       </c>
       <c r="L218" s="11"/>
       <c r="M218" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.25">
@@ -20147,10 +20130,10 @@
         <v>199</v>
       </c>
       <c r="C219" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D219" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E219" t="s">
         <v>434</v>
@@ -20177,7 +20160,7 @@
         <v>-51.6</v>
       </c>
       <c r="M219" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.25">
@@ -20188,10 +20171,10 @@
         <v>199</v>
       </c>
       <c r="C220" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D220" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E220" t="s">
         <v>454</v>
@@ -20218,7 +20201,7 @@
         <v>-72.9</v>
       </c>
       <c r="M220" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.25">
@@ -20229,10 +20212,10 @@
         <v>199</v>
       </c>
       <c r="C221" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D221" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E221" t="s">
         <v>423</v>
@@ -20259,7 +20242,7 @@
         <v>-86.4</v>
       </c>
       <c r="M221" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.25">
@@ -20270,10 +20253,10 @@
         <v>199</v>
       </c>
       <c r="C222" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D222" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E222" t="s">
         <v>439</v>
@@ -20300,7 +20283,7 @@
         <v>-90.4</v>
       </c>
       <c r="M222" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
@@ -20311,10 +20294,10 @@
         <v>199</v>
       </c>
       <c r="C223" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D223" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E223" t="s">
         <v>431</v>
@@ -20341,7 +20324,7 @@
         <v>-93.1</v>
       </c>
       <c r="M223" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.25">
@@ -20352,13 +20335,13 @@
         <v>199</v>
       </c>
       <c r="C224" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D224" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E224" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F224" s="12">
         <v>18.5</v>
@@ -20382,7 +20365,7 @@
         <v>-85.4</v>
       </c>
       <c r="M224" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
@@ -20393,13 +20376,13 @@
         <v>199</v>
       </c>
       <c r="C225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D225" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E225" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F225" s="12">
         <v>28</v>
@@ -20423,7 +20406,7 @@
         <v>-85.8</v>
       </c>
       <c r="M225" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="226" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -20456,7 +20439,7 @@
       </c>
       <c r="L226" s="11"/>
       <c r="M226" s="4" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
@@ -20497,7 +20480,7 @@
         <v>-49.6</v>
       </c>
       <c r="M227" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
@@ -20538,7 +20521,7 @@
         <v>-72.4</v>
       </c>
       <c r="M228" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
@@ -20579,7 +20562,7 @@
         <v>-83.4</v>
       </c>
       <c r="M229" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
@@ -20620,7 +20603,7 @@
         <v>-86</v>
       </c>
       <c r="M230" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
@@ -20661,7 +20644,7 @@
         <v>-89.6</v>
       </c>
       <c r="M231" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
@@ -20678,7 +20661,7 @@
         <v>541</v>
       </c>
       <c r="E232" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F232" s="12">
         <v>27</v>
@@ -20702,7 +20685,7 @@
         <v>-79.8</v>
       </c>
       <c r="M232" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
@@ -20719,7 +20702,7 @@
         <v>541</v>
       </c>
       <c r="E233" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F233" s="12">
         <v>50</v>
@@ -20743,7 +20726,7 @@
         <v>-79.8</v>
       </c>
       <c r="M233" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="234" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -20754,10 +20737,10 @@
         <v>208</v>
       </c>
       <c r="C234" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D234" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="D234" s="4" t="s">
-        <v>545</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>442</v>
@@ -20776,7 +20759,7 @@
       </c>
       <c r="L234" s="11"/>
       <c r="M234" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
@@ -20787,10 +20770,10 @@
         <v>208</v>
       </c>
       <c r="C235" t="s">
+        <v>543</v>
+      </c>
+      <c r="D235" t="s">
         <v>544</v>
-      </c>
-      <c r="D235" t="s">
-        <v>545</v>
       </c>
       <c r="E235" t="s">
         <v>434</v>
@@ -20817,7 +20800,7 @@
         <v>-55.3</v>
       </c>
       <c r="M235" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
@@ -20828,10 +20811,10 @@
         <v>208</v>
       </c>
       <c r="C236" t="s">
+        <v>543</v>
+      </c>
+      <c r="D236" t="s">
         <v>544</v>
-      </c>
-      <c r="D236" t="s">
-        <v>545</v>
       </c>
       <c r="E236" t="s">
         <v>454</v>
@@ -20858,7 +20841,7 @@
         <v>-79.7</v>
       </c>
       <c r="M236" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
@@ -20869,10 +20852,10 @@
         <v>208</v>
       </c>
       <c r="C237" t="s">
+        <v>543</v>
+      </c>
+      <c r="D237" t="s">
         <v>544</v>
-      </c>
-      <c r="D237" t="s">
-        <v>545</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -20899,7 +20882,7 @@
         <v>-91</v>
       </c>
       <c r="M237" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
@@ -20910,10 +20893,10 @@
         <v>208</v>
       </c>
       <c r="C238" t="s">
+        <v>543</v>
+      </c>
+      <c r="D238" t="s">
         <v>544</v>
-      </c>
-      <c r="D238" t="s">
-        <v>545</v>
       </c>
       <c r="E238" t="s">
         <v>439</v>
@@ -20940,7 +20923,7 @@
         <v>-95.3</v>
       </c>
       <c r="M238" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.25">
@@ -20951,10 +20934,10 @@
         <v>208</v>
       </c>
       <c r="C239" t="s">
+        <v>543</v>
+      </c>
+      <c r="D239" t="s">
         <v>544</v>
-      </c>
-      <c r="D239" t="s">
-        <v>545</v>
       </c>
       <c r="E239" t="s">
         <v>431</v>
@@ -20981,7 +20964,7 @@
         <v>-95.9</v>
       </c>
       <c r="M239" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
@@ -20992,13 +20975,13 @@
         <v>208</v>
       </c>
       <c r="C240" t="s">
+        <v>543</v>
+      </c>
+      <c r="D240" t="s">
         <v>544</v>
       </c>
-      <c r="D240" t="s">
-        <v>545</v>
-      </c>
       <c r="E240" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F240" s="12">
         <v>19</v>
@@ -21022,7 +21005,7 @@
         <v>-92.3</v>
       </c>
       <c r="M240" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
@@ -21033,13 +21016,13 @@
         <v>208</v>
       </c>
       <c r="C241" t="s">
+        <v>543</v>
+      </c>
+      <c r="D241" t="s">
         <v>544</v>
       </c>
-      <c r="D241" t="s">
-        <v>545</v>
-      </c>
       <c r="E241" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F241" s="12">
         <v>30</v>
@@ -21063,7 +21046,7 @@
         <v>-90.9</v>
       </c>
       <c r="M241" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="242" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -21074,7 +21057,7 @@
         <v>211</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>146</v>
@@ -21096,7 +21079,7 @@
       </c>
       <c r="L242" s="11"/>
       <c r="M242" s="4" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
@@ -21107,7 +21090,7 @@
         <v>211</v>
       </c>
       <c r="C243" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D243" t="s">
         <v>146</v>
@@ -21137,7 +21120,7 @@
         <v>-51.6</v>
       </c>
       <c r="M243" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
@@ -21148,7 +21131,7 @@
         <v>211</v>
       </c>
       <c r="C244" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D244" t="s">
         <v>146</v>
@@ -21178,7 +21161,7 @@
         <v>-77.4</v>
       </c>
       <c r="M244" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
@@ -21189,7 +21172,7 @@
         <v>211</v>
       </c>
       <c r="C245" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D245" t="s">
         <v>146</v>
@@ -21219,7 +21202,7 @@
         <v>-88.9</v>
       </c>
       <c r="M245" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
@@ -21230,7 +21213,7 @@
         <v>211</v>
       </c>
       <c r="C246" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D246" t="s">
         <v>146</v>
@@ -21260,7 +21243,7 @@
         <v>-93.4</v>
       </c>
       <c r="M246" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
@@ -21271,7 +21254,7 @@
         <v>211</v>
       </c>
       <c r="C247" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D247" t="s">
         <v>146</v>
@@ -21301,7 +21284,7 @@
         <v>-95.3</v>
       </c>
       <c r="M247" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
@@ -21312,13 +21295,13 @@
         <v>211</v>
       </c>
       <c r="C248" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D248" t="s">
         <v>146</v>
       </c>
       <c r="E248" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F248" s="12">
         <v>18.5</v>
@@ -21342,7 +21325,7 @@
         <v>-89.6</v>
       </c>
       <c r="M248" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
@@ -21353,13 +21336,13 @@
         <v>211</v>
       </c>
       <c r="C249" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D249" t="s">
         <v>146</v>
       </c>
       <c r="E249" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F249" s="12">
         <v>28</v>
@@ -21383,12 +21366,12 @@
         <v>-89.6</v>
       </c>
       <c r="M249" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="250" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>221</v>
@@ -21397,7 +21380,7 @@
         <v>34</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E250" s="4" t="s">
         <v>442</v>
@@ -21416,12 +21399,12 @@
       </c>
       <c r="L250" s="11"/>
       <c r="M250" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B251" t="s">
         <v>221</v>
@@ -21430,7 +21413,7 @@
         <v>34</v>
       </c>
       <c r="D251" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E251" t="s">
         <v>434</v>
@@ -21457,12 +21440,12 @@
         <v>-47.5</v>
       </c>
       <c r="M251" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B252" t="s">
         <v>221</v>
@@ -21471,7 +21454,7 @@
         <v>34</v>
       </c>
       <c r="D252" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E252" t="s">
         <v>454</v>
@@ -21498,12 +21481,12 @@
         <v>-66.7</v>
       </c>
       <c r="M252" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B253" t="s">
         <v>221</v>
@@ -21512,7 +21495,7 @@
         <v>34</v>
       </c>
       <c r="D253" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E253" t="s">
         <v>423</v>
@@ -21539,12 +21522,12 @@
         <v>-78.6</v>
       </c>
       <c r="M253" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B254" t="s">
         <v>221</v>
@@ -21553,7 +21536,7 @@
         <v>34</v>
       </c>
       <c r="D254" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E254" t="s">
         <v>439</v>
@@ -21580,12 +21563,12 @@
         <v>-87.9</v>
       </c>
       <c r="M254" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B255" t="s">
         <v>221</v>
@@ -21594,7 +21577,7 @@
         <v>34</v>
       </c>
       <c r="D255" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E255" t="s">
         <v>431</v>
@@ -21621,12 +21604,12 @@
         <v>-91.4</v>
       </c>
       <c r="M255" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B256" t="s">
         <v>221</v>
@@ -21635,10 +21618,10 @@
         <v>34</v>
       </c>
       <c r="D256" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E256" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F256" s="12">
         <v>30</v>
@@ -21662,12 +21645,12 @@
         <v>-89.6</v>
       </c>
       <c r="M256" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B257" t="s">
         <v>221</v>
@@ -21676,10 +21659,10 @@
         <v>34</v>
       </c>
       <c r="D257" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E257" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F257" s="12">
         <v>50</v>
@@ -21703,12 +21686,12 @@
         <v>-90.2</v>
       </c>
       <c r="M257" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="258" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>225</v>
@@ -21736,12 +21719,12 @@
       </c>
       <c r="L258" s="11"/>
       <c r="M258" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B259" t="s">
         <v>225</v>
@@ -21777,12 +21760,12 @@
         <v>-47</v>
       </c>
       <c r="M259" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B260" t="s">
         <v>225</v>
@@ -21818,12 +21801,12 @@
         <v>-69.1</v>
       </c>
       <c r="M260" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B261" t="s">
         <v>225</v>
@@ -21859,12 +21842,12 @@
         <v>-79.9</v>
       </c>
       <c r="M261" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B262" t="s">
         <v>225</v>
@@ -21900,12 +21883,12 @@
         <v>-87.7</v>
       </c>
       <c r="M262" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B263" t="s">
         <v>225</v>
@@ -21941,12 +21924,12 @@
         <v>-92.2</v>
       </c>
       <c r="M263" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B264" t="s">
         <v>225</v>
@@ -21958,7 +21941,7 @@
         <v>31</v>
       </c>
       <c r="E264" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F264" s="12">
         <v>19</v>
@@ -21982,12 +21965,12 @@
         <v>-85</v>
       </c>
       <c r="M264" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B265" t="s">
         <v>225</v>
@@ -21999,7 +21982,7 @@
         <v>31</v>
       </c>
       <c r="E265" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F265" s="12">
         <v>30</v>
@@ -22023,21 +22006,21 @@
         <v>-86</v>
       </c>
       <c r="M265" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="266" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B266" s="4" t="s">
         <v>228</v>
       </c>
       <c r="C266" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="D266" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="D266" s="4" t="s">
-        <v>563</v>
       </c>
       <c r="E266" s="4" t="s">
         <v>442</v>
@@ -22056,21 +22039,21 @@
       </c>
       <c r="L266" s="11"/>
       <c r="M266" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B267" t="s">
         <v>228</v>
       </c>
       <c r="C267" t="s">
+        <v>561</v>
+      </c>
+      <c r="D267" t="s">
         <v>562</v>
-      </c>
-      <c r="D267" t="s">
-        <v>563</v>
       </c>
       <c r="E267" t="s">
         <v>434</v>
@@ -22097,21 +22080,21 @@
         <v>-48.8</v>
       </c>
       <c r="M267" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B268" t="s">
         <v>228</v>
       </c>
       <c r="C268" t="s">
+        <v>561</v>
+      </c>
+      <c r="D268" t="s">
         <v>562</v>
-      </c>
-      <c r="D268" t="s">
-        <v>563</v>
       </c>
       <c r="E268" t="s">
         <v>454</v>
@@ -22138,21 +22121,21 @@
         <v>-70.2</v>
       </c>
       <c r="M268" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B269" t="s">
         <v>228</v>
       </c>
       <c r="C269" t="s">
+        <v>561</v>
+      </c>
+      <c r="D269" t="s">
         <v>562</v>
-      </c>
-      <c r="D269" t="s">
-        <v>563</v>
       </c>
       <c r="E269" t="s">
         <v>423</v>
@@ -22179,21 +22162,21 @@
         <v>-84</v>
       </c>
       <c r="M269" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B270" t="s">
         <v>228</v>
       </c>
       <c r="C270" t="s">
+        <v>561</v>
+      </c>
+      <c r="D270" t="s">
         <v>562</v>
-      </c>
-      <c r="D270" t="s">
-        <v>563</v>
       </c>
       <c r="E270" t="s">
         <v>439</v>
@@ -22220,21 +22203,21 @@
         <v>-90.2</v>
       </c>
       <c r="M270" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B271" t="s">
         <v>228</v>
       </c>
       <c r="C271" t="s">
+        <v>561</v>
+      </c>
+      <c r="D271" t="s">
         <v>562</v>
-      </c>
-      <c r="D271" t="s">
-        <v>563</v>
       </c>
       <c r="E271" t="s">
         <v>431</v>
@@ -22261,24 +22244,24 @@
         <v>-94.1</v>
       </c>
       <c r="M271" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B272" t="s">
         <v>228</v>
       </c>
       <c r="C272" t="s">
+        <v>561</v>
+      </c>
+      <c r="D272" t="s">
         <v>562</v>
       </c>
-      <c r="D272" t="s">
-        <v>563</v>
-      </c>
       <c r="E272" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F272" s="12">
         <v>13.5</v>
@@ -22302,24 +22285,24 @@
         <v>-87.4</v>
       </c>
       <c r="M272" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B273" t="s">
         <v>228</v>
       </c>
       <c r="C273" t="s">
+        <v>561</v>
+      </c>
+      <c r="D273" t="s">
         <v>562</v>
       </c>
-      <c r="D273" t="s">
-        <v>563</v>
-      </c>
       <c r="E273" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F273" s="12">
         <v>17</v>
@@ -22343,31 +22326,31 @@
         <v>-87.7</v>
       </c>
       <c r="M273" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
     <row r="274" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B274" s="4" t="s">
         <v>233</v>
       </c>
       <c r="C274" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D274" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="D274" s="4" t="s">
-        <v>569</v>
       </c>
       <c r="E274" s="4" t="s">
         <v>442</v>
       </c>
       <c r="F274" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G274" s="9"/>
       <c r="H274" s="10">
-        <v>0.736</v>
+        <v>1.131</v>
       </c>
       <c r="I274" s="11"/>
       <c r="J274" s="8"/>
@@ -22376,62 +22359,62 @@
       </c>
       <c r="L274" s="11"/>
       <c r="M274" s="4" t="s">
-        <v>880</v>
+        <v>633</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B275" t="s">
         <v>233</v>
       </c>
       <c r="C275" t="s">
+        <v>567</v>
+      </c>
+      <c r="D275" t="s">
         <v>568</v>
-      </c>
-      <c r="D275" t="s">
-        <v>569</v>
       </c>
       <c r="E275" t="s">
         <v>434</v>
       </c>
       <c r="F275" s="12">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="G275" s="13">
         <v>5.777</v>
       </c>
       <c r="H275" s="14">
-        <v>0.573</v>
+        <v>0.723</v>
       </c>
       <c r="I275" s="15">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="J275" s="12">
         <v>12.875</v>
       </c>
       <c r="K275" s="16">
-        <v>-6.525</v>
+        <v>-6.375</v>
       </c>
       <c r="L275" s="15">
-        <v>-50.7</v>
+        <v>-49.5</v>
       </c>
       <c r="M275" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B276" t="s">
         <v>233</v>
       </c>
       <c r="C276" t="s">
+        <v>567</v>
+      </c>
+      <c r="D276" t="s">
         <v>568</v>
-      </c>
-      <c r="D276" t="s">
-        <v>569</v>
       </c>
       <c r="E276" t="s">
         <v>454</v>
@@ -22440,80 +22423,80 @@
         <v>4.2</v>
       </c>
       <c r="G276" s="13">
-        <v>3.636</v>
+        <v>3.653</v>
       </c>
       <c r="H276" s="14">
-        <v>0.564</v>
+        <v>0.547</v>
       </c>
       <c r="I276" s="15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J276" s="12">
-        <v>14.917</v>
+        <v>15.25</v>
       </c>
       <c r="K276" s="16">
-        <v>-10.717</v>
+        <v>-11.05</v>
       </c>
       <c r="L276" s="15">
-        <v>-71.8</v>
+        <v>-72.5</v>
       </c>
       <c r="M276" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B277" t="s">
         <v>233</v>
       </c>
       <c r="C277" t="s">
+        <v>567</v>
+      </c>
+      <c r="D277" t="s">
         <v>568</v>
-      </c>
-      <c r="D277" t="s">
-        <v>569</v>
       </c>
       <c r="E277" t="s">
         <v>423</v>
       </c>
       <c r="F277" s="12">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G277" s="13">
-        <v>3.154</v>
+        <v>3.138</v>
       </c>
       <c r="H277" s="14">
-        <v>0.396</v>
+        <v>0.312</v>
       </c>
       <c r="I277" s="15">
-        <v>12.6</v>
+        <v>9.9</v>
       </c>
       <c r="J277" s="12">
-        <v>27.813</v>
+        <v>27.875</v>
       </c>
       <c r="K277" s="16">
-        <v>-24.263</v>
+        <v>-24.425</v>
       </c>
       <c r="L277" s="15">
-        <v>-87.2</v>
+        <v>-87.6</v>
       </c>
       <c r="M277" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B278" t="s">
         <v>233</v>
       </c>
       <c r="C278" t="s">
+        <v>567</v>
+      </c>
+      <c r="D278" t="s">
         <v>568</v>
-      </c>
-      <c r="D278" t="s">
-        <v>569</v>
       </c>
       <c r="E278" t="s">
         <v>439</v>
@@ -22522,39 +22505,39 @@
         <v>4.8</v>
       </c>
       <c r="G278" s="13">
-        <v>4.264</v>
+        <v>4.226</v>
       </c>
       <c r="H278" s="14">
-        <v>0.536</v>
+        <v>0.574</v>
       </c>
       <c r="I278" s="15">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="J278" s="12">
-        <v>87.1</v>
+        <v>87.6</v>
       </c>
       <c r="K278" s="16">
-        <v>-82.3</v>
+        <v>-82.8</v>
       </c>
       <c r="L278" s="15">
         <v>-94.5</v>
       </c>
       <c r="M278" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B279" t="s">
         <v>233</v>
       </c>
       <c r="C279" t="s">
+        <v>567</v>
+      </c>
+      <c r="D279" t="s">
         <v>568</v>
-      </c>
-      <c r="D279" t="s">
-        <v>569</v>
       </c>
       <c r="E279" t="s">
         <v>431</v>
@@ -22581,24 +22564,24 @@
         <v>-95.7</v>
       </c>
       <c r="M279" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B280" t="s">
         <v>233</v>
       </c>
       <c r="C280" t="s">
+        <v>567</v>
+      </c>
+      <c r="D280" t="s">
         <v>568</v>
       </c>
-      <c r="D280" t="s">
-        <v>569</v>
-      </c>
       <c r="E280" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F280" s="12">
         <v>13</v>
@@ -22622,59 +22605,59 @@
         <v>-92.5</v>
       </c>
       <c r="M280" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B281" t="s">
         <v>233</v>
       </c>
       <c r="C281" t="s">
+        <v>567</v>
+      </c>
+      <c r="D281" t="s">
         <v>568</v>
       </c>
-      <c r="D281" t="s">
-        <v>569</v>
-      </c>
       <c r="E281" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F281" s="12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G281" s="13">
         <v>17.096</v>
       </c>
       <c r="H281" s="14">
-        <v>0.904</v>
+        <v>1.404</v>
       </c>
       <c r="I281" s="15">
-        <v>5.3</v>
+        <v>8.2</v>
       </c>
       <c r="J281" s="12">
         <v>250.2</v>
       </c>
       <c r="K281" s="16">
-        <v>-232.2</v>
+        <v>-231.7</v>
       </c>
       <c r="L281" s="15">
-        <v>-92.8</v>
+        <v>-92.6</v>
       </c>
       <c r="M281" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="282" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B282" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>97</v>
@@ -22696,18 +22679,18 @@
       </c>
       <c r="L282" s="11"/>
       <c r="M282" s="4" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B283" t="s">
         <v>236</v>
       </c>
       <c r="C283" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D283" t="s">
         <v>97</v>
@@ -22737,18 +22720,18 @@
         <v>-42.6</v>
       </c>
       <c r="M283" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B284" t="s">
         <v>236</v>
       </c>
       <c r="C284" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D284" t="s">
         <v>97</v>
@@ -22778,18 +22761,18 @@
         <v>-68</v>
       </c>
       <c r="M284" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B285" t="s">
         <v>236</v>
       </c>
       <c r="C285" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D285" t="s">
         <v>97</v>
@@ -22819,18 +22802,18 @@
         <v>-81.1</v>
       </c>
       <c r="M285" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B286" t="s">
         <v>236</v>
       </c>
       <c r="C286" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D286" t="s">
         <v>97</v>
@@ -22860,18 +22843,18 @@
         <v>-88.3</v>
       </c>
       <c r="M286" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B287" t="s">
         <v>236</v>
       </c>
       <c r="C287" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D287" t="s">
         <v>97</v>
@@ -22901,24 +22884,24 @@
         <v>-93.2</v>
       </c>
       <c r="M287" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B288" t="s">
         <v>236</v>
       </c>
       <c r="C288" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D288" t="s">
         <v>97</v>
       </c>
       <c r="E288" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F288" s="12">
         <v>9.5</v>
@@ -22942,24 +22925,24 @@
         <v>-85.1</v>
       </c>
       <c r="M288" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B289" t="s">
         <v>236</v>
       </c>
       <c r="C289" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D289" t="s">
         <v>97</v>
       </c>
       <c r="E289" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F289" s="12">
         <v>12</v>
@@ -22983,12 +22966,12 @@
         <v>-84.8</v>
       </c>
       <c r="M289" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
     </row>
     <row r="290" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B290" s="4" t="s">
         <v>239</v>
@@ -22997,7 +22980,7 @@
         <v>60</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E290" s="4" t="s">
         <v>442</v>
@@ -23016,12 +22999,12 @@
       </c>
       <c r="L290" s="11"/>
       <c r="M290" s="4" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B291" t="s">
         <v>239</v>
@@ -23030,7 +23013,7 @@
         <v>60</v>
       </c>
       <c r="D291" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E291" t="s">
         <v>434</v>
@@ -23057,12 +23040,12 @@
         <v>-51.3</v>
       </c>
       <c r="M291" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B292" t="s">
         <v>239</v>
@@ -23071,7 +23054,7 @@
         <v>60</v>
       </c>
       <c r="D292" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E292" t="s">
         <v>454</v>
@@ -23098,12 +23081,12 @@
         <v>-81.2</v>
       </c>
       <c r="M292" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B293" t="s">
         <v>239</v>
@@ -23112,7 +23095,7 @@
         <v>60</v>
       </c>
       <c r="D293" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E293" t="s">
         <v>423</v>
@@ -23139,12 +23122,12 @@
         <v>-93.6</v>
       </c>
       <c r="M293" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B294" t="s">
         <v>239</v>
@@ -23153,7 +23136,7 @@
         <v>60</v>
       </c>
       <c r="D294" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E294" t="s">
         <v>439</v>
@@ -23180,12 +23163,12 @@
         <v>-96.8</v>
       </c>
       <c r="M294" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B295" t="s">
         <v>239</v>
@@ -23194,7 +23177,7 @@
         <v>60</v>
       </c>
       <c r="D295" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E295" t="s">
         <v>431</v>
@@ -23221,12 +23204,12 @@
         <v>-97.8</v>
       </c>
       <c r="M295" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B296" t="s">
         <v>239</v>
@@ -23235,10 +23218,10 @@
         <v>60</v>
       </c>
       <c r="D296" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E296" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F296" s="12">
         <v>6.45</v>
@@ -23262,12 +23245,12 @@
         <v>-96.4</v>
       </c>
       <c r="M296" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B297" t="s">
         <v>239</v>
@@ -23276,10 +23259,10 @@
         <v>60</v>
       </c>
       <c r="D297" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E297" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F297" s="12">
         <v>5.05</v>
@@ -23303,12 +23286,12 @@
         <v>-96.9</v>
       </c>
       <c r="M297" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="298" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B298" s="4" t="s">
         <v>243</v>
@@ -23336,12 +23319,12 @@
       </c>
       <c r="L298" s="11"/>
       <c r="M298" s="4" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B299" t="s">
         <v>243</v>
@@ -23377,12 +23360,12 @@
         <v>-50</v>
       </c>
       <c r="M299" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B300" t="s">
         <v>243</v>
@@ -23418,12 +23401,12 @@
         <v>-75.2</v>
       </c>
       <c r="M300" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B301" t="s">
         <v>243</v>
@@ -23459,12 +23442,12 @@
         <v>-88.2</v>
       </c>
       <c r="M301" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B302" t="s">
         <v>243</v>
@@ -23500,12 +23483,12 @@
         <v>-94.2</v>
       </c>
       <c r="M302" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B303" t="s">
         <v>243</v>
@@ -23541,12 +23524,12 @@
         <v>-95.9</v>
       </c>
       <c r="M303" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B304" t="s">
         <v>243</v>
@@ -23558,7 +23541,7 @@
         <v>312</v>
       </c>
       <c r="E304" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F304" s="12">
         <v>9.5</v>
@@ -23582,12 +23565,12 @@
         <v>-92.6</v>
       </c>
       <c r="M304" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B305" t="s">
         <v>243</v>
@@ -23599,7 +23582,7 @@
         <v>312</v>
       </c>
       <c r="E305" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F305" s="12">
         <v>12</v>
@@ -23623,21 +23606,21 @@
         <v>-91.2</v>
       </c>
       <c r="M305" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="306" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B306" s="4" t="s">
         <v>246</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E306" s="4" t="s">
         <v>442</v>
@@ -23647,7 +23630,7 @@
       </c>
       <c r="G306" s="9"/>
       <c r="H306" s="10">
-        <v>1.001</v>
+        <v>1.533</v>
       </c>
       <c r="I306" s="11"/>
       <c r="J306" s="8"/>
@@ -23656,308 +23639,308 @@
       </c>
       <c r="L306" s="11"/>
       <c r="M306" s="4" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B307" t="s">
         <v>246</v>
       </c>
       <c r="C307" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D307" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E307" t="s">
         <v>434</v>
       </c>
       <c r="F307" s="12">
-        <v>8.6</v>
+        <v>9.25</v>
       </c>
       <c r="G307" s="13">
-        <v>7.975</v>
+        <v>8.311</v>
       </c>
       <c r="H307" s="14">
-        <v>0.625</v>
+        <v>0.939</v>
       </c>
       <c r="I307" s="15">
-        <v>7.8</v>
+        <v>11.3</v>
       </c>
       <c r="J307" s="12">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="K307" s="16">
-        <v>-11.4</v>
+        <v>-13.25</v>
       </c>
       <c r="L307" s="15">
-        <v>-57</v>
+        <v>-58.9</v>
       </c>
       <c r="M307" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B308" t="s">
         <v>246</v>
       </c>
       <c r="C308" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D308" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E308" t="s">
         <v>454</v>
       </c>
       <c r="F308" s="12">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="G308" s="13">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="H308" s="14">
-        <v>0.44</v>
+        <v>0.83</v>
       </c>
       <c r="I308" s="15">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="J308" s="12">
-        <v>24.833</v>
+        <v>29.833</v>
       </c>
       <c r="K308" s="16">
-        <v>-19.983</v>
+        <v>-24.583</v>
       </c>
       <c r="L308" s="15">
-        <v>-80.5</v>
+        <v>-82.4</v>
       </c>
       <c r="M308" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B309" t="s">
         <v>246</v>
       </c>
       <c r="C309" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D309" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E309" t="s">
         <v>423</v>
       </c>
       <c r="F309" s="12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G309" s="13">
-        <v>3.405</v>
+        <v>3.455</v>
       </c>
       <c r="H309" s="14">
-        <v>0.345</v>
+        <v>0.395</v>
       </c>
       <c r="I309" s="15">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="J309" s="12">
-        <v>53.063</v>
+        <v>60.375</v>
       </c>
       <c r="K309" s="16">
-        <v>-49.313</v>
+        <v>-56.525</v>
       </c>
       <c r="L309" s="15">
-        <v>-92.9</v>
+        <v>-93.6</v>
       </c>
       <c r="M309" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B310" t="s">
         <v>246</v>
       </c>
       <c r="C310" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D310" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E310" t="s">
         <v>439</v>
       </c>
       <c r="F310" s="12">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="G310" s="13">
-        <v>3.865</v>
+        <v>3.817</v>
       </c>
       <c r="H310" s="14">
-        <v>0.385</v>
+        <v>0.183</v>
       </c>
       <c r="I310" s="15">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="J310" s="12">
-        <v>130</v>
+        <v>132.9</v>
       </c>
       <c r="K310" s="16">
-        <v>-125.75</v>
+        <v>-128.9</v>
       </c>
       <c r="L310" s="15">
-        <v>-96.7</v>
+        <v>-97</v>
       </c>
       <c r="M310" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B311" t="s">
         <v>246</v>
       </c>
       <c r="C311" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D311" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E311" t="s">
         <v>431</v>
       </c>
       <c r="F311" s="12">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="G311" s="13">
-        <v>5.303</v>
+        <v>5.105</v>
       </c>
       <c r="H311" s="14">
-        <v>1.197</v>
+        <v>1.145</v>
       </c>
       <c r="I311" s="15">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="J311" s="12">
-        <v>226.833</v>
+        <v>227.667</v>
       </c>
       <c r="K311" s="16">
-        <v>-220.333</v>
+        <v>-221.417</v>
       </c>
       <c r="L311" s="15">
-        <v>-97.1</v>
+        <v>-97.2</v>
       </c>
       <c r="M311" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B312" t="s">
         <v>246</v>
       </c>
       <c r="C312" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D312" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E312" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F312" s="12">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G312" s="13">
-        <v>9.815</v>
-      </c>
-      <c r="H312" s="14">
-        <v>0.185</v>
+        <v>9.827</v>
+      </c>
+      <c r="H312" s="17">
+        <v>-0.327</v>
       </c>
       <c r="I312" s="15">
-        <v>1.9</v>
+        <v>-3.3</v>
       </c>
       <c r="J312" s="12">
-        <v>190.2</v>
+        <v>191.4</v>
       </c>
       <c r="K312" s="16">
-        <v>-180.2</v>
+        <v>-181.9</v>
       </c>
       <c r="L312" s="15">
-        <v>-94.7</v>
+        <v>-95</v>
       </c>
       <c r="M312" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B313" t="s">
         <v>246</v>
       </c>
       <c r="C313" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D313" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E313" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F313" s="12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G313" s="13">
         <v>9.22</v>
       </c>
       <c r="H313" s="14">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="I313" s="15">
-        <v>19.3</v>
+        <v>13.9</v>
       </c>
       <c r="J313" s="12">
         <v>207.6</v>
       </c>
       <c r="K313" s="16">
-        <v>-196.6</v>
+        <v>-197.1</v>
       </c>
       <c r="L313" s="15">
-        <v>-94.7</v>
+        <v>-94.9</v>
       </c>
       <c r="M313" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="314" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>250</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E314" s="4" t="s">
         <v>442</v>
@@ -23976,21 +23959,21 @@
       </c>
       <c r="L314" s="11"/>
       <c r="M314" s="4" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B315" t="s">
         <v>250</v>
       </c>
       <c r="C315" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D315" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E315" t="s">
         <v>434</v>
@@ -24017,21 +24000,21 @@
         <v>-44</v>
       </c>
       <c r="M315" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B316" t="s">
         <v>250</v>
       </c>
       <c r="C316" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D316" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E316" t="s">
         <v>454</v>
@@ -24058,21 +24041,21 @@
         <v>-66.9</v>
       </c>
       <c r="M316" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B317" t="s">
         <v>250</v>
       </c>
       <c r="C317" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D317" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E317" t="s">
         <v>423</v>
@@ -24099,21 +24082,21 @@
         <v>-79.9</v>
       </c>
       <c r="M317" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B318" t="s">
         <v>250</v>
       </c>
       <c r="C318" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D318" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E318" t="s">
         <v>439</v>
@@ -24140,21 +24123,21 @@
         <v>-87.9</v>
       </c>
       <c r="M318" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B319" t="s">
         <v>250</v>
       </c>
       <c r="C319" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D319" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E319" t="s">
         <v>431</v>
@@ -24181,24 +24164,24 @@
         <v>-92.4</v>
       </c>
       <c r="M319" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B320" t="s">
         <v>250</v>
       </c>
       <c r="C320" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D320" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E320" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F320" s="12">
         <v>12.5</v>
@@ -24222,24 +24205,24 @@
         <v>-83.6</v>
       </c>
       <c r="M320" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B321" t="s">
         <v>250</v>
       </c>
       <c r="C321" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D321" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E321" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F321" s="12">
         <v>16</v>
@@ -24263,21 +24246,21 @@
         <v>-85.8</v>
       </c>
       <c r="M321" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="322" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B322" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E322" s="4" t="s">
         <v>442</v>
@@ -24296,21 +24279,21 @@
       </c>
       <c r="L322" s="11"/>
       <c r="M322" s="4" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B323" t="s">
         <v>253</v>
       </c>
       <c r="C323" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D323" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E323" t="s">
         <v>434</v>
@@ -24337,21 +24320,21 @@
         <v>-49.5</v>
       </c>
       <c r="M323" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B324" t="s">
         <v>253</v>
       </c>
       <c r="C324" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D324" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E324" t="s">
         <v>454</v>
@@ -24378,21 +24361,21 @@
         <v>-72.8</v>
       </c>
       <c r="M324" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B325" t="s">
         <v>253</v>
       </c>
       <c r="C325" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D325" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E325" t="s">
         <v>423</v>
@@ -24419,21 +24402,21 @@
         <v>-89.1</v>
       </c>
       <c r="M325" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B326" t="s">
         <v>253</v>
       </c>
       <c r="C326" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D326" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E326" t="s">
         <v>439</v>
@@ -24460,21 +24443,21 @@
         <v>-95.3</v>
       </c>
       <c r="M326" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B327" t="s">
         <v>253</v>
       </c>
       <c r="C327" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D327" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E327" t="s">
         <v>431</v>
@@ -24501,24 +24484,24 @@
         <v>-96.1</v>
       </c>
       <c r="M327" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B328" t="s">
         <v>253</v>
       </c>
       <c r="C328" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D328" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E328" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F328" s="12">
         <v>12.5</v>
@@ -24542,24 +24525,24 @@
         <v>-92.8</v>
       </c>
       <c r="M328" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B329" t="s">
         <v>253</v>
       </c>
       <c r="C329" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D329" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E329" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F329" s="12">
         <v>17</v>
@@ -24583,12 +24566,12 @@
         <v>-93.1</v>
       </c>
       <c r="M329" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
     </row>
     <row r="330" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B330" s="4" t="s">
         <v>256</v>
@@ -24597,7 +24580,7 @@
         <v>53</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E330" s="4" t="s">
         <v>442</v>
@@ -24616,12 +24599,12 @@
       </c>
       <c r="L330" s="11"/>
       <c r="M330" s="4" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B331" t="s">
         <v>256</v>
@@ -24630,7 +24613,7 @@
         <v>53</v>
       </c>
       <c r="D331" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E331" t="s">
         <v>434</v>
@@ -24657,12 +24640,12 @@
         <v>-46.1</v>
       </c>
       <c r="M331" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B332" t="s">
         <v>256</v>
@@ -24671,7 +24654,7 @@
         <v>53</v>
       </c>
       <c r="D332" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E332" t="s">
         <v>454</v>
@@ -24698,12 +24681,12 @@
         <v>-68.1</v>
       </c>
       <c r="M332" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B333" t="s">
         <v>256</v>
@@ -24712,7 +24695,7 @@
         <v>53</v>
       </c>
       <c r="D333" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E333" t="s">
         <v>423</v>
@@ -24739,12 +24722,12 @@
         <v>-79</v>
       </c>
       <c r="M333" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B334" t="s">
         <v>256</v>
@@ -24753,7 +24736,7 @@
         <v>53</v>
       </c>
       <c r="D334" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E334" t="s">
         <v>439</v>
@@ -24780,12 +24763,12 @@
         <v>-86.1</v>
       </c>
       <c r="M334" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B335" t="s">
         <v>256</v>
@@ -24794,7 +24777,7 @@
         <v>53</v>
       </c>
       <c r="D335" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E335" t="s">
         <v>431</v>
@@ -24821,12 +24804,12 @@
         <v>-92.1</v>
       </c>
       <c r="M335" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B336" t="s">
         <v>256</v>
@@ -24835,10 +24818,10 @@
         <v>53</v>
       </c>
       <c r="D336" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E336" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F336" s="12">
         <v>22</v>
@@ -24862,12 +24845,12 @@
         <v>-84.3</v>
       </c>
       <c r="M336" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B337" t="s">
         <v>256</v>
@@ -24876,10 +24859,10 @@
         <v>53</v>
       </c>
       <c r="D337" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E337" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F337" s="12">
         <v>36</v>
@@ -24903,21 +24886,21 @@
         <v>-84.2</v>
       </c>
       <c r="M337" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
     </row>
     <row r="338" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B338" s="4" t="s">
         <v>259</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E338" s="4" t="s">
         <v>442</v>
@@ -24936,21 +24919,21 @@
       </c>
       <c r="L338" s="11"/>
       <c r="M338" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B339" t="s">
         <v>259</v>
       </c>
       <c r="C339" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D339" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E339" t="s">
         <v>434</v>
@@ -24977,21 +24960,21 @@
         <v>-47.8</v>
       </c>
       <c r="M339" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B340" t="s">
         <v>259</v>
       </c>
       <c r="C340" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D340" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E340" t="s">
         <v>454</v>
@@ -25018,21 +25001,21 @@
         <v>-69.6</v>
       </c>
       <c r="M340" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B341" t="s">
         <v>259</v>
       </c>
       <c r="C341" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D341" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E341" t="s">
         <v>423</v>
@@ -25059,21 +25042,21 @@
         <v>-82.6</v>
       </c>
       <c r="M341" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B342" t="s">
         <v>259</v>
       </c>
       <c r="C342" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D342" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E342" t="s">
         <v>439</v>
@@ -25100,21 +25083,21 @@
         <v>-90.2</v>
       </c>
       <c r="M342" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B343" t="s">
         <v>259</v>
       </c>
       <c r="C343" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D343" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E343" t="s">
         <v>431</v>
@@ -25141,24 +25124,24 @@
         <v>-92.9</v>
       </c>
       <c r="M343" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B344" t="s">
         <v>259</v>
       </c>
       <c r="C344" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D344" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E344" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="F344" s="12">
         <v>20</v>
@@ -25182,24 +25165,24 @@
         <v>-89.6</v>
       </c>
       <c r="M344" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B345" t="s">
         <v>259</v>
       </c>
       <c r="C345" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D345" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E345" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F345" s="12">
         <v>29</v>
@@ -25223,7 +25206,7 @@
         <v>-90.8</v>
       </c>
       <c r="M345" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -25244,136 +25227,136 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B6" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B7" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B8" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B13" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="B14" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B15" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -25381,28 +25364,28 @@
         <v>442</v>
       </c>
       <c r="B20" s="21" t="s">
+        <v>970</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>971</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>972</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>973</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>974</v>
+      </c>
+      <c r="I20" s="21" t="s">
         <v>975</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>976</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>977</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>978</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>979</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -25410,22 +25393,22 @@
         <v>434</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>21</v>
@@ -25439,19 +25422,19 @@
         <v>454</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>21</v>
@@ -25467,17 +25450,17 @@
       <c r="A23" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>986</v>
+      <c r="B23" s="21" t="s">
+        <v>981</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>21</v>
@@ -25497,19 +25480,19 @@
         <v>439</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
@@ -25535,16 +25518,16 @@
         <v>21</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -25552,10 +25535,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
@@ -25567,21 +25550,21 @@
         <v>21</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>21</v>
@@ -25602,15 +25585,15 @@
         <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -25621,7 +25604,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -25635,109 +25618,109 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="E5">
         <v>3775</v>
       </c>
       <c r="F5" s="7">
-        <v>1275</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0.51</v>
+        <v>875</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.3017241379310345</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="E6">
         <v>2595</v>
       </c>
-      <c r="F6" s="7">
-        <v>95</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.038</v>
+      <c r="F6" s="23">
+        <v>-305</v>
+      </c>
+      <c r="G6" s="22">
+        <v>-0.10517241379310345</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="E7">
         <v>3965</v>
       </c>
       <c r="F7" s="7">
-        <v>1465</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0.586</v>
+        <v>1065</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.36724137931034484</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -25745,7 +25728,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -25757,25 +25740,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -26728,101 +26711,276 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="37" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>523</v>
+      </c>
+      <c r="B36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" t="s">
+        <v>494</v>
+      </c>
+      <c r="D36" t="s">
+        <v>524</v>
+      </c>
+      <c r="E36" t="s">
+        <v>525</v>
+      </c>
+      <c r="F36" t="s">
+        <v>439</v>
+      </c>
+      <c r="G36" s="12">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>527</v>
+      </c>
+      <c r="I36" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J36" s="28">
+        <v>1175</v>
+      </c>
+      <c r="K36" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L36" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>523</v>
+      </c>
+      <c r="B37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" t="s">
+        <v>494</v>
+      </c>
+      <c r="D37" t="s">
+        <v>532</v>
+      </c>
+      <c r="E37" t="s">
+        <v>533</v>
+      </c>
+      <c r="F37" t="s">
+        <v>423</v>
+      </c>
+      <c r="G37" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>434</v>
+      </c>
+      <c r="I37" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J37" s="28">
+        <v>1075</v>
+      </c>
+      <c r="K37" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L37" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>523</v>
+      </c>
+      <c r="B38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" t="s">
+        <v>537</v>
+      </c>
+      <c r="E38" t="s">
+        <v>538</v>
+      </c>
+      <c r="F38" t="s">
+        <v>423</v>
+      </c>
+      <c r="G38" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H38" t="s">
+        <v>439</v>
+      </c>
+      <c r="I38" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J38" s="28">
+        <v>975</v>
+      </c>
+      <c r="K38" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L38" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>523</v>
+      </c>
+      <c r="B39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" t="s">
+        <v>541</v>
+      </c>
+      <c r="F39" t="s">
+        <v>423</v>
+      </c>
+      <c r="G39" s="12">
+        <v>3.45</v>
+      </c>
+      <c r="H39" t="s">
+        <v>439</v>
+      </c>
+      <c r="I39" s="24">
+        <v>-100</v>
+      </c>
+      <c r="J39" s="28">
+        <v>875</v>
+      </c>
+      <c r="K39" s="26">
+        <v>-100</v>
+      </c>
+      <c r="L39" s="26">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>421</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" s="26">
+        <v>1650</v>
+      </c>
+      <c r="E43" s="26">
+        <v>1650</v>
+      </c>
+      <c r="F43" s="26">
+        <v>470</v>
+      </c>
+      <c r="G43" s="26">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>451</v>
+      </c>
+      <c r="B44">
+        <v>12</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" s="26">
+        <v>225</v>
+      </c>
+      <c r="E44" s="26">
+        <v>1875</v>
+      </c>
+      <c r="F44" s="26">
+        <v>-335</v>
+      </c>
+      <c r="G44" s="26">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>493</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
         <v>0</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>421</v>
-      </c>
-      <c r="B39">
-        <v>7</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39" s="26">
-        <v>1650</v>
-      </c>
-      <c r="E39" s="26">
-        <v>1650</v>
-      </c>
-      <c r="F39" s="26">
-        <v>470</v>
-      </c>
-      <c r="G39" s="26">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>451</v>
-      </c>
-      <c r="B40">
-        <v>12</v>
-      </c>
-      <c r="C40">
-        <v>3</v>
-      </c>
-      <c r="D40" s="26">
-        <v>225</v>
-      </c>
-      <c r="E40" s="26">
-        <v>1875</v>
-      </c>
-      <c r="F40" s="26">
-        <v>-335</v>
-      </c>
-      <c r="G40" s="26">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>493</v>
-      </c>
-      <c r="B41">
-        <v>6</v>
-      </c>
-      <c r="C41">
+      <c r="D45" s="26">
+        <v>-600</v>
+      </c>
+      <c r="E45" s="26">
+        <v>1275</v>
+      </c>
+      <c r="F45" s="26">
+        <v>95</v>
+      </c>
+      <c r="G45" s="26">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>523</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46">
         <v>0</v>
       </c>
-      <c r="D41" s="26">
-        <v>-600</v>
-      </c>
-      <c r="E41" s="26">
-        <v>1275</v>
-      </c>
-      <c r="F41" s="26">
-        <v>95</v>
-      </c>
-      <c r="G41" s="26">
-        <v>1465</v>
+      <c r="D46" s="26">
+        <v>-400</v>
+      </c>
+      <c r="E46" s="26">
+        <v>875</v>
+      </c>
+      <c r="F46" s="26">
+        <v>-305</v>
+      </c>
+      <c r="G46" s="26">
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -26842,10 +27000,10 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>442</v>
@@ -26863,15 +27021,15 @@
         <v>439</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -26889,21 +27047,21 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B3">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3">
         <v>26</v>
       </c>
       <c r="D3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3">
         <v>88</v>
@@ -26920,10 +27078,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B4">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -26938,7 +27096,7 @@
         <v>69</v>
       </c>
       <c r="G4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4">
         <v>67</v>
@@ -26946,10 +27104,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B5">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -26964,7 +27122,7 @@
         <v>52</v>
       </c>
       <c r="G5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H5">
         <v>49</v>
@@ -26972,7 +27130,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B6">
         <v>307</v>
@@ -26998,7 +27156,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="B7">
         <v>289</v>
@@ -27024,7 +27182,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B8">
         <v>279</v>
@@ -27050,7 +27208,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B9">
         <v>257</v>
@@ -27076,7 +27234,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B10">
         <v>237</v>
@@ -27102,7 +27260,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B11">
         <v>214</v>
@@ -27142,44 +27300,44 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>442</v>
@@ -27197,104 +27355,104 @@
         <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="30">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3">
         <v>0</v>
-      </c>
-      <c r="C9" s="30">
-        <v>24</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>9</v>
-      </c>
-      <c r="G9" s="3">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="D10" s="3">
+      <c r="F10" s="30">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3">
         <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="30">
-        <v>21</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B11" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="E11" s="3">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
       <c r="G11" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="C12" s="3">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="E12" s="30">
+        <v>29</v>
+      </c>
+      <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="30">
-        <v>28</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2</v>
-      </c>
       <c r="G12" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -27317,7 +27475,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -27340,7 +27498,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B15" s="30">
         <v>21</v>
@@ -27363,7 +27521,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -27386,7 +27544,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B17" s="30">
         <v>27</v>
@@ -27409,7 +27567,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
@@ -27446,7 +27604,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -27456,62 +27614,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -27521,42 +27679,42 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -27566,22 +27724,22 @@
     </row>
     <row r="25" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -27591,27 +27749,27 @@
     </row>
     <row r="30" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
@@ -27621,12 +27779,12 @@
     </row>
     <row r="36" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -4412,7 +4412,7 @@
     <t>2:5=300 5:2=150 负其他=75 平其他=250 胜其他=50</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-09T22:00:21+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-09T23:00:03+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -12834,8 +12834,8 @@
       <c r="F41" t="s">
         <v>582</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>70</v>
+      <c r="G41" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>21</v>
@@ -13163,8 +13163,8 @@
       <c r="F48" t="s">
         <v>614</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>70</v>
+      <c r="G48" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>21</v>
@@ -13445,8 +13445,8 @@
       <c r="F54" t="s">
         <v>631</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>70</v>
+      <c r="G54" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>21</v>
@@ -13727,8 +13727,8 @@
       <c r="F60" t="s">
         <v>660</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>70</v>
+      <c r="G60" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>21</v>
@@ -13868,8 +13868,8 @@
       <c r="F63" t="s">
         <v>673</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>70</v>
+      <c r="G63" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>21</v>
@@ -14479,8 +14479,8 @@
       <c r="F76" t="s">
         <v>720</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>70</v>
+      <c r="G76" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>21</v>
@@ -14620,8 +14620,8 @@
       <c r="F79" t="s">
         <v>734</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>70</v>
+      <c r="G79" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>21</v>
@@ -14949,8 +14949,8 @@
       <c r="F86" t="s">
         <v>752</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>70</v>
+      <c r="G86" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>21</v>
@@ -15043,8 +15043,8 @@
       <c r="F88" t="s">
         <v>757</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>70</v>
+      <c r="G88" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>21</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -4970,7 +4970,7 @@
     <t>2:5=650 5:2=250 负其他=350 平其他=550 胜其他=80</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-11T08:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-11T09:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -4916,7 +4916,7 @@
     <t>2:5=650 5:2=250 负其他=350 平其他=550 胜其他=80</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-12T08:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-12T09:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -2393,129 +2393,129 @@
     <t>10-13 01:00</t>
   </si>
   <si>
-    <t>2球 @3.75 ⚡</t>
+    <t>0球 @15</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
+    <t>10-12 15:00</t>
+  </si>
+  <si>
+    <t>奥斯KFUM</t>
+  </si>
+  <si>
+    <t>瓦勒伦加</t>
+  </si>
+  <si>
+    <t>7+球 @16</t>
+  </si>
+  <si>
+    <t>3球 @3.4 ⚡</t>
+  </si>
+  <si>
+    <t>都灵</t>
+  </si>
+  <si>
+    <t>乌迪内斯</t>
+  </si>
+  <si>
+    <t>10-13 02:45</t>
+  </si>
+  <si>
+    <t>2球 @3.25 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
+    <t>法乙</t>
+  </si>
+  <si>
+    <t>第戎</t>
+  </si>
+  <si>
+    <t>梅斯</t>
+  </si>
+  <si>
+    <t>2球 @3.4</t>
+  </si>
+  <si>
+    <t>考文垂</t>
+  </si>
+  <si>
+    <t>纽卡斯尔</t>
+  </si>
+  <si>
+    <t>10-13 03:00</t>
+  </si>
+  <si>
+    <t>0球 @15.5</t>
+  </si>
+  <si>
+    <t>2球 @4.1 ⚡</t>
+  </si>
+  <si>
+    <t>塞维利亚</t>
+  </si>
+  <si>
+    <t>0球 @11.5</t>
+  </si>
+  <si>
+    <t>3球 @3.8 ⚡</t>
+  </si>
+  <si>
+    <t>周一009</t>
+  </si>
+  <si>
+    <t>0球 @13.5</t>
+  </si>
+  <si>
+    <t>周一010</t>
+  </si>
+  <si>
+    <t>法马利康</t>
+  </si>
+  <si>
+    <t>阿尔维卡</t>
+  </si>
+  <si>
+    <t>10-13 03:15</t>
+  </si>
+  <si>
+    <t>2球 @3.35 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.75 ⚡</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>欧冠</t>
+  </si>
+  <si>
+    <t>10-14 00:45</t>
+  </si>
+  <si>
+    <t>布鲁日</t>
+  </si>
+  <si>
+    <t>10-14 03:00</t>
+  </si>
+  <si>
+    <t>1球 @7.75 ⚡</t>
+  </si>
+  <si>
+    <t>6球 @13</t>
+  </si>
+  <si>
+    <t>4球 @4.7 ⚡</t>
   </si>
   <si>
     <t>3球 @3.65 ⚡</t>
   </si>
   <si>
-    <t>奥斯KFUM</t>
-  </si>
-  <si>
-    <t>瓦勒伦加</t>
-  </si>
-  <si>
-    <t>7+球 @15.5</t>
-  </si>
-  <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
-    <t>都灵</t>
-  </si>
-  <si>
-    <t>乌迪内斯</t>
-  </si>
-  <si>
-    <t>10-13 02:45</t>
-  </si>
-  <si>
-    <t>2球 @3.25 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.85 ⚡</t>
-  </si>
-  <si>
-    <t>法乙</t>
-  </si>
-  <si>
-    <t>第戎</t>
-  </si>
-  <si>
-    <t>梅斯</t>
-  </si>
-  <si>
-    <t>2球 @3.4</t>
-  </si>
-  <si>
-    <t>3球 @3.55 ⚡</t>
-  </si>
-  <si>
-    <t>考文垂</t>
-  </si>
-  <si>
-    <t>纽卡斯尔</t>
-  </si>
-  <si>
-    <t>10-13 03:00</t>
-  </si>
-  <si>
-    <t>0球 @15.5</t>
-  </si>
-  <si>
-    <t>2球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>塞维利亚</t>
-  </si>
-  <si>
-    <t>0球 @11.5</t>
-  </si>
-  <si>
-    <t>3球 @3.8 ⚡</t>
-  </si>
-  <si>
-    <t>周一009</t>
-  </si>
-  <si>
-    <t>0球 @13.5</t>
-  </si>
-  <si>
-    <t>3球 @3.7 ⚡</t>
-  </si>
-  <si>
-    <t>周一010</t>
-  </si>
-  <si>
-    <t>法马利康</t>
-  </si>
-  <si>
-    <t>阿尔维卡</t>
-  </si>
-  <si>
-    <t>10-13 03:15</t>
-  </si>
-  <si>
-    <t>2球 @3.35 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
-  </si>
-  <si>
-    <t>2026-10-13</t>
-  </si>
-  <si>
-    <t>欧冠</t>
-  </si>
-  <si>
-    <t>10-14 00:45</t>
-  </si>
-  <si>
-    <t>布鲁日</t>
-  </si>
-  <si>
-    <t>10-14 03:00</t>
-  </si>
-  <si>
-    <t>1球 @7.75 ⚡</t>
-  </si>
-  <si>
-    <t>6球 @13</t>
-  </si>
-  <si>
-    <t>4球 @4.7 ⚡</t>
-  </si>
-  <si>
     <t>6球 @6.1</t>
   </si>
   <si>
@@ -5189,7 +5189,7 @@
     <t>2:5=300 5:2=90 负其他=60 平其他=150 胜其他=30</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-12T14:00:06+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-12T15:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -16694,10 +16694,10 @@
         <v>21</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>600</v>
+        <v>791</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>792</v>
@@ -16709,7 +16709,7 @@
         <v>21</v>
       </c>
       <c r="N105" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="O105" t="s">
         <v>21</v>
@@ -16726,10 +16726,10 @@
         <v>96</v>
       </c>
       <c r="D106" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E106" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F106" t="s">
         <v>790</v>
@@ -16741,13 +16741,13 @@
         <v>21</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L106" t="s">
         <v>21</v>
@@ -16756,7 +16756,7 @@
         <v>21</v>
       </c>
       <c r="N106" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="O106" t="s">
         <v>21</v>
@@ -16773,13 +16773,13 @@
         <v>42</v>
       </c>
       <c r="D107" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E107" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F107" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>55</v>
@@ -16791,10 +16791,10 @@
         <v>620</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L107" t="s">
         <v>21</v>
@@ -16803,7 +16803,7 @@
         <v>21</v>
       </c>
       <c r="N107" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="O107" t="s">
         <v>21</v>
@@ -16817,16 +16817,16 @@
         <v>383</v>
       </c>
       <c r="C108" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D108" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E108" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F108" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>55</v>
@@ -16835,13 +16835,13 @@
         <v>21</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="L108" t="s">
         <v>21</v>
@@ -16850,7 +16850,7 @@
         <v>21</v>
       </c>
       <c r="N108" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="O108" t="s">
         <v>21</v>
@@ -16888,7 +16888,7 @@
         <v>811</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="L109" t="s">
         <v>21</v>
@@ -16979,10 +16979,10 @@
         <v>816</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="L111" t="s">
         <v>21</v>
@@ -16991,7 +16991,7 @@
         <v>21</v>
       </c>
       <c r="N111" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="O111" t="s">
         <v>21</v>
@@ -17002,19 +17002,19 @@
         <v>778</v>
       </c>
       <c r="B112" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C112" t="s">
         <v>139</v>
       </c>
       <c r="D112" t="s">
+        <v>818</v>
+      </c>
+      <c r="E112" t="s">
         <v>819</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>820</v>
-      </c>
-      <c r="F112" t="s">
-        <v>821</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>55</v>
@@ -17026,10 +17026,10 @@
         <v>732</v>
       </c>
       <c r="J112" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="K112" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="L112" t="s">
         <v>21</v>
@@ -17046,13 +17046,13 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B113" t="s">
         <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D113" t="s">
         <v>577</v>
@@ -17061,7 +17061,7 @@
         <v>589</v>
       </c>
       <c r="F113" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>55</v>
@@ -17093,22 +17093,22 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B114" t="s">
         <v>397</v>
       </c>
       <c r="C114" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D114" t="s">
         <v>663</v>
       </c>
       <c r="E114" t="s">
+        <v>826</v>
+      </c>
+      <c r="F114" t="s">
         <v>827</v>
-      </c>
-      <c r="F114" t="s">
-        <v>828</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>55</v>
@@ -17120,10 +17120,10 @@
         <v>486</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L114" t="s">
         <v>21</v>
@@ -17140,13 +17140,13 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B115" t="s">
         <v>399</v>
       </c>
       <c r="C115" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D115" t="s">
         <v>612</v>
@@ -17155,7 +17155,7 @@
         <v>103</v>
       </c>
       <c r="F115" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>55</v>
@@ -17164,13 +17164,13 @@
         <v>21</v>
       </c>
       <c r="I115" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="J115" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="K115" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="K115" s="3" t="s">
-        <v>792</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>
@@ -17187,13 +17187,13 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B116" t="s">
         <v>402</v>
       </c>
       <c r="C116" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D116" t="s">
         <v>117</v>
@@ -17202,7 +17202,7 @@
         <v>44</v>
       </c>
       <c r="F116" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>70</v>
@@ -17234,13 +17234,13 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B117" t="s">
         <v>405</v>
       </c>
       <c r="C117" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D117" t="s">
         <v>97</v>
@@ -17249,7 +17249,7 @@
         <v>629</v>
       </c>
       <c r="F117" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G117" t="s">
         <v>21</v>
@@ -17281,13 +17281,13 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B118" t="s">
         <v>407</v>
       </c>
       <c r="C118" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D118" t="s">
         <v>83</v>
@@ -17296,7 +17296,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>55</v>
@@ -17328,13 +17328,13 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B119" t="s">
         <v>408</v>
       </c>
       <c r="C119" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D119" t="s">
         <v>837</v>
@@ -17343,7 +17343,7 @@
         <v>671</v>
       </c>
       <c r="F119" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>55</v>
@@ -17375,13 +17375,13 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B120" t="s">
         <v>409</v>
       </c>
       <c r="C120" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D120" t="s">
         <v>86</v>
@@ -17390,7 +17390,7 @@
         <v>107</v>
       </c>
       <c r="F120" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>70</v>
@@ -17402,7 +17402,7 @@
         <v>476</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>840</v>
@@ -50467,7 +50467,7 @@
       </c>
       <c r="G826" s="9"/>
       <c r="H826" s="10">
-        <v>0.205</v>
+        <v>0.226</v>
       </c>
       <c r="I826" s="11"/>
       <c r="J826" s="8"/>
@@ -50496,25 +50496,25 @@
         <v>433</v>
       </c>
       <c r="F827" s="12">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="G827" s="13">
         <v>5.156</v>
       </c>
       <c r="H827" s="14">
-        <v>0.344</v>
+        <v>0.594</v>
       </c>
       <c r="I827" s="15">
-        <v>6.7</v>
+        <v>11.5</v>
       </c>
       <c r="J827" s="12">
         <v>11.25</v>
       </c>
       <c r="K827" s="16">
-        <v>-5.75</v>
+        <v>-5.5</v>
       </c>
       <c r="L827" s="15">
-        <v>-51.1</v>
+        <v>-48.9</v>
       </c>
       <c r="M827" t="s">
         <v>1607</v>
@@ -50537,25 +50537,25 @@
         <v>453</v>
       </c>
       <c r="F828" s="12">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="G828" s="13">
         <v>3.406</v>
       </c>
       <c r="H828" s="14">
-        <v>0.344</v>
+        <v>0.244</v>
       </c>
       <c r="I828" s="15">
-        <v>10.1</v>
+        <v>7.2</v>
       </c>
       <c r="J828" s="12">
         <v>14.233</v>
       </c>
       <c r="K828" s="16">
-        <v>-10.483</v>
+        <v>-10.583</v>
       </c>
       <c r="L828" s="15">
-        <v>-73.6</v>
+        <v>-74.4</v>
       </c>
       <c r="M828" t="s">
         <v>1608</v>
@@ -50578,25 +50578,25 @@
         <v>423</v>
       </c>
       <c r="F829" s="12">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G829" s="13">
         <v>3.22</v>
       </c>
       <c r="H829" s="14">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="I829" s="15">
-        <v>13.4</v>
+        <v>10.3</v>
       </c>
       <c r="J829" s="12">
         <v>23.375</v>
       </c>
       <c r="K829" s="16">
-        <v>-19.725</v>
+        <v>-19.825</v>
       </c>
       <c r="L829" s="15">
-        <v>-84.4</v>
+        <v>-84.8</v>
       </c>
       <c r="M829" t="s">
         <v>1609</v>
@@ -50660,25 +50660,25 @@
         <v>430</v>
       </c>
       <c r="F831" s="12">
-        <v>8.7</v>
+        <v>9</v>
       </c>
       <c r="G831" s="13">
         <v>7.298</v>
       </c>
       <c r="H831" s="14">
-        <v>1.402</v>
+        <v>1.702</v>
       </c>
       <c r="I831" s="15">
-        <v>19.2</v>
+        <v>23.3</v>
       </c>
       <c r="J831" s="12">
         <v>126.667</v>
       </c>
       <c r="K831" s="16">
-        <v>-117.967</v>
+        <v>-117.667</v>
       </c>
       <c r="L831" s="15">
-        <v>-93.1</v>
+        <v>-92.9</v>
       </c>
       <c r="M831" t="s">
         <v>1611</v>
@@ -50701,25 +50701,25 @@
         <v>522</v>
       </c>
       <c r="F832" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G832" s="13">
         <v>16.071</v>
       </c>
-      <c r="H832" s="17">
-        <v>-0.071</v>
+      <c r="H832" s="14">
+        <v>0.929</v>
       </c>
       <c r="I832" s="15">
-        <v>-0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J832" s="12">
         <v>161</v>
       </c>
       <c r="K832" s="16">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="L832" s="15">
-        <v>-90.1</v>
+        <v>-89.4</v>
       </c>
       <c r="M832" t="s">
         <v>1612</v>
@@ -50774,10 +50774,10 @@
         <v>380</v>
       </c>
       <c r="C834" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D834" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E834" s="4" t="s">
         <v>441</v>
@@ -50787,7 +50787,7 @@
       </c>
       <c r="G834" s="9"/>
       <c r="H834" s="10">
-        <v>-0.152</v>
+        <v>0.184</v>
       </c>
       <c r="I834" s="11"/>
       <c r="J834" s="8"/>
@@ -50807,34 +50807,34 @@
         <v>380</v>
       </c>
       <c r="C835" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D835" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E835" t="s">
         <v>433</v>
       </c>
       <c r="F835" s="12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G835" s="13">
         <v>6.462</v>
       </c>
       <c r="H835" s="14">
-        <v>0.538</v>
+        <v>0.638</v>
       </c>
       <c r="I835" s="15">
-        <v>8.3</v>
+        <v>9.9</v>
       </c>
       <c r="J835" s="12">
         <v>13</v>
       </c>
       <c r="K835" s="16">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="L835" s="15">
-        <v>-46.1</v>
+        <v>-45.4</v>
       </c>
       <c r="M835" t="s">
         <v>1614</v>
@@ -50848,10 +50848,10 @@
         <v>380</v>
       </c>
       <c r="C836" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D836" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E836" t="s">
         <v>453</v>
@@ -50889,10 +50889,10 @@
         <v>380</v>
       </c>
       <c r="C837" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D837" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E837" t="s">
         <v>423</v>
@@ -50930,34 +50930,34 @@
         <v>380</v>
       </c>
       <c r="C838" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D838" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E838" t="s">
         <v>438</v>
       </c>
       <c r="F838" s="12">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="G838" s="13">
         <v>4</v>
       </c>
       <c r="H838" s="14">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="I838" s="15">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="J838" s="12">
         <v>38.5</v>
       </c>
       <c r="K838" s="16">
-        <v>-33.75</v>
+        <v>-33.9</v>
       </c>
       <c r="L838" s="15">
-        <v>-87.7</v>
+        <v>-88</v>
       </c>
       <c r="M838" t="s">
         <v>1617</v>
@@ -50971,10 +50971,10 @@
         <v>380</v>
       </c>
       <c r="C839" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D839" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E839" t="s">
         <v>430</v>
@@ -51012,34 +51012,34 @@
         <v>380</v>
       </c>
       <c r="C840" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D840" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E840" t="s">
         <v>522</v>
       </c>
       <c r="F840" s="12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G840" s="13">
         <v>11.801</v>
       </c>
       <c r="H840" s="14">
-        <v>0.699</v>
+        <v>1.199</v>
       </c>
       <c r="I840" s="15">
-        <v>5.9</v>
+        <v>10.2</v>
       </c>
       <c r="J840" s="12">
         <v>81.4</v>
       </c>
       <c r="K840" s="16">
-        <v>-68.9</v>
+        <v>-68.4</v>
       </c>
       <c r="L840" s="15">
-        <v>-84.6</v>
+        <v>-84</v>
       </c>
       <c r="M840" t="s">
         <v>1619</v>
@@ -51053,34 +51053,34 @@
         <v>380</v>
       </c>
       <c r="C841" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D841" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E841" t="s">
         <v>634</v>
       </c>
       <c r="F841" s="12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G841" s="13">
         <v>16.07</v>
       </c>
       <c r="H841" s="17">
-        <v>-0.57</v>
+        <v>-0.07</v>
       </c>
       <c r="I841" s="15">
-        <v>-3.5</v>
+        <v>-0.4</v>
       </c>
       <c r="J841" s="12">
         <v>114</v>
       </c>
       <c r="K841" s="16">
-        <v>-98.5</v>
+        <v>-98</v>
       </c>
       <c r="L841" s="15">
-        <v>-86.4</v>
+        <v>-86</v>
       </c>
       <c r="M841" t="s">
         <v>1620</v>
@@ -51094,10 +51094,10 @@
         <v>382</v>
       </c>
       <c r="C842" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D842" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E842" s="4" t="s">
         <v>441</v>
@@ -51127,10 +51127,10 @@
         <v>382</v>
       </c>
       <c r="C843" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D843" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E843" t="s">
         <v>433</v>
@@ -51168,10 +51168,10 @@
         <v>382</v>
       </c>
       <c r="C844" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D844" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E844" t="s">
         <v>453</v>
@@ -51209,10 +51209,10 @@
         <v>382</v>
       </c>
       <c r="C845" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D845" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E845" t="s">
         <v>423</v>
@@ -51250,10 +51250,10 @@
         <v>382</v>
       </c>
       <c r="C846" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D846" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E846" t="s">
         <v>438</v>
@@ -51291,10 +51291,10 @@
         <v>382</v>
       </c>
       <c r="C847" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D847" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E847" t="s">
         <v>430</v>
@@ -51332,10 +51332,10 @@
         <v>382</v>
       </c>
       <c r="C848" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D848" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E848" t="s">
         <v>522</v>
@@ -51373,10 +51373,10 @@
         <v>382</v>
       </c>
       <c r="C849" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D849" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E849" t="s">
         <v>634</v>
@@ -51414,10 +51414,10 @@
         <v>383</v>
       </c>
       <c r="C850" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D850" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E850" s="4" t="s">
         <v>441</v>
@@ -51447,10 +51447,10 @@
         <v>383</v>
       </c>
       <c r="C851" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D851" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E851" t="s">
         <v>433</v>
@@ -51488,10 +51488,10 @@
         <v>383</v>
       </c>
       <c r="C852" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D852" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E852" t="s">
         <v>453</v>
@@ -51529,10 +51529,10 @@
         <v>383</v>
       </c>
       <c r="C853" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D853" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E853" t="s">
         <v>423</v>
@@ -51570,10 +51570,10 @@
         <v>383</v>
       </c>
       <c r="C854" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D854" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E854" t="s">
         <v>438</v>
@@ -51611,10 +51611,10 @@
         <v>383</v>
       </c>
       <c r="C855" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D855" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E855" t="s">
         <v>430</v>
@@ -51652,10 +51652,10 @@
         <v>383</v>
       </c>
       <c r="C856" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D856" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E856" t="s">
         <v>522</v>
@@ -51693,10 +51693,10 @@
         <v>383</v>
       </c>
       <c r="C857" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D857" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E857" t="s">
         <v>634</v>
@@ -52387,12 +52387,12 @@
       </c>
       <c r="G874" s="9"/>
       <c r="H874" s="10">
-        <v>-0.617</v>
+        <v>-0.146</v>
       </c>
       <c r="I874" s="11"/>
       <c r="J874" s="8"/>
       <c r="K874" s="10">
-        <v>-4.454</v>
+        <v>-4.004</v>
       </c>
       <c r="L874" s="11"/>
       <c r="M874" s="4" t="s">
@@ -52416,25 +52416,25 @@
         <v>433</v>
       </c>
       <c r="F875" s="12">
-        <v>5.3</v>
+        <v>5.65</v>
       </c>
       <c r="G875" s="13">
         <v>4.918</v>
       </c>
       <c r="H875" s="14">
-        <v>0.382</v>
+        <v>0.732</v>
       </c>
       <c r="I875" s="15">
-        <v>7.8</v>
+        <v>14.9</v>
       </c>
       <c r="J875" s="12">
         <v>9.875</v>
       </c>
       <c r="K875" s="16">
-        <v>-4.575</v>
+        <v>-4.225</v>
       </c>
       <c r="L875" s="15">
-        <v>-46.3</v>
+        <v>-42.8</v>
       </c>
       <c r="M875" t="s">
         <v>1651</v>
@@ -52498,25 +52498,25 @@
         <v>423</v>
       </c>
       <c r="F877" s="12">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G877" s="13">
         <v>3.315</v>
       </c>
       <c r="H877" s="14">
-        <v>0.385</v>
+        <v>0.235</v>
       </c>
       <c r="I877" s="15">
-        <v>11.6</v>
+        <v>7.1</v>
       </c>
       <c r="J877" s="12">
         <v>19.313</v>
       </c>
       <c r="K877" s="16">
-        <v>-15.613</v>
+        <v>-15.763</v>
       </c>
       <c r="L877" s="15">
-        <v>-80.8</v>
+        <v>-81.6</v>
       </c>
       <c r="M877" t="s">
         <v>1653</v>
@@ -52691,13 +52691,13 @@
         <v>778</v>
       </c>
       <c r="B882" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="C882" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="C882" s="4" t="s">
+      <c r="D882" s="4" t="s">
         <v>819</v>
-      </c>
-      <c r="D882" s="4" t="s">
-        <v>820</v>
       </c>
       <c r="E882" s="4" t="s">
         <v>441</v>
@@ -52724,13 +52724,13 @@
         <v>778</v>
       </c>
       <c r="B883" t="s">
+        <v>817</v>
+      </c>
+      <c r="C883" t="s">
         <v>818</v>
       </c>
-      <c r="C883" t="s">
+      <c r="D883" t="s">
         <v>819</v>
-      </c>
-      <c r="D883" t="s">
-        <v>820</v>
       </c>
       <c r="E883" t="s">
         <v>433</v>
@@ -52765,13 +52765,13 @@
         <v>778</v>
       </c>
       <c r="B884" t="s">
+        <v>817</v>
+      </c>
+      <c r="C884" t="s">
         <v>818</v>
       </c>
-      <c r="C884" t="s">
+      <c r="D884" t="s">
         <v>819</v>
-      </c>
-      <c r="D884" t="s">
-        <v>820</v>
       </c>
       <c r="E884" t="s">
         <v>453</v>
@@ -52806,13 +52806,13 @@
         <v>778</v>
       </c>
       <c r="B885" t="s">
+        <v>817</v>
+      </c>
+      <c r="C885" t="s">
         <v>818</v>
       </c>
-      <c r="C885" t="s">
+      <c r="D885" t="s">
         <v>819</v>
-      </c>
-      <c r="D885" t="s">
-        <v>820</v>
       </c>
       <c r="E885" t="s">
         <v>423</v>
@@ -52847,13 +52847,13 @@
         <v>778</v>
       </c>
       <c r="B886" t="s">
+        <v>817</v>
+      </c>
+      <c r="C886" t="s">
         <v>818</v>
       </c>
-      <c r="C886" t="s">
+      <c r="D886" t="s">
         <v>819</v>
-      </c>
-      <c r="D886" t="s">
-        <v>820</v>
       </c>
       <c r="E886" t="s">
         <v>438</v>
@@ -52888,13 +52888,13 @@
         <v>778</v>
       </c>
       <c r="B887" t="s">
+        <v>817</v>
+      </c>
+      <c r="C887" t="s">
         <v>818</v>
       </c>
-      <c r="C887" t="s">
+      <c r="D887" t="s">
         <v>819</v>
-      </c>
-      <c r="D887" t="s">
-        <v>820</v>
       </c>
       <c r="E887" t="s">
         <v>430</v>
@@ -52929,13 +52929,13 @@
         <v>778</v>
       </c>
       <c r="B888" t="s">
+        <v>817</v>
+      </c>
+      <c r="C888" t="s">
         <v>818</v>
       </c>
-      <c r="C888" t="s">
+      <c r="D888" t="s">
         <v>819</v>
-      </c>
-      <c r="D888" t="s">
-        <v>820</v>
       </c>
       <c r="E888" t="s">
         <v>522</v>
@@ -52970,13 +52970,13 @@
         <v>778</v>
       </c>
       <c r="B889" t="s">
+        <v>817</v>
+      </c>
+      <c r="C889" t="s">
         <v>818</v>
       </c>
-      <c r="C889" t="s">
+      <c r="D889" t="s">
         <v>819</v>
-      </c>
-      <c r="D889" t="s">
-        <v>820</v>
       </c>
       <c r="E889" t="s">
         <v>634</v>
@@ -53008,7 +53008,7 @@
     </row>
     <row r="890" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A890" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B890" s="4" t="s">
         <v>171</v>
@@ -53041,7 +53041,7 @@
     </row>
     <row r="891" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B891" t="s">
         <v>171</v>
@@ -53082,7 +53082,7 @@
     </row>
     <row r="892" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B892" t="s">
         <v>171</v>
@@ -53123,7 +53123,7 @@
     </row>
     <row r="893" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B893" t="s">
         <v>171</v>
@@ -53164,7 +53164,7 @@
     </row>
     <row r="894" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B894" t="s">
         <v>171</v>
@@ -53205,7 +53205,7 @@
     </row>
     <row r="895" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B895" t="s">
         <v>171</v>
@@ -53246,7 +53246,7 @@
     </row>
     <row r="896" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B896" t="s">
         <v>171</v>
@@ -53287,7 +53287,7 @@
     </row>
     <row r="897" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B897" t="s">
         <v>171</v>
@@ -53328,7 +53328,7 @@
     </row>
     <row r="898" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A898" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B898" s="4" t="s">
         <v>397</v>
@@ -53337,7 +53337,7 @@
         <v>663</v>
       </c>
       <c r="D898" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E898" s="4" t="s">
         <v>441</v>
@@ -53361,7 +53361,7 @@
     </row>
     <row r="899" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B899" t="s">
         <v>397</v>
@@ -53370,7 +53370,7 @@
         <v>663</v>
       </c>
       <c r="D899" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E899" t="s">
         <v>433</v>
@@ -53402,7 +53402,7 @@
     </row>
     <row r="900" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B900" t="s">
         <v>397</v>
@@ -53411,7 +53411,7 @@
         <v>663</v>
       </c>
       <c r="D900" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E900" t="s">
         <v>453</v>
@@ -53443,7 +53443,7 @@
     </row>
     <row r="901" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B901" t="s">
         <v>397</v>
@@ -53452,7 +53452,7 @@
         <v>663</v>
       </c>
       <c r="D901" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E901" t="s">
         <v>423</v>
@@ -53484,7 +53484,7 @@
     </row>
     <row r="902" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B902" t="s">
         <v>397</v>
@@ -53493,7 +53493,7 @@
         <v>663</v>
       </c>
       <c r="D902" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E902" t="s">
         <v>438</v>
@@ -53525,7 +53525,7 @@
     </row>
     <row r="903" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B903" t="s">
         <v>397</v>
@@ -53534,7 +53534,7 @@
         <v>663</v>
       </c>
       <c r="D903" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E903" t="s">
         <v>430</v>
@@ -53566,7 +53566,7 @@
     </row>
     <row r="904" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B904" t="s">
         <v>397</v>
@@ -53575,7 +53575,7 @@
         <v>663</v>
       </c>
       <c r="D904" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E904" t="s">
         <v>522</v>
@@ -53607,7 +53607,7 @@
     </row>
     <row r="905" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B905" t="s">
         <v>397</v>
@@ -53616,7 +53616,7 @@
         <v>663</v>
       </c>
       <c r="D905" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E905" t="s">
         <v>634</v>
@@ -53648,7 +53648,7 @@
     </row>
     <row r="906" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A906" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B906" s="4" t="s">
         <v>399</v>
@@ -53681,7 +53681,7 @@
     </row>
     <row r="907" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B907" t="s">
         <v>399</v>
@@ -53722,7 +53722,7 @@
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B908" t="s">
         <v>399</v>
@@ -53763,7 +53763,7 @@
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B909" t="s">
         <v>399</v>
@@ -53804,7 +53804,7 @@
     </row>
     <row r="910" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B910" t="s">
         <v>399</v>
@@ -53845,7 +53845,7 @@
     </row>
     <row r="911" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B911" t="s">
         <v>399</v>
@@ -53886,7 +53886,7 @@
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B912" t="s">
         <v>399</v>
@@ -53927,7 +53927,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B913" t="s">
         <v>399</v>
@@ -53968,7 +53968,7 @@
     </row>
     <row r="914" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A914" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B914" s="4" t="s">
         <v>402</v>
@@ -54001,7 +54001,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B915" t="s">
         <v>402</v>
@@ -54042,7 +54042,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B916" t="s">
         <v>402</v>
@@ -54083,7 +54083,7 @@
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B917" t="s">
         <v>402</v>
@@ -54124,7 +54124,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B918" t="s">
         <v>402</v>
@@ -54165,7 +54165,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B919" t="s">
         <v>402</v>
@@ -54206,7 +54206,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B920" t="s">
         <v>402</v>
@@ -54247,7 +54247,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B921" t="s">
         <v>402</v>
@@ -54288,7 +54288,7 @@
     </row>
     <row r="922" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A922" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B922" s="4" t="s">
         <v>405</v>
@@ -54321,7 +54321,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B923" t="s">
         <v>405</v>
@@ -54362,7 +54362,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B924" t="s">
         <v>405</v>
@@ -54403,7 +54403,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B925" t="s">
         <v>405</v>
@@ -54444,7 +54444,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B926" t="s">
         <v>405</v>
@@ -54485,7 +54485,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B927" t="s">
         <v>405</v>
@@ -54526,7 +54526,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B928" t="s">
         <v>405</v>
@@ -54567,7 +54567,7 @@
     </row>
     <row r="929" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B929" t="s">
         <v>405</v>
@@ -54608,7 +54608,7 @@
     </row>
     <row r="930" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A930" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B930" s="4" t="s">
         <v>407</v>
@@ -54641,7 +54641,7 @@
     </row>
     <row r="931" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B931" t="s">
         <v>407</v>
@@ -54682,7 +54682,7 @@
     </row>
     <row r="932" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B932" t="s">
         <v>407</v>
@@ -54723,7 +54723,7 @@
     </row>
     <row r="933" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B933" t="s">
         <v>407</v>
@@ -54764,7 +54764,7 @@
     </row>
     <row r="934" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B934" t="s">
         <v>407</v>
@@ -54805,7 +54805,7 @@
     </row>
     <row r="935" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B935" t="s">
         <v>407</v>
@@ -54846,7 +54846,7 @@
     </row>
     <row r="936" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B936" t="s">
         <v>407</v>
@@ -54887,7 +54887,7 @@
     </row>
     <row r="937" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B937" t="s">
         <v>407</v>
@@ -54928,7 +54928,7 @@
     </row>
     <row r="938" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A938" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B938" s="4" t="s">
         <v>408</v>
@@ -54961,7 +54961,7 @@
     </row>
     <row r="939" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B939" t="s">
         <v>408</v>
@@ -55002,7 +55002,7 @@
     </row>
     <row r="940" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B940" t="s">
         <v>408</v>
@@ -55043,7 +55043,7 @@
     </row>
     <row r="941" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B941" t="s">
         <v>408</v>
@@ -55084,7 +55084,7 @@
     </row>
     <row r="942" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B942" t="s">
         <v>408</v>
@@ -55125,7 +55125,7 @@
     </row>
     <row r="943" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B943" t="s">
         <v>408</v>
@@ -55166,7 +55166,7 @@
     </row>
     <row r="944" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B944" t="s">
         <v>408</v>
@@ -55207,7 +55207,7 @@
     </row>
     <row r="945" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B945" t="s">
         <v>408</v>
@@ -55248,7 +55248,7 @@
     </row>
     <row r="946" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A946" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B946" s="4" t="s">
         <v>409</v>
@@ -55281,7 +55281,7 @@
     </row>
     <row r="947" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B947" t="s">
         <v>409</v>
@@ -55322,7 +55322,7 @@
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B948" t="s">
         <v>409</v>
@@ -55363,7 +55363,7 @@
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B949" t="s">
         <v>409</v>
@@ -55404,7 +55404,7 @@
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B950" t="s">
         <v>409</v>
@@ -55445,7 +55445,7 @@
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B951" t="s">
         <v>409</v>
@@ -55486,7 +55486,7 @@
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B952" t="s">
         <v>409</v>
@@ -55527,7 +55527,7 @@
     </row>
     <row r="953" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B953" t="s">
         <v>409</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -2369,174 +2369,174 @@
     <t>10-13 00:00</t>
   </si>
   <si>
-    <t>2球 @4.05</t>
+    <t>4球 @4.4 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.4 ⚡</t>
+  </si>
+  <si>
+    <t>10-12 18:00</t>
+  </si>
+  <si>
+    <t>威尼斯</t>
+  </si>
+  <si>
+    <t>10-13 00:30</t>
+  </si>
+  <si>
+    <t>4球 @4.45</t>
+  </si>
+  <si>
+    <t>1球 @7 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
+    <t>10-12 17:00</t>
+  </si>
+  <si>
+    <t>马尔默</t>
+  </si>
+  <si>
+    <t>卡尔马</t>
+  </si>
+  <si>
+    <t>10-13 01:00</t>
+  </si>
+  <si>
+    <t>2球 @3.65</t>
+  </si>
+  <si>
+    <t>2球 @3.65 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
+    <t>奥斯KFUM</t>
+  </si>
+  <si>
+    <t>瓦勒伦加</t>
+  </si>
+  <si>
+    <t>7+球 @16</t>
+  </si>
+  <si>
+    <t>10-12 16:00</t>
+  </si>
+  <si>
+    <t>都灵</t>
+  </si>
+  <si>
+    <t>乌迪内斯</t>
+  </si>
+  <si>
+    <t>10-13 02:45</t>
+  </si>
+  <si>
+    <t>0球 @10</t>
+  </si>
+  <si>
+    <t>1球 @4.5 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.7 ⚡</t>
+  </si>
+  <si>
+    <t>法乙</t>
+  </si>
+  <si>
+    <t>第戎</t>
+  </si>
+  <si>
+    <t>梅斯</t>
+  </si>
+  <si>
+    <t>2球 @3.4</t>
+  </si>
+  <si>
+    <t>1球 @5.95 ⚡</t>
+  </si>
+  <si>
+    <t>考文垂</t>
+  </si>
+  <si>
+    <t>纽卡斯尔</t>
+  </si>
+  <si>
+    <t>10-13 03:00</t>
+  </si>
+  <si>
+    <t>3球 @3.45 ⚡</t>
+  </si>
+  <si>
+    <t>塞维利亚</t>
+  </si>
+  <si>
+    <t>3球 @3.8 ⚡</t>
+  </si>
+  <si>
+    <t>周一009</t>
+  </si>
+  <si>
+    <t>0球 @14.5</t>
+  </si>
+  <si>
+    <t>1球 @5.75 ⚡</t>
+  </si>
+  <si>
+    <t>周一010</t>
+  </si>
+  <si>
+    <t>法马利康</t>
+  </si>
+  <si>
+    <t>阿尔维卡</t>
+  </si>
+  <si>
+    <t>10-13 03:15</t>
+  </si>
+  <si>
+    <t>7+球 @40</t>
+  </si>
+  <si>
+    <t>2球 @3.2 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.65 ⚡</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>欧冠</t>
+  </si>
+  <si>
+    <t>10-14 00:45</t>
+  </si>
+  <si>
+    <t>10-12 14:00</t>
+  </si>
+  <si>
+    <t>布鲁日</t>
+  </si>
+  <si>
+    <t>10-14 03:00</t>
+  </si>
+  <si>
+    <t>1球 @7.75 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.75 ⚡</t>
+  </si>
+  <si>
+    <t>6球 @13</t>
   </si>
   <si>
     <t>4球 @4.7 ⚡</t>
   </si>
   <si>
-    <t>3球 @3.5 ⚡</t>
-  </si>
-  <si>
-    <t>10-12 17:00</t>
-  </si>
-  <si>
-    <t>威尼斯</t>
-  </si>
-  <si>
-    <t>10-13 00:30</t>
-  </si>
-  <si>
-    <t>4球 @4.45</t>
-  </si>
-  <si>
-    <t>1球 @7 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.6 ⚡</t>
-  </si>
-  <si>
-    <t>马尔默</t>
-  </si>
-  <si>
-    <t>卡尔马</t>
-  </si>
-  <si>
-    <t>10-13 01:00</t>
-  </si>
-  <si>
-    <t>0球 @15</t>
-  </si>
-  <si>
-    <t>3球 @3.55 ⚡</t>
-  </si>
-  <si>
-    <t>10-12 16:00</t>
-  </si>
-  <si>
-    <t>奥斯KFUM</t>
-  </si>
-  <si>
-    <t>瓦勒伦加</t>
-  </si>
-  <si>
-    <t>7+球 @16</t>
-  </si>
-  <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
-    <t>都灵</t>
-  </si>
-  <si>
-    <t>乌迪内斯</t>
-  </si>
-  <si>
-    <t>10-13 02:45</t>
-  </si>
-  <si>
-    <t>0球 @10</t>
-  </si>
-  <si>
-    <t>1球 @4.5 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @6.6 ⚡</t>
-  </si>
-  <si>
-    <t>法乙</t>
-  </si>
-  <si>
-    <t>第戎</t>
-  </si>
-  <si>
-    <t>梅斯</t>
-  </si>
-  <si>
-    <t>2球 @3.4</t>
-  </si>
-  <si>
-    <t>10-12 15:00</t>
-  </si>
-  <si>
-    <t>考文垂</t>
-  </si>
-  <si>
-    <t>纽卡斯尔</t>
-  </si>
-  <si>
-    <t>10-13 03:00</t>
-  </si>
-  <si>
-    <t>0球 @15.5</t>
-  </si>
-  <si>
-    <t>2球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>塞维利亚</t>
-  </si>
-  <si>
-    <t>3球 @3.8 ⚡</t>
-  </si>
-  <si>
-    <t>周一009</t>
-  </si>
-  <si>
-    <t>0球 @14.5</t>
-  </si>
-  <si>
-    <t>1球 @5.75 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.45 ⚡</t>
-  </si>
-  <si>
-    <t>周一010</t>
-  </si>
-  <si>
-    <t>法马利康</t>
-  </si>
-  <si>
-    <t>阿尔维卡</t>
-  </si>
-  <si>
-    <t>10-13 03:15</t>
-  </si>
-  <si>
-    <t>2球 @3.35 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
-  </si>
-  <si>
-    <t>10-12 14:00</t>
-  </si>
-  <si>
-    <t>2026-10-13</t>
-  </si>
-  <si>
-    <t>欧冠</t>
-  </si>
-  <si>
-    <t>10-14 00:45</t>
-  </si>
-  <si>
-    <t>布鲁日</t>
-  </si>
-  <si>
-    <t>10-14 03:00</t>
-  </si>
-  <si>
-    <t>1球 @7.75 ⚡</t>
-  </si>
-  <si>
-    <t>6球 @13</t>
-  </si>
-  <si>
-    <t>3球 @3.65 ⚡</t>
-  </si>
-  <si>
     <t>6球 @6.1</t>
   </si>
   <si>
@@ -4820,25 +4820,25 @@
     <t>2:5=350 5:2=55 负其他=80 平其他=150 胜其他=17</t>
   </si>
   <si>
-    <t>0:1=10 1:0=14</t>
-  </si>
-  <si>
-    <t>0:2=12 1:1=7.5 2:0=22</t>
+    <t>0:1=10 1:0=16</t>
+  </si>
+  <si>
+    <t>0:2=12 1:1=7.5 2:0=26</t>
   </si>
   <si>
     <t>0:3=20 1:2=7 2:1=11 3:0=40</t>
   </si>
   <si>
-    <t>0:4=40 1:3=12.5 2:2=11.5 3:1=25 4:0=100</t>
-  </si>
-  <si>
-    <t>0:5=85 1:4=31 2:3=19 3:2=29 4:1=65 5:0=300</t>
-  </si>
-  <si>
-    <t>1:5=75 2:4=40 3:3=40 4:2=70 5:1=175</t>
-  </si>
-  <si>
-    <t>2:5=85 5:2=200 负其他=40 平其他=175 胜其他=65</t>
+    <t>0:4=35 1:3=12.5 2:2=11.5 3:1=25 4:0=100</t>
+  </si>
+  <si>
+    <t>0:5=70 1:4=30 2:3=19 3:2=29 4:1=65 5:0=300</t>
+  </si>
+  <si>
+    <t>1:5=60 2:4=33 3:3=40 4:2=70 5:1=175</t>
+  </si>
+  <si>
+    <t>2:5=70 5:2=200 负其他=30 平其他=150 胜其他=65</t>
   </si>
   <si>
     <t>0:1=20 1:0=9.25</t>
@@ -4862,25 +4862,25 @@
     <t>2:5=400 5:2=90 负其他=150 平其他=300 胜其他=22</t>
   </si>
   <si>
-    <t>0:1=14.5 1:0=8</t>
-  </si>
-  <si>
-    <t>0:2=27 1:1=7.2 2:0=8.5</t>
-  </si>
-  <si>
-    <t>0:3=60 1:2=13 2:1=7 3:0=13.5</t>
-  </si>
-  <si>
-    <t>0:4=200 1:3=36 2:2=13.5 3:1=11.5 4:0=28</t>
-  </si>
-  <si>
-    <t>0:5=500 1:4=100 2:3=37 3:2=21 4:1=27 5:0=75</t>
-  </si>
-  <si>
-    <t>1:5=500 2:4=125 3:3=60 4:2=45 5:1=75</t>
-  </si>
-  <si>
-    <t>2:5=500 5:2=125 负其他=125 平其他=300 胜其他=40</t>
+    <t>0:1=15.5 1:0=8</t>
+  </si>
+  <si>
+    <t>0:2=28 1:1=7.2 2:0=8.5</t>
+  </si>
+  <si>
+    <t>0:3=60 1:2=14 2:1=7 3:0=13.5</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=38 2:2=13.5 3:1=11.5 4:0=26</t>
+  </si>
+  <si>
+    <t>0:5=500 1:4=100 2:3=39 3:2=21 4:1=25 5:0=70</t>
+  </si>
+  <si>
+    <t>1:5=500 2:4=125 3:3=60 4:2=42 5:1=70</t>
+  </si>
+  <si>
+    <t>2:5=500 5:2=100 负其他=125 平其他=300 胜其他=36</t>
   </si>
   <si>
     <t>0:1=12 1:0=14</t>
@@ -4904,25 +4904,25 @@
     <t>2:5=150 5:2=175 负其他=40 平其他=150 胜其他=55</t>
   </si>
   <si>
-    <t>0:1=8.75 1:0=7.5</t>
-  </si>
-  <si>
-    <t>0:2=15 1:1=6 2:0=10.5</t>
+    <t>0:1=9 1:0=7.5</t>
+  </si>
+  <si>
+    <t>0:2=15 1:1=5.5 2:0=10.5</t>
   </si>
   <si>
     <t>0:3=37 1:2=10 2:1=8 3:0=21</t>
   </si>
   <si>
-    <t>0:4=100 1:3=26 2:2=13 3:1=17 4:0=60</t>
-  </si>
-  <si>
-    <t>0:5=400 1:4=90 2:3=40 3:2=28 4:1=50 5:0=200</t>
+    <t>0:4=120 1:3=26 2:2=13 3:1=18 4:0=70</t>
+  </si>
+  <si>
+    <t>0:5=400 1:4=90 2:3=40 3:2=28 4:1=55 5:0=250</t>
   </si>
   <si>
     <t>1:5=350 2:4=150 3:3=75 4:2=90 5:1=175</t>
   </si>
   <si>
-    <t>2:5=400 5:2=300 负其他=175 平其他=400 胜其他=100</t>
+    <t>2:5=400 5:2=300 负其他=175 平其他=400 胜其他=120</t>
   </si>
   <si>
     <t>0:1=9 1:0=10.5</t>
@@ -5015,25 +5015,25 @@
     <t>2:5=175 5:2=250 负其他=65 平其他=250 胜其他=85</t>
   </si>
   <si>
-    <t>0:1=10.5 1:0=6.5</t>
-  </si>
-  <si>
-    <t>0:2=21 1:1=6.5 2:0=8</t>
+    <t>0:1=11.5 1:0=6.75</t>
+  </si>
+  <si>
+    <t>0:2=21 1:1=6.25 2:0=8</t>
   </si>
   <si>
     <t>0:3=65 1:2=11.5 2:1=7 3:0=14</t>
   </si>
   <si>
-    <t>0:4=350 1:3=38 2:2=16 3:1=14 4:0=31</t>
+    <t>0:4=350 1:3=38 2:2=15 3:1=14 4:0=31</t>
   </si>
   <si>
     <t>0:5=750 1:4=200 2:3=55 3:2=28 4:1=36 5:0=120</t>
   </si>
   <si>
-    <t>1:5=550 2:4=250 3:3=100 4:2=80 5:1=120</t>
-  </si>
-  <si>
-    <t>2:5=650 5:2=250 负其他=350 平其他=550 胜其他=80</t>
+    <t>1:5=550 2:4=250 3:3=80 4:2=80 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=650 5:2=250 负其他=350 平其他=500 胜其他=80</t>
   </si>
   <si>
     <t>0:1=12 1:0=11.5</t>
@@ -5210,7 +5210,7 @@
     <t>2:5=300 5:2=90 负其他=60 平其他=150 胜其他=30</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-12T17:00:06+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-12T18:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -16621,22 +16621,22 @@
         <v>21</v>
       </c>
       <c r="I103" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J103" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="K103" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="L103" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" t="s">
+        <v>21</v>
+      </c>
+      <c r="N103" t="s">
         <v>785</v>
-      </c>
-      <c r="L103" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" t="s">
-        <v>21</v>
-      </c>
-      <c r="N103" t="s">
-        <v>786</v>
       </c>
       <c r="O103" t="s">
         <v>21</v>
@@ -16656,10 +16656,10 @@
         <v>114</v>
       </c>
       <c r="E104" t="s">
+        <v>786</v>
+      </c>
+      <c r="F104" t="s">
         <v>787</v>
-      </c>
-      <c r="F104" t="s">
-        <v>788</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>55</v>
@@ -16668,22 +16668,22 @@
         <v>21</v>
       </c>
       <c r="I104" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="J104" s="3" t="s">
+      <c r="K104" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="K104" s="3" t="s">
+      <c r="L104" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" t="s">
         <v>791</v>
-      </c>
-      <c r="L104" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" t="s">
-        <v>21</v>
-      </c>
-      <c r="N104" t="s">
-        <v>786</v>
       </c>
       <c r="O104" t="s">
         <v>21</v>
@@ -16721,7 +16721,7 @@
         <v>796</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L105" t="s">
         <v>21</v>
@@ -16730,7 +16730,7 @@
         <v>21</v>
       </c>
       <c r="N105" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="O105" t="s">
         <v>21</v>
@@ -16765,19 +16765,19 @@
         <v>800</v>
       </c>
       <c r="J106" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="L106" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" t="s">
+        <v>21</v>
+      </c>
+      <c r="N106" t="s">
         <v>801</v>
-      </c>
-      <c r="K106" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="L106" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" t="s">
-        <v>21</v>
-      </c>
-      <c r="N106" t="s">
-        <v>797</v>
       </c>
       <c r="O106" t="s">
         <v>21</v>
@@ -16824,7 +16824,7 @@
         <v>21</v>
       </c>
       <c r="N107" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O107" t="s">
         <v>21</v>
@@ -16859,10 +16859,10 @@
         <v>811</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="L108" t="s">
         <v>21</v>
@@ -16871,7 +16871,7 @@
         <v>21</v>
       </c>
       <c r="N108" t="s">
-        <v>812</v>
+        <v>785</v>
       </c>
       <c r="O108" t="s">
         <v>21</v>
@@ -16903,13 +16903,13 @@
         <v>21</v>
       </c>
       <c r="I109" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="J109" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="J109" s="3" t="s">
-        <v>817</v>
-      </c>
       <c r="K109" s="3" t="s">
-        <v>796</v>
+        <v>816</v>
       </c>
       <c r="L109" t="s">
         <v>21</v>
@@ -16918,7 +16918,7 @@
         <v>21</v>
       </c>
       <c r="N109" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="O109" t="s">
         <v>21</v>
@@ -16938,7 +16938,7 @@
         <v>118</v>
       </c>
       <c r="E110" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F110" t="s">
         <v>815</v>
@@ -16953,10 +16953,10 @@
         <v>425</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L110" t="s">
         <v>21</v>
@@ -16965,7 +16965,7 @@
         <v>21</v>
       </c>
       <c r="N110" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="O110" t="s">
         <v>21</v>
@@ -16976,7 +16976,7 @@
         <v>778</v>
       </c>
       <c r="B111" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C111" t="s">
         <v>144</v>
@@ -16997,13 +16997,13 @@
         <v>21</v>
       </c>
       <c r="I111" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="J111" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="J111" s="3" t="s">
-        <v>822</v>
-      </c>
       <c r="K111" s="3" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="L111" t="s">
         <v>21</v>
@@ -17012,7 +17012,7 @@
         <v>21</v>
       </c>
       <c r="N111" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="O111" t="s">
         <v>21</v>
@@ -17023,19 +17023,19 @@
         <v>778</v>
       </c>
       <c r="B112" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C112" t="s">
         <v>139</v>
       </c>
       <c r="D112" t="s">
+        <v>823</v>
+      </c>
+      <c r="E112" t="s">
+        <v>824</v>
+      </c>
+      <c r="F112" t="s">
         <v>825</v>
-      </c>
-      <c r="E112" t="s">
-        <v>826</v>
-      </c>
-      <c r="F112" t="s">
-        <v>827</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>55</v>
@@ -17044,14 +17044,14 @@
         <v>21</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>732</v>
+        <v>826</v>
       </c>
       <c r="J112" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="K112" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="K112" s="3" t="s">
-        <v>829</v>
-      </c>
       <c r="L112" t="s">
         <v>21</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>21</v>
       </c>
       <c r="N112" t="s">
-        <v>830</v>
+        <v>785</v>
       </c>
       <c r="O112" t="s">
         <v>21</v>
@@ -17067,13 +17067,13 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B113" t="s">
         <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D113" t="s">
         <v>577</v>
@@ -17082,7 +17082,7 @@
         <v>589</v>
       </c>
       <c r="F113" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>55</v>
@@ -17094,10 +17094,10 @@
         <v>454</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L113" t="s">
         <v>21</v>
@@ -17106,7 +17106,7 @@
         <v>21</v>
       </c>
       <c r="N113" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O113" t="s">
         <v>21</v>
@@ -17114,22 +17114,22 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B114" t="s">
         <v>397</v>
       </c>
       <c r="C114" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D114" t="s">
         <v>663</v>
       </c>
       <c r="E114" t="s">
+        <v>833</v>
+      </c>
+      <c r="F114" t="s">
         <v>834</v>
-      </c>
-      <c r="F114" t="s">
-        <v>835</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>55</v>
@@ -17141,11 +17141,11 @@
         <v>486</v>
       </c>
       <c r="J114" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="K114" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="K114" s="3" t="s">
-        <v>829</v>
-      </c>
       <c r="L114" t="s">
         <v>21</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>21</v>
       </c>
       <c r="N114" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O114" t="s">
         <v>21</v>
@@ -17161,13 +17161,13 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B115" t="s">
         <v>399</v>
       </c>
       <c r="C115" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D115" t="s">
         <v>612</v>
@@ -17176,7 +17176,7 @@
         <v>103</v>
       </c>
       <c r="F115" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>55</v>
@@ -17188,10 +17188,10 @@
         <v>837</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>784</v>
+        <v>838</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>
@@ -17200,7 +17200,7 @@
         <v>21</v>
       </c>
       <c r="N115" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O115" t="s">
         <v>21</v>
@@ -17208,13 +17208,13 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B116" t="s">
         <v>402</v>
       </c>
       <c r="C116" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D116" t="s">
         <v>117</v>
@@ -17223,7 +17223,7 @@
         <v>44</v>
       </c>
       <c r="F116" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>70</v>
@@ -17235,10 +17235,10 @@
         <v>723</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L116" t="s">
         <v>21</v>
@@ -17247,7 +17247,7 @@
         <v>21</v>
       </c>
       <c r="N116" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O116" t="s">
         <v>21</v>
@@ -17255,13 +17255,13 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B117" t="s">
         <v>405</v>
       </c>
       <c r="C117" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D117" t="s">
         <v>97</v>
@@ -17270,7 +17270,7 @@
         <v>629</v>
       </c>
       <c r="F117" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G117" t="s">
         <v>21</v>
@@ -17294,7 +17294,7 @@
         <v>21</v>
       </c>
       <c r="N117" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O117" t="s">
         <v>21</v>
@@ -17302,13 +17302,13 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B118" t="s">
         <v>407</v>
       </c>
       <c r="C118" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D118" t="s">
         <v>83</v>
@@ -17317,7 +17317,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>55</v>
@@ -17341,7 +17341,7 @@
         <v>21</v>
       </c>
       <c r="N118" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O118" t="s">
         <v>21</v>
@@ -17349,13 +17349,13 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B119" t="s">
         <v>408</v>
       </c>
       <c r="C119" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D119" t="s">
         <v>844</v>
@@ -17364,7 +17364,7 @@
         <v>671</v>
       </c>
       <c r="F119" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>55</v>
@@ -17388,7 +17388,7 @@
         <v>21</v>
       </c>
       <c r="N119" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O119" t="s">
         <v>21</v>
@@ -17396,13 +17396,13 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B120" t="s">
         <v>409</v>
       </c>
       <c r="C120" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D120" t="s">
         <v>86</v>
@@ -17411,7 +17411,7 @@
         <v>107</v>
       </c>
       <c r="F120" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>70</v>
@@ -17423,7 +17423,7 @@
         <v>476</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>847</v>
@@ -17435,7 +17435,7 @@
         <v>21</v>
       </c>
       <c r="N120" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O120" t="s">
         <v>21</v>
@@ -49844,11 +49844,11 @@
         <v>441</v>
       </c>
       <c r="F810" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G810" s="9"/>
       <c r="H810" s="10">
-        <v>1.178</v>
+        <v>0.816</v>
       </c>
       <c r="I810" s="11"/>
       <c r="J810" s="8"/>
@@ -49857,7 +49857,7 @@
       </c>
       <c r="L810" s="11"/>
       <c r="M810" s="4" t="s">
-        <v>914</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.25">
@@ -49877,25 +49877,25 @@
         <v>433</v>
       </c>
       <c r="F811" s="12">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="G811" s="13">
-        <v>5.833</v>
+        <v>6.154</v>
       </c>
       <c r="H811" s="14">
-        <v>0.467</v>
+        <v>0.646</v>
       </c>
       <c r="I811" s="15">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="J811" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K811" s="16">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="L811" s="15">
-        <v>-47.5</v>
+        <v>-47.7</v>
       </c>
       <c r="M811" t="s">
         <v>1600</v>
@@ -49918,25 +49918,25 @@
         <v>453</v>
       </c>
       <c r="F812" s="12">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="G812" s="13">
-        <v>3.815</v>
+        <v>3.92</v>
       </c>
       <c r="H812" s="14">
-        <v>0.235</v>
+        <v>0.43</v>
       </c>
       <c r="I812" s="15">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="J812" s="12">
-        <v>13.833</v>
+        <v>15.167</v>
       </c>
       <c r="K812" s="16">
-        <v>-9.783</v>
+        <v>-10.817</v>
       </c>
       <c r="L812" s="15">
-        <v>-70.7</v>
+        <v>-71.3</v>
       </c>
       <c r="M812" t="s">
         <v>1601</v>
@@ -49959,25 +49959,25 @@
         <v>423</v>
       </c>
       <c r="F813" s="12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G813" s="13">
         <v>3.239</v>
       </c>
       <c r="H813" s="14">
-        <v>0.261</v>
+        <v>0.161</v>
       </c>
       <c r="I813" s="15">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="J813" s="12">
         <v>19.5</v>
       </c>
       <c r="K813" s="16">
-        <v>-16</v>
+        <v>-16.1</v>
       </c>
       <c r="L813" s="15">
-        <v>-82</v>
+        <v>-82.6</v>
       </c>
       <c r="M813" t="s">
         <v>1602</v>
@@ -50000,25 +50000,25 @@
         <v>438</v>
       </c>
       <c r="F814" s="12">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="G814" s="13">
-        <v>4.133</v>
+        <v>4.073</v>
       </c>
       <c r="H814" s="14">
-        <v>0.567</v>
+        <v>0.327</v>
       </c>
       <c r="I814" s="15">
-        <v>13.7</v>
+        <v>8</v>
       </c>
       <c r="J814" s="12">
-        <v>37.8</v>
+        <v>36.8</v>
       </c>
       <c r="K814" s="16">
-        <v>-33.1</v>
+        <v>-32.4</v>
       </c>
       <c r="L814" s="15">
-        <v>-87.6</v>
+        <v>-88</v>
       </c>
       <c r="M814" t="s">
         <v>1603</v>
@@ -50044,22 +50044,22 @@
         <v>8</v>
       </c>
       <c r="G815" s="13">
-        <v>6.673</v>
+        <v>6.517</v>
       </c>
       <c r="H815" s="14">
-        <v>1.327</v>
+        <v>1.483</v>
       </c>
       <c r="I815" s="15">
-        <v>19.9</v>
+        <v>22.8</v>
       </c>
       <c r="J815" s="12">
-        <v>88.167</v>
+        <v>85.5</v>
       </c>
       <c r="K815" s="16">
-        <v>-80.167</v>
+        <v>-77.5</v>
       </c>
       <c r="L815" s="15">
-        <v>-90.9</v>
+        <v>-90.6</v>
       </c>
       <c r="M815" t="s">
         <v>1604</v>
@@ -50082,25 +50082,25 @@
         <v>522</v>
       </c>
       <c r="F816" s="12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G816" s="13">
-        <v>12</v>
+        <v>10.873</v>
       </c>
       <c r="H816" s="14">
-        <v>3</v>
+        <v>3.627</v>
       </c>
       <c r="I816" s="15">
-        <v>25</v>
+        <v>33.4</v>
       </c>
       <c r="J816" s="12">
-        <v>80</v>
+        <v>75.6</v>
       </c>
       <c r="K816" s="16">
-        <v>-65</v>
+        <v>-61.1</v>
       </c>
       <c r="L816" s="15">
-        <v>-81.2</v>
+        <v>-80.8</v>
       </c>
       <c r="M816" t="s">
         <v>1605</v>
@@ -50123,25 +50123,25 @@
         <v>634</v>
       </c>
       <c r="F817" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G817" s="13">
-        <v>15.907</v>
+        <v>13.392</v>
       </c>
       <c r="H817" s="14">
-        <v>4.093</v>
+        <v>2.608</v>
       </c>
       <c r="I817" s="15">
-        <v>25.7</v>
+        <v>19.5</v>
       </c>
       <c r="J817" s="12">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="K817" s="16">
-        <v>-93</v>
+        <v>-87</v>
       </c>
       <c r="L817" s="15">
-        <v>-82.3</v>
+        <v>-84.5</v>
       </c>
       <c r="M817" t="s">
         <v>1606</v>
@@ -50158,7 +50158,7 @@
         <v>114</v>
       </c>
       <c r="D818" s="4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E818" s="4" t="s">
         <v>441</v>
@@ -50191,7 +50191,7 @@
         <v>114</v>
       </c>
       <c r="D819" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E819" t="s">
         <v>433</v>
@@ -50232,7 +50232,7 @@
         <v>114</v>
       </c>
       <c r="D820" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E820" t="s">
         <v>453</v>
@@ -50273,7 +50273,7 @@
         <v>114</v>
       </c>
       <c r="D821" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E821" t="s">
         <v>423</v>
@@ -50314,7 +50314,7 @@
         <v>114</v>
       </c>
       <c r="D822" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E822" t="s">
         <v>438</v>
@@ -50355,7 +50355,7 @@
         <v>114</v>
       </c>
       <c r="D823" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E823" t="s">
         <v>430</v>
@@ -50396,7 +50396,7 @@
         <v>114</v>
       </c>
       <c r="D824" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E824" t="s">
         <v>522</v>
@@ -50437,7 +50437,7 @@
         <v>114</v>
       </c>
       <c r="D825" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E825" t="s">
         <v>634</v>
@@ -50488,7 +50488,7 @@
       </c>
       <c r="G826" s="9"/>
       <c r="H826" s="10">
-        <v>0.226</v>
+        <v>0.78</v>
       </c>
       <c r="I826" s="11"/>
       <c r="J826" s="8"/>
@@ -50520,22 +50520,22 @@
         <v>5.75</v>
       </c>
       <c r="G827" s="13">
-        <v>5.156</v>
+        <v>5.277</v>
       </c>
       <c r="H827" s="14">
-        <v>0.594</v>
+        <v>0.473</v>
       </c>
       <c r="I827" s="15">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="J827" s="12">
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
       <c r="K827" s="16">
-        <v>-5.5</v>
+        <v>-6</v>
       </c>
       <c r="L827" s="15">
-        <v>-48.9</v>
+        <v>-51.1</v>
       </c>
       <c r="M827" t="s">
         <v>1614</v>
@@ -50561,22 +50561,22 @@
         <v>3.65</v>
       </c>
       <c r="G828" s="13">
-        <v>3.406</v>
+        <v>3.422</v>
       </c>
       <c r="H828" s="14">
-        <v>0.244</v>
+        <v>0.228</v>
       </c>
       <c r="I828" s="15">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J828" s="12">
-        <v>14.233</v>
+        <v>14.567</v>
       </c>
       <c r="K828" s="16">
-        <v>-10.583</v>
+        <v>-10.917</v>
       </c>
       <c r="L828" s="15">
-        <v>-74.4</v>
+        <v>-74.9</v>
       </c>
       <c r="M828" t="s">
         <v>1615</v>
@@ -50602,22 +50602,22 @@
         <v>3.55</v>
       </c>
       <c r="G829" s="13">
-        <v>3.22</v>
+        <v>3.278</v>
       </c>
       <c r="H829" s="14">
-        <v>0.33</v>
+        <v>0.272</v>
       </c>
       <c r="I829" s="15">
-        <v>10.3</v>
+        <v>8.3</v>
       </c>
       <c r="J829" s="12">
-        <v>23.375</v>
+        <v>23.625</v>
       </c>
       <c r="K829" s="16">
-        <v>-19.825</v>
+        <v>-20.075</v>
       </c>
       <c r="L829" s="15">
-        <v>-84.8</v>
+        <v>-85</v>
       </c>
       <c r="M829" t="s">
         <v>1616</v>
@@ -50643,13 +50643,13 @@
         <v>5.15</v>
       </c>
       <c r="G830" s="13">
-        <v>4.357</v>
+        <v>4.333</v>
       </c>
       <c r="H830" s="14">
-        <v>0.793</v>
+        <v>0.817</v>
       </c>
       <c r="I830" s="15">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="J830" s="12">
         <v>57.8</v>
@@ -50684,22 +50684,22 @@
         <v>9</v>
       </c>
       <c r="G831" s="13">
-        <v>7.298</v>
+        <v>7.166</v>
       </c>
       <c r="H831" s="14">
-        <v>1.702</v>
+        <v>1.834</v>
       </c>
       <c r="I831" s="15">
-        <v>23.3</v>
+        <v>25.6</v>
       </c>
       <c r="J831" s="12">
-        <v>126.667</v>
+        <v>125.833</v>
       </c>
       <c r="K831" s="16">
-        <v>-117.667</v>
+        <v>-116.833</v>
       </c>
       <c r="L831" s="15">
-        <v>-92.9</v>
+        <v>-92.8</v>
       </c>
       <c r="M831" t="s">
         <v>1618</v>
@@ -50725,22 +50725,22 @@
         <v>17</v>
       </c>
       <c r="G832" s="13">
-        <v>16.071</v>
+        <v>15.441</v>
       </c>
       <c r="H832" s="14">
-        <v>0.929</v>
+        <v>1.559</v>
       </c>
       <c r="I832" s="15">
-        <v>5.8</v>
+        <v>10.1</v>
       </c>
       <c r="J832" s="12">
-        <v>161</v>
+        <v>159.4</v>
       </c>
       <c r="K832" s="16">
-        <v>-144</v>
+        <v>-142.4</v>
       </c>
       <c r="L832" s="15">
-        <v>-89.4</v>
+        <v>-89.3</v>
       </c>
       <c r="M832" t="s">
         <v>1619</v>
@@ -50766,22 +50766,22 @@
         <v>23</v>
       </c>
       <c r="G833" s="13">
-        <v>21.583</v>
+        <v>19.565</v>
       </c>
       <c r="H833" s="14">
-        <v>1.417</v>
+        <v>3.435</v>
       </c>
       <c r="I833" s="15">
-        <v>6.6</v>
+        <v>17.6</v>
       </c>
       <c r="J833" s="12">
-        <v>218</v>
+        <v>212.2</v>
       </c>
       <c r="K833" s="16">
-        <v>-195</v>
+        <v>-189.2</v>
       </c>
       <c r="L833" s="15">
-        <v>-89.4</v>
+        <v>-89.2</v>
       </c>
       <c r="M833" t="s">
         <v>1620</v>
@@ -51128,12 +51128,12 @@
       </c>
       <c r="G842" s="9"/>
       <c r="H842" s="10">
-        <v>-2.564</v>
+        <v>-2.117</v>
       </c>
       <c r="I842" s="11"/>
       <c r="J842" s="8"/>
       <c r="K842" s="10">
-        <v>-3.232</v>
+        <v>-3.393</v>
       </c>
       <c r="L842" s="11"/>
       <c r="M842" s="4" t="s">
@@ -51160,22 +51160,22 @@
         <v>4.5</v>
       </c>
       <c r="G843" s="13">
-        <v>4.038</v>
+        <v>4.091</v>
       </c>
       <c r="H843" s="14">
-        <v>0.462</v>
+        <v>0.409</v>
       </c>
       <c r="I843" s="15">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="J843" s="12">
-        <v>8.125</v>
+        <v>8.25</v>
       </c>
       <c r="K843" s="16">
-        <v>-3.625</v>
+        <v>-3.75</v>
       </c>
       <c r="L843" s="15">
-        <v>-44.6</v>
+        <v>-45.4</v>
       </c>
       <c r="M843" t="s">
         <v>1628</v>
@@ -51198,25 +51198,25 @@
         <v>453</v>
       </c>
       <c r="F844" s="12">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="G844" s="13">
-        <v>3.043</v>
+        <v>2.909</v>
       </c>
       <c r="H844" s="14">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="I844" s="15">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J844" s="12">
-        <v>10.5</v>
+        <v>10.333</v>
       </c>
       <c r="K844" s="16">
-        <v>-7.45</v>
+        <v>-7.383</v>
       </c>
       <c r="L844" s="15">
-        <v>-70.9</v>
+        <v>-71.4</v>
       </c>
       <c r="M844" t="s">
         <v>1629</v>
@@ -51239,25 +51239,25 @@
         <v>423</v>
       </c>
       <c r="F845" s="12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G845" s="13">
         <v>3.337</v>
       </c>
       <c r="H845" s="14">
-        <v>0.413</v>
+        <v>0.363</v>
       </c>
       <c r="I845" s="15">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="J845" s="12">
         <v>19</v>
       </c>
       <c r="K845" s="16">
-        <v>-15.25</v>
+        <v>-15.3</v>
       </c>
       <c r="L845" s="15">
-        <v>-80.3</v>
+        <v>-80.5</v>
       </c>
       <c r="M845" t="s">
         <v>1630</v>
@@ -51280,25 +51280,25 @@
         <v>438</v>
       </c>
       <c r="F846" s="12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="G846" s="13">
-        <v>4.978</v>
+        <v>5.166</v>
       </c>
       <c r="H846" s="14">
-        <v>1.622</v>
+        <v>1.834</v>
       </c>
       <c r="I846" s="15">
-        <v>32.6</v>
+        <v>35.5</v>
       </c>
       <c r="J846" s="12">
-        <v>43.2</v>
+        <v>49.4</v>
       </c>
       <c r="K846" s="16">
-        <v>-36.6</v>
+        <v>-42.4</v>
       </c>
       <c r="L846" s="15">
-        <v>-84.7</v>
+        <v>-85.8</v>
       </c>
       <c r="M846" t="s">
         <v>1631</v>
@@ -51321,25 +51321,25 @@
         <v>430</v>
       </c>
       <c r="F847" s="12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G847" s="13">
-        <v>10.068</v>
+        <v>10.362</v>
       </c>
       <c r="H847" s="14">
-        <v>3.432</v>
+        <v>3.638</v>
       </c>
       <c r="I847" s="15">
-        <v>34.1</v>
+        <v>35.1</v>
       </c>
       <c r="J847" s="12">
-        <v>134.667</v>
+        <v>143.833</v>
       </c>
       <c r="K847" s="16">
-        <v>-121.167</v>
+        <v>-129.833</v>
       </c>
       <c r="L847" s="15">
-        <v>-90</v>
+        <v>-90.3</v>
       </c>
       <c r="M847" t="s">
         <v>1632</v>
@@ -51362,25 +51362,25 @@
         <v>522</v>
       </c>
       <c r="F848" s="12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G848" s="13">
         <v>25.2</v>
       </c>
       <c r="H848" s="14">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="I848" s="15">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="J848" s="12">
         <v>168</v>
       </c>
       <c r="K848" s="16">
-        <v>-141</v>
+        <v>-140</v>
       </c>
       <c r="L848" s="15">
-        <v>-83.9</v>
+        <v>-83.3</v>
       </c>
       <c r="M848" t="s">
         <v>1633</v>
@@ -51403,25 +51403,25 @@
         <v>634</v>
       </c>
       <c r="F849" s="12">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G849" s="13">
-        <v>41.584</v>
-      </c>
-      <c r="H849" s="17">
-        <v>-1.584</v>
+        <v>44.681</v>
+      </c>
+      <c r="H849" s="14">
+        <v>0.319</v>
       </c>
       <c r="I849" s="15">
-        <v>-3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J849" s="12">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K849" s="16">
-        <v>-235</v>
+        <v>-234</v>
       </c>
       <c r="L849" s="15">
-        <v>-85.4</v>
+        <v>-83.9</v>
       </c>
       <c r="M849" t="s">
         <v>1634</v>
@@ -51448,12 +51448,12 @@
       </c>
       <c r="G850" s="9"/>
       <c r="H850" s="10">
-        <v>0.186</v>
+        <v>0.722</v>
       </c>
       <c r="I850" s="11"/>
       <c r="J850" s="8"/>
       <c r="K850" s="10">
-        <v>-3.971</v>
+        <v>-3.457</v>
       </c>
       <c r="L850" s="11"/>
       <c r="M850" s="4" t="s">
@@ -51477,25 +51477,25 @@
         <v>433</v>
       </c>
       <c r="F851" s="12">
-        <v>5.55</v>
+        <v>5.95</v>
       </c>
       <c r="G851" s="13">
         <v>4.846</v>
       </c>
       <c r="H851" s="14">
-        <v>0.704</v>
+        <v>1.104</v>
       </c>
       <c r="I851" s="15">
-        <v>14.5</v>
+        <v>22.8</v>
       </c>
       <c r="J851" s="12">
         <v>9.75</v>
       </c>
       <c r="K851" s="16">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
       <c r="L851" s="15">
-        <v>-43.1</v>
+        <v>-39</v>
       </c>
       <c r="M851" t="s">
         <v>1635</v>
@@ -51559,25 +51559,25 @@
         <v>423</v>
       </c>
       <c r="F853" s="12">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G853" s="13">
         <v>3.221</v>
       </c>
       <c r="H853" s="14">
-        <v>0.329</v>
+        <v>0.179</v>
       </c>
       <c r="I853" s="15">
-        <v>10.2</v>
+        <v>5.6</v>
       </c>
       <c r="J853" s="12">
         <v>18.688</v>
       </c>
       <c r="K853" s="16">
-        <v>-15.138</v>
+        <v>-15.288</v>
       </c>
       <c r="L853" s="15">
-        <v>-81</v>
+        <v>-81.8</v>
       </c>
       <c r="M853" t="s">
         <v>1637</v>
@@ -51768,7 +51768,7 @@
       </c>
       <c r="G858" s="9"/>
       <c r="H858" s="10">
-        <v>0.165</v>
+        <v>0.808</v>
       </c>
       <c r="I858" s="11"/>
       <c r="J858" s="8"/>
@@ -51879,25 +51879,25 @@
         <v>423</v>
       </c>
       <c r="F861" s="12">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G861" s="13">
         <v>3.16</v>
       </c>
       <c r="H861" s="14">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="I861" s="15">
-        <v>12.3</v>
+        <v>9.2</v>
       </c>
       <c r="J861" s="12">
         <v>19.188</v>
       </c>
       <c r="K861" s="16">
-        <v>-15.638</v>
+        <v>-15.738</v>
       </c>
       <c r="L861" s="15">
-        <v>-81.5</v>
+        <v>-82</v>
       </c>
       <c r="M861" t="s">
         <v>1645</v>
@@ -51920,25 +51920,25 @@
         <v>438</v>
       </c>
       <c r="F862" s="12">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="G862" s="13">
         <v>4.108</v>
       </c>
       <c r="H862" s="14">
-        <v>0.642</v>
+        <v>0.542</v>
       </c>
       <c r="I862" s="15">
-        <v>15.6</v>
+        <v>13.2</v>
       </c>
       <c r="J862" s="12">
         <v>44</v>
       </c>
       <c r="K862" s="16">
-        <v>-39.25</v>
+        <v>-39.35</v>
       </c>
       <c r="L862" s="15">
-        <v>-89.2</v>
+        <v>-89.4</v>
       </c>
       <c r="M862" t="s">
         <v>1646</v>
@@ -51961,25 +51961,25 @@
         <v>430</v>
       </c>
       <c r="F863" s="12">
-        <v>8</v>
+        <v>8.3</v>
       </c>
       <c r="G863" s="13">
         <v>6.553</v>
       </c>
       <c r="H863" s="14">
-        <v>1.447</v>
+        <v>1.747</v>
       </c>
       <c r="I863" s="15">
-        <v>22.1</v>
+        <v>26.7</v>
       </c>
       <c r="J863" s="12">
         <v>111.5</v>
       </c>
       <c r="K863" s="16">
-        <v>-103.5</v>
+        <v>-103.2</v>
       </c>
       <c r="L863" s="15">
-        <v>-92.8</v>
+        <v>-92.6</v>
       </c>
       <c r="M863" t="s">
         <v>1647</v>
@@ -52002,25 +52002,25 @@
         <v>522</v>
       </c>
       <c r="F864" s="12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="G864" s="13">
         <v>13.145</v>
       </c>
       <c r="H864" s="14">
-        <v>0.355</v>
+        <v>1.355</v>
       </c>
       <c r="I864" s="15">
-        <v>2.7</v>
+        <v>10.3</v>
       </c>
       <c r="J864" s="12">
         <v>91.6</v>
       </c>
       <c r="K864" s="16">
-        <v>-78.1</v>
+        <v>-77.1</v>
       </c>
       <c r="L864" s="15">
-        <v>-85.3</v>
+        <v>-84.2</v>
       </c>
       <c r="M864" t="s">
         <v>1648</v>
@@ -52043,25 +52043,25 @@
         <v>634</v>
       </c>
       <c r="F865" s="12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G865" s="13">
         <v>19.715</v>
       </c>
       <c r="H865" s="14">
-        <v>1.285</v>
+        <v>3.285</v>
       </c>
       <c r="I865" s="15">
-        <v>6.5</v>
+        <v>16.7</v>
       </c>
       <c r="J865" s="12">
         <v>150</v>
       </c>
       <c r="K865" s="16">
-        <v>-129</v>
+        <v>-127</v>
       </c>
       <c r="L865" s="15">
-        <v>-86</v>
+        <v>-84.7</v>
       </c>
       <c r="M865" t="s">
         <v>1649</v>
@@ -52078,7 +52078,7 @@
         <v>118</v>
       </c>
       <c r="D866" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E866" s="4" t="s">
         <v>441</v>
@@ -52111,7 +52111,7 @@
         <v>118</v>
       </c>
       <c r="D867" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E867" t="s">
         <v>433</v>
@@ -52152,7 +52152,7 @@
         <v>118</v>
       </c>
       <c r="D868" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E868" t="s">
         <v>453</v>
@@ -52193,7 +52193,7 @@
         <v>118</v>
       </c>
       <c r="D869" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E869" t="s">
         <v>423</v>
@@ -52234,7 +52234,7 @@
         <v>118</v>
       </c>
       <c r="D870" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E870" t="s">
         <v>438</v>
@@ -52275,7 +52275,7 @@
         <v>118</v>
       </c>
       <c r="D871" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E871" t="s">
         <v>430</v>
@@ -52316,7 +52316,7 @@
         <v>118</v>
       </c>
       <c r="D872" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E872" t="s">
         <v>522</v>
@@ -52357,7 +52357,7 @@
         <v>118</v>
       </c>
       <c r="D873" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E873" t="s">
         <v>634</v>
@@ -52392,7 +52392,7 @@
         <v>778</v>
       </c>
       <c r="B874" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C874" s="4" t="s">
         <v>538</v>
@@ -52425,7 +52425,7 @@
         <v>778</v>
       </c>
       <c r="B875" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C875" t="s">
         <v>538</v>
@@ -52466,7 +52466,7 @@
         <v>778</v>
       </c>
       <c r="B876" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C876" t="s">
         <v>538</v>
@@ -52507,7 +52507,7 @@
         <v>778</v>
       </c>
       <c r="B877" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C877" t="s">
         <v>538</v>
@@ -52548,7 +52548,7 @@
         <v>778</v>
       </c>
       <c r="B878" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C878" t="s">
         <v>538</v>
@@ -52589,7 +52589,7 @@
         <v>778</v>
       </c>
       <c r="B879" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C879" t="s">
         <v>538</v>
@@ -52630,7 +52630,7 @@
         <v>778</v>
       </c>
       <c r="B880" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C880" t="s">
         <v>538</v>
@@ -52671,7 +52671,7 @@
         <v>778</v>
       </c>
       <c r="B881" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C881" t="s">
         <v>538</v>
@@ -52712,13 +52712,13 @@
         <v>778</v>
       </c>
       <c r="B882" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="C882" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="D882" s="4" t="s">
         <v>824</v>
-      </c>
-      <c r="C882" s="4" t="s">
-        <v>825</v>
-      </c>
-      <c r="D882" s="4" t="s">
-        <v>826</v>
       </c>
       <c r="E882" s="4" t="s">
         <v>441</v>
@@ -52728,12 +52728,12 @@
       </c>
       <c r="G882" s="9"/>
       <c r="H882" s="10">
-        <v>-2.155</v>
+        <v>-1.907</v>
       </c>
       <c r="I882" s="11"/>
       <c r="J882" s="8"/>
       <c r="K882" s="10">
-        <v>-3.843</v>
+        <v>-4.196</v>
       </c>
       <c r="L882" s="11"/>
       <c r="M882" s="4" t="s">
@@ -52745,37 +52745,37 @@
         <v>778</v>
       </c>
       <c r="B883" t="s">
+        <v>822</v>
+      </c>
+      <c r="C883" t="s">
+        <v>823</v>
+      </c>
+      <c r="D883" t="s">
         <v>824</v>
-      </c>
-      <c r="C883" t="s">
-        <v>825</v>
-      </c>
-      <c r="D883" t="s">
-        <v>826</v>
       </c>
       <c r="E883" t="s">
         <v>433</v>
       </c>
       <c r="F883" s="12">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="G883" s="13">
-        <v>4.015</v>
+        <v>4.253</v>
       </c>
       <c r="H883" s="14">
-        <v>0.385</v>
+        <v>0.497</v>
       </c>
       <c r="I883" s="15">
-        <v>9.6</v>
+        <v>11.7</v>
       </c>
       <c r="J883" s="12">
-        <v>8.5</v>
+        <v>9.125</v>
       </c>
       <c r="K883" s="16">
-        <v>-4.1</v>
+        <v>-4.375</v>
       </c>
       <c r="L883" s="15">
-        <v>-48.2</v>
+        <v>-47.9</v>
       </c>
       <c r="M883" t="s">
         <v>1665</v>
@@ -52786,37 +52786,37 @@
         <v>778</v>
       </c>
       <c r="B884" t="s">
+        <v>822</v>
+      </c>
+      <c r="C884" t="s">
+        <v>823</v>
+      </c>
+      <c r="D884" t="s">
         <v>824</v>
-      </c>
-      <c r="C884" t="s">
-        <v>825</v>
-      </c>
-      <c r="D884" t="s">
-        <v>826</v>
       </c>
       <c r="E884" t="s">
         <v>453</v>
       </c>
       <c r="F884" s="12">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="G884" s="13">
-        <v>3.063</v>
+        <v>3.006</v>
       </c>
       <c r="H884" s="14">
-        <v>0.287</v>
+        <v>0.194</v>
       </c>
       <c r="I884" s="15">
-        <v>9.4</v>
+        <v>6.5</v>
       </c>
       <c r="J884" s="12">
-        <v>11.833</v>
+        <v>11.75</v>
       </c>
       <c r="K884" s="16">
-        <v>-8.483</v>
+        <v>-8.55</v>
       </c>
       <c r="L884" s="15">
-        <v>-71.7</v>
+        <v>-72.8</v>
       </c>
       <c r="M884" t="s">
         <v>1666</v>
@@ -52827,37 +52827,37 @@
         <v>778</v>
       </c>
       <c r="B885" t="s">
+        <v>822</v>
+      </c>
+      <c r="C885" t="s">
+        <v>823</v>
+      </c>
+      <c r="D885" t="s">
         <v>824</v>
-      </c>
-      <c r="C885" t="s">
-        <v>825</v>
-      </c>
-      <c r="D885" t="s">
-        <v>826</v>
       </c>
       <c r="E885" t="s">
         <v>423</v>
       </c>
       <c r="F885" s="12">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="G885" s="13">
         <v>3.158</v>
       </c>
       <c r="H885" s="14">
-        <v>0.592</v>
+        <v>0.492</v>
       </c>
       <c r="I885" s="15">
-        <v>18.8</v>
+        <v>15.6</v>
       </c>
       <c r="J885" s="12">
         <v>24.375</v>
       </c>
       <c r="K885" s="16">
-        <v>-20.625</v>
+        <v>-20.725</v>
       </c>
       <c r="L885" s="15">
-        <v>-84.6</v>
+        <v>-85</v>
       </c>
       <c r="M885" t="s">
         <v>1667</v>
@@ -52868,13 +52868,13 @@
         <v>778</v>
       </c>
       <c r="B886" t="s">
+        <v>822</v>
+      </c>
+      <c r="C886" t="s">
+        <v>823</v>
+      </c>
+      <c r="D886" t="s">
         <v>824</v>
-      </c>
-      <c r="C886" t="s">
-        <v>825</v>
-      </c>
-      <c r="D886" t="s">
-        <v>826</v>
       </c>
       <c r="E886" t="s">
         <v>438</v>
@@ -52883,19 +52883,19 @@
         <v>6.2</v>
       </c>
       <c r="G886" s="13">
-        <v>5.119</v>
+        <v>5.012</v>
       </c>
       <c r="H886" s="14">
-        <v>1.081</v>
+        <v>1.188</v>
       </c>
       <c r="I886" s="15">
-        <v>21.1</v>
+        <v>23.7</v>
       </c>
       <c r="J886" s="12">
-        <v>89.8</v>
+        <v>89.6</v>
       </c>
       <c r="K886" s="16">
-        <v>-83.6</v>
+        <v>-83.4</v>
       </c>
       <c r="L886" s="15">
         <v>-93.1</v>
@@ -52909,13 +52909,13 @@
         <v>778</v>
       </c>
       <c r="B887" t="s">
+        <v>822</v>
+      </c>
+      <c r="C887" t="s">
+        <v>823</v>
+      </c>
+      <c r="D887" t="s">
         <v>824</v>
-      </c>
-      <c r="C887" t="s">
-        <v>825</v>
-      </c>
-      <c r="D887" t="s">
-        <v>826</v>
       </c>
       <c r="E887" t="s">
         <v>430</v>
@@ -52950,37 +52950,37 @@
         <v>778</v>
       </c>
       <c r="B888" t="s">
+        <v>822</v>
+      </c>
+      <c r="C888" t="s">
+        <v>823</v>
+      </c>
+      <c r="D888" t="s">
         <v>824</v>
-      </c>
-      <c r="C888" t="s">
-        <v>825</v>
-      </c>
-      <c r="D888" t="s">
-        <v>826</v>
       </c>
       <c r="E888" t="s">
         <v>522</v>
       </c>
       <c r="F888" s="12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G888" s="13">
-        <v>27.284</v>
+        <v>25.542</v>
       </c>
       <c r="H888" s="17">
-        <v>-4.284</v>
+        <v>-1.542</v>
       </c>
       <c r="I888" s="15">
-        <v>-15.7</v>
+        <v>-6</v>
       </c>
       <c r="J888" s="12">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K888" s="16">
-        <v>-197</v>
+        <v>-192</v>
       </c>
       <c r="L888" s="15">
-        <v>-89.5</v>
+        <v>-88.9</v>
       </c>
       <c r="M888" t="s">
         <v>1670</v>
@@ -52991,37 +52991,37 @@
         <v>778</v>
       </c>
       <c r="B889" t="s">
+        <v>822</v>
+      </c>
+      <c r="C889" t="s">
+        <v>823</v>
+      </c>
+      <c r="D889" t="s">
         <v>824</v>
-      </c>
-      <c r="C889" t="s">
-        <v>825</v>
-      </c>
-      <c r="D889" t="s">
-        <v>826</v>
       </c>
       <c r="E889" t="s">
         <v>634</v>
       </c>
       <c r="F889" s="12">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G889" s="13">
-        <v>44.026</v>
+        <v>43.677</v>
       </c>
       <c r="H889" s="17">
-        <v>-9.026</v>
+        <v>-3.677</v>
       </c>
       <c r="I889" s="15">
-        <v>-20.5</v>
+        <v>-8.4</v>
       </c>
       <c r="J889" s="12">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="K889" s="16">
-        <v>-341</v>
+        <v>-326</v>
       </c>
       <c r="L889" s="15">
-        <v>-90.7</v>
+        <v>-89.1</v>
       </c>
       <c r="M889" t="s">
         <v>1671</v>
@@ -53029,7 +53029,7 @@
     </row>
     <row r="890" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A890" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B890" s="4" t="s">
         <v>171</v>
@@ -53062,7 +53062,7 @@
     </row>
     <row r="891" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B891" t="s">
         <v>171</v>
@@ -53103,7 +53103,7 @@
     </row>
     <row r="892" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B892" t="s">
         <v>171</v>
@@ -53144,7 +53144,7 @@
     </row>
     <row r="893" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B893" t="s">
         <v>171</v>
@@ -53185,7 +53185,7 @@
     </row>
     <row r="894" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B894" t="s">
         <v>171</v>
@@ -53226,7 +53226,7 @@
     </row>
     <row r="895" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B895" t="s">
         <v>171</v>
@@ -53267,7 +53267,7 @@
     </row>
     <row r="896" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B896" t="s">
         <v>171</v>
@@ -53308,7 +53308,7 @@
     </row>
     <row r="897" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B897" t="s">
         <v>171</v>
@@ -53349,7 +53349,7 @@
     </row>
     <row r="898" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A898" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B898" s="4" t="s">
         <v>397</v>
@@ -53358,7 +53358,7 @@
         <v>663</v>
       </c>
       <c r="D898" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E898" s="4" t="s">
         <v>441</v>
@@ -53382,7 +53382,7 @@
     </row>
     <row r="899" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B899" t="s">
         <v>397</v>
@@ -53391,7 +53391,7 @@
         <v>663</v>
       </c>
       <c r="D899" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E899" t="s">
         <v>433</v>
@@ -53423,7 +53423,7 @@
     </row>
     <row r="900" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B900" t="s">
         <v>397</v>
@@ -53432,7 +53432,7 @@
         <v>663</v>
       </c>
       <c r="D900" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E900" t="s">
         <v>453</v>
@@ -53464,7 +53464,7 @@
     </row>
     <row r="901" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B901" t="s">
         <v>397</v>
@@ -53473,7 +53473,7 @@
         <v>663</v>
       </c>
       <c r="D901" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E901" t="s">
         <v>423</v>
@@ -53505,7 +53505,7 @@
     </row>
     <row r="902" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B902" t="s">
         <v>397</v>
@@ -53514,7 +53514,7 @@
         <v>663</v>
       </c>
       <c r="D902" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E902" t="s">
         <v>438</v>
@@ -53546,7 +53546,7 @@
     </row>
     <row r="903" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B903" t="s">
         <v>397</v>
@@ -53555,7 +53555,7 @@
         <v>663</v>
       </c>
       <c r="D903" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E903" t="s">
         <v>430</v>
@@ -53587,7 +53587,7 @@
     </row>
     <row r="904" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B904" t="s">
         <v>397</v>
@@ -53596,7 +53596,7 @@
         <v>663</v>
       </c>
       <c r="D904" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E904" t="s">
         <v>522</v>
@@ -53628,7 +53628,7 @@
     </row>
     <row r="905" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B905" t="s">
         <v>397</v>
@@ -53637,7 +53637,7 @@
         <v>663</v>
       </c>
       <c r="D905" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E905" t="s">
         <v>634</v>
@@ -53669,7 +53669,7 @@
     </row>
     <row r="906" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A906" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B906" s="4" t="s">
         <v>399</v>
@@ -53702,7 +53702,7 @@
     </row>
     <row r="907" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B907" t="s">
         <v>399</v>
@@ -53743,7 +53743,7 @@
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B908" t="s">
         <v>399</v>
@@ -53784,7 +53784,7 @@
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B909" t="s">
         <v>399</v>
@@ -53825,7 +53825,7 @@
     </row>
     <row r="910" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B910" t="s">
         <v>399</v>
@@ -53866,7 +53866,7 @@
     </row>
     <row r="911" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B911" t="s">
         <v>399</v>
@@ -53907,7 +53907,7 @@
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B912" t="s">
         <v>399</v>
@@ -53948,7 +53948,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B913" t="s">
         <v>399</v>
@@ -53989,7 +53989,7 @@
     </row>
     <row r="914" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A914" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B914" s="4" t="s">
         <v>402</v>
@@ -54022,7 +54022,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B915" t="s">
         <v>402</v>
@@ -54063,7 +54063,7 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B916" t="s">
         <v>402</v>
@@ -54104,7 +54104,7 @@
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B917" t="s">
         <v>402</v>
@@ -54145,7 +54145,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B918" t="s">
         <v>402</v>
@@ -54186,7 +54186,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B919" t="s">
         <v>402</v>
@@ -54227,7 +54227,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B920" t="s">
         <v>402</v>
@@ -54268,7 +54268,7 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B921" t="s">
         <v>402</v>
@@ -54309,7 +54309,7 @@
     </row>
     <row r="922" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A922" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B922" s="4" t="s">
         <v>405</v>
@@ -54342,7 +54342,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B923" t="s">
         <v>405</v>
@@ -54383,7 +54383,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B924" t="s">
         <v>405</v>
@@ -54424,7 +54424,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B925" t="s">
         <v>405</v>
@@ -54465,7 +54465,7 @@
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B926" t="s">
         <v>405</v>
@@ -54506,7 +54506,7 @@
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B927" t="s">
         <v>405</v>
@@ -54547,7 +54547,7 @@
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B928" t="s">
         <v>405</v>
@@ -54588,7 +54588,7 @@
     </row>
     <row r="929" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B929" t="s">
         <v>405</v>
@@ -54629,7 +54629,7 @@
     </row>
     <row r="930" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A930" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B930" s="4" t="s">
         <v>407</v>
@@ -54662,7 +54662,7 @@
     </row>
     <row r="931" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B931" t="s">
         <v>407</v>
@@ -54703,7 +54703,7 @@
     </row>
     <row r="932" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B932" t="s">
         <v>407</v>
@@ -54744,7 +54744,7 @@
     </row>
     <row r="933" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B933" t="s">
         <v>407</v>
@@ -54785,7 +54785,7 @@
     </row>
     <row r="934" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B934" t="s">
         <v>407</v>
@@ -54826,7 +54826,7 @@
     </row>
     <row r="935" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B935" t="s">
         <v>407</v>
@@ -54867,7 +54867,7 @@
     </row>
     <row r="936" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B936" t="s">
         <v>407</v>
@@ -54908,7 +54908,7 @@
     </row>
     <row r="937" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B937" t="s">
         <v>407</v>
@@ -54949,7 +54949,7 @@
     </row>
     <row r="938" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A938" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B938" s="4" t="s">
         <v>408</v>
@@ -54982,7 +54982,7 @@
     </row>
     <row r="939" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B939" t="s">
         <v>408</v>
@@ -55023,7 +55023,7 @@
     </row>
     <row r="940" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B940" t="s">
         <v>408</v>
@@ -55064,7 +55064,7 @@
     </row>
     <row r="941" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B941" t="s">
         <v>408</v>
@@ -55105,7 +55105,7 @@
     </row>
     <row r="942" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B942" t="s">
         <v>408</v>
@@ -55146,7 +55146,7 @@
     </row>
     <row r="943" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B943" t="s">
         <v>408</v>
@@ -55187,7 +55187,7 @@
     </row>
     <row r="944" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B944" t="s">
         <v>408</v>
@@ -55228,7 +55228,7 @@
     </row>
     <row r="945" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B945" t="s">
         <v>408</v>
@@ -55269,7 +55269,7 @@
     </row>
     <row r="946" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A946" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B946" s="4" t="s">
         <v>409</v>
@@ -55302,7 +55302,7 @@
     </row>
     <row r="947" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B947" t="s">
         <v>409</v>
@@ -55343,7 +55343,7 @@
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B948" t="s">
         <v>409</v>
@@ -55384,7 +55384,7 @@
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B949" t="s">
         <v>409</v>
@@ -55425,7 +55425,7 @@
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B950" t="s">
         <v>409</v>
@@ -55466,7 +55466,7 @@
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B951" t="s">
         <v>409</v>
@@ -55507,7 +55507,7 @@
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B952" t="s">
         <v>409</v>
@@ -55548,7 +55548,7 @@
     </row>
     <row r="953" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B953" t="s">
         <v>409</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5168,7 +5168,7 @@
     <t>2:5=300 5:2=90 负其他=60 平其他=150 胜其他=30</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-12T22:19:27+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-12T23:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -16850,8 +16850,8 @@
       <c r="F109" t="s">
         <v>804</v>
       </c>
-      <c r="G109" s="5" t="s">
-        <v>70</v>
+      <c r="G109" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>21</v>
@@ -17179,8 +17179,8 @@
       <c r="F116" t="s">
         <v>821</v>
       </c>
-      <c r="G116" s="5" t="s">
-        <v>70</v>
+      <c r="G116" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>21</v>
@@ -17367,8 +17367,8 @@
       <c r="F120" t="s">
         <v>821</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>70</v>
+      <c r="G120" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>21</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5150,7 +5150,7 @@
     <t>2:5=300 5:2=90 负其他=60 平其他=150 胜其他=30</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-13T09:00:03+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-13T10:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -2465,10 +2465,10 @@
     <t>10-14 03:00</t>
   </si>
   <si>
-    <t>4球 @4.4 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
+    <t>10-13 11:00</t>
   </si>
   <si>
     <t>6球 @13</t>
@@ -5018,25 +5018,25 @@
     <t>2:5=500 5:2=60 负其他=200 平其他=300 胜其他=13</t>
   </si>
   <si>
-    <t>0:1=28 1:0=7.75</t>
-  </si>
-  <si>
-    <t>0:2=80 1:1=10.5 2:0=6.5</t>
-  </si>
-  <si>
-    <t>0:3=300 1:2=30 2:1=8.5 3:0=7.25</t>
-  </si>
-  <si>
-    <t>0:4=500 1:3=100 2:2=22 3:1=10.5 4:0=11.5</t>
-  </si>
-  <si>
-    <t>0:5=800 1:4=400 2:3=90 3:2=28 4:1=16 5:0=20</t>
+    <t>0:1=31 1:0=7.75</t>
+  </si>
+  <si>
+    <t>0:2=90 1:1=11 2:0=6.5</t>
+  </si>
+  <si>
+    <t>0:3=300 1:2=35 2:1=8.5 3:0=7</t>
+  </si>
+  <si>
+    <t>0:4=500 1:3=100 2:2=24 3:1=10.5 4:0=11</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=400 2:3=90 3:2=28 4:1=16 5:0=19</t>
   </si>
   <si>
     <t>1:5=800 2:4=400 3:3=100 4:2=50 5:1=30</t>
   </si>
   <si>
-    <t>2:5=800 5:2=100 负其他=40 平其他=400 胜其他=16</t>
+    <t>2:5=800 5:2=90 负其他=40 平其他=400 胜其他=15</t>
   </si>
   <si>
     <t>0:1=13 1:0=10</t>
@@ -5150,7 +5150,7 @@
     <t>2:5=300 5:2=90 负其他=60 平其他=150 胜其他=30</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-13T10:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-13T11:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -17080,22 +17080,22 @@
         <v>21</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>484</v>
+        <v>683</v>
       </c>
       <c r="J114" s="3" t="s">
         <v>815</v>
       </c>
       <c r="K114" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="L114" t="s">
+        <v>21</v>
+      </c>
+      <c r="M114" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" t="s">
         <v>816</v>
-      </c>
-      <c r="L114" t="s">
-        <v>21</v>
-      </c>
-      <c r="M114" t="s">
-        <v>21</v>
-      </c>
-      <c r="N114" t="s">
-        <v>812</v>
       </c>
       <c r="O114" t="s">
         <v>21</v>
@@ -17142,7 +17142,7 @@
         <v>21</v>
       </c>
       <c r="N115" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="O115" t="s">
         <v>21</v>
@@ -17330,7 +17330,7 @@
         <v>21</v>
       </c>
       <c r="N119" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="O119" t="s">
         <v>21</v>
@@ -17377,7 +17377,7 @@
         <v>21</v>
       </c>
       <c r="N120" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="O120" t="s">
         <v>21</v>
@@ -53310,7 +53310,7 @@
       </c>
       <c r="G898" s="9"/>
       <c r="H898" s="10">
-        <v>1.305</v>
+        <v>1.555</v>
       </c>
       <c r="I898" s="11"/>
       <c r="J898" s="8"/>
@@ -53339,25 +53339,25 @@
         <v>433</v>
       </c>
       <c r="F899" s="12">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G899" s="13">
         <v>7.156</v>
       </c>
       <c r="H899" s="14">
-        <v>0.594</v>
+        <v>0.844</v>
       </c>
       <c r="I899" s="15">
-        <v>8.3</v>
+        <v>11.8</v>
       </c>
       <c r="J899" s="12">
         <v>19.25</v>
       </c>
       <c r="K899" s="16">
-        <v>-11.5</v>
+        <v>-11.25</v>
       </c>
       <c r="L899" s="15">
-        <v>-59.7</v>
+        <v>-58.4</v>
       </c>
       <c r="M899" t="s">
         <v>1659</v>
@@ -53380,25 +53380,25 @@
         <v>452</v>
       </c>
       <c r="F900" s="12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G900" s="13">
         <v>4.173</v>
       </c>
       <c r="H900" s="14">
-        <v>0.427</v>
+        <v>0.527</v>
       </c>
       <c r="I900" s="15">
-        <v>10.2</v>
+        <v>12.6</v>
       </c>
       <c r="J900" s="12">
         <v>27.833</v>
       </c>
       <c r="K900" s="16">
-        <v>-23.233</v>
+        <v>-23.133</v>
       </c>
       <c r="L900" s="15">
-        <v>-83.5</v>
+        <v>-83.1</v>
       </c>
       <c r="M900" t="s">
         <v>1660</v>
@@ -53421,25 +53421,25 @@
         <v>423</v>
       </c>
       <c r="F901" s="12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G901" s="13">
         <v>3.434</v>
       </c>
       <c r="H901" s="14">
-        <v>0.316</v>
+        <v>0.416</v>
       </c>
       <c r="I901" s="15">
-        <v>9.2</v>
+        <v>12.1</v>
       </c>
       <c r="J901" s="12">
         <v>60.313</v>
       </c>
       <c r="K901" s="16">
-        <v>-56.563</v>
+        <v>-56.463</v>
       </c>
       <c r="L901" s="15">
-        <v>-93.8</v>
+        <v>-93.6</v>
       </c>
       <c r="M901" t="s">
         <v>1661</v>
@@ -53503,25 +53503,25 @@
         <v>430</v>
       </c>
       <c r="F903" s="12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G903" s="13">
         <v>5.525</v>
       </c>
       <c r="H903" s="14">
-        <v>1.275</v>
+        <v>1.075</v>
       </c>
       <c r="I903" s="15">
-        <v>23.1</v>
+        <v>19.5</v>
       </c>
       <c r="J903" s="12">
         <v>203</v>
       </c>
       <c r="K903" s="16">
-        <v>-196.2</v>
+        <v>-196.4</v>
       </c>
       <c r="L903" s="15">
-        <v>-96.6</v>
+        <v>-96.7</v>
       </c>
       <c r="M903" t="s">
         <v>1663</v>
@@ -53544,25 +53544,25 @@
         <v>521</v>
       </c>
       <c r="F904" s="12">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G904" s="13">
         <v>11.095</v>
       </c>
       <c r="H904" s="17">
-        <v>-1.095</v>
+        <v>-1.595</v>
       </c>
       <c r="I904" s="15">
-        <v>-9.9</v>
+        <v>-14.4</v>
       </c>
       <c r="J904" s="12">
         <v>206.2</v>
       </c>
       <c r="K904" s="16">
-        <v>-196.2</v>
+        <v>-196.7</v>
       </c>
       <c r="L904" s="15">
-        <v>-95.1</v>
+        <v>-95.4</v>
       </c>
       <c r="M904" t="s">
         <v>1664</v>
@@ -53585,25 +53585,25 @@
         <v>632</v>
       </c>
       <c r="F905" s="12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G905" s="13">
         <v>9.623</v>
       </c>
       <c r="H905" s="14">
-        <v>3.377</v>
+        <v>2.377</v>
       </c>
       <c r="I905" s="15">
-        <v>35.1</v>
+        <v>24.7</v>
       </c>
       <c r="J905" s="12">
         <v>214.6</v>
       </c>
       <c r="K905" s="16">
-        <v>-201.6</v>
+        <v>-202.6</v>
       </c>
       <c r="L905" s="15">
-        <v>-93.9</v>
+        <v>-94.4</v>
       </c>
       <c r="M905" t="s">
         <v>1665</v>
@@ -53630,7 +53630,7 @@
       </c>
       <c r="G906" s="9"/>
       <c r="H906" s="10">
-        <v>1.036</v>
+        <v>0.857</v>
       </c>
       <c r="I906" s="11"/>
       <c r="J906" s="8"/>
@@ -53662,22 +53662,22 @@
         <v>6.5</v>
       </c>
       <c r="G907" s="13">
-        <v>6.07</v>
+        <v>6.2</v>
       </c>
       <c r="H907" s="14">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="I907" s="15">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="J907" s="12">
-        <v>17.875</v>
+        <v>19.375</v>
       </c>
       <c r="K907" s="16">
-        <v>-11.375</v>
+        <v>-12.875</v>
       </c>
       <c r="L907" s="15">
-        <v>-63.6</v>
+        <v>-66.4</v>
       </c>
       <c r="M907" t="s">
         <v>1666</v>
@@ -53703,22 +53703,22 @@
         <v>4.2</v>
       </c>
       <c r="G908" s="13">
-        <v>3.823</v>
+        <v>3.908</v>
       </c>
       <c r="H908" s="14">
-        <v>0.377</v>
+        <v>0.292</v>
       </c>
       <c r="I908" s="15">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="J908" s="12">
-        <v>32.333</v>
+        <v>35.833</v>
       </c>
       <c r="K908" s="16">
-        <v>-28.133</v>
+        <v>-31.633</v>
       </c>
       <c r="L908" s="15">
-        <v>-87</v>
+        <v>-88.3</v>
       </c>
       <c r="M908" t="s">
         <v>1667</v>
@@ -53744,19 +53744,19 @@
         <v>3.65</v>
       </c>
       <c r="G909" s="13">
-        <v>3.422</v>
+        <v>3.42</v>
       </c>
       <c r="H909" s="14">
-        <v>0.228</v>
+        <v>0.23</v>
       </c>
       <c r="I909" s="15">
         <v>6.7</v>
       </c>
       <c r="J909" s="12">
-        <v>86.438</v>
+        <v>87.625</v>
       </c>
       <c r="K909" s="16">
-        <v>-82.788</v>
+        <v>-83.975</v>
       </c>
       <c r="L909" s="15">
         <v>-95.8</v>
@@ -53785,22 +53785,22 @@
         <v>4.7</v>
       </c>
       <c r="G910" s="13">
-        <v>4.173</v>
+        <v>4.17</v>
       </c>
       <c r="H910" s="14">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="I910" s="15">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="J910" s="12">
-        <v>128.8</v>
+        <v>129.1</v>
       </c>
       <c r="K910" s="16">
-        <v>-124.1</v>
+        <v>-124.4</v>
       </c>
       <c r="L910" s="15">
-        <v>-96.3</v>
+        <v>-96.4</v>
       </c>
       <c r="M910" t="s">
         <v>1669</v>
@@ -53826,19 +53826,19 @@
         <v>7.4</v>
       </c>
       <c r="G911" s="13">
-        <v>6.132</v>
+        <v>6.035</v>
       </c>
       <c r="H911" s="14">
-        <v>1.268</v>
+        <v>1.365</v>
       </c>
       <c r="I911" s="15">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="J911" s="12">
-        <v>225.667</v>
+        <v>225.5</v>
       </c>
       <c r="K911" s="16">
-        <v>-218.267</v>
+        <v>-218.1</v>
       </c>
       <c r="L911" s="15">
         <v>-96.7</v>
@@ -53908,22 +53908,22 @@
         <v>16</v>
       </c>
       <c r="G913" s="13">
-        <v>9.877</v>
+        <v>9.387</v>
       </c>
       <c r="H913" s="14">
-        <v>6.123</v>
+        <v>6.613</v>
       </c>
       <c r="I913" s="15">
-        <v>62</v>
+        <v>70.5</v>
       </c>
       <c r="J913" s="12">
-        <v>271.2</v>
+        <v>269</v>
       </c>
       <c r="K913" s="16">
-        <v>-255.2</v>
+        <v>-253</v>
       </c>
       <c r="L913" s="15">
-        <v>-94.1</v>
+        <v>-94</v>
       </c>
       <c r="M913" t="s">
         <v>1672</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11267" uniqueCount="2019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11278" uniqueCount="2020">
   <si>
     <t>日期</t>
   </si>
@@ -2468,6 +2468,9 @@
     <t>10-13 15:00</t>
   </si>
   <si>
+    <t>10-13 19:00</t>
+  </si>
+  <si>
     <t>上海海港</t>
   </si>
   <si>
@@ -2486,81 +2489,81 @@
     <t>10-13 20:15</t>
   </si>
   <si>
+    <t>3球 @3.7 ⚡</t>
+  </si>
+  <si>
+    <t>欧冠</t>
+  </si>
+  <si>
+    <t>10-14 00:45</t>
+  </si>
+  <si>
+    <t>4球 @4.6 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.35 ⚡</t>
+  </si>
+  <si>
+    <t>布鲁日</t>
+  </si>
+  <si>
+    <t>10-14 03:00</t>
+  </si>
+  <si>
+    <t>3球 @3.75 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.5 ⚡</t>
+  </si>
+  <si>
+    <t>6球 @6.1</t>
+  </si>
+  <si>
+    <t>5球 @4.85 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @5.3 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @4.1 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @4.1 ⚡</t>
+  </si>
+  <si>
+    <t>加拉塔萨</t>
+  </si>
+  <si>
+    <t>3球 @4.3</t>
+  </si>
+  <si>
+    <t>3球 @4.3 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.4 ⚡</t>
+  </si>
+  <si>
+    <t>斯托克城</t>
+  </si>
+  <si>
+    <t>米堡</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>全北现代</t>
+  </si>
+  <si>
+    <t>10-14 18:00</t>
+  </si>
+  <si>
     <t>3球 @3.6 ⚡</t>
   </si>
   <si>
-    <t>欧冠</t>
-  </si>
-  <si>
-    <t>10-14 00:45</t>
-  </si>
-  <si>
-    <t>4球 @4.6 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.35 ⚡</t>
-  </si>
-  <si>
-    <t>布鲁日</t>
-  </si>
-  <si>
-    <t>10-14 03:00</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.5 ⚡</t>
-  </si>
-  <si>
-    <t>6球 @6.1</t>
-  </si>
-  <si>
-    <t>5球 @4.85 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @5.3 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>加拉塔萨</t>
-  </si>
-  <si>
-    <t>6球 @6.95</t>
-  </si>
-  <si>
-    <t>3球 @4.6 ⚡</t>
-  </si>
-  <si>
     <t>10-13 14:00</t>
   </si>
   <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
-    <t>斯托克城</t>
-  </si>
-  <si>
-    <t>米堡</t>
-  </si>
-  <si>
-    <t>4球 @5 ⚡</t>
-  </si>
-  <si>
-    <t>2026-10-14</t>
-  </si>
-  <si>
-    <t>全北现代</t>
-  </si>
-  <si>
-    <t>10-14 18:00</t>
-  </si>
-  <si>
     <t>曼谷港务</t>
   </si>
   <si>
@@ -2570,9 +2573,6 @@
     <t>4球 @4.4 ⚡</t>
   </si>
   <si>
-    <t>3球 @3.7 ⚡</t>
-  </si>
-  <si>
     <t>清水鼓动</t>
   </si>
   <si>
@@ -5150,25 +5150,22 @@
     <t>2:5=175 5:2=100 负其他=60 平其他=150 胜其他=37</t>
   </si>
   <si>
-    <t>0:1=14 1:0=10</t>
-  </si>
-  <si>
-    <t>0:2=21 1:1=7.5 2:0=12</t>
-  </si>
-  <si>
-    <t>0:3=45 1:2=10.5 2:1=7.25 3:0=20</t>
-  </si>
-  <si>
-    <t>0:4=100 1:3=23 2:2=11 3:1=13.5 4:0=40</t>
-  </si>
-  <si>
-    <t>0:5=300 1:4=75 2:3=26 3:2=18 4:1=30 5:0=100</t>
-  </si>
-  <si>
-    <t>1:5=175 2:4=80 3:3=40 4:2=45 5:1=75</t>
-  </si>
-  <si>
-    <t>2:5=250 5:2=100 负其他=70 平其他=175 胜其他=35</t>
+    <t>0:2=23 1:1=7.6 2:0=12</t>
+  </si>
+  <si>
+    <t>0:3=45 1:2=11.5 2:1=7.25 3:0=17</t>
+  </si>
+  <si>
+    <t>0:4=100 1:3=23 2:2=12 3:1=12.5 4:0=35</t>
+  </si>
+  <si>
+    <t>0:5=300 1:4=75 2:3=28 3:2=18 4:1=28 5:0=90</t>
+  </si>
+  <si>
+    <t>1:5=175 2:4=80 3:3=40 4:2=40 5:1=75</t>
+  </si>
+  <si>
+    <t>2:5=250 5:2=100 负其他=70 平其他=175 胜其他=32</t>
   </si>
   <si>
     <t>0:1=11.5 1:0=12</t>
@@ -5192,25 +5189,25 @@
     <t>2:5=130 5:2=150 负其他=50 平其他=200 胜其他=55</t>
   </si>
   <si>
-    <t>0:1=40 1:0=11</t>
-  </si>
-  <si>
-    <t>0:2=80 1:1=13 2:0=7.5</t>
-  </si>
-  <si>
-    <t>0:3=200 1:2=27 2:1=8.25 3:0=7.5</t>
+    <t>0:1=40 1:0=11.5</t>
+  </si>
+  <si>
+    <t>0:2=80 1:1=13.5 2:0=7.6</t>
+  </si>
+  <si>
+    <t>0:3=200 1:2=28 2:1=8.25 3:0=7.5</t>
   </si>
   <si>
     <t>0:4=500 1:3=100 2:2=20 3:1=8.5 4:0=11.5</t>
   </si>
   <si>
-    <t>0:5=800 1:4=400 2:3=80 3:2=21 4:1=14 5:0=20</t>
-  </si>
-  <si>
-    <t>1:5=600 2:4=400 3:3=75 4:2=30 5:1=24</t>
-  </si>
-  <si>
-    <t>2:5=500 5:2=55 负其他=300 平其他=300 胜其他=10</t>
+    <t>0:5=800 1:4=300 2:3=80 3:2=21 4:1=14 5:0=20</t>
+  </si>
+  <si>
+    <t>1:5=600 2:4=300 3:3=65 4:2=28 5:1=24</t>
+  </si>
+  <si>
+    <t>2:5=500 5:2=50 负其他=220 平其他=250 胜其他=10</t>
   </si>
   <si>
     <t>0:1=36 1:0=8</t>
@@ -5276,49 +5273,49 @@
     <t>2:5=30 5:2=700 负其他=4 平其他=200 胜其他=175</t>
   </si>
   <si>
-    <t>0:1=30 1:0=16.5</t>
-  </si>
-  <si>
-    <t>0:2=40 1:1=11 2:0=13</t>
-  </si>
-  <si>
-    <t>0:3=70 1:2=14 2:1=8 3:0=18</t>
-  </si>
-  <si>
-    <t>0:4=150 1:3=27 2:2=10.5 3:1=11.5 4:0=28</t>
-  </si>
-  <si>
-    <t>0:5=300 1:4=60 2:3=23 3:2=13 4:1=18 5:0=65</t>
-  </si>
-  <si>
-    <t>1:5=200 2:4=60 3:3=25 4:2=22 5:1=35</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=40 负其他=35 平其他=90 胜其他=13</t>
+    <t>0:1=34 1:0=16.5</t>
+  </si>
+  <si>
+    <t>0:2=45 1:1=12 2:0=13</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=16 2:1=8 3:0=17</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=32 2:2=11 3:1=10 4:0=26</t>
+  </si>
+  <si>
+    <t>0:5=300 1:4=70 2:3=24 3:2=12.5 4:1=16 5:0=55</t>
+  </si>
+  <si>
+    <t>1:5=200 2:4=65 3:3=25 4:2=21 5:1=32</t>
+  </si>
+  <si>
+    <t>2:5=150 5:2=40 负其他=35 平其他=90 胜其他=12</t>
   </si>
   <si>
     <t>0:0=55</t>
   </si>
   <si>
-    <t>0:1=18 1:0=50</t>
-  </si>
-  <si>
-    <t>0:2=12 1:1=15 2:0=80</t>
-  </si>
-  <si>
-    <t>0:3=12 1:2=9.5 2:1=25 3:0=150</t>
-  </si>
-  <si>
-    <t>0:4=15 1:3=9 2:2=16 3:1=60 4:0=400</t>
-  </si>
-  <si>
-    <t>0:5=21 1:4=13 2:3=15 3:2=30 4:1=150 5:0=600</t>
-  </si>
-  <si>
-    <t>1:5=20 2:4=20 3:3=35 4:2=100 5:1=400</t>
-  </si>
-  <si>
-    <t>2:5=30 5:2=300 负其他=6.5 平其他=100 胜其他=75</t>
+    <t>0:1=19 1:0=50</t>
+  </si>
+  <si>
+    <t>0:2=12 1:1=15 2:0=85</t>
+  </si>
+  <si>
+    <t>0:3=11 1:2=9.5 2:1=27 3:0=150</t>
+  </si>
+  <si>
+    <t>0:4=15.5 1:3=8.5 2:2=16 3:1=65 4:0=400</t>
+  </si>
+  <si>
+    <t>0:5=22 1:4=12 2:3=16 3:2=35 4:1=150 5:0=600</t>
+  </si>
+  <si>
+    <t>1:5=20 2:4=19 3:3=35 4:2=100 5:1=400</t>
+  </si>
+  <si>
+    <t>2:5=30 5:2=300 负其他=6.5 平其他=100 胜其他=80</t>
   </si>
   <si>
     <t>0:1=15 1:0=11</t>
@@ -5594,7 +5591,7 @@
     <t>2:5=400 5:2=500 负其他=250 平其他=650 胜其他=280</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-13T18:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-13T19:00:07+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -5609,19 +5606,19 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>14/110 = 12.7%</t>
+    <t>14/111 = 12.6%</t>
   </si>
   <si>
     <t>模型A 命中率（数据核心·自修正）</t>
   </si>
   <si>
-    <t>20/110 = 18.2%</t>
+    <t>20/111 = 18.0%</t>
   </si>
   <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
-    <t>27/110 = 24.5%</t>
+    <t>27/111 = 24.3%</t>
   </si>
   <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
@@ -5666,7 +5663,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>86 场（另剔除爆冷 24 场）</t>
+    <t>87 场（另剔除爆冷 24 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -5711,7 +5708,7 @@
     <t>0% (0/20)</t>
   </si>
   <si>
-    <t>0% (0/16)</t>
+    <t>0% (0/17)</t>
   </si>
   <si>
     <t>25% (2/8)</t>
@@ -5729,93 +5726,96 @@
     <t>17% (1/6)</t>
   </si>
   <si>
+    <t>0% (0/11)</t>
+  </si>
+  <si>
+    <t>0% (0/9)</t>
+  </si>
+  <si>
+    <t>20% (4/20)</t>
+  </si>
+  <si>
+    <t>20% (5/25)</t>
+  </si>
+  <si>
+    <t>29% (4/14)</t>
+  </si>
+  <si>
+    <t>0% (0/6)</t>
+  </si>
+  <si>
+    <t>26% (5/19)</t>
+  </si>
+  <si>
+    <t>19% (7/36)</t>
+  </si>
+  <si>
+    <t>55% (11/20)</t>
+  </si>
+  <si>
+    <t>33% (2/6)</t>
+  </si>
+  <si>
+    <t>60% (3/5)</t>
+  </si>
+  <si>
+    <t>0% (0/1)</t>
+  </si>
+  <si>
+    <t>29% (2/7)</t>
+  </si>
+  <si>
+    <t>33% (3/9)</t>
+  </si>
+  <si>
+    <t>25% (3/12)</t>
+  </si>
+  <si>
+    <t>22% (7/32)</t>
+  </si>
+  <si>
+    <t>25% (4/16)</t>
+  </si>
+  <si>
+    <t>0% (0/7)</t>
+  </si>
+  <si>
+    <t>0% (0/4)</t>
+  </si>
+  <si>
+    <t>50% (1/2)</t>
+  </si>
+  <si>
+    <t>8% (1/13)</t>
+  </si>
+  <si>
+    <t>0% (0/34)</t>
+  </si>
+  <si>
+    <t>0% (0/23)</t>
+  </si>
+  <si>
     <t>0% (0/10)</t>
   </si>
   <si>
-    <t>0% (0/9)</t>
-  </si>
-  <si>
-    <t>20% (4/20)</t>
-  </si>
-  <si>
-    <t>13% (2/15)</t>
-  </si>
-  <si>
-    <t>20% (5/25)</t>
-  </si>
-  <si>
-    <t>29% (4/14)</t>
-  </si>
-  <si>
-    <t>0% (0/6)</t>
-  </si>
-  <si>
-    <t>28% (5/18)</t>
-  </si>
-  <si>
-    <t>19% (7/36)</t>
-  </si>
-  <si>
-    <t>55% (11/20)</t>
-  </si>
-  <si>
-    <t>33% (2/6)</t>
-  </si>
-  <si>
-    <t>60% (3/5)</t>
-  </si>
-  <si>
-    <t>0% (0/1)</t>
-  </si>
-  <si>
-    <t>29% (2/7)</t>
-  </si>
-  <si>
-    <t>33% (3/9)</t>
-  </si>
-  <si>
-    <t>18% (2/11)</t>
-  </si>
-  <si>
-    <t>22% (7/32)</t>
-  </si>
-  <si>
-    <t>25% (4/16)</t>
-  </si>
-  <si>
-    <t>0% (0/7)</t>
-  </si>
-  <si>
-    <t>0% (0/4)</t>
-  </si>
-  <si>
-    <t>50% (1/2)</t>
+    <t>0% (0/21)</t>
+  </si>
+  <si>
+    <t>20% (1/5)</t>
+  </si>
+  <si>
+    <t>33% (1/3)</t>
+  </si>
+  <si>
+    <t>10% (1/10)</t>
+  </si>
+  <si>
+    <t>0% (0/24)</t>
   </si>
   <si>
     <t>8% (1/12)</t>
   </si>
   <si>
-    <t>0% (0/34)</t>
-  </si>
-  <si>
-    <t>0% (0/23)</t>
-  </si>
-  <si>
-    <t>0% (0/21)</t>
-  </si>
-  <si>
-    <t>20% (1/5)</t>
-  </si>
-  <si>
-    <t>10% (1/10)</t>
-  </si>
-  <si>
-    <t>0% (0/11)</t>
-  </si>
-  <si>
-    <t>0% (0/24)</t>
-  </si>
-  <si>
     <t>0% (0/5)</t>
   </si>
   <si>
@@ -5936,7 +5936,7 @@
     <t>010</t>
   </si>
   <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-12，警戒线 30 次）</t>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-10-13，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -5952,6 +5952,9 @@
   </si>
   <si>
     <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
@@ -6151,12 +6154,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -6212,10 +6215,10 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -17472,7 +17475,7 @@
         <v>55</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>553</v>
@@ -17483,17 +17486,17 @@
       <c r="K113" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="L113" t="s">
-        <v>21</v>
-      </c>
-      <c r="M113" t="s">
-        <v>21</v>
+      <c r="L113" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M113" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="N113" t="s">
         <v>815</v>
       </c>
       <c r="O113" t="s">
-        <v>21</v>
+        <v>816</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
@@ -17507,13 +17510,13 @@
         <v>776</v>
       </c>
       <c r="D114" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E114" t="s">
         <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>55</v>
@@ -17537,7 +17540,7 @@
         <v>21</v>
       </c>
       <c r="N114" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O114" t="s">
         <v>21</v>
@@ -17554,13 +17557,13 @@
         <v>776</v>
       </c>
       <c r="D115" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E115" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F115" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G115" s="5" t="s">
         <v>70</v>
@@ -17569,13 +17572,13 @@
         <v>21</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>
@@ -17584,7 +17587,7 @@
         <v>21</v>
       </c>
       <c r="N115" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="O115" t="s">
         <v>21</v>
@@ -17598,7 +17601,7 @@
         <v>171</v>
       </c>
       <c r="C116" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D116" t="s">
         <v>579</v>
@@ -17607,7 +17610,7 @@
         <v>591</v>
       </c>
       <c r="F116" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>55</v>
@@ -17619,10 +17622,10 @@
         <v>454</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L116" t="s">
         <v>21</v>
@@ -17631,7 +17634,7 @@
         <v>21</v>
       </c>
       <c r="N116" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O116" t="s">
         <v>21</v>
@@ -17645,16 +17648,16 @@
         <v>397</v>
       </c>
       <c r="C117" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D117" t="s">
         <v>661</v>
       </c>
       <c r="E117" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F117" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>55</v>
@@ -17666,10 +17669,10 @@
         <v>685</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L117" t="s">
         <v>21</v>
@@ -17678,7 +17681,7 @@
         <v>21</v>
       </c>
       <c r="N117" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="O117" t="s">
         <v>21</v>
@@ -17692,7 +17695,7 @@
         <v>399</v>
       </c>
       <c r="C118" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D118" t="s">
         <v>613</v>
@@ -17701,7 +17704,7 @@
         <v>103</v>
       </c>
       <c r="F118" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>55</v>
@@ -17713,10 +17716,10 @@
         <v>727</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="L118" t="s">
         <v>21</v>
@@ -17725,7 +17728,7 @@
         <v>21</v>
       </c>
       <c r="N118" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O118" t="s">
         <v>21</v>
@@ -17739,7 +17742,7 @@
         <v>402</v>
       </c>
       <c r="C119" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D119" t="s">
         <v>117</v>
@@ -17748,7 +17751,7 @@
         <v>44</v>
       </c>
       <c r="F119" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>70</v>
@@ -17760,10 +17763,10 @@
         <v>605</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L119" t="s">
         <v>21</v>
@@ -17772,7 +17775,7 @@
         <v>21</v>
       </c>
       <c r="N119" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O119" t="s">
         <v>21</v>
@@ -17786,7 +17789,7 @@
         <v>405</v>
       </c>
       <c r="C120" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D120" t="s">
         <v>97</v>
@@ -17795,7 +17798,7 @@
         <v>629</v>
       </c>
       <c r="F120" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G120" t="s">
         <v>21</v>
@@ -17804,13 +17807,13 @@
         <v>21</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L120" t="s">
         <v>21</v>
@@ -17833,7 +17836,7 @@
         <v>407</v>
       </c>
       <c r="C121" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D121" t="s">
         <v>83</v>
@@ -17842,7 +17845,7 @@
         <v>60</v>
       </c>
       <c r="F121" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>55</v>
@@ -17851,13 +17854,13 @@
         <v>21</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>578</v>
+        <v>463</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="L121" t="s">
         <v>21</v>
@@ -17866,7 +17869,7 @@
         <v>21</v>
       </c>
       <c r="N121" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O121" t="s">
         <v>21</v>
@@ -17880,16 +17883,16 @@
         <v>408</v>
       </c>
       <c r="C122" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D122" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E122" t="s">
         <v>670</v>
       </c>
       <c r="F122" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>55</v>
@@ -17898,13 +17901,13 @@
         <v>21</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="L122" t="s">
         <v>21</v>
@@ -17913,7 +17916,7 @@
         <v>21</v>
       </c>
       <c r="N122" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="O122" t="s">
         <v>21</v>
@@ -17927,7 +17930,7 @@
         <v>409</v>
       </c>
       <c r="C123" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D123" t="s">
         <v>86</v>
@@ -17936,7 +17939,7 @@
         <v>107</v>
       </c>
       <c r="F123" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>70</v>
@@ -17960,7 +17963,7 @@
         <v>21</v>
       </c>
       <c r="N123" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O123" t="s">
         <v>21</v>
@@ -17983,7 +17986,7 @@
         <v>842</v>
       </c>
       <c r="F124" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>55</v>
@@ -17992,13 +17995,13 @@
         <v>21</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>605</v>
+        <v>492</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="L124" t="s">
         <v>21</v>
@@ -18007,7 +18010,7 @@
         <v>21</v>
       </c>
       <c r="N124" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O124" t="s">
         <v>21</v>
@@ -18015,7 +18018,7 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B125" t="s">
         <v>179</v>
@@ -18027,10 +18030,10 @@
         <v>31</v>
       </c>
       <c r="E125" t="s">
+        <v>844</v>
+      </c>
+      <c r="F125" t="s">
         <v>845</v>
-      </c>
-      <c r="F125" t="s">
-        <v>846</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>55</v>
@@ -18042,10 +18045,10 @@
         <v>492</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>822</v>
+        <v>846</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>822</v>
+        <v>846</v>
       </c>
       <c r="L125" t="s">
         <v>21</v>
@@ -18054,7 +18057,7 @@
         <v>21</v>
       </c>
       <c r="N125" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O125" t="s">
         <v>21</v>
@@ -18062,7 +18065,7 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B126" t="s">
         <v>183</v>
@@ -18074,10 +18077,10 @@
         <v>26</v>
       </c>
       <c r="E126" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F126" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>55</v>
@@ -18086,13 +18089,13 @@
         <v>21</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>850</v>
+        <v>823</v>
       </c>
       <c r="L126" t="s">
         <v>21</v>
@@ -18101,7 +18104,7 @@
         <v>21</v>
       </c>
       <c r="N126" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O126" t="s">
         <v>21</v>
@@ -18109,7 +18112,7 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B127" t="s">
         <v>501</v>
@@ -18124,7 +18127,7 @@
         <v>851</v>
       </c>
       <c r="F127" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>55</v>
@@ -18136,7 +18139,7 @@
         <v>852</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>853</v>
@@ -18148,7 +18151,7 @@
         <v>21</v>
       </c>
       <c r="N127" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O127" t="s">
         <v>21</v>
@@ -18156,13 +18159,13 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B128" t="s">
         <v>505</v>
       </c>
       <c r="C128" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D128" t="s">
         <v>673</v>
@@ -18186,7 +18189,7 @@
         <v>855</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L128" t="s">
         <v>21</v>
@@ -18195,7 +18198,7 @@
         <v>21</v>
       </c>
       <c r="N128" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O128" t="s">
         <v>21</v>
@@ -18203,13 +18206,13 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B129" t="s">
         <v>512</v>
       </c>
       <c r="C129" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D129" t="s">
         <v>856</v>
@@ -18230,7 +18233,7 @@
         <v>685</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>857</v>
@@ -18242,7 +18245,7 @@
         <v>21</v>
       </c>
       <c r="N129" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O129" t="s">
         <v>21</v>
@@ -18250,13 +18253,13 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B130" t="s">
         <v>858</v>
       </c>
       <c r="C130" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D130" t="s">
         <v>721</v>
@@ -18280,7 +18283,7 @@
         <v>855</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L130" t="s">
         <v>21</v>
@@ -18289,7 +18292,7 @@
         <v>21</v>
       </c>
       <c r="N130" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O130" t="s">
         <v>21</v>
@@ -18297,13 +18300,13 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B131" t="s">
         <v>860</v>
       </c>
       <c r="C131" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D131" t="s">
         <v>861</v>
@@ -18324,7 +18327,7 @@
         <v>577</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K131" s="3" t="s">
         <v>862</v>
@@ -18336,7 +18339,7 @@
         <v>21</v>
       </c>
       <c r="N131" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O131" t="s">
         <v>21</v>
@@ -18344,13 +18347,13 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B132" t="s">
         <v>863</v>
       </c>
       <c r="C132" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D132" t="s">
         <v>122</v>
@@ -18383,7 +18386,7 @@
         <v>21</v>
       </c>
       <c r="N132" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O132" t="s">
         <v>21</v>
@@ -18391,13 +18394,13 @@
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B133" t="s">
         <v>865</v>
       </c>
       <c r="C133" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D133" t="s">
         <v>72</v>
@@ -18415,13 +18418,13 @@
         <v>21</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>850</v>
+        <v>823</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>850</v>
+        <v>823</v>
       </c>
       <c r="L133" t="s">
         <v>21</v>
@@ -18430,7 +18433,7 @@
         <v>21</v>
       </c>
       <c r="N133" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="O133" t="s">
         <v>21</v>
@@ -18438,13 +18441,13 @@
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B134" t="s">
         <v>866</v>
       </c>
       <c r="C134" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D134" t="s">
         <v>647</v>
@@ -18465,10 +18468,10 @@
         <v>524</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>850</v>
+        <v>823</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>850</v>
+        <v>823</v>
       </c>
       <c r="L134" t="s">
         <v>21</v>
@@ -18477,7 +18480,7 @@
         <v>21</v>
       </c>
       <c r="N134" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O134" t="s">
         <v>21</v>
@@ -18485,7 +18488,7 @@
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B135" t="s">
         <v>868</v>
@@ -18524,7 +18527,7 @@
         <v>21</v>
       </c>
       <c r="N135" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O135" t="s">
         <v>21</v>
@@ -54444,7 +54447,7 @@
         <v>163</v>
       </c>
       <c r="C898" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D898" s="4" t="s">
         <v>35</v>
@@ -54477,7 +54480,7 @@
         <v>163</v>
       </c>
       <c r="C899" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D899" t="s">
         <v>35</v>
@@ -54518,7 +54521,7 @@
         <v>163</v>
       </c>
       <c r="C900" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D900" t="s">
         <v>35</v>
@@ -54559,7 +54562,7 @@
         <v>163</v>
       </c>
       <c r="C901" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D901" t="s">
         <v>35</v>
@@ -54600,7 +54603,7 @@
         <v>163</v>
       </c>
       <c r="C902" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D902" t="s">
         <v>35</v>
@@ -54641,7 +54644,7 @@
         <v>163</v>
       </c>
       <c r="C903" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D903" t="s">
         <v>35</v>
@@ -54682,7 +54685,7 @@
         <v>163</v>
       </c>
       <c r="C904" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D904" t="s">
         <v>35</v>
@@ -54723,7 +54726,7 @@
         <v>163</v>
       </c>
       <c r="C905" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D905" t="s">
         <v>35</v>
@@ -54764,10 +54767,10 @@
         <v>168</v>
       </c>
       <c r="C906" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D906" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E906" s="4" t="s">
         <v>441</v>
@@ -54777,7 +54780,7 @@
       </c>
       <c r="G906" s="9"/>
       <c r="H906" s="10">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="I906" s="11"/>
       <c r="J906" s="8"/>
@@ -54797,37 +54800,37 @@
         <v>168</v>
       </c>
       <c r="C907" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D907" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E907" t="s">
         <v>433</v>
       </c>
       <c r="F907" s="12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G907" s="13">
-        <v>5.833</v>
+        <v>5.918</v>
       </c>
       <c r="H907" s="14">
-        <v>0.167</v>
+        <v>0.282</v>
       </c>
       <c r="I907" s="15">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J907" s="12">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="K907" s="16">
-        <v>-6</v>
+        <v>-6.05</v>
       </c>
       <c r="L907" s="15">
-        <v>-50</v>
+        <v>-49.4</v>
       </c>
       <c r="M907" t="s">
-        <v>1710</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.25">
@@ -54838,37 +54841,37 @@
         <v>168</v>
       </c>
       <c r="C908" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D908" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E908" t="s">
         <v>452</v>
       </c>
       <c r="F908" s="12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G908" s="13">
-        <v>3.784</v>
+        <v>3.87</v>
       </c>
       <c r="H908" s="14">
-        <v>0.216</v>
+        <v>0.23</v>
       </c>
       <c r="I908" s="15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J908" s="12">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="K908" s="16">
-        <v>-9.5</v>
+        <v>-10.1</v>
       </c>
       <c r="L908" s="15">
-        <v>-70.4</v>
+        <v>-71.1</v>
       </c>
       <c r="M908" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.25">
@@ -54879,37 +54882,37 @@
         <v>168</v>
       </c>
       <c r="C909" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D909" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E909" t="s">
         <v>423</v>
       </c>
       <c r="F909" s="12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G909" s="13">
-        <v>3.274</v>
+        <v>3.269</v>
       </c>
       <c r="H909" s="14">
-        <v>0.326</v>
+        <v>0.431</v>
       </c>
       <c r="I909" s="15">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="J909" s="12">
-        <v>20.688</v>
+        <v>20.188</v>
       </c>
       <c r="K909" s="16">
-        <v>-17.088</v>
+        <v>-16.488</v>
       </c>
       <c r="L909" s="15">
-        <v>-82.6</v>
+        <v>-81.7</v>
       </c>
       <c r="M909" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="910" spans="1:13" x14ac:dyDescent="0.25">
@@ -54920,10 +54923,10 @@
         <v>168</v>
       </c>
       <c r="C910" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D910" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E910" t="s">
         <v>438</v>
@@ -54932,25 +54935,25 @@
         <v>5</v>
       </c>
       <c r="G910" s="13">
-        <v>4.107</v>
+        <v>4.075</v>
       </c>
       <c r="H910" s="14">
-        <v>0.893</v>
+        <v>0.925</v>
       </c>
       <c r="I910" s="15">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="J910" s="12">
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
       <c r="K910" s="16">
-        <v>-32.5</v>
+        <v>-31.5</v>
       </c>
       <c r="L910" s="15">
-        <v>-86.7</v>
+        <v>-86.3</v>
       </c>
       <c r="M910" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="911" spans="1:13" x14ac:dyDescent="0.25">
@@ -54961,37 +54964,37 @@
         <v>168</v>
       </c>
       <c r="C911" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D911" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E911" t="s">
         <v>430</v>
       </c>
       <c r="F911" s="12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="G911" s="13">
-        <v>6.493</v>
+        <v>6.462</v>
       </c>
       <c r="H911" s="14">
-        <v>1.307</v>
+        <v>1.138</v>
       </c>
       <c r="I911" s="15">
-        <v>20.1</v>
+        <v>17.6</v>
       </c>
       <c r="J911" s="12">
-        <v>91.5</v>
+        <v>89.833</v>
       </c>
       <c r="K911" s="16">
-        <v>-83.7</v>
+        <v>-82.233</v>
       </c>
       <c r="L911" s="15">
         <v>-91.5</v>
       </c>
       <c r="M911" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.25">
@@ -55002,37 +55005,37 @@
         <v>168</v>
       </c>
       <c r="C912" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D912" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E912" t="s">
         <v>522</v>
       </c>
       <c r="F912" s="12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G912" s="13">
-        <v>12.695</v>
-      </c>
-      <c r="H912" s="14">
-        <v>1.305</v>
+        <v>12.263</v>
+      </c>
+      <c r="H912" s="17">
+        <v>-0.263</v>
       </c>
       <c r="I912" s="15">
-        <v>10.3</v>
+        <v>-2.1</v>
       </c>
       <c r="J912" s="12">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K912" s="16">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="L912" s="15">
-        <v>-83.1</v>
+        <v>-85.4</v>
       </c>
       <c r="M912" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.25">
@@ -55043,37 +55046,37 @@
         <v>168</v>
       </c>
       <c r="C913" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D913" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E913" t="s">
         <v>634</v>
       </c>
       <c r="F913" s="12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G913" s="13">
-        <v>15.982</v>
+        <v>15.326</v>
       </c>
       <c r="H913" s="14">
-        <v>4.018</v>
+        <v>2.674</v>
       </c>
       <c r="I913" s="15">
-        <v>25.1</v>
+        <v>17.5</v>
       </c>
       <c r="J913" s="12">
-        <v>126</v>
+        <v>125.4</v>
       </c>
       <c r="K913" s="16">
-        <v>-106</v>
+        <v>-107.4</v>
       </c>
       <c r="L913" s="15">
-        <v>-84.1</v>
+        <v>-85.6</v>
       </c>
       <c r="M913" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="914" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -55147,7 +55150,7 @@
         <v>-41.3</v>
       </c>
       <c r="M915" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.25">
@@ -55188,7 +55191,7 @@
         <v>-65</v>
       </c>
       <c r="M916" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.25">
@@ -55229,7 +55232,7 @@
         <v>-80</v>
       </c>
       <c r="M917" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.25">
@@ -55270,7 +55273,7 @@
         <v>-86.7</v>
       </c>
       <c r="M918" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.25">
@@ -55311,7 +55314,7 @@
         <v>-89.7</v>
       </c>
       <c r="M919" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
@@ -55352,7 +55355,7 @@
         <v>-81.1</v>
       </c>
       <c r="M920" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
@@ -55393,7 +55396,7 @@
         <v>-82.9</v>
       </c>
       <c r="M921" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="922" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -55407,7 +55410,7 @@
         <v>661</v>
       </c>
       <c r="D922" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E922" s="4" t="s">
         <v>441</v>
@@ -55417,7 +55420,7 @@
       </c>
       <c r="G922" s="9"/>
       <c r="H922" s="10">
-        <v>2.771</v>
+        <v>2.249</v>
       </c>
       <c r="I922" s="11"/>
       <c r="J922" s="8"/>
@@ -55440,7 +55443,7 @@
         <v>661</v>
       </c>
       <c r="D923" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E923" t="s">
         <v>433</v>
@@ -55449,25 +55452,25 @@
         <v>10</v>
       </c>
       <c r="G923" s="13">
-        <v>8.627</v>
+        <v>8.932</v>
       </c>
       <c r="H923" s="14">
-        <v>1.373</v>
+        <v>1.068</v>
       </c>
       <c r="I923" s="15">
-        <v>15.9</v>
+        <v>12</v>
       </c>
       <c r="J923" s="12">
-        <v>25.5</v>
+        <v>25.75</v>
       </c>
       <c r="K923" s="16">
-        <v>-15.5</v>
+        <v>-15.75</v>
       </c>
       <c r="L923" s="15">
-        <v>-60.8</v>
+        <v>-61.2</v>
       </c>
       <c r="M923" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
@@ -55481,7 +55484,7 @@
         <v>661</v>
       </c>
       <c r="D924" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E924" t="s">
         <v>452</v>
@@ -55490,25 +55493,25 @@
         <v>5.25</v>
       </c>
       <c r="G924" s="13">
-        <v>4.489</v>
+        <v>4.584</v>
       </c>
       <c r="H924" s="14">
-        <v>0.761</v>
+        <v>0.666</v>
       </c>
       <c r="I924" s="15">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="J924" s="12">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="K924" s="16">
-        <v>-28.25</v>
+        <v>-28.45</v>
       </c>
       <c r="L924" s="15">
-        <v>-84.3</v>
+        <v>-84.4</v>
       </c>
       <c r="M924" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
@@ -55522,7 +55525,7 @@
         <v>661</v>
       </c>
       <c r="D925" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E925" t="s">
         <v>423</v>
@@ -55531,25 +55534,25 @@
         <v>3.75</v>
       </c>
       <c r="G925" s="13">
-        <v>3.372</v>
+        <v>3.387</v>
       </c>
       <c r="H925" s="14">
-        <v>0.378</v>
+        <v>0.363</v>
       </c>
       <c r="I925" s="15">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="J925" s="12">
-        <v>60.688</v>
+        <v>60.938</v>
       </c>
       <c r="K925" s="16">
-        <v>-56.938</v>
+        <v>-57.188</v>
       </c>
       <c r="L925" s="15">
         <v>-93.8</v>
       </c>
       <c r="M925" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
@@ -55563,7 +55566,7 @@
         <v>661</v>
       </c>
       <c r="D926" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E926" t="s">
         <v>438</v>
@@ -55590,7 +55593,7 @@
         <v>-97</v>
       </c>
       <c r="M926" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="927" spans="1:13" x14ac:dyDescent="0.25">
@@ -55604,7 +55607,7 @@
         <v>661</v>
       </c>
       <c r="D927" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E927" t="s">
         <v>430</v>
@@ -55613,25 +55616,25 @@
         <v>6.5</v>
       </c>
       <c r="G927" s="13">
-        <v>5.397</v>
+        <v>5.373</v>
       </c>
       <c r="H927" s="14">
-        <v>1.103</v>
+        <v>1.127</v>
       </c>
       <c r="I927" s="15">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="J927" s="12">
-        <v>222.5</v>
+        <v>205.833</v>
       </c>
       <c r="K927" s="16">
-        <v>-216</v>
+        <v>-199.333</v>
       </c>
       <c r="L927" s="15">
-        <v>-97.1</v>
+        <v>-96.8</v>
       </c>
       <c r="M927" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="928" spans="1:13" x14ac:dyDescent="0.25">
@@ -55645,7 +55648,7 @@
         <v>661</v>
       </c>
       <c r="D928" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E928" t="s">
         <v>522</v>
@@ -55654,25 +55657,25 @@
         <v>9.5</v>
       </c>
       <c r="G928" s="13">
-        <v>10.811</v>
+        <v>10.229</v>
       </c>
       <c r="H928" s="17">
-        <v>-1.311</v>
+        <v>-0.729</v>
       </c>
       <c r="I928" s="15">
-        <v>-12.1</v>
+        <v>-7.1</v>
       </c>
       <c r="J928" s="12">
-        <v>225.8</v>
+        <v>203.4</v>
       </c>
       <c r="K928" s="16">
-        <v>-216.3</v>
+        <v>-193.9</v>
       </c>
       <c r="L928" s="15">
-        <v>-95.8</v>
+        <v>-95.3</v>
       </c>
       <c r="M928" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="929" spans="1:13" x14ac:dyDescent="0.25">
@@ -55686,7 +55689,7 @@
         <v>661</v>
       </c>
       <c r="D929" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E929" t="s">
         <v>634</v>
@@ -55695,25 +55698,25 @@
         <v>10.5</v>
       </c>
       <c r="G929" s="13">
-        <v>7.883</v>
+        <v>7.66</v>
       </c>
       <c r="H929" s="14">
-        <v>2.617</v>
+        <v>2.84</v>
       </c>
       <c r="I929" s="15">
-        <v>33.2</v>
+        <v>37.1</v>
       </c>
       <c r="J929" s="12">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="K929" s="16">
-        <v>-222.5</v>
+        <v>-195.5</v>
       </c>
       <c r="L929" s="15">
-        <v>-95.5</v>
+        <v>-94.9</v>
       </c>
       <c r="M929" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="930" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -55787,7 +55790,7 @@
         <v>-68.2</v>
       </c>
       <c r="M931" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="932" spans="1:13" x14ac:dyDescent="0.25">
@@ -55828,7 +55831,7 @@
         <v>-88.8</v>
       </c>
       <c r="M932" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="933" spans="1:13" x14ac:dyDescent="0.25">
@@ -55869,7 +55872,7 @@
         <v>-96.1</v>
       </c>
       <c r="M933" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="934" spans="1:13" x14ac:dyDescent="0.25">
@@ -55910,7 +55913,7 @@
         <v>-96.9</v>
       </c>
       <c r="M934" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="935" spans="1:13" x14ac:dyDescent="0.25">
@@ -55951,7 +55954,7 @@
         <v>-96.6</v>
       </c>
       <c r="M935" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="936" spans="1:13" x14ac:dyDescent="0.25">
@@ -55992,7 +55995,7 @@
         <v>-95.5</v>
       </c>
       <c r="M936" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="937" spans="1:13" x14ac:dyDescent="0.25">
@@ -56033,7 +56036,7 @@
         <v>-94</v>
       </c>
       <c r="M937" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="938" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -56107,7 +56110,7 @@
         <v>-43.5</v>
       </c>
       <c r="M939" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="940" spans="1:13" x14ac:dyDescent="0.25">
@@ -56148,7 +56151,7 @@
         <v>-72.1</v>
       </c>
       <c r="M940" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="941" spans="1:13" x14ac:dyDescent="0.25">
@@ -56189,7 +56192,7 @@
         <v>-83.1</v>
       </c>
       <c r="M941" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="942" spans="1:13" x14ac:dyDescent="0.25">
@@ -56230,7 +56233,7 @@
         <v>-87</v>
       </c>
       <c r="M942" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="943" spans="1:13" x14ac:dyDescent="0.25">
@@ -56271,7 +56274,7 @@
         <v>-91.5</v>
       </c>
       <c r="M943" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="944" spans="1:13" x14ac:dyDescent="0.25">
@@ -56312,7 +56315,7 @@
         <v>-82.6</v>
       </c>
       <c r="M944" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="945" spans="1:13" x14ac:dyDescent="0.25">
@@ -56353,7 +56356,7 @@
         <v>-81.4</v>
       </c>
       <c r="M945" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="946" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -56427,7 +56430,7 @@
         <v>-62.4</v>
       </c>
       <c r="M947" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.25">
@@ -56468,7 +56471,7 @@
         <v>-89.2</v>
       </c>
       <c r="M948" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.25">
@@ -56509,7 +56512,7 @@
         <v>-95.5</v>
       </c>
       <c r="M949" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.25">
@@ -56550,7 +56553,7 @@
         <v>-97.2</v>
       </c>
       <c r="M950" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.25">
@@ -56591,7 +56594,7 @@
         <v>-97.8</v>
       </c>
       <c r="M951" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.25">
@@ -56632,7 +56635,7 @@
         <v>-97.5</v>
       </c>
       <c r="M952" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="953" spans="1:13" x14ac:dyDescent="0.25">
@@ -56673,7 +56676,7 @@
         <v>-98.1</v>
       </c>
       <c r="M953" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="954" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -56697,7 +56700,7 @@
       </c>
       <c r="G954" s="9"/>
       <c r="H954" s="10">
-        <v>2.458</v>
+        <v>1.786</v>
       </c>
       <c r="I954" s="11"/>
       <c r="J954" s="8"/>
@@ -56729,25 +56732,25 @@
         <v>12</v>
       </c>
       <c r="G955" s="13">
-        <v>10.645</v>
+        <v>11.109</v>
       </c>
       <c r="H955" s="14">
-        <v>1.355</v>
+        <v>0.891</v>
       </c>
       <c r="I955" s="15">
-        <v>12.7</v>
+        <v>8</v>
       </c>
       <c r="J955" s="12">
-        <v>23.25</v>
+        <v>25.25</v>
       </c>
       <c r="K955" s="16">
-        <v>-11.25</v>
+        <v>-13.25</v>
       </c>
       <c r="L955" s="15">
-        <v>-48.4</v>
+        <v>-52.5</v>
       </c>
       <c r="M955" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="956" spans="1:13" x14ac:dyDescent="0.25">
@@ -56770,25 +56773,25 @@
         <v>6</v>
       </c>
       <c r="G956" s="13">
-        <v>5.186</v>
+        <v>5.48</v>
       </c>
       <c r="H956" s="14">
-        <v>0.814</v>
+        <v>0.52</v>
       </c>
       <c r="I956" s="15">
-        <v>15.7</v>
+        <v>9.5</v>
       </c>
       <c r="J956" s="12">
-        <v>21.333</v>
+        <v>23.333</v>
       </c>
       <c r="K956" s="16">
-        <v>-15.333</v>
+        <v>-17.333</v>
       </c>
       <c r="L956" s="15">
-        <v>-71.9</v>
+        <v>-74.3</v>
       </c>
       <c r="M956" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="957" spans="1:13" x14ac:dyDescent="0.25">
@@ -56811,25 +56814,25 @@
         <v>4.1</v>
       </c>
       <c r="G957" s="13">
-        <v>3.756</v>
+        <v>3.864</v>
       </c>
       <c r="H957" s="14">
-        <v>0.344</v>
+        <v>0.236</v>
       </c>
       <c r="I957" s="15">
-        <v>9.2</v>
+        <v>6.1</v>
       </c>
       <c r="J957" s="12">
-        <v>27.5</v>
+        <v>30.25</v>
       </c>
       <c r="K957" s="16">
-        <v>-23.4</v>
+        <v>-26.15</v>
       </c>
       <c r="L957" s="15">
-        <v>-85.1</v>
+        <v>-86.4</v>
       </c>
       <c r="M957" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="958" spans="1:13" x14ac:dyDescent="0.25">
@@ -56852,25 +56855,25 @@
         <v>4.1</v>
       </c>
       <c r="G958" s="13">
-        <v>3.822</v>
+        <v>3.765</v>
       </c>
       <c r="H958" s="14">
-        <v>0.278</v>
+        <v>0.335</v>
       </c>
       <c r="I958" s="15">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J958" s="12">
-        <v>45.4</v>
+        <v>55.8</v>
       </c>
       <c r="K958" s="16">
-        <v>-41.3</v>
+        <v>-51.7</v>
       </c>
       <c r="L958" s="15">
-        <v>-91</v>
+        <v>-92.6</v>
       </c>
       <c r="M958" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="959" spans="1:13" x14ac:dyDescent="0.25">
@@ -56893,25 +56896,25 @@
         <v>5.5</v>
       </c>
       <c r="G959" s="13">
-        <v>4.732</v>
+        <v>4.546</v>
       </c>
       <c r="H959" s="14">
-        <v>0.768</v>
+        <v>0.954</v>
       </c>
       <c r="I959" s="15">
-        <v>16.2</v>
+        <v>21</v>
       </c>
       <c r="J959" s="12">
-        <v>79.833</v>
+        <v>79.583</v>
       </c>
       <c r="K959" s="16">
-        <v>-74.333</v>
+        <v>-74.083</v>
       </c>
       <c r="L959" s="15">
         <v>-93.1</v>
       </c>
       <c r="M959" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="960" spans="1:13" x14ac:dyDescent="0.25">
@@ -56934,25 +56937,25 @@
         <v>7.75</v>
       </c>
       <c r="G960" s="13">
-        <v>7.37</v>
+        <v>7.181</v>
       </c>
       <c r="H960" s="14">
-        <v>0.38</v>
+        <v>0.569</v>
       </c>
       <c r="I960" s="15">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="J960" s="12">
-        <v>68.4</v>
+        <v>68.6</v>
       </c>
       <c r="K960" s="16">
-        <v>-60.65</v>
+        <v>-60.85</v>
       </c>
       <c r="L960" s="15">
         <v>-88.7</v>
       </c>
       <c r="M960" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="961" spans="1:13" x14ac:dyDescent="0.25">
@@ -56975,25 +56978,25 @@
         <v>7.9</v>
       </c>
       <c r="G961" s="13">
-        <v>6.744</v>
+        <v>6.465</v>
       </c>
       <c r="H961" s="14">
-        <v>1.156</v>
+        <v>1.435</v>
       </c>
       <c r="I961" s="15">
-        <v>17.1</v>
+        <v>22.2</v>
       </c>
       <c r="J961" s="12">
-        <v>65.6</v>
+        <v>65.4</v>
       </c>
       <c r="K961" s="16">
-        <v>-57.7</v>
+        <v>-57.5</v>
       </c>
       <c r="L961" s="15">
-        <v>-88</v>
+        <v>-87.9</v>
       </c>
       <c r="M961" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="962" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -57004,7 +57007,7 @@
         <v>408</v>
       </c>
       <c r="C962" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D962" s="4" t="s">
         <v>670</v>
@@ -57017,7 +57020,7 @@
       </c>
       <c r="G962" s="9"/>
       <c r="H962" s="10">
-        <v>3.054</v>
+        <v>2.429</v>
       </c>
       <c r="I962" s="11"/>
       <c r="J962" s="8"/>
@@ -57026,7 +57029,7 @@
       </c>
       <c r="L962" s="11"/>
       <c r="M962" s="4" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="963" spans="1:13" x14ac:dyDescent="0.25">
@@ -57037,7 +57040,7 @@
         <v>408</v>
       </c>
       <c r="C963" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D963" t="s">
         <v>670</v>
@@ -57049,25 +57052,25 @@
         <v>15</v>
       </c>
       <c r="G963" s="13">
-        <v>13.235</v>
+        <v>13.768</v>
       </c>
       <c r="H963" s="14">
-        <v>1.765</v>
+        <v>1.232</v>
       </c>
       <c r="I963" s="15">
-        <v>13.3</v>
+        <v>9</v>
       </c>
       <c r="J963" s="12">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="K963" s="16">
-        <v>-19</v>
+        <v>-19.5</v>
       </c>
       <c r="L963" s="15">
-        <v>-55.9</v>
+        <v>-56.5</v>
       </c>
       <c r="M963" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="964" spans="1:13" x14ac:dyDescent="0.25">
@@ -57078,7 +57081,7 @@
         <v>408</v>
       </c>
       <c r="C964" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D964" t="s">
         <v>670</v>
@@ -57087,28 +57090,28 @@
         <v>452</v>
       </c>
       <c r="F964" s="12">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="G964" s="13">
-        <v>6.154</v>
+        <v>6.182</v>
       </c>
       <c r="H964" s="14">
-        <v>0.846</v>
+        <v>1.118</v>
       </c>
       <c r="I964" s="15">
-        <v>13.8</v>
+        <v>18.1</v>
       </c>
       <c r="J964" s="12">
-        <v>35.667</v>
+        <v>37.333</v>
       </c>
       <c r="K964" s="16">
-        <v>-28.667</v>
+        <v>-30.033</v>
       </c>
       <c r="L964" s="15">
         <v>-80.4</v>
       </c>
       <c r="M964" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.25">
@@ -57119,7 +57122,7 @@
         <v>408</v>
       </c>
       <c r="C965" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D965" t="s">
         <v>670</v>
@@ -57128,28 +57131,28 @@
         <v>423</v>
       </c>
       <c r="F965" s="12">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G965" s="13">
-        <v>4.251</v>
+        <v>4.169</v>
       </c>
       <c r="H965" s="14">
-        <v>0.349</v>
+        <v>0.131</v>
       </c>
       <c r="I965" s="15">
-        <v>8.2</v>
+        <v>3.1</v>
       </c>
       <c r="J965" s="12">
-        <v>49.125</v>
+        <v>49.375</v>
       </c>
       <c r="K965" s="16">
-        <v>-44.525</v>
+        <v>-45.075</v>
       </c>
       <c r="L965" s="15">
-        <v>-90.6</v>
+        <v>-91.3</v>
       </c>
       <c r="M965" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.25">
@@ -57160,7 +57163,7 @@
         <v>408</v>
       </c>
       <c r="C966" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D966" t="s">
         <v>670</v>
@@ -57169,28 +57172,28 @@
         <v>438</v>
       </c>
       <c r="F966" s="12">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G966" s="13">
-        <v>3.854</v>
+        <v>3.809</v>
       </c>
       <c r="H966" s="14">
-        <v>0.446</v>
+        <v>0.291</v>
       </c>
       <c r="I966" s="15">
-        <v>11.6</v>
+        <v>7.6</v>
       </c>
       <c r="J966" s="12">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K966" s="16">
-        <v>-95.7</v>
+        <v>-96.9</v>
       </c>
       <c r="L966" s="15">
-        <v>-95.7</v>
+        <v>-95.9</v>
       </c>
       <c r="M966" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.25">
@@ -57201,7 +57204,7 @@
         <v>408</v>
       </c>
       <c r="C967" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D967" t="s">
         <v>670</v>
@@ -57210,28 +57213,28 @@
         <v>430</v>
       </c>
       <c r="F967" s="12">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G967" s="13">
-        <v>4.294</v>
+        <v>4.382</v>
       </c>
       <c r="H967" s="14">
-        <v>0.706</v>
+        <v>0.818</v>
       </c>
       <c r="I967" s="15">
-        <v>16.4</v>
+        <v>18.7</v>
       </c>
       <c r="J967" s="12">
-        <v>138.167</v>
+        <v>139.167</v>
       </c>
       <c r="K967" s="16">
-        <v>-133.167</v>
+        <v>-133.967</v>
       </c>
       <c r="L967" s="15">
-        <v>-96.4</v>
+        <v>-96.3</v>
       </c>
       <c r="M967" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.25">
@@ -57242,7 +57245,7 @@
         <v>408</v>
       </c>
       <c r="C968" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D968" t="s">
         <v>670</v>
@@ -57251,28 +57254,28 @@
         <v>522</v>
       </c>
       <c r="F968" s="12">
-        <v>6.95</v>
+        <v>7.2</v>
       </c>
       <c r="G968" s="13">
-        <v>7.089</v>
-      </c>
-      <c r="H968" s="17">
-        <v>-0.139</v>
+        <v>6.959</v>
+      </c>
+      <c r="H968" s="14">
+        <v>0.241</v>
       </c>
       <c r="I968" s="15">
-        <v>-2</v>
+        <v>3.5</v>
       </c>
       <c r="J968" s="12">
-        <v>115</v>
+        <v>114.8</v>
       </c>
       <c r="K968" s="16">
-        <v>-108.05</v>
+        <v>-107.6</v>
       </c>
       <c r="L968" s="15">
-        <v>-94</v>
+        <v>-93.7</v>
       </c>
       <c r="M968" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.25">
@@ -57283,7 +57286,7 @@
         <v>408</v>
       </c>
       <c r="C969" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D969" t="s">
         <v>670</v>
@@ -57292,28 +57295,28 @@
         <v>634</v>
       </c>
       <c r="F969" s="12">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G969" s="13">
-        <v>4.676</v>
+        <v>4.695</v>
       </c>
       <c r="H969" s="14">
-        <v>0.824</v>
+        <v>1.005</v>
       </c>
       <c r="I969" s="15">
-        <v>17.6</v>
+        <v>21.4</v>
       </c>
       <c r="J969" s="12">
-        <v>102.3</v>
+        <v>103.3</v>
       </c>
       <c r="K969" s="16">
-        <v>-96.8</v>
+        <v>-97.6</v>
       </c>
       <c r="L969" s="15">
-        <v>-94.6</v>
+        <v>-94.5</v>
       </c>
       <c r="M969" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="970" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -57387,7 +57390,7 @@
         <v>-50.8</v>
       </c>
       <c r="M971" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.25">
@@ -57428,7 +57431,7 @@
         <v>-71.2</v>
       </c>
       <c r="M972" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="973" spans="1:13" x14ac:dyDescent="0.25">
@@ -57469,7 +57472,7 @@
         <v>-85.1</v>
       </c>
       <c r="M973" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="974" spans="1:13" x14ac:dyDescent="0.25">
@@ -57510,7 +57513,7 @@
         <v>-88.9</v>
       </c>
       <c r="M974" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="975" spans="1:13" x14ac:dyDescent="0.25">
@@ -57551,7 +57554,7 @@
         <v>-92.2</v>
       </c>
       <c r="M975" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="976" spans="1:13" x14ac:dyDescent="0.25">
@@ -57592,7 +57595,7 @@
         <v>-83</v>
       </c>
       <c r="M976" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="977" spans="1:13" x14ac:dyDescent="0.25">
@@ -57633,7 +57636,7 @@
         <v>-84.5</v>
       </c>
       <c r="M977" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="978" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -57657,7 +57660,7 @@
       </c>
       <c r="G978" s="9"/>
       <c r="H978" s="10">
-        <v>1.064</v>
+        <v>1.444</v>
       </c>
       <c r="I978" s="11"/>
       <c r="J978" s="8"/>
@@ -57707,7 +57710,7 @@
         <v>-48.7</v>
       </c>
       <c r="M979" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="980" spans="1:13" x14ac:dyDescent="0.25">
@@ -57727,28 +57730,28 @@
         <v>452</v>
       </c>
       <c r="F980" s="12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G980" s="13">
         <v>3.468</v>
       </c>
       <c r="H980" s="14">
-        <v>0.132</v>
+        <v>0.032</v>
       </c>
       <c r="I980" s="15">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J980" s="12">
         <v>13</v>
       </c>
       <c r="K980" s="16">
-        <v>-9.4</v>
+        <v>-9.5</v>
       </c>
       <c r="L980" s="15">
-        <v>-72.3</v>
+        <v>-73.1</v>
       </c>
       <c r="M980" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="981" spans="1:13" x14ac:dyDescent="0.25">
@@ -57768,28 +57771,28 @@
         <v>423</v>
       </c>
       <c r="F981" s="12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G981" s="13">
         <v>3.205</v>
       </c>
       <c r="H981" s="14">
-        <v>0.295</v>
+        <v>0.195</v>
       </c>
       <c r="I981" s="15">
-        <v>9.2</v>
+        <v>6.1</v>
       </c>
       <c r="J981" s="12">
         <v>21.188</v>
       </c>
       <c r="K981" s="16">
-        <v>-17.688</v>
+        <v>-17.788</v>
       </c>
       <c r="L981" s="15">
-        <v>-83.5</v>
+        <v>-83.9</v>
       </c>
       <c r="M981" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="982" spans="1:13" x14ac:dyDescent="0.25">
@@ -57830,7 +57833,7 @@
         <v>-89.4</v>
       </c>
       <c r="M982" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="983" spans="1:13" x14ac:dyDescent="0.25">
@@ -57850,28 +57853,28 @@
         <v>430</v>
       </c>
       <c r="F983" s="12">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G983" s="13">
         <v>7.278</v>
       </c>
       <c r="H983" s="14">
-        <v>1.722</v>
+        <v>2.222</v>
       </c>
       <c r="I983" s="15">
-        <v>23.7</v>
+        <v>30.5</v>
       </c>
       <c r="J983" s="12">
         <v>128.5</v>
       </c>
       <c r="K983" s="16">
-        <v>-119.5</v>
+        <v>-119</v>
       </c>
       <c r="L983" s="15">
-        <v>-93</v>
+        <v>-92.6</v>
       </c>
       <c r="M983" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="984" spans="1:13" x14ac:dyDescent="0.25">
@@ -57891,28 +57894,28 @@
         <v>522</v>
       </c>
       <c r="F984" s="12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G984" s="13">
         <v>14.797</v>
       </c>
       <c r="H984" s="14">
-        <v>2.203</v>
+        <v>4.203</v>
       </c>
       <c r="I984" s="15">
-        <v>14.9</v>
+        <v>28.4</v>
       </c>
       <c r="J984" s="12">
         <v>125</v>
       </c>
       <c r="K984" s="16">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="L984" s="15">
-        <v>-86.4</v>
+        <v>-84.8</v>
       </c>
       <c r="M984" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="985" spans="1:13" x14ac:dyDescent="0.25">
@@ -57932,33 +57935,33 @@
         <v>634</v>
       </c>
       <c r="F985" s="12">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G985" s="13">
         <v>20.192</v>
       </c>
       <c r="H985" s="14">
-        <v>5.808</v>
+        <v>8.808</v>
       </c>
       <c r="I985" s="15">
-        <v>28.8</v>
+        <v>43.6</v>
       </c>
       <c r="J985" s="12">
         <v>168</v>
       </c>
       <c r="K985" s="16">
-        <v>-142</v>
+        <v>-139</v>
       </c>
       <c r="L985" s="15">
-        <v>-84.5</v>
+        <v>-82.7</v>
       </c>
       <c r="M985" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="986" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A986" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B986" s="4" t="s">
         <v>179</v>
@@ -57967,7 +57970,7 @@
         <v>31</v>
       </c>
       <c r="D986" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E986" s="4" t="s">
         <v>441</v>
@@ -57991,7 +57994,7 @@
     </row>
     <row r="987" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B987" t="s">
         <v>179</v>
@@ -58000,7 +58003,7 @@
         <v>31</v>
       </c>
       <c r="D987" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E987" t="s">
         <v>433</v>
@@ -58032,7 +58035,7 @@
     </row>
     <row r="988" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B988" t="s">
         <v>179</v>
@@ -58041,7 +58044,7 @@
         <v>31</v>
       </c>
       <c r="D988" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E988" t="s">
         <v>452</v>
@@ -58068,12 +58071,12 @@
         <v>-77.3</v>
       </c>
       <c r="M988" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="989" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B989" t="s">
         <v>179</v>
@@ -58082,7 +58085,7 @@
         <v>31</v>
       </c>
       <c r="D989" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E989" t="s">
         <v>423</v>
@@ -58109,12 +58112,12 @@
         <v>-89.2</v>
       </c>
       <c r="M989" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="990" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B990" t="s">
         <v>179</v>
@@ -58123,7 +58126,7 @@
         <v>31</v>
       </c>
       <c r="D990" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E990" t="s">
         <v>438</v>
@@ -58150,12 +58153,12 @@
         <v>-93</v>
       </c>
       <c r="M990" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="991" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B991" t="s">
         <v>179</v>
@@ -58164,7 +58167,7 @@
         <v>31</v>
       </c>
       <c r="D991" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E991" t="s">
         <v>430</v>
@@ -58191,12 +58194,12 @@
         <v>-94.9</v>
       </c>
       <c r="M991" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="992" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B992" t="s">
         <v>179</v>
@@ -58205,7 +58208,7 @@
         <v>31</v>
       </c>
       <c r="D992" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E992" t="s">
         <v>522</v>
@@ -58232,12 +58235,12 @@
         <v>-88.9</v>
       </c>
       <c r="M992" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="993" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B993" t="s">
         <v>179</v>
@@ -58246,7 +58249,7 @@
         <v>31</v>
       </c>
       <c r="D993" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E993" t="s">
         <v>634</v>
@@ -58273,12 +58276,12 @@
         <v>-90.1</v>
       </c>
       <c r="M993" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="994" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A994" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B994" s="4" t="s">
         <v>183</v>
@@ -58287,7 +58290,7 @@
         <v>26</v>
       </c>
       <c r="D994" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E994" s="4" t="s">
         <v>441</v>
@@ -58311,7 +58314,7 @@
     </row>
     <row r="995" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B995" t="s">
         <v>183</v>
@@ -58320,7 +58323,7 @@
         <v>26</v>
       </c>
       <c r="D995" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E995" t="s">
         <v>433</v>
@@ -58347,12 +58350,12 @@
         <v>-62.6</v>
       </c>
       <c r="M995" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="996" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B996" t="s">
         <v>183</v>
@@ -58361,7 +58364,7 @@
         <v>26</v>
       </c>
       <c r="D996" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E996" t="s">
         <v>452</v>
@@ -58388,12 +58391,12 @@
         <v>-84.8</v>
       </c>
       <c r="M996" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="997" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B997" t="s">
         <v>183</v>
@@ -58402,7 +58405,7 @@
         <v>26</v>
       </c>
       <c r="D997" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E997" t="s">
         <v>423</v>
@@ -58429,12 +58432,12 @@
         <v>-95</v>
       </c>
       <c r="M997" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="998" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B998" t="s">
         <v>183</v>
@@ -58443,7 +58446,7 @@
         <v>26</v>
       </c>
       <c r="D998" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E998" t="s">
         <v>438</v>
@@ -58470,12 +58473,12 @@
         <v>-97.1</v>
       </c>
       <c r="M998" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="999" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B999" t="s">
         <v>183</v>
@@ -58484,7 +58487,7 @@
         <v>26</v>
       </c>
       <c r="D999" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E999" t="s">
         <v>430</v>
@@ -58511,12 +58514,12 @@
         <v>-97.3</v>
       </c>
       <c r="M999" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1000" t="s">
         <v>183</v>
@@ -58525,7 +58528,7 @@
         <v>26</v>
       </c>
       <c r="D1000" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E1000" t="s">
         <v>522</v>
@@ -58552,12 +58555,12 @@
         <v>-96.3</v>
       </c>
       <c r="M1000" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1001" t="s">
         <v>183</v>
@@ -58566,7 +58569,7 @@
         <v>26</v>
       </c>
       <c r="D1001" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E1001" t="s">
         <v>634</v>
@@ -58593,12 +58596,12 @@
         <v>-96.3</v>
       </c>
       <c r="M1001" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1002" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1002" s="4" t="s">
         <v>501</v>
@@ -58631,7 +58634,7 @@
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1003" t="s">
         <v>501</v>
@@ -58667,12 +58670,12 @@
         <v>-45.4</v>
       </c>
       <c r="M1003" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1004" t="s">
         <v>501</v>
@@ -58708,12 +58711,12 @@
         <v>-69.1</v>
       </c>
       <c r="M1004" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1005" t="s">
         <v>501</v>
@@ -58749,12 +58752,12 @@
         <v>-80.5</v>
       </c>
       <c r="M1005" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1006" t="s">
         <v>501</v>
@@ -58790,12 +58793,12 @@
         <v>-86.7</v>
       </c>
       <c r="M1006" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1007" t="s">
         <v>501</v>
@@ -58831,12 +58834,12 @@
         <v>-92.3</v>
       </c>
       <c r="M1007" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1008" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1008" t="s">
         <v>501</v>
@@ -58872,12 +58875,12 @@
         <v>-84.7</v>
       </c>
       <c r="M1008" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1009" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1009" t="s">
         <v>501</v>
@@ -58913,12 +58916,12 @@
         <v>-88.4</v>
       </c>
       <c r="M1009" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1010" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1010" s="4" t="s">
         <v>505</v>
@@ -58951,7 +58954,7 @@
     </row>
     <row r="1011" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1011" t="s">
         <v>505</v>
@@ -58987,12 +58990,12 @@
         <v>-47.5</v>
       </c>
       <c r="M1011" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1012" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1012" t="s">
         <v>505</v>
@@ -59028,12 +59031,12 @@
         <v>-69.3</v>
       </c>
       <c r="M1012" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1013" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1013" t="s">
         <v>505</v>
@@ -59069,12 +59072,12 @@
         <v>-83.7</v>
       </c>
       <c r="M1013" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1014" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1014" t="s">
         <v>505</v>
@@ -59110,12 +59113,12 @@
         <v>-88.8</v>
       </c>
       <c r="M1014" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1015" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1015" t="s">
         <v>505</v>
@@ -59151,12 +59154,12 @@
         <v>-92.2</v>
       </c>
       <c r="M1015" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1016" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1016" t="s">
         <v>505</v>
@@ -59192,12 +59195,12 @@
         <v>-87.1</v>
       </c>
       <c r="M1016" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1017" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1017" t="s">
         <v>505</v>
@@ -59233,12 +59236,12 @@
         <v>-87</v>
       </c>
       <c r="M1017" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1018" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1018" s="4" t="s">
         <v>512</v>
@@ -59266,12 +59269,12 @@
       </c>
       <c r="L1018" s="11"/>
       <c r="M1018" s="4" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1019" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1019" t="s">
         <v>512</v>
@@ -59307,12 +59310,12 @@
         <v>-57.7</v>
       </c>
       <c r="M1019" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1020" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1020" t="s">
         <v>512</v>
@@ -59348,12 +59351,12 @@
         <v>-82.7</v>
       </c>
       <c r="M1020" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1021" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1021" t="s">
         <v>512</v>
@@ -59389,12 +59392,12 @@
         <v>-93.7</v>
       </c>
       <c r="M1021" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1022" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1022" t="s">
         <v>512</v>
@@ -59430,12 +59433,12 @@
         <v>-96.3</v>
       </c>
       <c r="M1022" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1023" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1023" t="s">
         <v>512</v>
@@ -59471,12 +59474,12 @@
         <v>-97.2</v>
       </c>
       <c r="M1023" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1024" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1024" t="s">
         <v>512</v>
@@ -59512,12 +59515,12 @@
         <v>-95.3</v>
       </c>
       <c r="M1024" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1025" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1025" t="s">
         <v>512</v>
@@ -59553,12 +59556,12 @@
         <v>-95.7</v>
       </c>
       <c r="M1025" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1026" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1026" s="4" t="s">
         <v>858</v>
@@ -59586,12 +59589,12 @@
       </c>
       <c r="L1026" s="11"/>
       <c r="M1026" s="4" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1027" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1027" t="s">
         <v>858</v>
@@ -59627,12 +59630,12 @@
         <v>-46.9</v>
       </c>
       <c r="M1027" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1028" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1028" t="s">
         <v>858</v>
@@ -59668,12 +59671,12 @@
         <v>-70</v>
       </c>
       <c r="M1028" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1029" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1029" t="s">
         <v>858</v>
@@ -59709,12 +59712,12 @@
         <v>-82.8</v>
       </c>
       <c r="M1029" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1030" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1030" t="s">
         <v>858</v>
@@ -59750,12 +59753,12 @@
         <v>-90.3</v>
       </c>
       <c r="M1030" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1031" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1031" t="s">
         <v>858</v>
@@ -59791,12 +59794,12 @@
         <v>-93.8</v>
       </c>
       <c r="M1031" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1032" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1032" t="s">
         <v>858</v>
@@ -59832,12 +59835,12 @@
         <v>-87.1</v>
       </c>
       <c r="M1032" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1033" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1033" t="s">
         <v>858</v>
@@ -59873,12 +59876,12 @@
         <v>-88</v>
       </c>
       <c r="M1033" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1034" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1034" s="4" t="s">
         <v>860</v>
@@ -59911,7 +59914,7 @@
     </row>
     <row r="1035" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1035" t="s">
         <v>860</v>
@@ -59947,12 +59950,12 @@
         <v>-47.1</v>
       </c>
       <c r="M1035" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1036" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1036" t="s">
         <v>860</v>
@@ -59988,12 +59991,12 @@
         <v>-68.1</v>
       </c>
       <c r="M1036" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1037" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1037" t="s">
         <v>860</v>
@@ -60029,12 +60032,12 @@
         <v>-83.1</v>
       </c>
       <c r="M1037" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1038" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1038" t="s">
         <v>860</v>
@@ -60070,12 +60073,12 @@
         <v>-89.2</v>
       </c>
       <c r="M1038" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1039" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1039" t="s">
         <v>860</v>
@@ -60111,12 +60114,12 @@
         <v>-92.9</v>
       </c>
       <c r="M1039" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1040" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1040" t="s">
         <v>860</v>
@@ -60152,12 +60155,12 @@
         <v>-87.6</v>
       </c>
       <c r="M1040" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1041" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1041" t="s">
         <v>860</v>
@@ -60193,12 +60196,12 @@
         <v>-86.6</v>
       </c>
       <c r="M1041" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1042" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1042" s="4" t="s">
         <v>863</v>
@@ -60231,7 +60234,7 @@
     </row>
     <row r="1043" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1043" t="s">
         <v>863</v>
@@ -60267,12 +60270,12 @@
         <v>-45.4</v>
       </c>
       <c r="M1043" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1044" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1044" t="s">
         <v>863</v>
@@ -60308,12 +60311,12 @@
         <v>-69.2</v>
       </c>
       <c r="M1044" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1045" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1045" t="s">
         <v>863</v>
@@ -60349,12 +60352,12 @@
         <v>-83.7</v>
       </c>
       <c r="M1045" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1046" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1046" t="s">
         <v>863</v>
@@ -60390,12 +60393,12 @@
         <v>-89.6</v>
       </c>
       <c r="M1046" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1047" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1047" t="s">
         <v>863</v>
@@ -60431,12 +60434,12 @@
         <v>-93.2</v>
       </c>
       <c r="M1047" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1048" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1048" t="s">
         <v>863</v>
@@ -60472,12 +60475,12 @@
         <v>-88.6</v>
       </c>
       <c r="M1048" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1049" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1049" t="s">
         <v>863</v>
@@ -60513,12 +60516,12 @@
         <v>-88.3</v>
       </c>
       <c r="M1049" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1050" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1050" s="4" t="s">
         <v>865</v>
@@ -60551,7 +60554,7 @@
     </row>
     <row r="1051" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1051" t="s">
         <v>865</v>
@@ -60587,12 +60590,12 @@
         <v>-42.9</v>
       </c>
       <c r="M1051" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1052" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1052" t="s">
         <v>865</v>
@@ -60628,12 +60631,12 @@
         <v>-67.7</v>
       </c>
       <c r="M1052" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1053" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1053" t="s">
         <v>865</v>
@@ -60669,12 +60672,12 @@
         <v>-80.4</v>
       </c>
       <c r="M1053" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1054" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1054" t="s">
         <v>865</v>
@@ -60710,12 +60713,12 @@
         <v>-86.7</v>
       </c>
       <c r="M1054" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1055" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1055" t="s">
         <v>865</v>
@@ -60751,12 +60754,12 @@
         <v>-91.3</v>
       </c>
       <c r="M1055" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1056" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1056" t="s">
         <v>865</v>
@@ -60792,12 +60795,12 @@
         <v>-85</v>
       </c>
       <c r="M1056" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1057" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1057" t="s">
         <v>865</v>
@@ -60833,12 +60836,12 @@
         <v>-85.4</v>
       </c>
       <c r="M1057" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1058" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1058" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1058" s="4" t="s">
         <v>866</v>
@@ -60871,7 +60874,7 @@
     </row>
     <row r="1059" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1059" t="s">
         <v>866</v>
@@ -60907,12 +60910,12 @@
         <v>-52.3</v>
       </c>
       <c r="M1059" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1060" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1060" t="s">
         <v>866</v>
@@ -60948,12 +60951,12 @@
         <v>-74</v>
       </c>
       <c r="M1060" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1061" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1061" t="s">
         <v>866</v>
@@ -60994,7 +60997,7 @@
     </row>
     <row r="1062" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1062" t="s">
         <v>866</v>
@@ -61030,12 +61033,12 @@
         <v>-92.7</v>
       </c>
       <c r="M1062" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1063" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1063" t="s">
         <v>866</v>
@@ -61071,12 +61074,12 @@
         <v>-94.8</v>
       </c>
       <c r="M1063" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1064" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1064" t="s">
         <v>866</v>
@@ -61112,12 +61115,12 @@
         <v>-91.1</v>
       </c>
       <c r="M1064" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1065" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1065" t="s">
         <v>866</v>
@@ -61153,12 +61156,12 @@
         <v>-89.7</v>
       </c>
       <c r="M1065" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1066" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1066" s="4" t="s">
         <v>868</v>
@@ -61186,12 +61189,12 @@
       </c>
       <c r="L1066" s="11"/>
       <c r="M1066" s="4" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1067" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1067" t="s">
         <v>868</v>
@@ -61227,12 +61230,12 @@
         <v>-48.5</v>
       </c>
       <c r="M1067" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1068" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1068" t="s">
         <v>868</v>
@@ -61268,12 +61271,12 @@
         <v>-68.3</v>
       </c>
       <c r="M1068" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1069" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1069" t="s">
         <v>868</v>
@@ -61309,12 +61312,12 @@
         <v>-79.5</v>
       </c>
       <c r="M1069" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1070" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1070" t="s">
         <v>868</v>
@@ -61350,12 +61353,12 @@
         <v>-84.6</v>
       </c>
       <c r="M1070" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1071" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1071" t="s">
         <v>868</v>
@@ -61391,12 +61394,12 @@
         <v>-88</v>
       </c>
       <c r="M1071" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1072" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1072" t="s">
         <v>868</v>
@@ -61432,12 +61435,12 @@
         <v>-83.8</v>
       </c>
       <c r="M1072" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1073" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1073" t="s">
         <v>868</v>
@@ -61473,7 +61476,7 @@
         <v>-86.8</v>
       </c>
       <c r="M1073" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
   </sheetData>
@@ -61494,162 +61497,162 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B4">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B5">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B6" t="s">
         <v>1862</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B7" t="s">
         <v>1864</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1865</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B8" t="s">
         <v>1866</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B12" t="s">
         <v>1870</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B13" t="s">
         <v>1872</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B17">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B18" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B19" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B20" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>1881</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>1883</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>1884</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>1885</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>1886</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>1887</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>1888</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>1889</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>1890</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -61663,22 +61666,22 @@
         <v>21</v>
       </c>
       <c r="D25" s="21" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E25" s="21" t="s">
         <v>1892</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="F25" s="21" t="s">
         <v>1893</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="G25" s="21" t="s">
         <v>1894</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="H25" s="21" t="s">
         <v>1895</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="I25" s="21" t="s">
         <v>1896</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -61686,25 +61689,25 @@
         <v>433</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>1898</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="D26" s="21" t="s">
         <v>1899</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="E26" s="21" t="s">
         <v>1900</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="F26" s="21" t="s">
         <v>1901</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="G26" s="21" t="s">
         <v>1902</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="H26" s="21" t="s">
         <v>1903</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>1904</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -61715,22 +61718,22 @@
         <v>452</v>
       </c>
       <c r="B27" s="21" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>1905</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="E27" s="21" t="s">
         <v>1906</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="F27" s="21" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G27" s="21" t="s">
         <v>1907</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>1908</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>1902</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>1909</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -61744,22 +61747,22 @@
         <v>423</v>
       </c>
       <c r="B28" s="21" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>1910</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>1911</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="F28" s="22" t="s">
         <v>1912</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="G28" s="21" t="s">
         <v>1913</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>1914</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>1915</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -61773,25 +61776,25 @@
         <v>438</v>
       </c>
       <c r="B29" s="21" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>1916</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="E29" s="21" t="s">
         <v>1917</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="F29" s="21" t="s">
         <v>1918</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="G29" s="21" t="s">
         <v>1919</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="H29" s="21" t="s">
         <v>1920</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>1921</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>1922</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -61805,25 +61808,25 @@
         <v>21</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="D30" s="21" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G30" s="21" t="s">
         <v>1923</v>
       </c>
-      <c r="E30" s="21" t="s">
-        <v>1922</v>
-      </c>
-      <c r="F30" s="21" t="s">
+      <c r="H30" s="21" t="s">
         <v>1924</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="I30" s="21" t="s">
         <v>1925</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>1926</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -61831,28 +61834,28 @@
         <v>522</v>
       </c>
       <c r="B31" s="21" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>1927</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="D31" s="21" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E31" s="21" t="s">
         <v>1928</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>1922</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>1923</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>1929</v>
       </c>
       <c r="G31" s="21" t="s">
+        <v>1902</v>
+      </c>
+      <c r="H31" s="21" t="s">
         <v>1930</v>
       </c>
-      <c r="H31" s="21" t="s">
-        <v>1931</v>
-      </c>
       <c r="I31" s="21" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -61860,25 +61863,25 @@
         <v>634</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>1924</v>
+        <v>1931</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>1932</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="I32" s="21" t="s">
         <v>1933</v>
@@ -61897,7 +61900,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L133"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -61947,22 +61950,22 @@
         <v>1944</v>
       </c>
       <c r="B5">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="E5">
         <v>8375</v>
       </c>
       <c r="F5" s="23">
-        <v>-2625</v>
+        <v>-2725</v>
       </c>
       <c r="G5" s="24">
-        <v>-0.23863636363636365</v>
+        <v>-0.24549549549549549</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -61970,22 +61973,22 @@
         <v>1945</v>
       </c>
       <c r="B6">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="E6">
         <v>6265</v>
       </c>
       <c r="F6" s="23">
-        <v>-4735</v>
+        <v>-4835</v>
       </c>
       <c r="G6" s="24">
-        <v>-0.4304545454545455</v>
+        <v>-0.4355855855855856</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -61993,22 +61996,22 @@
         <v>1946</v>
       </c>
       <c r="B7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <v>27</v>
       </c>
       <c r="D7">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="E7">
         <v>11645</v>
       </c>
       <c r="F7" s="7">
-        <v>645</v>
+        <v>545</v>
       </c>
       <c r="G7" s="24">
-        <v>0.05863636363636364</v>
+        <v>0.0490990990990991</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
@@ -66234,106 +66237,121 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="122" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="19" t="s">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>811</v>
+      </c>
+      <c r="B121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C121" t="s">
+        <v>776</v>
+      </c>
+      <c r="D121" t="s">
+        <v>812</v>
+      </c>
+      <c r="E121" t="s">
+        <v>30</v>
+      </c>
+      <c r="F121" t="s">
+        <v>522</v>
+      </c>
+      <c r="G121" s="12">
+        <v>9.25</v>
+      </c>
+      <c r="H121" t="s">
+        <v>438</v>
+      </c>
+      <c r="I121" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J121" s="26">
+        <v>-2725</v>
+      </c>
+      <c r="K121" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L121" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="19" t="s">
         <v>1954</v>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
+    <row r="124" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B124" s="2" t="s">
         <v>1955</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>1956</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="E124" s="2" t="s">
         <v>1957</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>1958</v>
       </c>
-      <c r="G123" s="2" t="s">
+      <c r="G124" s="2" t="s">
         <v>1959</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>421</v>
-      </c>
-      <c r="B124">
-        <v>7</v>
-      </c>
-      <c r="C124">
-        <v>1</v>
-      </c>
-      <c r="D124" s="27">
-        <v>50</v>
-      </c>
-      <c r="E124" s="27">
-        <v>50</v>
-      </c>
-      <c r="F124" s="27">
-        <v>-280</v>
-      </c>
-      <c r="G124" s="27">
-        <v>520</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="B125">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" s="27">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E125" s="27">
-        <v>275</v>
+        <v>50</v>
       </c>
       <c r="F125" s="27">
-        <v>-1085</v>
+        <v>-280</v>
       </c>
       <c r="G125" s="27">
-        <v>1150</v>
+        <v>520</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>487</v>
+        <v>449</v>
       </c>
       <c r="B126">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D126" s="27">
-        <v>-600</v>
+        <v>225</v>
       </c>
       <c r="E126" s="27">
-        <v>-325</v>
+        <v>275</v>
       </c>
       <c r="F126" s="27">
-        <v>-655</v>
+        <v>-1085</v>
       </c>
       <c r="G126" s="27">
-        <v>1465</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="B127">
         <v>6</v>
@@ -66345,105 +66363,151 @@
         <v>-600</v>
       </c>
       <c r="E127" s="27">
-        <v>-925</v>
+        <v>-325</v>
       </c>
       <c r="F127" s="27">
-        <v>-1255</v>
+        <v>-655</v>
       </c>
       <c r="G127" s="27">
-        <v>1395</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B128">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D128" s="27">
-        <v>-15</v>
+        <v>-600</v>
       </c>
       <c r="E128" s="27">
-        <v>-940</v>
+        <v>-925</v>
       </c>
       <c r="F128" s="27">
-        <v>-1820</v>
+        <v>-1255</v>
       </c>
       <c r="G128" s="27">
-        <v>1660</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>595</v>
+        <v>545</v>
       </c>
       <c r="B129">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D129" s="27">
-        <v>-795</v>
+        <v>-15</v>
       </c>
       <c r="E129" s="27">
-        <v>-1735</v>
+        <v>-940</v>
       </c>
       <c r="F129" s="27">
-        <v>-2585</v>
+        <v>-1820</v>
       </c>
       <c r="G129" s="27">
-        <v>1155</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>705</v>
+        <v>595</v>
       </c>
       <c r="B130">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D130" s="27">
-        <v>-595</v>
+        <v>-795</v>
       </c>
       <c r="E130" s="27">
-        <v>-2330</v>
+        <v>-1735</v>
       </c>
       <c r="F130" s="27">
-        <v>-5065</v>
+        <v>-2585</v>
       </c>
       <c r="G130" s="27">
-        <v>940</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>705</v>
+      </c>
+      <c r="B131">
+        <v>28</v>
+      </c>
+      <c r="C131">
+        <v>6</v>
+      </c>
+      <c r="D131" s="27">
+        <v>-595</v>
+      </c>
+      <c r="E131" s="27">
+        <v>-2330</v>
+      </c>
+      <c r="F131" s="27">
+        <v>-5065</v>
+      </c>
+      <c r="G131" s="27">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>775</v>
       </c>
-      <c r="B131">
+      <c r="B132">
         <v>10</v>
       </c>
-      <c r="C131">
+      <c r="C132">
         <v>2</v>
       </c>
-      <c r="D131" s="27">
+      <c r="D132" s="27">
         <v>-295</v>
       </c>
-      <c r="E131" s="27">
+      <c r="E132" s="27">
         <v>-2625</v>
       </c>
-      <c r="F131" s="27">
+      <c r="F132" s="27">
         <v>-4735</v>
       </c>
-      <c r="G131" s="27">
+      <c r="G132" s="27">
         <v>645</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>811</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133" s="27">
+        <v>-100</v>
+      </c>
+      <c r="E133" s="27">
+        <v>-2725</v>
+      </c>
+      <c r="F133" s="27">
+        <v>-4835</v>
+      </c>
+      <c r="G133" s="27">
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -66492,7 +66556,7 @@
         <v>1962</v>
       </c>
       <c r="B2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C2">
         <v>26</v>
@@ -66507,7 +66571,7 @@
         <v>73</v>
       </c>
       <c r="G2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H2">
         <v>59</v>
@@ -66755,7 +66819,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -66805,121 +66869,115 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+    <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="23">
+        <v>30</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>1978</v>
       </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="E6" s="23">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>1961</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>1962</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2</v>
-      </c>
-      <c r="C9" s="31">
-        <v>29</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C10" s="31">
+        <v>30</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B11" s="3">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
         <v>3</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <v>4</v>
-      </c>
-      <c r="G11" s="3">
-        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3">
         <v>5</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" s="3">
         <v>9</v>
@@ -66927,68 +66985,68 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
       </c>
       <c r="F13" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>9</v>
-      </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B15" s="3">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
         <v>1</v>
       </c>
-      <c r="C15" s="3">
-        <v>5</v>
-      </c>
       <c r="D15" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -66996,22 +67054,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3">
         <v>6</v>
       </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>9</v>
-      </c>
       <c r="E16" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
@@ -67019,47 +67077,70 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B17" s="32">
-        <v>31</v>
+        <v>1969</v>
+      </c>
+      <c r="B17" s="3">
+        <v>6</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
       </c>
       <c r="D17" s="3">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3">
         <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2</v>
-      </c>
-      <c r="G17" s="3">
-        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B18" s="31">
+        <v>31</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>1971</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B19" s="3">
         <v>7</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="32">
         <v>24</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E19" s="3">
         <v>10</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F19" s="3">
         <v>4</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G19" s="3">
         <v>0</v>
       </c>
     </row>
@@ -67079,7 +67160,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -67089,62 +67170,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -67154,82 +67235,82 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -67239,22 +67320,22 @@
     </row>
     <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
@@ -67264,27 +67345,27 @@
     </row>
     <row r="38" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -67294,12 +67375,12 @@
     </row>
     <row r="44" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5615,7 +5615,7 @@
     <t>2:5=400 5:2=500 负其他=250 平其他=650 胜其他=280</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-13T22:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-13T23:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -17774,8 +17774,8 @@
       <c r="F119" t="s">
         <v>829</v>
       </c>
-      <c r="G119" s="5" t="s">
-        <v>70</v>
+      <c r="G119" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>21</v>
@@ -17962,8 +17962,8 @@
       <c r="F123" t="s">
         <v>829</v>
       </c>
-      <c r="G123" s="5" t="s">
-        <v>70</v>
+      <c r="G123" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>21</v>
@@ -18291,8 +18291,8 @@
       <c r="F130" t="s">
         <v>865</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>70</v>
+      <c r="G130" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>21</v>
@@ -18432,8 +18432,8 @@
       <c r="F133" t="s">
         <v>865</v>
       </c>
-      <c r="G133" s="5" t="s">
-        <v>70</v>
+      <c r="G133" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>21</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5603,7 +5603,7 @@
     <t>2:5=400 5:2=500 负其他=250 平其他=650 胜其他=280</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-14T09:00:08+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-14T10:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -2555,42 +2555,45 @@
     <t>10-14 15:45</t>
   </si>
   <si>
+    <t>2球 @3.85</t>
+  </si>
+  <si>
     <t>3球 @3.5 ⚡</t>
   </si>
   <si>
+    <t>10-14 13:00</t>
+  </si>
+  <si>
+    <t>全北现代</t>
+  </si>
+  <si>
+    <t>10-14 18:00</t>
+  </si>
+  <si>
+    <t>4球 @5.5 ⚡</t>
+  </si>
+  <si>
+    <t>曼谷港务</t>
+  </si>
+  <si>
+    <t>6球 @8.5</t>
+  </si>
+  <si>
+    <t>4球 @4.2 ⚡</t>
+  </si>
+  <si>
+    <t>清水鼓动</t>
+  </si>
+  <si>
+    <t>3球 @3.75 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.9 ⚡</t>
+  </si>
+  <si>
     <t>10-14 12:00</t>
   </si>
   <si>
-    <t>全北现代</t>
-  </si>
-  <si>
-    <t>10-14 18:00</t>
-  </si>
-  <si>
-    <t>4球 @5.5 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.6 ⚡</t>
-  </si>
-  <si>
-    <t>曼谷港务</t>
-  </si>
-  <si>
-    <t>4球 @4.3 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.85 ⚡</t>
-  </si>
-  <si>
-    <t>清水鼓动</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5.9 ⚡</t>
-  </si>
-  <si>
     <t>10-15 00:45</t>
   </si>
   <si>
@@ -2645,9 +2648,6 @@
     <t>周三011</t>
   </si>
   <si>
-    <t>6球 @10.5</t>
-  </si>
-  <si>
     <t>周三012</t>
   </si>
   <si>
@@ -5444,25 +5444,25 @@
     <t>2:5=700 5:2=120 负其他=250 平其他=400 胜其他=40</t>
   </si>
   <si>
-    <t>0:1=38 1:0=10</t>
-  </si>
-  <si>
-    <t>0:2=85 1:1=14.5 2:0=7</t>
-  </si>
-  <si>
-    <t>0:3=250 1:2=36 2:1=8.75 3:0=7.5</t>
-  </si>
-  <si>
-    <t>0:4=650 1:3=90 2:2=25 3:1=9 4:0=10</t>
-  </si>
-  <si>
-    <t>0:5=1000 1:4=350 2:3=70 3:2=25 4:1=13 5:0=16</t>
-  </si>
-  <si>
-    <t>1:5=1000 2:4=300 3:3=80 4:2=34 5:1=23</t>
-  </si>
-  <si>
-    <t>2:5=900 5:2=60 负其他=300 平其他=350 胜其他=9.5</t>
+    <t>0:1=48 1:0=12</t>
+  </si>
+  <si>
+    <t>0:2=100 1:1=15 2:0=7</t>
+  </si>
+  <si>
+    <t>0:3=250 1:2=40 2:1=9 3:0=7.5</t>
+  </si>
+  <si>
+    <t>0:4=650 1:3=100 2:2=25 3:1=9 4:0=9.5</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=350 2:3=80 3:2=25 4:1=12.5 5:0=15</t>
+  </si>
+  <si>
+    <t>1:5=1000 2:4=300 3:3=80 4:2=30 5:1=20</t>
+  </si>
+  <si>
+    <t>2:5=900 5:2=50 负其他=300 平其他=350 胜其他=8.5</t>
   </si>
   <si>
     <t>0:2=18 1:1=6.5 2:0=9.5</t>
@@ -5612,25 +5612,25 @@
     <t>2:5=350 5:2=120 负其他=90 平其他=250 胜其他=42</t>
   </si>
   <si>
-    <t>0:1=15 1:0=13</t>
-  </si>
-  <si>
-    <t>0:2=19 1:1=8.25 2:0=14.5</t>
-  </si>
-  <si>
-    <t>0:3=35 1:2=9.5 2:1=8 3:0=23</t>
-  </si>
-  <si>
-    <t>0:4=75 1:3=20 2:2=10 3:1=14.5 4:0=50</t>
-  </si>
-  <si>
-    <t>0:5=200 1:4=45 2:3=19 3:2=17 4:1=32 5:0=150</t>
-  </si>
-  <si>
-    <t>1:5=150 2:4=55 3:3=30 4:2=36 5:1=80</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=100 负其他=42 平其他=120 胜其他=32</t>
+    <t>0:1=17 1:0=12</t>
+  </si>
+  <si>
+    <t>0:2=21 1:1=8.25 2:0=13.5</t>
+  </si>
+  <si>
+    <t>0:3=38 1:2=9.75 2:1=8 3:0=22</t>
+  </si>
+  <si>
+    <t>0:4=90 1:3=20 2:2=10 3:1=13.5 4:0=45</t>
+  </si>
+  <si>
+    <t>0:5=200 1:4=50 2:3=22 3:2=17 4:1=32 5:0=100</t>
+  </si>
+  <si>
+    <t>1:5=150 2:4=55 3:3=30 4:2=35 5:1=70</t>
+  </si>
+  <si>
+    <t>2:5=150 5:2=90 负其他=42 平其他=120 胜其他=31</t>
   </si>
   <si>
     <t>0:1=17 1:0=9</t>
@@ -5696,7 +5696,7 @@
     <t>2:5=150 5:2=110 负其他=36 平其他=150 胜其他=30</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-14T12:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-14T13:00:03+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -18135,13 +18135,13 @@
         <v>21</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>531</v>
+        <v>845</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="L125" t="s">
         <v>21</v>
@@ -18150,7 +18150,7 @@
         <v>21</v>
       </c>
       <c r="N125" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O125" t="s">
         <v>21</v>
@@ -18170,10 +18170,10 @@
         <v>31</v>
       </c>
       <c r="E126" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F126" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>55</v>
@@ -18185,10 +18185,10 @@
         <v>492</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="L126" t="s">
         <v>21</v>
@@ -18197,7 +18197,7 @@
         <v>21</v>
       </c>
       <c r="N126" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O126" t="s">
         <v>21</v>
@@ -18220,7 +18220,7 @@
         <v>851</v>
       </c>
       <c r="F127" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>55</v>
@@ -18229,10 +18229,10 @@
         <v>21</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>685</v>
+        <v>852</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>853</v>
@@ -18244,7 +18244,7 @@
         <v>21</v>
       </c>
       <c r="N127" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O127" t="s">
         <v>21</v>
@@ -18267,7 +18267,7 @@
         <v>854</v>
       </c>
       <c r="F128" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>55</v>
@@ -18291,7 +18291,7 @@
         <v>21</v>
       </c>
       <c r="N128" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="O128" t="s">
         <v>21</v>
@@ -18314,7 +18314,7 @@
         <v>79</v>
       </c>
       <c r="F129" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>55</v>
@@ -18326,7 +18326,7 @@
         <v>485</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>855</v>
@@ -18338,7 +18338,7 @@
         <v>21</v>
       </c>
       <c r="N129" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="O129" t="s">
         <v>21</v>
@@ -18355,13 +18355,13 @@
         <v>824</v>
       </c>
       <c r="D130" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E130" t="s">
         <v>69</v>
       </c>
       <c r="F130" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>55</v>
@@ -18373,10 +18373,10 @@
         <v>685</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="L130" t="s">
         <v>21</v>
@@ -18385,7 +18385,7 @@
         <v>21</v>
       </c>
       <c r="N130" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O130" t="s">
         <v>21</v>
@@ -18396,19 +18396,19 @@
         <v>841</v>
       </c>
       <c r="B131" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C131" t="s">
         <v>46</v>
       </c>
       <c r="D131" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E131" t="s">
         <v>724</v>
       </c>
       <c r="F131" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>55</v>
@@ -18420,10 +18420,10 @@
         <v>585</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="L131" t="s">
         <v>21</v>
@@ -18432,7 +18432,7 @@
         <v>21</v>
       </c>
       <c r="N131" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="O131" t="s">
         <v>21</v>
@@ -18443,7 +18443,7 @@
         <v>841</v>
       </c>
       <c r="B132" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C132" t="s">
         <v>824</v>
@@ -18455,7 +18455,7 @@
         <v>87</v>
       </c>
       <c r="F132" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>70</v>
@@ -18467,7 +18467,7 @@
         <v>685</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K132" s="3" t="s">
         <v>855</v>
@@ -18479,7 +18479,7 @@
         <v>21</v>
       </c>
       <c r="N132" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="O132" t="s">
         <v>21</v>
@@ -18490,19 +18490,19 @@
         <v>841</v>
       </c>
       <c r="B133" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C133" t="s">
         <v>824</v>
       </c>
       <c r="D133" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E133" t="s">
         <v>574</v>
       </c>
       <c r="F133" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>55</v>
@@ -18511,13 +18511,13 @@
         <v>21</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="L133" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>21</v>
       </c>
       <c r="N133" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O133" t="s">
         <v>21</v>
@@ -18537,7 +18537,7 @@
         <v>841</v>
       </c>
       <c r="B134" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C134" t="s">
         <v>824</v>
@@ -18549,7 +18549,7 @@
         <v>140</v>
       </c>
       <c r="F134" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>55</v>
@@ -18561,10 +18561,10 @@
         <v>760</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="L134" t="s">
         <v>21</v>
@@ -18573,7 +18573,7 @@
         <v>21</v>
       </c>
       <c r="N134" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="O134" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>841</v>
       </c>
       <c r="B135" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C135" t="s">
         <v>824</v>
@@ -18596,7 +18596,7 @@
         <v>133</v>
       </c>
       <c r="F135" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>70</v>
@@ -18605,13 +18605,13 @@
         <v>21</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>875</v>
+        <v>486</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="L135" t="s">
         <v>21</v>
@@ -18620,7 +18620,7 @@
         <v>21</v>
       </c>
       <c r="N135" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O135" t="s">
         <v>21</v>
@@ -18643,7 +18643,7 @@
         <v>877</v>
       </c>
       <c r="F136" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>55</v>
@@ -18658,7 +18658,7 @@
         <v>878</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="L136" t="s">
         <v>21</v>
@@ -18667,7 +18667,7 @@
         <v>21</v>
       </c>
       <c r="N136" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="O136" t="s">
         <v>21</v>
@@ -18714,7 +18714,7 @@
         <v>21</v>
       </c>
       <c r="N137" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="O137" t="s">
         <v>21</v>
@@ -18749,10 +18749,10 @@
         <v>885</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="L138" t="s">
         <v>21</v>
@@ -18761,7 +18761,7 @@
         <v>21</v>
       </c>
       <c r="N138" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="O138" t="s">
         <v>21</v>
@@ -58214,7 +58214,7 @@
       </c>
       <c r="G986" s="9"/>
       <c r="H986" s="10">
-        <v>1.488</v>
+        <v>0.798</v>
       </c>
       <c r="I986" s="11"/>
       <c r="J986" s="8"/>
@@ -58243,25 +58243,25 @@
         <v>433</v>
       </c>
       <c r="F987" s="12">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="G987" s="13">
         <v>6.094</v>
       </c>
       <c r="H987" s="14">
-        <v>0.656</v>
+        <v>0.156</v>
       </c>
       <c r="I987" s="15">
-        <v>10.8</v>
+        <v>2.6</v>
       </c>
       <c r="J987" s="12">
         <v>13.25</v>
       </c>
       <c r="K987" s="16">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
       <c r="L987" s="15">
-        <v>-49.1</v>
+        <v>-52.8</v>
       </c>
       <c r="M987" t="s">
         <v>1795</v>
@@ -58284,25 +58284,25 @@
         <v>452</v>
       </c>
       <c r="F988" s="12">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="G988" s="13">
         <v>3.779</v>
       </c>
       <c r="H988" s="14">
-        <v>0.321</v>
+        <v>0.071</v>
       </c>
       <c r="I988" s="15">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J988" s="12">
         <v>14.917</v>
       </c>
       <c r="K988" s="16">
-        <v>-10.817</v>
+        <v>-11.067</v>
       </c>
       <c r="L988" s="15">
-        <v>-72.5</v>
+        <v>-74.2</v>
       </c>
       <c r="M988" t="s">
         <v>1796</v>
@@ -58366,25 +58366,25 @@
         <v>438</v>
       </c>
       <c r="F990" s="12">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="G990" s="13">
         <v>4.21</v>
       </c>
       <c r="H990" s="14">
-        <v>0.54</v>
+        <v>0.69</v>
       </c>
       <c r="I990" s="15">
-        <v>12.8</v>
+        <v>16.4</v>
       </c>
       <c r="J990" s="12">
         <v>52.3</v>
       </c>
       <c r="K990" s="16">
-        <v>-47.55</v>
+        <v>-47.4</v>
       </c>
       <c r="L990" s="15">
-        <v>-90.9</v>
+        <v>-90.6</v>
       </c>
       <c r="M990" t="s">
         <v>1798</v>
@@ -58407,25 +58407,25 @@
         <v>430</v>
       </c>
       <c r="F991" s="12">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G991" s="13">
         <v>6.541</v>
       </c>
       <c r="H991" s="14">
-        <v>1.459</v>
+        <v>1.959</v>
       </c>
       <c r="I991" s="15">
-        <v>22.3</v>
+        <v>30</v>
       </c>
       <c r="J991" s="12">
         <v>112.833</v>
       </c>
       <c r="K991" s="16">
-        <v>-104.833</v>
+        <v>-104.333</v>
       </c>
       <c r="L991" s="15">
-        <v>-92.9</v>
+        <v>-92.5</v>
       </c>
       <c r="M991" t="s">
         <v>1799</v>
@@ -58448,25 +58448,25 @@
         <v>522</v>
       </c>
       <c r="F992" s="12">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G992" s="13">
         <v>12.321</v>
       </c>
       <c r="H992" s="14">
-        <v>1.679</v>
+        <v>3.679</v>
       </c>
       <c r="I992" s="15">
-        <v>13.6</v>
+        <v>29.9</v>
       </c>
       <c r="J992" s="12">
         <v>105.6</v>
       </c>
       <c r="K992" s="16">
-        <v>-91.6</v>
+        <v>-89.6</v>
       </c>
       <c r="L992" s="15">
-        <v>-86.7</v>
+        <v>-84.8</v>
       </c>
       <c r="M992" t="s">
         <v>1800</v>
@@ -58489,25 +58489,25 @@
         <v>634</v>
       </c>
       <c r="F993" s="12">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="G993" s="13">
         <v>15.942</v>
       </c>
       <c r="H993" s="14">
-        <v>1.558</v>
+        <v>3.058</v>
       </c>
       <c r="I993" s="15">
-        <v>9.8</v>
+        <v>19.2</v>
       </c>
       <c r="J993" s="12">
         <v>160.2</v>
       </c>
       <c r="K993" s="16">
-        <v>-142.7</v>
+        <v>-141.2</v>
       </c>
       <c r="L993" s="15">
-        <v>-89.1</v>
+        <v>-88.1</v>
       </c>
       <c r="M993" t="s">
         <v>1801</v>
@@ -58524,7 +58524,7 @@
         <v>31</v>
       </c>
       <c r="D994" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E994" s="4" t="s">
         <v>441</v>
@@ -58534,7 +58534,7 @@
       </c>
       <c r="G994" s="9"/>
       <c r="H994" s="10">
-        <v>1.264</v>
+        <v>1.704</v>
       </c>
       <c r="I994" s="11"/>
       <c r="J994" s="8"/>
@@ -58557,31 +58557,31 @@
         <v>31</v>
       </c>
       <c r="D995" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E995" t="s">
         <v>433</v>
       </c>
       <c r="F995" s="12">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G995" s="13">
         <v>4.667</v>
       </c>
       <c r="H995" s="14">
-        <v>0.433</v>
+        <v>0.633</v>
       </c>
       <c r="I995" s="15">
-        <v>9.3</v>
+        <v>13.6</v>
       </c>
       <c r="J995" s="12">
         <v>10.5</v>
       </c>
       <c r="K995" s="16">
-        <v>-5.4</v>
+        <v>-5.2</v>
       </c>
       <c r="L995" s="15">
-        <v>-51.4</v>
+        <v>-49.5</v>
       </c>
       <c r="M995" t="s">
         <v>1075</v>
@@ -58598,7 +58598,7 @@
         <v>31</v>
       </c>
       <c r="D996" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E996" t="s">
         <v>452</v>
@@ -58639,31 +58639,31 @@
         <v>31</v>
       </c>
       <c r="D997" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E997" t="s">
         <v>423</v>
       </c>
       <c r="F997" s="12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G997" s="13">
         <v>3.263</v>
       </c>
       <c r="H997" s="14">
-        <v>0.337</v>
+        <v>0.237</v>
       </c>
       <c r="I997" s="15">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="J997" s="12">
         <v>33.375</v>
       </c>
       <c r="K997" s="16">
-        <v>-29.775</v>
+        <v>-29.875</v>
       </c>
       <c r="L997" s="15">
-        <v>-89.2</v>
+        <v>-89.5</v>
       </c>
       <c r="M997" t="s">
         <v>1803</v>
@@ -58680,7 +58680,7 @@
         <v>31</v>
       </c>
       <c r="D998" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E998" t="s">
         <v>438</v>
@@ -58721,7 +58721,7 @@
         <v>31</v>
       </c>
       <c r="D999" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E999" t="s">
         <v>430</v>
@@ -58762,7 +58762,7 @@
         <v>31</v>
       </c>
       <c r="D1000" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E1000" t="s">
         <v>522</v>
@@ -58803,7 +58803,7 @@
         <v>31</v>
       </c>
       <c r="D1001" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E1001" t="s">
         <v>634</v>
@@ -58850,11 +58850,11 @@
         <v>441</v>
       </c>
       <c r="F1002" s="8">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G1002" s="9"/>
       <c r="H1002" s="10">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="I1002" s="11"/>
       <c r="J1002" s="8"/>
@@ -58863,7 +58863,7 @@
       </c>
       <c r="L1002" s="11"/>
       <c r="M1002" s="4" t="s">
-        <v>1737</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
@@ -58883,25 +58883,25 @@
         <v>433</v>
       </c>
       <c r="F1003" s="12">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="G1003" s="13">
-        <v>7.917</v>
+        <v>9.6</v>
       </c>
       <c r="H1003" s="14">
-        <v>1.083</v>
+        <v>0.9</v>
       </c>
       <c r="I1003" s="15">
-        <v>13.7</v>
+        <v>9.4</v>
       </c>
       <c r="J1003" s="12">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K1003" s="16">
-        <v>-15</v>
+        <v>-19.5</v>
       </c>
       <c r="L1003" s="15">
-        <v>-62.5</v>
+        <v>-65</v>
       </c>
       <c r="M1003" t="s">
         <v>1808</v>
@@ -58924,25 +58924,25 @@
         <v>452</v>
       </c>
       <c r="F1004" s="12">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="G1004" s="13">
-        <v>4.473</v>
+        <v>4.555</v>
       </c>
       <c r="H1004" s="14">
-        <v>0.577</v>
+        <v>0.945</v>
       </c>
       <c r="I1004" s="15">
-        <v>12.9</v>
+        <v>20.8</v>
       </c>
       <c r="J1004" s="12">
-        <v>35.5</v>
+        <v>40.667</v>
       </c>
       <c r="K1004" s="16">
-        <v>-30.45</v>
+        <v>-35.167</v>
       </c>
       <c r="L1004" s="15">
-        <v>-85.8</v>
+        <v>-86.5</v>
       </c>
       <c r="M1004" t="s">
         <v>1809</v>
@@ -58965,25 +58965,25 @@
         <v>423</v>
       </c>
       <c r="F1005" s="12">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G1005" s="13">
-        <v>3.579</v>
+        <v>3.657</v>
       </c>
       <c r="H1005" s="14">
-        <v>0.271</v>
+        <v>0.443</v>
       </c>
       <c r="I1005" s="15">
-        <v>7.6</v>
+        <v>12.1</v>
       </c>
       <c r="J1005" s="12">
-        <v>75.563</v>
+        <v>76.625</v>
       </c>
       <c r="K1005" s="16">
-        <v>-71.713</v>
+        <v>-72.525</v>
       </c>
       <c r="L1005" s="15">
-        <v>-94.9</v>
+        <v>-94.6</v>
       </c>
       <c r="M1005" t="s">
         <v>1810</v>
@@ -59006,22 +59006,22 @@
         <v>438</v>
       </c>
       <c r="F1006" s="12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G1006" s="13">
-        <v>3.791</v>
+        <v>3.733</v>
       </c>
       <c r="H1006" s="14">
-        <v>0.509</v>
+        <v>0.467</v>
       </c>
       <c r="I1006" s="15">
-        <v>13.4</v>
+        <v>12.5</v>
       </c>
       <c r="J1006" s="12">
-        <v>156.8</v>
+        <v>158.7</v>
       </c>
       <c r="K1006" s="16">
-        <v>-152.5</v>
+        <v>-154.5</v>
       </c>
       <c r="L1006" s="15">
         <v>-97.3</v>
@@ -59047,25 +59047,25 @@
         <v>430</v>
       </c>
       <c r="F1007" s="12">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="G1007" s="13">
-        <v>5.062</v>
+        <v>4.926</v>
       </c>
       <c r="H1007" s="14">
-        <v>0.938</v>
+        <v>0.774</v>
       </c>
       <c r="I1007" s="15">
-        <v>18.5</v>
+        <v>15.7</v>
       </c>
       <c r="J1007" s="12">
-        <v>245.667</v>
+        <v>247.083</v>
       </c>
       <c r="K1007" s="16">
-        <v>-239.667</v>
+        <v>-241.383</v>
       </c>
       <c r="L1007" s="15">
-        <v>-97.6</v>
+        <v>-97.7</v>
       </c>
       <c r="M1007" t="s">
         <v>1812</v>
@@ -59088,25 +59088,25 @@
         <v>522</v>
       </c>
       <c r="F1008" s="12">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="G1008" s="13">
-        <v>11.145</v>
+        <v>9.983</v>
       </c>
       <c r="H1008" s="17">
-        <v>-1.645</v>
+        <v>-1.483</v>
       </c>
       <c r="I1008" s="15">
-        <v>-14.8</v>
+        <v>-14.9</v>
       </c>
       <c r="J1008" s="12">
-        <v>287.4</v>
+        <v>286</v>
       </c>
       <c r="K1008" s="16">
-        <v>-277.9</v>
+        <v>-277.5</v>
       </c>
       <c r="L1008" s="15">
-        <v>-96.7</v>
+        <v>-97</v>
       </c>
       <c r="M1008" t="s">
         <v>1813</v>
@@ -59129,25 +59129,25 @@
         <v>634</v>
       </c>
       <c r="F1009" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1009" s="13">
-        <v>7.738</v>
+        <v>6.899</v>
       </c>
       <c r="H1009" s="14">
-        <v>2.262</v>
+        <v>1.101</v>
       </c>
       <c r="I1009" s="15">
-        <v>29.2</v>
+        <v>16</v>
       </c>
       <c r="J1009" s="12">
-        <v>323.9</v>
+        <v>321.7</v>
       </c>
       <c r="K1009" s="16">
-        <v>-313.9</v>
+        <v>-313.7</v>
       </c>
       <c r="L1009" s="15">
-        <v>-96.9</v>
+        <v>-97.5</v>
       </c>
       <c r="M1009" t="s">
         <v>1814</v>
@@ -59801,7 +59801,7 @@
         <v>512</v>
       </c>
       <c r="C1026" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1026" s="4" t="s">
         <v>69</v>
@@ -59834,7 +59834,7 @@
         <v>512</v>
       </c>
       <c r="C1027" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1027" t="s">
         <v>69</v>
@@ -59875,7 +59875,7 @@
         <v>512</v>
       </c>
       <c r="C1028" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1028" t="s">
         <v>69</v>
@@ -59916,7 +59916,7 @@
         <v>512</v>
       </c>
       <c r="C1029" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1029" t="s">
         <v>69</v>
@@ -59957,7 +59957,7 @@
         <v>512</v>
       </c>
       <c r="C1030" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1030" t="s">
         <v>69</v>
@@ -59998,7 +59998,7 @@
         <v>512</v>
       </c>
       <c r="C1031" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1031" t="s">
         <v>69</v>
@@ -60039,7 +60039,7 @@
         <v>512</v>
       </c>
       <c r="C1032" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1032" t="s">
         <v>69</v>
@@ -60080,7 +60080,7 @@
         <v>512</v>
       </c>
       <c r="C1033" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D1033" t="s">
         <v>69</v>
@@ -60118,10 +60118,10 @@
         <v>841</v>
       </c>
       <c r="B1034" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1034" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1034" s="4" t="s">
         <v>724</v>
@@ -60151,10 +60151,10 @@
         <v>841</v>
       </c>
       <c r="B1035" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1035" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1035" t="s">
         <v>724</v>
@@ -60192,10 +60192,10 @@
         <v>841</v>
       </c>
       <c r="B1036" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1036" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1036" t="s">
         <v>724</v>
@@ -60233,10 +60233,10 @@
         <v>841</v>
       </c>
       <c r="B1037" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1037" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1037" t="s">
         <v>724</v>
@@ -60274,10 +60274,10 @@
         <v>841</v>
       </c>
       <c r="B1038" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1038" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1038" t="s">
         <v>724</v>
@@ -60315,10 +60315,10 @@
         <v>841</v>
       </c>
       <c r="B1039" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1039" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1039" t="s">
         <v>724</v>
@@ -60356,10 +60356,10 @@
         <v>841</v>
       </c>
       <c r="B1040" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1040" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1040" t="s">
         <v>724</v>
@@ -60397,10 +60397,10 @@
         <v>841</v>
       </c>
       <c r="B1041" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C1041" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D1041" t="s">
         <v>724</v>
@@ -60438,7 +60438,7 @@
         <v>841</v>
       </c>
       <c r="B1042" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1042" s="4" t="s">
         <v>721</v>
@@ -60471,7 +60471,7 @@
         <v>841</v>
       </c>
       <c r="B1043" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1043" t="s">
         <v>721</v>
@@ -60512,7 +60512,7 @@
         <v>841</v>
       </c>
       <c r="B1044" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1044" t="s">
         <v>721</v>
@@ -60553,7 +60553,7 @@
         <v>841</v>
       </c>
       <c r="B1045" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1045" t="s">
         <v>721</v>
@@ -60594,7 +60594,7 @@
         <v>841</v>
       </c>
       <c r="B1046" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1046" t="s">
         <v>721</v>
@@ -60635,7 +60635,7 @@
         <v>841</v>
       </c>
       <c r="B1047" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1047" t="s">
         <v>721</v>
@@ -60676,7 +60676,7 @@
         <v>841</v>
       </c>
       <c r="B1048" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1048" t="s">
         <v>721</v>
@@ -60717,7 +60717,7 @@
         <v>841</v>
       </c>
       <c r="B1049" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C1049" t="s">
         <v>721</v>
@@ -60758,10 +60758,10 @@
         <v>841</v>
       </c>
       <c r="B1050" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1050" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1050" s="4" t="s">
         <v>574</v>
@@ -60791,10 +60791,10 @@
         <v>841</v>
       </c>
       <c r="B1051" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1051" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1051" t="s">
         <v>574</v>
@@ -60832,10 +60832,10 @@
         <v>841</v>
       </c>
       <c r="B1052" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1052" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1052" t="s">
         <v>574</v>
@@ -60873,10 +60873,10 @@
         <v>841</v>
       </c>
       <c r="B1053" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1053" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1053" t="s">
         <v>574</v>
@@ -60914,10 +60914,10 @@
         <v>841</v>
       </c>
       <c r="B1054" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1054" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1054" t="s">
         <v>574</v>
@@ -60955,10 +60955,10 @@
         <v>841</v>
       </c>
       <c r="B1055" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1055" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1055" t="s">
         <v>574</v>
@@ -60996,10 +60996,10 @@
         <v>841</v>
       </c>
       <c r="B1056" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1056" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1056" t="s">
         <v>574</v>
@@ -61037,10 +61037,10 @@
         <v>841</v>
       </c>
       <c r="B1057" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C1057" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D1057" t="s">
         <v>574</v>
@@ -61078,7 +61078,7 @@
         <v>841</v>
       </c>
       <c r="B1058" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1058" s="4" t="s">
         <v>122</v>
@@ -61111,7 +61111,7 @@
         <v>841</v>
       </c>
       <c r="B1059" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1059" t="s">
         <v>122</v>
@@ -61152,7 +61152,7 @@
         <v>841</v>
       </c>
       <c r="B1060" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1060" t="s">
         <v>122</v>
@@ -61193,7 +61193,7 @@
         <v>841</v>
       </c>
       <c r="B1061" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1061" t="s">
         <v>122</v>
@@ -61234,7 +61234,7 @@
         <v>841</v>
       </c>
       <c r="B1062" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1062" t="s">
         <v>122</v>
@@ -61275,7 +61275,7 @@
         <v>841</v>
       </c>
       <c r="B1063" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1063" t="s">
         <v>122</v>
@@ -61316,7 +61316,7 @@
         <v>841</v>
       </c>
       <c r="B1064" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1064" t="s">
         <v>122</v>
@@ -61357,7 +61357,7 @@
         <v>841</v>
       </c>
       <c r="B1065" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C1065" t="s">
         <v>122</v>
@@ -61398,7 +61398,7 @@
         <v>841</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1066" s="4" t="s">
         <v>72</v>
@@ -61414,7 +61414,7 @@
       </c>
       <c r="G1066" s="9"/>
       <c r="H1066" s="10">
-        <v>1.852</v>
+        <v>1.584</v>
       </c>
       <c r="I1066" s="11"/>
       <c r="J1066" s="8"/>
@@ -61431,7 +61431,7 @@
         <v>841</v>
       </c>
       <c r="B1067" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1067" t="s">
         <v>72</v>
@@ -61446,22 +61446,22 @@
         <v>8</v>
       </c>
       <c r="G1067" s="13">
-        <v>6.964</v>
+        <v>7.034</v>
       </c>
       <c r="H1067" s="14">
-        <v>1.036</v>
+        <v>0.966</v>
       </c>
       <c r="I1067" s="15">
-        <v>14.9</v>
+        <v>13.7</v>
       </c>
       <c r="J1067" s="12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="K1067" s="16">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="L1067" s="15">
-        <v>-42.9</v>
+        <v>-44.8</v>
       </c>
       <c r="M1067" t="s">
         <v>1864</v>
@@ -61472,7 +61472,7 @@
         <v>841</v>
       </c>
       <c r="B1068" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1068" t="s">
         <v>72</v>
@@ -61487,22 +61487,22 @@
         <v>4.5</v>
       </c>
       <c r="G1068" s="13">
-        <v>4.118</v>
+        <v>4.117</v>
       </c>
       <c r="H1068" s="14">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="I1068" s="15">
         <v>9.3</v>
       </c>
       <c r="J1068" s="12">
-        <v>13.917</v>
+        <v>14.25</v>
       </c>
       <c r="K1068" s="16">
-        <v>-9.417</v>
+        <v>-9.75</v>
       </c>
       <c r="L1068" s="15">
-        <v>-67.7</v>
+        <v>-68.4</v>
       </c>
       <c r="M1068" t="s">
         <v>1865</v>
@@ -61513,7 +61513,7 @@
         <v>841</v>
       </c>
       <c r="B1069" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1069" t="s">
         <v>72</v>
@@ -61528,22 +61528,22 @@
         <v>3.7</v>
       </c>
       <c r="G1069" s="13">
-        <v>3.308</v>
+        <v>3.341</v>
       </c>
       <c r="H1069" s="14">
-        <v>0.392</v>
+        <v>0.359</v>
       </c>
       <c r="I1069" s="15">
-        <v>11.9</v>
+        <v>10.8</v>
       </c>
       <c r="J1069" s="12">
-        <v>18.875</v>
+        <v>19.438</v>
       </c>
       <c r="K1069" s="16">
-        <v>-15.175</v>
+        <v>-15.738</v>
       </c>
       <c r="L1069" s="15">
-        <v>-80.4</v>
+        <v>-81</v>
       </c>
       <c r="M1069" t="s">
         <v>1866</v>
@@ -61554,7 +61554,7 @@
         <v>841</v>
       </c>
       <c r="B1070" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1070" t="s">
         <v>72</v>
@@ -61569,22 +61569,22 @@
         <v>4.5</v>
       </c>
       <c r="G1070" s="13">
-        <v>3.964</v>
+        <v>3.885</v>
       </c>
       <c r="H1070" s="14">
-        <v>0.536</v>
+        <v>0.615</v>
       </c>
       <c r="I1070" s="15">
-        <v>13.5</v>
+        <v>15.8</v>
       </c>
       <c r="J1070" s="12">
-        <v>33.9</v>
+        <v>35.7</v>
       </c>
       <c r="K1070" s="16">
-        <v>-29.4</v>
+        <v>-31.2</v>
       </c>
       <c r="L1070" s="15">
-        <v>-86.7</v>
+        <v>-87.4</v>
       </c>
       <c r="M1070" t="s">
         <v>1867</v>
@@ -61595,7 +61595,7 @@
         <v>841</v>
       </c>
       <c r="B1071" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1071" t="s">
         <v>72</v>
@@ -61610,22 +61610,22 @@
         <v>6.7</v>
       </c>
       <c r="G1071" s="13">
-        <v>5.663</v>
+        <v>5.864</v>
       </c>
       <c r="H1071" s="14">
-        <v>1.037</v>
+        <v>0.836</v>
       </c>
       <c r="I1071" s="15">
-        <v>18.3</v>
+        <v>14.3</v>
       </c>
       <c r="J1071" s="12">
-        <v>77.167</v>
+        <v>70.167</v>
       </c>
       <c r="K1071" s="16">
-        <v>-70.467</v>
+        <v>-63.467</v>
       </c>
       <c r="L1071" s="15">
-        <v>-91.3</v>
+        <v>-90.4</v>
       </c>
       <c r="M1071" t="s">
         <v>1868</v>
@@ -61636,7 +61636,7 @@
         <v>841</v>
       </c>
       <c r="B1072" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1072" t="s">
         <v>72</v>
@@ -61651,22 +61651,22 @@
         <v>10.5</v>
       </c>
       <c r="G1072" s="13">
-        <v>10.156</v>
+        <v>9.897</v>
       </c>
       <c r="H1072" s="14">
-        <v>0.344</v>
+        <v>0.603</v>
       </c>
       <c r="I1072" s="15">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="J1072" s="12">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="K1072" s="16">
-        <v>-59.7</v>
+        <v>-57.5</v>
       </c>
       <c r="L1072" s="15">
-        <v>-85</v>
+        <v>-84.6</v>
       </c>
       <c r="M1072" t="s">
         <v>1869</v>
@@ -61677,7 +61677,7 @@
         <v>841</v>
       </c>
       <c r="B1073" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C1073" t="s">
         <v>72</v>
@@ -61692,22 +61692,22 @@
         <v>13</v>
       </c>
       <c r="G1073" s="13">
-        <v>12.491</v>
+        <v>12.169</v>
       </c>
       <c r="H1073" s="14">
-        <v>0.509</v>
+        <v>0.831</v>
       </c>
       <c r="I1073" s="15">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J1073" s="12">
-        <v>88.8</v>
+        <v>86.6</v>
       </c>
       <c r="K1073" s="16">
-        <v>-75.8</v>
+        <v>-73.6</v>
       </c>
       <c r="L1073" s="15">
-        <v>-85.4</v>
+        <v>-85</v>
       </c>
       <c r="M1073" t="s">
         <v>1870</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11552" uniqueCount="2052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11573" uniqueCount="2058">
   <si>
     <t>日期</t>
   </si>
@@ -2561,7 +2561,7 @@
     <t>10-14 15:00</t>
   </si>
   <si>
-    <t>10-14 19:00</t>
+    <t>10-14 21:00</t>
   </si>
   <si>
     <t>全北现代</t>
@@ -2600,42 +2600,42 @@
     <t>3球 @3.75 ⚡</t>
   </si>
   <si>
+    <t>LASK林茨</t>
+  </si>
+  <si>
+    <t>4球 @4.6 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
+    <t>周三007</t>
+  </si>
+  <si>
+    <t>诺维奇</t>
+  </si>
+  <si>
+    <t>10-15 02:45</t>
+  </si>
+  <si>
+    <t>周三008</t>
+  </si>
+  <si>
+    <t>10-15 03:00</t>
+  </si>
+  <si>
+    <t>周三009</t>
+  </si>
+  <si>
+    <t>博德闪耀</t>
+  </si>
+  <si>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
     <t>10-14 20:00</t>
   </si>
   <si>
-    <t>LASK林茨</t>
-  </si>
-  <si>
-    <t>4球 @4.6 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.6 ⚡</t>
-  </si>
-  <si>
-    <t>周三007</t>
-  </si>
-  <si>
-    <t>诺维奇</t>
-  </si>
-  <si>
-    <t>10-15 02:45</t>
-  </si>
-  <si>
-    <t>周三008</t>
-  </si>
-  <si>
-    <t>10-15 03:00</t>
-  </si>
-  <si>
-    <t>周三009</t>
-  </si>
-  <si>
-    <t>博德闪耀</t>
-  </si>
-  <si>
-    <t>3球 @3.85 ⚡</t>
-  </si>
-  <si>
     <t>周三010</t>
   </si>
   <si>
@@ -2672,7 +2672,7 @@
     <t>周三014</t>
   </si>
   <si>
-    <t>3球 @3.65 ⚡</t>
+    <t>3球 @3.8 ⚡</t>
   </si>
   <si>
     <t>编号</t>
@@ -5618,34 +5618,37 @@
     <t>2:5=350 5:2=100 负其他=90 平其他=250 胜其他=40</t>
   </si>
   <si>
-    <t>0:1=20 1:0=13</t>
-  </si>
-  <si>
-    <t>0:2=26 1:1=8.25 2:0=14</t>
-  </si>
-  <si>
-    <t>0:3=42 1:2=11 2:1=8 3:0=21</t>
-  </si>
-  <si>
-    <t>0:4=90 1:3=20 2:2=9.5 3:1=12 4:0=40</t>
-  </si>
-  <si>
-    <t>0:5=200 1:4=50 2:3=22 3:2=15.5 4:1=28 5:0=100</t>
-  </si>
-  <si>
-    <t>1:5=150 2:4=55 3:3=28 4:2=34 5:1=65</t>
+    <t>0:1=20 1:0=14</t>
+  </si>
+  <si>
+    <t>0:2=26 1:1=8.5 2:0=14</t>
+  </si>
+  <si>
+    <t>0:3=42 1:2=11 2:1=7.7 3:0=21</t>
+  </si>
+  <si>
+    <t>0:4=90 1:3=22 2:2=9.5 3:1=12 4:0=40</t>
+  </si>
+  <si>
+    <t>0:5=200 1:4=50 2:3=22 3:2=14.5 4:1=28 5:0=100</t>
+  </si>
+  <si>
+    <t>1:5=150 2:4=55 3:3=28 4:2=30 5:1=65</t>
   </si>
   <si>
     <t>2:5=150 5:2=75 负其他=42 平其他=100 胜其他=23</t>
   </si>
   <si>
-    <t>0:2=30 1:1=8.25 2:0=8.75</t>
-  </si>
-  <si>
-    <t>0:4=200 1:3=38 2:2=13.5 3:1=11 4:0=25</t>
-  </si>
-  <si>
-    <t>0:5=450 1:4=100 2:3=36 3:2=19 4:1=22 5:0=65</t>
+    <t>0:2=32 1:1=8.25 2:0=8.75</t>
+  </si>
+  <si>
+    <t>0:3=80 1:2=14 2:1=6.7 3:0=13</t>
+  </si>
+  <si>
+    <t>0:4=200 1:3=38 2:2=13.5 3:1=10.5 4:0=25</t>
+  </si>
+  <si>
+    <t>0:5=450 1:4=100 2:3=36 3:2=17 4:1=22 5:0=65</t>
   </si>
   <si>
     <t>1:5=350 2:4=100 3:3=45 4:2=35 5:1=50</t>
@@ -5678,28 +5681,28 @@
     <t>2:5=350 5:2=450 负其他=200 平其他=550 胜其他=250</t>
   </si>
   <si>
-    <t>0:1=16.5 1:0=13</t>
-  </si>
-  <si>
-    <t>0:2=22 1:1=8 2:0=15</t>
-  </si>
-  <si>
-    <t>0:3=38 1:2=9.5 2:1=8 3:0=21</t>
-  </si>
-  <si>
-    <t>0:4=80 1:3=20 2:2=11 3:1=13 4:0=45</t>
-  </si>
-  <si>
-    <t>0:5=225 1:4=55 2:3=21 3:2=15 4:1=30 5:0=100</t>
-  </si>
-  <si>
-    <t>1:5=120 2:4=55 3:3=30 4:2=36 5:1=70</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=100 负其他=37 平其他=150 胜其他=28</t>
-  </si>
-  <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-14T20:00:04+08:00）</t>
+    <t>0:1=17.5 1:0=13</t>
+  </si>
+  <si>
+    <t>0:2=23 1:1=8.2 2:0=15</t>
+  </si>
+  <si>
+    <t>0:3=40 1:2=10 2:1=8 3:0=21</t>
+  </si>
+  <si>
+    <t>0:4=80 1:3=20 2:2=11 3:1=12.5 4:0=45</t>
+  </si>
+  <si>
+    <t>0:5=225 1:4=55 2:3=21 3:2=14.5 4:1=30 5:0=100</t>
+  </si>
+  <si>
+    <t>1:5=120 2:4=55 3:3=30 4:2=31 5:1=70</t>
+  </si>
+  <si>
+    <t>2:5=150 5:2=80 负其他=37 平其他=150 胜其他=26</t>
+  </si>
+  <si>
+    <t>进球数预测 · 模型统计（截至 2026-10-14T21:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -5714,19 +5717,19 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>15/123 = 12.2%</t>
+    <t>16/126 = 12.7%</t>
   </si>
   <si>
     <t>模型A 命中率（数据核心·自修正）</t>
   </si>
   <si>
-    <t>22/123 = 17.9%</t>
+    <t>22/126 = 17.5%</t>
   </si>
   <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
-    <t>29/123 = 23.6%</t>
+    <t>30/126 = 23.8%</t>
   </si>
   <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
@@ -5771,7 +5774,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>96 场（另剔除爆冷 27 场）</t>
+    <t>99 场（另剔除爆冷 27 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -5810,112 +5813,127 @@
     <t>11% (3/28)</t>
   </si>
   <si>
-    <t>0% (0/15)</t>
+    <t>0% (0/17)</t>
   </si>
   <si>
     <t>0% (0/21)</t>
   </si>
   <si>
-    <t>0% (0/20)</t>
-  </si>
-  <si>
     <t>25% (2/8)</t>
   </si>
   <si>
     <t>11% (2/18)</t>
   </si>
   <si>
+    <t>22% (5/23)</t>
+  </si>
+  <si>
+    <t>26% (5/19)</t>
+  </si>
+  <si>
+    <t>17% (1/6)</t>
+  </si>
+  <si>
+    <t>0% (0/13)</t>
+  </si>
+  <si>
+    <t>0% (0/12)</t>
+  </si>
+  <si>
+    <t>17% (4/23)</t>
+  </si>
+  <si>
+    <t>17% (3/18)</t>
+  </si>
+  <si>
+    <t>26% (7/27)</t>
+  </si>
+  <si>
+    <t>29% (4/14)</t>
+  </si>
+  <si>
+    <t>22% (2/9)</t>
+  </si>
+  <si>
+    <t>0% (0/8)</t>
+  </si>
+  <si>
     <t>24% (5/21)</t>
   </si>
   <si>
-    <t>26% (5/19)</t>
-  </si>
-  <si>
-    <t>17% (1/6)</t>
-  </si>
-  <si>
-    <t>0% (0/13)</t>
+    <t>20% (8/40)</t>
+  </si>
+  <si>
+    <t>52% (13/25)</t>
+  </si>
+  <si>
+    <t>29% (2/7)</t>
+  </si>
+  <si>
+    <t>60% (3/5)</t>
+  </si>
+  <si>
+    <t>0% (0/1)</t>
+  </si>
+  <si>
+    <t>25% (3/12)</t>
+  </si>
+  <si>
+    <t>23% (3/13)</t>
+  </si>
+  <si>
+    <t>22% (8/36)</t>
+  </si>
+  <si>
+    <t>22% (4/18)</t>
+  </si>
+  <si>
+    <t>0% (0/7)</t>
+  </si>
+  <si>
+    <t>0% (0/4)</t>
+  </si>
+  <si>
+    <t>33% (1/3)</t>
+  </si>
+  <si>
+    <t>14% (1/7)</t>
+  </si>
+  <si>
+    <t>7% (1/14)</t>
+  </si>
+  <si>
+    <t>0% (0/36)</t>
+  </si>
+  <si>
+    <t>0% (0/28)</t>
+  </si>
+  <si>
+    <t>0% (0/10)</t>
+  </si>
+  <si>
+    <t>8% (2/26)</t>
+  </si>
+  <si>
+    <t>8% (1/12)</t>
   </si>
   <si>
     <t>0% (0/11)</t>
   </si>
   <si>
-    <t>18% (4/22)</t>
-  </si>
-  <si>
-    <t>12% (2/17)</t>
-  </si>
-  <si>
-    <t>26% (7/27)</t>
-  </si>
-  <si>
-    <t>29% (4/14)</t>
-  </si>
-  <si>
-    <t>0% (0/8)</t>
-  </si>
-  <si>
-    <t>25% (5/20)</t>
-  </si>
-  <si>
-    <t>18% (7/38)</t>
-  </si>
-  <si>
-    <t>52% (13/25)</t>
-  </si>
-  <si>
-    <t>29% (2/7)</t>
-  </si>
-  <si>
-    <t>60% (3/5)</t>
-  </si>
-  <si>
-    <t>0% (0/1)</t>
-  </si>
-  <si>
-    <t>25% (3/12)</t>
-  </si>
-  <si>
-    <t>23% (8/35)</t>
-  </si>
-  <si>
-    <t>24% (4/17)</t>
-  </si>
-  <si>
-    <t>0% (0/7)</t>
-  </si>
-  <si>
-    <t>0% (0/4)</t>
-  </si>
-  <si>
-    <t>33% (1/3)</t>
-  </si>
-  <si>
-    <t>7% (1/14)</t>
-  </si>
-  <si>
-    <t>0% (0/36)</t>
-  </si>
-  <si>
     <t>0% (0/26)</t>
   </si>
   <si>
-    <t>0% (0/10)</t>
-  </si>
-  <si>
-    <t>4% (1/25)</t>
-  </si>
-  <si>
-    <t>9% (1/11)</t>
-  </si>
-  <si>
     <t>8% (1/13)</t>
   </si>
   <si>
-    <t>0% (0/5)</t>
-  </si>
-  <si>
-    <t>0% (0/55)</t>
+    <t>0% (0/3)</t>
+  </si>
+  <si>
+    <t>0% (0/6)</t>
+  </si>
+  <si>
+    <t>0% (0/56)</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -18182,7 +18200,7 @@
         <v>55</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>21</v>
+        <v>452</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>531</v>
@@ -18193,17 +18211,17 @@
       <c r="K126" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="L126" t="s">
-        <v>21</v>
-      </c>
-      <c r="M126" t="s">
-        <v>21</v>
+      <c r="L126" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="N126" t="s">
         <v>849</v>
       </c>
       <c r="O126" t="s">
-        <v>21</v>
+        <v>847</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
@@ -18229,7 +18247,7 @@
         <v>55</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>851</v>
@@ -18240,17 +18258,17 @@
       <c r="K127" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="L127" t="s">
-        <v>21</v>
-      </c>
-      <c r="M127" t="s">
-        <v>21</v>
+      <c r="L127" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M127" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="N127" t="s">
         <v>853</v>
       </c>
       <c r="O127" t="s">
-        <v>21</v>
+        <v>847</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
@@ -18276,7 +18294,7 @@
         <v>55</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>855</v>
@@ -18287,17 +18305,17 @@
       <c r="K128" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="L128" t="s">
-        <v>21</v>
-      </c>
-      <c r="M128" t="s">
-        <v>21</v>
+      <c r="L128" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M128" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="N128" t="s">
         <v>849</v>
       </c>
       <c r="O128" t="s">
-        <v>21</v>
+        <v>847</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
@@ -18341,7 +18359,7 @@
         <v>21</v>
       </c>
       <c r="N129" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="O129" t="s">
         <v>21</v>
@@ -18358,7 +18376,7 @@
         <v>824</v>
       </c>
       <c r="D130" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E130" t="s">
         <v>69</v>
@@ -18376,11 +18394,11 @@
         <v>564</v>
       </c>
       <c r="J130" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="K130" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="K130" s="3" t="s">
-        <v>863</v>
-      </c>
       <c r="L130" t="s">
         <v>21</v>
       </c>
@@ -18388,7 +18406,7 @@
         <v>21</v>
       </c>
       <c r="N130" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="O130" t="s">
         <v>21</v>
@@ -18399,19 +18417,19 @@
         <v>841</v>
       </c>
       <c r="B131" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C131" t="s">
         <v>46</v>
       </c>
       <c r="D131" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E131" t="s">
         <v>724</v>
       </c>
       <c r="F131" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>55</v>
@@ -18423,10 +18441,10 @@
         <v>694</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="L131" t="s">
         <v>21</v>
@@ -18435,7 +18453,7 @@
         <v>21</v>
       </c>
       <c r="N131" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="O131" t="s">
         <v>21</v>
@@ -18446,7 +18464,7 @@
         <v>841</v>
       </c>
       <c r="B132" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C132" t="s">
         <v>824</v>
@@ -18458,7 +18476,7 @@
         <v>87</v>
       </c>
       <c r="F132" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>70</v>
@@ -18470,10 +18488,10 @@
         <v>432</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="L132" t="s">
         <v>21</v>
@@ -18482,7 +18500,7 @@
         <v>21</v>
       </c>
       <c r="N132" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="O132" t="s">
         <v>21</v>
@@ -18493,19 +18511,19 @@
         <v>841</v>
       </c>
       <c r="B133" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C133" t="s">
         <v>824</v>
       </c>
       <c r="D133" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E133" t="s">
         <v>574</v>
       </c>
       <c r="F133" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>55</v>
@@ -18517,19 +18535,19 @@
         <v>636</v>
       </c>
       <c r="J133" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="K133" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="L133" t="s">
+        <v>21</v>
+      </c>
+      <c r="M133" t="s">
+        <v>21</v>
+      </c>
+      <c r="N133" t="s">
         <v>871</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="L133" t="s">
-        <v>21</v>
-      </c>
-      <c r="M133" t="s">
-        <v>21</v>
-      </c>
-      <c r="N133" t="s">
-        <v>860</v>
       </c>
       <c r="O133" t="s">
         <v>21</v>
@@ -18552,7 +18570,7 @@
         <v>140</v>
       </c>
       <c r="F134" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>55</v>
@@ -18576,7 +18594,7 @@
         <v>21</v>
       </c>
       <c r="N134" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="O134" t="s">
         <v>21</v>
@@ -18599,7 +18617,7 @@
         <v>133</v>
       </c>
       <c r="F135" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>70</v>
@@ -18623,7 +18641,7 @@
         <v>21</v>
       </c>
       <c r="N135" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="O135" t="s">
         <v>21</v>
@@ -18646,7 +18664,7 @@
         <v>877</v>
       </c>
       <c r="F136" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>55</v>
@@ -18670,7 +18688,7 @@
         <v>21</v>
       </c>
       <c r="N136" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="O136" t="s">
         <v>21</v>
@@ -18717,7 +18735,7 @@
         <v>21</v>
       </c>
       <c r="N137" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="O137" t="s">
         <v>21</v>
@@ -18749,7 +18767,7 @@
         <v>21</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>474</v>
+        <v>553</v>
       </c>
       <c r="J138" s="3" t="s">
         <v>884</v>
@@ -18764,7 +18782,7 @@
         <v>21</v>
       </c>
       <c r="N138" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="O138" t="s">
         <v>21</v>
@@ -59804,7 +59822,7 @@
         <v>512</v>
       </c>
       <c r="C1026" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1026" s="4" t="s">
         <v>69</v>
@@ -59837,7 +59855,7 @@
         <v>512</v>
       </c>
       <c r="C1027" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1027" t="s">
         <v>69</v>
@@ -59878,7 +59896,7 @@
         <v>512</v>
       </c>
       <c r="C1028" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1028" t="s">
         <v>69</v>
@@ -59919,7 +59937,7 @@
         <v>512</v>
       </c>
       <c r="C1029" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1029" t="s">
         <v>69</v>
@@ -59960,7 +59978,7 @@
         <v>512</v>
       </c>
       <c r="C1030" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1030" t="s">
         <v>69</v>
@@ -60001,7 +60019,7 @@
         <v>512</v>
       </c>
       <c r="C1031" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1031" t="s">
         <v>69</v>
@@ -60042,7 +60060,7 @@
         <v>512</v>
       </c>
       <c r="C1032" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1032" t="s">
         <v>69</v>
@@ -60083,7 +60101,7 @@
         <v>512</v>
       </c>
       <c r="C1033" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1033" t="s">
         <v>69</v>
@@ -60121,10 +60139,10 @@
         <v>841</v>
       </c>
       <c r="B1034" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1034" s="4" t="s">
         <v>864</v>
-      </c>
-      <c r="C1034" s="4" t="s">
-        <v>865</v>
       </c>
       <c r="D1034" s="4" t="s">
         <v>724</v>
@@ -60154,10 +60172,10 @@
         <v>841</v>
       </c>
       <c r="B1035" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1035" t="s">
         <v>864</v>
-      </c>
-      <c r="C1035" t="s">
-        <v>865</v>
       </c>
       <c r="D1035" t="s">
         <v>724</v>
@@ -60195,10 +60213,10 @@
         <v>841</v>
       </c>
       <c r="B1036" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1036" t="s">
         <v>864</v>
-      </c>
-      <c r="C1036" t="s">
-        <v>865</v>
       </c>
       <c r="D1036" t="s">
         <v>724</v>
@@ -60236,10 +60254,10 @@
         <v>841</v>
       </c>
       <c r="B1037" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1037" t="s">
         <v>864</v>
-      </c>
-      <c r="C1037" t="s">
-        <v>865</v>
       </c>
       <c r="D1037" t="s">
         <v>724</v>
@@ -60277,10 +60295,10 @@
         <v>841</v>
       </c>
       <c r="B1038" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1038" t="s">
         <v>864</v>
-      </c>
-      <c r="C1038" t="s">
-        <v>865</v>
       </c>
       <c r="D1038" t="s">
         <v>724</v>
@@ -60318,10 +60336,10 @@
         <v>841</v>
       </c>
       <c r="B1039" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1039" t="s">
         <v>864</v>
-      </c>
-      <c r="C1039" t="s">
-        <v>865</v>
       </c>
       <c r="D1039" t="s">
         <v>724</v>
@@ -60359,10 +60377,10 @@
         <v>841</v>
       </c>
       <c r="B1040" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1040" t="s">
         <v>864</v>
-      </c>
-      <c r="C1040" t="s">
-        <v>865</v>
       </c>
       <c r="D1040" t="s">
         <v>724</v>
@@ -60400,10 +60418,10 @@
         <v>841</v>
       </c>
       <c r="B1041" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1041" t="s">
         <v>864</v>
-      </c>
-      <c r="C1041" t="s">
-        <v>865</v>
       </c>
       <c r="D1041" t="s">
         <v>724</v>
@@ -60441,7 +60459,7 @@
         <v>841</v>
       </c>
       <c r="B1042" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1042" s="4" t="s">
         <v>721</v>
@@ -60457,7 +60475,7 @@
       </c>
       <c r="G1042" s="9"/>
       <c r="H1042" s="10">
-        <v>1.996</v>
+        <v>2.086</v>
       </c>
       <c r="I1042" s="11"/>
       <c r="J1042" s="8"/>
@@ -60474,7 +60492,7 @@
         <v>841</v>
       </c>
       <c r="B1043" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1043" t="s">
         <v>721</v>
@@ -60515,7 +60533,7 @@
         <v>841</v>
       </c>
       <c r="B1044" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1044" t="s">
         <v>721</v>
@@ -60556,7 +60574,7 @@
         <v>841</v>
       </c>
       <c r="B1045" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1045" t="s">
         <v>721</v>
@@ -60597,7 +60615,7 @@
         <v>841</v>
       </c>
       <c r="B1046" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1046" t="s">
         <v>721</v>
@@ -60609,25 +60627,25 @@
         <v>438</v>
       </c>
       <c r="F1046" s="12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G1046" s="13">
         <v>3.785</v>
       </c>
       <c r="H1046" s="14">
-        <v>0.415</v>
+        <v>0.315</v>
       </c>
       <c r="I1046" s="15">
-        <v>11</v>
+        <v>8.3</v>
       </c>
       <c r="J1046" s="12">
         <v>46.4</v>
       </c>
       <c r="K1046" s="16">
-        <v>-42.2</v>
+        <v>-42.3</v>
       </c>
       <c r="L1046" s="15">
-        <v>-90.9</v>
+        <v>-91.2</v>
       </c>
       <c r="M1046" t="s">
         <v>1848</v>
@@ -60638,7 +60656,7 @@
         <v>841</v>
       </c>
       <c r="B1047" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1047" t="s">
         <v>721</v>
@@ -60650,22 +60668,22 @@
         <v>430</v>
       </c>
       <c r="F1047" s="12">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="G1047" s="13">
         <v>5.363</v>
       </c>
       <c r="H1047" s="14">
-        <v>0.887</v>
+        <v>0.937</v>
       </c>
       <c r="I1047" s="15">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="J1047" s="12">
         <v>100.917</v>
       </c>
       <c r="K1047" s="16">
-        <v>-94.667</v>
+        <v>-94.617</v>
       </c>
       <c r="L1047" s="15">
         <v>-93.8</v>
@@ -60679,7 +60697,7 @@
         <v>841</v>
       </c>
       <c r="B1048" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1048" t="s">
         <v>721</v>
@@ -60691,25 +60709,25 @@
         <v>522</v>
       </c>
       <c r="F1048" s="12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G1048" s="13">
         <v>9.134</v>
       </c>
       <c r="H1048" s="14">
-        <v>0.866</v>
+        <v>1.366</v>
       </c>
       <c r="I1048" s="15">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="J1048" s="12">
         <v>73.8</v>
       </c>
       <c r="K1048" s="16">
-        <v>-63.8</v>
+        <v>-63.3</v>
       </c>
       <c r="L1048" s="15">
-        <v>-86.4</v>
+        <v>-85.8</v>
       </c>
       <c r="M1048" t="s">
         <v>1850</v>
@@ -60720,7 +60738,7 @@
         <v>841</v>
       </c>
       <c r="B1049" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C1049" t="s">
         <v>721</v>
@@ -60761,10 +60779,10 @@
         <v>841</v>
       </c>
       <c r="B1050" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1050" s="4" t="s">
         <v>869</v>
-      </c>
-      <c r="C1050" s="4" t="s">
-        <v>870</v>
       </c>
       <c r="D1050" s="4" t="s">
         <v>574</v>
@@ -60794,10 +60812,10 @@
         <v>841</v>
       </c>
       <c r="B1051" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1051" t="s">
         <v>869</v>
-      </c>
-      <c r="C1051" t="s">
-        <v>870</v>
       </c>
       <c r="D1051" t="s">
         <v>574</v>
@@ -60835,10 +60853,10 @@
         <v>841</v>
       </c>
       <c r="B1052" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1052" t="s">
         <v>869</v>
-      </c>
-      <c r="C1052" t="s">
-        <v>870</v>
       </c>
       <c r="D1052" t="s">
         <v>574</v>
@@ -60876,10 +60894,10 @@
         <v>841</v>
       </c>
       <c r="B1053" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1053" t="s">
         <v>869</v>
-      </c>
-      <c r="C1053" t="s">
-        <v>870</v>
       </c>
       <c r="D1053" t="s">
         <v>574</v>
@@ -60917,10 +60935,10 @@
         <v>841</v>
       </c>
       <c r="B1054" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1054" t="s">
         <v>869</v>
-      </c>
-      <c r="C1054" t="s">
-        <v>870</v>
       </c>
       <c r="D1054" t="s">
         <v>574</v>
@@ -60958,10 +60976,10 @@
         <v>841</v>
       </c>
       <c r="B1055" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1055" t="s">
         <v>869</v>
-      </c>
-      <c r="C1055" t="s">
-        <v>870</v>
       </c>
       <c r="D1055" t="s">
         <v>574</v>
@@ -60999,10 +61017,10 @@
         <v>841</v>
       </c>
       <c r="B1056" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1056" t="s">
         <v>869</v>
-      </c>
-      <c r="C1056" t="s">
-        <v>870</v>
       </c>
       <c r="D1056" t="s">
         <v>574</v>
@@ -61040,10 +61058,10 @@
         <v>841</v>
       </c>
       <c r="B1057" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1057" t="s">
         <v>869</v>
-      </c>
-      <c r="C1057" t="s">
-        <v>870</v>
       </c>
       <c r="D1057" t="s">
         <v>574</v>
@@ -61417,7 +61435,7 @@
       </c>
       <c r="G1066" s="9"/>
       <c r="H1066" s="10">
-        <v>2.235</v>
+        <v>1.665</v>
       </c>
       <c r="I1066" s="11"/>
       <c r="J1066" s="8"/>
@@ -61449,22 +61467,22 @@
         <v>9</v>
       </c>
       <c r="G1067" s="13">
-        <v>7.879</v>
+        <v>8.235</v>
       </c>
       <c r="H1067" s="14">
-        <v>1.121</v>
+        <v>0.765</v>
       </c>
       <c r="I1067" s="15">
-        <v>14.2</v>
+        <v>9.3</v>
       </c>
       <c r="J1067" s="12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="K1067" s="16">
-        <v>-7.5</v>
+        <v>-8</v>
       </c>
       <c r="L1067" s="15">
-        <v>-45.4</v>
+        <v>-47.1</v>
       </c>
       <c r="M1067" t="s">
         <v>1866</v>
@@ -61490,22 +61508,22 @@
         <v>5.1</v>
       </c>
       <c r="G1068" s="13">
-        <v>4.327</v>
+        <v>4.395</v>
       </c>
       <c r="H1068" s="14">
-        <v>0.773</v>
+        <v>0.705</v>
       </c>
       <c r="I1068" s="15">
-        <v>17.9</v>
+        <v>16</v>
       </c>
       <c r="J1068" s="12">
-        <v>16.083</v>
+        <v>16.167</v>
       </c>
       <c r="K1068" s="16">
-        <v>-10.983</v>
+        <v>-11.067</v>
       </c>
       <c r="L1068" s="15">
-        <v>-68.3</v>
+        <v>-68.4</v>
       </c>
       <c r="M1068" t="s">
         <v>1867</v>
@@ -61531,22 +61549,22 @@
         <v>3.55</v>
       </c>
       <c r="G1069" s="13">
-        <v>3.48</v>
+        <v>3.422</v>
       </c>
       <c r="H1069" s="14">
-        <v>0.07</v>
+        <v>0.128</v>
       </c>
       <c r="I1069" s="15">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J1069" s="12">
-        <v>20.5</v>
+        <v>20.425</v>
       </c>
       <c r="K1069" s="16">
-        <v>-16.95</v>
+        <v>-16.875</v>
       </c>
       <c r="L1069" s="15">
-        <v>-82.7</v>
+        <v>-82.6</v>
       </c>
       <c r="M1069" t="s">
         <v>1868</v>
@@ -61572,22 +61590,22 @@
         <v>4.15</v>
       </c>
       <c r="G1070" s="13">
-        <v>3.64</v>
+        <v>3.701</v>
       </c>
       <c r="H1070" s="14">
-        <v>0.51</v>
+        <v>0.449</v>
       </c>
       <c r="I1070" s="15">
-        <v>14</v>
+        <v>12.1</v>
       </c>
       <c r="J1070" s="12">
-        <v>34.3</v>
+        <v>34.7</v>
       </c>
       <c r="K1070" s="16">
-        <v>-30.15</v>
+        <v>-30.55</v>
       </c>
       <c r="L1070" s="15">
-        <v>-87.9</v>
+        <v>-88</v>
       </c>
       <c r="M1070" t="s">
         <v>1869</v>
@@ -61613,19 +61631,19 @@
         <v>6.5</v>
       </c>
       <c r="G1071" s="13">
-        <v>5.534</v>
+        <v>5.401</v>
       </c>
       <c r="H1071" s="14">
-        <v>0.966</v>
+        <v>1.099</v>
       </c>
       <c r="I1071" s="15">
-        <v>17.5</v>
+        <v>20.4</v>
       </c>
       <c r="J1071" s="12">
-        <v>69.25</v>
+        <v>69.083</v>
       </c>
       <c r="K1071" s="16">
-        <v>-62.75</v>
+        <v>-62.583</v>
       </c>
       <c r="L1071" s="15">
         <v>-90.6</v>
@@ -61654,22 +61672,22 @@
         <v>10.25</v>
       </c>
       <c r="G1072" s="13">
-        <v>9.491</v>
+        <v>9.151</v>
       </c>
       <c r="H1072" s="14">
-        <v>0.759</v>
+        <v>1.099</v>
       </c>
       <c r="I1072" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1072" s="12">
-        <v>66.4</v>
+        <v>65.6</v>
       </c>
       <c r="K1072" s="16">
-        <v>-56.15</v>
+        <v>-55.35</v>
       </c>
       <c r="L1072" s="15">
-        <v>-84.6</v>
+        <v>-84.4</v>
       </c>
       <c r="M1072" t="s">
         <v>1871</v>
@@ -61737,7 +61755,7 @@
       </c>
       <c r="G1074" s="9"/>
       <c r="H1074" s="10">
-        <v>2.327</v>
+        <v>1.826</v>
       </c>
       <c r="I1074" s="11"/>
       <c r="J1074" s="8"/>
@@ -61769,25 +61787,25 @@
         <v>6.7</v>
       </c>
       <c r="G1075" s="13">
-        <v>6</v>
+        <v>6.333</v>
       </c>
       <c r="H1075" s="14">
-        <v>0.7</v>
+        <v>0.367</v>
       </c>
       <c r="I1075" s="15">
-        <v>11.7</v>
+        <v>5.8</v>
       </c>
       <c r="J1075" s="12">
-        <v>13.5</v>
+        <v>14.25</v>
       </c>
       <c r="K1075" s="16">
-        <v>-6.8</v>
+        <v>-7.55</v>
       </c>
       <c r="L1075" s="15">
-        <v>-50.4</v>
+        <v>-53</v>
       </c>
       <c r="M1075" t="s">
-        <v>1154</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1076" spans="1:13" x14ac:dyDescent="0.25">
@@ -61810,22 +61828,22 @@
         <v>4.2</v>
       </c>
       <c r="G1076" s="13">
-        <v>3.72</v>
+        <v>3.749</v>
       </c>
       <c r="H1076" s="14">
-        <v>0.48</v>
+        <v>0.451</v>
       </c>
       <c r="I1076" s="15">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="J1076" s="12">
-        <v>15.667</v>
+        <v>16.333</v>
       </c>
       <c r="K1076" s="16">
-        <v>-11.467</v>
+        <v>-12.133</v>
       </c>
       <c r="L1076" s="15">
-        <v>-73.2</v>
+        <v>-74.3</v>
       </c>
       <c r="M1076" t="s">
         <v>1873</v>
@@ -61851,25 +61869,25 @@
         <v>3.3</v>
       </c>
       <c r="G1077" s="13">
-        <v>3.234</v>
+        <v>3.225</v>
       </c>
       <c r="H1077" s="14">
-        <v>0.066</v>
+        <v>0.075</v>
       </c>
       <c r="I1077" s="15">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J1077" s="12">
-        <v>28.25</v>
+        <v>28.425</v>
       </c>
       <c r="K1077" s="16">
-        <v>-24.95</v>
+        <v>-25.125</v>
       </c>
       <c r="L1077" s="15">
-        <v>-88.3</v>
+        <v>-88.4</v>
       </c>
       <c r="M1077" t="s">
-        <v>1433</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1078" spans="1:13" x14ac:dyDescent="0.25">
@@ -61892,25 +61910,25 @@
         <v>4.35</v>
       </c>
       <c r="G1078" s="13">
-        <v>4.232</v>
+        <v>4.156</v>
       </c>
       <c r="H1078" s="14">
-        <v>0.118</v>
+        <v>0.194</v>
       </c>
       <c r="I1078" s="15">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J1078" s="12">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="K1078" s="16">
-        <v>-53.15</v>
+        <v>-53.05</v>
       </c>
       <c r="L1078" s="15">
         <v>-92.4</v>
       </c>
       <c r="M1078" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1079" spans="1:13" x14ac:dyDescent="0.25">
@@ -61933,25 +61951,25 @@
         <v>8.5</v>
       </c>
       <c r="G1079" s="13">
-        <v>6.516</v>
+        <v>6.263</v>
       </c>
       <c r="H1079" s="14">
-        <v>1.984</v>
+        <v>2.237</v>
       </c>
       <c r="I1079" s="15">
-        <v>30.5</v>
+        <v>35.7</v>
       </c>
       <c r="J1079" s="12">
-        <v>115.333</v>
+        <v>115</v>
       </c>
       <c r="K1079" s="16">
-        <v>-106.833</v>
+        <v>-106.5</v>
       </c>
       <c r="L1079" s="15">
         <v>-92.6</v>
       </c>
       <c r="M1079" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1080" spans="1:13" x14ac:dyDescent="0.25">
@@ -61992,7 +62010,7 @@
         <v>-86.2</v>
       </c>
       <c r="M1080" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1081" spans="1:13" x14ac:dyDescent="0.25">
@@ -62033,7 +62051,7 @@
         <v>-85.4</v>
       </c>
       <c r="M1081" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1082" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -62066,7 +62084,7 @@
       </c>
       <c r="L1082" s="11"/>
       <c r="M1082" s="4" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1083" spans="1:13" x14ac:dyDescent="0.25">
@@ -62107,7 +62125,7 @@
         <v>-46.4</v>
       </c>
       <c r="M1083" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1084" spans="1:13" x14ac:dyDescent="0.25">
@@ -62148,7 +62166,7 @@
         <v>-70.2</v>
       </c>
       <c r="M1084" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1085" spans="1:13" x14ac:dyDescent="0.25">
@@ -62189,7 +62207,7 @@
         <v>-80.3</v>
       </c>
       <c r="M1085" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1086" spans="1:13" x14ac:dyDescent="0.25">
@@ -62230,7 +62248,7 @@
         <v>-84</v>
       </c>
       <c r="M1086" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1087" spans="1:13" x14ac:dyDescent="0.25">
@@ -62271,7 +62289,7 @@
         <v>-86</v>
       </c>
       <c r="M1087" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1088" spans="1:13" x14ac:dyDescent="0.25">
@@ -62312,7 +62330,7 @@
         <v>-78.9</v>
       </c>
       <c r="M1088" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="1089" spans="1:13" x14ac:dyDescent="0.25">
@@ -62353,7 +62371,7 @@
         <v>-84.7</v>
       </c>
       <c r="M1089" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1090" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -62377,7 +62395,7 @@
       </c>
       <c r="G1090" s="9"/>
       <c r="H1090" s="10">
-        <v>1.449</v>
+        <v>1.002</v>
       </c>
       <c r="I1090" s="11"/>
       <c r="J1090" s="8"/>
@@ -62409,25 +62427,25 @@
         <v>8.1</v>
       </c>
       <c r="G1091" s="13">
-        <v>7.271</v>
+        <v>7.459</v>
       </c>
       <c r="H1091" s="14">
-        <v>0.829</v>
+        <v>0.641</v>
       </c>
       <c r="I1091" s="15">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="J1091" s="12">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
       <c r="K1091" s="16">
-        <v>-6.65</v>
+        <v>-7.15</v>
       </c>
       <c r="L1091" s="15">
-        <v>-45.1</v>
+        <v>-46.9</v>
       </c>
       <c r="M1091" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1092" spans="1:13" x14ac:dyDescent="0.25">
@@ -62450,25 +62468,25 @@
         <v>4.8</v>
       </c>
       <c r="G1092" s="13">
-        <v>4.217</v>
+        <v>4.309</v>
       </c>
       <c r="H1092" s="14">
-        <v>0.583</v>
+        <v>0.491</v>
       </c>
       <c r="I1092" s="15">
-        <v>13.8</v>
+        <v>11.4</v>
       </c>
       <c r="J1092" s="12">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="K1092" s="16">
-        <v>-10.2</v>
+        <v>-10.6</v>
       </c>
       <c r="L1092" s="15">
-        <v>-68</v>
+        <v>-68.8</v>
       </c>
       <c r="M1092" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1093" spans="1:13" x14ac:dyDescent="0.25">
@@ -62488,28 +62506,28 @@
         <v>423</v>
       </c>
       <c r="F1093" s="12">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G1093" s="13">
-        <v>3.287</v>
+        <v>3.36</v>
       </c>
       <c r="H1093" s="14">
-        <v>0.363</v>
+        <v>0.44</v>
       </c>
       <c r="I1093" s="15">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="J1093" s="12">
-        <v>19.125</v>
+        <v>19.75</v>
       </c>
       <c r="K1093" s="16">
-        <v>-15.475</v>
+        <v>-15.95</v>
       </c>
       <c r="L1093" s="15">
-        <v>-80.9</v>
+        <v>-80.8</v>
       </c>
       <c r="M1093" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1094" spans="1:13" x14ac:dyDescent="0.25">
@@ -62532,25 +62550,25 @@
         <v>4.4</v>
       </c>
       <c r="G1094" s="13">
-        <v>3.96</v>
+        <v>3.912</v>
       </c>
       <c r="H1094" s="14">
-        <v>0.44</v>
+        <v>0.488</v>
       </c>
       <c r="I1094" s="15">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="J1094" s="12">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="K1094" s="16">
-        <v>-29.4</v>
+        <v>-29.3</v>
       </c>
       <c r="L1094" s="15">
-        <v>-87</v>
+        <v>-86.9</v>
       </c>
       <c r="M1094" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="1095" spans="1:13" x14ac:dyDescent="0.25">
@@ -62570,28 +62588,28 @@
         <v>430</v>
       </c>
       <c r="F1095" s="12">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="G1095" s="13">
-        <v>5.548</v>
+        <v>5.478</v>
       </c>
       <c r="H1095" s="14">
-        <v>0.852</v>
+        <v>0.822</v>
       </c>
       <c r="I1095" s="15">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="J1095" s="12">
-        <v>74.333</v>
+        <v>74.25</v>
       </c>
       <c r="K1095" s="16">
-        <v>-67.933</v>
+        <v>-67.95</v>
       </c>
       <c r="L1095" s="15">
-        <v>-91.4</v>
+        <v>-91.5</v>
       </c>
       <c r="M1095" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1096" spans="1:13" x14ac:dyDescent="0.25">
@@ -62611,28 +62629,28 @@
         <v>522</v>
       </c>
       <c r="F1096" s="12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G1096" s="13">
-        <v>9.812</v>
+        <v>9.399</v>
       </c>
       <c r="H1096" s="14">
-        <v>0.688</v>
+        <v>0.601</v>
       </c>
       <c r="I1096" s="15">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J1096" s="12">
-        <v>62.2</v>
+        <v>61.2</v>
       </c>
       <c r="K1096" s="16">
-        <v>-51.7</v>
+        <v>-51.2</v>
       </c>
       <c r="L1096" s="15">
-        <v>-83.1</v>
+        <v>-83.7</v>
       </c>
       <c r="M1096" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1097" spans="1:13" x14ac:dyDescent="0.25">
@@ -62652,28 +62670,28 @@
         <v>634</v>
       </c>
       <c r="F1097" s="12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G1097" s="13">
-        <v>11.618</v>
+        <v>10.95</v>
       </c>
       <c r="H1097" s="14">
-        <v>0.882</v>
+        <v>1.05</v>
       </c>
       <c r="I1097" s="15">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="J1097" s="12">
-        <v>93</v>
+        <v>88.6</v>
       </c>
       <c r="K1097" s="16">
-        <v>-80.5</v>
+        <v>-76.6</v>
       </c>
       <c r="L1097" s="15">
-        <v>-86.6</v>
+        <v>-86.5</v>
       </c>
       <c r="M1097" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
   </sheetData>
@@ -62694,162 +62712,162 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B4">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B6" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B7" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B8" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B12" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B13" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B17">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B18" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B19" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B20" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -62863,19 +62881,19 @@
         <v>21</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="I25" s="21" t="s">
         <v>1932</v>
@@ -62927,10 +62945,10 @@
         <v>1943</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>1933</v>
+        <v>1944</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -62944,22 +62962,22 @@
         <v>423</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -62976,25 +62994,25 @@
         <v>1933</v>
       </c>
       <c r="C29" s="21" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>1956</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>1957</v>
+      </c>
+      <c r="I29" s="21" t="s">
         <v>1951</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>1951</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>1952</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>1953</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>1954</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>1955</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -63005,25 +63023,25 @@
         <v>21</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>1937</v>
+        <v>1959</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -63031,28 +63049,28 @@
         <v>522</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>1937</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>1939</v>
+        <v>1966</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>1959</v>
+        <v>1967</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>1960</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -63060,33 +63078,33 @@
         <v>634</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>1963</v>
+        <v>1968</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>1927</v>
+        <v>1969</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
     </row>
   </sheetData>
@@ -63097,7 +63115,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -63111,109 +63129,109 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>1967</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>1968</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="B5">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>22</v>
       </c>
       <c r="D5">
-        <v>12300</v>
+        <v>12600</v>
       </c>
       <c r="E5">
         <v>9065</v>
       </c>
       <c r="F5" s="23">
-        <v>-3235</v>
+        <v>-3535</v>
       </c>
       <c r="G5" s="24">
-        <v>-0.2630081300813008</v>
+        <v>-0.28055555555555556</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
       <c r="B6">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>12300</v>
+        <v>12600</v>
       </c>
       <c r="E6">
-        <v>6875</v>
+        <v>7615</v>
       </c>
       <c r="F6" s="23">
-        <v>-5425</v>
+        <v>-4985</v>
       </c>
       <c r="G6" s="24">
-        <v>-0.4410569105691057</v>
+        <v>-0.3956349206349206</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="B7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>12300</v>
+        <v>12600</v>
       </c>
       <c r="E7">
-        <v>12335</v>
+        <v>12700</v>
       </c>
       <c r="F7" s="7">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="G7" s="24">
-        <v>0.002845528455284553</v>
+        <v>0.007936507936507936</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -63233,25 +63251,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1983</v>
+        <v>1989</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1985</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -67928,129 +67946,174 @@
         <v>250</v>
       </c>
     </row>
-    <row r="135" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="19" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>841</v>
+      </c>
+      <c r="B134" t="s">
+        <v>179</v>
+      </c>
+      <c r="C134" t="s">
+        <v>776</v>
+      </c>
+      <c r="D134" t="s">
+        <v>31</v>
+      </c>
+      <c r="E134" t="s">
+        <v>848</v>
+      </c>
+      <c r="F134" t="s">
+        <v>423</v>
+      </c>
+      <c r="G134" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H134" t="s">
+        <v>452</v>
+      </c>
+      <c r="I134" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J134" s="26">
+        <v>-3335</v>
+      </c>
+      <c r="K134" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L134" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>841</v>
+      </c>
+      <c r="B135" t="s">
+        <v>183</v>
+      </c>
+      <c r="C135" t="s">
+        <v>776</v>
+      </c>
+      <c r="D135" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" t="s">
+        <v>850</v>
+      </c>
+      <c r="F135" t="s">
+        <v>438</v>
+      </c>
+      <c r="G135" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H135" t="s">
+        <v>522</v>
+      </c>
+      <c r="I135" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J135" s="26">
+        <v>-3435</v>
+      </c>
+      <c r="K135" s="27">
+        <v>640</v>
+      </c>
+      <c r="L135" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>841</v>
+      </c>
+      <c r="B136" t="s">
+        <v>501</v>
+      </c>
+      <c r="C136" t="s">
+        <v>393</v>
+      </c>
+      <c r="D136" t="s">
+        <v>401</v>
+      </c>
+      <c r="E136" t="s">
+        <v>854</v>
+      </c>
+      <c r="F136" t="s">
+        <v>438</v>
+      </c>
+      <c r="G136" s="12">
+        <v>6</v>
+      </c>
+      <c r="H136" t="s">
+        <v>423</v>
+      </c>
+      <c r="I136" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J136" s="26">
+        <v>-3535</v>
+      </c>
+      <c r="K136" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L136" s="27">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="19" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C136" s="2" t="s">
+      <c r="B139" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>1988</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>1989</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>1990</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>421</v>
-      </c>
-      <c r="B137">
-        <v>7</v>
-      </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-      <c r="D137" s="27">
-        <v>50</v>
-      </c>
-      <c r="E137" s="27">
-        <v>50</v>
-      </c>
-      <c r="F137" s="27">
-        <v>-280</v>
-      </c>
-      <c r="G137" s="27">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>449</v>
-      </c>
-      <c r="B138">
-        <v>12</v>
-      </c>
-      <c r="C138">
-        <v>3</v>
-      </c>
-      <c r="D138" s="27">
-        <v>225</v>
-      </c>
-      <c r="E138" s="27">
-        <v>275</v>
-      </c>
-      <c r="F138" s="27">
-        <v>-1085</v>
-      </c>
-      <c r="G138" s="27">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>487</v>
-      </c>
-      <c r="B139">
-        <v>6</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-      <c r="D139" s="27">
-        <v>-600</v>
-      </c>
-      <c r="E139" s="27">
-        <v>-325</v>
-      </c>
-      <c r="F139" s="27">
-        <v>-655</v>
-      </c>
-      <c r="G139" s="27">
-        <v>1465</v>
+      <c r="D139" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>518</v>
+        <v>421</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140" s="27">
-        <v>-600</v>
+        <v>50</v>
       </c>
       <c r="E140" s="27">
-        <v>-925</v>
+        <v>50</v>
       </c>
       <c r="F140" s="27">
-        <v>-1255</v>
+        <v>-280</v>
       </c>
       <c r="G140" s="27">
-        <v>1395</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>545</v>
+        <v>449</v>
       </c>
       <c r="B141">
         <v>12</v>
@@ -68059,131 +68122,200 @@
         <v>3</v>
       </c>
       <c r="D141" s="27">
-        <v>-15</v>
+        <v>225</v>
       </c>
       <c r="E141" s="27">
-        <v>-940</v>
+        <v>275</v>
       </c>
       <c r="F141" s="27">
-        <v>-1820</v>
+        <v>-1085</v>
       </c>
       <c r="G141" s="27">
-        <v>1660</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>595</v>
+        <v>487</v>
       </c>
       <c r="B142">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D142" s="27">
-        <v>-795</v>
+        <v>-600</v>
       </c>
       <c r="E142" s="27">
-        <v>-1735</v>
+        <v>-325</v>
       </c>
       <c r="F142" s="27">
-        <v>-2585</v>
+        <v>-655</v>
       </c>
       <c r="G142" s="27">
-        <v>1155</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>705</v>
+        <v>518</v>
       </c>
       <c r="B143">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D143" s="27">
-        <v>-595</v>
+        <v>-600</v>
       </c>
       <c r="E143" s="27">
-        <v>-2330</v>
+        <v>-925</v>
       </c>
       <c r="F143" s="27">
-        <v>-5065</v>
+        <v>-1255</v>
       </c>
       <c r="G143" s="27">
-        <v>940</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>775</v>
+        <v>545</v>
       </c>
       <c r="B144">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" s="27">
-        <v>-295</v>
+        <v>-15</v>
       </c>
       <c r="E144" s="27">
-        <v>-2625</v>
+        <v>-940</v>
       </c>
       <c r="F144" s="27">
-        <v>-4735</v>
+        <v>-1820</v>
       </c>
       <c r="G144" s="27">
-        <v>645</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>811</v>
+        <v>595</v>
       </c>
       <c r="B145">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D145" s="27">
-        <v>-860</v>
+        <v>-795</v>
       </c>
       <c r="E145" s="27">
-        <v>-3485</v>
+        <v>-1735</v>
       </c>
       <c r="F145" s="27">
-        <v>-5325</v>
+        <v>-2585</v>
       </c>
       <c r="G145" s="27">
-        <v>-215</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>705</v>
+      </c>
+      <c r="B146">
+        <v>28</v>
+      </c>
+      <c r="C146">
+        <v>6</v>
+      </c>
+      <c r="D146" s="27">
+        <v>-595</v>
+      </c>
+      <c r="E146" s="27">
+        <v>-2330</v>
+      </c>
+      <c r="F146" s="27">
+        <v>-5065</v>
+      </c>
+      <c r="G146" s="27">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>775</v>
+      </c>
+      <c r="B147">
+        <v>10</v>
+      </c>
+      <c r="C147">
+        <v>2</v>
+      </c>
+      <c r="D147" s="27">
+        <v>-295</v>
+      </c>
+      <c r="E147" s="27">
+        <v>-2625</v>
+      </c>
+      <c r="F147" s="27">
+        <v>-4735</v>
+      </c>
+      <c r="G147" s="27">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>811</v>
+      </c>
+      <c r="B148">
+        <v>12</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+      <c r="D148" s="27">
+        <v>-860</v>
+      </c>
+      <c r="E148" s="27">
+        <v>-3485</v>
+      </c>
+      <c r="F148" s="27">
+        <v>-5325</v>
+      </c>
+      <c r="G148" s="27">
+        <v>-215</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>841</v>
       </c>
-      <c r="B146">
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149">
         <v>1</v>
       </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146" s="27">
-        <v>250</v>
-      </c>
-      <c r="E146" s="27">
-        <v>-3235</v>
-      </c>
-      <c r="F146" s="27">
-        <v>-5425</v>
-      </c>
-      <c r="G146" s="27">
-        <v>35</v>
+      <c r="D149" s="27">
+        <v>-50</v>
+      </c>
+      <c r="E149" s="27">
+        <v>-3535</v>
+      </c>
+      <c r="F149" s="27">
+        <v>-4985</v>
+      </c>
+      <c r="G149" s="27">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -68206,7 +68338,7 @@
         <v>885</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>441</v>
@@ -68224,12 +68356,12 @@
         <v>438</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="B2">
         <v>340</v>
@@ -68255,10 +68387,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="B3">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -68267,7 +68399,7 @@
         <v>61</v>
       </c>
       <c r="E3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>75</v>
@@ -68281,10 +68413,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="B4">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C4">
         <v>23</v>
@@ -68302,15 +68434,15 @@
         <v>48</v>
       </c>
       <c r="H4">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="B5">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -68322,7 +68454,7 @@
         <v>82</v>
       </c>
       <c r="F5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>67</v>
@@ -68333,7 +68465,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="B6">
         <v>313</v>
@@ -68359,7 +68491,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="B7">
         <v>294</v>
@@ -68385,7 +68517,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="B8">
         <v>284</v>
@@ -68411,7 +68543,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="B9">
         <v>262</v>
@@ -68437,7 +68569,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B10">
         <v>242</v>
@@ -68463,7 +68595,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="B11">
         <v>219</v>
@@ -68503,12 +68635,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -68519,18 +68651,18 @@
         <v>886</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>441</v>
@@ -68539,7 +68671,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="E5" s="23">
         <v>11</v>
@@ -68547,7 +68679,7 @@
     </row>
     <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>433</v>
@@ -68556,7 +68688,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="E6" s="23">
         <v>57</v>
@@ -68564,7 +68696,7 @@
     </row>
     <row r="8" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -68587,12 +68719,12 @@
         <v>438</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="B10" s="3">
         <v>4</v>
@@ -68615,76 +68747,76 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
       </c>
       <c r="E11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="B12" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6</v>
+      </c>
+      <c r="G12" s="3">
         <v>0</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3">
-        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3">
+        <v>4</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3">
-        <v>2</v>
-      </c>
       <c r="G13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -68707,7 +68839,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -68730,7 +68862,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -68753,7 +68885,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="B17" s="3">
         <v>7</v>
@@ -68776,7 +68908,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B18" s="31">
         <v>32</v>
@@ -68799,7 +68931,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="B19" s="3">
         <v>8</v>
@@ -68836,7 +68968,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -68846,62 +68978,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2013</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2016</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2021</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -68911,82 +69043,82 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2027</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2028</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2029</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2033</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2037</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2038</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2039</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2040</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -68996,22 +69128,22 @@
     </row>
     <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>2041</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2042</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2043</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
@@ -69021,27 +69153,27 @@
     </row>
     <row r="38" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2046</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2047</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2049</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -69051,12 +69183,12 @@
     </row>
     <row r="44" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5708,7 +5708,7 @@
     <t>2:5=125 5:2=80 负其他=34 平其他=100 胜其他=26</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-14T22:00:05+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-14T23:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -18484,8 +18484,8 @@
       <c r="F132" t="s">
         <v>868</v>
       </c>
-      <c r="G132" s="5" t="s">
-        <v>70</v>
+      <c r="G132" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>21</v>
@@ -18625,8 +18625,8 @@
       <c r="F135" t="s">
         <v>868</v>
       </c>
-      <c r="G135" s="5" t="s">
-        <v>70</v>
+      <c r="G135" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>21</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5690,7 +5690,7 @@
     <t>2:5=125 5:2=80 负其他=34 平其他=100 胜其他=26</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-15T09:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-15T10:00:03+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -5690,7 +5690,7 @@
     <t>2:5=125 5:2=80 负其他=34 平其他=100 胜其他=26</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-15T10:00:03+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-15T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -2723,6 +2723,9 @@
     <t>3球 @3.85 ⚡</t>
   </si>
   <si>
+    <t>10-15 19:00</t>
+  </si>
+  <si>
     <t>10-16 03:00</t>
   </si>
   <si>
@@ -2750,9 +2753,6 @@
     <t>格风暴</t>
   </si>
   <si>
-    <t>4球 @4 ⚡</t>
-  </si>
-  <si>
     <t>3球 @3.7 ⚡</t>
   </si>
   <si>
@@ -6098,25 +6098,25 @@
     <t>2:5=250 5:2=100 负其他=70 平其他=200 胜其他=45</t>
   </si>
   <si>
-    <t>0:1=36 1:0=9</t>
-  </si>
-  <si>
-    <t>0:2=80 1:1=12.5 2:0=6.3</t>
-  </si>
-  <si>
-    <t>0:3=350 1:2=38 2:1=9.25 3:0=6.75</t>
+    <t>0:1=40 1:0=9.5</t>
+  </si>
+  <si>
+    <t>0:2=80 1:1=13 2:0=6.3</t>
+  </si>
+  <si>
+    <t>0:3=350 1:2=40 2:1=9.25 3:0=6.75</t>
   </si>
   <si>
     <t>0:4=850 1:3=120 2:2=24 3:1=9.5 4:0=9</t>
   </si>
   <si>
-    <t>0:5=1000 1:4=550 2:3=90 3:2=26 4:1=12 5:0=14</t>
-  </si>
-  <si>
-    <t>1:5=1000 2:4=450 3:3=80 4:2=35 5:1=21</t>
-  </si>
-  <si>
-    <t>2:5=1000 5:2=55 负其他=350 平其他=400 胜其他=9.5</t>
+    <t>0:5=1000 1:4=550 2:3=90 3:2=26 4:1=11 5:0=14</t>
+  </si>
+  <si>
+    <t>1:5=1000 2:4=450 3:3=80 4:2=30 5:1=20</t>
+  </si>
+  <si>
+    <t>2:5=1000 5:2=50 负其他=350 平其他=400 胜其他=9.25</t>
   </si>
   <si>
     <t>0:0=34</t>
@@ -6410,7 +6410,7 @@
     <t>2:5=300 5:2=175 负其他=95 平其他=275 胜其他=65</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-15T18:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-15T19:00:05+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -19757,7 +19757,7 @@
         <v>21</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>587</v>
+        <v>797</v>
       </c>
       <c r="J144" s="3" t="s">
         <v>900</v>
@@ -19772,7 +19772,7 @@
         <v>21</v>
       </c>
       <c r="N144" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="O144" t="s">
         <v>21</v>
@@ -19795,7 +19795,7 @@
         <v>113</v>
       </c>
       <c r="F145" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>70</v>
@@ -19830,7 +19830,7 @@
         <v>881</v>
       </c>
       <c r="B146" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C146" t="s">
         <v>882</v>
@@ -19839,10 +19839,10 @@
         <v>125</v>
       </c>
       <c r="E146" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F146" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>55</v>
@@ -19866,7 +19866,7 @@
         <v>21</v>
       </c>
       <c r="N146" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O146" t="s">
         <v>21</v>
@@ -19877,7 +19877,7 @@
         <v>881</v>
       </c>
       <c r="B147" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C147" t="s">
         <v>882</v>
@@ -19886,10 +19886,10 @@
         <v>132</v>
       </c>
       <c r="E147" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F147" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>55</v>
@@ -19901,10 +19901,10 @@
         <v>435</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="L147" t="s">
         <v>21</v>
@@ -19924,7 +19924,7 @@
         <v>881</v>
       </c>
       <c r="B148" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C148" t="s">
         <v>882</v>
@@ -19933,10 +19933,10 @@
         <v>68</v>
       </c>
       <c r="E148" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F148" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G148" t="s">
         <v>21</v>
@@ -19945,10 +19945,10 @@
         <v>21</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>685</v>
+        <v>814</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K148" s="3" t="s">
         <v>911</v>
@@ -19960,7 +19960,7 @@
         <v>21</v>
       </c>
       <c r="N148" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="O148" t="s">
         <v>21</v>
@@ -19983,7 +19983,7 @@
         <v>913</v>
       </c>
       <c r="F149" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>55</v>
@@ -20030,7 +20030,7 @@
         <v>590</v>
       </c>
       <c r="F150" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>55</v>
@@ -20101,7 +20101,7 @@
         <v>21</v>
       </c>
       <c r="N151" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O151" t="s">
         <v>21</v>
@@ -20148,7 +20148,7 @@
         <v>21</v>
       </c>
       <c r="N152" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O152" t="s">
         <v>21</v>
@@ -20195,7 +20195,7 @@
         <v>21</v>
       </c>
       <c r="N153" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O153" t="s">
         <v>21</v>
@@ -20242,7 +20242,7 @@
         <v>21</v>
       </c>
       <c r="N154" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O154" t="s">
         <v>21</v>
@@ -20289,7 +20289,7 @@
         <v>21</v>
       </c>
       <c r="N155" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O155" t="s">
         <v>21</v>
@@ -20336,7 +20336,7 @@
         <v>21</v>
       </c>
       <c r="N156" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O156" t="s">
         <v>21</v>
@@ -20383,7 +20383,7 @@
         <v>21</v>
       </c>
       <c r="N157" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O157" t="s">
         <v>21</v>
@@ -20430,7 +20430,7 @@
         <v>21</v>
       </c>
       <c r="N158" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O158" t="s">
         <v>21</v>
@@ -20477,7 +20477,7 @@
         <v>21</v>
       </c>
       <c r="N159" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O159" t="s">
         <v>21</v>
@@ -20524,7 +20524,7 @@
         <v>21</v>
       </c>
       <c r="N160" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O160" t="s">
         <v>21</v>
@@ -20571,7 +20571,7 @@
         <v>21</v>
       </c>
       <c r="N161" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O161" t="s">
         <v>21</v>
@@ -20618,7 +20618,7 @@
         <v>21</v>
       </c>
       <c r="N162" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O162" t="s">
         <v>21</v>
@@ -66151,7 +66151,7 @@
       </c>
       <c r="G1138" s="9"/>
       <c r="H1138" s="10">
-        <v>0.923</v>
+        <v>1.163</v>
       </c>
       <c r="I1138" s="11"/>
       <c r="J1138" s="8"/>
@@ -66180,25 +66180,25 @@
         <v>433</v>
       </c>
       <c r="F1139" s="12">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G1139" s="13">
         <v>3.409</v>
       </c>
       <c r="H1139" s="14">
-        <v>0.241</v>
+        <v>0.391</v>
       </c>
       <c r="I1139" s="15">
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
       <c r="J1139" s="12">
         <v>6.875</v>
       </c>
       <c r="K1139" s="16">
-        <v>-3.225</v>
+        <v>-3.075</v>
       </c>
       <c r="L1139" s="15">
-        <v>-46.9</v>
+        <v>-44.7</v>
       </c>
       <c r="M1139" t="s">
         <v>1998</v>
@@ -66221,25 +66221,25 @@
         <v>452</v>
       </c>
       <c r="F1140" s="12">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="G1140" s="13">
         <v>2.815</v>
       </c>
       <c r="H1140" s="14">
-        <v>0.135</v>
+        <v>0.035</v>
       </c>
       <c r="I1140" s="15">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J1140" s="12">
         <v>9.7</v>
       </c>
       <c r="K1140" s="16">
-        <v>-6.75</v>
+        <v>-6.85</v>
       </c>
       <c r="L1140" s="15">
-        <v>-69.6</v>
+        <v>-70.6</v>
       </c>
       <c r="M1140" t="s">
         <v>1999</v>
@@ -66303,25 +66303,25 @@
         <v>438</v>
       </c>
       <c r="F1142" s="12">
-        <v>7.35</v>
+        <v>7.4</v>
       </c>
       <c r="G1142" s="13">
         <v>5.52</v>
       </c>
       <c r="H1142" s="14">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="I1142" s="15">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="J1142" s="12">
         <v>42.8</v>
       </c>
       <c r="K1142" s="16">
-        <v>-35.45</v>
+        <v>-35.4</v>
       </c>
       <c r="L1142" s="15">
-        <v>-82.8</v>
+        <v>-82.7</v>
       </c>
       <c r="M1142" t="s">
         <v>2001</v>
@@ -66775,13 +66775,13 @@
         <v>881</v>
       </c>
       <c r="B1154" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1154" s="4" t="s">
         <v>125</v>
       </c>
       <c r="D1154" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1154" s="4" t="s">
         <v>441</v>
@@ -66808,13 +66808,13 @@
         <v>881</v>
       </c>
       <c r="B1155" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1155" t="s">
         <v>125</v>
       </c>
       <c r="D1155" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1155" t="s">
         <v>433</v>
@@ -66849,13 +66849,13 @@
         <v>881</v>
       </c>
       <c r="B1156" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1156" t="s">
         <v>125</v>
       </c>
       <c r="D1156" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1156" t="s">
         <v>452</v>
@@ -66890,13 +66890,13 @@
         <v>881</v>
       </c>
       <c r="B1157" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1157" t="s">
         <v>125</v>
       </c>
       <c r="D1157" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1157" t="s">
         <v>423</v>
@@ -66931,13 +66931,13 @@
         <v>881</v>
       </c>
       <c r="B1158" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1158" t="s">
         <v>125</v>
       </c>
       <c r="D1158" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1158" t="s">
         <v>438</v>
@@ -66972,13 +66972,13 @@
         <v>881</v>
       </c>
       <c r="B1159" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1159" t="s">
         <v>125</v>
       </c>
       <c r="D1159" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1159" t="s">
         <v>430</v>
@@ -67013,13 +67013,13 @@
         <v>881</v>
       </c>
       <c r="B1160" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1160" t="s">
         <v>125</v>
       </c>
       <c r="D1160" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1160" t="s">
         <v>522</v>
@@ -67054,13 +67054,13 @@
         <v>881</v>
       </c>
       <c r="B1161" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C1161" t="s">
         <v>125</v>
       </c>
       <c r="D1161" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E1161" t="s">
         <v>634</v>
@@ -67095,13 +67095,13 @@
         <v>881</v>
       </c>
       <c r="B1162" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1162" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D1162" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1162" s="4" t="s">
         <v>441</v>
@@ -67128,13 +67128,13 @@
         <v>881</v>
       </c>
       <c r="B1163" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1163" t="s">
         <v>132</v>
       </c>
       <c r="D1163" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1163" t="s">
         <v>433</v>
@@ -67169,13 +67169,13 @@
         <v>881</v>
       </c>
       <c r="B1164" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1164" t="s">
         <v>132</v>
       </c>
       <c r="D1164" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1164" t="s">
         <v>452</v>
@@ -67210,13 +67210,13 @@
         <v>881</v>
       </c>
       <c r="B1165" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1165" t="s">
         <v>132</v>
       </c>
       <c r="D1165" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1165" t="s">
         <v>423</v>
@@ -67251,13 +67251,13 @@
         <v>881</v>
       </c>
       <c r="B1166" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1166" t="s">
         <v>132</v>
       </c>
       <c r="D1166" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1166" t="s">
         <v>438</v>
@@ -67292,13 +67292,13 @@
         <v>881</v>
       </c>
       <c r="B1167" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1167" t="s">
         <v>132</v>
       </c>
       <c r="D1167" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1167" t="s">
         <v>430</v>
@@ -67333,13 +67333,13 @@
         <v>881</v>
       </c>
       <c r="B1168" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1168" t="s">
         <v>132</v>
       </c>
       <c r="D1168" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1168" t="s">
         <v>522</v>
@@ -67374,13 +67374,13 @@
         <v>881</v>
       </c>
       <c r="B1169" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C1169" t="s">
         <v>132</v>
       </c>
       <c r="D1169" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E1169" t="s">
         <v>634</v>
@@ -67415,23 +67415,23 @@
         <v>881</v>
       </c>
       <c r="B1170" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1170" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D1170" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1170" s="4" t="s">
         <v>441</v>
       </c>
       <c r="F1170" s="8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G1170" s="9"/>
       <c r="H1170" s="10">
-        <v>2.729</v>
+        <v>3.156</v>
       </c>
       <c r="I1170" s="11"/>
       <c r="J1170" s="8"/>
@@ -67440,7 +67440,7 @@
       </c>
       <c r="L1170" s="11"/>
       <c r="M1170" s="4" t="s">
-        <v>1913</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="1171" spans="1:13" x14ac:dyDescent="0.25">
@@ -67448,37 +67448,37 @@
         <v>881</v>
       </c>
       <c r="B1171" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1171" t="s">
         <v>68</v>
       </c>
       <c r="D1171" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1171" t="s">
         <v>433</v>
       </c>
       <c r="F1171" s="12">
-        <v>8.5</v>
+        <v>9.2</v>
       </c>
       <c r="G1171" s="13">
-        <v>7.2</v>
+        <v>7.677</v>
       </c>
       <c r="H1171" s="14">
-        <v>1.3</v>
+        <v>1.523</v>
       </c>
       <c r="I1171" s="15">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="J1171" s="12">
-        <v>22.5</v>
+        <v>24.75</v>
       </c>
       <c r="K1171" s="16">
-        <v>-14</v>
+        <v>-15.55</v>
       </c>
       <c r="L1171" s="15">
-        <v>-62.2</v>
+        <v>-62.8</v>
       </c>
       <c r="M1171" t="s">
         <v>2026</v>
@@ -67489,37 +67489,37 @@
         <v>881</v>
       </c>
       <c r="B1172" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1172" t="s">
         <v>68</v>
       </c>
       <c r="D1172" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1172" t="s">
         <v>452</v>
       </c>
       <c r="F1172" s="12">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="G1172" s="13">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="H1172" s="14">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="I1172" s="15">
-        <v>21.9</v>
+        <v>24.1</v>
       </c>
       <c r="J1172" s="12">
-        <v>32.933</v>
+        <v>33.1</v>
       </c>
       <c r="K1172" s="16">
-        <v>-28.083</v>
+        <v>-28.1</v>
       </c>
       <c r="L1172" s="15">
-        <v>-85.3</v>
+        <v>-84.9</v>
       </c>
       <c r="M1172" t="s">
         <v>2027</v>
@@ -67530,13 +67530,13 @@
         <v>881</v>
       </c>
       <c r="B1173" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1173" t="s">
         <v>68</v>
       </c>
       <c r="D1173" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1173" t="s">
         <v>423</v>
@@ -67545,19 +67545,19 @@
         <v>3.7</v>
       </c>
       <c r="G1173" s="13">
-        <v>3.503</v>
+        <v>3.52</v>
       </c>
       <c r="H1173" s="14">
-        <v>0.197</v>
+        <v>0.18</v>
       </c>
       <c r="I1173" s="15">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J1173" s="12">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="K1173" s="16">
-        <v>-97.3</v>
+        <v>-97.8</v>
       </c>
       <c r="L1173" s="15">
         <v>-96.3</v>
@@ -67571,37 +67571,37 @@
         <v>881</v>
       </c>
       <c r="B1174" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1174" t="s">
         <v>68</v>
       </c>
       <c r="D1174" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1174" t="s">
         <v>438</v>
       </c>
       <c r="F1174" s="12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G1174" s="13">
         <v>3.738</v>
       </c>
       <c r="H1174" s="14">
-        <v>0.262</v>
+        <v>0.162</v>
       </c>
       <c r="I1174" s="15">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="J1174" s="12">
         <v>202.5</v>
       </c>
       <c r="K1174" s="16">
-        <v>-198.5</v>
+        <v>-198.6</v>
       </c>
       <c r="L1174" s="15">
-        <v>-98</v>
+        <v>-98.1</v>
       </c>
       <c r="M1174" t="s">
         <v>2029</v>
@@ -67612,37 +67612,37 @@
         <v>881</v>
       </c>
       <c r="B1175" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1175" t="s">
         <v>68</v>
       </c>
       <c r="D1175" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1175" t="s">
         <v>430</v>
       </c>
       <c r="F1175" s="12">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="G1175" s="13">
-        <v>4.827</v>
+        <v>4.657</v>
       </c>
       <c r="H1175" s="14">
-        <v>1.173</v>
+        <v>1.093</v>
       </c>
       <c r="I1175" s="15">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="J1175" s="12">
-        <v>282</v>
+        <v>281.833</v>
       </c>
       <c r="K1175" s="16">
-        <v>-276</v>
+        <v>-276.083</v>
       </c>
       <c r="L1175" s="15">
-        <v>-97.9</v>
+        <v>-98</v>
       </c>
       <c r="M1175" t="s">
         <v>2030</v>
@@ -67653,37 +67653,37 @@
         <v>881</v>
       </c>
       <c r="B1176" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1176" t="s">
         <v>68</v>
       </c>
       <c r="D1176" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1176" t="s">
         <v>522</v>
       </c>
       <c r="F1176" s="12">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="G1176" s="13">
-        <v>10.88</v>
+        <v>10.095</v>
       </c>
       <c r="H1176" s="17">
-        <v>-1.38</v>
+        <v>-0.845</v>
       </c>
       <c r="I1176" s="15">
-        <v>-12.7</v>
+        <v>-8.4</v>
       </c>
       <c r="J1176" s="12">
-        <v>317.2</v>
+        <v>316</v>
       </c>
       <c r="K1176" s="16">
-        <v>-307.7</v>
+        <v>-306.75</v>
       </c>
       <c r="L1176" s="15">
-        <v>-97</v>
+        <v>-97.1</v>
       </c>
       <c r="M1176" t="s">
         <v>2031</v>
@@ -67694,37 +67694,37 @@
         <v>881</v>
       </c>
       <c r="B1177" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C1177" t="s">
         <v>68</v>
       </c>
       <c r="D1177" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E1177" t="s">
         <v>634</v>
       </c>
       <c r="F1177" s="12">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G1177" s="13">
-        <v>7.704</v>
+        <v>7.437</v>
       </c>
       <c r="H1177" s="14">
-        <v>2.296</v>
+        <v>2.063</v>
       </c>
       <c r="I1177" s="15">
-        <v>29.8</v>
+        <v>27.7</v>
       </c>
       <c r="J1177" s="12">
-        <v>362.9</v>
+        <v>361.85</v>
       </c>
       <c r="K1177" s="16">
-        <v>-352.9</v>
+        <v>-352.35</v>
       </c>
       <c r="L1177" s="15">
-        <v>-97.2</v>
+        <v>-97.4</v>
       </c>
       <c r="M1177" t="s">
         <v>2032</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13155" uniqueCount="2296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13155" uniqueCount="2295">
   <si>
     <t>日期</t>
   </si>
@@ -2672,13 +2672,13 @@
     <t>10-16 00:45</t>
   </si>
   <si>
-    <t>3球 @3.1</t>
-  </si>
-  <si>
-    <t>3球 @3.1 ⚡</t>
-  </si>
-  <si>
-    <t>10-15 17:00</t>
+    <t>3球 @3</t>
+  </si>
+  <si>
+    <t>3球 @3 ⚡</t>
+  </si>
+  <si>
+    <t>10-15 21:00</t>
   </si>
   <si>
     <t>托林斯</t>
@@ -2696,141 +2696,141 @@
     <t>波兹南</t>
   </si>
   <si>
+    <t>3球 @3.65 ⚡</t>
+  </si>
+  <si>
+    <t>圣吉联合</t>
+  </si>
+  <si>
+    <t>5球 @6.8 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.4 ⚡</t>
+  </si>
+  <si>
+    <t>萨尔茨堡</t>
+  </si>
+  <si>
+    <t>3球 @3.2</t>
+  </si>
+  <si>
+    <t>3球 @3.2 ⚡</t>
+  </si>
+  <si>
+    <t>欧协联</t>
+  </si>
+  <si>
+    <t>克拉约瓦</t>
+  </si>
+  <si>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
+    <t>10-16 03:00</t>
+  </si>
+  <si>
+    <t>2球 @3</t>
+  </si>
+  <si>
+    <t>周四009</t>
+  </si>
+  <si>
+    <t>贝西克塔</t>
+  </si>
+  <si>
+    <t>4球 @4.15 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.45 ⚡</t>
+  </si>
+  <si>
+    <t>周四010</t>
+  </si>
+  <si>
+    <t>奥林匹亚</t>
+  </si>
+  <si>
+    <t>3球 @3.3 ⚡</t>
+  </si>
+  <si>
+    <t>周四011</t>
+  </si>
+  <si>
+    <t>格风暴</t>
+  </si>
+  <si>
+    <t>6球 @8.7</t>
+  </si>
+  <si>
+    <t>3球 @3.75 ⚡</t>
+  </si>
+  <si>
+    <t>周四012</t>
+  </si>
+  <si>
+    <t>凯尔特人</t>
+  </si>
+  <si>
+    <t>4球 @3.9 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
+    <t>周四013</t>
+  </si>
+  <si>
+    <t>哥本哈根</t>
+  </si>
+  <si>
+    <t>周四014</t>
+  </si>
+  <si>
+    <t>拉普大学</t>
+  </si>
+  <si>
+    <t>10-16 08:30</t>
+  </si>
+  <si>
+    <t>3球 @4.15 ⚡</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>澳超</t>
+  </si>
+  <si>
+    <t>悉尼FC</t>
+  </si>
+  <si>
+    <t>西悉尼</t>
+  </si>
+  <si>
+    <t>10-16 17:00</t>
+  </si>
+  <si>
+    <t>6球 @13</t>
+  </si>
+  <si>
+    <t>3球 @3.7 ⚡</t>
+  </si>
+  <si>
+    <t>10-15 14:00</t>
+  </si>
+  <si>
+    <t>科特布斯</t>
+  </si>
+  <si>
+    <t>纽伦堡</t>
+  </si>
+  <si>
+    <t>10-17 00:30</t>
+  </si>
+  <si>
     <t>4球 @4.2 ⚡</t>
   </si>
   <si>
-    <t>3球 @3.65 ⚡</t>
-  </si>
-  <si>
-    <t>圣吉联合</t>
-  </si>
-  <si>
-    <t>5球 @6.8 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
-    <t>萨尔茨堡</t>
-  </si>
-  <si>
-    <t>3球 @3.2</t>
-  </si>
-  <si>
-    <t>3球 @3.2 ⚡</t>
-  </si>
-  <si>
-    <t>欧协联</t>
-  </si>
-  <si>
-    <t>克拉约瓦</t>
-  </si>
-  <si>
-    <t>3球 @3.85 ⚡</t>
-  </si>
-  <si>
-    <t>10-16 03:00</t>
-  </si>
-  <si>
-    <t>2球 @3</t>
-  </si>
-  <si>
-    <t>周四009</t>
-  </si>
-  <si>
-    <t>贝西克塔</t>
-  </si>
-  <si>
-    <t>4球 @4.15 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.45 ⚡</t>
-  </si>
-  <si>
-    <t>周四010</t>
-  </si>
-  <si>
-    <t>奥林匹亚</t>
-  </si>
-  <si>
-    <t>3球 @3.3 ⚡</t>
-  </si>
-  <si>
-    <t>周四011</t>
-  </si>
-  <si>
-    <t>格风暴</t>
-  </si>
-  <si>
-    <t>6球 @8.85</t>
-  </si>
-  <si>
-    <t>4球 @3.9 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
-  </si>
-  <si>
-    <t>周四012</t>
-  </si>
-  <si>
-    <t>凯尔特人</t>
-  </si>
-  <si>
-    <t>3球 @3.6 ⚡</t>
-  </si>
-  <si>
-    <t>周四013</t>
-  </si>
-  <si>
-    <t>哥本哈根</t>
-  </si>
-  <si>
-    <t>周四014</t>
-  </si>
-  <si>
-    <t>拉普大学</t>
-  </si>
-  <si>
-    <t>10-16 08:30</t>
-  </si>
-  <si>
-    <t>3球 @4.15 ⚡</t>
-  </si>
-  <si>
-    <t>10-15 14:00</t>
-  </si>
-  <si>
-    <t>2026-10-16</t>
-  </si>
-  <si>
-    <t>澳超</t>
-  </si>
-  <si>
-    <t>悉尼FC</t>
-  </si>
-  <si>
-    <t>西悉尼</t>
-  </si>
-  <si>
-    <t>10-16 17:00</t>
-  </si>
-  <si>
-    <t>6球 @13</t>
-  </si>
-  <si>
-    <t>3球 @3.7 ⚡</t>
-  </si>
-  <si>
-    <t>科特布斯</t>
-  </si>
-  <si>
-    <t>纽伦堡</t>
-  </si>
-  <si>
-    <t>10-17 00:30</t>
-  </si>
-  <si>
     <t>布鲁马波</t>
   </si>
   <si>
@@ -5915,294 +5915,291 @@
     <t>2:5=125 5:2=80 负其他=34 平其他=100 胜其他=26</t>
   </si>
   <si>
-    <t>0:1=12 1:0=10</t>
-  </si>
-  <si>
-    <t>0:2=17 1:1=6.75 2:0=12.5</t>
+    <t>0:1=12 1:0=10.5</t>
+  </si>
+  <si>
+    <t>0:2=17 1:1=6.75 2:0=13.5</t>
+  </si>
+  <si>
+    <t>0:3=29 1:2=8 2:1=7.5 3:0=24</t>
+  </si>
+  <si>
+    <t>0:4=70 1:3=18 2:2=10 3:1=16 4:0=60</t>
+  </si>
+  <si>
+    <t>0:5=250 1:4=50 2:3=21 3:2=20 4:1=36 5:0=120</t>
+  </si>
+  <si>
+    <t>1:5=150 2:4=55 3:3=38 4:2=45 5:1=80</t>
+  </si>
+  <si>
+    <t>2:5=150 5:2=100 负其他=50 平其他=200 胜其他=45</t>
+  </si>
+  <si>
+    <t>0:1=8 1:0=25</t>
+  </si>
+  <si>
+    <t>0:2=6.5 1:1=10.5 2:0=55</t>
+  </si>
+  <si>
+    <t>0:3=7.5 1:2=7.5 2:1=26 3:0=150</t>
+  </si>
+  <si>
+    <t>0:4=12 1:3=9.25 2:2=21 3:1=70 4:0=500</t>
+  </si>
+  <si>
+    <t>0:5=22 1:4=15 2:3=24 3:2=60 4:1=300 5:0=1000</t>
+  </si>
+  <si>
+    <t>1:5=27 2:4=35 3:3=75 4:2=250 5:1=900</t>
+  </si>
+  <si>
+    <t>2:5=60 5:2=800 负其他=14 平其他=400 胜其他=300</t>
+  </si>
+  <si>
+    <t>0:1=11.5 1:0=23</t>
+  </si>
+  <si>
+    <t>0:2=10 1:1=9.5 2:0=36</t>
+  </si>
+  <si>
+    <t>0:3=13 1:2=7 2:1=16 3:0=90</t>
+  </si>
+  <si>
+    <t>0:4=22 1:3=8.5 2:2=12 3:1=38 4:0=200</t>
+  </si>
+  <si>
+    <t>0:5=40 1:4=15 2:3=15 3:2=31 4:1=90 5:0=400</t>
+  </si>
+  <si>
+    <t>1:5=34 2:4=23 3:3=35 4:2=85 5:1=250</t>
+  </si>
+  <si>
+    <t>2:5=45 5:2=250 负其他=14 平其他=120 胜其他=70</t>
+  </si>
+  <si>
+    <t>0:2=15 1:1=7 2:0=13</t>
+  </si>
+  <si>
+    <t>0:3=29 1:2=8.5 2:1=8 3:0=22</t>
+  </si>
+  <si>
+    <t>0:4=60 1:3=20 2:2=9.5 3:1=16 4:0=45</t>
+  </si>
+  <si>
+    <t>0:5=200 1:4=45 2:3=23 3:2=20 4:1=35 5:0=120</t>
+  </si>
+  <si>
+    <t>1:5=120 2:4=50 3:3=32 4:2=45 5:1=80</t>
+  </si>
+  <si>
+    <t>2:5=150 5:2=100 负其他=55 平其他=125 胜其他=45</t>
+  </si>
+  <si>
+    <t>0:2=9.5 1:1=7.5 2:0=23</t>
+  </si>
+  <si>
+    <t>0:3=14 1:2=7 2:1=11 3:0=50</t>
+  </si>
+  <si>
+    <t>0:4=25 1:3=12 2:2=12 3:1=30 4:0=150</t>
+  </si>
+  <si>
+    <t>0:5=55 1:4=22 2:3=19 3:2=28 4:1=80 5:0=400</t>
+  </si>
+  <si>
+    <t>1:5=55 2:4=36 3:3=42 4:2=80 5:1=250</t>
+  </si>
+  <si>
+    <t>2:5=80 5:2=250 负其他=29 平其他=200 胜其他=80</t>
+  </si>
+  <si>
+    <t>0:0=8.25</t>
+  </si>
+  <si>
+    <t>0:1=6.5 1:0=6.75</t>
+  </si>
+  <si>
+    <t>0:2=10.5 1:1=5.6 2:0=11.5</t>
+  </si>
+  <si>
+    <t>0:3=25 1:2=8.75 2:1=9.5 3:0=30</t>
+  </si>
+  <si>
+    <t>0:4=60 1:3=24 2:2=15 3:1=27 4:0=80</t>
+  </si>
+  <si>
+    <t>0:5=250 1:4=65 2:3=38 3:2=40 4:1=70 5:0=300</t>
+  </si>
+  <si>
+    <t>1:5=225 2:4=90 3:3=70 4:2=100 5:1=300</t>
+  </si>
+  <si>
+    <t>2:5=275 5:2=350 负其他=100 平其他=400 胜其他=125</t>
+  </si>
+  <si>
+    <t>0:1=7 1:0=10</t>
+  </si>
+  <si>
+    <t>0:2=9 1:1=5.5 2:0=18</t>
+  </si>
+  <si>
+    <t>0:3=18 1:2=7.25 2:1=10.5 3:0=40</t>
+  </si>
+  <si>
+    <t>0:4=45 1:3=15 2:2=15 3:1=29 4:0=120</t>
+  </si>
+  <si>
+    <t>0:5=100 1:4=42 2:3=29 3:2=35 4:1=80 5:0=400</t>
+  </si>
+  <si>
+    <t>1:5=80 2:4=65 3:3=60 4:2=100 5:1=300</t>
+  </si>
+  <si>
+    <t>2:5=150 5:2=400 负其他=60 平其他=400 胜其他=120</t>
+  </si>
+  <si>
+    <t>0:1=17 1:0=12</t>
+  </si>
+  <si>
+    <t>0:2=23 1:1=8.25 2:0=12</t>
+  </si>
+  <si>
+    <t>0:3=45 1:2=11 2:1=7.25 3:0=17</t>
+  </si>
+  <si>
+    <t>0:4=90 1:3=23 2:2=10.5 3:1=11.5 4:0=31</t>
+  </si>
+  <si>
+    <t>0:5=300 1:4=55 2:3=23 3:2=16 4:1=22 5:0=60</t>
+  </si>
+  <si>
+    <t>1:5=175 2:4=55 3:3=30 4:2=31 5:1=50</t>
+  </si>
+  <si>
+    <t>2:5=175 5:2=60 负其他=45 平其他=100 胜其他=22</t>
+  </si>
+  <si>
+    <t>0:1=11 1:0=9</t>
+  </si>
+  <si>
+    <t>0:2=17 1:1=6.25 2:0=11</t>
+  </si>
+  <si>
+    <t>0:3=32 1:2=9.25 2:1=7.5 3:0=21</t>
+  </si>
+  <si>
+    <t>0:4=80 1:3=22 2:2=11 3:1=15 4:0=48</t>
+  </si>
+  <si>
+    <t>0:5=250 1:4=60 2:3=26 3:2=20 4:1=35 5:0=100</t>
+  </si>
+  <si>
+    <t>1:5=200 2:4=70 3:3=45 4:2=45 5:1=90</t>
+  </si>
+  <si>
+    <t>2:5=250 5:2=100 负其他=70 平其他=200 胜其他=55</t>
+  </si>
+  <si>
+    <t>0:0=36</t>
+  </si>
+  <si>
+    <t>0:1=55 1:0=10.5</t>
+  </si>
+  <si>
+    <t>0:2=120 1:1=15.5 2:0=6.3</t>
+  </si>
+  <si>
+    <t>0:3=350 1:2=46 2:1=9.25 3:0=6.6</t>
+  </si>
+  <si>
+    <t>0:4=800 1:3=120 2:2=24 3:1=9 4:0=8.75</t>
+  </si>
+  <si>
+    <t>0:5=800 1:4=500 2:3=90 3:2=25 4:1=11 5:0=13.5</t>
+  </si>
+  <si>
+    <t>1:5=800 2:4=400 3:3=80 4:2=30 5:1=18</t>
+  </si>
+  <si>
+    <t>2:5=800 5:2=45 负其他=300 平其他=300 胜其他=8.25</t>
+  </si>
+  <si>
+    <t>0:1=48 1:0=11</t>
+  </si>
+  <si>
+    <t>0:2=90 1:1=14.5 2:0=7</t>
+  </si>
+  <si>
+    <t>0:3=200 1:2=39 2:1=8.5 3:0=7.25</t>
+  </si>
+  <si>
+    <t>0:4=600 1:3=80 2:2=23 3:1=8.5 4:0=9.5</t>
+  </si>
+  <si>
+    <t>0:5=1000 1:4=300 2:3=65 3:2=23 4:1=12 5:0=15</t>
+  </si>
+  <si>
+    <t>1:5=900 2:4=250 3:3=60 4:2=28 5:1=18</t>
+  </si>
+  <si>
+    <t>2:5=800 5:2=45 负其他=250 平其他=300 胜其他=8</t>
+  </si>
+  <si>
+    <t>0:1=8.75 1:0=7.8</t>
+  </si>
+  <si>
+    <t>0:2=13 1:1=5.8 2:0=11</t>
+  </si>
+  <si>
+    <t>0:3=32 1:2=9 2:1=8.5 3:0=25</t>
+  </si>
+  <si>
+    <t>0:4=90 1:3=24 2:2=12 3:1=20 4:0=55</t>
+  </si>
+  <si>
+    <t>0:5=250 1:4=60 2:3=30 3:2=27 4:1=45 5:0=150</t>
+  </si>
+  <si>
+    <t>1:5=200 2:4=80 3:3=50 4:2=60 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=250 5:2=200 负其他=80 平其他=300 胜其他=70</t>
+  </si>
+  <si>
+    <t>0:0=6.25</t>
+  </si>
+  <si>
+    <t>0:1=5.15 1:0=7.5</t>
+  </si>
+  <si>
+    <t>0:2=8.25 1:1=5.5 2:0=17</t>
+  </si>
+  <si>
+    <t>0:3=20 1:2=7.75 2:1=12.5 3:0=45</t>
+  </si>
+  <si>
+    <t>0:4=45 1:3=19 2:2=18 3:1=45 4:0=150</t>
+  </si>
+  <si>
+    <t>0:5=150 1:4=55 2:3=40 3:2=60 4:1=150 5:0=600</t>
+  </si>
+  <si>
+    <t>1:5=200 2:4=120 3:3=100 4:2=250 5:1=500</t>
+  </si>
+  <si>
+    <t>2:5=400 5:2=600 负其他=150 平其他=600 胜其他=300</t>
+  </si>
+  <si>
+    <t>0:1=10.5 1:0=9.65</t>
+  </si>
+  <si>
+    <t>0:2=16 1:1=6.5 2:0=12</t>
   </si>
   <si>
     <t>0:3=32 1:2=8.75 2:1=7.5 3:0=22</t>
   </si>
   <si>
-    <t>0:4=70 1:3=19 2:2=10.5 3:1=15 4:0=45</t>
-  </si>
-  <si>
-    <t>0:5=250 1:4=55 2:3=22 3:2=20 4:1=32 5:0=100</t>
-  </si>
-  <si>
-    <t>1:5=150 2:4=55 3:3=38 4:2=45 5:1=80</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=100 负其他=60 平其他=200 胜其他=45</t>
-  </si>
-  <si>
-    <t>0:1=8 1:0=25</t>
-  </si>
-  <si>
-    <t>0:2=6.5 1:1=10.5 2:0=55</t>
-  </si>
-  <si>
-    <t>0:3=7.5 1:2=7.5 2:1=26 3:0=150</t>
-  </si>
-  <si>
-    <t>0:4=12 1:3=9.25 2:2=21 3:1=70 4:0=500</t>
-  </si>
-  <si>
-    <t>0:5=22 1:4=15 2:3=24 3:2=60 4:1=300 5:0=1000</t>
-  </si>
-  <si>
-    <t>1:5=27 2:4=35 3:3=75 4:2=250 5:1=900</t>
-  </si>
-  <si>
-    <t>2:5=60 5:2=800 负其他=14 平其他=400 胜其他=300</t>
-  </si>
-  <si>
-    <t>0:1=11 1:0=22</t>
-  </si>
-  <si>
-    <t>0:2=10 1:1=8.9 2:0=35</t>
-  </si>
-  <si>
-    <t>0:3=13 1:2=7 2:1=16 3:0=70</t>
-  </si>
-  <si>
-    <t>0:4=23 1:3=9 2:2=12 3:1=38 4:0=150</t>
-  </si>
-  <si>
-    <t>0:5=45 1:4=16 2:3=15 3:2=31 4:1=75 5:0=400</t>
-  </si>
-  <si>
-    <t>1:5=36 2:4=24 3:3=35 4:2=70 5:1=250</t>
-  </si>
-  <si>
-    <t>2:5=50 5:2=250 负其他=15 平其他=120 胜其他=60</t>
-  </si>
-  <si>
-    <t>0:1=12 1:0=10.5</t>
-  </si>
-  <si>
-    <t>0:2=15 1:1=7 2:0=13</t>
-  </si>
-  <si>
-    <t>0:3=29 1:2=8.5 2:1=8 3:0=22</t>
-  </si>
-  <si>
-    <t>0:4=60 1:3=20 2:2=9.5 3:1=16 4:0=45</t>
-  </si>
-  <si>
-    <t>0:5=200 1:4=45 2:3=23 3:2=20 4:1=35 5:0=120</t>
-  </si>
-  <si>
-    <t>1:5=120 2:4=50 3:3=32 4:2=45 5:1=80</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=100 负其他=55 平其他=125 胜其他=45</t>
-  </si>
-  <si>
-    <t>0:2=9.5 1:1=7.5 2:0=23</t>
-  </si>
-  <si>
-    <t>0:3=14 1:2=7 2:1=11 3:0=50</t>
-  </si>
-  <si>
-    <t>0:4=25 1:3=12 2:2=12 3:1=30 4:0=150</t>
-  </si>
-  <si>
-    <t>0:5=55 1:4=22 2:3=19 3:2=28 4:1=80 5:0=400</t>
-  </si>
-  <si>
-    <t>1:5=55 2:4=36 3:3=42 4:2=80 5:1=250</t>
-  </si>
-  <si>
-    <t>2:5=80 5:2=250 负其他=29 平其他=200 胜其他=80</t>
-  </si>
-  <si>
-    <t>0:0=8.25</t>
-  </si>
-  <si>
-    <t>0:1=6.25 1:0=7.5</t>
-  </si>
-  <si>
-    <t>0:2=9.5 1:1=5.6 2:0=14</t>
-  </si>
-  <si>
-    <t>0:3=20 1:2=8 2:1=10.5 3:0=38</t>
-  </si>
-  <si>
-    <t>0:4=50 1:3=20 2:2=15 3:1=29 4:0=100</t>
-  </si>
-  <si>
-    <t>0:5=150 1:4=50 2:3=34 3:2=45 4:1=80 5:0=400</t>
-  </si>
-  <si>
-    <t>1:5=150 2:4=80 3:3=80 4:2=120 5:1=300</t>
-  </si>
-  <si>
-    <t>2:5=250 5:2=400 负其他=100 平其他=500 胜其他=150</t>
-  </si>
-  <si>
-    <t>0:1=7 1:0=10</t>
-  </si>
-  <si>
-    <t>0:2=9 1:1=5.5 2:0=18</t>
-  </si>
-  <si>
-    <t>0:3=18 1:2=7.25 2:1=10.5 3:0=40</t>
-  </si>
-  <si>
-    <t>0:4=45 1:3=15 2:2=15 3:1=29 4:0=120</t>
-  </si>
-  <si>
-    <t>0:5=100 1:4=42 2:3=29 3:2=35 4:1=80 5:0=400</t>
-  </si>
-  <si>
-    <t>1:5=80 2:4=65 3:3=60 4:2=100 5:1=300</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=400 负其他=60 平其他=400 胜其他=120</t>
-  </si>
-  <si>
-    <t>0:1=17 1:0=12</t>
-  </si>
-  <si>
-    <t>0:2=23 1:1=8.25 2:0=12</t>
-  </si>
-  <si>
-    <t>0:3=45 1:2=11 2:1=7.25 3:0=17</t>
-  </si>
-  <si>
-    <t>0:4=90 1:3=23 2:2=10.5 3:1=11.5 4:0=31</t>
-  </si>
-  <si>
-    <t>0:5=300 1:4=55 2:3=23 3:2=16 4:1=22 5:0=60</t>
-  </si>
-  <si>
-    <t>1:5=175 2:4=55 3:3=30 4:2=31 5:1=50</t>
-  </si>
-  <si>
-    <t>2:5=175 5:2=60 负其他=45 平其他=100 胜其他=22</t>
-  </si>
-  <si>
-    <t>0:1=11 1:0=9</t>
-  </si>
-  <si>
-    <t>0:2=17 1:1=6.25 2:0=11</t>
-  </si>
-  <si>
-    <t>0:3=32 1:2=9.25 2:1=7.5 3:0=21</t>
-  </si>
-  <si>
-    <t>0:4=80 1:3=22 2:2=11 3:1=15 4:0=48</t>
-  </si>
-  <si>
-    <t>0:5=250 1:4=60 2:3=26 3:2=20 4:1=35 5:0=100</t>
-  </si>
-  <si>
-    <t>1:5=200 2:4=70 3:3=45 4:2=45 5:1=90</t>
-  </si>
-  <si>
-    <t>2:5=250 5:2=100 负其他=70 平其他=200 胜其他=55</t>
-  </si>
-  <si>
-    <t>0:0=34</t>
-  </si>
-  <si>
-    <t>0:1=50 1:0=10</t>
-  </si>
-  <si>
-    <t>0:2=100 1:1=14 2:0=6.3</t>
-  </si>
-  <si>
-    <t>0:3=350 1:2=45 2:1=9.25 3:0=6.75</t>
-  </si>
-  <si>
-    <t>0:4=800 1:3=120 2:2=24 3:1=9 4:0=9</t>
-  </si>
-  <si>
-    <t>0:5=800 1:4=500 2:3=90 3:2=26 4:1=11 5:0=14</t>
-  </si>
-  <si>
-    <t>1:5=800 2:4=400 3:3=80 4:2=30 5:1=19</t>
-  </si>
-  <si>
-    <t>2:5=800 5:2=45 负其他=300 平其他=300 胜其他=8.5</t>
-  </si>
-  <si>
-    <t>0:0=36</t>
-  </si>
-  <si>
-    <t>0:1=45 1:0=11</t>
-  </si>
-  <si>
-    <t>0:2=90 1:1=13.5 2:0=7</t>
-  </si>
-  <si>
-    <t>0:3=200 1:2=38 2:1=8.5 3:0=7.25</t>
-  </si>
-  <si>
-    <t>0:4=600 1:3=80 2:2=23 3:1=8.5 4:0=10</t>
-  </si>
-  <si>
-    <t>0:5=1000 1:4=300 2:3=65 3:2=23 4:1=12 5:0=15</t>
-  </si>
-  <si>
-    <t>1:5=900 2:4=250 3:3=60 4:2=28 5:1=18</t>
-  </si>
-  <si>
-    <t>2:5=800 5:2=45 负其他=250 平其他=300 胜其他=8.25</t>
-  </si>
-  <si>
-    <t>0:1=8.75 1:0=7.8</t>
-  </si>
-  <si>
-    <t>0:2=13 1:1=5.8 2:0=11</t>
-  </si>
-  <si>
-    <t>0:3=32 1:2=9.5 2:1=8.25 3:0=23</t>
-  </si>
-  <si>
-    <t>0:4=90 1:3=24 2:2=13 3:1=18 4:0=55</t>
-  </si>
-  <si>
-    <t>0:5=250 1:4=60 2:3=30 3:2=27 4:1=45 5:0=150</t>
-  </si>
-  <si>
-    <t>1:5=200 2:4=80 3:3=50 4:2=60 5:1=120</t>
-  </si>
-  <si>
-    <t>2:5=250 5:2=200 负其他=80 平其他=300 胜其他=70</t>
-  </si>
-  <si>
-    <t>0:0=6.25</t>
-  </si>
-  <si>
-    <t>0:1=5.15 1:0=7.5</t>
-  </si>
-  <si>
-    <t>0:2=8.25 1:1=5.5 2:0=17</t>
-  </si>
-  <si>
-    <t>0:3=20 1:2=7.75 2:1=12.5 3:0=45</t>
-  </si>
-  <si>
-    <t>0:4=45 1:3=19 2:2=18 3:1=45 4:0=150</t>
-  </si>
-  <si>
-    <t>0:5=150 1:4=55 2:3=40 3:2=60 4:1=150 5:0=600</t>
-  </si>
-  <si>
-    <t>1:5=200 2:4=120 3:3=100 4:2=250 5:1=500</t>
-  </si>
-  <si>
-    <t>2:5=400 5:2=600 负其他=150 平其他=600 胜其他=300</t>
-  </si>
-  <si>
-    <t>0:1=10.5 1:0=9.65</t>
-  </si>
-  <si>
-    <t>0:2=16 1:1=6.5 2:0=12</t>
-  </si>
-  <si>
     <t>0:4=90 1:3=19 2:2=10 3:1=16 4:0=60</t>
   </si>
   <si>
@@ -6416,7 +6413,7 @@
     <t>2:5=300 5:2=175 负其他=95 平其他=275 胜其他=65</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-15T20:00:07+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-15T21:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -19628,7 +19625,7 @@
         <v>892</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="L141" t="s">
         <v>21</v>
@@ -19637,7 +19634,7 @@
         <v>21</v>
       </c>
       <c r="N141" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="O141" t="s">
         <v>21</v>
@@ -19654,7 +19651,7 @@
         <v>882</v>
       </c>
       <c r="D142" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E142" t="s">
         <v>136</v>
@@ -19672,10 +19669,10 @@
         <v>435</v>
       </c>
       <c r="J142" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="K142" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="K142" s="3" t="s">
-        <v>896</v>
       </c>
       <c r="L142" t="s">
         <v>21</v>
@@ -19701,7 +19698,7 @@
         <v>882</v>
       </c>
       <c r="D143" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E143" t="s">
         <v>128</v>
@@ -19716,13 +19713,13 @@
         <v>21</v>
       </c>
       <c r="I143" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="J143" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="J143" s="3" t="s">
-        <v>899</v>
-      </c>
       <c r="K143" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="L143" t="s">
         <v>21</v>
@@ -19745,10 +19742,10 @@
         <v>211</v>
       </c>
       <c r="C144" t="s">
+        <v>899</v>
+      </c>
+      <c r="D144" t="s">
         <v>900</v>
-      </c>
-      <c r="D144" t="s">
-        <v>901</v>
       </c>
       <c r="E144" t="s">
         <v>52</v>
@@ -19766,10 +19763,10 @@
         <v>797</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="L144" t="s">
         <v>21</v>
@@ -19778,7 +19775,7 @@
         <v>21</v>
       </c>
       <c r="N144" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="O144" t="s">
         <v>21</v>
@@ -19801,7 +19798,7 @@
         <v>113</v>
       </c>
       <c r="F145" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>70</v>
@@ -19810,13 +19807,13 @@
         <v>21</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L145" t="s">
         <v>21</v>
@@ -19836,7 +19833,7 @@
         <v>881</v>
       </c>
       <c r="B146" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C146" t="s">
         <v>882</v>
@@ -19845,10 +19842,10 @@
         <v>125</v>
       </c>
       <c r="E146" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F146" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>55</v>
@@ -19860,10 +19857,10 @@
         <v>480</v>
       </c>
       <c r="J146" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="K146" s="3" t="s">
         <v>907</v>
-      </c>
-      <c r="K146" s="3" t="s">
-        <v>908</v>
       </c>
       <c r="L146" t="s">
         <v>21</v>
@@ -19883,7 +19880,7 @@
         <v>881</v>
       </c>
       <c r="B147" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C147" t="s">
         <v>882</v>
@@ -19892,10 +19889,10 @@
         <v>132</v>
       </c>
       <c r="E147" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F147" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>55</v>
@@ -19907,10 +19904,10 @@
         <v>440</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L147" t="s">
         <v>21</v>
@@ -19930,7 +19927,7 @@
         <v>881</v>
       </c>
       <c r="B148" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C148" t="s">
         <v>882</v>
@@ -19939,25 +19936,25 @@
         <v>68</v>
       </c>
       <c r="E148" t="s">
+        <v>912</v>
+      </c>
+      <c r="F148" t="s">
+        <v>902</v>
+      </c>
+      <c r="G148" t="s">
+        <v>21</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I148" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="F148" t="s">
-        <v>903</v>
-      </c>
-      <c r="G148" t="s">
-        <v>21</v>
-      </c>
-      <c r="H148" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I148" s="3" t="s">
+      <c r="J148" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="J148" s="3" t="s">
-        <v>915</v>
-      </c>
       <c r="K148" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="L148" t="s">
         <v>21</v>
@@ -19966,7 +19963,7 @@
         <v>21</v>
       </c>
       <c r="N148" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="O148" t="s">
         <v>21</v>
@@ -19977,7 +19974,7 @@
         <v>881</v>
       </c>
       <c r="B149" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C149" t="s">
         <v>882</v>
@@ -19986,10 +19983,10 @@
         <v>141</v>
       </c>
       <c r="E149" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="F149" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>55</v>
@@ -19998,13 +19995,13 @@
         <v>21</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>829</v>
+        <v>640</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L149" t="s">
         <v>21</v>
@@ -20013,7 +20010,7 @@
         <v>21</v>
       </c>
       <c r="N149" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="O149" t="s">
         <v>21</v>
@@ -20024,19 +20021,19 @@
         <v>881</v>
       </c>
       <c r="B150" t="s">
+        <v>919</v>
+      </c>
+      <c r="C150" t="s">
+        <v>899</v>
+      </c>
+      <c r="D150" t="s">
         <v>920</v>
-      </c>
-      <c r="C150" t="s">
-        <v>900</v>
-      </c>
-      <c r="D150" t="s">
-        <v>921</v>
       </c>
       <c r="E150" t="s">
         <v>590</v>
       </c>
       <c r="F150" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>55</v>
@@ -20060,7 +20057,7 @@
         <v>21</v>
       </c>
       <c r="N150" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="O150" t="s">
         <v>21</v>
@@ -20071,19 +20068,19 @@
         <v>881</v>
       </c>
       <c r="B151" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C151" t="s">
         <v>875</v>
       </c>
       <c r="D151" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E151" t="s">
         <v>534</v>
       </c>
       <c r="F151" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>55</v>
@@ -20095,10 +20092,10 @@
         <v>469</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="L151" t="s">
         <v>21</v>
@@ -20107,7 +20104,7 @@
         <v>21</v>
       </c>
       <c r="N151" t="s">
-        <v>926</v>
+        <v>886</v>
       </c>
       <c r="O151" t="s">
         <v>21</v>
@@ -20115,22 +20112,22 @@
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B152" t="s">
         <v>221</v>
       </c>
       <c r="C152" t="s">
+        <v>926</v>
+      </c>
+      <c r="D152" t="s">
+        <v>927</v>
+      </c>
+      <c r="E152" t="s">
         <v>928</v>
       </c>
-      <c r="D152" t="s">
+      <c r="F152" t="s">
         <v>929</v>
-      </c>
-      <c r="E152" t="s">
-        <v>930</v>
-      </c>
-      <c r="F152" t="s">
-        <v>931</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>70</v>
@@ -20139,22 +20136,22 @@
         <v>21</v>
       </c>
       <c r="I152" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="K152" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="L152" t="s">
+        <v>21</v>
+      </c>
+      <c r="M152" t="s">
+        <v>21</v>
+      </c>
+      <c r="N152" t="s">
         <v>932</v>
-      </c>
-      <c r="J152" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="K152" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="L152" t="s">
-        <v>21</v>
-      </c>
-      <c r="M152" t="s">
-        <v>21</v>
-      </c>
-      <c r="N152" t="s">
-        <v>926</v>
       </c>
       <c r="O152" t="s">
         <v>21</v>
@@ -20162,7 +20159,7 @@
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B153" t="s">
         <v>225</v>
@@ -20171,13 +20168,13 @@
         <v>554</v>
       </c>
       <c r="D153" t="s">
+        <v>933</v>
+      </c>
+      <c r="E153" t="s">
         <v>934</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>935</v>
-      </c>
-      <c r="F153" t="s">
-        <v>936</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>55</v>
@@ -20189,10 +20186,10 @@
         <v>697</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>892</v>
+        <v>936</v>
       </c>
       <c r="L153" t="s">
         <v>21</v>
@@ -20201,7 +20198,7 @@
         <v>21</v>
       </c>
       <c r="N153" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O153" t="s">
         <v>21</v>
@@ -20209,7 +20206,7 @@
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B154" t="s">
         <v>228</v>
@@ -20248,7 +20245,7 @@
         <v>21</v>
       </c>
       <c r="N154" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O154" t="s">
         <v>21</v>
@@ -20256,7 +20253,7 @@
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B155" t="s">
         <v>233</v>
@@ -20283,10 +20280,10 @@
         <v>942</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="L155" t="s">
         <v>21</v>
@@ -20295,7 +20292,7 @@
         <v>21</v>
       </c>
       <c r="N155" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O155" t="s">
         <v>21</v>
@@ -20303,7 +20300,7 @@
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B156" t="s">
         <v>236</v>
@@ -20330,10 +20327,10 @@
         <v>432</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L156" t="s">
         <v>21</v>
@@ -20342,7 +20339,7 @@
         <v>21</v>
       </c>
       <c r="N156" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O156" t="s">
         <v>21</v>
@@ -20350,7 +20347,7 @@
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B157" t="s">
         <v>239</v>
@@ -20377,10 +20374,10 @@
         <v>829</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="L157" t="s">
         <v>21</v>
@@ -20389,7 +20386,7 @@
         <v>21</v>
       </c>
       <c r="N157" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O157" t="s">
         <v>21</v>
@@ -20397,7 +20394,7 @@
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B158" t="s">
         <v>243</v>
@@ -20436,7 +20433,7 @@
         <v>21</v>
       </c>
       <c r="N158" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O158" t="s">
         <v>21</v>
@@ -20444,7 +20441,7 @@
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B159" t="s">
         <v>246</v>
@@ -20471,10 +20468,10 @@
         <v>564</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L159" t="s">
         <v>21</v>
@@ -20483,7 +20480,7 @@
         <v>21</v>
       </c>
       <c r="N159" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O159" t="s">
         <v>21</v>
@@ -20491,7 +20488,7 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B160" t="s">
         <v>250</v>
@@ -20518,7 +20515,7 @@
         <v>610</v>
       </c>
       <c r="J160" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K160" s="3" t="s">
         <v>952</v>
@@ -20530,7 +20527,7 @@
         <v>21</v>
       </c>
       <c r="N160" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O160" t="s">
         <v>21</v>
@@ -20538,7 +20535,7 @@
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B161" t="s">
         <v>253</v>
@@ -20565,7 +20562,7 @@
         <v>623</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K161" s="3" t="s">
         <v>953</v>
@@ -20577,7 +20574,7 @@
         <v>21</v>
       </c>
       <c r="N161" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O161" t="s">
         <v>21</v>
@@ -20585,7 +20582,7 @@
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B162" t="s">
         <v>256</v>
@@ -20612,10 +20609,10 @@
         <v>955</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K162" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L162" t="s">
         <v>21</v>
@@ -20624,7 +20621,7 @@
         <v>21</v>
       </c>
       <c r="N162" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="O162" t="s">
         <v>21</v>
@@ -64557,7 +64554,7 @@
       </c>
       <c r="G1098" s="9"/>
       <c r="H1098" s="10">
-        <v>3.091</v>
+        <v>3.188</v>
       </c>
       <c r="I1098" s="11"/>
       <c r="J1098" s="8"/>
@@ -64589,22 +64586,22 @@
         <v>6.75</v>
       </c>
       <c r="G1099" s="13">
-        <v>5.455</v>
+        <v>5.6</v>
       </c>
       <c r="H1099" s="14">
-        <v>1.295</v>
+        <v>1.15</v>
       </c>
       <c r="I1099" s="15">
-        <v>23.7</v>
+        <v>20.5</v>
       </c>
       <c r="J1099" s="12">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="K1099" s="16">
-        <v>-4.25</v>
+        <v>-4.5</v>
       </c>
       <c r="L1099" s="15">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="M1099" t="s">
         <v>1965</v>
@@ -64630,22 +64627,22 @@
         <v>4.2</v>
       </c>
       <c r="G1100" s="13">
-        <v>3.485</v>
+        <v>3.558</v>
       </c>
       <c r="H1100" s="14">
-        <v>0.715</v>
+        <v>0.642</v>
       </c>
       <c r="I1100" s="15">
-        <v>20.5</v>
+        <v>18</v>
       </c>
       <c r="J1100" s="12">
-        <v>12.083</v>
+        <v>12.417</v>
       </c>
       <c r="K1100" s="16">
-        <v>-7.883</v>
+        <v>-8.217</v>
       </c>
       <c r="L1100" s="15">
-        <v>-65.2</v>
+        <v>-66.2</v>
       </c>
       <c r="M1100" t="s">
         <v>1966</v>
@@ -64668,25 +64665,25 @@
         <v>423</v>
       </c>
       <c r="F1101" s="12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G1101" s="13">
-        <v>3.083</v>
+        <v>2.99</v>
       </c>
       <c r="H1101" s="14">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="I1101" s="15">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J1101" s="12">
-        <v>17.563</v>
+        <v>17.125</v>
       </c>
       <c r="K1101" s="16">
-        <v>-14.463</v>
+        <v>-14.125</v>
       </c>
       <c r="L1101" s="15">
-        <v>-82.3</v>
+        <v>-82.5</v>
       </c>
       <c r="M1101" t="s">
         <v>1967</v>
@@ -64709,25 +64706,25 @@
         <v>438</v>
       </c>
       <c r="F1102" s="12">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="G1102" s="13">
-        <v>3.983</v>
+        <v>4.016</v>
       </c>
       <c r="H1102" s="14">
-        <v>0.167</v>
+        <v>0.034</v>
       </c>
       <c r="I1102" s="15">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J1102" s="12">
-        <v>31.9</v>
+        <v>34.8</v>
       </c>
       <c r="K1102" s="16">
-        <v>-27.75</v>
+        <v>-30.75</v>
       </c>
       <c r="L1102" s="15">
-        <v>-87</v>
+        <v>-88.4</v>
       </c>
       <c r="M1102" t="s">
         <v>1968</v>
@@ -64750,25 +64747,25 @@
         <v>430</v>
       </c>
       <c r="F1103" s="12">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="G1103" s="13">
-        <v>6.294</v>
+        <v>6.34</v>
       </c>
       <c r="H1103" s="14">
-        <v>1.456</v>
+        <v>1.91</v>
       </c>
       <c r="I1103" s="15">
-        <v>23.1</v>
+        <v>30.1</v>
       </c>
       <c r="J1103" s="12">
-        <v>79.833</v>
+        <v>82.833</v>
       </c>
       <c r="K1103" s="16">
-        <v>-72.083</v>
+        <v>-74.583</v>
       </c>
       <c r="L1103" s="15">
-        <v>-90.3</v>
+        <v>-90</v>
       </c>
       <c r="M1103" t="s">
         <v>1969</v>
@@ -64791,25 +64788,25 @@
         <v>522</v>
       </c>
       <c r="F1104" s="12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G1104" s="13">
         <v>11.643</v>
       </c>
       <c r="H1104" s="14">
-        <v>2.357</v>
+        <v>3.357</v>
       </c>
       <c r="I1104" s="15">
-        <v>20.2</v>
+        <v>28.8</v>
       </c>
       <c r="J1104" s="12">
         <v>73.6</v>
       </c>
       <c r="K1104" s="16">
-        <v>-59.6</v>
+        <v>-58.6</v>
       </c>
       <c r="L1104" s="15">
-        <v>-81</v>
+        <v>-79.6</v>
       </c>
       <c r="M1104" t="s">
         <v>1970</v>
@@ -64832,25 +64829,25 @@
         <v>634</v>
       </c>
       <c r="F1105" s="12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G1105" s="13">
-        <v>16.514</v>
+        <v>15.652</v>
       </c>
       <c r="H1105" s="14">
-        <v>5.486</v>
+        <v>8.348</v>
       </c>
       <c r="I1105" s="15">
-        <v>33.2</v>
+        <v>53.3</v>
       </c>
       <c r="J1105" s="12">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K1105" s="16">
-        <v>-89</v>
+        <v>-85</v>
       </c>
       <c r="L1105" s="15">
-        <v>-80.2</v>
+        <v>-78</v>
       </c>
       <c r="M1105" t="s">
         <v>1971</v>
@@ -65197,7 +65194,7 @@
       </c>
       <c r="G1114" s="9"/>
       <c r="H1114" s="10">
-        <v>2.465</v>
+        <v>1.908</v>
       </c>
       <c r="I1114" s="11"/>
       <c r="J1114" s="8"/>
@@ -65229,22 +65226,22 @@
         <v>8.75</v>
       </c>
       <c r="G1115" s="13">
-        <v>7.333</v>
+        <v>7.667</v>
       </c>
       <c r="H1115" s="14">
-        <v>1.417</v>
+        <v>1.083</v>
       </c>
       <c r="I1115" s="15">
-        <v>19.3</v>
+        <v>14.1</v>
       </c>
       <c r="J1115" s="12">
-        <v>16.5</v>
+        <v>17.25</v>
       </c>
       <c r="K1115" s="16">
-        <v>-7.75</v>
+        <v>-8.5</v>
       </c>
       <c r="L1115" s="15">
-        <v>-47</v>
+        <v>-49.3</v>
       </c>
       <c r="M1115" t="s">
         <v>1979</v>
@@ -65270,22 +65267,22 @@
         <v>4.85</v>
       </c>
       <c r="G1116" s="13">
-        <v>4.151</v>
+        <v>4.291</v>
       </c>
       <c r="H1116" s="14">
-        <v>0.699</v>
+        <v>0.559</v>
       </c>
       <c r="I1116" s="15">
-        <v>16.8</v>
+        <v>13</v>
       </c>
       <c r="J1116" s="12">
-        <v>17.967</v>
+        <v>18.5</v>
       </c>
       <c r="K1116" s="16">
-        <v>-13.117</v>
+        <v>-13.65</v>
       </c>
       <c r="L1116" s="15">
-        <v>-73</v>
+        <v>-73.8</v>
       </c>
       <c r="M1116" t="s">
         <v>1980</v>
@@ -65311,22 +65308,22 @@
         <v>3.65</v>
       </c>
       <c r="G1117" s="13">
-        <v>3.372</v>
+        <v>3.408</v>
       </c>
       <c r="H1117" s="14">
-        <v>0.278</v>
+        <v>0.242</v>
       </c>
       <c r="I1117" s="15">
-        <v>8.2</v>
+        <v>7.1</v>
       </c>
       <c r="J1117" s="12">
-        <v>26.5</v>
+        <v>31.5</v>
       </c>
       <c r="K1117" s="16">
-        <v>-22.85</v>
+        <v>-27.85</v>
       </c>
       <c r="L1117" s="15">
-        <v>-86.2</v>
+        <v>-88.4</v>
       </c>
       <c r="M1117" t="s">
         <v>1981</v>
@@ -65352,22 +65349,22 @@
         <v>4.2</v>
       </c>
       <c r="G1118" s="13">
-        <v>3.691</v>
+        <v>3.6</v>
       </c>
       <c r="H1118" s="14">
-        <v>0.509</v>
+        <v>0.6</v>
       </c>
       <c r="I1118" s="15">
-        <v>13.8</v>
+        <v>16.7</v>
       </c>
       <c r="J1118" s="12">
-        <v>46.4</v>
+        <v>56.1</v>
       </c>
       <c r="K1118" s="16">
-        <v>-42.2</v>
+        <v>-51.9</v>
       </c>
       <c r="L1118" s="15">
-        <v>-90.9</v>
+        <v>-92.5</v>
       </c>
       <c r="M1118" t="s">
         <v>1982</v>
@@ -65393,22 +65390,22 @@
         <v>5.75</v>
       </c>
       <c r="G1119" s="13">
-        <v>5.013</v>
+        <v>4.897</v>
       </c>
       <c r="H1119" s="14">
-        <v>0.737</v>
+        <v>0.853</v>
       </c>
       <c r="I1119" s="15">
-        <v>14.7</v>
+        <v>17.4</v>
       </c>
       <c r="J1119" s="12">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="K1119" s="16">
-        <v>-91.25</v>
+        <v>-92.75</v>
       </c>
       <c r="L1119" s="15">
-        <v>-94.1</v>
+        <v>-94.2</v>
       </c>
       <c r="M1119" t="s">
         <v>1983</v>
@@ -65434,22 +65431,22 @@
         <v>8.75</v>
       </c>
       <c r="G1120" s="13">
-        <v>8.598</v>
+        <v>8.531</v>
       </c>
       <c r="H1120" s="14">
-        <v>0.152</v>
+        <v>0.219</v>
       </c>
       <c r="I1120" s="15">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J1120" s="12">
-        <v>83</v>
+        <v>85.4</v>
       </c>
       <c r="K1120" s="16">
-        <v>-74.25</v>
+        <v>-76.65</v>
       </c>
       <c r="L1120" s="15">
-        <v>-89.5</v>
+        <v>-89.7</v>
       </c>
       <c r="M1120" t="s">
         <v>1984</v>
@@ -65475,22 +65472,22 @@
         <v>10</v>
       </c>
       <c r="G1121" s="13">
-        <v>8.646</v>
+        <v>8.315</v>
       </c>
       <c r="H1121" s="14">
-        <v>1.354</v>
+        <v>1.685</v>
       </c>
       <c r="I1121" s="15">
-        <v>15.7</v>
+        <v>20.3</v>
       </c>
       <c r="J1121" s="12">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="K1121" s="16">
-        <v>-89</v>
+        <v>-89.8</v>
       </c>
       <c r="L1121" s="15">
-        <v>-89.9</v>
+        <v>-90</v>
       </c>
       <c r="M1121" t="s">
         <v>1985</v>
@@ -65504,7 +65501,7 @@
         <v>203</v>
       </c>
       <c r="C1122" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1122" s="4" t="s">
         <v>136</v>
@@ -65537,7 +65534,7 @@
         <v>203</v>
       </c>
       <c r="C1123" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1123" t="s">
         <v>136</v>
@@ -65567,7 +65564,7 @@
         <v>-35.1</v>
       </c>
       <c r="M1123" t="s">
-        <v>1986</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1124" spans="1:13" x14ac:dyDescent="0.25">
@@ -65578,7 +65575,7 @@
         <v>203</v>
       </c>
       <c r="C1124" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1124" t="s">
         <v>136</v>
@@ -65608,7 +65605,7 @@
         <v>-64.9</v>
       </c>
       <c r="M1124" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1125" spans="1:13" x14ac:dyDescent="0.25">
@@ -65619,7 +65616,7 @@
         <v>203</v>
       </c>
       <c r="C1125" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1125" t="s">
         <v>136</v>
@@ -65649,7 +65646,7 @@
         <v>-79.8</v>
       </c>
       <c r="M1125" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1126" spans="1:13" x14ac:dyDescent="0.25">
@@ -65660,7 +65657,7 @@
         <v>203</v>
       </c>
       <c r="C1126" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1126" t="s">
         <v>136</v>
@@ -65690,7 +65687,7 @@
         <v>-85.9</v>
       </c>
       <c r="M1126" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1127" spans="1:13" x14ac:dyDescent="0.25">
@@ -65701,7 +65698,7 @@
         <v>203</v>
       </c>
       <c r="C1127" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1127" t="s">
         <v>136</v>
@@ -65731,7 +65728,7 @@
         <v>-90.8</v>
       </c>
       <c r="M1127" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1128" spans="1:13" x14ac:dyDescent="0.25">
@@ -65742,7 +65739,7 @@
         <v>203</v>
       </c>
       <c r="C1128" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1128" t="s">
         <v>136</v>
@@ -65772,7 +65769,7 @@
         <v>-82.4</v>
       </c>
       <c r="M1128" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1129" spans="1:13" x14ac:dyDescent="0.25">
@@ -65783,7 +65780,7 @@
         <v>203</v>
       </c>
       <c r="C1129" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1129" t="s">
         <v>136</v>
@@ -65813,7 +65810,7 @@
         <v>-83.2</v>
       </c>
       <c r="M1129" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1130" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -65824,7 +65821,7 @@
         <v>208</v>
       </c>
       <c r="C1130" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1130" s="4" t="s">
         <v>128</v>
@@ -65857,7 +65854,7 @@
         <v>208</v>
       </c>
       <c r="C1131" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1131" t="s">
         <v>128</v>
@@ -65898,7 +65895,7 @@
         <v>208</v>
       </c>
       <c r="C1132" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1132" t="s">
         <v>128</v>
@@ -65928,7 +65925,7 @@
         <v>-69.2</v>
       </c>
       <c r="M1132" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1133" spans="1:13" x14ac:dyDescent="0.25">
@@ -65939,7 +65936,7 @@
         <v>208</v>
       </c>
       <c r="C1133" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1133" t="s">
         <v>128</v>
@@ -65969,7 +65966,7 @@
         <v>-84.4</v>
       </c>
       <c r="M1133" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1134" spans="1:13" x14ac:dyDescent="0.25">
@@ -65980,7 +65977,7 @@
         <v>208</v>
       </c>
       <c r="C1134" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1134" t="s">
         <v>128</v>
@@ -66010,7 +66007,7 @@
         <v>-90.8</v>
       </c>
       <c r="M1134" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1135" spans="1:13" x14ac:dyDescent="0.25">
@@ -66021,7 +66018,7 @@
         <v>208</v>
       </c>
       <c r="C1135" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1135" t="s">
         <v>128</v>
@@ -66051,7 +66048,7 @@
         <v>-92.5</v>
       </c>
       <c r="M1135" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1136" spans="1:13" x14ac:dyDescent="0.25">
@@ -66062,7 +66059,7 @@
         <v>208</v>
       </c>
       <c r="C1136" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1136" t="s">
         <v>128</v>
@@ -66092,7 +66089,7 @@
         <v>-84.9</v>
       </c>
       <c r="M1136" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1137" spans="1:13" x14ac:dyDescent="0.25">
@@ -66103,7 +66100,7 @@
         <v>208</v>
       </c>
       <c r="C1137" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1137" t="s">
         <v>128</v>
@@ -66133,7 +66130,7 @@
         <v>-84.3</v>
       </c>
       <c r="M1137" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="1138" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -66144,7 +66141,7 @@
         <v>211</v>
       </c>
       <c r="C1138" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1138" s="4" t="s">
         <v>52</v>
@@ -66157,7 +66154,7 @@
       </c>
       <c r="G1138" s="9"/>
       <c r="H1138" s="10">
-        <v>1.163</v>
+        <v>1.135</v>
       </c>
       <c r="I1138" s="11"/>
       <c r="J1138" s="8"/>
@@ -66166,7 +66163,7 @@
       </c>
       <c r="L1138" s="11"/>
       <c r="M1138" s="4" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="1139" spans="1:13" x14ac:dyDescent="0.25">
@@ -66177,7 +66174,7 @@
         <v>211</v>
       </c>
       <c r="C1139" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1139" t="s">
         <v>52</v>
@@ -66189,25 +66186,25 @@
         <v>3.8</v>
       </c>
       <c r="G1139" s="13">
-        <v>3.409</v>
+        <v>3.311</v>
       </c>
       <c r="H1139" s="14">
-        <v>0.391</v>
+        <v>0.489</v>
       </c>
       <c r="I1139" s="15">
-        <v>11.5</v>
+        <v>14.8</v>
       </c>
       <c r="J1139" s="12">
-        <v>6.875</v>
+        <v>6.625</v>
       </c>
       <c r="K1139" s="16">
-        <v>-3.075</v>
+        <v>-2.825</v>
       </c>
       <c r="L1139" s="15">
-        <v>-44.7</v>
+        <v>-42.6</v>
       </c>
       <c r="M1139" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1140" spans="1:13" x14ac:dyDescent="0.25">
@@ -66218,7 +66215,7 @@
         <v>211</v>
       </c>
       <c r="C1140" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1140" t="s">
         <v>52</v>
@@ -66230,25 +66227,25 @@
         <v>2.85</v>
       </c>
       <c r="G1140" s="13">
-        <v>2.815</v>
+        <v>2.772</v>
       </c>
       <c r="H1140" s="14">
-        <v>0.035</v>
+        <v>0.078</v>
       </c>
       <c r="I1140" s="15">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J1140" s="12">
-        <v>9.7</v>
+        <v>9.2</v>
       </c>
       <c r="K1140" s="16">
-        <v>-6.85</v>
+        <v>-6.35</v>
       </c>
       <c r="L1140" s="15">
-        <v>-70.6</v>
+        <v>-69</v>
       </c>
       <c r="M1140" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1141" spans="1:13" x14ac:dyDescent="0.25">
@@ -66259,7 +66256,7 @@
         <v>211</v>
       </c>
       <c r="C1141" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1141" t="s">
         <v>52</v>
@@ -66271,25 +66268,25 @@
         <v>3.85</v>
       </c>
       <c r="G1141" s="13">
-        <v>3.372</v>
+        <v>3.414</v>
       </c>
       <c r="H1141" s="14">
-        <v>0.478</v>
+        <v>0.436</v>
       </c>
       <c r="I1141" s="15">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="J1141" s="12">
-        <v>19.125</v>
+        <v>18.313</v>
       </c>
       <c r="K1141" s="16">
-        <v>-15.275</v>
+        <v>-14.463</v>
       </c>
       <c r="L1141" s="15">
-        <v>-79.9</v>
+        <v>-79</v>
       </c>
       <c r="M1141" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1142" spans="1:13" x14ac:dyDescent="0.25">
@@ -66300,7 +66297,7 @@
         <v>211</v>
       </c>
       <c r="C1142" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1142" t="s">
         <v>52</v>
@@ -66312,25 +66309,25 @@
         <v>7.4</v>
       </c>
       <c r="G1142" s="13">
-        <v>5.52</v>
+        <v>5.729</v>
       </c>
       <c r="H1142" s="14">
-        <v>1.88</v>
+        <v>1.671</v>
       </c>
       <c r="I1142" s="15">
-        <v>34.1</v>
+        <v>29.2</v>
       </c>
       <c r="J1142" s="12">
-        <v>42.8</v>
+        <v>41.2</v>
       </c>
       <c r="K1142" s="16">
-        <v>-35.4</v>
+        <v>-33.8</v>
       </c>
       <c r="L1142" s="15">
-        <v>-82.7</v>
+        <v>-82</v>
       </c>
       <c r="M1142" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1143" spans="1:13" x14ac:dyDescent="0.25">
@@ -66341,7 +66338,7 @@
         <v>211</v>
       </c>
       <c r="C1143" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1143" t="s">
         <v>52</v>
@@ -66353,25 +66350,25 @@
         <v>14</v>
       </c>
       <c r="G1143" s="13">
-        <v>10.718</v>
+        <v>11.323</v>
       </c>
       <c r="H1143" s="14">
-        <v>3.282</v>
+        <v>2.677</v>
       </c>
       <c r="I1143" s="15">
-        <v>30.6</v>
+        <v>23.6</v>
       </c>
       <c r="J1143" s="12">
-        <v>126.5</v>
+        <v>127.167</v>
       </c>
       <c r="K1143" s="16">
-        <v>-112.5</v>
+        <v>-113.167</v>
       </c>
       <c r="L1143" s="15">
-        <v>-88.9</v>
+        <v>-89</v>
       </c>
       <c r="M1143" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="1144" spans="1:13" x14ac:dyDescent="0.25">
@@ -66382,7 +66379,7 @@
         <v>211</v>
       </c>
       <c r="C1144" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1144" t="s">
         <v>52</v>
@@ -66394,25 +66391,25 @@
         <v>29</v>
       </c>
       <c r="G1144" s="13">
-        <v>23.077</v>
+        <v>23.162</v>
       </c>
       <c r="H1144" s="14">
-        <v>5.923</v>
+        <v>5.838</v>
       </c>
       <c r="I1144" s="15">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="J1144" s="12">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K1144" s="16">
-        <v>-117</v>
+        <v>-128</v>
       </c>
       <c r="L1144" s="15">
-        <v>-80.1</v>
+        <v>-81.5</v>
       </c>
       <c r="M1144" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1145" spans="1:13" x14ac:dyDescent="0.25">
@@ -66423,7 +66420,7 @@
         <v>211</v>
       </c>
       <c r="C1145" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1145" t="s">
         <v>52</v>
@@ -66435,25 +66432,25 @@
         <v>55</v>
       </c>
       <c r="G1145" s="13">
-        <v>39.735</v>
+        <v>37.046</v>
       </c>
       <c r="H1145" s="14">
-        <v>15.265</v>
+        <v>17.954</v>
       </c>
       <c r="I1145" s="15">
-        <v>38.4</v>
+        <v>48.5</v>
       </c>
       <c r="J1145" s="12">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="K1145" s="16">
-        <v>-225</v>
+        <v>-195</v>
       </c>
       <c r="L1145" s="15">
-        <v>-80.4</v>
+        <v>-78</v>
       </c>
       <c r="M1145" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1146" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -66527,7 +66524,7 @@
         <v>-48.8</v>
       </c>
       <c r="M1147" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1148" spans="1:13" x14ac:dyDescent="0.25">
@@ -66568,7 +66565,7 @@
         <v>-72.3</v>
       </c>
       <c r="M1148" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1149" spans="1:13" x14ac:dyDescent="0.25">
@@ -66609,7 +66606,7 @@
         <v>-82</v>
       </c>
       <c r="M1149" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1150" spans="1:13" x14ac:dyDescent="0.25">
@@ -66650,7 +66647,7 @@
         <v>-86.6</v>
       </c>
       <c r="M1150" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1151" spans="1:13" x14ac:dyDescent="0.25">
@@ -66691,7 +66688,7 @@
         <v>-87.8</v>
       </c>
       <c r="M1151" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1152" spans="1:13" x14ac:dyDescent="0.25">
@@ -66732,7 +66729,7 @@
         <v>-77.7</v>
       </c>
       <c r="M1152" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1153" spans="1:13" x14ac:dyDescent="0.25">
@@ -66773,7 +66770,7 @@
         <v>-80.1</v>
       </c>
       <c r="M1153" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1154" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -66781,13 +66778,13 @@
         <v>881</v>
       </c>
       <c r="B1154" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1154" s="4" t="s">
         <v>125</v>
       </c>
       <c r="D1154" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1154" s="4" t="s">
         <v>441</v>
@@ -66814,13 +66811,13 @@
         <v>881</v>
       </c>
       <c r="B1155" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1155" t="s">
         <v>125</v>
       </c>
       <c r="D1155" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1155" t="s">
         <v>433</v>
@@ -66847,7 +66844,7 @@
         <v>-46.9</v>
       </c>
       <c r="M1155" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1156" spans="1:13" x14ac:dyDescent="0.25">
@@ -66855,13 +66852,13 @@
         <v>881</v>
       </c>
       <c r="B1156" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1156" t="s">
         <v>125</v>
       </c>
       <c r="D1156" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1156" t="s">
         <v>452</v>
@@ -66888,7 +66885,7 @@
         <v>-68.4</v>
       </c>
       <c r="M1156" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1157" spans="1:13" x14ac:dyDescent="0.25">
@@ -66896,13 +66893,13 @@
         <v>881</v>
       </c>
       <c r="B1157" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1157" t="s">
         <v>125</v>
       </c>
       <c r="D1157" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1157" t="s">
         <v>423</v>
@@ -66929,7 +66926,7 @@
         <v>-82.8</v>
       </c>
       <c r="M1157" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1158" spans="1:13" x14ac:dyDescent="0.25">
@@ -66937,13 +66934,13 @@
         <v>881</v>
       </c>
       <c r="B1158" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1158" t="s">
         <v>125</v>
       </c>
       <c r="D1158" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1158" t="s">
         <v>438</v>
@@ -66970,7 +66967,7 @@
         <v>-87.5</v>
       </c>
       <c r="M1158" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1159" spans="1:13" x14ac:dyDescent="0.25">
@@ -66978,13 +66975,13 @@
         <v>881</v>
       </c>
       <c r="B1159" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1159" t="s">
         <v>125</v>
       </c>
       <c r="D1159" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1159" t="s">
         <v>430</v>
@@ -67011,7 +67008,7 @@
         <v>-91.8</v>
       </c>
       <c r="M1159" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1160" spans="1:13" x14ac:dyDescent="0.25">
@@ -67019,13 +67016,13 @@
         <v>881</v>
       </c>
       <c r="B1160" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1160" t="s">
         <v>125</v>
       </c>
       <c r="D1160" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1160" t="s">
         <v>522</v>
@@ -67052,7 +67049,7 @@
         <v>-84.6</v>
       </c>
       <c r="M1160" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1161" spans="1:13" x14ac:dyDescent="0.25">
@@ -67060,13 +67057,13 @@
         <v>881</v>
       </c>
       <c r="B1161" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C1161" t="s">
         <v>125</v>
       </c>
       <c r="D1161" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1161" t="s">
         <v>634</v>
@@ -67093,7 +67090,7 @@
         <v>-85.1</v>
       </c>
       <c r="M1161" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1162" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -67101,13 +67098,13 @@
         <v>881</v>
       </c>
       <c r="B1162" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1162" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D1162" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1162" s="4" t="s">
         <v>441</v>
@@ -67134,13 +67131,13 @@
         <v>881</v>
       </c>
       <c r="B1163" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1163" t="s">
         <v>132</v>
       </c>
       <c r="D1163" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1163" t="s">
         <v>433</v>
@@ -67167,7 +67164,7 @@
         <v>-42.5</v>
       </c>
       <c r="M1163" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1164" spans="1:13" x14ac:dyDescent="0.25">
@@ -67175,13 +67172,13 @@
         <v>881</v>
       </c>
       <c r="B1164" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1164" t="s">
         <v>132</v>
       </c>
       <c r="D1164" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1164" t="s">
         <v>452</v>
@@ -67208,7 +67205,7 @@
         <v>-67.1</v>
       </c>
       <c r="M1164" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1165" spans="1:13" x14ac:dyDescent="0.25">
@@ -67216,13 +67213,13 @@
         <v>881</v>
       </c>
       <c r="B1165" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1165" t="s">
         <v>132</v>
       </c>
       <c r="D1165" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1165" t="s">
         <v>423</v>
@@ -67249,7 +67246,7 @@
         <v>-81.1</v>
       </c>
       <c r="M1165" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1166" spans="1:13" x14ac:dyDescent="0.25">
@@ -67257,13 +67254,13 @@
         <v>881</v>
       </c>
       <c r="B1166" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1166" t="s">
         <v>132</v>
       </c>
       <c r="D1166" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1166" t="s">
         <v>438</v>
@@ -67290,7 +67287,7 @@
         <v>-86.4</v>
       </c>
       <c r="M1166" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1167" spans="1:13" x14ac:dyDescent="0.25">
@@ -67298,13 +67295,13 @@
         <v>881</v>
       </c>
       <c r="B1167" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1167" t="s">
         <v>132</v>
       </c>
       <c r="D1167" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1167" t="s">
         <v>430</v>
@@ -67331,7 +67328,7 @@
         <v>-89.7</v>
       </c>
       <c r="M1167" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1168" spans="1:13" x14ac:dyDescent="0.25">
@@ -67339,13 +67336,13 @@
         <v>881</v>
       </c>
       <c r="B1168" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1168" t="s">
         <v>132</v>
       </c>
       <c r="D1168" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1168" t="s">
         <v>522</v>
@@ -67372,7 +67369,7 @@
         <v>-83.9</v>
       </c>
       <c r="M1168" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1169" spans="1:13" x14ac:dyDescent="0.25">
@@ -67380,13 +67377,13 @@
         <v>881</v>
       </c>
       <c r="B1169" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C1169" t="s">
         <v>132</v>
       </c>
       <c r="D1169" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1169" t="s">
         <v>634</v>
@@ -67413,7 +67410,7 @@
         <v>-84.4</v>
       </c>
       <c r="M1169" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1170" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -67421,23 +67418,23 @@
         <v>881</v>
       </c>
       <c r="B1170" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1170" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D1170" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1170" s="4" t="s">
         <v>441</v>
       </c>
       <c r="F1170" s="8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1170" s="9"/>
       <c r="H1170" s="10">
-        <v>2.729</v>
+        <v>2.757</v>
       </c>
       <c r="I1170" s="11"/>
       <c r="J1170" s="8"/>
@@ -67446,7 +67443,7 @@
       </c>
       <c r="L1170" s="11"/>
       <c r="M1170" s="4" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1171" spans="1:13" x14ac:dyDescent="0.25">
@@ -67454,40 +67451,40 @@
         <v>881</v>
       </c>
       <c r="B1171" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1171" t="s">
         <v>68</v>
       </c>
       <c r="D1171" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1171" t="s">
         <v>433</v>
       </c>
       <c r="F1171" s="12">
-        <v>9.7</v>
+        <v>10.2</v>
       </c>
       <c r="G1171" s="13">
-        <v>8.333</v>
+        <v>8.817</v>
       </c>
       <c r="H1171" s="14">
-        <v>1.367</v>
+        <v>1.383</v>
       </c>
       <c r="I1171" s="15">
-        <v>16.4</v>
+        <v>15.7</v>
       </c>
       <c r="J1171" s="12">
-        <v>30</v>
+        <v>32.75</v>
       </c>
       <c r="K1171" s="16">
-        <v>-20.3</v>
+        <v>-22.55</v>
       </c>
       <c r="L1171" s="15">
-        <v>-67.7</v>
+        <v>-68.8</v>
       </c>
       <c r="M1171" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1172" spans="1:13" x14ac:dyDescent="0.25">
@@ -67495,40 +67492,40 @@
         <v>881</v>
       </c>
       <c r="B1172" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1172" t="s">
         <v>68</v>
       </c>
       <c r="D1172" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1172" t="s">
         <v>452</v>
       </c>
       <c r="F1172" s="12">
-        <v>5.15</v>
+        <v>5.35</v>
       </c>
       <c r="G1172" s="13">
-        <v>4.164</v>
+        <v>4.318</v>
       </c>
       <c r="H1172" s="14">
-        <v>0.986</v>
+        <v>1.032</v>
       </c>
       <c r="I1172" s="15">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="J1172" s="12">
-        <v>40.1</v>
+        <v>47.267</v>
       </c>
       <c r="K1172" s="16">
-        <v>-34.95</v>
+        <v>-41.917</v>
       </c>
       <c r="L1172" s="15">
-        <v>-87.2</v>
+        <v>-88.7</v>
       </c>
       <c r="M1172" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1173" spans="1:13" x14ac:dyDescent="0.25">
@@ -67536,13 +67533,13 @@
         <v>881</v>
       </c>
       <c r="B1173" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1173" t="s">
         <v>68</v>
       </c>
       <c r="D1173" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1173" t="s">
         <v>423</v>
@@ -67551,25 +67548,25 @@
         <v>3.75</v>
       </c>
       <c r="G1173" s="13">
-        <v>3.554</v>
+        <v>3.518</v>
       </c>
       <c r="H1173" s="14">
-        <v>0.196</v>
+        <v>0.232</v>
       </c>
       <c r="I1173" s="15">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J1173" s="12">
-        <v>102.75</v>
+        <v>102.963</v>
       </c>
       <c r="K1173" s="16">
-        <v>-99</v>
+        <v>-99.213</v>
       </c>
       <c r="L1173" s="15">
-        <v>-96.3</v>
+        <v>-96.4</v>
       </c>
       <c r="M1173" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1174" spans="1:13" x14ac:dyDescent="0.25">
@@ -67577,40 +67574,40 @@
         <v>881</v>
       </c>
       <c r="B1174" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1174" t="s">
         <v>68</v>
       </c>
       <c r="D1174" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1174" t="s">
         <v>438</v>
       </c>
       <c r="F1174" s="12">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G1174" s="13">
-        <v>3.657</v>
+        <v>3.615</v>
       </c>
       <c r="H1174" s="14">
-        <v>0.243</v>
+        <v>0.185</v>
       </c>
       <c r="I1174" s="15">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="J1174" s="12">
-        <v>192.4</v>
+        <v>192.35</v>
       </c>
       <c r="K1174" s="16">
-        <v>-188.5</v>
+        <v>-188.55</v>
       </c>
       <c r="L1174" s="15">
         <v>-98</v>
       </c>
       <c r="M1174" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1175" spans="1:13" x14ac:dyDescent="0.25">
@@ -67618,40 +67615,40 @@
         <v>881</v>
       </c>
       <c r="B1175" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1175" t="s">
         <v>68</v>
       </c>
       <c r="D1175" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1175" t="s">
         <v>430</v>
       </c>
       <c r="F1175" s="12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G1175" s="13">
-        <v>4.648</v>
+        <v>4.559</v>
       </c>
       <c r="H1175" s="14">
-        <v>0.952</v>
+        <v>0.941</v>
       </c>
       <c r="I1175" s="15">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="J1175" s="12">
-        <v>240.167</v>
+        <v>239.917</v>
       </c>
       <c r="K1175" s="16">
-        <v>-234.567</v>
+        <v>-234.417</v>
       </c>
       <c r="L1175" s="15">
         <v>-97.7</v>
       </c>
       <c r="M1175" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1176" spans="1:13" x14ac:dyDescent="0.25">
@@ -67659,40 +67656,40 @@
         <v>881</v>
       </c>
       <c r="B1176" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1176" t="s">
         <v>68</v>
       </c>
       <c r="D1176" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1176" t="s">
         <v>522</v>
       </c>
       <c r="F1176" s="12">
-        <v>8.85</v>
+        <v>8.7</v>
       </c>
       <c r="G1176" s="13">
-        <v>9.783</v>
+        <v>9.511</v>
       </c>
       <c r="H1176" s="17">
-        <v>-0.933</v>
+        <v>-0.811</v>
       </c>
       <c r="I1176" s="15">
-        <v>-9.5</v>
+        <v>-8.5</v>
       </c>
       <c r="J1176" s="12">
-        <v>265.8</v>
+        <v>265.6</v>
       </c>
       <c r="K1176" s="16">
-        <v>-256.95</v>
+        <v>-256.9</v>
       </c>
       <c r="L1176" s="15">
         <v>-96.7</v>
       </c>
       <c r="M1176" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.25">
@@ -67700,40 +67697,40 @@
         <v>881</v>
       </c>
       <c r="B1177" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C1177" t="s">
         <v>68</v>
       </c>
       <c r="D1177" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1177" t="s">
         <v>634</v>
       </c>
       <c r="F1177" s="12">
-        <v>8.85</v>
+        <v>8.7</v>
       </c>
       <c r="G1177" s="13">
-        <v>6.767</v>
+        <v>6.607</v>
       </c>
       <c r="H1177" s="14">
-        <v>2.083</v>
+        <v>2.093</v>
       </c>
       <c r="I1177" s="15">
-        <v>30.8</v>
+        <v>31.7</v>
       </c>
       <c r="J1177" s="12">
-        <v>290.7</v>
+        <v>290.65</v>
       </c>
       <c r="K1177" s="16">
-        <v>-281.85</v>
+        <v>-281.95</v>
       </c>
       <c r="L1177" s="15">
         <v>-97</v>
       </c>
       <c r="M1177" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1178" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -67741,23 +67738,23 @@
         <v>881</v>
       </c>
       <c r="B1178" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1178" s="4" t="s">
         <v>141</v>
       </c>
       <c r="D1178" s="4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1178" s="4" t="s">
         <v>441</v>
       </c>
       <c r="F1178" s="8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1178" s="9"/>
       <c r="H1178" s="10">
-        <v>2.324</v>
+        <v>2.991</v>
       </c>
       <c r="I1178" s="11"/>
       <c r="J1178" s="8"/>
@@ -67766,7 +67763,7 @@
       </c>
       <c r="L1178" s="11"/>
       <c r="M1178" s="4" t="s">
-        <v>2036</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1179" spans="1:13" x14ac:dyDescent="0.25">
@@ -67774,40 +67771,40 @@
         <v>881</v>
       </c>
       <c r="B1179" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1179" t="s">
         <v>141</v>
       </c>
       <c r="D1179" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1179" t="s">
         <v>433</v>
       </c>
       <c r="F1179" s="12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G1179" s="13">
-        <v>8.839</v>
+        <v>8.949</v>
       </c>
       <c r="H1179" s="14">
-        <v>1.161</v>
+        <v>1.551</v>
       </c>
       <c r="I1179" s="15">
-        <v>13.1</v>
+        <v>17.3</v>
       </c>
       <c r="J1179" s="12">
-        <v>28</v>
+        <v>29.5</v>
       </c>
       <c r="K1179" s="16">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="L1179" s="15">
-        <v>-64.3</v>
+        <v>-64.4</v>
       </c>
       <c r="M1179" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1180" spans="1:13" x14ac:dyDescent="0.25">
@@ -67815,40 +67812,40 @@
         <v>881</v>
       </c>
       <c r="B1180" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1180" t="s">
         <v>141</v>
       </c>
       <c r="D1180" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1180" t="s">
         <v>452</v>
       </c>
       <c r="F1180" s="12">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G1180" s="13">
-        <v>4.385</v>
+        <v>4.486</v>
       </c>
       <c r="H1180" s="14">
-        <v>1.215</v>
+        <v>1.214</v>
       </c>
       <c r="I1180" s="15">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="J1180" s="12">
-        <v>36.833</v>
+        <v>37.167</v>
       </c>
       <c r="K1180" s="16">
-        <v>-31.233</v>
+        <v>-31.467</v>
       </c>
       <c r="L1180" s="15">
-        <v>-84.8</v>
+        <v>-84.7</v>
       </c>
       <c r="M1180" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1181" spans="1:13" x14ac:dyDescent="0.25">
@@ -67856,13 +67853,13 @@
         <v>881</v>
       </c>
       <c r="B1181" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1181" t="s">
         <v>141</v>
       </c>
       <c r="D1181" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1181" t="s">
         <v>423</v>
@@ -67871,25 +67868,25 @@
         <v>3.6</v>
       </c>
       <c r="G1181" s="13">
-        <v>3.486</v>
+        <v>3.494</v>
       </c>
       <c r="H1181" s="14">
-        <v>0.114</v>
+        <v>0.106</v>
       </c>
       <c r="I1181" s="15">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J1181" s="12">
-        <v>63.438</v>
+        <v>63.688</v>
       </c>
       <c r="K1181" s="16">
-        <v>-59.838</v>
+        <v>-60.088</v>
       </c>
       <c r="L1181" s="15">
         <v>-94.3</v>
       </c>
       <c r="M1181" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1182" spans="1:13" x14ac:dyDescent="0.25">
@@ -67897,13 +67894,13 @@
         <v>881</v>
       </c>
       <c r="B1182" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1182" t="s">
         <v>141</v>
       </c>
       <c r="D1182" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1182" t="s">
         <v>438</v>
@@ -67912,25 +67909,25 @@
         <v>3.9</v>
       </c>
       <c r="G1182" s="13">
-        <v>3.633</v>
+        <v>3.564</v>
       </c>
       <c r="H1182" s="14">
-        <v>0.267</v>
+        <v>0.336</v>
       </c>
       <c r="I1182" s="15">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="J1182" s="12">
-        <v>144.3</v>
+        <v>144.2</v>
       </c>
       <c r="K1182" s="16">
-        <v>-140.4</v>
+        <v>-140.3</v>
       </c>
       <c r="L1182" s="15">
         <v>-97.3</v>
       </c>
       <c r="M1182" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1183" spans="1:13" x14ac:dyDescent="0.25">
@@ -67938,13 +67935,13 @@
         <v>881</v>
       </c>
       <c r="B1183" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1183" t="s">
         <v>141</v>
       </c>
       <c r="D1183" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1183" t="s">
         <v>430</v>
@@ -67971,7 +67968,7 @@
         <v>-97.7</v>
       </c>
       <c r="M1183" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1184" spans="1:13" x14ac:dyDescent="0.25">
@@ -67979,40 +67976,40 @@
         <v>881</v>
       </c>
       <c r="B1184" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1184" t="s">
         <v>141</v>
       </c>
       <c r="D1184" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1184" t="s">
         <v>522</v>
       </c>
       <c r="F1184" s="12">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="G1184" s="13">
         <v>8.846</v>
       </c>
       <c r="H1184" s="17">
-        <v>-0.096</v>
+        <v>-0.446</v>
       </c>
       <c r="I1184" s="15">
-        <v>-1.1</v>
+        <v>-5</v>
       </c>
       <c r="J1184" s="12">
         <v>251.2</v>
       </c>
       <c r="K1184" s="16">
-        <v>-242.45</v>
+        <v>-242.8</v>
       </c>
       <c r="L1184" s="15">
-        <v>-96.5</v>
+        <v>-96.7</v>
       </c>
       <c r="M1184" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1185" spans="1:13" x14ac:dyDescent="0.25">
@@ -68020,40 +68017,40 @@
         <v>881</v>
       </c>
       <c r="B1185" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1185" t="s">
         <v>141</v>
       </c>
       <c r="D1185" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E1185" t="s">
         <v>634</v>
       </c>
       <c r="F1185" s="12">
-        <v>8.5</v>
+        <v>8.2</v>
       </c>
       <c r="G1185" s="13">
-        <v>6.578</v>
+        <v>6.418</v>
       </c>
       <c r="H1185" s="14">
-        <v>1.922</v>
+        <v>1.782</v>
       </c>
       <c r="I1185" s="15">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="J1185" s="12">
-        <v>280.65</v>
+        <v>280.6</v>
       </c>
       <c r="K1185" s="16">
-        <v>-272.15</v>
+        <v>-272.4</v>
       </c>
       <c r="L1185" s="15">
-        <v>-97</v>
+        <v>-97.1</v>
       </c>
       <c r="M1185" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1186" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -68061,10 +68058,10 @@
         <v>881</v>
       </c>
       <c r="B1186" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1186" s="4" t="s">
         <v>920</v>
-      </c>
-      <c r="C1186" s="4" t="s">
-        <v>921</v>
       </c>
       <c r="D1186" s="4" t="s">
         <v>590</v>
@@ -68077,7 +68074,7 @@
       </c>
       <c r="G1186" s="9"/>
       <c r="H1186" s="10">
-        <v>2.169</v>
+        <v>2.167</v>
       </c>
       <c r="I1186" s="11"/>
       <c r="J1186" s="8"/>
@@ -68094,10 +68091,10 @@
         <v>881</v>
       </c>
       <c r="B1187" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1187" t="s">
         <v>920</v>
-      </c>
-      <c r="C1187" t="s">
-        <v>921</v>
       </c>
       <c r="D1187" t="s">
         <v>590</v>
@@ -68127,7 +68124,7 @@
         <v>-45.6</v>
       </c>
       <c r="M1187" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1188" spans="1:13" x14ac:dyDescent="0.25">
@@ -68135,10 +68132,10 @@
         <v>881</v>
       </c>
       <c r="B1188" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1188" t="s">
         <v>920</v>
-      </c>
-      <c r="C1188" t="s">
-        <v>921</v>
       </c>
       <c r="D1188" t="s">
         <v>590</v>
@@ -68168,7 +68165,7 @@
         <v>-69.3</v>
       </c>
       <c r="M1188" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1189" spans="1:13" x14ac:dyDescent="0.25">
@@ -68176,10 +68173,10 @@
         <v>881</v>
       </c>
       <c r="B1189" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1189" t="s">
         <v>920</v>
-      </c>
-      <c r="C1189" t="s">
-        <v>921</v>
       </c>
       <c r="D1189" t="s">
         <v>590</v>
@@ -68191,25 +68188,25 @@
         <v>3.5</v>
       </c>
       <c r="G1189" s="13">
-        <v>3.32</v>
+        <v>3.333</v>
       </c>
       <c r="H1189" s="14">
-        <v>0.18</v>
+        <v>0.167</v>
       </c>
       <c r="I1189" s="15">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J1189" s="12">
-        <v>18.188</v>
+        <v>18.625</v>
       </c>
       <c r="K1189" s="16">
-        <v>-14.688</v>
+        <v>-15.125</v>
       </c>
       <c r="L1189" s="15">
-        <v>-80.8</v>
+        <v>-81.2</v>
       </c>
       <c r="M1189" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1190" spans="1:13" x14ac:dyDescent="0.25">
@@ -68217,10 +68214,10 @@
         <v>881</v>
       </c>
       <c r="B1190" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1190" t="s">
         <v>920</v>
-      </c>
-      <c r="C1190" t="s">
-        <v>921</v>
       </c>
       <c r="D1190" t="s">
         <v>590</v>
@@ -68232,25 +68229,25 @@
         <v>5.85</v>
       </c>
       <c r="G1190" s="13">
-        <v>4.915</v>
+        <v>4.895</v>
       </c>
       <c r="H1190" s="14">
-        <v>0.935</v>
+        <v>0.955</v>
       </c>
       <c r="I1190" s="15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J1190" s="12">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="K1190" s="16">
-        <v>-34.15</v>
+        <v>-34.35</v>
       </c>
       <c r="L1190" s="15">
         <v>-85.4</v>
       </c>
       <c r="M1190" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1191" spans="1:13" x14ac:dyDescent="0.25">
@@ -68258,10 +68255,10 @@
         <v>881</v>
       </c>
       <c r="B1191" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1191" t="s">
         <v>920</v>
-      </c>
-      <c r="C1191" t="s">
-        <v>921</v>
       </c>
       <c r="D1191" t="s">
         <v>590</v>
@@ -68291,7 +68288,7 @@
         <v>-87.2</v>
       </c>
       <c r="M1191" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1192" spans="1:13" x14ac:dyDescent="0.25">
@@ -68299,10 +68296,10 @@
         <v>881</v>
       </c>
       <c r="B1192" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1192" t="s">
         <v>920</v>
-      </c>
-      <c r="C1192" t="s">
-        <v>921</v>
       </c>
       <c r="D1192" t="s">
         <v>590</v>
@@ -68332,7 +68329,7 @@
         <v>-75.5</v>
       </c>
       <c r="M1192" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1193" spans="1:13" x14ac:dyDescent="0.25">
@@ -68340,10 +68337,10 @@
         <v>881</v>
       </c>
       <c r="B1193" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1193" t="s">
         <v>920</v>
-      </c>
-      <c r="C1193" t="s">
-        <v>921</v>
       </c>
       <c r="D1193" t="s">
         <v>590</v>
@@ -68373,7 +68370,7 @@
         <v>-76.7</v>
       </c>
       <c r="M1193" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1194" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -68381,10 +68378,10 @@
         <v>881</v>
       </c>
       <c r="B1194" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1194" s="4" t="s">
         <v>922</v>
-      </c>
-      <c r="C1194" s="4" t="s">
-        <v>923</v>
       </c>
       <c r="D1194" s="4" t="s">
         <v>534</v>
@@ -68406,7 +68403,7 @@
       </c>
       <c r="L1194" s="11"/>
       <c r="M1194" s="4" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1195" spans="1:13" x14ac:dyDescent="0.25">
@@ -68414,10 +68411,10 @@
         <v>881</v>
       </c>
       <c r="B1195" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1195" t="s">
         <v>922</v>
-      </c>
-      <c r="C1195" t="s">
-        <v>923</v>
       </c>
       <c r="D1195" t="s">
         <v>534</v>
@@ -68447,7 +68444,7 @@
         <v>-49.4</v>
       </c>
       <c r="M1195" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1196" spans="1:13" x14ac:dyDescent="0.25">
@@ -68455,10 +68452,10 @@
         <v>881</v>
       </c>
       <c r="B1196" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1196" t="s">
         <v>922</v>
-      </c>
-      <c r="C1196" t="s">
-        <v>923</v>
       </c>
       <c r="D1196" t="s">
         <v>534</v>
@@ -68488,7 +68485,7 @@
         <v>-70.2</v>
       </c>
       <c r="M1196" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1197" spans="1:13" x14ac:dyDescent="0.25">
@@ -68496,10 +68493,10 @@
         <v>881</v>
       </c>
       <c r="B1197" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1197" t="s">
         <v>922</v>
-      </c>
-      <c r="C1197" t="s">
-        <v>923</v>
       </c>
       <c r="D1197" t="s">
         <v>534</v>
@@ -68529,7 +68526,7 @@
         <v>-80.5</v>
       </c>
       <c r="M1197" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1198" spans="1:13" x14ac:dyDescent="0.25">
@@ -68537,10 +68534,10 @@
         <v>881</v>
       </c>
       <c r="B1198" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1198" t="s">
         <v>922</v>
-      </c>
-      <c r="C1198" t="s">
-        <v>923</v>
       </c>
       <c r="D1198" t="s">
         <v>534</v>
@@ -68570,7 +68567,7 @@
         <v>-85.6</v>
       </c>
       <c r="M1198" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1199" spans="1:13" x14ac:dyDescent="0.25">
@@ -68578,10 +68575,10 @@
         <v>881</v>
       </c>
       <c r="B1199" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1199" t="s">
         <v>922</v>
-      </c>
-      <c r="C1199" t="s">
-        <v>923</v>
       </c>
       <c r="D1199" t="s">
         <v>534</v>
@@ -68611,7 +68608,7 @@
         <v>-88.6</v>
       </c>
       <c r="M1199" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1200" spans="1:13" x14ac:dyDescent="0.25">
@@ -68619,10 +68616,10 @@
         <v>881</v>
       </c>
       <c r="B1200" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1200" t="s">
         <v>922</v>
-      </c>
-      <c r="C1200" t="s">
-        <v>923</v>
       </c>
       <c r="D1200" t="s">
         <v>534</v>
@@ -68652,7 +68649,7 @@
         <v>-80.8</v>
       </c>
       <c r="M1200" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="1201" spans="1:13" x14ac:dyDescent="0.25">
@@ -68660,10 +68657,10 @@
         <v>881</v>
       </c>
       <c r="B1201" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1201" t="s">
         <v>922</v>
-      </c>
-      <c r="C1201" t="s">
-        <v>923</v>
       </c>
       <c r="D1201" t="s">
         <v>534</v>
@@ -68693,21 +68690,21 @@
         <v>-84.1</v>
       </c>
       <c r="M1201" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1202" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1202" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1202" s="4" t="s">
         <v>221</v>
       </c>
       <c r="C1202" s="4" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1202" s="4" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1202" s="4" t="s">
         <v>441</v>
@@ -68731,16 +68728,16 @@
     </row>
     <row r="1203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1203" t="s">
         <v>221</v>
       </c>
       <c r="C1203" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1203" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1203" t="s">
         <v>433</v>
@@ -68767,21 +68764,21 @@
         <v>-42.4</v>
       </c>
       <c r="M1203" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1204" t="s">
         <v>221</v>
       </c>
       <c r="C1204" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1204" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1204" t="s">
         <v>452</v>
@@ -68808,21 +68805,21 @@
         <v>-67.4</v>
       </c>
       <c r="M1204" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1205" t="s">
         <v>221</v>
       </c>
       <c r="C1205" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1205" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1205" t="s">
         <v>423</v>
@@ -68849,21 +68846,21 @@
         <v>-78.9</v>
       </c>
       <c r="M1205" t="s">
-        <v>1967</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1206" t="s">
         <v>221</v>
       </c>
       <c r="C1206" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1206" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1206" t="s">
         <v>438</v>
@@ -68890,21 +68887,21 @@
         <v>-87.9</v>
       </c>
       <c r="M1206" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1207" t="s">
         <v>221</v>
       </c>
       <c r="C1207" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1207" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1207" t="s">
         <v>430</v>
@@ -68931,21 +68928,21 @@
         <v>-91.6</v>
       </c>
       <c r="M1207" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1208" t="s">
         <v>221</v>
       </c>
       <c r="C1208" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1208" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1208" t="s">
         <v>522</v>
@@ -68972,21 +68969,21 @@
         <v>-85.9</v>
       </c>
       <c r="M1208" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="1209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1209" t="s">
         <v>221</v>
       </c>
       <c r="C1209" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D1209" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E1209" t="s">
         <v>634</v>
@@ -69013,21 +69010,21 @@
         <v>-84.7</v>
       </c>
       <c r="M1209" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1210" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1210" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1210" s="4" t="s">
         <v>225</v>
       </c>
       <c r="C1210" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1210" s="4" t="s">
         <v>934</v>
-      </c>
-      <c r="D1210" s="4" t="s">
-        <v>935</v>
       </c>
       <c r="E1210" s="4" t="s">
         <v>441</v>
@@ -69046,21 +69043,21 @@
       </c>
       <c r="L1210" s="11"/>
       <c r="M1210" s="4" t="s">
-        <v>2036</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1211" t="s">
         <v>225</v>
       </c>
       <c r="C1211" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1211" t="s">
         <v>934</v>
-      </c>
-      <c r="D1211" t="s">
-        <v>935</v>
       </c>
       <c r="E1211" t="s">
         <v>433</v>
@@ -69087,21 +69084,21 @@
         <v>-44.4</v>
       </c>
       <c r="M1211" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1212" t="s">
         <v>225</v>
       </c>
       <c r="C1212" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1212" t="s">
         <v>934</v>
-      </c>
-      <c r="D1212" t="s">
-        <v>935</v>
       </c>
       <c r="E1212" t="s">
         <v>452</v>
@@ -69128,21 +69125,21 @@
         <v>-64.5</v>
       </c>
       <c r="M1212" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1213" t="s">
         <v>225</v>
       </c>
       <c r="C1213" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1213" t="s">
         <v>934</v>
-      </c>
-      <c r="D1213" t="s">
-        <v>935</v>
       </c>
       <c r="E1213" t="s">
         <v>423</v>
@@ -69169,21 +69166,21 @@
         <v>-79.2</v>
       </c>
       <c r="M1213" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1214" t="s">
         <v>225</v>
       </c>
       <c r="C1214" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1214" t="s">
         <v>934</v>
-      </c>
-      <c r="D1214" t="s">
-        <v>935</v>
       </c>
       <c r="E1214" t="s">
         <v>438</v>
@@ -69210,21 +69207,21 @@
         <v>-87.4</v>
       </c>
       <c r="M1214" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1215" t="s">
         <v>225</v>
       </c>
       <c r="C1215" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1215" t="s">
         <v>934</v>
-      </c>
-      <c r="D1215" t="s">
-        <v>935</v>
       </c>
       <c r="E1215" t="s">
         <v>430</v>
@@ -69251,21 +69248,21 @@
         <v>-93.3</v>
       </c>
       <c r="M1215" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1216" t="s">
         <v>225</v>
       </c>
       <c r="C1216" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1216" t="s">
         <v>934</v>
-      </c>
-      <c r="D1216" t="s">
-        <v>935</v>
       </c>
       <c r="E1216" t="s">
         <v>522</v>
@@ -69292,21 +69289,21 @@
         <v>-85.2</v>
       </c>
       <c r="M1216" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1217" t="s">
         <v>225</v>
       </c>
       <c r="C1217" t="s">
+        <v>933</v>
+      </c>
+      <c r="D1217" t="s">
         <v>934</v>
-      </c>
-      <c r="D1217" t="s">
-        <v>935</v>
       </c>
       <c r="E1217" t="s">
         <v>634</v>
@@ -69333,12 +69330,12 @@
         <v>-87.4</v>
       </c>
       <c r="M1217" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1218" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1218" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1218" s="4" t="s">
         <v>228</v>
@@ -69371,7 +69368,7 @@
     </row>
     <row r="1219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1219" t="s">
         <v>228</v>
@@ -69407,12 +69404,12 @@
         <v>-51.4</v>
       </c>
       <c r="M1219" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1220" t="s">
         <v>228</v>
@@ -69448,12 +69445,12 @@
         <v>-76</v>
       </c>
       <c r="M1220" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1221" t="s">
         <v>228</v>
@@ -69489,12 +69486,12 @@
         <v>-88.5</v>
       </c>
       <c r="M1221" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1222" t="s">
         <v>228</v>
@@ -69530,12 +69527,12 @@
         <v>-94.4</v>
       </c>
       <c r="M1222" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1223" t="s">
         <v>228</v>
@@ -69571,12 +69568,12 @@
         <v>-95.1</v>
       </c>
       <c r="M1223" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1224" t="s">
         <v>228</v>
@@ -69612,12 +69609,12 @@
         <v>-91.7</v>
       </c>
       <c r="M1224" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1225" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1225" t="s">
         <v>228</v>
@@ -69653,12 +69650,12 @@
         <v>-92</v>
       </c>
       <c r="M1225" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1226" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1226" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1226" s="4" t="s">
         <v>233</v>
@@ -69691,7 +69688,7 @@
     </row>
     <row r="1227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1227" t="s">
         <v>233</v>
@@ -69732,7 +69729,7 @@
     </row>
     <row r="1228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1228" t="s">
         <v>233</v>
@@ -69768,12 +69765,12 @@
         <v>-72.8</v>
       </c>
       <c r="M1228" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1229" t="s">
         <v>233</v>
@@ -69809,12 +69806,12 @@
         <v>-84.1</v>
       </c>
       <c r="M1229" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1230" t="s">
         <v>233</v>
@@ -69850,12 +69847,12 @@
         <v>-91.5</v>
       </c>
       <c r="M1230" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1231" t="s">
         <v>233</v>
@@ -69891,12 +69888,12 @@
         <v>-94.7</v>
       </c>
       <c r="M1231" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1232" t="s">
         <v>233</v>
@@ -69932,12 +69929,12 @@
         <v>-91</v>
       </c>
       <c r="M1232" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1233" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1233" t="s">
         <v>233</v>
@@ -69973,12 +69970,12 @@
         <v>-88.9</v>
       </c>
       <c r="M1233" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1234" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1234" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1234" s="4" t="s">
         <v>236</v>
@@ -70011,7 +70008,7 @@
     </row>
     <row r="1235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1235" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1235" t="s">
         <v>236</v>
@@ -70047,12 +70044,12 @@
         <v>-46.6</v>
       </c>
       <c r="M1235" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1236" t="s">
         <v>236</v>
@@ -70088,12 +70085,12 @@
         <v>-70.5</v>
       </c>
       <c r="M1236" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1237" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1237" t="s">
         <v>236</v>
@@ -70129,12 +70126,12 @@
         <v>-84</v>
       </c>
       <c r="M1237" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1238" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1238" t="s">
         <v>236</v>
@@ -70170,12 +70167,12 @@
         <v>-89.2</v>
       </c>
       <c r="M1238" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1239" t="s">
         <v>236</v>
@@ -70211,12 +70208,12 @@
         <v>-94.3</v>
       </c>
       <c r="M1239" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1240" t="s">
         <v>236</v>
@@ -70252,12 +70249,12 @@
         <v>-88.4</v>
       </c>
       <c r="M1240" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1241" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1241" t="s">
         <v>236</v>
@@ -70293,12 +70290,12 @@
         <v>-89.1</v>
       </c>
       <c r="M1241" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1242" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1242" s="4" t="s">
         <v>239</v>
@@ -70331,7 +70328,7 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1243" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1243" t="s">
         <v>239</v>
@@ -70372,7 +70369,7 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1244" t="s">
         <v>239</v>
@@ -70408,12 +70405,12 @@
         <v>-66.7</v>
       </c>
       <c r="M1244" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1245" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1245" t="s">
         <v>239</v>
@@ -70449,12 +70446,12 @@
         <v>-82.5</v>
       </c>
       <c r="M1245" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1246" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1246" t="s">
         <v>239</v>
@@ -70490,12 +70487,12 @@
         <v>-88</v>
       </c>
       <c r="M1246" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1247" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1247" t="s">
         <v>239</v>
@@ -70531,12 +70528,12 @@
         <v>-93.7</v>
       </c>
       <c r="M1247" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1248" t="s">
         <v>239</v>
@@ -70572,12 +70569,12 @@
         <v>-87.2</v>
       </c>
       <c r="M1248" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1249" t="s">
         <v>239</v>
@@ -70613,12 +70610,12 @@
         <v>-87.9</v>
       </c>
       <c r="M1249" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1250" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1250" s="4" t="s">
         <v>243</v>
@@ -70651,7 +70648,7 @@
     </row>
     <row r="1251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1251" t="s">
         <v>243</v>
@@ -70687,12 +70684,12 @@
         <v>-42.9</v>
       </c>
       <c r="M1251" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1252" t="s">
         <v>243</v>
@@ -70728,12 +70725,12 @@
         <v>-64.8</v>
       </c>
       <c r="M1252" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1253" t="s">
         <v>243</v>
@@ -70769,12 +70766,12 @@
         <v>-79</v>
       </c>
       <c r="M1253" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1254" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1254" t="s">
         <v>243</v>
@@ -70810,12 +70807,12 @@
         <v>-86.6</v>
       </c>
       <c r="M1254" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1255" t="s">
         <v>243</v>
@@ -70851,12 +70848,12 @@
         <v>-91.4</v>
       </c>
       <c r="M1255" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1256" t="s">
         <v>243</v>
@@ -70892,12 +70889,12 @@
         <v>-84.1</v>
       </c>
       <c r="M1256" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1257" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1257" t="s">
         <v>243</v>
@@ -70933,12 +70930,12 @@
         <v>-87.5</v>
       </c>
       <c r="M1257" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1258" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1258" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1258" s="4" t="s">
         <v>246</v>
@@ -70971,7 +70968,7 @@
     </row>
     <row r="1259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1259" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1259" t="s">
         <v>246</v>
@@ -71007,12 +71004,12 @@
         <v>-44.5</v>
       </c>
       <c r="M1259" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1260" t="s">
         <v>246</v>
@@ -71048,12 +71045,12 @@
         <v>-67.5</v>
       </c>
       <c r="M1260" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1261" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1261" t="s">
         <v>246</v>
@@ -71089,12 +71086,12 @@
         <v>-78.2</v>
       </c>
       <c r="M1261" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1262" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1262" t="s">
         <v>246</v>
@@ -71130,12 +71127,12 @@
         <v>-87.3</v>
       </c>
       <c r="M1262" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1263" t="s">
         <v>246</v>
@@ -71171,12 +71168,12 @@
         <v>-91.8</v>
       </c>
       <c r="M1263" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1264" t="s">
         <v>246</v>
@@ -71212,12 +71209,12 @@
         <v>-85.4</v>
       </c>
       <c r="M1264" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1265" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1265" t="s">
         <v>246</v>
@@ -71253,12 +71250,12 @@
         <v>-86.5</v>
       </c>
       <c r="M1265" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1266" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1266" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1266" s="4" t="s">
         <v>250</v>
@@ -71291,7 +71288,7 @@
     </row>
     <row r="1267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1267" t="s">
         <v>250</v>
@@ -71327,12 +71324,12 @@
         <v>-44.2</v>
       </c>
       <c r="M1267" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1268" t="s">
         <v>250</v>
@@ -71368,12 +71365,12 @@
         <v>-66.2</v>
       </c>
       <c r="M1268" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1269" t="s">
         <v>250</v>
@@ -71409,12 +71406,12 @@
         <v>-79.6</v>
       </c>
       <c r="M1269" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1270" t="s">
         <v>250</v>
@@ -71450,12 +71447,12 @@
         <v>-87.3</v>
       </c>
       <c r="M1270" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1271" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1271" t="s">
         <v>250</v>
@@ -71491,12 +71488,12 @@
         <v>-92.3</v>
       </c>
       <c r="M1271" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1272" t="s">
         <v>250</v>
@@ -71532,12 +71529,12 @@
         <v>-86.2</v>
       </c>
       <c r="M1272" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1273" t="s">
         <v>250</v>
@@ -71573,12 +71570,12 @@
         <v>-88.5</v>
       </c>
       <c r="M1273" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1274" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1274" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1274" s="4" t="s">
         <v>253</v>
@@ -71611,7 +71608,7 @@
     </row>
     <row r="1275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1275" t="s">
         <v>253</v>
@@ -71652,7 +71649,7 @@
     </row>
     <row r="1276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1276" t="s">
         <v>253</v>
@@ -71688,12 +71685,12 @@
         <v>-67.5</v>
       </c>
       <c r="M1276" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1277" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1277" t="s">
         <v>253</v>
@@ -71729,12 +71726,12 @@
         <v>-80.4</v>
       </c>
       <c r="M1277" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1278" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1278" t="s">
         <v>253</v>
@@ -71770,12 +71767,12 @@
         <v>-88.7</v>
       </c>
       <c r="M1278" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1279" t="s">
         <v>253</v>
@@ -71811,12 +71808,12 @@
         <v>-92.5</v>
       </c>
       <c r="M1279" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1280" t="s">
         <v>253</v>
@@ -71852,12 +71849,12 @@
         <v>-87.3</v>
       </c>
       <c r="M1280" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1281" t="s">
         <v>253</v>
@@ -71893,12 +71890,12 @@
         <v>-89.5</v>
       </c>
       <c r="M1281" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1282" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1282" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1282" s="4" t="s">
         <v>256</v>
@@ -71931,7 +71928,7 @@
     </row>
     <row r="1283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1283" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1283" t="s">
         <v>256</v>
@@ -71967,12 +71964,12 @@
         <v>-47.6</v>
       </c>
       <c r="M1283" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1284" t="s">
         <v>256</v>
@@ -72008,12 +72005,12 @@
         <v>-68.4</v>
       </c>
       <c r="M1284" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1285" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1285" t="s">
         <v>256</v>
@@ -72049,12 +72046,12 @@
         <v>-80.5</v>
       </c>
       <c r="M1285" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1286" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1286" t="s">
         <v>256</v>
@@ -72090,12 +72087,12 @@
         <v>-85.7</v>
       </c>
       <c r="M1286" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1287" t="s">
         <v>256</v>
@@ -72131,12 +72128,12 @@
         <v>-89.3</v>
       </c>
       <c r="M1287" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1288" t="s">
         <v>256</v>
@@ -72172,12 +72169,12 @@
         <v>-83.5</v>
       </c>
       <c r="M1288" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1289" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B1289" t="s">
         <v>256</v>
@@ -72213,7 +72210,7 @@
         <v>-82.4</v>
       </c>
       <c r="M1289" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
   </sheetData>
@@ -72234,17 +72231,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="B4">
         <v>136</v>
@@ -72252,7 +72249,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="B5">
         <v>136</v>
@@ -72260,67 +72257,67 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B6" t="s">
         <v>2136</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B7" t="s">
         <v>2138</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B8" t="s">
         <v>2140</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B12" t="s">
         <v>2144</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2145</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B13" t="s">
         <v>2146</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2147</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B17">
         <v>136</v>
@@ -72328,68 +72325,68 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B18" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B19" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B20" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>2155</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>2157</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>2158</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>2159</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>2160</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>2161</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>2163</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>2164</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>2165</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -72403,22 +72400,22 @@
         <v>21</v>
       </c>
       <c r="D25" s="21" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E25" s="21" t="s">
         <v>2166</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="F25" s="21" t="s">
         <v>2167</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="G25" s="21" t="s">
         <v>2168</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="H25" s="21" t="s">
         <v>2169</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="I25" s="21" t="s">
         <v>2170</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>2171</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -72426,25 +72423,25 @@
         <v>433</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>2172</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="D26" s="21" t="s">
         <v>2173</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="E26" s="21" t="s">
         <v>2174</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="F26" s="21" t="s">
         <v>2175</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="G26" s="21" t="s">
         <v>2176</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="H26" s="21" t="s">
         <v>2177</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>2178</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -72455,22 +72452,22 @@
         <v>452</v>
       </c>
       <c r="B27" s="21" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>2179</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>2173</v>
-      </c>
-      <c r="D27" s="21" t="s">
+      <c r="E27" s="21" t="s">
         <v>2180</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="F27" s="21" t="s">
         <v>2181</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="G27" s="21" t="s">
         <v>2182</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>2183</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -72484,22 +72481,22 @@
         <v>423</v>
       </c>
       <c r="B28" s="21" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>2184</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="D28" s="21" t="s">
         <v>2185</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>2186</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="F28" s="22" t="s">
         <v>2187</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="G28" s="21" t="s">
         <v>2188</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>2189</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -72513,28 +72510,28 @@
         <v>438</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="C29" s="21" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E29" s="21" t="s">
         <v>2190</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>2190</v>
-      </c>
-      <c r="E29" s="21" t="s">
+      <c r="F29" s="21" t="s">
         <v>2191</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="G29" s="21" t="s">
         <v>2192</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="H29" s="21" t="s">
         <v>2193</v>
       </c>
-      <c r="H29" s="21" t="s">
-        <v>2194</v>
-      </c>
       <c r="I29" s="21" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -72545,25 +72542,25 @@
         <v>21</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D30" s="21" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E30" s="21" t="s">
         <v>2195</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="F30" s="21" t="s">
         <v>2196</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="G30" s="21" t="s">
         <v>2197</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="H30" s="21" t="s">
         <v>2198</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="I30" s="21" t="s">
         <v>2199</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>2200</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -72571,28 +72568,28 @@
         <v>522</v>
       </c>
       <c r="B31" s="21" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>2201</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="D31" s="21" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F31" s="21" t="s">
         <v>2202</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>2194</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>2195</v>
-      </c>
-      <c r="F31" s="21" t="s">
+      <c r="G31" s="21" t="s">
         <v>2203</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="H31" s="21" t="s">
         <v>2204</v>
       </c>
-      <c r="H31" s="21" t="s">
-        <v>2205</v>
-      </c>
       <c r="I31" s="21" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -72600,33 +72597,33 @@
         <v>634</v>
       </c>
       <c r="B32" s="21" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E32" s="21" t="s">
         <v>2206</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>2194</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>2166</v>
-      </c>
-      <c r="E32" s="21" t="s">
+      <c r="F32" s="21" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G32" s="21" t="s">
         <v>2207</v>
       </c>
-      <c r="F32" s="21" t="s">
-        <v>2193</v>
-      </c>
-      <c r="G32" s="21" t="s">
+      <c r="H32" s="21" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I32" s="21" t="s">
         <v>2208</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>2183</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>2209</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
     </row>
   </sheetData>
@@ -72651,40 +72648,40 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2213</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>2214</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>2215</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>2216</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>2217</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>2218</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="B5">
         <v>136</v>
@@ -72707,7 +72704,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B6">
         <v>136</v>
@@ -72730,7 +72727,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="B7">
         <v>136</v>
@@ -72753,7 +72750,7 @@
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -72773,25 +72770,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>2223</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>2224</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>2225</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>2225</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>2226</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>2227</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>2228</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -77964,7 +77961,7 @@
     </row>
     <row r="148" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -77972,22 +77969,22 @@
         <v>0</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D149" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>2232</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="F149" s="2" t="s">
         <v>2233</v>
       </c>
-      <c r="F149" s="2" t="s">
+      <c r="G149" s="2" t="s">
         <v>2234</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -78240,7 +78237,7 @@
         <v>956</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>441</v>
@@ -78258,12 +78255,12 @@
         <v>438</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B2">
         <v>340</v>
@@ -78289,7 +78286,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B3">
         <v>339</v>
@@ -78315,7 +78312,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B4">
         <v>330</v>
@@ -78341,7 +78338,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B5">
         <v>322</v>
@@ -78367,7 +78364,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B6">
         <v>314</v>
@@ -78393,7 +78390,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B7">
         <v>295</v>
@@ -78419,7 +78416,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B8">
         <v>285</v>
@@ -78445,7 +78442,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B9">
         <v>263</v>
@@ -78471,7 +78468,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B10">
         <v>243</v>
@@ -78497,7 +78494,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="B11">
         <v>220</v>
@@ -78537,12 +78534,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -78553,18 +78550,18 @@
         <v>957</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>2250</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>2251</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>441</v>
@@ -78573,7 +78570,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="E5" s="23">
         <v>11</v>
@@ -78581,7 +78578,7 @@
     </row>
     <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>433</v>
@@ -78590,7 +78587,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="E6" s="23">
         <v>57</v>
@@ -78598,7 +78595,7 @@
     </row>
     <row r="8" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -78621,12 +78618,12 @@
         <v>438</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B10" s="3">
         <v>4</v>
@@ -78649,7 +78646,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B11" s="3">
         <v>15</v>
@@ -78672,7 +78669,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B12" s="3">
         <v>5</v>
@@ -78695,7 +78692,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -78718,7 +78715,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B14" s="3">
         <v>3</v>
@@ -78741,7 +78738,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -78764,7 +78761,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -78787,7 +78784,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B17" s="3">
         <v>8</v>
@@ -78810,7 +78807,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B18" s="31">
         <v>33</v>
@@ -78833,7 +78830,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="B19" s="3">
         <v>9</v>
@@ -78870,7 +78867,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -78880,62 +78877,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -78945,82 +78942,82 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -79030,22 +79027,22 @@
     </row>
     <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
@@ -79055,27 +79052,27 @@
     </row>
     <row r="38" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -79085,12 +79082,12 @@
     </row>
     <row r="44" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -6422,7 +6422,7 @@
     <t>2:5=300 5:2=175 负其他=95 平其他=275 胜其他=65</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-15T22:00:04+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-15T23:00:03+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -19527,8 +19527,8 @@
       <c r="F139" t="s">
         <v>883</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>70</v>
+      <c r="G139" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>21</v>
@@ -19809,8 +19809,8 @@
       <c r="F145" t="s">
         <v>903</v>
       </c>
-      <c r="G145" s="5" t="s">
-        <v>70</v>
+      <c r="G145" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>21</v>
@@ -20138,8 +20138,8 @@
       <c r="F152" t="s">
         <v>930</v>
       </c>
-      <c r="G152" s="5" t="s">
-        <v>70</v>
+      <c r="G152" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H152" s="3" t="s">
         <v>21</v>
@@ -20373,8 +20373,8 @@
       <c r="F157" t="s">
         <v>945</v>
       </c>
-      <c r="G157" s="5" t="s">
-        <v>70</v>
+      <c r="G157" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>21</v>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13212" uniqueCount="2291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13240" uniqueCount="2290">
   <si>
     <t>日期</t>
   </si>
@@ -2678,7 +2678,7 @@
     <t>10-15 22:00</t>
   </si>
   <si>
-    <t>10-16 09:00</t>
+    <t>10-16 10:00</t>
   </si>
   <si>
     <t>托林斯</t>
@@ -6227,16 +6227,16 @@
     <t>0:1=9 1:0=19</t>
   </si>
   <si>
-    <t>0:2=8 1:1=9.5 2:0=35</t>
-  </si>
-  <si>
-    <t>0:3=10.5 1:2=7 2:1=14 3:0=90</t>
-  </si>
-  <si>
-    <t>0:4=18 1:3=9.5 2:2=13 3:1=50 4:0=300</t>
-  </si>
-  <si>
-    <t>0:5=40 1:4=17 2:3=16 3:2=35 4:1=150 5:0=600</t>
+    <t>0:2=8 1:1=9.5 2:0=36</t>
+  </si>
+  <si>
+    <t>0:3=10.5 1:2=6.75 2:1=15.5 3:0=90</t>
+  </si>
+  <si>
+    <t>0:4=18 1:3=9.25 2:2=13 3:1=55 4:0=300</t>
+  </si>
+  <si>
+    <t>0:5=40 1:4=16 2:3=16 3:2=38 4:1=150 5:0=600</t>
   </si>
   <si>
     <t>1:5=35 2:4=30 3:3=50 4:2=150 5:1=400</t>
@@ -6404,7 +6404,7 @@
     <t>2:5=300 5:2=175 负其他=95 平其他=275 胜其他=65</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-16T09:00:03+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-16T10:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -6419,19 +6419,19 @@
     <t>基线A 命中率（差值最小项）</t>
   </si>
   <si>
-    <t>17/144 = 11.8%</t>
+    <t>17/148 = 11.5%</t>
   </si>
   <si>
     <t>模型A 命中率（数据核心·自修正）</t>
   </si>
   <si>
-    <t>25/144 = 17.4%</t>
+    <t>27/148 = 18.2%</t>
   </si>
   <si>
     <t>模型B 命中率（简单平均口径·对照）</t>
   </si>
   <si>
-    <t>32/144 = 22.2%</t>
+    <t>34/148 = 23.0%</t>
   </si>
   <si>
     <t>说明：口径B的平均赔率随比分个数放大，差值不可跨档比较，不产出基线预测（详见"说明"表）。</t>
@@ -6443,13 +6443,13 @@
     <t>当前因子权重（滚动自学习）</t>
   </si>
   <si>
-    <t>排名A 66% · 排名B 6% · 谷值 7% · 市场 15% · 趋势 6%</t>
+    <t>排名A 65% · 排名B 6% · 谷值 7% · 市场 16% · 趋势 6%</t>
   </si>
   <si>
     <t>权重评测样本</t>
   </si>
   <si>
-    <t>144 场（各自单独命中率：排名A 18% · 排名B 24% · 谷值 15% · 市场 18% · 趋势 6% · 基础 24%）</t>
+    <t>148 场（各自单独命中率：排名A 19% · 排名B 24% · 谷值 16% · 市场 18% · 趋势 7% · 基础 25%）</t>
   </si>
   <si>
     <t>说明：因子对真实结果的"信息量"（对数似然）需超过基础分布才获得权重（0.12 纳特封顶），达不到的自动休眠、权重≈0；全部因子只由赔率与赔率变化派生（v5 起联赛/球队等外部数据因子已下线）。</t>
@@ -6476,7 +6476,7 @@
     <t>学习样本</t>
   </si>
   <si>
-    <t>111 场（另剔除爆冷 33 场）</t>
+    <t>115 场（另剔除爆冷 33 场）</t>
   </si>
   <si>
     <t>进球数 ＼ 差值排名</t>
@@ -6512,7 +6512,7 @@
     <t>9% (1/11)</t>
   </si>
   <si>
-    <t>10% (3/30)</t>
+    <t>10% (3/31)</t>
   </si>
   <si>
     <t>0% (0/21)</t>
@@ -6521,7 +6521,7 @@
     <t>0% (0/23)</t>
   </si>
   <si>
-    <t>0% (0/24)</t>
+    <t>0% (0/27)</t>
   </si>
   <si>
     <t>25% (2/8)</t>
@@ -6530,22 +6530,25 @@
     <t>16% (3/19)</t>
   </si>
   <si>
+    <t>18% (5/28)</t>
+  </si>
+  <si>
+    <t>25% (6/24)</t>
+  </si>
+  <si>
+    <t>17% (1/6)</t>
+  </si>
+  <si>
+    <t>0% (0/18)</t>
+  </si>
+  <si>
+    <t>0% (0/12)</t>
+  </si>
+  <si>
     <t>19% (5/27)</t>
   </si>
   <si>
-    <t>22% (5/23)</t>
-  </si>
-  <si>
-    <t>17% (1/6)</t>
-  </si>
-  <si>
-    <t>0% (0/16)</t>
-  </si>
-  <si>
-    <t>0% (0/12)</t>
-  </si>
-  <si>
-    <t>19% (5/26)</t>
+    <t>15% (3/20)</t>
   </si>
   <si>
     <t>25% (8/32)</t>
@@ -6554,70 +6557,67 @@
     <t>25% (4/16)</t>
   </si>
   <si>
+    <t>17% (2/12)</t>
+  </si>
+  <si>
+    <t>0% (0/8)</t>
+  </si>
+  <si>
+    <t>24% (11/46)</t>
+  </si>
+  <si>
+    <t>50% (14/28)</t>
+  </si>
+  <si>
+    <t>38% (3/8)</t>
+  </si>
+  <si>
+    <t>60% (3/5)</t>
+  </si>
+  <si>
+    <t>0% (0/1)</t>
+  </si>
+  <si>
+    <t>22% (4/18)</t>
+  </si>
+  <si>
+    <t>20% (8/40)</t>
+  </si>
+  <si>
+    <t>19% (4/21)</t>
+  </si>
+  <si>
+    <t>0% (0/7)</t>
+  </si>
+  <si>
+    <t>0% (0/4)</t>
+  </si>
+  <si>
+    <t>33% (1/3)</t>
+  </si>
+  <si>
     <t>20% (2/10)</t>
   </si>
   <si>
-    <t>0% (0/8)</t>
-  </si>
-  <si>
-    <t>23% (10/44)</t>
-  </si>
-  <si>
-    <t>48% (13/27)</t>
-  </si>
-  <si>
-    <t>38% (3/8)</t>
-  </si>
-  <si>
-    <t>60% (3/5)</t>
-  </si>
-  <si>
-    <t>0% (0/1)</t>
-  </si>
-  <si>
-    <t>24% (4/17)</t>
-  </si>
-  <si>
-    <t>29% (4/14)</t>
-  </si>
-  <si>
-    <t>21% (8/39)</t>
-  </si>
-  <si>
-    <t>19% (4/21)</t>
-  </si>
-  <si>
-    <t>0% (0/7)</t>
-  </si>
-  <si>
-    <t>0% (0/4)</t>
-  </si>
-  <si>
-    <t>33% (1/3)</t>
-  </si>
-  <si>
-    <t>13% (1/8)</t>
-  </si>
-  <si>
     <t>21% (4/19)</t>
   </si>
   <si>
-    <t>0% (0/39)</t>
-  </si>
-  <si>
-    <t>0% (0/31)</t>
+    <t>0% (0/40)</t>
+  </si>
+  <si>
+    <t>0% (0/32)</t>
   </si>
   <si>
     <t>0% (0/10)</t>
   </si>
   <si>
-    <t>7% (2/28)</t>
+    <t>7% (2/30)</t>
   </si>
   <si>
     <t>29% (2/7)</t>
   </si>
   <si>
-    <t>8% (1/13)</t>
+    <t>7% (1/14)</t>
   </si>
   <si>
     <t>0% (0/13)</t>
@@ -6629,10 +6629,7 @@
     <t>0% (0/3)</t>
   </si>
   <si>
-    <t>0% (0/6)</t>
-  </si>
-  <si>
-    <t>0% (0/64)</t>
+    <t>0% (0/65)</t>
   </si>
   <si>
     <t>说明：模型的预测 = 取"该进球数在它当前差值排名下、历史上命中率最高"的进球数（平滑处理，样本&lt;3 的行仅供参考）。</t>
@@ -6953,7 +6950,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6970,11 +6967,6 @@
         <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -6988,7 +6980,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7029,9 +7021,6 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -19886,7 +19875,7 @@
         <v>55</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>21</v>
+        <v>433</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>440</v>
@@ -19897,17 +19886,17 @@
       <c r="K147" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="L147" t="s">
-        <v>21</v>
-      </c>
-      <c r="M147" t="s">
-        <v>21</v>
+      <c r="L147" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M147" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="N147" t="s">
         <v>893</v>
       </c>
       <c r="O147" t="s">
-        <v>21</v>
+        <v>886</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
@@ -19933,7 +19922,7 @@
         <v>21</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>904</v>
@@ -19944,17 +19933,17 @@
       <c r="K148" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="L148" t="s">
-        <v>21</v>
-      </c>
-      <c r="M148" t="s">
-        <v>21</v>
+      <c r="L148" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="M148" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="N148" t="s">
         <v>885</v>
       </c>
       <c r="O148" t="s">
-        <v>21</v>
+        <v>886</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
@@ -19980,7 +19969,7 @@
         <v>55</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>640</v>
@@ -19991,17 +19980,17 @@
       <c r="K149" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="L149" t="s">
-        <v>21</v>
-      </c>
-      <c r="M149" t="s">
-        <v>21</v>
+      <c r="L149" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M149" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="N149" t="s">
         <v>908</v>
       </c>
       <c r="O149" t="s">
-        <v>21</v>
+        <v>886</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
@@ -20027,7 +20016,7 @@
         <v>55</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>702</v>
@@ -20038,17 +20027,17 @@
       <c r="K150" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="L150" t="s">
-        <v>21</v>
-      </c>
-      <c r="M150" t="s">
-        <v>21</v>
+      <c r="L150" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="M150" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="N150" t="s">
         <v>908</v>
       </c>
       <c r="O150" t="s">
-        <v>21</v>
+        <v>886</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
@@ -20233,7 +20222,7 @@
         <v>21</v>
       </c>
       <c r="N154" t="s">
-        <v>914</v>
+        <v>886</v>
       </c>
       <c r="O154" t="s">
         <v>21</v>
@@ -69342,7 +69331,7 @@
       </c>
       <c r="G1218" s="9"/>
       <c r="H1218" s="10">
-        <v>1.526</v>
+        <v>1.555</v>
       </c>
       <c r="I1218" s="11"/>
       <c r="J1218" s="8"/>
@@ -69415,22 +69404,22 @@
         <v>4.2</v>
       </c>
       <c r="G1220" s="13">
-        <v>3.863</v>
+        <v>3.875</v>
       </c>
       <c r="H1220" s="14">
-        <v>0.337</v>
+        <v>0.325</v>
       </c>
       <c r="I1220" s="15">
-        <v>8.7</v>
+        <v>8.4</v>
       </c>
       <c r="J1220" s="12">
-        <v>17.5</v>
+        <v>17.833</v>
       </c>
       <c r="K1220" s="16">
-        <v>-13.3</v>
+        <v>-13.633</v>
       </c>
       <c r="L1220" s="15">
-        <v>-76</v>
+        <v>-76.4</v>
       </c>
       <c r="M1220" t="s">
         <v>2069</v>
@@ -69456,22 +69445,22 @@
         <v>3.5</v>
       </c>
       <c r="G1221" s="13">
-        <v>3.119</v>
+        <v>3.135</v>
       </c>
       <c r="H1221" s="14">
-        <v>0.381</v>
+        <v>0.365</v>
       </c>
       <c r="I1221" s="15">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="J1221" s="12">
-        <v>30.375</v>
+        <v>30.688</v>
       </c>
       <c r="K1221" s="16">
-        <v>-26.875</v>
+        <v>-27.188</v>
       </c>
       <c r="L1221" s="15">
-        <v>-88.5</v>
+        <v>-88.6</v>
       </c>
       <c r="M1221" t="s">
         <v>2070</v>
@@ -69497,19 +69486,19 @@
         <v>4.4</v>
       </c>
       <c r="G1222" s="13">
-        <v>3.83</v>
+        <v>3.815</v>
       </c>
       <c r="H1222" s="14">
-        <v>0.57</v>
+        <v>0.585</v>
       </c>
       <c r="I1222" s="15">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="J1222" s="12">
-        <v>78.1</v>
+        <v>79.05</v>
       </c>
       <c r="K1222" s="16">
-        <v>-73.7</v>
+        <v>-74.65</v>
       </c>
       <c r="L1222" s="15">
         <v>-94.4</v>
@@ -69538,19 +69527,19 @@
         <v>7</v>
       </c>
       <c r="G1223" s="13">
-        <v>5.458</v>
+        <v>5.416</v>
       </c>
       <c r="H1223" s="14">
-        <v>1.542</v>
+        <v>1.584</v>
       </c>
       <c r="I1223" s="15">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="J1223" s="12">
-        <v>143</v>
+        <v>143.333</v>
       </c>
       <c r="K1223" s="16">
-        <v>-136</v>
+        <v>-136.333</v>
       </c>
       <c r="L1223" s="15">
         <v>-95.1</v>
@@ -72232,7 +72221,7 @@
         <v>2130</v>
       </c>
       <c r="B4">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -72240,7 +72229,7 @@
         <v>2131</v>
       </c>
       <c r="B5">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -72308,7 +72297,7 @@
         <v>2146</v>
       </c>
       <c r="B17">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -72443,19 +72432,19 @@
         <v>2175</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>2169</v>
+        <v>2176</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -72472,19 +72461,19 @@
         <v>2175</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>2180</v>
-      </c>
-      <c r="D28" s="21" t="s">
         <v>2181</v>
       </c>
+      <c r="D28" s="22" t="s">
+        <v>2182</v>
+      </c>
       <c r="E28" s="21" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -72501,10 +72490,10 @@
         <v>2168</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>2186</v>
+        <v>2178</v>
       </c>
       <c r="E29" s="21" t="s">
         <v>2187</v>
@@ -72519,7 +72508,7 @@
         <v>2190</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -72530,7 +72519,7 @@
         <v>21</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>2191</v>
@@ -72600,18 +72589,18 @@
         <v>2189</v>
       </c>
       <c r="G32" s="21" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I32" s="21" t="s">
         <v>2203</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>2196</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
   </sheetData>
@@ -72622,7 +72611,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:L172"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -72636,109 +72625,109 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2208</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>2209</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>2210</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>2211</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>2212</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>2213</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>2214</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B5">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>14400</v>
+        <v>14800</v>
       </c>
       <c r="E5">
-        <v>10230</v>
+        <v>10965</v>
       </c>
       <c r="F5" s="23">
-        <v>-4170</v>
+        <v>-3835</v>
       </c>
       <c r="G5" s="24">
-        <v>-0.28958333333333336</v>
+        <v>-0.2591216216216216</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B6">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>14400</v>
+        <v>14800</v>
       </c>
       <c r="E6">
         <v>7900</v>
       </c>
       <c r="F6" s="23">
-        <v>-6500</v>
+        <v>-6900</v>
       </c>
       <c r="G6" s="24">
-        <v>-0.4513888888888889</v>
+        <v>-0.46621621621621623</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>14400</v>
+        <v>14800</v>
       </c>
       <c r="E7">
-        <v>13390</v>
+        <v>14125</v>
       </c>
       <c r="F7" s="23">
-        <v>-1010</v>
+        <v>-675</v>
       </c>
       <c r="G7" s="24">
-        <v>-0.07013888888888889</v>
+        <v>-0.04560810810810811</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -72758,25 +72747,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>2219</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>2220</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>2221</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>2223</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>2224</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -78251,285 +78240,437 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="156" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="19" t="s">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>881</v>
+      </c>
+      <c r="B155" t="s">
+        <v>900</v>
+      </c>
+      <c r="C155" t="s">
+        <v>882</v>
+      </c>
+      <c r="D155" t="s">
+        <v>132</v>
+      </c>
+      <c r="E155" t="s">
+        <v>901</v>
+      </c>
+      <c r="F155" t="s">
+        <v>423</v>
+      </c>
+      <c r="G155" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="H155" t="s">
+        <v>433</v>
+      </c>
+      <c r="I155" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J155" s="26">
+        <v>-4270</v>
+      </c>
+      <c r="K155" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L155" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>881</v>
+      </c>
+      <c r="B156" t="s">
+        <v>902</v>
+      </c>
+      <c r="C156" t="s">
+        <v>882</v>
+      </c>
+      <c r="D156" t="s">
+        <v>68</v>
+      </c>
+      <c r="E156" t="s">
+        <v>903</v>
+      </c>
+      <c r="F156" t="s">
+        <v>423</v>
+      </c>
+      <c r="G156" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H156" t="s">
+        <v>423</v>
+      </c>
+      <c r="I156" s="28">
+        <v>285</v>
+      </c>
+      <c r="J156" s="26">
+        <v>-3985</v>
+      </c>
+      <c r="K156" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L156" s="27">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>881</v>
+      </c>
+      <c r="B157" t="s">
+        <v>905</v>
+      </c>
+      <c r="C157" t="s">
+        <v>882</v>
+      </c>
+      <c r="D157" t="s">
+        <v>141</v>
+      </c>
+      <c r="E157" t="s">
+        <v>906</v>
+      </c>
+      <c r="F157" t="s">
+        <v>438</v>
+      </c>
+      <c r="G157" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H157" t="s">
+        <v>430</v>
+      </c>
+      <c r="I157" s="25">
+        <v>-100</v>
+      </c>
+      <c r="J157" s="26">
+        <v>-4085</v>
+      </c>
+      <c r="K157" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L157" s="27">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>881</v>
+      </c>
+      <c r="B158" t="s">
+        <v>909</v>
+      </c>
+      <c r="C158" t="s">
+        <v>894</v>
+      </c>
+      <c r="D158" t="s">
+        <v>910</v>
+      </c>
+      <c r="E158" t="s">
+        <v>590</v>
+      </c>
+      <c r="F158" t="s">
+        <v>423</v>
+      </c>
+      <c r="G158" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H158" t="s">
+        <v>423</v>
+      </c>
+      <c r="I158" s="28">
+        <v>250</v>
+      </c>
+      <c r="J158" s="26">
+        <v>-3835</v>
+      </c>
+      <c r="K158" s="27">
+        <v>-100</v>
+      </c>
+      <c r="L158" s="27">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="19" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>2225</v>
       </c>
-    </row>
-    <row r="157" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B157" s="2" t="s">
+      <c r="C161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="2" t="s">
         <v>2226</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D157" s="2" t="s">
+      <c r="E161" s="2" t="s">
         <v>2227</v>
       </c>
-      <c r="E157" s="2" t="s">
+      <c r="F161" s="2" t="s">
         <v>2228</v>
       </c>
-      <c r="F157" s="2" t="s">
+      <c r="G161" s="2" t="s">
         <v>2229</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>421</v>
-      </c>
-      <c r="B158">
-        <v>7</v>
-      </c>
-      <c r="C158">
-        <v>1</v>
-      </c>
-      <c r="D158" s="27">
-        <v>50</v>
-      </c>
-      <c r="E158" s="27">
-        <v>50</v>
-      </c>
-      <c r="F158" s="27">
-        <v>-280</v>
-      </c>
-      <c r="G158" s="27">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>449</v>
-      </c>
-      <c r="B159">
-        <v>12</v>
-      </c>
-      <c r="C159">
-        <v>3</v>
-      </c>
-      <c r="D159" s="27">
-        <v>225</v>
-      </c>
-      <c r="E159" s="27">
-        <v>275</v>
-      </c>
-      <c r="F159" s="27">
-        <v>-1085</v>
-      </c>
-      <c r="G159" s="27">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>487</v>
-      </c>
-      <c r="B160">
-        <v>6</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-      <c r="D160" s="27">
-        <v>-600</v>
-      </c>
-      <c r="E160" s="27">
-        <v>-325</v>
-      </c>
-      <c r="F160" s="27">
-        <v>-655</v>
-      </c>
-      <c r="G160" s="27">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>518</v>
-      </c>
-      <c r="B161">
-        <v>6</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161" s="27">
-        <v>-600</v>
-      </c>
-      <c r="E161" s="27">
-        <v>-925</v>
-      </c>
-      <c r="F161" s="27">
-        <v>-1255</v>
-      </c>
-      <c r="G161" s="27">
-        <v>1395</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>545</v>
+        <v>421</v>
       </c>
       <c r="B162">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" s="27">
-        <v>-15</v>
+        <v>50</v>
       </c>
       <c r="E162" s="27">
-        <v>-940</v>
+        <v>50</v>
       </c>
       <c r="F162" s="27">
-        <v>-1820</v>
+        <v>-280</v>
       </c>
       <c r="G162" s="27">
-        <v>1660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>595</v>
+        <v>449</v>
       </c>
       <c r="B163">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C163">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D163" s="27">
-        <v>-795</v>
+        <v>225</v>
       </c>
       <c r="E163" s="27">
-        <v>-1735</v>
+        <v>275</v>
       </c>
       <c r="F163" s="27">
-        <v>-2585</v>
+        <v>-1085</v>
       </c>
       <c r="G163" s="27">
-        <v>1155</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>705</v>
+        <v>487</v>
       </c>
       <c r="B164">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C164">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D164" s="27">
-        <v>-595</v>
+        <v>-600</v>
       </c>
       <c r="E164" s="27">
-        <v>-2330</v>
+        <v>-325</v>
       </c>
       <c r="F164" s="27">
-        <v>-5065</v>
+        <v>-655</v>
       </c>
       <c r="G164" s="27">
-        <v>940</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>775</v>
+        <v>518</v>
       </c>
       <c r="B165">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D165" s="27">
-        <v>-295</v>
+        <v>-600</v>
       </c>
       <c r="E165" s="27">
-        <v>-2625</v>
+        <v>-925</v>
       </c>
       <c r="F165" s="27">
-        <v>-4735</v>
+        <v>-1255</v>
       </c>
       <c r="G165" s="27">
-        <v>645</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>811</v>
+        <v>545</v>
       </c>
       <c r="B166">
         <v>12</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" s="27">
-        <v>-860</v>
+        <v>-15</v>
       </c>
       <c r="E166" s="27">
-        <v>-3485</v>
+        <v>-940</v>
       </c>
       <c r="F166" s="27">
-        <v>-5325</v>
+        <v>-1820</v>
       </c>
       <c r="G166" s="27">
-        <v>-215</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>841</v>
+        <v>595</v>
       </c>
       <c r="B167">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D167" s="27">
-        <v>-635</v>
+        <v>-795</v>
       </c>
       <c r="E167" s="27">
-        <v>-4120</v>
+        <v>-1735</v>
       </c>
       <c r="F167" s="27">
-        <v>-5985</v>
+        <v>-2585</v>
       </c>
       <c r="G167" s="27">
-        <v>-900</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>705</v>
+      </c>
+      <c r="B168">
+        <v>28</v>
+      </c>
+      <c r="C168">
+        <v>6</v>
+      </c>
+      <c r="D168" s="27">
+        <v>-595</v>
+      </c>
+      <c r="E168" s="27">
+        <v>-2330</v>
+      </c>
+      <c r="F168" s="27">
+        <v>-5065</v>
+      </c>
+      <c r="G168" s="27">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>775</v>
+      </c>
+      <c r="B169">
+        <v>10</v>
+      </c>
+      <c r="C169">
+        <v>2</v>
+      </c>
+      <c r="D169" s="27">
+        <v>-295</v>
+      </c>
+      <c r="E169" s="27">
+        <v>-2625</v>
+      </c>
+      <c r="F169" s="27">
+        <v>-4735</v>
+      </c>
+      <c r="G169" s="27">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>811</v>
+      </c>
+      <c r="B170">
+        <v>12</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" s="27">
+        <v>-860</v>
+      </c>
+      <c r="E170" s="27">
+        <v>-3485</v>
+      </c>
+      <c r="F170" s="27">
+        <v>-5325</v>
+      </c>
+      <c r="G170" s="27">
+        <v>-215</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>841</v>
+      </c>
+      <c r="B171">
+        <v>14</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+      <c r="D171" s="27">
+        <v>-635</v>
+      </c>
+      <c r="E171" s="27">
+        <v>-4120</v>
+      </c>
+      <c r="F171" s="27">
+        <v>-5985</v>
+      </c>
+      <c r="G171" s="27">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>881</v>
       </c>
-      <c r="B168">
-        <v>8</v>
-      </c>
-      <c r="C168">
-        <v>2</v>
-      </c>
-      <c r="D168" s="27">
-        <v>-50</v>
-      </c>
-      <c r="E168" s="27">
-        <v>-4170</v>
-      </c>
-      <c r="F168" s="27">
-        <v>-6500</v>
-      </c>
-      <c r="G168" s="27">
-        <v>-1010</v>
+      <c r="B172">
+        <v>12</v>
+      </c>
+      <c r="C172">
+        <v>4</v>
+      </c>
+      <c r="D172" s="27">
+        <v>285</v>
+      </c>
+      <c r="E172" s="27">
+        <v>-3835</v>
+      </c>
+      <c r="F172" s="27">
+        <v>-6900</v>
+      </c>
+      <c r="G172" s="27">
+        <v>-675</v>
       </c>
     </row>
   </sheetData>
@@ -78552,7 +78693,7 @@
         <v>952</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>441</v>
@@ -78570,12 +78711,12 @@
         <v>438</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B2">
         <v>341</v>
@@ -78601,7 +78742,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B3">
         <v>340</v>
@@ -78627,7 +78768,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B4">
         <v>331</v>
@@ -78653,7 +78794,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B5">
         <v>323</v>
@@ -78679,7 +78820,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B6">
         <v>315</v>
@@ -78705,7 +78846,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B7">
         <v>296</v>
@@ -78731,7 +78872,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B8">
         <v>285</v>
@@ -78757,7 +78898,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B9">
         <v>264</v>
@@ -78783,7 +78924,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B10">
         <v>244</v>
@@ -78809,16 +78950,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B11">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C11">
         <v>18</v>
       </c>
       <c r="D11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11">
         <v>51</v>
@@ -78849,12 +78990,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -78865,18 +79006,18 @@
         <v>953</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>2245</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>2246</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>441</v>
@@ -78885,7 +79026,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="E5" s="23">
         <v>11</v>
@@ -78893,7 +79034,7 @@
     </row>
     <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>433</v>
@@ -78902,7 +79043,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="E6" s="23">
         <v>57</v>
@@ -78910,7 +79051,7 @@
     </row>
     <row r="8" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -78933,12 +79074,12 @@
         <v>438</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
@@ -78961,7 +79102,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -78984,7 +79125,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B12" s="3">
         <v>6</v>
@@ -79007,7 +79148,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -79030,7 +79171,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B14" s="3">
         <v>4</v>
@@ -79053,7 +79194,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -79076,7 +79217,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -79099,7 +79240,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B17" s="3">
         <v>9</v>
@@ -79122,7 +79263,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B18" s="31">
         <v>34</v>
@@ -79145,25 +79286,25 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B19" s="3">
-        <v>9</v>
-      </c>
-      <c r="C19" s="32">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
       </c>
       <c r="D19" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -79182,7 +79323,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -79192,62 +79333,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -79257,82 +79398,82 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -79342,22 +79483,22 @@
     </row>
     <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
@@ -79367,27 +79508,27 @@
     </row>
     <row r="38" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -79397,12 +79538,12 @@
     </row>
     <row r="44" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15389" uniqueCount="2569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15389" uniqueCount="2570">
   <si>
     <t>日期</t>
   </si>
@@ -2780,48 +2780,54 @@
     <t>10-16 17:00</t>
   </si>
   <si>
+    <t>3球 @3.8 ⚡</t>
+  </si>
+  <si>
+    <t>10-16 13:00</t>
+  </si>
+  <si>
+    <t>科特布斯</t>
+  </si>
+  <si>
+    <t>纽伦堡</t>
+  </si>
+  <si>
+    <t>10-17 00:30</t>
+  </si>
+  <si>
+    <t>5球 @5.1 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
+    <t>布鲁马波</t>
+  </si>
+  <si>
+    <t>佐加顿斯</t>
+  </si>
+  <si>
+    <t>10-17 01:00</t>
+  </si>
+  <si>
+    <t>3球 @3.5 ⚡</t>
+  </si>
+  <si>
+    <t>10-16 12:00</t>
+  </si>
+  <si>
+    <t>SBV精英</t>
+  </si>
+  <si>
+    <t>10-17 02:00</t>
+  </si>
+  <si>
+    <t>6球 @9.8</t>
+  </si>
+  <si>
     <t>3球 @3.7 ⚡</t>
   </si>
   <si>
-    <t>10-16 12:00</t>
-  </si>
-  <si>
-    <t>科特布斯</t>
-  </si>
-  <si>
-    <t>纽伦堡</t>
-  </si>
-  <si>
-    <t>10-17 00:30</t>
-  </si>
-  <si>
-    <t>3球 @3.85 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @4.2 ⚡</t>
-  </si>
-  <si>
-    <t>布鲁马波</t>
-  </si>
-  <si>
-    <t>佐加顿斯</t>
-  </si>
-  <si>
-    <t>10-17 01:00</t>
-  </si>
-  <si>
-    <t>3球 @3.5 ⚡</t>
-  </si>
-  <si>
-    <t>SBV精英</t>
-  </si>
-  <si>
-    <t>10-17 02:00</t>
-  </si>
-  <si>
-    <t>6球 @9.8</t>
-  </si>
-  <si>
     <t>奥斯</t>
   </si>
   <si>
@@ -2831,123 +2837,120 @@
     <t>10-17 02:30</t>
   </si>
   <si>
+    <t>10-17 02:45</t>
+  </si>
+  <si>
+    <t>6球 @10.5</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @4.5 ⚡</t>
+  </si>
+  <si>
+    <t>勒芒</t>
+  </si>
+  <si>
+    <t>伯恩利</t>
+  </si>
+  <si>
+    <t>10-17 03:00</t>
+  </si>
+  <si>
+    <t>3球 @3.45 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.65 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.8 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 07:00</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>麦克阿瑟</t>
+  </si>
+  <si>
+    <t>珀斯</t>
+  </si>
+  <si>
+    <t>10-17 14:00</t>
+  </si>
+  <si>
+    <t>鹿岛鹿角</t>
+  </si>
+  <si>
+    <t>长崎航海</t>
+  </si>
+  <si>
+    <t>6球 @15</t>
+  </si>
+  <si>
+    <t>3球 @3.4 ⚡</t>
+  </si>
+  <si>
+    <t>富川FC</t>
+  </si>
+  <si>
+    <t>10-17 15:30</t>
+  </si>
+  <si>
+    <t>中央海岸</t>
+  </si>
+  <si>
+    <t>10-17 16:40</t>
+  </si>
+  <si>
+    <t>10-17 18:00</t>
+  </si>
+  <si>
+    <t>宫崎牛鸟</t>
+  </si>
+  <si>
+    <t>磐田喜悦</t>
+  </si>
+  <si>
+    <t>10-17 19:30</t>
+  </si>
+  <si>
+    <t>4球 @4.7 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 20:00</t>
+  </si>
+  <si>
+    <t>10-17 21:00</t>
+  </si>
+  <si>
+    <t>10-17 21:30</t>
+  </si>
+  <si>
+    <t>7+球 @19</t>
+  </si>
+  <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @4.3 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 22:00</t>
+  </si>
+  <si>
+    <t>4球 @4.1 ⚡</t>
+  </si>
+  <si>
     <t>3球 @3.75 ⚡</t>
   </si>
   <si>
-    <t>10-17 02:45</t>
-  </si>
-  <si>
-    <t>6球 @10.5</t>
-  </si>
-  <si>
-    <t>3球 @3.55 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @4.5 ⚡</t>
-  </si>
-  <si>
-    <t>勒芒</t>
-  </si>
-  <si>
-    <t>3球 @3.6 ⚡</t>
-  </si>
-  <si>
-    <t>伯恩利</t>
-  </si>
-  <si>
-    <t>10-17 03:00</t>
-  </si>
-  <si>
-    <t>3球 @3.45 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.65 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5.8 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 07:00</t>
-  </si>
-  <si>
-    <t>2026-10-17</t>
-  </si>
-  <si>
-    <t>麦克阿瑟</t>
-  </si>
-  <si>
-    <t>珀斯</t>
-  </si>
-  <si>
-    <t>10-17 14:00</t>
-  </si>
-  <si>
-    <t>3球 @3.8 ⚡</t>
-  </si>
-  <si>
-    <t>鹿岛鹿角</t>
-  </si>
-  <si>
-    <t>长崎航海</t>
-  </si>
-  <si>
-    <t>6球 @15</t>
-  </si>
-  <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
-    <t>富川FC</t>
-  </si>
-  <si>
-    <t>10-17 15:30</t>
-  </si>
-  <si>
-    <t>中央海岸</t>
-  </si>
-  <si>
-    <t>10-17 16:40</t>
-  </si>
-  <si>
-    <t>10-17 18:00</t>
-  </si>
-  <si>
-    <t>宫崎牛鸟</t>
-  </si>
-  <si>
-    <t>磐田喜悦</t>
-  </si>
-  <si>
-    <t>10-17 19:30</t>
-  </si>
-  <si>
-    <t>4球 @4.7 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 20:00</t>
-  </si>
-  <si>
-    <t>10-17 21:00</t>
-  </si>
-  <si>
-    <t>10-17 21:30</t>
-  </si>
-  <si>
-    <t>7+球 @19</t>
-  </si>
-  <si>
-    <t>4球 @4.3 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 22:00</t>
-  </si>
-  <si>
-    <t>4球 @4.1 ⚡</t>
-  </si>
-  <si>
     <t>10-17 22:15</t>
   </si>
   <si>
@@ -2969,9 +2972,6 @@
     <t>3球 @4.9 ⚡</t>
   </si>
   <si>
-    <t>5球 @5.1 ⚡</t>
-  </si>
-  <si>
     <t>特尔斯达</t>
   </si>
   <si>
@@ -6332,40 +6332,40 @@
     <t>0:2=16 1:1=6.7 2:0=12.5</t>
   </si>
   <si>
-    <t>0:3=35 1:2=9.5 2:1=7.25 3:0=22</t>
-  </si>
-  <si>
-    <t>0:4=90 1:3=19 2:2=10 3:1=15 4:0=60</t>
-  </si>
-  <si>
-    <t>0:5=250 1:4=55 2:3=22 3:2=20 4:1=32 5:0=150</t>
-  </si>
-  <si>
-    <t>1:5=175 2:4=55 3:3=35 4:2=50 5:1=90</t>
-  </si>
-  <si>
-    <t>2:5=175 5:2=150 负其他=55 平其他=100 胜其他=45</t>
-  </si>
-  <si>
-    <t>0:1=16 1:0=20</t>
-  </si>
-  <si>
-    <t>0:2=15 1:1=9.5 2:0=22</t>
-  </si>
-  <si>
-    <t>0:3=21 1:2=8 2:1=10 3:0=35</t>
-  </si>
-  <si>
-    <t>0:4=35 1:3=12.5 2:2=10 3:1=19 4:0=90</t>
-  </si>
-  <si>
-    <t>0:5=100 1:4=24 2:3=13 3:2=16 4:1=55 5:0=250</t>
-  </si>
-  <si>
-    <t>1:5=55 2:4=27 3:3=23 4:2=45 5:1=120</t>
-  </si>
-  <si>
-    <t>2:5=65 5:2=120 负其他=16 平其他=90 胜其他=27</t>
+    <t>0:3=35 1:2=10 2:1=7.25 3:0=22</t>
+  </si>
+  <si>
+    <t>0:4=90 1:3=22 2:2=10 3:1=15 4:0=60</t>
+  </si>
+  <si>
+    <t>0:5=250 1:4=55 2:3=24 3:2=18 4:1=30 5:0=125</t>
+  </si>
+  <si>
+    <t>1:5=175 2:4=55 3:3=35 4:2=45 5:1=80</t>
+  </si>
+  <si>
+    <t>2:5=175 5:2=125 负其他=55 平其他=100 胜其他=40</t>
+  </si>
+  <si>
+    <t>0:1=16 1:0=22</t>
+  </si>
+  <si>
+    <t>0:2=15 1:1=10 2:0=24</t>
+  </si>
+  <si>
+    <t>0:3=21 1:2=7.7 2:1=11 3:0=38</t>
+  </si>
+  <si>
+    <t>0:4=32 1:3=11.5 2:2=10 3:1=20 4:0=90</t>
+  </si>
+  <si>
+    <t>0:5=90 1:4=22 2:3=12 3:2=18 4:1=55 5:0=250</t>
+  </si>
+  <si>
+    <t>1:5=50 2:4=25 3:3=23 4:2=48 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=55 5:2=120 负其他=15 平其他=90 胜其他=27</t>
   </si>
   <si>
     <t>0:1=9 1:0=19</t>
@@ -6428,19 +6428,22 @@
     <t>2:5=250 5:2=50 负其他=55 平其他=110 胜其他=19</t>
   </si>
   <si>
-    <t>0:2=23 1:1=8.25 2:0=12.5</t>
-  </si>
-  <si>
-    <t>0:3=50 1:2=10 2:1=7.5 3:0=18</t>
-  </si>
-  <si>
-    <t>0:4=100 1:3=22 2:2=10.5 3:1=12 4:0=30</t>
-  </si>
-  <si>
-    <t>0:5=350 1:4=60 2:3=19 3:2=14 4:1=22 5:0=80</t>
-  </si>
-  <si>
-    <t>1:5=175 2:4=60 3:3=27 4:2=30 5:1=50</t>
+    <t>0:1=20 1:0=13</t>
+  </si>
+  <si>
+    <t>0:2=25 1:1=8.25 2:0=12</t>
+  </si>
+  <si>
+    <t>0:3=50 1:2=11 2:1=7.5 3:0=18</t>
+  </si>
+  <si>
+    <t>0:4=100 1:3=22 2:2=10.5 3:1=11 4:0=30</t>
+  </si>
+  <si>
+    <t>0:5=350 1:4=60 2:3=19 3:2=13.5 4:1=21 5:0=75</t>
+  </si>
+  <si>
+    <t>1:5=175 2:4=60 3:3=27 4:2=29 5:1=45</t>
   </si>
   <si>
     <t>2:5=175 5:2=80 负其他=40 平其他=100 胜其他=19</t>
@@ -7238,7 +7241,7 @@
     <t>2:5=150 5:2=750 负其他=45 平其他=500 胜其他=250</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-16T12:00:07+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-16T13:00:03+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -20950,7 +20953,7 @@
         <v>21</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>715</v>
+        <v>475</v>
       </c>
       <c r="J152" s="3" t="s">
         <v>920</v>
@@ -20997,7 +21000,7 @@
         <v>21</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>697</v>
+        <v>636</v>
       </c>
       <c r="J153" s="3" t="s">
         <v>925</v>
@@ -21059,7 +21062,7 @@
         <v>21</v>
       </c>
       <c r="N154" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O154" t="s">
         <v>21</v>
@@ -21079,10 +21082,10 @@
         <v>568</v>
       </c>
       <c r="E155" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F155" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>55</v>
@@ -21091,13 +21094,13 @@
         <v>21</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="L155" t="s">
         <v>21</v>
@@ -21106,7 +21109,7 @@
         <v>21</v>
       </c>
       <c r="N155" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O155" t="s">
         <v>21</v>
@@ -21126,10 +21129,10 @@
         <v>363</v>
       </c>
       <c r="E156" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F156" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>55</v>
@@ -21141,10 +21144,10 @@
         <v>432</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="L156" t="s">
         <v>21</v>
@@ -21176,7 +21179,7 @@
         <v>747</v>
       </c>
       <c r="F157" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>70</v>
@@ -21185,10 +21188,10 @@
         <v>21</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>829</v>
+        <v>904</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="K157" s="3" t="s">
         <v>937</v>
@@ -21223,7 +21226,7 @@
         <v>758</v>
       </c>
       <c r="F158" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>55</v>
@@ -21232,13 +21235,13 @@
         <v>21</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K158" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="L158" t="s">
         <v>21</v>
@@ -21264,13 +21267,13 @@
         <v>101</v>
       </c>
       <c r="D159" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E159" t="s">
         <v>693</v>
       </c>
       <c r="F159" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>55</v>
@@ -21279,13 +21282,13 @@
         <v>21</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>564</v>
+        <v>727</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="L159" t="s">
         <v>21</v>
@@ -21294,7 +21297,7 @@
         <v>21</v>
       </c>
       <c r="N159" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="O159" t="s">
         <v>21</v>
@@ -21435,7 +21438,7 @@
         <v>21</v>
       </c>
       <c r="N162" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O162" t="s">
         <v>21</v>
@@ -21470,10 +21473,10 @@
         <v>727</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="L163" t="s">
         <v>21</v>
@@ -21482,7 +21485,7 @@
         <v>21</v>
       </c>
       <c r="N163" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O163" t="s">
         <v>21</v>
@@ -21499,10 +21502,10 @@
         <v>24</v>
       </c>
       <c r="D164" t="s">
+        <v>955</v>
+      </c>
+      <c r="E164" t="s">
         <v>956</v>
-      </c>
-      <c r="E164" t="s">
-        <v>957</v>
       </c>
       <c r="F164" t="s">
         <v>954</v>
@@ -21514,13 +21517,13 @@
         <v>21</v>
       </c>
       <c r="I164" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="J164" s="3" t="s">
         <v>958</v>
       </c>
-      <c r="J164" s="3" t="s">
-        <v>959</v>
-      </c>
       <c r="K164" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L164" t="s">
         <v>21</v>
@@ -21529,7 +21532,7 @@
         <v>21</v>
       </c>
       <c r="N164" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O164" t="s">
         <v>21</v>
@@ -21549,10 +21552,10 @@
         <v>707</v>
       </c>
       <c r="E165" t="s">
+        <v>959</v>
+      </c>
+      <c r="F165" t="s">
         <v>960</v>
-      </c>
-      <c r="F165" t="s">
-        <v>961</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>70</v>
@@ -21561,7 +21564,7 @@
         <v>21</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="J165" s="3" t="s">
         <v>946</v>
@@ -21576,7 +21579,7 @@
         <v>21</v>
       </c>
       <c r="N165" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O165" t="s">
         <v>21</v>
@@ -21593,13 +21596,13 @@
         <v>916</v>
       </c>
       <c r="D166" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E166" t="s">
         <v>812</v>
       </c>
       <c r="F166" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>55</v>
@@ -21611,10 +21614,10 @@
         <v>685</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="L166" t="s">
         <v>21</v>
@@ -21623,7 +21626,7 @@
         <v>21</v>
       </c>
       <c r="N166" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O166" t="s">
         <v>21</v>
@@ -21646,7 +21649,7 @@
         <v>713</v>
       </c>
       <c r="F167" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>55</v>
@@ -21658,10 +21661,10 @@
         <v>564</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L167" t="s">
         <v>21</v>
@@ -21670,7 +21673,7 @@
         <v>21</v>
       </c>
       <c r="N167" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O167" t="s">
         <v>21</v>
@@ -21687,13 +21690,13 @@
         <v>272</v>
       </c>
       <c r="D168" t="s">
+        <v>964</v>
+      </c>
+      <c r="E168" t="s">
         <v>965</v>
       </c>
-      <c r="E168" t="s">
-        <v>966</v>
-      </c>
       <c r="F168" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>55</v>
@@ -21717,7 +21720,7 @@
         <v>21</v>
       </c>
       <c r="N168" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O168" t="s">
         <v>21</v>
@@ -21740,7 +21743,7 @@
         <v>646</v>
       </c>
       <c r="F169" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>70</v>
@@ -21752,7 +21755,7 @@
         <v>531</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="K169" s="3" t="s">
         <v>930</v>
@@ -21764,7 +21767,7 @@
         <v>21</v>
       </c>
       <c r="N169" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O169" t="s">
         <v>21</v>
@@ -21787,7 +21790,7 @@
         <v>86</v>
       </c>
       <c r="F170" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>55</v>
@@ -21799,10 +21802,10 @@
         <v>601</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L170" t="s">
         <v>21</v>
@@ -21811,7 +21814,7 @@
         <v>21</v>
       </c>
       <c r="N170" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O170" t="s">
         <v>21</v>
@@ -21834,7 +21837,7 @@
         <v>44</v>
       </c>
       <c r="F171" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>55</v>
@@ -21843,7 +21846,7 @@
         <v>21</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="J171" s="3" t="s">
         <v>930</v>
@@ -21858,7 +21861,7 @@
         <v>21</v>
       </c>
       <c r="N171" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O171" t="s">
         <v>21</v>
@@ -21881,7 +21884,7 @@
         <v>628</v>
       </c>
       <c r="F172" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>55</v>
@@ -21905,7 +21908,7 @@
         <v>21</v>
       </c>
       <c r="N172" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O172" t="s">
         <v>21</v>
@@ -21928,7 +21931,7 @@
         <v>124</v>
       </c>
       <c r="F173" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>55</v>
@@ -21952,7 +21955,7 @@
         <v>21</v>
       </c>
       <c r="N173" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O173" t="s">
         <v>21</v>
@@ -21975,7 +21978,7 @@
         <v>633</v>
       </c>
       <c r="F174" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>55</v>
@@ -21984,13 +21987,13 @@
         <v>21</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="J174" s="3" t="s">
         <v>946</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L174" t="s">
         <v>21</v>
@@ -21999,7 +22002,7 @@
         <v>21</v>
       </c>
       <c r="N174" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O174" t="s">
         <v>21</v>
@@ -22022,7 +22025,7 @@
         <v>638</v>
       </c>
       <c r="F175" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>55</v>
@@ -22034,10 +22037,10 @@
         <v>577</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="L175" t="s">
         <v>21</v>
@@ -22046,7 +22049,7 @@
         <v>21</v>
       </c>
       <c r="N175" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O175" t="s">
         <v>21</v>
@@ -22069,7 +22072,7 @@
         <v>574</v>
       </c>
       <c r="F176" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>70</v>
@@ -22084,7 +22087,7 @@
         <v>973</v>
       </c>
       <c r="K176" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L176" t="s">
         <v>21</v>
@@ -22093,7 +22096,7 @@
         <v>21</v>
       </c>
       <c r="N176" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O176" t="s">
         <v>21</v>
@@ -22140,7 +22143,7 @@
         <v>21</v>
       </c>
       <c r="N177" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O177" t="s">
         <v>21</v>
@@ -22178,7 +22181,7 @@
         <v>975</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>937</v>
+        <v>976</v>
       </c>
       <c r="L178" t="s">
         <v>21</v>
@@ -22187,7 +22190,7 @@
         <v>21</v>
       </c>
       <c r="N178" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O178" t="s">
         <v>21</v>
@@ -22234,7 +22237,7 @@
         <v>21</v>
       </c>
       <c r="N179" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O179" t="s">
         <v>21</v>
@@ -22257,7 +22260,7 @@
         <v>728</v>
       </c>
       <c r="F180" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>55</v>
@@ -22281,7 +22284,7 @@
         <v>21</v>
       </c>
       <c r="N180" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O180" t="s">
         <v>21</v>
@@ -22304,7 +22307,7 @@
         <v>133</v>
       </c>
       <c r="F181" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>55</v>
@@ -22316,10 +22319,10 @@
         <v>697</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="K181" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="L181" t="s">
         <v>21</v>
@@ -22328,7 +22331,7 @@
         <v>21</v>
       </c>
       <c r="N181" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O181" t="s">
         <v>21</v>
@@ -22351,7 +22354,7 @@
         <v>661</v>
       </c>
       <c r="F182" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>55</v>
@@ -22360,13 +22363,13 @@
         <v>21</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="L182" t="s">
         <v>21</v>
@@ -22375,7 +22378,7 @@
         <v>21</v>
       </c>
       <c r="N182" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O182" t="s">
         <v>21</v>
@@ -22398,7 +22401,7 @@
         <v>647</v>
       </c>
       <c r="F183" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>70</v>
@@ -22422,7 +22425,7 @@
         <v>21</v>
       </c>
       <c r="N183" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O183" t="s">
         <v>21</v>
@@ -22445,7 +22448,7 @@
         <v>83</v>
       </c>
       <c r="F184" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G184" t="s">
         <v>21</v>
@@ -22454,10 +22457,10 @@
         <v>21</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="J184" s="3" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="K184" s="3" t="s">
         <v>973</v>
@@ -22469,7 +22472,7 @@
         <v>21</v>
       </c>
       <c r="N184" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O184" t="s">
         <v>21</v>
@@ -22492,7 +22495,7 @@
         <v>670</v>
       </c>
       <c r="F185" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>55</v>
@@ -22504,10 +22507,10 @@
         <v>636</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="L185" t="s">
         <v>21</v>
@@ -22516,7 +22519,7 @@
         <v>21</v>
       </c>
       <c r="N185" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O185" t="s">
         <v>21</v>
@@ -22551,10 +22554,10 @@
         <v>685</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="L186" t="s">
         <v>21</v>
@@ -22563,7 +22566,7 @@
         <v>21</v>
       </c>
       <c r="N186" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O186" t="s">
         <v>21</v>
@@ -22595,7 +22598,7 @@
         <v>21</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="J187" s="3" t="s">
         <v>930</v>
@@ -22610,7 +22613,7 @@
         <v>21</v>
       </c>
       <c r="N187" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O187" t="s">
         <v>21</v>
@@ -22645,10 +22648,10 @@
         <v>711</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="K188" s="3" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="L188" t="s">
         <v>21</v>
@@ -22657,7 +22660,7 @@
         <v>21</v>
       </c>
       <c r="N188" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O188" t="s">
         <v>21</v>
@@ -22692,10 +22695,10 @@
         <v>751</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="K189" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L189" t="s">
         <v>21</v>
@@ -22704,7 +22707,7 @@
         <v>21</v>
       </c>
       <c r="N189" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O189" t="s">
         <v>21</v>
@@ -22739,10 +22742,10 @@
         <v>694</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="L190" t="s">
         <v>21</v>
@@ -22751,7 +22754,7 @@
         <v>21</v>
       </c>
       <c r="N190" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O190" t="s">
         <v>21</v>
@@ -22786,10 +22789,10 @@
         <v>623</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="L191" t="s">
         <v>21</v>
@@ -22798,7 +22801,7 @@
         <v>21</v>
       </c>
       <c r="N191" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O191" t="s">
         <v>21</v>
@@ -22830,13 +22833,13 @@
         <v>21</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L192" t="s">
         <v>21</v>
@@ -22845,7 +22848,7 @@
         <v>21</v>
       </c>
       <c r="N192" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O192" t="s">
         <v>21</v>
@@ -22877,7 +22880,7 @@
         <v>21</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="J193" s="3" t="s">
         <v>946</v>
@@ -22892,7 +22895,7 @@
         <v>21</v>
       </c>
       <c r="N193" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O193" t="s">
         <v>21</v>
@@ -22939,7 +22942,7 @@
         <v>21</v>
       </c>
       <c r="N194" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O194" t="s">
         <v>21</v>
@@ -22974,10 +22977,10 @@
         <v>998</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="K195" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="L195" t="s">
         <v>21</v>
@@ -22986,7 +22989,7 @@
         <v>21</v>
       </c>
       <c r="N195" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O195" t="s">
         <v>21</v>
@@ -23033,7 +23036,7 @@
         <v>21</v>
       </c>
       <c r="N196" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="O196" t="s">
         <v>21</v>
@@ -71126,7 +71129,7 @@
       </c>
       <c r="G1202" s="9"/>
       <c r="H1202" s="10">
-        <v>0.504</v>
+        <v>0.575</v>
       </c>
       <c r="I1202" s="11"/>
       <c r="J1202" s="8"/>
@@ -71155,25 +71158,25 @@
         <v>433</v>
       </c>
       <c r="F1203" s="12">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="G1203" s="13">
         <v>5.349</v>
       </c>
       <c r="H1203" s="14">
-        <v>0.601</v>
+        <v>0.651</v>
       </c>
       <c r="I1203" s="15">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="J1203" s="12">
         <v>10.75</v>
       </c>
       <c r="K1203" s="16">
-        <v>-4.8</v>
+        <v>-4.75</v>
       </c>
       <c r="L1203" s="15">
-        <v>-44.6</v>
+        <v>-44.2</v>
       </c>
       <c r="M1203" t="s">
         <v>1336</v>
@@ -71196,25 +71199,25 @@
         <v>452</v>
       </c>
       <c r="F1204" s="12">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="G1204" s="13">
         <v>3.428</v>
       </c>
       <c r="H1204" s="14">
-        <v>0.522</v>
+        <v>0.622</v>
       </c>
       <c r="I1204" s="15">
-        <v>15.2</v>
+        <v>18.1</v>
       </c>
       <c r="J1204" s="12">
         <v>11.733</v>
       </c>
       <c r="K1204" s="16">
-        <v>-7.783</v>
+        <v>-7.683</v>
       </c>
       <c r="L1204" s="15">
-        <v>-66.3</v>
+        <v>-65.5</v>
       </c>
       <c r="M1204" t="s">
         <v>2103</v>
@@ -71237,25 +71240,25 @@
         <v>423</v>
       </c>
       <c r="F1205" s="12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G1205" s="13">
-        <v>3.152</v>
+        <v>3.206</v>
       </c>
       <c r="H1205" s="14">
-        <v>0.548</v>
+        <v>0.594</v>
       </c>
       <c r="I1205" s="15">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="J1205" s="12">
-        <v>18.438</v>
+        <v>18.563</v>
       </c>
       <c r="K1205" s="16">
-        <v>-14.738</v>
+        <v>-14.763</v>
       </c>
       <c r="L1205" s="15">
-        <v>-79.9</v>
+        <v>-79.5</v>
       </c>
       <c r="M1205" t="s">
         <v>2104</v>
@@ -71281,22 +71284,22 @@
         <v>4.85</v>
       </c>
       <c r="G1206" s="13">
-        <v>4.047</v>
+        <v>4.168</v>
       </c>
       <c r="H1206" s="14">
-        <v>0.803</v>
+        <v>0.682</v>
       </c>
       <c r="I1206" s="15">
-        <v>19.8</v>
+        <v>16.4</v>
       </c>
       <c r="J1206" s="12">
-        <v>38.8</v>
+        <v>39.4</v>
       </c>
       <c r="K1206" s="16">
-        <v>-33.95</v>
+        <v>-34.55</v>
       </c>
       <c r="L1206" s="15">
-        <v>-87.5</v>
+        <v>-87.7</v>
       </c>
       <c r="M1206" t="s">
         <v>2105</v>
@@ -71319,25 +71322,25 @@
         <v>430</v>
       </c>
       <c r="F1207" s="12">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="G1207" s="13">
-        <v>6.429</v>
+        <v>6.221</v>
       </c>
       <c r="H1207" s="14">
-        <v>0.571</v>
+        <v>0.479</v>
       </c>
       <c r="I1207" s="15">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J1207" s="12">
-        <v>88.167</v>
+        <v>83.667</v>
       </c>
       <c r="K1207" s="16">
-        <v>-81.167</v>
+        <v>-76.967</v>
       </c>
       <c r="L1207" s="15">
-        <v>-92.1</v>
+        <v>-92</v>
       </c>
       <c r="M1207" t="s">
         <v>2106</v>
@@ -71360,25 +71363,25 @@
         <v>522</v>
       </c>
       <c r="F1208" s="12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G1208" s="13">
-        <v>11.965</v>
+        <v>11.469</v>
       </c>
       <c r="H1208" s="17">
-        <v>-0.465</v>
+        <v>-0.469</v>
       </c>
       <c r="I1208" s="15">
-        <v>-3.9</v>
+        <v>-4.1</v>
       </c>
       <c r="J1208" s="12">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K1208" s="16">
-        <v>-69.5</v>
+        <v>-67</v>
       </c>
       <c r="L1208" s="15">
-        <v>-85.8</v>
+        <v>-85.9</v>
       </c>
       <c r="M1208" t="s">
         <v>2107</v>
@@ -71401,22 +71404,22 @@
         <v>634</v>
       </c>
       <c r="F1209" s="12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1209" s="13">
-        <v>15.927</v>
+        <v>14.949</v>
       </c>
       <c r="H1209" s="14">
-        <v>0.073</v>
+        <v>0.051</v>
       </c>
       <c r="I1209" s="15">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J1209" s="12">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K1209" s="16">
-        <v>-89</v>
+        <v>-84</v>
       </c>
       <c r="L1209" s="15">
         <v>-84.8</v>
@@ -71446,7 +71449,7 @@
       </c>
       <c r="G1210" s="9"/>
       <c r="H1210" s="10">
-        <v>1.506</v>
+        <v>0.892</v>
       </c>
       <c r="I1210" s="11"/>
       <c r="J1210" s="8"/>
@@ -71478,22 +71481,22 @@
         <v>10</v>
       </c>
       <c r="G1211" s="13">
-        <v>8.889</v>
+        <v>9.263</v>
       </c>
       <c r="H1211" s="14">
-        <v>1.111</v>
+        <v>0.737</v>
       </c>
       <c r="I1211" s="15">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="J1211" s="12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K1211" s="16">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="L1211" s="15">
-        <v>-44.4</v>
+        <v>-47.4</v>
       </c>
       <c r="M1211" t="s">
         <v>2109</v>
@@ -71519,22 +71522,22 @@
         <v>5.5</v>
       </c>
       <c r="G1212" s="13">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H1212" s="14">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I1212" s="15">
-        <v>19.6</v>
+        <v>14.6</v>
       </c>
       <c r="J1212" s="12">
-        <v>15.5</v>
+        <v>16.333</v>
       </c>
       <c r="K1212" s="16">
-        <v>-10</v>
+        <v>-10.833</v>
       </c>
       <c r="L1212" s="15">
-        <v>-64.5</v>
+        <v>-66.3</v>
       </c>
       <c r="M1212" t="s">
         <v>2110</v>
@@ -71560,22 +71563,22 @@
         <v>3.85</v>
       </c>
       <c r="G1213" s="13">
-        <v>3.32</v>
+        <v>3.393</v>
       </c>
       <c r="H1213" s="14">
-        <v>0.53</v>
+        <v>0.457</v>
       </c>
       <c r="I1213" s="15">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="J1213" s="12">
-        <v>18.5</v>
+        <v>19.425</v>
       </c>
       <c r="K1213" s="16">
-        <v>-14.65</v>
+        <v>-15.575</v>
       </c>
       <c r="L1213" s="15">
-        <v>-79.2</v>
+        <v>-80.2</v>
       </c>
       <c r="M1213" t="s">
         <v>2111</v>
@@ -71601,22 +71604,22 @@
         <v>4.2</v>
       </c>
       <c r="G1214" s="13">
-        <v>3.672</v>
+        <v>3.58</v>
       </c>
       <c r="H1214" s="14">
-        <v>0.528</v>
+        <v>0.62</v>
       </c>
       <c r="I1214" s="15">
-        <v>14.4</v>
+        <v>17.3</v>
       </c>
       <c r="J1214" s="12">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="K1214" s="16">
-        <v>-29.1</v>
+        <v>-28.5</v>
       </c>
       <c r="L1214" s="15">
-        <v>-87.4</v>
+        <v>-87.2</v>
       </c>
       <c r="M1214" t="s">
         <v>2112</v>
@@ -71642,22 +71645,22 @@
         <v>5.1</v>
       </c>
       <c r="G1215" s="13">
-        <v>4.689</v>
+        <v>4.595</v>
       </c>
       <c r="H1215" s="14">
-        <v>0.411</v>
+        <v>0.505</v>
       </c>
       <c r="I1215" s="15">
-        <v>8.8</v>
+        <v>11</v>
       </c>
       <c r="J1215" s="12">
-        <v>76.333</v>
+        <v>74.5</v>
       </c>
       <c r="K1215" s="16">
-        <v>-71.233</v>
+        <v>-69.4</v>
       </c>
       <c r="L1215" s="15">
-        <v>-93.3</v>
+        <v>-93.1</v>
       </c>
       <c r="M1215" t="s">
         <v>2113</v>
@@ -71683,22 +71686,22 @@
         <v>8</v>
       </c>
       <c r="G1216" s="13">
-        <v>7.737</v>
+        <v>7.539</v>
       </c>
       <c r="H1216" s="14">
-        <v>0.263</v>
+        <v>0.461</v>
       </c>
       <c r="I1216" s="15">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="J1216" s="12">
-        <v>54</v>
+        <v>53.2</v>
       </c>
       <c r="K1216" s="16">
-        <v>-46</v>
+        <v>-45.2</v>
       </c>
       <c r="L1216" s="15">
-        <v>-85.2</v>
+        <v>-85</v>
       </c>
       <c r="M1216" t="s">
         <v>2114</v>
@@ -71724,22 +71727,22 @@
         <v>8</v>
       </c>
       <c r="G1217" s="13">
-        <v>7.442</v>
+        <v>7.076</v>
       </c>
       <c r="H1217" s="14">
-        <v>0.558</v>
+        <v>0.924</v>
       </c>
       <c r="I1217" s="15">
-        <v>7.5</v>
+        <v>13.1</v>
       </c>
       <c r="J1217" s="12">
-        <v>63.6</v>
+        <v>61.4</v>
       </c>
       <c r="K1217" s="16">
-        <v>-55.6</v>
+        <v>-53.4</v>
       </c>
       <c r="L1217" s="15">
-        <v>-87.4</v>
+        <v>-87</v>
       </c>
       <c r="M1217" t="s">
         <v>2115</v>
@@ -72076,7 +72079,7 @@
         <v>568</v>
       </c>
       <c r="D1226" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1226" s="4" t="s">
         <v>441</v>
@@ -72109,7 +72112,7 @@
         <v>568</v>
       </c>
       <c r="D1227" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1227" t="s">
         <v>433</v>
@@ -72150,7 +72153,7 @@
         <v>568</v>
       </c>
       <c r="D1228" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1228" t="s">
         <v>452</v>
@@ -72191,7 +72194,7 @@
         <v>568</v>
       </c>
       <c r="D1229" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1229" t="s">
         <v>423</v>
@@ -72232,7 +72235,7 @@
         <v>568</v>
       </c>
       <c r="D1230" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1230" t="s">
         <v>438</v>
@@ -72273,7 +72276,7 @@
         <v>568</v>
       </c>
       <c r="D1231" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1231" t="s">
         <v>430</v>
@@ -72314,7 +72317,7 @@
         <v>568</v>
       </c>
       <c r="D1232" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1232" t="s">
         <v>522</v>
@@ -72355,7 +72358,7 @@
         <v>568</v>
       </c>
       <c r="D1233" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E1233" t="s">
         <v>634</v>
@@ -72396,7 +72399,7 @@
         <v>363</v>
       </c>
       <c r="D1234" s="4" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1234" s="4" t="s">
         <v>441</v>
@@ -72429,7 +72432,7 @@
         <v>363</v>
       </c>
       <c r="D1235" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1235" t="s">
         <v>433</v>
@@ -72470,7 +72473,7 @@
         <v>363</v>
       </c>
       <c r="D1236" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1236" t="s">
         <v>452</v>
@@ -72511,7 +72514,7 @@
         <v>363</v>
       </c>
       <c r="D1237" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1237" t="s">
         <v>423</v>
@@ -72552,7 +72555,7 @@
         <v>363</v>
       </c>
       <c r="D1238" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1238" t="s">
         <v>438</v>
@@ -72593,7 +72596,7 @@
         <v>363</v>
       </c>
       <c r="D1239" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1239" t="s">
         <v>430</v>
@@ -72634,7 +72637,7 @@
         <v>363</v>
       </c>
       <c r="D1240" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1240" t="s">
         <v>522</v>
@@ -72675,7 +72678,7 @@
         <v>363</v>
       </c>
       <c r="D1241" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E1241" t="s">
         <v>634</v>
@@ -72722,11 +72725,11 @@
         <v>441</v>
       </c>
       <c r="F1242" s="8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1242" s="9"/>
       <c r="H1242" s="10">
-        <v>1.65</v>
+        <v>2.273</v>
       </c>
       <c r="I1242" s="11"/>
       <c r="J1242" s="8"/>
@@ -72735,7 +72738,7 @@
       </c>
       <c r="L1242" s="11"/>
       <c r="M1242" s="4" t="s">
-        <v>1300</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.25">
@@ -72755,28 +72758,28 @@
         <v>433</v>
       </c>
       <c r="F1243" s="12">
-        <v>8.6</v>
+        <v>9.2</v>
       </c>
       <c r="G1243" s="13">
-        <v>7.548</v>
+        <v>7.879</v>
       </c>
       <c r="H1243" s="14">
-        <v>1.052</v>
+        <v>1.321</v>
       </c>
       <c r="I1243" s="15">
-        <v>13.9</v>
+        <v>16.8</v>
       </c>
       <c r="J1243" s="12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="K1243" s="16">
-        <v>-6.9</v>
+        <v>-7.3</v>
       </c>
       <c r="L1243" s="15">
-        <v>-44.5</v>
+        <v>-44.2</v>
       </c>
       <c r="M1243" t="s">
-        <v>1662</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.25">
@@ -72796,28 +72799,28 @@
         <v>452</v>
       </c>
       <c r="F1244" s="12">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="G1244" s="13">
-        <v>4.087</v>
+        <v>4.089</v>
       </c>
       <c r="H1244" s="14">
-        <v>0.763</v>
+        <v>0.911</v>
       </c>
       <c r="I1244" s="15">
-        <v>18.7</v>
+        <v>22.3</v>
       </c>
       <c r="J1244" s="12">
-        <v>14.583</v>
+        <v>15.083</v>
       </c>
       <c r="K1244" s="16">
-        <v>-9.733</v>
+        <v>-10.083</v>
       </c>
       <c r="L1244" s="15">
-        <v>-66.7</v>
+        <v>-66.8</v>
       </c>
       <c r="M1244" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1245" spans="1:13" x14ac:dyDescent="0.25">
@@ -72837,28 +72840,28 @@
         <v>423</v>
       </c>
       <c r="F1245" s="12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G1245" s="13">
-        <v>3.237</v>
+        <v>3.336</v>
       </c>
       <c r="H1245" s="14">
-        <v>0.513</v>
+        <v>0.364</v>
       </c>
       <c r="I1245" s="15">
-        <v>15.9</v>
+        <v>10.9</v>
       </c>
       <c r="J1245" s="12">
-        <v>21.375</v>
+        <v>21.625</v>
       </c>
       <c r="K1245" s="16">
-        <v>-17.625</v>
+        <v>-17.925</v>
       </c>
       <c r="L1245" s="15">
-        <v>-82.5</v>
+        <v>-82.9</v>
       </c>
       <c r="M1245" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1246" spans="1:13" x14ac:dyDescent="0.25">
@@ -72878,28 +72881,28 @@
         <v>438</v>
       </c>
       <c r="F1246" s="12">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="G1246" s="13">
-        <v>3.74</v>
+        <v>3.637</v>
       </c>
       <c r="H1246" s="14">
-        <v>0.46</v>
+        <v>0.513</v>
       </c>
       <c r="I1246" s="15">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="J1246" s="12">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="K1246" s="16">
-        <v>-30.7</v>
+        <v>-30.55</v>
       </c>
       <c r="L1246" s="15">
         <v>-88</v>
       </c>
       <c r="M1246" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.25">
@@ -72919,28 +72922,28 @@
         <v>430</v>
       </c>
       <c r="F1247" s="12">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="G1247" s="13">
-        <v>4.962</v>
+        <v>4.827</v>
       </c>
       <c r="H1247" s="14">
-        <v>0.738</v>
+        <v>0.823</v>
       </c>
       <c r="I1247" s="15">
-        <v>14.9</v>
+        <v>17.1</v>
       </c>
       <c r="J1247" s="12">
-        <v>90.833</v>
+        <v>89.75</v>
       </c>
       <c r="K1247" s="16">
-        <v>-85.133</v>
+        <v>-84.1</v>
       </c>
       <c r="L1247" s="15">
         <v>-93.7</v>
       </c>
       <c r="M1247" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1248" spans="1:13" x14ac:dyDescent="0.25">
@@ -72960,28 +72963,28 @@
         <v>522</v>
       </c>
       <c r="F1248" s="12">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="G1248" s="13">
-        <v>8.869</v>
+        <v>8.612</v>
       </c>
       <c r="H1248" s="17">
-        <v>-0.119</v>
+        <v>-0.112</v>
       </c>
       <c r="I1248" s="15">
         <v>-1.3</v>
       </c>
       <c r="J1248" s="12">
-        <v>68.4</v>
+        <v>67.2</v>
       </c>
       <c r="K1248" s="16">
-        <v>-59.65</v>
+        <v>-58.7</v>
       </c>
       <c r="L1248" s="15">
-        <v>-87.2</v>
+        <v>-87.3</v>
       </c>
       <c r="M1248" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1249" spans="1:13" x14ac:dyDescent="0.25">
@@ -73001,28 +73004,28 @@
         <v>634</v>
       </c>
       <c r="F1249" s="12">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G1249" s="13">
         <v>9.448</v>
       </c>
-      <c r="H1249" s="14">
-        <v>0.552</v>
+      <c r="H1249" s="17">
+        <v>-0.048</v>
       </c>
       <c r="I1249" s="15">
-        <v>5.8</v>
+        <v>-0.5</v>
       </c>
       <c r="J1249" s="12">
         <v>82.8</v>
       </c>
       <c r="K1249" s="16">
-        <v>-72.8</v>
+        <v>-73.4</v>
       </c>
       <c r="L1249" s="15">
-        <v>-87.9</v>
+        <v>-88.6</v>
       </c>
       <c r="M1249" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1250" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -73096,7 +73099,7 @@
         <v>-42.9</v>
       </c>
       <c r="M1251" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1252" spans="1:13" x14ac:dyDescent="0.25">
@@ -73137,7 +73140,7 @@
         <v>-64.8</v>
       </c>
       <c r="M1252" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1253" spans="1:13" x14ac:dyDescent="0.25">
@@ -73178,7 +73181,7 @@
         <v>-79</v>
       </c>
       <c r="M1253" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1254" spans="1:13" x14ac:dyDescent="0.25">
@@ -73219,7 +73222,7 @@
         <v>-86.6</v>
       </c>
       <c r="M1254" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1255" spans="1:13" x14ac:dyDescent="0.25">
@@ -73260,7 +73263,7 @@
         <v>-91.4</v>
       </c>
       <c r="M1255" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1256" spans="1:13" x14ac:dyDescent="0.25">
@@ -73301,7 +73304,7 @@
         <v>-84.1</v>
       </c>
       <c r="M1256" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1257" spans="1:13" x14ac:dyDescent="0.25">
@@ -73342,7 +73345,7 @@
         <v>-87.5</v>
       </c>
       <c r="M1257" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1258" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -73353,7 +73356,7 @@
         <v>246</v>
       </c>
       <c r="C1258" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1258" s="4" t="s">
         <v>693</v>
@@ -73366,7 +73369,7 @@
       </c>
       <c r="G1258" s="9"/>
       <c r="H1258" s="10">
-        <v>1.035</v>
+        <v>1.175</v>
       </c>
       <c r="I1258" s="11"/>
       <c r="J1258" s="8"/>
@@ -73386,7 +73389,7 @@
         <v>246</v>
       </c>
       <c r="C1259" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1259" t="s">
         <v>693</v>
@@ -73416,7 +73419,7 @@
         <v>-44.5</v>
       </c>
       <c r="M1259" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1260" spans="1:13" x14ac:dyDescent="0.25">
@@ -73427,7 +73430,7 @@
         <v>246</v>
       </c>
       <c r="C1260" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1260" t="s">
         <v>693</v>
@@ -73457,7 +73460,7 @@
         <v>-67.5</v>
       </c>
       <c r="M1260" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1261" spans="1:13" x14ac:dyDescent="0.25">
@@ -73468,7 +73471,7 @@
         <v>246</v>
       </c>
       <c r="C1261" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1261" t="s">
         <v>693</v>
@@ -73477,28 +73480,28 @@
         <v>423</v>
       </c>
       <c r="F1261" s="12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G1261" s="13">
         <v>2.991</v>
       </c>
       <c r="H1261" s="14">
-        <v>0.609</v>
+        <v>0.509</v>
       </c>
       <c r="I1261" s="15">
-        <v>20.4</v>
+        <v>17</v>
       </c>
       <c r="J1261" s="12">
         <v>16.5</v>
       </c>
       <c r="K1261" s="16">
-        <v>-12.9</v>
+        <v>-13</v>
       </c>
       <c r="L1261" s="15">
-        <v>-78.2</v>
+        <v>-78.8</v>
       </c>
       <c r="M1261" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1262" spans="1:13" x14ac:dyDescent="0.25">
@@ -73509,7 +73512,7 @@
         <v>246</v>
       </c>
       <c r="C1262" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1262" t="s">
         <v>693</v>
@@ -73539,7 +73542,7 @@
         <v>-87.3</v>
       </c>
       <c r="M1262" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1263" spans="1:13" x14ac:dyDescent="0.25">
@@ -73550,7 +73553,7 @@
         <v>246</v>
       </c>
       <c r="C1263" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1263" t="s">
         <v>693</v>
@@ -73559,28 +73562,28 @@
         <v>430</v>
       </c>
       <c r="F1263" s="12">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="G1263" s="13">
         <v>6.006</v>
       </c>
       <c r="H1263" s="14">
-        <v>1.194</v>
+        <v>1.294</v>
       </c>
       <c r="I1263" s="15">
-        <v>19.9</v>
+        <v>21.6</v>
       </c>
       <c r="J1263" s="12">
         <v>88.167</v>
       </c>
       <c r="K1263" s="16">
-        <v>-80.967</v>
+        <v>-80.867</v>
       </c>
       <c r="L1263" s="15">
-        <v>-91.8</v>
+        <v>-91.7</v>
       </c>
       <c r="M1263" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1264" spans="1:13" x14ac:dyDescent="0.25">
@@ -73591,7 +73594,7 @@
         <v>246</v>
       </c>
       <c r="C1264" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1264" t="s">
         <v>693</v>
@@ -73600,28 +73603,28 @@
         <v>522</v>
       </c>
       <c r="F1264" s="12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G1264" s="13">
         <v>12.186</v>
       </c>
-      <c r="H1264" s="17">
-        <v>-0.186</v>
+      <c r="H1264" s="14">
+        <v>0.314</v>
       </c>
       <c r="I1264" s="15">
-        <v>-1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J1264" s="12">
         <v>82</v>
       </c>
       <c r="K1264" s="16">
-        <v>-70</v>
+        <v>-69.5</v>
       </c>
       <c r="L1264" s="15">
-        <v>-85.4</v>
+        <v>-84.8</v>
       </c>
       <c r="M1264" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="1265" spans="1:13" x14ac:dyDescent="0.25">
@@ -73632,7 +73635,7 @@
         <v>246</v>
       </c>
       <c r="C1265" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D1265" t="s">
         <v>693</v>
@@ -73662,7 +73665,7 @@
         <v>-86.5</v>
       </c>
       <c r="M1265" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1266" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -73736,7 +73739,7 @@
         <v>-44.2</v>
       </c>
       <c r="M1267" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="1268" spans="1:13" x14ac:dyDescent="0.25">
@@ -73777,7 +73780,7 @@
         <v>-66.2</v>
       </c>
       <c r="M1268" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1269" spans="1:13" x14ac:dyDescent="0.25">
@@ -73818,7 +73821,7 @@
         <v>-79.6</v>
       </c>
       <c r="M1269" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1270" spans="1:13" x14ac:dyDescent="0.25">
@@ -73859,7 +73862,7 @@
         <v>-87.3</v>
       </c>
       <c r="M1270" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1271" spans="1:13" x14ac:dyDescent="0.25">
@@ -73900,7 +73903,7 @@
         <v>-92.3</v>
       </c>
       <c r="M1271" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1272" spans="1:13" x14ac:dyDescent="0.25">
@@ -73941,7 +73944,7 @@
         <v>-86.2</v>
       </c>
       <c r="M1272" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1273" spans="1:13" x14ac:dyDescent="0.25">
@@ -73982,7 +73985,7 @@
         <v>-88.5</v>
       </c>
       <c r="M1273" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1274" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -74097,7 +74100,7 @@
         <v>-67.5</v>
       </c>
       <c r="M1276" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1277" spans="1:13" x14ac:dyDescent="0.25">
@@ -74138,7 +74141,7 @@
         <v>-80.4</v>
       </c>
       <c r="M1277" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1278" spans="1:13" x14ac:dyDescent="0.25">
@@ -74179,7 +74182,7 @@
         <v>-88.7</v>
       </c>
       <c r="M1278" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="1279" spans="1:13" x14ac:dyDescent="0.25">
@@ -74220,7 +74223,7 @@
         <v>-92.5</v>
       </c>
       <c r="M1279" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="1280" spans="1:13" x14ac:dyDescent="0.25">
@@ -74261,7 +74264,7 @@
         <v>-87.3</v>
       </c>
       <c r="M1280" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.25">
@@ -74302,7 +74305,7 @@
         <v>-89.5</v>
       </c>
       <c r="M1281" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1282" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -74376,7 +74379,7 @@
         <v>-47.6</v>
       </c>
       <c r="M1283" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.25">
@@ -74417,7 +74420,7 @@
         <v>-69.9</v>
       </c>
       <c r="M1284" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.25">
@@ -74458,7 +74461,7 @@
         <v>-80.5</v>
       </c>
       <c r="M1285" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.25">
@@ -74499,7 +74502,7 @@
         <v>-85.4</v>
       </c>
       <c r="M1286" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.25">
@@ -74540,7 +74543,7 @@
         <v>-88.8</v>
       </c>
       <c r="M1287" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.25">
@@ -74581,7 +74584,7 @@
         <v>-82.6</v>
       </c>
       <c r="M1288" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.25">
@@ -74622,7 +74625,7 @@
         <v>-80.2</v>
       </c>
       <c r="M1289" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1290" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -74696,7 +74699,7 @@
         <v>-47.1</v>
       </c>
       <c r="M1291" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="1292" spans="1:13" x14ac:dyDescent="0.25">
@@ -74737,7 +74740,7 @@
         <v>-71.7</v>
       </c>
       <c r="M1292" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="1293" spans="1:13" x14ac:dyDescent="0.25">
@@ -74778,7 +74781,7 @@
         <v>-83.7</v>
       </c>
       <c r="M1293" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="1294" spans="1:13" x14ac:dyDescent="0.25">
@@ -74819,7 +74822,7 @@
         <v>-90</v>
       </c>
       <c r="M1294" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1295" spans="1:13" x14ac:dyDescent="0.25">
@@ -74860,7 +74863,7 @@
         <v>-93.1</v>
       </c>
       <c r="M1295" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="1296" spans="1:13" x14ac:dyDescent="0.25">
@@ -74901,7 +74904,7 @@
         <v>-87.2</v>
       </c>
       <c r="M1296" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1297" spans="1:13" x14ac:dyDescent="0.25">
@@ -74942,7 +74945,7 @@
         <v>-87.4</v>
       </c>
       <c r="M1297" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="1298" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -74953,10 +74956,10 @@
         <v>271</v>
       </c>
       <c r="C1298" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1298" s="4" t="s">
         <v>956</v>
-      </c>
-      <c r="D1298" s="4" t="s">
-        <v>957</v>
       </c>
       <c r="E1298" s="4" t="s">
         <v>441</v>
@@ -74986,10 +74989,10 @@
         <v>271</v>
       </c>
       <c r="C1299" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1299" t="s">
         <v>956</v>
-      </c>
-      <c r="D1299" t="s">
-        <v>957</v>
       </c>
       <c r="E1299" t="s">
         <v>433</v>
@@ -75016,7 +75019,7 @@
         <v>-52.7</v>
       </c>
       <c r="M1299" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="1300" spans="1:13" x14ac:dyDescent="0.25">
@@ -75027,10 +75030,10 @@
         <v>271</v>
       </c>
       <c r="C1300" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1300" t="s">
         <v>956</v>
-      </c>
-      <c r="D1300" t="s">
-        <v>957</v>
       </c>
       <c r="E1300" t="s">
         <v>452</v>
@@ -75057,7 +75060,7 @@
         <v>-77.4</v>
       </c>
       <c r="M1300" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1301" spans="1:13" x14ac:dyDescent="0.25">
@@ -75068,10 +75071,10 @@
         <v>271</v>
       </c>
       <c r="C1301" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1301" t="s">
         <v>956</v>
-      </c>
-      <c r="D1301" t="s">
-        <v>957</v>
       </c>
       <c r="E1301" t="s">
         <v>423</v>
@@ -75098,7 +75101,7 @@
         <v>-89.6</v>
       </c>
       <c r="M1301" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="1302" spans="1:13" x14ac:dyDescent="0.25">
@@ -75109,10 +75112,10 @@
         <v>271</v>
       </c>
       <c r="C1302" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1302" t="s">
         <v>956</v>
-      </c>
-      <c r="D1302" t="s">
-        <v>957</v>
       </c>
       <c r="E1302" t="s">
         <v>438</v>
@@ -75139,7 +75142,7 @@
         <v>-95.1</v>
       </c>
       <c r="M1302" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="1303" spans="1:13" x14ac:dyDescent="0.25">
@@ -75150,10 +75153,10 @@
         <v>271</v>
       </c>
       <c r="C1303" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1303" t="s">
         <v>956</v>
-      </c>
-      <c r="D1303" t="s">
-        <v>957</v>
       </c>
       <c r="E1303" t="s">
         <v>430</v>
@@ -75180,7 +75183,7 @@
         <v>-95.3</v>
       </c>
       <c r="M1303" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="1304" spans="1:13" x14ac:dyDescent="0.25">
@@ -75191,10 +75194,10 @@
         <v>271</v>
       </c>
       <c r="C1304" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1304" t="s">
         <v>956</v>
-      </c>
-      <c r="D1304" t="s">
-        <v>957</v>
       </c>
       <c r="E1304" t="s">
         <v>522</v>
@@ -75221,7 +75224,7 @@
         <v>-92.3</v>
       </c>
       <c r="M1304" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="1305" spans="1:13" x14ac:dyDescent="0.25">
@@ -75232,10 +75235,10 @@
         <v>271</v>
       </c>
       <c r="C1305" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1305" t="s">
         <v>956</v>
-      </c>
-      <c r="D1305" t="s">
-        <v>957</v>
       </c>
       <c r="E1305" t="s">
         <v>634</v>
@@ -75262,7 +75265,7 @@
         <v>-91.8</v>
       </c>
       <c r="M1305" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="1306" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -75276,7 +75279,7 @@
         <v>707</v>
       </c>
       <c r="D1306" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1306" s="4" t="s">
         <v>441</v>
@@ -75309,7 +75312,7 @@
         <v>707</v>
       </c>
       <c r="D1307" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1307" t="s">
         <v>433</v>
@@ -75336,7 +75339,7 @@
         <v>-47.9</v>
       </c>
       <c r="M1307" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="1308" spans="1:13" x14ac:dyDescent="0.25">
@@ -75350,7 +75353,7 @@
         <v>707</v>
       </c>
       <c r="D1308" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1308" t="s">
         <v>452</v>
@@ -75377,7 +75380,7 @@
         <v>-74.6</v>
       </c>
       <c r="M1308" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="1309" spans="1:13" x14ac:dyDescent="0.25">
@@ -75391,7 +75394,7 @@
         <v>707</v>
       </c>
       <c r="D1309" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1309" t="s">
         <v>423</v>
@@ -75418,7 +75421,7 @@
         <v>-86.9</v>
       </c>
       <c r="M1309" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="1310" spans="1:13" x14ac:dyDescent="0.25">
@@ -75432,7 +75435,7 @@
         <v>707</v>
       </c>
       <c r="D1310" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1310" t="s">
         <v>438</v>
@@ -75459,7 +75462,7 @@
         <v>-93.6</v>
       </c>
       <c r="M1310" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="1311" spans="1:13" x14ac:dyDescent="0.25">
@@ -75473,7 +75476,7 @@
         <v>707</v>
       </c>
       <c r="D1311" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1311" t="s">
         <v>430</v>
@@ -75500,7 +75503,7 @@
         <v>-95.2</v>
       </c>
       <c r="M1311" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="1312" spans="1:13" x14ac:dyDescent="0.25">
@@ -75514,7 +75517,7 @@
         <v>707</v>
       </c>
       <c r="D1312" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1312" t="s">
         <v>522</v>
@@ -75541,7 +75544,7 @@
         <v>-90.8</v>
       </c>
       <c r="M1312" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1313" spans="1:13" x14ac:dyDescent="0.25">
@@ -75555,7 +75558,7 @@
         <v>707</v>
       </c>
       <c r="D1313" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1313" t="s">
         <v>634</v>
@@ -75582,7 +75585,7 @@
         <v>-90.3</v>
       </c>
       <c r="M1313" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1314" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -75593,7 +75596,7 @@
         <v>279</v>
       </c>
       <c r="C1314" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1314" s="4" t="s">
         <v>812</v>
@@ -75626,7 +75629,7 @@
         <v>279</v>
       </c>
       <c r="C1315" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1315" t="s">
         <v>812</v>
@@ -75656,7 +75659,7 @@
         <v>-45.8</v>
       </c>
       <c r="M1315" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="1316" spans="1:13" x14ac:dyDescent="0.25">
@@ -75667,7 +75670,7 @@
         <v>279</v>
       </c>
       <c r="C1316" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1316" t="s">
         <v>812</v>
@@ -75697,7 +75700,7 @@
         <v>-69.8</v>
       </c>
       <c r="M1316" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1317" spans="1:13" x14ac:dyDescent="0.25">
@@ -75708,7 +75711,7 @@
         <v>279</v>
       </c>
       <c r="C1317" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1317" t="s">
         <v>812</v>
@@ -75738,7 +75741,7 @@
         <v>-83.2</v>
       </c>
       <c r="M1317" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1318" spans="1:13" x14ac:dyDescent="0.25">
@@ -75749,7 +75752,7 @@
         <v>279</v>
       </c>
       <c r="C1318" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1318" t="s">
         <v>812</v>
@@ -75779,7 +75782,7 @@
         <v>-88.2</v>
       </c>
       <c r="M1318" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1319" spans="1:13" x14ac:dyDescent="0.25">
@@ -75790,7 +75793,7 @@
         <v>279</v>
       </c>
       <c r="C1319" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1319" t="s">
         <v>812</v>
@@ -75820,7 +75823,7 @@
         <v>-91.7</v>
       </c>
       <c r="M1319" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="1320" spans="1:13" x14ac:dyDescent="0.25">
@@ -75831,7 +75834,7 @@
         <v>279</v>
       </c>
       <c r="C1320" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1320" t="s">
         <v>812</v>
@@ -75861,7 +75864,7 @@
         <v>-86.4</v>
       </c>
       <c r="M1320" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="1321" spans="1:13" x14ac:dyDescent="0.25">
@@ -75872,7 +75875,7 @@
         <v>279</v>
       </c>
       <c r="C1321" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1321" t="s">
         <v>812</v>
@@ -75902,7 +75905,7 @@
         <v>-87.3</v>
       </c>
       <c r="M1321" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="1322" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -75976,7 +75979,7 @@
         <v>-51.6</v>
       </c>
       <c r="M1323" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1324" spans="1:13" x14ac:dyDescent="0.25">
@@ -76017,7 +76020,7 @@
         <v>-73.8</v>
       </c>
       <c r="M1324" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="1325" spans="1:13" x14ac:dyDescent="0.25">
@@ -76058,7 +76061,7 @@
         <v>-87.2</v>
       </c>
       <c r="M1325" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1326" spans="1:13" x14ac:dyDescent="0.25">
@@ -76099,7 +76102,7 @@
         <v>-93.3</v>
       </c>
       <c r="M1326" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1327" spans="1:13" x14ac:dyDescent="0.25">
@@ -76140,7 +76143,7 @@
         <v>-95.4</v>
       </c>
       <c r="M1327" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1328" spans="1:13" x14ac:dyDescent="0.25">
@@ -76181,7 +76184,7 @@
         <v>-90.4</v>
       </c>
       <c r="M1328" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="1329" spans="1:13" x14ac:dyDescent="0.25">
@@ -76222,7 +76225,7 @@
         <v>-89.7</v>
       </c>
       <c r="M1329" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1330" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -76233,10 +76236,10 @@
         <v>285</v>
       </c>
       <c r="C1330" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1330" s="4" t="s">
         <v>965</v>
-      </c>
-      <c r="D1330" s="4" t="s">
-        <v>966</v>
       </c>
       <c r="E1330" s="4" t="s">
         <v>441</v>
@@ -76266,10 +76269,10 @@
         <v>285</v>
       </c>
       <c r="C1331" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1331" t="s">
         <v>965</v>
-      </c>
-      <c r="D1331" t="s">
-        <v>966</v>
       </c>
       <c r="E1331" t="s">
         <v>433</v>
@@ -76296,7 +76299,7 @@
         <v>-44.5</v>
       </c>
       <c r="M1331" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="1332" spans="1:13" x14ac:dyDescent="0.25">
@@ -76307,10 +76310,10 @@
         <v>285</v>
       </c>
       <c r="C1332" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1332" t="s">
         <v>965</v>
-      </c>
-      <c r="D1332" t="s">
-        <v>966</v>
       </c>
       <c r="E1332" t="s">
         <v>452</v>
@@ -76337,7 +76340,7 @@
         <v>-66.9</v>
       </c>
       <c r="M1332" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1333" spans="1:13" x14ac:dyDescent="0.25">
@@ -76348,10 +76351,10 @@
         <v>285</v>
       </c>
       <c r="C1333" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1333" t="s">
         <v>965</v>
-      </c>
-      <c r="D1333" t="s">
-        <v>966</v>
       </c>
       <c r="E1333" t="s">
         <v>423</v>
@@ -76378,7 +76381,7 @@
         <v>-80.3</v>
       </c>
       <c r="M1333" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="1334" spans="1:13" x14ac:dyDescent="0.25">
@@ -76389,10 +76392,10 @@
         <v>285</v>
       </c>
       <c r="C1334" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1334" t="s">
         <v>965</v>
-      </c>
-      <c r="D1334" t="s">
-        <v>966</v>
       </c>
       <c r="E1334" t="s">
         <v>438</v>
@@ -76419,7 +76422,7 @@
         <v>-86.4</v>
       </c>
       <c r="M1334" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1335" spans="1:13" x14ac:dyDescent="0.25">
@@ -76430,10 +76433,10 @@
         <v>285</v>
       </c>
       <c r="C1335" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1335" t="s">
         <v>965</v>
-      </c>
-      <c r="D1335" t="s">
-        <v>966</v>
       </c>
       <c r="E1335" t="s">
         <v>430</v>
@@ -76460,7 +76463,7 @@
         <v>-91</v>
       </c>
       <c r="M1335" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="1336" spans="1:13" x14ac:dyDescent="0.25">
@@ -76471,10 +76474,10 @@
         <v>285</v>
       </c>
       <c r="C1336" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1336" t="s">
         <v>965</v>
-      </c>
-      <c r="D1336" t="s">
-        <v>966</v>
       </c>
       <c r="E1336" t="s">
         <v>522</v>
@@ -76501,7 +76504,7 @@
         <v>-85.3</v>
       </c>
       <c r="M1336" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1337" spans="1:13" x14ac:dyDescent="0.25">
@@ -76512,10 +76515,10 @@
         <v>285</v>
       </c>
       <c r="C1337" t="s">
+        <v>964</v>
+      </c>
+      <c r="D1337" t="s">
         <v>965</v>
-      </c>
-      <c r="D1337" t="s">
-        <v>966</v>
       </c>
       <c r="E1337" t="s">
         <v>634</v>
@@ -76542,7 +76545,7 @@
         <v>-86.4</v>
       </c>
       <c r="M1337" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="1338" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -76616,7 +76619,7 @@
         <v>-45.4</v>
       </c>
       <c r="M1339" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1340" spans="1:13" x14ac:dyDescent="0.25">
@@ -76657,7 +76660,7 @@
         <v>-67.3</v>
       </c>
       <c r="M1340" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1341" spans="1:13" x14ac:dyDescent="0.25">
@@ -76698,7 +76701,7 @@
         <v>-81.5</v>
       </c>
       <c r="M1341" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="1342" spans="1:13" x14ac:dyDescent="0.25">
@@ -76739,7 +76742,7 @@
         <v>-89.2</v>
       </c>
       <c r="M1342" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="1343" spans="1:13" x14ac:dyDescent="0.25">
@@ -76780,7 +76783,7 @@
         <v>-92.2</v>
       </c>
       <c r="M1343" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1344" spans="1:13" x14ac:dyDescent="0.25">
@@ -76821,7 +76824,7 @@
         <v>-85.6</v>
       </c>
       <c r="M1344" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1345" spans="1:13" x14ac:dyDescent="0.25">
@@ -76862,7 +76865,7 @@
         <v>-85.9</v>
       </c>
       <c r="M1345" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1346" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -76936,7 +76939,7 @@
         <v>-47.3</v>
       </c>
       <c r="M1347" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1348" spans="1:13" x14ac:dyDescent="0.25">
@@ -76977,7 +76980,7 @@
         <v>-72.5</v>
       </c>
       <c r="M1348" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="1349" spans="1:13" x14ac:dyDescent="0.25">
@@ -77018,7 +77021,7 @@
         <v>-87.1</v>
       </c>
       <c r="M1349" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="1350" spans="1:13" x14ac:dyDescent="0.25">
@@ -77059,7 +77062,7 @@
         <v>-93.6</v>
       </c>
       <c r="M1350" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1351" spans="1:13" x14ac:dyDescent="0.25">
@@ -77100,7 +77103,7 @@
         <v>-93.5</v>
       </c>
       <c r="M1351" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="1352" spans="1:13" x14ac:dyDescent="0.25">
@@ -77182,7 +77185,7 @@
         <v>-88.5</v>
       </c>
       <c r="M1353" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="1354" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -77256,7 +77259,7 @@
         <v>-48</v>
       </c>
       <c r="M1355" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="1356" spans="1:13" x14ac:dyDescent="0.25">
@@ -77297,7 +77300,7 @@
         <v>-71.1</v>
       </c>
       <c r="M1356" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1357" spans="1:13" x14ac:dyDescent="0.25">
@@ -77338,7 +77341,7 @@
         <v>-84.5</v>
       </c>
       <c r="M1357" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="1358" spans="1:13" x14ac:dyDescent="0.25">
@@ -77379,7 +77382,7 @@
         <v>-91.3</v>
       </c>
       <c r="M1358" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="1359" spans="1:13" x14ac:dyDescent="0.25">
@@ -77420,7 +77423,7 @@
         <v>-94.7</v>
       </c>
       <c r="M1359" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="1360" spans="1:13" x14ac:dyDescent="0.25">
@@ -77461,7 +77464,7 @@
         <v>-91.5</v>
       </c>
       <c r="M1360" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1361" spans="1:13" x14ac:dyDescent="0.25">
@@ -77502,7 +77505,7 @@
         <v>-90.9</v>
       </c>
       <c r="M1361" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="1362" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -77576,7 +77579,7 @@
         <v>-40.7</v>
       </c>
       <c r="M1363" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="1364" spans="1:13" x14ac:dyDescent="0.25">
@@ -77617,7 +77620,7 @@
         <v>-64.9</v>
       </c>
       <c r="M1364" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1365" spans="1:13" x14ac:dyDescent="0.25">
@@ -77658,7 +77661,7 @@
         <v>-80.2</v>
       </c>
       <c r="M1365" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="1366" spans="1:13" x14ac:dyDescent="0.25">
@@ -77699,7 +77702,7 @@
         <v>-87.1</v>
       </c>
       <c r="M1366" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="1367" spans="1:13" x14ac:dyDescent="0.25">
@@ -77740,7 +77743,7 @@
         <v>-92.4</v>
       </c>
       <c r="M1367" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="1368" spans="1:13" x14ac:dyDescent="0.25">
@@ -77781,7 +77784,7 @@
         <v>-85.5</v>
       </c>
       <c r="M1368" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1369" spans="1:13" x14ac:dyDescent="0.25">
@@ -77822,7 +77825,7 @@
         <v>-85.7</v>
       </c>
       <c r="M1369" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="1370" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -77896,7 +77899,7 @@
         <v>-44.4</v>
       </c>
       <c r="M1371" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="1372" spans="1:13" x14ac:dyDescent="0.25">
@@ -77937,7 +77940,7 @@
         <v>-70.7</v>
       </c>
       <c r="M1372" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="1373" spans="1:13" x14ac:dyDescent="0.25">
@@ -77978,7 +77981,7 @@
         <v>-84.8</v>
       </c>
       <c r="M1373" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="1374" spans="1:13" x14ac:dyDescent="0.25">
@@ -78019,7 +78022,7 @@
         <v>-92.1</v>
       </c>
       <c r="M1374" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="1375" spans="1:13" x14ac:dyDescent="0.25">
@@ -78060,7 +78063,7 @@
         <v>-94.6</v>
       </c>
       <c r="M1375" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="1376" spans="1:13" x14ac:dyDescent="0.25">
@@ -78101,7 +78104,7 @@
         <v>-90.3</v>
       </c>
       <c r="M1376" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="1377" spans="1:13" x14ac:dyDescent="0.25">
@@ -78142,7 +78145,7 @@
         <v>-90.4</v>
       </c>
       <c r="M1377" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1378" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -78216,7 +78219,7 @@
         <v>-42.9</v>
       </c>
       <c r="M1379" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1380" spans="1:13" x14ac:dyDescent="0.25">
@@ -78257,7 +78260,7 @@
         <v>-68.3</v>
       </c>
       <c r="M1380" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="1381" spans="1:13" x14ac:dyDescent="0.25">
@@ -78298,7 +78301,7 @@
         <v>-78.9</v>
       </c>
       <c r="M1381" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1382" spans="1:13" x14ac:dyDescent="0.25">
@@ -78339,7 +78342,7 @@
         <v>-87.4</v>
       </c>
       <c r="M1382" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="1383" spans="1:13" x14ac:dyDescent="0.25">
@@ -78380,7 +78383,7 @@
         <v>-92.7</v>
       </c>
       <c r="M1383" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="1384" spans="1:13" x14ac:dyDescent="0.25">
@@ -78421,7 +78424,7 @@
         <v>-85.5</v>
       </c>
       <c r="M1384" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="1385" spans="1:13" x14ac:dyDescent="0.25">
@@ -78462,7 +78465,7 @@
         <v>-88.3</v>
       </c>
       <c r="M1385" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="1386" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -78536,7 +78539,7 @@
         <v>-41.5</v>
       </c>
       <c r="M1387" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="1388" spans="1:13" x14ac:dyDescent="0.25">
@@ -78577,7 +78580,7 @@
         <v>-68.7</v>
       </c>
       <c r="M1388" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="1389" spans="1:13" x14ac:dyDescent="0.25">
@@ -78618,7 +78621,7 @@
         <v>-84.6</v>
       </c>
       <c r="M1389" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="1390" spans="1:13" x14ac:dyDescent="0.25">
@@ -78659,7 +78662,7 @@
         <v>-91</v>
       </c>
       <c r="M1390" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="1391" spans="1:13" x14ac:dyDescent="0.25">
@@ -78700,7 +78703,7 @@
         <v>-95</v>
       </c>
       <c r="M1391" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="1392" spans="1:13" x14ac:dyDescent="0.25">
@@ -78741,7 +78744,7 @@
         <v>-87.7</v>
       </c>
       <c r="M1392" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="1393" spans="1:13" x14ac:dyDescent="0.25">
@@ -78782,7 +78785,7 @@
         <v>-89.9</v>
       </c>
       <c r="M1393" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="1394" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -78897,7 +78900,7 @@
         <v>-72.5</v>
       </c>
       <c r="M1396" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="1397" spans="1:13" x14ac:dyDescent="0.25">
@@ -78938,7 +78941,7 @@
         <v>-88.8</v>
       </c>
       <c r="M1397" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="1398" spans="1:13" x14ac:dyDescent="0.25">
@@ -78979,7 +78982,7 @@
         <v>-94.4</v>
       </c>
       <c r="M1398" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="1399" spans="1:13" x14ac:dyDescent="0.25">
@@ -79020,7 +79023,7 @@
         <v>-95.8</v>
       </c>
       <c r="M1399" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="1400" spans="1:13" x14ac:dyDescent="0.25">
@@ -79061,7 +79064,7 @@
         <v>-92.5</v>
       </c>
       <c r="M1400" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="1401" spans="1:13" x14ac:dyDescent="0.25">
@@ -79102,7 +79105,7 @@
         <v>-92.9</v>
       </c>
       <c r="M1401" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="1402" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -79176,7 +79179,7 @@
         <v>-43.5</v>
       </c>
       <c r="M1403" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="1404" spans="1:13" x14ac:dyDescent="0.25">
@@ -79258,7 +79261,7 @@
         <v>-80.1</v>
       </c>
       <c r="M1405" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="1406" spans="1:13" x14ac:dyDescent="0.25">
@@ -79299,7 +79302,7 @@
         <v>-87.3</v>
       </c>
       <c r="M1406" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="1407" spans="1:13" x14ac:dyDescent="0.25">
@@ -79340,7 +79343,7 @@
         <v>-93.5</v>
       </c>
       <c r="M1407" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1408" spans="1:13" x14ac:dyDescent="0.25">
@@ -79381,7 +79384,7 @@
         <v>-84.3</v>
       </c>
       <c r="M1408" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="1409" spans="1:13" x14ac:dyDescent="0.25">
@@ -79422,7 +79425,7 @@
         <v>-86.3</v>
       </c>
       <c r="M1409" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="1410" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -79496,7 +79499,7 @@
         <v>-64</v>
       </c>
       <c r="M1411" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="1412" spans="1:13" x14ac:dyDescent="0.25">
@@ -79537,7 +79540,7 @@
         <v>-86.3</v>
       </c>
       <c r="M1412" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="1413" spans="1:13" x14ac:dyDescent="0.25">
@@ -79578,7 +79581,7 @@
         <v>-95.7</v>
       </c>
       <c r="M1413" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="1414" spans="1:13" x14ac:dyDescent="0.25">
@@ -79619,7 +79622,7 @@
         <v>-97.7</v>
       </c>
       <c r="M1414" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="1415" spans="1:13" x14ac:dyDescent="0.25">
@@ -79660,7 +79663,7 @@
         <v>-97.8</v>
       </c>
       <c r="M1415" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="1416" spans="1:13" x14ac:dyDescent="0.25">
@@ -79701,7 +79704,7 @@
         <v>-97.1</v>
       </c>
       <c r="M1416" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1417" spans="1:13" x14ac:dyDescent="0.25">
@@ -79742,7 +79745,7 @@
         <v>-97.1</v>
       </c>
       <c r="M1417" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1418" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -79816,7 +79819,7 @@
         <v>-51.6</v>
       </c>
       <c r="M1419" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1420" spans="1:13" x14ac:dyDescent="0.25">
@@ -79857,7 +79860,7 @@
         <v>-78.3</v>
       </c>
       <c r="M1420" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1421" spans="1:13" x14ac:dyDescent="0.25">
@@ -79898,7 +79901,7 @@
         <v>-89.5</v>
       </c>
       <c r="M1421" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1422" spans="1:13" x14ac:dyDescent="0.25">
@@ -79939,7 +79942,7 @@
         <v>-95</v>
       </c>
       <c r="M1422" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1423" spans="1:13" x14ac:dyDescent="0.25">
@@ -79980,7 +79983,7 @@
         <v>-95.8</v>
       </c>
       <c r="M1423" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1424" spans="1:13" x14ac:dyDescent="0.25">
@@ -80021,7 +80024,7 @@
         <v>-92.8</v>
       </c>
       <c r="M1424" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1425" spans="1:13" x14ac:dyDescent="0.25">
@@ -80062,7 +80065,7 @@
         <v>-92.1</v>
       </c>
       <c r="M1425" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1426" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -80177,7 +80180,7 @@
         <v>-77.8</v>
       </c>
       <c r="M1428" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1429" spans="1:13" x14ac:dyDescent="0.25">
@@ -80218,7 +80221,7 @@
         <v>-89.7</v>
       </c>
       <c r="M1429" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1430" spans="1:13" x14ac:dyDescent="0.25">
@@ -80259,7 +80262,7 @@
         <v>-94.5</v>
       </c>
       <c r="M1430" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="1431" spans="1:13" x14ac:dyDescent="0.25">
@@ -80300,7 +80303,7 @@
         <v>-95.7</v>
       </c>
       <c r="M1431" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="1432" spans="1:13" x14ac:dyDescent="0.25">
@@ -80341,7 +80344,7 @@
         <v>-92</v>
       </c>
       <c r="M1432" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="1433" spans="1:13" x14ac:dyDescent="0.25">
@@ -80382,7 +80385,7 @@
         <v>-92.7</v>
       </c>
       <c r="M1433" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1434" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -80456,7 +80459,7 @@
         <v>-50.6</v>
       </c>
       <c r="M1435" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="1436" spans="1:13" x14ac:dyDescent="0.25">
@@ -80497,7 +80500,7 @@
         <v>-75.9</v>
       </c>
       <c r="M1436" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1437" spans="1:13" x14ac:dyDescent="0.25">
@@ -80538,7 +80541,7 @@
         <v>-88.8</v>
       </c>
       <c r="M1437" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="1438" spans="1:13" x14ac:dyDescent="0.25">
@@ -80579,7 +80582,7 @@
         <v>-94.5</v>
       </c>
       <c r="M1438" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="1439" spans="1:13" x14ac:dyDescent="0.25">
@@ -80620,7 +80623,7 @@
         <v>-96.4</v>
       </c>
       <c r="M1439" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="1440" spans="1:13" x14ac:dyDescent="0.25">
@@ -80661,7 +80664,7 @@
         <v>-94.1</v>
       </c>
       <c r="M1440" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="1441" spans="1:13" x14ac:dyDescent="0.25">
@@ -80702,7 +80705,7 @@
         <v>-93.7</v>
       </c>
       <c r="M1441" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="1442" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -80776,7 +80779,7 @@
         <v>-47.9</v>
       </c>
       <c r="M1443" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1444" spans="1:13" x14ac:dyDescent="0.25">
@@ -80817,7 +80820,7 @@
         <v>-74.1</v>
       </c>
       <c r="M1444" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="1445" spans="1:13" x14ac:dyDescent="0.25">
@@ -80858,7 +80861,7 @@
         <v>-88.3</v>
       </c>
       <c r="M1445" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="1446" spans="1:13" x14ac:dyDescent="0.25">
@@ -80899,7 +80902,7 @@
         <v>-94.5</v>
       </c>
       <c r="M1446" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="1447" spans="1:13" x14ac:dyDescent="0.25">
@@ -80940,7 +80943,7 @@
         <v>-95.5</v>
       </c>
       <c r="M1447" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="1448" spans="1:13" x14ac:dyDescent="0.25">
@@ -80981,7 +80984,7 @@
         <v>-92.4</v>
       </c>
       <c r="M1448" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="1449" spans="1:13" x14ac:dyDescent="0.25">
@@ -81022,7 +81025,7 @@
         <v>-91.6</v>
       </c>
       <c r="M1449" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="1450" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -81096,7 +81099,7 @@
         <v>-49</v>
       </c>
       <c r="M1451" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="1452" spans="1:13" x14ac:dyDescent="0.25">
@@ -81137,7 +81140,7 @@
         <v>-68.4</v>
       </c>
       <c r="M1452" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="1453" spans="1:13" x14ac:dyDescent="0.25">
@@ -81178,7 +81181,7 @@
         <v>-80.1</v>
       </c>
       <c r="M1453" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="1454" spans="1:13" x14ac:dyDescent="0.25">
@@ -81219,7 +81222,7 @@
         <v>-88.3</v>
       </c>
       <c r="M1454" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="1455" spans="1:13" x14ac:dyDescent="0.25">
@@ -81260,7 +81263,7 @@
         <v>-93.3</v>
       </c>
       <c r="M1455" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="1456" spans="1:13" x14ac:dyDescent="0.25">
@@ -81301,7 +81304,7 @@
         <v>-86</v>
       </c>
       <c r="M1456" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="1457" spans="1:13" x14ac:dyDescent="0.25">
@@ -81342,7 +81345,7 @@
         <v>-85.1</v>
       </c>
       <c r="M1457" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="1458" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -81416,7 +81419,7 @@
         <v>-56</v>
       </c>
       <c r="M1459" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="1460" spans="1:13" x14ac:dyDescent="0.25">
@@ -81457,7 +81460,7 @@
         <v>-82.6</v>
       </c>
       <c r="M1460" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="1461" spans="1:13" x14ac:dyDescent="0.25">
@@ -81498,7 +81501,7 @@
         <v>-93.5</v>
       </c>
       <c r="M1461" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="1462" spans="1:13" x14ac:dyDescent="0.25">
@@ -81539,7 +81542,7 @@
         <v>-96.5</v>
       </c>
       <c r="M1462" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="1463" spans="1:13" x14ac:dyDescent="0.25">
@@ -81580,7 +81583,7 @@
         <v>-97.9</v>
       </c>
       <c r="M1463" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1464" spans="1:13" x14ac:dyDescent="0.25">
@@ -81621,7 +81624,7 @@
         <v>-95.8</v>
       </c>
       <c r="M1464" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1465" spans="1:13" x14ac:dyDescent="0.25">
@@ -81662,7 +81665,7 @@
         <v>-97.1</v>
       </c>
       <c r="M1465" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1466" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -81736,7 +81739,7 @@
         <v>-47.6</v>
       </c>
       <c r="M1467" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="1468" spans="1:13" x14ac:dyDescent="0.25">
@@ -81777,7 +81780,7 @@
         <v>-76</v>
       </c>
       <c r="M1468" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="1469" spans="1:13" x14ac:dyDescent="0.25">
@@ -81818,7 +81821,7 @@
         <v>-87.8</v>
       </c>
       <c r="M1469" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="1470" spans="1:13" x14ac:dyDescent="0.25">
@@ -81859,7 +81862,7 @@
         <v>-94.7</v>
       </c>
       <c r="M1470" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="1471" spans="1:13" x14ac:dyDescent="0.25">
@@ -81900,7 +81903,7 @@
         <v>-95.6</v>
       </c>
       <c r="M1471" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="1472" spans="1:13" x14ac:dyDescent="0.25">
@@ -81941,7 +81944,7 @@
         <v>-91.6</v>
       </c>
       <c r="M1472" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="1473" spans="1:13" x14ac:dyDescent="0.25">
@@ -81982,7 +81985,7 @@
         <v>-92.7</v>
       </c>
       <c r="M1473" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="1474" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -82056,7 +82059,7 @@
         <v>-56</v>
       </c>
       <c r="M1475" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="1476" spans="1:13" x14ac:dyDescent="0.25">
@@ -82097,7 +82100,7 @@
         <v>-81.2</v>
       </c>
       <c r="M1476" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="1477" spans="1:13" x14ac:dyDescent="0.25">
@@ -82138,7 +82141,7 @@
         <v>-92.8</v>
       </c>
       <c r="M1477" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="1478" spans="1:13" x14ac:dyDescent="0.25">
@@ -82179,7 +82182,7 @@
         <v>-96.7</v>
       </c>
       <c r="M1478" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="1479" spans="1:13" x14ac:dyDescent="0.25">
@@ -82220,7 +82223,7 @@
         <v>-97.5</v>
       </c>
       <c r="M1479" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1480" spans="1:13" x14ac:dyDescent="0.25">
@@ -82261,7 +82264,7 @@
         <v>-95</v>
       </c>
       <c r="M1480" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="1481" spans="1:13" x14ac:dyDescent="0.25">
@@ -82302,7 +82305,7 @@
         <v>-94.7</v>
       </c>
       <c r="M1481" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="1482" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -82417,7 +82420,7 @@
         <v>-82.7</v>
       </c>
       <c r="M1484" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="1485" spans="1:13" x14ac:dyDescent="0.25">
@@ -82458,7 +82461,7 @@
         <v>-93.3</v>
       </c>
       <c r="M1485" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="1486" spans="1:13" x14ac:dyDescent="0.25">
@@ -82499,7 +82502,7 @@
         <v>-96</v>
       </c>
       <c r="M1486" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="1487" spans="1:13" x14ac:dyDescent="0.25">
@@ -82540,7 +82543,7 @@
         <v>-96.6</v>
       </c>
       <c r="M1487" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="1488" spans="1:13" x14ac:dyDescent="0.25">
@@ -82581,7 +82584,7 @@
         <v>-94.8</v>
       </c>
       <c r="M1488" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1489" spans="1:13" x14ac:dyDescent="0.25">
@@ -82622,7 +82625,7 @@
         <v>-94.1</v>
       </c>
       <c r="M1489" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="1490" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -82696,7 +82699,7 @@
         <v>-44</v>
       </c>
       <c r="M1491" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="1492" spans="1:13" x14ac:dyDescent="0.25">
@@ -82737,7 +82740,7 @@
         <v>-68.6</v>
       </c>
       <c r="M1492" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1493" spans="1:13" x14ac:dyDescent="0.25">
@@ -82778,7 +82781,7 @@
         <v>-83.1</v>
       </c>
       <c r="M1493" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1494" spans="1:13" x14ac:dyDescent="0.25">
@@ -82819,7 +82822,7 @@
         <v>-88.2</v>
       </c>
       <c r="M1494" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1495" spans="1:13" x14ac:dyDescent="0.25">
@@ -82860,7 +82863,7 @@
         <v>-90.2</v>
       </c>
       <c r="M1495" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1496" spans="1:13" x14ac:dyDescent="0.25">
@@ -82901,7 +82904,7 @@
         <v>-85.5</v>
       </c>
       <c r="M1496" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1497" spans="1:13" x14ac:dyDescent="0.25">
@@ -82942,7 +82945,7 @@
         <v>-84.6</v>
       </c>
       <c r="M1497" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1498" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -83016,7 +83019,7 @@
         <v>-53.6</v>
       </c>
       <c r="M1499" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="1500" spans="1:13" x14ac:dyDescent="0.25">
@@ -83057,7 +83060,7 @@
         <v>-80.7</v>
       </c>
       <c r="M1500" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="1501" spans="1:13" x14ac:dyDescent="0.25">
@@ -83098,7 +83101,7 @@
         <v>-92.5</v>
       </c>
       <c r="M1501" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="1502" spans="1:13" x14ac:dyDescent="0.25">
@@ -83139,7 +83142,7 @@
         <v>-95.9</v>
       </c>
       <c r="M1502" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="1503" spans="1:13" x14ac:dyDescent="0.25">
@@ -83180,7 +83183,7 @@
         <v>-96.9</v>
       </c>
       <c r="M1503" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="1504" spans="1:13" x14ac:dyDescent="0.25">
@@ -83221,7 +83224,7 @@
         <v>-93.8</v>
       </c>
       <c r="M1504" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="1505" spans="1:13" x14ac:dyDescent="0.25">
@@ -83262,7 +83265,7 @@
         <v>-93.9</v>
       </c>
       <c r="M1505" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="1506" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -83377,7 +83380,7 @@
         <v>-68.9</v>
       </c>
       <c r="M1508" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="1509" spans="1:13" x14ac:dyDescent="0.25">
@@ -83418,7 +83421,7 @@
         <v>-80.6</v>
       </c>
       <c r="M1509" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="1510" spans="1:13" x14ac:dyDescent="0.25">
@@ -83459,7 +83462,7 @@
         <v>-89.2</v>
       </c>
       <c r="M1510" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="1511" spans="1:13" x14ac:dyDescent="0.25">
@@ -83500,7 +83503,7 @@
         <v>-92.3</v>
       </c>
       <c r="M1511" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="1512" spans="1:13" x14ac:dyDescent="0.25">
@@ -83541,7 +83544,7 @@
         <v>-86.8</v>
       </c>
       <c r="M1512" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="1513" spans="1:13" x14ac:dyDescent="0.25">
@@ -83582,7 +83585,7 @@
         <v>-87.4</v>
       </c>
       <c r="M1513" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="1514" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -83656,7 +83659,7 @@
         <v>-47.9</v>
       </c>
       <c r="M1515" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="1516" spans="1:13" x14ac:dyDescent="0.25">
@@ -83697,7 +83700,7 @@
         <v>-70.7</v>
       </c>
       <c r="M1516" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="1517" spans="1:13" x14ac:dyDescent="0.25">
@@ -83738,7 +83741,7 @@
         <v>-86.5</v>
       </c>
       <c r="M1517" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="1518" spans="1:13" x14ac:dyDescent="0.25">
@@ -83779,7 +83782,7 @@
         <v>-92.6</v>
       </c>
       <c r="M1518" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="1519" spans="1:13" x14ac:dyDescent="0.25">
@@ -83820,7 +83823,7 @@
         <v>-93.8</v>
       </c>
       <c r="M1519" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="1520" spans="1:13" x14ac:dyDescent="0.25">
@@ -83861,7 +83864,7 @@
         <v>-89.6</v>
       </c>
       <c r="M1520" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="1521" spans="1:13" x14ac:dyDescent="0.25">
@@ -83902,7 +83905,7 @@
         <v>-91</v>
       </c>
       <c r="M1521" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="1522" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -83976,7 +83979,7 @@
         <v>-42.9</v>
       </c>
       <c r="M1523" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="1524" spans="1:13" x14ac:dyDescent="0.25">
@@ -84017,7 +84020,7 @@
         <v>-66</v>
       </c>
       <c r="M1524" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="1525" spans="1:13" x14ac:dyDescent="0.25">
@@ -84058,7 +84061,7 @@
         <v>-81.2</v>
       </c>
       <c r="M1525" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="1526" spans="1:13" x14ac:dyDescent="0.25">
@@ -84099,7 +84102,7 @@
         <v>-88.2</v>
       </c>
       <c r="M1526" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="1527" spans="1:13" x14ac:dyDescent="0.25">
@@ -84140,7 +84143,7 @@
         <v>-91.6</v>
       </c>
       <c r="M1527" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="1528" spans="1:13" x14ac:dyDescent="0.25">
@@ -84181,7 +84184,7 @@
         <v>-84.6</v>
       </c>
       <c r="M1528" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="1529" spans="1:13" x14ac:dyDescent="0.25">
@@ -84222,7 +84225,7 @@
         <v>-87.7</v>
       </c>
       <c r="M1529" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="1530" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -84337,7 +84340,7 @@
         <v>-67.4</v>
       </c>
       <c r="M1532" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="1533" spans="1:13" x14ac:dyDescent="0.25">
@@ -84378,7 +84381,7 @@
         <v>-79.7</v>
       </c>
       <c r="M1533" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="1534" spans="1:13" x14ac:dyDescent="0.25">
@@ -84419,7 +84422,7 @@
         <v>-87.5</v>
       </c>
       <c r="M1534" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="1535" spans="1:13" x14ac:dyDescent="0.25">
@@ -84460,7 +84463,7 @@
         <v>-92.8</v>
       </c>
       <c r="M1535" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="1536" spans="1:13" x14ac:dyDescent="0.25">
@@ -84501,7 +84504,7 @@
         <v>-83.3</v>
       </c>
       <c r="M1536" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="1537" spans="1:13" x14ac:dyDescent="0.25">
@@ -84542,7 +84545,7 @@
         <v>-85.6</v>
       </c>
       <c r="M1537" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="1538" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -84616,7 +84619,7 @@
         <v>-46</v>
       </c>
       <c r="M1539" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="1540" spans="1:13" x14ac:dyDescent="0.25">
@@ -84657,7 +84660,7 @@
         <v>-66.9</v>
       </c>
       <c r="M1540" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1541" spans="1:13" x14ac:dyDescent="0.25">
@@ -84698,7 +84701,7 @@
         <v>-80.8</v>
       </c>
       <c r="M1541" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="1542" spans="1:13" x14ac:dyDescent="0.25">
@@ -84739,7 +84742,7 @@
         <v>-86.8</v>
       </c>
       <c r="M1542" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="1543" spans="1:13" x14ac:dyDescent="0.25">
@@ -84780,7 +84783,7 @@
         <v>-93.6</v>
       </c>
       <c r="M1543" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="1544" spans="1:13" x14ac:dyDescent="0.25">
@@ -84821,7 +84824,7 @@
         <v>-87.9</v>
       </c>
       <c r="M1544" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="1545" spans="1:13" x14ac:dyDescent="0.25">
@@ -84862,7 +84865,7 @@
         <v>-89.9</v>
       </c>
       <c r="M1545" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="1546" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -84936,7 +84939,7 @@
         <v>-45.3</v>
       </c>
       <c r="M1547" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="1548" spans="1:13" x14ac:dyDescent="0.25">
@@ -84977,7 +84980,7 @@
         <v>-69.7</v>
       </c>
       <c r="M1548" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="1549" spans="1:13" x14ac:dyDescent="0.25">
@@ -85018,7 +85021,7 @@
         <v>-84.1</v>
       </c>
       <c r="M1549" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="1550" spans="1:13" x14ac:dyDescent="0.25">
@@ -85059,7 +85062,7 @@
         <v>-92.1</v>
       </c>
       <c r="M1550" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="1551" spans="1:13" x14ac:dyDescent="0.25">
@@ -85100,7 +85103,7 @@
         <v>-95.2</v>
       </c>
       <c r="M1551" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="1552" spans="1:13" x14ac:dyDescent="0.25">
@@ -85141,7 +85144,7 @@
         <v>-91.4</v>
       </c>
       <c r="M1552" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="1553" spans="1:13" x14ac:dyDescent="0.25">
@@ -85182,7 +85185,7 @@
         <v>-91.9</v>
       </c>
       <c r="M1553" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="1554" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -85256,7 +85259,7 @@
         <v>-53</v>
       </c>
       <c r="M1555" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1556" spans="1:13" x14ac:dyDescent="0.25">
@@ -85297,7 +85300,7 @@
         <v>-77.2</v>
       </c>
       <c r="M1556" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="1557" spans="1:13" x14ac:dyDescent="0.25">
@@ -85338,7 +85341,7 @@
         <v>-88.4</v>
       </c>
       <c r="M1557" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="1558" spans="1:13" x14ac:dyDescent="0.25">
@@ -85379,7 +85382,7 @@
         <v>-94.5</v>
       </c>
       <c r="M1558" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="1559" spans="1:13" x14ac:dyDescent="0.25">
@@ -85420,7 +85423,7 @@
         <v>-95.6</v>
       </c>
       <c r="M1559" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="1560" spans="1:13" x14ac:dyDescent="0.25">
@@ -85461,7 +85464,7 @@
         <v>-91.7</v>
       </c>
       <c r="M1560" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="1561" spans="1:13" x14ac:dyDescent="0.25">
@@ -85502,7 +85505,7 @@
         <v>-91.1</v>
       </c>
       <c r="M1561" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
   </sheetData>
@@ -85523,17 +85526,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="B4">
         <v>149</v>
@@ -85541,7 +85544,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="B5">
         <v>149</v>
@@ -85549,67 +85552,67 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="B6" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="B7" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="B8" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="11" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="B12" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="B13" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="B17">
         <v>149</v>
@@ -85617,68 +85620,68 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="B18" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="B19" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="B20" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -85692,22 +85695,22 @@
         <v>21</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -85715,25 +85718,25 @@
         <v>433</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -85744,22 +85747,22 @@
         <v>452</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -85773,22 +85776,22 @@
         <v>423</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -85802,28 +85805,28 @@
         <v>438</v>
       </c>
       <c r="B29" s="21" t="s">
+        <v>2465</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>2468</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>2469</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>2470</v>
+      </c>
+      <c r="I29" s="21" t="s">
         <v>2464</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>2465</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>2456</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>2466</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>2467</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>2468</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>2463</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -85834,25 +85837,25 @@
         <v>21</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -85860,28 +85863,28 @@
         <v>522</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -85889,33 +85892,33 @@
         <v>634</v>
       </c>
       <c r="B32" s="21" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>2469</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>2469</v>
+      </c>
+      <c r="H32" s="21" t="s">
         <v>2480</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>2469</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>2440</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>2468</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>2468</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>2479</v>
-      </c>
       <c r="I32" s="21" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
     </row>
   </sheetData>
@@ -85940,40 +85943,40 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="B5">
         <v>149</v>
@@ -85996,7 +85999,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="B6">
         <v>149</v>
@@ -86019,7 +86022,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="B7">
         <v>149</v>
@@ -86042,7 +86045,7 @@
     </row>
     <row r="9" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -86062,25 +86065,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -91747,7 +91750,7 @@
     </row>
     <row r="161" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="19" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -91755,22 +91758,22 @@
         <v>0</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -92046,7 +92049,7 @@
         <v>1000</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>441</v>
@@ -92064,12 +92067,12 @@
         <v>438</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="B2">
         <v>341</v>
@@ -92095,7 +92098,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="B3">
         <v>340</v>
@@ -92121,7 +92124,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="B4">
         <v>331</v>
@@ -92147,7 +92150,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="B5">
         <v>323</v>
@@ -92173,7 +92176,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="B6">
         <v>315</v>
@@ -92199,7 +92202,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="B7">
         <v>296</v>
@@ -92225,7 +92228,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="B8">
         <v>285</v>
@@ -92251,7 +92254,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="B9">
         <v>264</v>
@@ -92277,7 +92280,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="B10">
         <v>244</v>
@@ -92303,7 +92306,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="B11">
         <v>221</v>
@@ -92343,12 +92346,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -92359,18 +92362,18 @@
         <v>1001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>441</v>
@@ -92379,7 +92382,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="E5" s="23">
         <v>11</v>
@@ -92387,7 +92390,7 @@
     </row>
     <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>433</v>
@@ -92396,7 +92399,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="E6" s="23">
         <v>57</v>
@@ -92404,7 +92407,7 @@
     </row>
     <row r="8" spans="1:1" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -92427,12 +92430,12 @@
         <v>438</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
@@ -92455,7 +92458,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -92478,7 +92481,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="B12" s="3">
         <v>6</v>
@@ -92501,7 +92504,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -92524,7 +92527,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="B14" s="3">
         <v>4</v>
@@ -92547,7 +92550,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -92570,7 +92573,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
@@ -92593,7 +92596,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="B17" s="3">
         <v>9</v>
@@ -92616,7 +92619,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="B18" s="31">
         <v>34</v>
@@ -92639,7 +92642,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="B19" s="3">
         <v>10</v>
@@ -92676,7 +92679,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -92686,62 +92689,62 @@
     </row>
     <row r="3" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -92751,82 +92754,82 @@
     </row>
     <row r="16" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -92836,22 +92839,22 @@
     </row>
     <row r="33" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
@@ -92861,27 +92864,27 @@
     </row>
     <row r="38" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -92891,12 +92894,12 @@
     </row>
     <row r="44" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩进球数预测.xlsx
+++ b/docs/excel/竞彩进球数预测.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15389" uniqueCount="2570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15389" uniqueCount="2571">
   <si>
     <t>日期</t>
   </si>
@@ -2783,7 +2783,7 @@
     <t>3球 @3.8 ⚡</t>
   </si>
   <si>
-    <t>10-16 13:00</t>
+    <t>10-16 14:00</t>
   </si>
   <si>
     <t>科特布斯</t>
@@ -2795,183 +2795,183 @@
     <t>10-17 00:30</t>
   </si>
   <si>
+    <t>0球 @36</t>
+  </si>
+  <si>
+    <t>3球 @3.85 ⚡</t>
+  </si>
+  <si>
+    <t>布鲁马波</t>
+  </si>
+  <si>
+    <t>佐加顿斯</t>
+  </si>
+  <si>
+    <t>10-17 01:00</t>
+  </si>
+  <si>
+    <t>3球 @3.5 ⚡</t>
+  </si>
+  <si>
+    <t>SBV精英</t>
+  </si>
+  <si>
+    <t>10-17 02:00</t>
+  </si>
+  <si>
+    <t>2球 @4.3</t>
+  </si>
+  <si>
+    <t>3球 @3.7 ⚡</t>
+  </si>
+  <si>
+    <t>奥斯</t>
+  </si>
+  <si>
+    <t>4球 @4.15 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 02:30</t>
+  </si>
+  <si>
+    <t>10-17 02:45</t>
+  </si>
+  <si>
+    <t>7+球 @11.5</t>
+  </si>
+  <si>
+    <t>3球 @3.55 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @4.4 ⚡</t>
+  </si>
+  <si>
+    <t>勒芒</t>
+  </si>
+  <si>
+    <t>伯恩利</t>
+  </si>
+  <si>
+    <t>10-17 03:00</t>
+  </si>
+  <si>
+    <t>3球 @3.45 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.65 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @5.8 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 07:00</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>麦克阿瑟</t>
+  </si>
+  <si>
+    <t>珀斯</t>
+  </si>
+  <si>
+    <t>10-17 14:00</t>
+  </si>
+  <si>
+    <t>鹿岛鹿角</t>
+  </si>
+  <si>
+    <t>长崎航海</t>
+  </si>
+  <si>
+    <t>6球 @15</t>
+  </si>
+  <si>
+    <t>3球 @3.4 ⚡</t>
+  </si>
+  <si>
+    <t>富川FC</t>
+  </si>
+  <si>
+    <t>10-17 15:30</t>
+  </si>
+  <si>
+    <t>中央海岸</t>
+  </si>
+  <si>
+    <t>10-17 16:40</t>
+  </si>
+  <si>
+    <t>10-17 18:00</t>
+  </si>
+  <si>
+    <t>宫崎牛鸟</t>
+  </si>
+  <si>
+    <t>磐田喜悦</t>
+  </si>
+  <si>
+    <t>10-17 19:30</t>
+  </si>
+  <si>
+    <t>4球 @4.7 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 20:00</t>
+  </si>
+  <si>
+    <t>10-17 21:00</t>
+  </si>
+  <si>
+    <t>10-17 21:30</t>
+  </si>
+  <si>
+    <t>7+球 @19</t>
+  </si>
+  <si>
+    <t>3球 @3.6 ⚡</t>
+  </si>
+  <si>
+    <t>4球 @4.3 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 22:00</t>
+  </si>
+  <si>
+    <t>4球 @4.1 ⚡</t>
+  </si>
+  <si>
+    <t>3球 @3.75 ⚡</t>
+  </si>
+  <si>
+    <t>10-17 22:15</t>
+  </si>
+  <si>
+    <t>10-17 23:15</t>
+  </si>
+  <si>
+    <t>10-18 00:00</t>
+  </si>
+  <si>
+    <t>6球 @13</t>
+  </si>
+  <si>
+    <t>10-18 00:30</t>
+  </si>
+  <si>
+    <t>6球 @5.8</t>
+  </si>
+  <si>
+    <t>3球 @4.9 ⚡</t>
+  </si>
+  <si>
     <t>5球 @5.1 ⚡</t>
   </si>
   <si>
-    <t>3球 @3.85 ⚡</t>
-  </si>
-  <si>
-    <t>布鲁马波</t>
-  </si>
-  <si>
-    <t>佐加顿斯</t>
-  </si>
-  <si>
-    <t>10-17 01:00</t>
-  </si>
-  <si>
-    <t>3球 @3.5 ⚡</t>
-  </si>
-  <si>
-    <t>10-16 12:00</t>
-  </si>
-  <si>
-    <t>SBV精英</t>
-  </si>
-  <si>
-    <t>10-17 02:00</t>
-  </si>
-  <si>
-    <t>6球 @9.8</t>
-  </si>
-  <si>
-    <t>3球 @3.7 ⚡</t>
-  </si>
-  <si>
-    <t>奥斯</t>
-  </si>
-  <si>
-    <t>4球 @4.15 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 02:30</t>
-  </si>
-  <si>
-    <t>10-17 02:45</t>
-  </si>
-  <si>
-    <t>6球 @10.5</t>
-  </si>
-  <si>
-    <t>3球 @3.55 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @4.5 ⚡</t>
-  </si>
-  <si>
-    <t>勒芒</t>
-  </si>
-  <si>
-    <t>伯恩利</t>
-  </si>
-  <si>
-    <t>10-17 03:00</t>
-  </si>
-  <si>
-    <t>3球 @3.45 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.65 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @5.8 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 07:00</t>
-  </si>
-  <si>
-    <t>2026-10-17</t>
-  </si>
-  <si>
-    <t>麦克阿瑟</t>
-  </si>
-  <si>
-    <t>珀斯</t>
-  </si>
-  <si>
-    <t>10-17 14:00</t>
-  </si>
-  <si>
-    <t>鹿岛鹿角</t>
-  </si>
-  <si>
-    <t>长崎航海</t>
-  </si>
-  <si>
-    <t>6球 @15</t>
-  </si>
-  <si>
-    <t>3球 @3.4 ⚡</t>
-  </si>
-  <si>
-    <t>富川FC</t>
-  </si>
-  <si>
-    <t>10-17 15:30</t>
-  </si>
-  <si>
-    <t>中央海岸</t>
-  </si>
-  <si>
-    <t>10-17 16:40</t>
-  </si>
-  <si>
-    <t>10-17 18:00</t>
-  </si>
-  <si>
-    <t>宫崎牛鸟</t>
-  </si>
-  <si>
-    <t>磐田喜悦</t>
-  </si>
-  <si>
-    <t>10-17 19:30</t>
-  </si>
-  <si>
-    <t>4球 @4.7 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 20:00</t>
-  </si>
-  <si>
-    <t>10-17 21:00</t>
-  </si>
-  <si>
-    <t>10-17 21:30</t>
-  </si>
-  <si>
-    <t>7+球 @19</t>
-  </si>
-  <si>
-    <t>3球 @3.6 ⚡</t>
-  </si>
-  <si>
-    <t>4球 @4.3 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 22:00</t>
-  </si>
-  <si>
-    <t>4球 @4.1 ⚡</t>
-  </si>
-  <si>
-    <t>3球 @3.75 ⚡</t>
-  </si>
-  <si>
-    <t>10-17 22:15</t>
-  </si>
-  <si>
-    <t>10-17 23:15</t>
-  </si>
-  <si>
-    <t>10-18 00:00</t>
-  </si>
-  <si>
-    <t>6球 @13</t>
-  </si>
-  <si>
-    <t>10-18 00:30</t>
-  </si>
-  <si>
-    <t>6球 @5.8</t>
-  </si>
-  <si>
-    <t>3球 @4.9 ⚡</t>
-  </si>
-  <si>
     <t>特尔斯达</t>
   </si>
   <si>
@@ -6347,25 +6347,25 @@
     <t>2:5=175 5:2=125 负其他=55 平其他=100 胜其他=40</t>
   </si>
   <si>
-    <t>0:1=16 1:0=22</t>
-  </si>
-  <si>
-    <t>0:2=15 1:1=10 2:0=24</t>
-  </si>
-  <si>
-    <t>0:3=21 1:2=7.7 2:1=11 3:0=38</t>
-  </si>
-  <si>
-    <t>0:4=32 1:3=11.5 2:2=10 3:1=20 4:0=90</t>
-  </si>
-  <si>
-    <t>0:5=90 1:4=22 2:3=12 3:2=18 4:1=55 5:0=250</t>
-  </si>
-  <si>
-    <t>1:5=50 2:4=25 3:3=23 4:2=48 5:1=120</t>
-  </si>
-  <si>
-    <t>2:5=55 5:2=120 负其他=15 平其他=90 胜其他=27</t>
+    <t>0:1=16 1:0=24</t>
+  </si>
+  <si>
+    <t>0:2=13.5 1:1=10 2:0=28</t>
+  </si>
+  <si>
+    <t>0:3=19 1:2=7.5 2:1=12 3:0=42</t>
+  </si>
+  <si>
+    <t>0:4=30 1:3=10.5 2:2=10.5 3:1=23 4:0=90</t>
+  </si>
+  <si>
+    <t>0:5=70 1:4=20 2:3=12 3:2=19 4:1=60 5:0=250</t>
+  </si>
+  <si>
+    <t>1:5=45 2:4=23 3:3=24 4:2=50 5:1=120</t>
+  </si>
+  <si>
+    <t>2:5=50 5:2=120 负其他=15 平其他=90 胜其他=30</t>
   </si>
   <si>
     <t>0:1=9 1:0=19</t>
@@ -6389,22 +6389,25 @@
     <t>2:5=75 5:2=400 负其他=19 平其他=250 胜其他=100</t>
   </si>
   <si>
-    <t>0:2=29 1:1=8.5 2:0=10</t>
-  </si>
-  <si>
-    <t>0:3=60 1:2=13 2:1=7.2 3:0=13</t>
+    <t>0:1=20 1:0=11</t>
+  </si>
+  <si>
+    <t>0:2=31 1:1=8.7 2:0=10</t>
+  </si>
+  <si>
+    <t>0:3=60 1:2=13.5 2:1=7.2 3:0=13</t>
   </si>
   <si>
     <t>0:4=180 1:3=30 2:2=11 3:1=10.5 4:0=23</t>
   </si>
   <si>
-    <t>0:5=500 1:4=85 2:3=25 3:2=14 4:1=19 5:0=50</t>
-  </si>
-  <si>
-    <t>1:5=350 2:4=80 3:3=33 4:2=29 5:1=50</t>
-  </si>
-  <si>
-    <t>2:5=250 5:2=60 负其他=65 平其他=150 胜其他=18</t>
+    <t>0:5=500 1:4=85 2:3=25 3:2=14 4:1=19 5:0=45</t>
+  </si>
+  <si>
+    <t>1:5=350 2:4=80 3:3=33 4:2=27 5:1=45</t>
+  </si>
+  <si>
+    <t>2:5=250 5:2=60 负其他=65 平其他=150 胜其他=17</t>
   </si>
   <si>
     <t>0:1=20 1:0=12</t>
@@ -6449,25 +6452,25 @@
     <t>2:5=175 5:2=80 负其他=40 平其他=100 胜其他=19</t>
   </si>
   <si>
-    <t>0:1=12.5 1:0=12</t>
-  </si>
-  <si>
-    <t>0:2=15 1:1=7.25 2:0=14</t>
-  </si>
-  <si>
-    <t>0:3=26 1:2=8.5 2:1=8.25 3:0=25</t>
-  </si>
-  <si>
-    <t>0:4=65 1:3=17 2:2=10 3:1=16 4:0=60</t>
-  </si>
-  <si>
-    <t>0:5=175 1:4=35 2:3=18 3:2=17 4:1=35 5:0=175</t>
-  </si>
-  <si>
-    <t>1:5=100 2:4=50 3:3=30 4:2=50 5:1=100</t>
-  </si>
-  <si>
-    <t>2:5=150 5:2=150 负其他=35 平其他=150 胜其他=35</t>
+    <t>0:1=14.5 1:0=12.5</t>
+  </si>
+  <si>
+    <t>0:2=18 1:1=7.5 2:0=15</t>
+  </si>
+  <si>
+    <t>0:3=27 1:2=8.5 2:1=8.25 3:0=23</t>
+  </si>
+  <si>
+    <t>0:4=60 1:3=18 2:2=9.5 3:1=15 4:0=55</t>
+  </si>
+  <si>
+    <t>0:5=150 1:4=33 2:3=19 3:2=16 4:1=33 5:0=150</t>
+  </si>
+  <si>
+    <t>1:5=90 2:4=45 3:3=26 4:2=45 5:1=90</t>
+  </si>
+  <si>
+    <t>2:5=120 5:2=120 负其他=32 平其他=120 胜其他=32</t>
   </si>
   <si>
     <t>0:1=10 1:0=12</t>
@@ -6533,13 +6536,13 @@
     <t>0:1=10 1:0=7.75</t>
   </si>
   <si>
-    <t>0:2=15 1:1=5.85 2:0=11</t>
-  </si>
-  <si>
-    <t>0:3=33 1:2=9.5 2:1=7.25 3:0=21</t>
-  </si>
-  <si>
-    <t>0:4=95 1:3=23 2:2=12.5 3:1=15 4:0=40</t>
+    <t>0:2=16 1:1=5.85 2:0=11</t>
+  </si>
+  <si>
+    <t>0:3=35 1:2=10 2:1=6.75 3:0=21</t>
+  </si>
+  <si>
+    <t>0:4=95 1:3=25 2:2=12.5 3:1=14 4:0=40</t>
   </si>
   <si>
     <t>0:5=300 1:4=70 2:3=32 3:2=24 4:1=40 5:0=125</t>
@@ -7241,7 +7244,7 @@
     <t>2:5=150 5:2=750 负其他=45 平其他=500 胜其他=250</t>
   </si>
   <si>
-    <t>进球数预测 · 模型统计（截至 2026-10-16T13:00:03+08:00）</t>
+    <t>进球数预测 · 模型统计（截至 2026-10-16T14:00:04+08:00）</t>
   </si>
   <si>
     <t>总体</t>
@@ -21000,10 +21003,10 @@
         <v>21</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>636</v>
+        <v>925</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>926</v>
@@ -21062,7 +21065,7 @@
         <v>21</v>
       </c>
       <c r="N154" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O154" t="s">
         <v>21</v>
@@ -21082,10 +21085,10 @@
         <v>568</v>
       </c>
       <c r="E155" t="s">
+        <v>931</v>
+      </c>
+      <c r="F155" t="s">
         <v>932</v>
-      </c>
-      <c r="F155" t="s">
-        <v>933</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>55</v>
@@ -21094,13 +21097,13 @@
         <v>21</v>
       </c>
       <c r="I155" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="J155" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="J155" s="3" t="s">
-        <v>935</v>
-      </c>
       <c r="K155" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L155" t="s">
         <v>21</v>
@@ -21109,7 +21112,7 @@
         <v>21</v>
       </c>
       <c r="N155" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O155" t="s">
         <v>21</v>
@@ -21129,10 +21132,10 @@
         <v>363</v>
       </c>
       <c r="E156" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F156" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>55</v>
@@ -21144,10 +21147,10 @@
         <v>432</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="L156" t="s">
         <v>21</v>
@@ -21179,7 +21182,7 @@
         <v>747</v>
       </c>
       <c r="F157" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>70</v>
@@ -21191,10 +21194,10 @@
         <v>904</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="L157" t="s">
         <v>21</v>
@@ -21226,7 +21229,7 @@
         <v>758</v>
       </c>
       <c r="F158" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>55</v>
@@ -21235,14 +21238,14 @@
         <v>21</v>
       </c>
       <c r="I158" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="J158" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="J158" s="3" t="s">
+      <c r="K158" s="3" t="s">
         <v>941</v>
       </c>
-      <c r="K158" s="3" t="s">
-        <v>942</v>
-      </c>
       <c r="L158" t="s">
         <v>21</v>
       </c>
@@ -21250,7 +21253,7 @@
         <v>21</v>
       </c>
       <c r="N158" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="O158" t="s">
         <v>21</v>
@@ -21267,13 +21270,13 @@
         <v>101</v>
       </c>
       <c r="D159" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E159" t="s">
         <v>693</v>
       </c>
       <c r="F159" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>55</v>
@@ -21314,13 +21317,13 @@
         <v>46</v>
       </c>
       <c r="D160" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E160" t="s">
         <v>47</v>
       </c>
       <c r="F160" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>55</v>
@@ -21332,11 +21335,11 @@
         <v>610</v>
       </c>
       <c r="J160" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="K160" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="K160" s="3" t="s">
-        <v>947</v>
-      </c>
       <c r="L160" t="s">
         <v>21</v>
       </c>
@@ -21344,7 +21347,7 @@
         <v>21</v>
       </c>
       <c r="N160" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="O160" t="s">
         <v>21</v>
@@ -21367,7 +21370,7 @@
         <v>118</v>
       </c>
       <c r="F161" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>55</v>
@@ -21379,11 +21382,11 @@
         <v>623</v>
       </c>
       <c r="J161" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K161" s="3" t="s">
         <v>948</v>
       </c>
-      <c r="K161" s="3" t="s">
-        <v>949</v>
-      </c>
       <c r="L161" t="s">
         <v>21</v>
       </c>
@@ -21391,7 +21394,7 @@
         <v>21</v>
       </c>
       <c r="N161" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="O161" t="s">
         <v>21</v>
@@ -21414,7 +21417,7 @@
         <v>494</v>
       </c>
       <c r="F162" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>55</v>
@@ -21426,10 +21429,10 @@
         <v>424</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K162" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L162" t="s">
         <v>21</v>
@@ -21438,7 +21441,7 @@
         <v>21</v>
       </c>
       <c r="N162" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O162" t="s">
         <v>21</v>
@@ -21446,7 +21449,7 @@
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B163" t="s">
         <v>268</v>
@@ -21455,13 +21458,13 @@
         <v>916</v>
       </c>
       <c r="D163" t="s">
+        <v>951</v>
+      </c>
+      <c r="E163" t="s">
         <v>952</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>953</v>
-      </c>
-      <c r="F163" t="s">
-        <v>954</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>55</v>
@@ -21485,7 +21488,7 @@
         <v>21</v>
       </c>
       <c r="N163" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O163" t="s">
         <v>21</v>
@@ -21493,7 +21496,7 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B164" t="s">
         <v>271</v>
@@ -21502,13 +21505,13 @@
         <v>24</v>
       </c>
       <c r="D164" t="s">
+        <v>954</v>
+      </c>
+      <c r="E164" t="s">
         <v>955</v>
       </c>
-      <c r="E164" t="s">
-        <v>956</v>
-      </c>
       <c r="F164" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>55</v>
@@ -21517,13 +21520,13 @@
         <v>21</v>
       </c>
       <c r="I164" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="J164" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="J164" s="3" t="s">
-        <v>958</v>
-      </c>
       <c r="K164" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L164" t="s">
         <v>21</v>
@@ -21532,7 +21535,7 @@
         <v>21</v>
       </c>
       <c r="N164" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O164" t="s">
         <v>21</v>
@@ -21540,7 +21543,7 @@
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B165" t="s">
         <v>276</v>
@@ -21552,10 +21555,10 @@
         <v>707</v>
       </c>
       <c r="E165" t="s">
+        <v>958</v>
+      </c>
+      <c r="F165" t="s">
         <v>959</v>
-      </c>
-      <c r="F165" t="s">
-        <v>960</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>70</v>
@@ -21564,13 +21567,13 @@
         <v>21</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L165" t="s">
         <v>21</v>
@@ -21579,7 +21582,7 @@
         <v>21</v>
       </c>
       <c r="N165" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O165" t="s">
         <v>21</v>
@@ -21587,7 +21590,7 @@
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B166" t="s">
         <v>279</v>
@@ -21596,13 +21599,13 @@
         <v>916</v>
       </c>
       <c r="D166" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E166" t="s">
         <v>812</v>
       </c>
       <c r="F166" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>55</v>
@@ -21626,7 +21629,7 @@
         <v>21</v>
       </c>
       <c r="N166" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O166" t="s">
         <v>21</v>
@@ -21634,7 +21637,7 @@
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B167" t="s">
         <v>282</v>
@@ -21649,7 +21652,7 @@
         <v>713</v>
       </c>
       <c r="F167" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>55</v>
@@ -21661,10 +21664,10 @@
         <v>564</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L167" t="s">
         <v>21</v>
@@ -21673,7 +21676,7 @@
         <v>21</v>
       </c>
       <c r="N167" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O167" t="s">
         <v>21</v>
@@ -21681,7 +21684,7 @@
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B168" t="s">
         <v>285</v>
@@ -21690,13 +21693,13 @@
         <v>272</v>
       </c>
       <c r="D168" t="s">
+        <v>963</v>
+      </c>
+      <c r="E168" t="s">
         <v>964</v>
       </c>
-      <c r="E168" t="s">
-        <v>965</v>
-      </c>
       <c r="F168" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>55</v>
@@ -21720,7 +21723,7 @@
         <v>21</v>
       </c>
       <c r="N168" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O168" t="s">
         <v>21</v>
@@ -21728,7 +21731,7 @@
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B169" t="s">
         <v>288</v>
@@ -21743,7 +21746,7 @@
         <v>646</v>
       </c>
       <c r="F169" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>70</v>
@@ -21755,7 +21758,7 @@
         <v>531</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K169" s="3" t="s">
         <v>930</v>
@@ -21767,7 +21770,7 @@
         <v>21</v>
       </c>
       <c r="N169" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O169" t="s">
         <v>21</v>
@@ -21775,7 +21778,7 @@
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B170" t="s">
         <v>296</v>
@@ -21790,7 +21793,7 @@
         <v>86</v>
       </c>
       <c r="F170" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>55</v>
@@ -21802,10 +21805,10 @@
         <v>601</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L170" t="s">
         <v>21</v>
@@ -21814,7 +21817,7 @@
         <v>21</v>
       </c>
       <c r="N170" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O170" t="s">
         <v>21</v>
@@ -21822,7 +21825,7 @@
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B171" t="s">
         <v>304</v>
@@ -21837,7 +21840,7 @@
         <v>44</v>
       </c>
       <c r="F171" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>55</v>
@@ -21846,13 +21849,13 @@
         <v>21</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="J171" s="3" t="s">
         <v>930</v>
       </c>
       <c r="K171" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="L171" t="s">
         <v>21</v>
@@ -21861,7 +21864,7 @@
         <v>21</v>
       </c>
       <c r="N171" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O171" t="s">
         <v>21</v>
@@ -21869,7 +21872,7 @@
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B172" t="s">
         <v>310</v>
@@ -21884,7 +21887,7 @@
         <v>628</v>
       </c>
       <c r="F172" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>55</v>
@@ -21908,7 +21911,7 @@
         <v>21</v>
       </c>
       <c r="N172" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O172" t="s">
         <v>21</v>
@@ -21916,7 +21919,7 @@
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B173" t="s">
         <v>314</v>
@@ -21931,7 +21934,7 @@
         <v>124</v>
       </c>
       <c r="F173" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>55</v>
@@ -21943,10 +21946,10 @@
         <v>475</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L173" t="s">
         <v>21</v>
@@ -21955,7 +21958,7 @@
         <v>21</v>
       </c>
       <c r="N173" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O173" t="s">
         <v>21</v>
@@ -21963,7 +21966,7 @@
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B174" t="s">
         <v>318</v>
@@ -21978,7 +21981,7 @@
         <v>633</v>
       </c>
       <c r="F174" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>55</v>
@@ -21987,13 +21990,13 @@
         <v>21</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L174" t="s">
         <v>21</v>
@@ -22002,7 +22005,7 @@
         <v>21</v>
       </c>
       <c r="N174" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O174" t="s">
         <v>21</v>
@@ -22010,7 +22013,7 @@
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B175" t="s">
         <v>321</v>
@@ -22025,7 +22028,7 @@
         <v>638</v>
       </c>
       <c r="F175" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>55</v>
@@ -22037,10 +22040,10 @@
         <v>577</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="L175" t="s">
         <v>21</v>
@@ -22049,7 +22052,7 @@
         <v>21</v>
       </c>
       <c r="N175" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O175" t="s">
         <v>21</v>
@@ -22057,7 +22060,7 @@
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B176" t="s">
         <v>324</v>
@@ -22072,7 +22075,7 @@
         <v>574</v>
       </c>
       <c r="F176" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>70</v>
@@ -22084,10 +22087,10 @@
         <v>435</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="K176" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L176" t="s">
         <v>21</v>
@@ -22096,7 +22099,7 @@
         <v>21</v>
       </c>
       <c r="N176" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O176" t="s">
         <v>21</v>
@@ -22104,7 +22107,7 @@
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B177" t="s">
         <v>328</v>
@@ -22119,7 +22122,7 @@
         <v>69</v>
       </c>
       <c r="F177" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>55</v>
@@ -22131,10 +22134,10 @@
         <v>453</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K177" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L177" t="s">
         <v>21</v>
@@ -22143,7 +22146,7 @@
         <v>21</v>
       </c>
       <c r="N177" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O177" t="s">
         <v>21</v>
@@ -22151,7 +22154,7 @@
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B178" t="s">
         <v>332</v>
@@ -22166,7 +22169,7 @@
         <v>643</v>
       </c>
       <c r="F178" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>55</v>
@@ -22178,11 +22181,11 @@
         <v>904</v>
       </c>
       <c r="J178" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="K178" s="3" t="s">
         <v>975</v>
       </c>
-      <c r="K178" s="3" t="s">
-        <v>976</v>
-      </c>
       <c r="L178" t="s">
         <v>21</v>
       </c>
@@ -22190,7 +22193,7 @@
         <v>21</v>
       </c>
       <c r="N178" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O178" t="s">
         <v>21</v>
@@ -22198,7 +22201,7 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B179" t="s">
         <v>336</v>
@@ -22213,7 +22216,7 @@
         <v>738</v>
       </c>
       <c r="F179" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>55</v>
@@ -22225,10 +22228,10 @@
         <v>615</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L179" t="s">
         <v>21</v>
@@ -22237,7 +22240,7 @@
         <v>21</v>
       </c>
       <c r="N179" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O179" t="s">
         <v>21</v>
@@ -22245,7 +22248,7 @@
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B180" t="s">
         <v>339</v>
@@ -22260,7 +22263,7 @@
         <v>728</v>
       </c>
       <c r="F180" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>55</v>
@@ -22272,10 +22275,10 @@
         <v>480</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L180" t="s">
         <v>21</v>
@@ -22284,7 +22287,7 @@
         <v>21</v>
       </c>
       <c r="N180" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O180" t="s">
         <v>21</v>
@@ -22292,7 +22295,7 @@
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B181" t="s">
         <v>343</v>
@@ -22307,7 +22310,7 @@
         <v>133</v>
       </c>
       <c r="F181" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>55</v>
@@ -22331,7 +22334,7 @@
         <v>21</v>
       </c>
       <c r="N181" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O181" t="s">
         <v>21</v>
@@ -22339,7 +22342,7 @@
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B182" t="s">
         <v>346</v>
@@ -22354,7 +22357,7 @@
         <v>661</v>
       </c>
       <c r="F182" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>55</v>
@@ -22363,13 +22366,13 @@
         <v>21</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L182" t="s">
         <v>21</v>
@@ -22378,7 +22381,7 @@
         <v>21</v>
       </c>
       <c r="N182" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O182" t="s">
         <v>21</v>
@@ -22386,7 +22389,7 @@
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B183" t="s">
         <v>349</v>
@@ -22401,7 +22404,7 @@
         <v>647</v>
       </c>
       <c r="F183" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>70</v>
@@ -22425,7 +22428,7 @@
         <v>21</v>
       </c>
       <c r="N183" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O183" t="s">
         <v>21</v>
@@ -22433,7 +22436,7 @@
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B184" t="s">
         <v>353</v>
@@ -22448,22 +22451,22 @@
         <v>83</v>
       </c>
       <c r="F184" t="s">
+        <v>980</v>
+      </c>
+      <c r="G184" t="s">
+        <v>21</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I184" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="G184" t="s">
-        <v>21</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I184" s="3" t="s">
+      <c r="J184" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="J184" s="3" t="s">
-        <v>983</v>
-      </c>
       <c r="K184" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="L184" t="s">
         <v>21</v>
@@ -22472,7 +22475,7 @@
         <v>21</v>
       </c>
       <c r="N184" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O184" t="s">
         <v>21</v>
@@ -22480,7 +22483,7 @@
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B185" t="s">
         <v>686</v>
@@ -22495,7 +22498,7 @@
         <v>670</v>
       </c>
       <c r="F185" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>55</v>
@@ -22507,7 +22510,7 @@
         <v>636</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>925</v>
+        <v>983</v>
       </c>
       <c r="K185" s="3" t="s">
         <v>926</v>
@@ -22519,7 +22522,7 @@
         <v>21</v>
       </c>
       <c r="N185" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O185" t="s">
         <v>21</v>
@@ -22527,7 +22530,7 @@
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B186" t="s">
         <v>689</v>
@@ -22566,7 +22569,7 @@
         <v>21</v>
       </c>
       <c r="N186" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O186" t="s">
         <v>21</v>
@@ -22574,7 +22577,7 @@
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B187" t="s">
         <v>691</v>
@@ -22598,7 +22601,7 @@
         <v>21</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="J187" s="3" t="s">
         <v>930</v>
@@ -22613,7 +22616,7 @@
         <v>21</v>
       </c>
       <c r="N187" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O187" t="s">
         <v>21</v>
@@ -22621,7 +22624,7 @@
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B188" t="s">
         <v>695</v>
@@ -22648,10 +22651,10 @@
         <v>711</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="K188" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="L188" t="s">
         <v>21</v>
@@ -22660,7 +22663,7 @@
         <v>21</v>
       </c>
       <c r="N188" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O188" t="s">
         <v>21</v>
@@ -22695,10 +22698,10 @@
         <v>751</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="K189" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L189" t="s">
         <v>21</v>
@@ -22707,7 +22710,7 @@
         <v>21</v>
       </c>
       <c r="N189" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O189" t="s">
         <v>21</v>
@@ -22742,10 +22745,10 @@
         <v>694</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L190" t="s">
         <v>21</v>
@@ -22754,7 +22757,7 @@
         <v>21</v>
       </c>
       <c r="N190" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O190" t="s">
         <v>21</v>
@@ -22789,10 +22792,10 @@
         <v>623</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="L191" t="s">
         <v>21</v>
@@ -22801,7 +22804,7 @@
         <v>21</v>
       </c>
       <c r="N191" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O191" t="s">
         <v>21</v>
@@ -22833,13 +22836,13 @@
         <v>21</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L192" t="s">
         <v>21</v>
@@ -22848,7 +22851,7 @@
         <v>21</v>
       </c>
       <c r="N192" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O192" t="s">
         <v>21</v>
@@ -22880,13 +22883,13 @@
         <v>21</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="K193" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L193" t="s">
         <v>21</v>
@@ -22895,7 +22898,7 @@
         <v>21</v>
       </c>
       <c r="N193" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O193" t="s">
         <v>21</v>
@@ -22942,7 +22945,7 @@
         <v>21</v>
       </c>
       <c r="N194" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O194" t="s">
         <v>21</v>
@@ -22977,10 +22980,10 @@
         <v>998</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="K195" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L195" t="s">
         <v>21</v>
@@ -22989,7 +22992,7 @@
         <v>21</v>
       </c>
       <c r="N195" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O195" t="s">
         <v>21</v>
@@ -23036,7 +23039,7 @@
         <v>21</v>
       </c>
       <c r="N196" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="O196" t="s">
         <v>21</v>
@@ -71449,7 +71452,7 @@
       </c>
       <c r="G1210" s="9"/>
       <c r="H1210" s="10">
-        <v>0.892</v>
+        <v>0.349</v>
       </c>
       <c r="I1210" s="11"/>
       <c r="J1210" s="8"/>
@@ -71481,22 +71484,22 @@
         <v>10</v>
       </c>
       <c r="G1211" s="13">
-        <v>9.263</v>
+        <v>9.6</v>
       </c>
       <c r="H1211" s="14">
-        <v>0.737</v>
+        <v>0.4</v>
       </c>
       <c r="I1211" s="15">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="J1211" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1211" s="16">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="L1211" s="15">
-        <v>-47.4</v>
+        <v>-50</v>
       </c>
       <c r="M1211" t="s">
         <v>2109</v>
@@ -71522,22 +71525,22 @@
         <v>5.5</v>
       </c>
       <c r="G1212" s="13">
-        <v>4.8</v>
+        <v>4.767</v>
       </c>
       <c r="H1212" s="14">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="I1212" s="15">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="J1212" s="12">
-        <v>16.333</v>
+        <v>17.167</v>
       </c>
       <c r="K1212" s="16">
-        <v>-10.833</v>
+        <v>-11.667</v>
       </c>
       <c r="L1212" s="15">
-        <v>-66.3</v>
+        <v>-68</v>
       </c>
       <c r="M1212" t="s">
         <v>2110</v>
@@ -71563,22 +71566,22 @@
         <v>3.85</v>
       </c>
       <c r="G1213" s="13">
-        <v>3.393</v>
+        <v>3.412</v>
       </c>
       <c r="H1213" s="14">
-        <v>0.457</v>
+        <v>0.438</v>
       </c>
       <c r="I1213" s="15">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="J1213" s="12">
-        <v>19.425</v>
+        <v>20.125</v>
       </c>
       <c r="K1213" s="16">
-        <v>-15.575</v>
+        <v>-16.275</v>
       </c>
       <c r="L1213" s="15">
-        <v>-80.2</v>
+        <v>-80.9</v>
       </c>
       <c r="M1213" t="s">
         <v>2111</v>
@@ -71604,19 +71607,19 @@
         <v>4.2</v>
       </c>
       <c r="G1214" s="13">
-        <v>3.58</v>
+        <v>3.592</v>
       </c>
       <c r="H1214" s="14">
-        <v>0.62</v>
+        <v>0.608</v>
       </c>
       <c r="I1214" s="15">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="J1214" s="12">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="K1214" s="16">
-        <v>-28.5</v>
+        <v>-28.6</v>
       </c>
       <c r="L1214" s="15">
         <v>-87.2</v>
@@ -71645,22 +71648,22 @@
         <v>5.1</v>
       </c>
       <c r="G1215" s="13">
-        <v>4.595</v>
+        <v>4.527</v>
       </c>
       <c r="H1215" s="14">
-        <v>0.505</v>
+        <v>0.573</v>
       </c>
       <c r="I1215" s="15">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="J1215" s="12">
-        <v>74.5</v>
+        <v>71.833</v>
       </c>
       <c r="K1215" s="16">
-        <v>-69.4</v>
+        <v>-66.733</v>
       </c>
       <c r="L1215" s="15">
-        <v>-93.1</v>
+        <v>-92.9</v>
       </c>
       <c r="M1215" t="s">
         <v>2113</v>
@@ -71686,22 +71689,22 @@
         <v>8</v>
       </c>
       <c r="G1216" s="13">
-        <v>7.539</v>
+        <v>7.369</v>
       </c>
       <c r="H1216" s="14">
-        <v>0.461</v>
+        <v>0.631</v>
       </c>
       <c r="I1216" s="15">
-        <v>6.1</v>
+        <v>8.6</v>
       </c>
       <c r="J1216" s="12">
-        <v>53.2</v>
+        <v>52.4</v>
       </c>
       <c r="K1216" s="16">
-        <v>-45.2</v>
+        <v>-44.4</v>
       </c>
       <c r="L1216" s="15">
-        <v>-85</v>
+        <v>-84.7</v>
       </c>
       <c r="M1216" t="s">
         <v>2114</v>
@@ -71727,22 +71730,22 @@
         <v>8</v>
       </c>
       <c r="G1217" s="13">
-        <v>7.076</v>
+        <v>7.171</v>
       </c>
       <c r="H1217" s="14">
-        <v>0.924</v>
+        <v>0.829</v>
       </c>
       <c r="I1217" s="15">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="J1217" s="12">
-        <v>61.4</v>
+        <v>61</v>
       </c>
       <c r="K1217" s="16">
-        <v>-53.4</v>
+        <v>-53</v>
       </c>
       <c r="L1217" s="15">
-        <v>-87</v>
+        <v>-86.9</v>
       </c>
       <c r="M1217" t="s">
         <v>2115</v>
@@ -72079,7 +72082,7 @@
         <v>568</v>
       </c>
       <c r="D1226" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1226" s="4" t="s">
         <v>441</v>
@@ -72089,7 +72092,7 @@
       </c>
       <c r="G1226" s="9"/>
       <c r="H1226" s="10">
-        <v>1.226</v>
+        <v>1.05</v>
       </c>
       <c r="I1226" s="11"/>
       <c r="J1226" s="8"/>
@@ -72112,7 +72115,7 @@
         <v>568</v>
       </c>
       <c r="D1227" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1227" t="s">
         <v>433</v>
@@ -72121,25 +72124,25 @@
         <v>7.7</v>
       </c>
       <c r="G1227" s="13">
-        <v>6.967</v>
+        <v>7.097</v>
       </c>
       <c r="H1227" s="14">
-        <v>0.733</v>
+        <v>0.603</v>
       </c>
       <c r="I1227" s="15">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="J1227" s="12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="K1227" s="16">
-        <v>-7.3</v>
+        <v>-7.8</v>
       </c>
       <c r="L1227" s="15">
-        <v>-48.7</v>
+        <v>-50.3</v>
       </c>
       <c r="M1227" t="s">
-        <v>1262</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1228" spans="1:13" x14ac:dyDescent="0.25">
@@ -72153,7 +72156,7 @@
         <v>568</v>
       </c>
       <c r="D1228" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1228" t="s">
         <v>452</v>
@@ -72162,25 +72165,25 @@
         <v>4.3</v>
       </c>
       <c r="G1228" s="13">
-        <v>3.966</v>
+        <v>4.045</v>
       </c>
       <c r="H1228" s="14">
-        <v>0.334</v>
+        <v>0.255</v>
       </c>
       <c r="I1228" s="15">
-        <v>8.4</v>
+        <v>6.3</v>
       </c>
       <c r="J1228" s="12">
-        <v>15.833</v>
+        <v>16.567</v>
       </c>
       <c r="K1228" s="16">
-        <v>-11.533</v>
+        <v>-12.267</v>
       </c>
       <c r="L1228" s="15">
-        <v>-72.8</v>
+        <v>-74</v>
       </c>
       <c r="M1228" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.25">
@@ -72194,7 +72197,7 @@
         <v>568</v>
       </c>
       <c r="D1229" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1229" t="s">
         <v>423</v>
@@ -72203,25 +72206,25 @@
         <v>3.7</v>
       </c>
       <c r="G1229" s="13">
-        <v>3.232</v>
+        <v>3.262</v>
       </c>
       <c r="H1229" s="14">
-        <v>0.468</v>
+        <v>0.438</v>
       </c>
       <c r="I1229" s="15">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="J1229" s="12">
-        <v>23.3</v>
+        <v>23.425</v>
       </c>
       <c r="K1229" s="16">
-        <v>-19.6</v>
+        <v>-19.725</v>
       </c>
       <c r="L1229" s="15">
-        <v>-84.1</v>
+        <v>-84.2</v>
       </c>
       <c r="M1229" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.25">
@@ -72235,7 +72238,7 @@
         <v>568</v>
       </c>
       <c r="D1230" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1230" t="s">
         <v>438</v>
@@ -72262,7 +72265,7 @@
         <v>-91.5</v>
       </c>
       <c r="M1230" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.25">
@@ -72276,7 +72279,7 @@
         <v>568</v>
       </c>
       <c r="D1231" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1231" t="s">
         <v>430</v>
@@ -72285,25 +72288,25 @@
         <v>6.1</v>
       </c>
       <c r="G1231" s="13">
-        <v>5.055</v>
+        <v>4.999</v>
       </c>
       <c r="H1231" s="14">
-        <v>1.045</v>
+        <v>1.101</v>
       </c>
       <c r="I1231" s="15">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="J1231" s="12">
-        <v>115.5</v>
+        <v>114.667</v>
       </c>
       <c r="K1231" s="16">
-        <v>-109.4</v>
+        <v>-108.567</v>
       </c>
       <c r